--- a/ETF動態清單.xlsx
+++ b/ETF動態清單.xlsx
@@ -1542,169 +1542,169 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>00715L.TW</t>
+          <t>00409A.TW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>期街口布蘭特正2</t>
+          <t>主動復華全球50</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4.112709034415023</v>
+        <v>0.04529145504918319</v>
       </c>
       <c r="D14" t="n">
-        <v>2.915440428595469</v>
+        <v>0.04059283058808605</v>
       </c>
       <c r="E14" t="n">
-        <v>63.54999923706055</v>
+        <v>10.30000019073486</v>
       </c>
       <c r="F14" t="n">
-        <v>41.48</v>
+        <v>84.43000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>464</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>82.76000000000001</v>
+        <v>100</v>
       </c>
       <c r="I14" t="n">
         <v>2.97</v>
       </c>
       <c r="J14" t="n">
-        <v>12.9073275862069</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>5300092.3</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
+        <v>39429977.1</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>23.38</v>
+        <v>2.97</v>
       </c>
       <c r="O14" t="n">
-        <v>-45.56</v>
+        <v>2.97</v>
       </c>
       <c r="P14" t="n">
-        <v>-22.18</v>
+        <v>5.94</v>
       </c>
       <c r="Q14" t="n">
-        <v>17.84</v>
+        <v>3419.41</v>
       </c>
       <c r="R14" t="n">
-        <v>1.197268605819554</v>
+        <v>0.004698624461097145</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1378.93</v>
+        <v>2.97</v>
       </c>
       <c r="U14" t="n">
-        <v>5989</v>
+        <v>3</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9915356603769351</v>
+        <v>1.047386640705338</v>
       </c>
       <c r="W14" t="n">
-        <v>1.169320661112599</v>
+        <v>1.10062302128131</v>
       </c>
       <c r="X14" t="n">
-        <v>64.09249992370606</v>
+        <v>9.833999967575073</v>
       </c>
       <c r="Y14" t="n">
-        <v>54.34779470722194</v>
+        <v>9.358336134695719</v>
       </c>
       <c r="Z14" t="n">
-        <v>167358922.990799</v>
+        <v>585144040.8356667</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>00409A.TW</t>
+          <t>00715L.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>主動復華全球50</t>
+          <t>期街口布蘭特正2</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.04529145504918319</v>
+        <v>4.112709034415023</v>
       </c>
       <c r="D15" t="n">
-        <v>0.04059283058808605</v>
+        <v>2.915440428595469</v>
       </c>
       <c r="E15" t="n">
-        <v>10.30000019073486</v>
+        <v>63.54999923706055</v>
       </c>
       <c r="F15" t="n">
-        <v>84.43000000000001</v>
+        <v>41.48</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>464</v>
       </c>
       <c r="H15" t="n">
-        <v>100</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="I15" t="n">
         <v>2.97</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>12.9073275862069</v>
       </c>
       <c r="K15" t="n">
-        <v>39429977.1</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
+        <v>5300092.3</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
       <c r="M15" t="n">
         <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>2.97</v>
+        <v>23.38</v>
       </c>
       <c r="O15" t="n">
-        <v>2.97</v>
+        <v>-45.56</v>
       </c>
       <c r="P15" t="n">
-        <v>5.94</v>
+        <v>-22.18</v>
       </c>
       <c r="Q15" t="n">
-        <v>3419.41</v>
+        <v>17.84</v>
       </c>
       <c r="R15" t="n">
-        <v>0.004698624461097145</v>
+        <v>1.197268605819554</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.97</v>
+        <v>1378.93</v>
       </c>
       <c r="U15" t="n">
-        <v>3</v>
+        <v>5989</v>
       </c>
       <c r="V15" t="n">
-        <v>1.047386640705338</v>
+        <v>0.9915356603769351</v>
       </c>
       <c r="W15" t="n">
-        <v>1.10062302128131</v>
+        <v>1.169320661112599</v>
       </c>
       <c r="X15" t="n">
-        <v>9.833999967575073</v>
+        <v>64.09249992370606</v>
       </c>
       <c r="Y15" t="n">
-        <v>9.358336134695719</v>
+        <v>54.34779470722194</v>
       </c>
       <c r="Z15" t="n">
-        <v>585144040.8356667</v>
+        <v>167358922.990799</v>
       </c>
     </row>
     <row r="16">
@@ -2305,7 +2305,7 @@
         <v>78.56</v>
       </c>
       <c r="G23" t="n">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H23" t="n">
         <v>94.68000000000001</v>
@@ -2314,7 +2314,7 @@
         <v>2.06</v>
       </c>
       <c r="J23" t="n">
-        <v>9.933721777130371</v>
+        <v>9.925655976676385</v>
       </c>
       <c r="K23" t="n">
         <v>18078.85</v>
@@ -2333,7 +2333,7 @@
         <v>6.779999999999999</v>
       </c>
       <c r="Q23" t="n">
-        <v>9.460000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="R23" t="n">
         <v>2.891655268617813</v>
@@ -2342,10 +2342,10 @@
         <v>1.685</v>
       </c>
       <c r="T23" t="n">
-        <v>2829.89</v>
+        <v>2827.99</v>
       </c>
       <c r="U23" t="n">
-        <v>13639</v>
+        <v>13618</v>
       </c>
       <c r="V23" t="n">
         <v>1.024556522176362</v>

--- a/ETF動態清單.xlsx
+++ b/ETF動態清單.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z38"/>
+  <dimension ref="A1:Z36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,16 +567,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.2628628763373908</v>
+        <v>0.3169263350635774</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2614181838406879</v>
+        <v>0.2948682760504933</v>
       </c>
       <c r="E2" t="n">
-        <v>17.55999946594238</v>
+        <v>18.36000061035156</v>
       </c>
       <c r="F2" t="n">
-        <v>81.95999999999999</v>
+        <v>86.43000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>34</v>
@@ -591,7 +591,7 @@
         <v>11.67647058823529</v>
       </c>
       <c r="K2" t="n">
-        <v>3562083.7</v>
+        <v>4427547.35</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
@@ -610,7 +610,7 @@
         <v>258.57</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001444692496702871</v>
+        <v>0.02205805901308411</v>
       </c>
       <c r="S2" t="n">
         <v>0.7190000000000001</v>
@@ -622,19 +622,19 @@
         <v>397</v>
       </c>
       <c r="V2" t="n">
-        <v>1.039114698593433</v>
+        <v>1.080762914518722</v>
       </c>
       <c r="W2" t="n">
-        <v>1.08478966057591</v>
+        <v>1.143974637984809</v>
       </c>
       <c r="X2" t="n">
-        <v>16.89900016784668</v>
+        <v>16.98800020217896</v>
       </c>
       <c r="Y2" t="n">
-        <v>16.18746942759379</v>
+        <v>16.0493073890991</v>
       </c>
       <c r="Z2" t="n">
-        <v>95314447.90117264</v>
+        <v>427283004.0444031</v>
       </c>
     </row>
     <row r="3">
@@ -649,16 +649,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9009993043507185</v>
+        <v>0.9680374205572622</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6487979878326244</v>
+        <v>0.692302121387661</v>
       </c>
       <c r="E3" t="n">
-        <v>31.44000053405762</v>
+        <v>32.65000152587891</v>
       </c>
       <c r="F3" t="n">
-        <v>91.52</v>
+        <v>93.28</v>
       </c>
       <c r="G3" t="n">
         <v>42</v>
@@ -673,7 +673,7 @@
         <v>8.761904761904763</v>
       </c>
       <c r="K3" t="n">
-        <v>148033048.3</v>
+        <v>154372794.75</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
@@ -692,7 +692,7 @@
         <v>347.51</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2522013165180941</v>
+        <v>0.2757352991696012</v>
       </c>
       <c r="S3" t="n">
         <v>1.67</v>
@@ -704,19 +704,19 @@
         <v>368</v>
       </c>
       <c r="V3" t="n">
-        <v>1.054644277960013</v>
+        <v>1.088805196735343</v>
       </c>
       <c r="W3" t="n">
-        <v>1.11793315289962</v>
+        <v>1.169119202604759</v>
       </c>
       <c r="X3" t="n">
-        <v>29.81099996566773</v>
+        <v>29.98700008392334</v>
       </c>
       <c r="Y3" t="n">
-        <v>28.12332781482564</v>
+        <v>27.92700817259333</v>
       </c>
       <c r="Z3" t="n">
-        <v>4791106782.984447</v>
+        <v>9102424544.146538</v>
       </c>
     </row>
     <row r="4">
@@ -731,16 +731,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.3402138405421271</v>
+        <v>0.3931220572931799</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2844312495251144</v>
+        <v>0.3184460190512697</v>
       </c>
       <c r="E4" t="n">
-        <v>19.39999961853027</v>
+        <v>20.20999908447266</v>
       </c>
       <c r="F4" t="n">
-        <v>92.98</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>34</v>
@@ -755,7 +755,7 @@
         <v>10.64705882352941</v>
       </c>
       <c r="K4" t="n">
-        <v>31776316.95</v>
+        <v>32754874.45</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
@@ -774,7 +774,7 @@
         <v>286.03</v>
       </c>
       <c r="R4" t="n">
-        <v>0.05578259101701266</v>
+        <v>0.07467603824191027</v>
       </c>
       <c r="S4" t="n">
         <v>0.47</v>
@@ -786,19 +786,19 @@
         <v>362</v>
       </c>
       <c r="V4" t="n">
-        <v>1.060514928451644</v>
+        <v>1.098279985409143</v>
       </c>
       <c r="W4" t="n">
-        <v>1.126356190340834</v>
+        <v>1.185130665611613</v>
       </c>
       <c r="X4" t="n">
-        <v>18.29300003051758</v>
+        <v>18.40149993896484</v>
       </c>
       <c r="Y4" t="n">
-        <v>17.22368091452479</v>
+        <v>17.05297117937864</v>
       </c>
       <c r="Z4" t="n">
-        <v>821925875.4381523</v>
+        <v>1235533221.319466</v>
       </c>
     </row>
     <row r="5">
@@ -813,16 +813,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.2969741353502806</v>
+        <v>0.3436102147926752</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2844312495251144</v>
+        <v>0.3184460190512697</v>
       </c>
       <c r="E5" t="n">
-        <v>17.68000030517578</v>
+        <v>18.34000015258789</v>
       </c>
       <c r="F5" t="n">
-        <v>91.47</v>
+        <v>92.3</v>
       </c>
       <c r="G5" t="n">
         <v>30</v>
@@ -837,7 +837,7 @@
         <v>11.93333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>1948003.7</v>
+        <v>2178015.6</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
@@ -856,7 +856,7 @@
         <v>247.59</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01254288582516616</v>
+        <v>0.02516419574140549</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -868,19 +868,19 @@
         <v>358</v>
       </c>
       <c r="V5" t="n">
-        <v>1.063106964560182</v>
+        <v>1.095644914239844</v>
       </c>
       <c r="W5" t="n">
-        <v>1.138568191163208</v>
+        <v>1.188487554589605</v>
       </c>
       <c r="X5" t="n">
-        <v>16.63049993515015</v>
+        <v>16.73899993896485</v>
       </c>
       <c r="Y5" t="n">
-        <v>15.52827528679962</v>
+        <v>15.43137753673899</v>
       </c>
       <c r="Z5" t="n">
-        <v>55475049.6775589</v>
+        <v>119545953.1146164</v>
       </c>
     </row>
     <row r="6">
@@ -895,16 +895,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.3207861532017542</v>
+        <v>0.3723053259120572</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2975281275154391</v>
+        <v>0.3318698608900639</v>
       </c>
       <c r="E6" t="n">
-        <v>18.69000053405762</v>
+        <v>19.46999931335449</v>
       </c>
       <c r="F6" t="n">
-        <v>87.26000000000001</v>
+        <v>91</v>
       </c>
       <c r="G6" t="n">
         <v>39</v>
@@ -919,7 +919,7 @@
         <v>11.41025641025641</v>
       </c>
       <c r="K6" t="n">
-        <v>58616656.15</v>
+        <v>63741852.75</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
@@ -938,7 +938,7 @@
         <v>213.42</v>
       </c>
       <c r="R6" t="n">
-        <v>0.02325802568631508</v>
+        <v>0.04043546502199336</v>
       </c>
       <c r="S6" t="n">
         <v>0.77</v>
@@ -950,19 +950,19 @@
         <v>445</v>
       </c>
       <c r="V6" t="n">
-        <v>1.057216418212261</v>
+        <v>1.094650394063759</v>
       </c>
       <c r="W6" t="n">
-        <v>1.114993016380879</v>
+        <v>1.172875681825446</v>
       </c>
       <c r="X6" t="n">
-        <v>17.67850008010864</v>
+        <v>17.78650007247925</v>
       </c>
       <c r="Y6" t="n">
-        <v>16.76243730630969</v>
+        <v>16.60022423097023</v>
       </c>
       <c r="Z6" t="n">
-        <v>1676765417.282751</v>
+        <v>3520463915.024334</v>
       </c>
     </row>
     <row r="7">
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.2493215575647785</v>
+        <v>0.298005637594233</v>
       </c>
       <c r="D7" t="n">
-        <v>0.237690146004667</v>
+        <v>0.2705525248042091</v>
       </c>
       <c r="E7" t="n">
-        <v>18.10000038146973</v>
+        <v>18.82999992370605</v>
       </c>
       <c r="F7" t="n">
-        <v>88.20999999999999</v>
+        <v>91.31</v>
       </c>
       <c r="G7" t="n">
         <v>26</v>
@@ -1001,7 +1001,7 @@
         <v>11.46153846153846</v>
       </c>
       <c r="K7" t="n">
-        <v>3600323.05</v>
+        <v>3811117.7</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
@@ -1020,7 +1020,7 @@
         <v>268.56</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01163141156011149</v>
+        <v>0.02745311279002394</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1032,19 +1032,19 @@
         <v>298</v>
       </c>
       <c r="V7" t="n">
-        <v>1.043017275933675</v>
+        <v>1.079392366944967</v>
       </c>
       <c r="W7" t="n">
-        <v>1.098240269913047</v>
+        <v>1.149727861610913</v>
       </c>
       <c r="X7" t="n">
-        <v>17.35350008010864</v>
+        <v>17.44500007629394</v>
       </c>
       <c r="Y7" t="n">
-        <v>16.48091121526876</v>
+        <v>16.37778865106641</v>
       </c>
       <c r="Z7" t="n">
-        <v>54817516.35531616</v>
+        <v>156630782.6953754</v>
       </c>
     </row>
     <row r="8">
@@ -1059,16 +1059,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.389588041086078</v>
+        <v>1.434723459059454</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9892739791403073</v>
+        <v>1.04209788083989</v>
       </c>
       <c r="E8" t="n">
-        <v>40.47999954223633</v>
+        <v>41.29999923706055</v>
       </c>
       <c r="F8" t="n">
-        <v>76.01000000000001</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="G8" t="n">
         <v>67</v>
@@ -1083,7 +1083,7 @@
         <v>10.44776119402985</v>
       </c>
       <c r="K8" t="n">
-        <v>6319387.95</v>
+        <v>7004766.75</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
@@ -1102,7 +1102,7 @@
         <v>151.1</v>
       </c>
       <c r="R8" t="n">
-        <v>0.400314061945771</v>
+        <v>0.392625578219564</v>
       </c>
       <c r="S8" t="n">
         <v>0.78</v>
@@ -1114,19 +1114,19 @@
         <v>700</v>
       </c>
       <c r="V8" t="n">
-        <v>1.046995821079717</v>
+        <v>1.061874068706451</v>
       </c>
       <c r="W8" t="n">
-        <v>1.139938535262427</v>
+        <v>1.15756259006224</v>
       </c>
       <c r="X8" t="n">
-        <v>38.66300010681152</v>
+        <v>38.8935001373291</v>
       </c>
       <c r="Y8" t="n">
-        <v>35.51068613793056</v>
+        <v>35.67841565685008</v>
       </c>
       <c r="Z8" t="n">
-        <v>330407876.2636185</v>
+        <v>847423368.1454544</v>
       </c>
     </row>
     <row r="9">
@@ -1141,16 +1141,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.7485176150417285</v>
+        <v>0.8160432562134525</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6984129938398904</v>
+        <v>0.7432198339885738</v>
       </c>
       <c r="E9" t="n">
-        <v>25.8700008392334</v>
+        <v>26.95999908447266</v>
       </c>
       <c r="F9" t="n">
-        <v>87.66</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>41</v>
@@ -1165,7 +1165,7 @@
         <v>10.17073170731707</v>
       </c>
       <c r="K9" t="n">
-        <v>7350380.5</v>
+        <v>7826566.9</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
@@ -1184,7 +1184,7 @@
         <v>225.65</v>
       </c>
       <c r="R9" t="n">
-        <v>0.05010462120183812</v>
+        <v>0.0728234222248787</v>
       </c>
       <c r="S9" t="n">
         <v>1.814</v>
@@ -1196,19 +1196,19 @@
         <v>417</v>
       </c>
       <c r="V9" t="n">
-        <v>1.040585695434498</v>
+        <v>1.07846467685458</v>
       </c>
       <c r="W9" t="n">
-        <v>1.093264015102766</v>
+        <v>1.145759361542372</v>
       </c>
       <c r="X9" t="n">
-        <v>24.86099987030029</v>
+        <v>24.99849987030029</v>
       </c>
       <c r="Y9" t="n">
-        <v>23.66308639254136</v>
+        <v>23.53024552047323</v>
       </c>
       <c r="Z9" t="n">
-        <v>294582630.8763809</v>
+        <v>456546717.4562531</v>
       </c>
     </row>
     <row r="10">
@@ -1223,16 +1223,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.5970678623501626</v>
+        <v>0.6308668118264726</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5523069492169321</v>
+        <v>0.5932806868251006</v>
       </c>
       <c r="E10" t="n">
-        <v>24.04000091552734</v>
+        <v>24.57999992370605</v>
       </c>
       <c r="F10" t="n">
-        <v>87.06</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>38</v>
@@ -1247,7 +1247,7 @@
         <v>10.3421052631579</v>
       </c>
       <c r="K10" t="n">
-        <v>6067366.45</v>
+        <v>8683611.050000001</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
@@ -1266,7 +1266,7 @@
         <v>230.74</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0447609131332305</v>
+        <v>0.03758612500137204</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1278,19 +1278,19 @@
         <v>393</v>
       </c>
       <c r="V10" t="n">
-        <v>1.03927548408119</v>
+        <v>1.058638580411474</v>
       </c>
       <c r="W10" t="n">
-        <v>1.078965021570558</v>
+        <v>1.108634301413421</v>
       </c>
       <c r="X10" t="n">
-        <v>23.13150005340576</v>
+        <v>23.21850004196167</v>
       </c>
       <c r="Y10" t="n">
-        <v>22.28061191505017</v>
+        <v>22.17142288703183</v>
       </c>
       <c r="Z10" t="n">
-        <v>1344378658.038643</v>
+        <v>1343409351.010187</v>
       </c>
     </row>
     <row r="11">
@@ -1305,16 +1305,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.1090827838523023</v>
+        <v>0.1557338955346266</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0645146786548374</v>
+        <v>0.09231845768151592</v>
       </c>
       <c r="E11" t="n">
-        <v>12.67000007629395</v>
+        <v>13.23999977111816</v>
       </c>
       <c r="F11" t="n">
-        <v>92.44</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="G11" t="n">
         <v>5</v>
@@ -1329,7 +1329,7 @@
         <v>7</v>
       </c>
       <c r="K11" t="n">
-        <v>5738246.1</v>
+        <v>5376133.75</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
@@ -1348,7 +1348,7 @@
         <v>1487.78</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0445681051974649</v>
+        <v>0.06341543785311066</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1360,19 +1360,19 @@
         <v>35</v>
       </c>
       <c r="V11" t="n">
-        <v>1.049275372780728</v>
+        <v>1.090160547047693</v>
       </c>
       <c r="W11" t="n">
-        <v>1.107663318598685</v>
+        <v>1.167415057327739</v>
       </c>
       <c r="X11" t="n">
-        <v>12.07499995231628</v>
+        <v>12.1449999332428</v>
       </c>
       <c r="Y11" t="n">
-        <v>11.43849386682126</v>
+        <v>11.34129604377818</v>
       </c>
       <c r="Z11" t="n">
-        <v>39568650.96826744</v>
+        <v>95198484.6742897</v>
       </c>
     </row>
     <row r="12">
@@ -1387,16 +1387,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.6582467667511382</v>
+        <v>0.7136169574281035</v>
       </c>
       <c r="D12" t="n">
-        <v>0.653849095088989</v>
+        <v>0.6974869649718565</v>
       </c>
       <c r="E12" t="n">
-        <v>23.79000091552734</v>
+        <v>24.67000007629395</v>
       </c>
       <c r="F12" t="n">
-        <v>81.38</v>
+        <v>87.09</v>
       </c>
       <c r="G12" t="n">
         <v>57</v>
@@ -1411,7 +1411,7 @@
         <v>9.754385964912281</v>
       </c>
       <c r="K12" t="n">
-        <v>16208444.6</v>
+        <v>17067203.45</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
@@ -1430,7 +1430,7 @@
         <v>163.14</v>
       </c>
       <c r="R12" t="n">
-        <v>0.004397671662149216</v>
+        <v>0.01612999245624702</v>
       </c>
       <c r="S12" t="n">
         <v>2.227</v>
@@ -1442,19 +1442,19 @@
         <v>556</v>
       </c>
       <c r="V12" t="n">
-        <v>1.044704065837936</v>
+        <v>1.077998695126831</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08701278104474</v>
+        <v>1.13740707795105</v>
       </c>
       <c r="X12" t="n">
-        <v>22.77199993133545</v>
+        <v>22.88499994277954</v>
       </c>
       <c r="Y12" t="n">
-        <v>21.88566807159572</v>
+        <v>21.68968397905086</v>
       </c>
       <c r="Z12" t="n">
-        <v>985985961.2043915</v>
+        <v>930825327.0886517</v>
       </c>
     </row>
     <row r="13">
@@ -1469,16 +1469,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.07897241326617133</v>
+        <v>0.1268482110201226</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0672881308756661</v>
+        <v>0.09579521576764871</v>
       </c>
       <c r="E13" t="n">
-        <v>10.23999977111816</v>
+        <v>10.71000003814697</v>
       </c>
       <c r="F13" t="n">
-        <v>89.48999999999999</v>
+        <v>91.67</v>
       </c>
       <c r="G13" t="n">
         <v>6</v>
@@ -1493,7 +1493,7 @@
         <v>7</v>
       </c>
       <c r="K13" t="n">
-        <v>41503528.85</v>
+        <v>43719699.85</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
@@ -1512,7 +1512,7 @@
         <v>1195.63</v>
       </c>
       <c r="R13" t="n">
-        <v>0.01168428239050523</v>
+        <v>0.03105299525247385</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1524,19 +1524,19 @@
         <v>42</v>
       </c>
       <c r="V13" t="n">
-        <v>1.047570303955613</v>
+        <v>1.08924485196882</v>
       </c>
       <c r="W13" t="n">
-        <v>1.113000810724853</v>
+        <v>1.172053322028615</v>
       </c>
       <c r="X13" t="n">
-        <v>9.775000047683715</v>
+        <v>9.83250002861023</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.200352481728434</v>
+        <v>9.137809549150781</v>
       </c>
       <c r="Z13" t="n">
-        <v>624631087.4784069</v>
+        <v>839591389.190464</v>
       </c>
     </row>
     <row r="14">
@@ -1551,16 +1551,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.2454915807082756</v>
+        <v>0.2746462301631303</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2204523037900423</v>
+        <v>0.2528875044931336</v>
       </c>
       <c r="E14" t="n">
-        <v>16.57999992370605</v>
+        <v>16.98999977111816</v>
       </c>
       <c r="F14" t="n">
-        <v>75.13</v>
+        <v>81.17</v>
       </c>
       <c r="G14" t="n">
         <v>30</v>
@@ -1575,7 +1575,7 @@
         <v>10.53333333333333</v>
       </c>
       <c r="K14" t="n">
-        <v>90651527</v>
+        <v>92827564.40000001</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
@@ -1594,7 +1594,7 @@
         <v>195.69</v>
       </c>
       <c r="R14" t="n">
-        <v>0.02503927691823327</v>
+        <v>0.0217587256699967</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -1606,19 +1606,19 @@
         <v>316</v>
       </c>
       <c r="V14" t="n">
-        <v>1.024057305491415</v>
+        <v>1.044959693432451</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06506622356434</v>
+        <v>1.089013194720787</v>
       </c>
       <c r="X14" t="n">
-        <v>16.19050011634827</v>
+        <v>16.25900011062622</v>
       </c>
       <c r="Y14" t="n">
-        <v>15.5671070557656</v>
+        <v>15.60127999686381</v>
       </c>
       <c r="Z14" t="n">
-        <v>1687700492.333937</v>
+        <v>1957170991.94385</v>
       </c>
     </row>
     <row r="15">
@@ -1633,16 +1633,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.7508327668668466</v>
+        <v>0.7966588977497384</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7409552890844509</v>
+        <v>0.7868805504294092</v>
       </c>
       <c r="E15" t="n">
-        <v>24.10000038146973</v>
+        <v>24.81999969482422</v>
       </c>
       <c r="F15" t="n">
-        <v>72.86</v>
+        <v>81.12</v>
       </c>
       <c r="G15" t="n">
         <v>67</v>
@@ -1657,7 +1657,7 @@
         <v>8.880597014925373</v>
       </c>
       <c r="K15" t="n">
-        <v>1086571.35</v>
+        <v>1226847.05</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
@@ -1676,7 +1676,7 @@
         <v>124.83</v>
       </c>
       <c r="R15" t="n">
-        <v>0.009877477782395783</v>
+        <v>0.009778347320329228</v>
       </c>
       <c r="S15" t="n">
         <v>2.786</v>
@@ -1688,19 +1688,19 @@
         <v>595</v>
       </c>
       <c r="V15" t="n">
-        <v>1.027981582858455</v>
+        <v>1.053793551648129</v>
       </c>
       <c r="W15" t="n">
-        <v>1.075483759533887</v>
+        <v>1.106837618296197</v>
       </c>
       <c r="X15" t="n">
-        <v>23.44400014877319</v>
+        <v>23.55300016403198</v>
       </c>
       <c r="Y15" t="n">
-        <v>22.4085209728454</v>
+        <v>22.42424659638033</v>
       </c>
       <c r="Z15" t="n">
-        <v>18260690.78904152</v>
+        <v>92022084.82853699</v>
       </c>
     </row>
     <row r="16">
@@ -1715,16 +1715,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.1681447377416561</v>
+        <v>0.2203335047147861</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1373581581073724</v>
+        <v>0.1677135561688152</v>
       </c>
       <c r="E16" t="n">
-        <v>15.77999973297119</v>
+        <v>16.52000045776367</v>
       </c>
       <c r="F16" t="n">
-        <v>87.28</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="G16" t="n">
         <v>18</v>
@@ -1739,7 +1739,7 @@
         <v>13.77777777777778</v>
       </c>
       <c r="K16" t="n">
-        <v>31098159.2</v>
+        <v>31616493.75</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
@@ -1758,7 +1758,7 @@
         <v>122.81</v>
       </c>
       <c r="R16" t="n">
-        <v>0.03078657963428366</v>
+        <v>0.05261994854597085</v>
       </c>
       <c r="S16" t="n">
         <v>0.36</v>
@@ -1770,19 +1770,19 @@
         <v>248</v>
       </c>
       <c r="V16" t="n">
-        <v>1.042444236733672</v>
+        <v>1.085449609751579</v>
       </c>
       <c r="W16" t="n">
-        <v>1.100362002283843</v>
+        <v>1.160838090231799</v>
       </c>
       <c r="X16" t="n">
-        <v>15.13750009536743</v>
+        <v>15.21950011253357</v>
       </c>
       <c r="Y16" t="n">
-        <v>14.34073486745199</v>
+        <v>14.23109785660541</v>
       </c>
       <c r="Z16" t="n">
-        <v>393220582.5059299</v>
+        <v>816211476.5769463</v>
       </c>
     </row>
     <row r="17">
@@ -1797,16 +1797,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2.755814883261024</v>
+        <v>2.812583607435554</v>
       </c>
       <c r="D17" t="n">
-        <v>2.504715147186296</v>
+        <v>2.596870790978858</v>
       </c>
       <c r="E17" t="n">
-        <v>91.25</v>
+        <v>92.90000152587891</v>
       </c>
       <c r="F17" t="n">
-        <v>94.26000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="G17" t="n">
         <v>489</v>
@@ -1821,7 +1821,7 @@
         <v>12.34560327198364</v>
       </c>
       <c r="K17" t="n">
-        <v>6769609.3</v>
+        <v>6935280.25</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
@@ -1840,7 +1840,7 @@
         <v>19.93</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2510997360747282</v>
+        <v>0.2157128164566959</v>
       </c>
       <c r="S17" t="n">
         <v>17.71</v>
@@ -1852,19 +1852,19 @@
         <v>6037</v>
       </c>
       <c r="V17" t="n">
-        <v>1.084663163035389</v>
+        <v>1.095486592690261</v>
       </c>
       <c r="W17" t="n">
-        <v>1.191869942456173</v>
+        <v>1.21190296230218</v>
       </c>
       <c r="X17" t="n">
-        <v>84.12749977111817</v>
+        <v>84.80249977111816</v>
       </c>
       <c r="Y17" t="n">
-        <v>76.56036682320769</v>
+        <v>76.65630369398743</v>
       </c>
       <c r="Z17" t="n">
-        <v>590803873.75</v>
+        <v>780375341.3176346</v>
       </c>
     </row>
     <row r="18">
@@ -1879,16 +1879,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.58716525949762</v>
+        <v>17.45207912237185</v>
       </c>
       <c r="D18" t="n">
-        <v>3.735447421253986</v>
+        <v>3.858061559756839</v>
       </c>
       <c r="E18" t="n">
-        <v>39.58000183105469</v>
+        <v>41.54000091552734</v>
       </c>
       <c r="F18" t="n">
-        <v>88.78</v>
+        <v>90.38</v>
       </c>
       <c r="G18" t="n">
         <v>618</v>
@@ -1903,7 +1903,7 @@
         <v>12.48705501618123</v>
       </c>
       <c r="K18" t="n">
-        <v>152548859.15</v>
+        <v>159482066.9</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
@@ -1922,7 +1922,7 @@
         <v>16.33</v>
       </c>
       <c r="R18" t="n">
-        <v>12.85171783824363</v>
+        <v>13.59401756261501</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -1934,19 +1934,19 @@
         <v>7717</v>
       </c>
       <c r="V18" t="n">
-        <v>1.056227184240037</v>
+        <v>1.099538116649976</v>
       </c>
       <c r="W18" t="n">
-        <v>1.143069137703345</v>
+        <v>1.200996893898137</v>
       </c>
       <c r="X18" t="n">
-        <v>37.47300052642822</v>
+        <v>37.77950057983399</v>
       </c>
       <c r="Y18" t="n">
-        <v>34.62607862073755</v>
+        <v>34.5879336795775</v>
       </c>
       <c r="Z18" t="n">
-        <v>3915167932.103958</v>
+        <v>11483532697.97311</v>
       </c>
     </row>
     <row r="19">
@@ -1961,16 +1961,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.985559925335459</v>
+        <v>2.042329286411374</v>
       </c>
       <c r="D19" t="n">
-        <v>1.848916664945249</v>
+        <v>1.924449686178473</v>
       </c>
       <c r="E19" t="n">
-        <v>44.04999923706055</v>
+        <v>44.9900016784668</v>
       </c>
       <c r="F19" t="n">
-        <v>85.11</v>
+        <v>88.84999999999999</v>
       </c>
       <c r="G19" t="n">
         <v>231</v>
@@ -1985,7 +1985,7 @@
         <v>10.48917748917749</v>
       </c>
       <c r="K19" t="n">
-        <v>1072370.7</v>
+        <v>1225424</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
@@ -2004,7 +2004,7 @@
         <v>40.54</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1366432603902106</v>
+        <v>0.1178796002329014</v>
       </c>
       <c r="S19" t="n">
         <v>4.850000000000001</v>
@@ -2016,921 +2016,921 @@
         <v>2423</v>
       </c>
       <c r="V19" t="n">
-        <v>1.047300904281113</v>
+        <v>1.063354611950043</v>
       </c>
       <c r="W19" t="n">
-        <v>1.113987349424677</v>
+        <v>1.134107209346856</v>
       </c>
       <c r="X19" t="n">
-        <v>42.0604995727539</v>
+        <v>42.30949974060059</v>
       </c>
       <c r="Y19" t="n">
-        <v>39.5426386662383</v>
+        <v>39.66997238680548</v>
       </c>
       <c r="Z19" t="n">
-        <v>179406792.842701</v>
+        <v>175872215.1613617</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>00409A.TW</t>
+          <t>00913.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>主動復華全球50</t>
+          <t>兆豐台灣晶圓製造</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.04367390308314101</v>
+        <v>1.975194484945144</v>
       </c>
       <c r="D20" t="n">
-        <v>0.03825432359488512</v>
+        <v>1.826242026597972</v>
       </c>
       <c r="E20" t="n">
-        <v>10.30000019073486</v>
+        <v>54.54999923706055</v>
       </c>
       <c r="F20" t="n">
-        <v>89.58</v>
+        <v>83.34</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>263</v>
       </c>
       <c r="H20" t="n">
-        <v>100</v>
+        <v>96.95999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>3.68</v>
+        <v>3.53</v>
       </c>
       <c r="J20" t="n">
-        <v>4</v>
+        <v>12.54372623574145</v>
       </c>
       <c r="K20" t="n">
-        <v>35380228.6</v>
+        <v>1499524.55</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
         <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>3.68</v>
+        <v>13.5</v>
       </c>
       <c r="O20" t="n">
-        <v>3.68</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>7.36</v>
+        <v>4.039999999999999</v>
       </c>
       <c r="Q20" t="n">
-        <v>2605</v>
+        <v>29.41</v>
       </c>
       <c r="R20" t="n">
-        <v>0.005419579488255888</v>
+        <v>0.1489524583471722</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>6.699999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>3.68</v>
+        <v>928.22</v>
       </c>
       <c r="U20" t="n">
-        <v>4</v>
+        <v>3299</v>
       </c>
       <c r="V20" t="n">
-        <v>1.044201156191854</v>
+        <v>1.074368760912484</v>
       </c>
       <c r="W20" t="n">
-        <v>1.101409196594619</v>
+        <v>1.173112197842067</v>
       </c>
       <c r="X20" t="n">
-        <v>9.86399998664856</v>
+        <v>50.77399978637695</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.351656244183195</v>
+        <v>46.50024041809891</v>
       </c>
       <c r="Z20" t="n">
-        <v>289491795.0607939</v>
+        <v>165191689.7896194</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>00913.TW</t>
+          <t>009809.TW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>兆豐台灣晶圓製造</t>
+          <t>富邦淨零ESG50</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.949734619779547</v>
+        <v>0.4517333026553574</v>
       </c>
       <c r="D21" t="n">
-        <v>1.75321956551864</v>
+        <v>0.4397411916563148</v>
       </c>
       <c r="E21" t="n">
-        <v>54</v>
+        <v>19.01000022888184</v>
       </c>
       <c r="F21" t="n">
-        <v>84.22</v>
+        <v>77.53</v>
       </c>
       <c r="G21" t="n">
-        <v>263</v>
+        <v>34</v>
       </c>
       <c r="H21" t="n">
-        <v>96.95999999999999</v>
+        <v>97.06</v>
       </c>
       <c r="I21" t="n">
-        <v>3.53</v>
+        <v>3.44</v>
       </c>
       <c r="J21" t="n">
-        <v>12.54372623574145</v>
+        <v>8.529411764705882</v>
       </c>
       <c r="K21" t="n">
-        <v>1431722.45</v>
+        <v>251013.35</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
         <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>13.5</v>
+        <v>7.76</v>
       </c>
       <c r="O21" t="n">
-        <v>-9.460000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="P21" t="n">
-        <v>4.039999999999999</v>
+        <v>7.64</v>
       </c>
       <c r="Q21" t="n">
-        <v>29.41</v>
+        <v>164.86</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1965150542609067</v>
+        <v>0.01199211099904263</v>
       </c>
       <c r="S21" t="n">
-        <v>6.699999999999999</v>
+        <v>0.315</v>
       </c>
       <c r="T21" t="n">
-        <v>928.22</v>
+        <v>116.82</v>
       </c>
       <c r="U21" t="n">
-        <v>3299</v>
+        <v>290</v>
       </c>
       <c r="V21" t="n">
-        <v>1.07180072689243</v>
+        <v>1.034388946523505</v>
       </c>
       <c r="W21" t="n">
-        <v>1.170615319629845</v>
+        <v>1.069181875035618</v>
       </c>
       <c r="X21" t="n">
-        <v>50.38249988555908</v>
+        <v>18.37800016403198</v>
       </c>
       <c r="Y21" t="n">
-        <v>46.12958594893078</v>
+        <v>17.77994995308777</v>
       </c>
       <c r="Z21" t="n">
-        <v>117755694</v>
+        <v>1330053.676013947</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>009809.TW</t>
+          <t>00685L.TW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>富邦淨零ESG50</t>
+          <t>群益臺灣加權正2</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.4294711162418798</v>
+        <v>12.04304935075706</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4026786329340311</v>
+        <v>3.166605229921184</v>
       </c>
       <c r="E22" t="n">
-        <v>18.69000053405762</v>
+        <v>13.76000022888184</v>
       </c>
       <c r="F22" t="n">
-        <v>75.12</v>
+        <v>89.84999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>34</v>
+        <v>526</v>
       </c>
       <c r="H22" t="n">
-        <v>97.06</v>
+        <v>87.45</v>
       </c>
       <c r="I22" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="J22" t="n">
-        <v>8.529411764705882</v>
+        <v>12.24524714828897</v>
       </c>
       <c r="K22" t="n">
-        <v>280765.05</v>
+        <v>202281081.65</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
         <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>7.76</v>
+        <v>15.89</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.12</v>
+        <v>-18.5</v>
       </c>
       <c r="P22" t="n">
-        <v>7.64</v>
+        <v>-2.609999999999999</v>
       </c>
       <c r="Q22" t="n">
-        <v>164.86</v>
+        <v>17.94</v>
       </c>
       <c r="R22" t="n">
-        <v>0.02679248330784878</v>
+        <v>8.87644412083587</v>
       </c>
       <c r="S22" t="n">
-        <v>0.315</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>116.82</v>
+        <v>1738.26</v>
       </c>
       <c r="U22" t="n">
-        <v>290</v>
+        <v>6441</v>
       </c>
       <c r="V22" t="n">
-        <v>1.020558626880216</v>
+        <v>1.102475769367826</v>
       </c>
       <c r="W22" t="n">
-        <v>1.054513542835625</v>
+        <v>1.208821734564203</v>
       </c>
       <c r="X22" t="n">
-        <v>18.31350011825561</v>
+        <v>12.4810001373291</v>
       </c>
       <c r="Y22" t="n">
-        <v>17.72381271064527</v>
+        <v>11.38298546050093</v>
       </c>
       <c r="Z22" t="n">
-        <v>1588650.045394897</v>
+        <v>3674961170.248768</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>00685L.TW</t>
+          <t>00715L.TW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>群益臺灣加權正2</t>
+          <t>期街口布蘭特正2</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>11.44134510621718</v>
+        <v>4.619301116535601</v>
       </c>
       <c r="D23" t="n">
-        <v>3.06061636930392</v>
+        <v>3.013094419387573</v>
       </c>
       <c r="E23" t="n">
-        <v>13.11999988555908</v>
+        <v>69.90000152587891</v>
       </c>
       <c r="F23" t="n">
-        <v>88.16</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>526</v>
+        <v>429</v>
       </c>
       <c r="H23" t="n">
-        <v>87.45</v>
+        <v>78.55</v>
       </c>
       <c r="I23" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="J23" t="n">
-        <v>12.24524714828897</v>
+        <v>17.20745920745921</v>
       </c>
       <c r="K23" t="n">
-        <v>197882021.8</v>
+        <v>4906926.3</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
         <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>15.89</v>
+        <v>32.14</v>
       </c>
       <c r="O23" t="n">
-        <v>-18.5</v>
+        <v>-45.45</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.609999999999999</v>
+        <v>-13.31</v>
       </c>
       <c r="Q23" t="n">
-        <v>17.94</v>
+        <v>14.29</v>
       </c>
       <c r="R23" t="n">
-        <v>8.380728736913259</v>
+        <v>1.606206697148028</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>1738.26</v>
+        <v>1389.98</v>
       </c>
       <c r="U23" t="n">
-        <v>6441</v>
+        <v>7382</v>
       </c>
       <c r="V23" t="n">
-        <v>1.059987863006417</v>
+        <v>1.067623834207527</v>
       </c>
       <c r="W23" t="n">
-        <v>1.151147921898978</v>
+        <v>1.236494703294306</v>
       </c>
       <c r="X23" t="n">
-        <v>12.37750010490418</v>
+        <v>65.47250003814698</v>
       </c>
       <c r="Y23" t="n">
-        <v>11.39731882929157</v>
+        <v>56.53077311180488</v>
       </c>
       <c r="Z23" t="n">
-        <v>1744077769.747053</v>
+        <v>138619112.4259796</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>00715L.TW</t>
+          <t>00675L.TW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>期街口布蘭特正2</t>
+          <t>富邦臺灣加權正2</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4.689793549877404</v>
+        <v>12.76787946198546</v>
       </c>
       <c r="D24" t="n">
-        <v>2.910802057183035</v>
+        <v>3.301201567177383</v>
       </c>
       <c r="E24" t="n">
-        <v>70.75</v>
+        <v>364.4500122070312</v>
       </c>
       <c r="F24" t="n">
-        <v>55.61</v>
+        <v>90.06999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>429</v>
+        <v>555</v>
       </c>
       <c r="H24" t="n">
-        <v>78.55</v>
+        <v>86.31</v>
       </c>
       <c r="I24" t="n">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
       <c r="J24" t="n">
-        <v>17.20745920745921</v>
+        <v>12.35135135135135</v>
       </c>
       <c r="K24" t="n">
-        <v>5008221</v>
+        <v>967524.15</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="n">
         <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>32.14</v>
+        <v>15.7</v>
       </c>
       <c r="O24" t="n">
-        <v>-45.45</v>
+        <v>-24.73</v>
       </c>
       <c r="P24" t="n">
-        <v>-13.31</v>
+        <v>-9.030000000000001</v>
       </c>
       <c r="Q24" t="n">
-        <v>14.29</v>
+        <v>16.91</v>
       </c>
       <c r="R24" t="n">
-        <v>1.778991492694369</v>
+        <v>9.466677894808077</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>1389.98</v>
+        <v>1779.77</v>
       </c>
       <c r="U24" t="n">
-        <v>7382</v>
+        <v>6855</v>
       </c>
       <c r="V24" t="n">
-        <v>1.092158074765746</v>
+        <v>1.1018396983832</v>
       </c>
       <c r="W24" t="n">
-        <v>1.281819225390067</v>
+        <v>1.207452796319666</v>
       </c>
       <c r="X24" t="n">
-        <v>64.77999992370606</v>
+        <v>330.7650039672852</v>
       </c>
       <c r="Y24" t="n">
-        <v>55.19499052486927</v>
+        <v>301.8337555868687</v>
       </c>
       <c r="Z24" t="n">
-        <v>530783904.5</v>
+        <v>766780229.7828369</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>00675L.TW</t>
+          <t>00935.TW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>富邦臺灣加權正2</t>
+          <t>野村臺灣新科技50</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>12.13255197548924</v>
+        <v>1.749162911191024</v>
       </c>
       <c r="D25" t="n">
-        <v>3.191972054560829</v>
+        <v>1.311843173966012</v>
       </c>
       <c r="E25" t="n">
-        <v>347.5</v>
+        <v>63.54999923706055</v>
       </c>
       <c r="F25" t="n">
-        <v>88.56</v>
+        <v>87.13</v>
       </c>
       <c r="G25" t="n">
-        <v>555</v>
+        <v>137</v>
       </c>
       <c r="H25" t="n">
-        <v>86.31</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>3.21</v>
+        <v>3.14</v>
       </c>
       <c r="J25" t="n">
-        <v>12.35135135135135</v>
+        <v>12.38686131386861</v>
       </c>
       <c r="K25" t="n">
-        <v>915885.45</v>
+        <v>11328333.95</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
         <v>2</v>
       </c>
       <c r="N25" t="n">
-        <v>15.7</v>
+        <v>14.6</v>
       </c>
       <c r="O25" t="n">
-        <v>-24.73</v>
+        <v>-8.99</v>
       </c>
       <c r="P25" t="n">
-        <v>-9.030000000000001</v>
+        <v>5.609999999999999</v>
       </c>
       <c r="Q25" t="n">
-        <v>16.91</v>
+        <v>43.19</v>
       </c>
       <c r="R25" t="n">
-        <v>8.94057992092841</v>
+        <v>0.4373197372250113</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="T25" t="n">
-        <v>1779.77</v>
+        <v>430.76</v>
       </c>
       <c r="U25" t="n">
-        <v>6855</v>
+        <v>1697</v>
       </c>
       <c r="V25" t="n">
-        <v>1.059313950003287</v>
+        <v>1.062176151019624</v>
       </c>
       <c r="W25" t="n">
-        <v>1.149814946015057</v>
+        <v>1.131735048794595</v>
       </c>
       <c r="X25" t="n">
-        <v>328.0425033569336</v>
+        <v>59.83000011444092</v>
       </c>
       <c r="Y25" t="n">
-        <v>302.2225456403568</v>
+        <v>56.15271816910441</v>
       </c>
       <c r="Z25" t="n">
-        <v>158207715</v>
+        <v>774259318.5547523</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>00935.TW</t>
+          <t>00894.TW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>野村臺灣新科技50</t>
+          <t>中信小資高價30</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.686512093714594</v>
+        <v>2.37325183336789</v>
       </c>
       <c r="D26" t="n">
-        <v>1.252018462617569</v>
+        <v>1.982954182806191</v>
       </c>
       <c r="E26" t="n">
-        <v>61.95000076293945</v>
+        <v>52.75</v>
       </c>
       <c r="F26" t="n">
-        <v>82.39</v>
+        <v>89.72</v>
       </c>
       <c r="G26" t="n">
-        <v>137</v>
+        <v>243</v>
       </c>
       <c r="H26" t="n">
-        <v>83.20999999999999</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="J26" t="n">
-        <v>12.38686131386861</v>
+        <v>15.33333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>11060920.25</v>
+        <v>1112408.2</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="n">
         <v>2</v>
       </c>
       <c r="N26" t="n">
-        <v>14.6</v>
+        <v>15.7</v>
       </c>
       <c r="O26" t="n">
-        <v>-8.99</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>5.609999999999999</v>
+        <v>7.319999999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>43.19</v>
+        <v>22.72</v>
       </c>
       <c r="R26" t="n">
-        <v>0.4344936310970255</v>
+        <v>0.3902976505617</v>
       </c>
       <c r="S26" t="n">
-        <v>4.98</v>
+        <v>7.549999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>430.76</v>
+        <v>708.49</v>
       </c>
       <c r="U26" t="n">
-        <v>1697</v>
+        <v>3726</v>
       </c>
       <c r="V26" t="n">
-        <v>1.040739194698601</v>
+        <v>1.084732513902628</v>
       </c>
       <c r="W26" t="n">
-        <v>1.103657401765217</v>
+        <v>1.163876439311488</v>
       </c>
       <c r="X26" t="n">
-        <v>59.52500019073486</v>
+        <v>48.62950019836425</v>
       </c>
       <c r="Y26" t="n">
-        <v>56.13155012040431</v>
+        <v>45.32268049966302</v>
       </c>
       <c r="Z26" t="n">
-        <v>558348108.726284</v>
+        <v>99337903.25</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>00894.TW</t>
+          <t>00901.TW</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>中信小資高價30</t>
+          <t>永豐智能車供應鏈</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2.248711117535538</v>
+        <v>2.066175265086512</v>
       </c>
       <c r="D27" t="n">
-        <v>1.905953115553319</v>
+        <v>1.943112320989987</v>
       </c>
       <c r="E27" t="n">
-        <v>50.54999923706055</v>
+        <v>50.20000076293945</v>
       </c>
       <c r="F27" t="n">
-        <v>85.73</v>
+        <v>85.55</v>
       </c>
       <c r="G27" t="n">
-        <v>243</v>
+        <v>269</v>
       </c>
       <c r="H27" t="n">
-        <v>83.54000000000001</v>
+        <v>90.33</v>
       </c>
       <c r="I27" t="n">
-        <v>2.92</v>
+        <v>2.79</v>
       </c>
       <c r="J27" t="n">
-        <v>15.33333333333333</v>
+        <v>13.22304832713755</v>
       </c>
       <c r="K27" t="n">
-        <v>1053602.6</v>
+        <v>294600.05</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="n">
         <v>2</v>
       </c>
       <c r="N27" t="n">
-        <v>15.7</v>
+        <v>15.18</v>
       </c>
       <c r="O27" t="n">
-        <v>-8.380000000000001</v>
+        <v>-7.07</v>
       </c>
       <c r="P27" t="n">
-        <v>7.319999999999999</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="Q27" t="n">
-        <v>22.72</v>
+        <v>24.56</v>
       </c>
       <c r="R27" t="n">
-        <v>0.3427580019822192</v>
+        <v>0.123062944096525</v>
       </c>
       <c r="S27" t="n">
-        <v>7.549999999999999</v>
+        <v>4.671</v>
       </c>
       <c r="T27" t="n">
-        <v>708.49</v>
+        <v>750.16</v>
       </c>
       <c r="U27" t="n">
-        <v>3726</v>
+        <v>3557</v>
       </c>
       <c r="V27" t="n">
-        <v>1.046107344674515</v>
+        <v>1.062107931093273</v>
       </c>
       <c r="W27" t="n">
-        <v>1.111080736646388</v>
+        <v>1.124481782888495</v>
       </c>
       <c r="X27" t="n">
-        <v>48.32200012207031</v>
+        <v>47.26450042724609</v>
       </c>
       <c r="Y27" t="n">
-        <v>45.49624304498097</v>
+        <v>44.6427870391897</v>
       </c>
       <c r="Z27" t="n">
-        <v>36300510.50212479</v>
+        <v>40700253.01856232</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>00901.TW</t>
+          <t>00881.TW</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>永豐智能車供應鏈</t>
+          <t>國泰台灣科技龍頭</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1.984551142877283</v>
+        <v>2.238330076865061</v>
       </c>
       <c r="D28" t="n">
-        <v>1.867107138786814</v>
+        <v>2.062872865056776</v>
       </c>
       <c r="E28" t="n">
-        <v>48.7400016784668</v>
+        <v>54.45000076293945</v>
       </c>
       <c r="F28" t="n">
-        <v>82.43000000000001</v>
+        <v>84.73</v>
       </c>
       <c r="G28" t="n">
-        <v>269</v>
+        <v>323</v>
       </c>
       <c r="H28" t="n">
-        <v>90.33</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>2.79</v>
+        <v>2.56</v>
       </c>
       <c r="J28" t="n">
-        <v>13.22304832713755</v>
+        <v>13.88854489164087</v>
       </c>
       <c r="K28" t="n">
-        <v>268564.8</v>
+        <v>15823618.8</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="n">
         <v>2</v>
       </c>
       <c r="N28" t="n">
-        <v>15.18</v>
+        <v>10.9</v>
       </c>
       <c r="O28" t="n">
-        <v>-7.07</v>
+        <v>-7.15</v>
       </c>
       <c r="P28" t="n">
-        <v>8.109999999999999</v>
+        <v>3.75</v>
       </c>
       <c r="Q28" t="n">
-        <v>24.56</v>
+        <v>19.85</v>
       </c>
       <c r="R28" t="n">
-        <v>0.1174440040904687</v>
+        <v>0.1754572118082849</v>
       </c>
       <c r="S28" t="n">
-        <v>4.671</v>
+        <v>12.5</v>
       </c>
       <c r="T28" t="n">
-        <v>750.16</v>
+        <v>825.49</v>
       </c>
       <c r="U28" t="n">
-        <v>3557</v>
+        <v>4486</v>
       </c>
       <c r="V28" t="n">
-        <v>1.036370815662846</v>
+        <v>1.061279398503448</v>
       </c>
       <c r="W28" t="n">
-        <v>1.091032355357989</v>
+        <v>1.119231050758579</v>
       </c>
       <c r="X28" t="n">
-        <v>47.02950038909912</v>
+        <v>51.30599994659424</v>
       </c>
       <c r="Y28" t="n">
-        <v>44.67328712948594</v>
+        <v>48.64947298061018</v>
       </c>
       <c r="Z28" t="n">
-        <v>12185195.37962341</v>
+        <v>1855149314.293877</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>00881.TW</t>
+          <t>0057.TW</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>國泰台灣科技龍頭</t>
+          <t>富邦摩台</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2.154654515851852</v>
+        <v>6.309587311255153</v>
       </c>
       <c r="D29" t="n">
-        <v>1.983887161760339</v>
+        <v>3.32673903121997</v>
       </c>
       <c r="E29" t="n">
-        <v>52.75</v>
+        <v>343.6499938964844</v>
       </c>
       <c r="F29" t="n">
-        <v>80.13</v>
+        <v>86.81999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>323</v>
+        <v>1250</v>
       </c>
       <c r="H29" t="n">
-        <v>90.70999999999999</v>
+        <v>93.52</v>
       </c>
       <c r="I29" t="n">
-        <v>2.56</v>
+        <v>2.51</v>
       </c>
       <c r="J29" t="n">
-        <v>13.88854489164087</v>
+        <v>13.0928</v>
       </c>
       <c r="K29" t="n">
-        <v>14832794.95</v>
+        <v>19465.7</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="n">
         <v>2</v>
       </c>
       <c r="N29" t="n">
-        <v>10.9</v>
+        <v>14.45</v>
       </c>
       <c r="O29" t="n">
-        <v>-7.15</v>
+        <v>-6.48</v>
       </c>
       <c r="P29" t="n">
-        <v>3.75</v>
+        <v>7.969999999999999</v>
       </c>
       <c r="Q29" t="n">
-        <v>19.85</v>
+        <v>8.06</v>
       </c>
       <c r="R29" t="n">
-        <v>0.1707673540915136</v>
+        <v>2.982848280035182</v>
       </c>
       <c r="S29" t="n">
-        <v>12.5</v>
+        <v>1.685</v>
       </c>
       <c r="T29" t="n">
-        <v>825.49</v>
+        <v>3133.95</v>
       </c>
       <c r="U29" t="n">
-        <v>4486</v>
+        <v>16366</v>
       </c>
       <c r="V29" t="n">
-        <v>1.03282524467595</v>
+        <v>1.046373523595314</v>
       </c>
       <c r="W29" t="n">
-        <v>1.081662677182352</v>
+        <v>1.091069629905982</v>
       </c>
       <c r="X29" t="n">
-        <v>51.0734998703003</v>
+        <v>328.4200012207031</v>
       </c>
       <c r="Y29" t="n">
-        <v>48.7675142285668</v>
+        <v>314.9661437520691</v>
       </c>
       <c r="Z29" t="n">
-        <v>631833539.25</v>
+        <v>17133014.09570312</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>0057.TW</t>
+          <t>0050.TW</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>富邦摩台</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6.146676263355002</v>
+        <v>3.330666428410618</v>
       </c>
       <c r="D30" t="n">
-        <v>3.218288117728774</v>
+        <v>3.330666428410618</v>
       </c>
       <c r="E30" t="n">
-        <v>335.8999938964844</v>
+        <v>115.9499969482422</v>
       </c>
       <c r="F30" t="n">
-        <v>83.48999999999999</v>
+        <v>85.17</v>
       </c>
       <c r="G30" t="n">
-        <v>1250</v>
+        <v>1229</v>
       </c>
       <c r="H30" t="n">
-        <v>93.52</v>
+        <v>90.89</v>
       </c>
       <c r="I30" t="n">
-        <v>2.51</v>
+        <v>2.19</v>
       </c>
       <c r="J30" t="n">
-        <v>13.0928</v>
+        <v>13.92758340113914</v>
       </c>
       <c r="K30" t="n">
-        <v>17228.35</v>
+        <v>71075200.34999999</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="n">
         <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>14.45</v>
+        <v>15.64</v>
       </c>
       <c r="O30" t="n">
-        <v>-6.48</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="P30" t="n">
-        <v>7.969999999999999</v>
+        <v>6.75</v>
       </c>
       <c r="Q30" t="n">
-        <v>8.06</v>
+        <v>7.36</v>
       </c>
       <c r="R30" t="n">
-        <v>2.928388145626228</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.685</v>
+        <v>13.505</v>
       </c>
       <c r="T30" t="n">
-        <v>3133.95</v>
+        <v>2696.19</v>
       </c>
       <c r="U30" t="n">
-        <v>16366</v>
+        <v>17117</v>
       </c>
       <c r="V30" t="n">
-        <v>1.026824584882459</v>
+        <v>1.05172449539736</v>
       </c>
       <c r="W30" t="n">
-        <v>1.066857458699382</v>
+        <v>1.100869131799052</v>
       </c>
       <c r="X30" t="n">
-        <v>327.1250015258789</v>
+        <v>110.2475006103516</v>
       </c>
       <c r="Y30" t="n">
-        <v>314.8499278488279</v>
+        <v>105.3258680791199</v>
       </c>
       <c r="Z30" t="n">
-        <v>2687199.951171875</v>
+        <v>11879724652.13037</v>
       </c>
     </row>
     <row r="31">
@@ -2945,16 +2945,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2.018873462337603</v>
+        <v>2.087442844360512</v>
       </c>
       <c r="D31" t="n">
-        <v>1.924888111546837</v>
+        <v>2.002374444568464</v>
       </c>
       <c r="E31" t="n">
-        <v>43.31000137329102</v>
+        <v>44.40000152587891</v>
       </c>
       <c r="F31" t="n">
-        <v>63.91</v>
+        <v>75.94</v>
       </c>
       <c r="G31" t="n">
         <v>241</v>
@@ -2969,7 +2969,7 @@
         <v>15.9792531120332</v>
       </c>
       <c r="K31" t="n">
-        <v>4196905.7</v>
+        <v>4378655.55</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="n">
@@ -2988,7 +2988,7 @@
         <v>19.03</v>
       </c>
       <c r="R31" t="n">
-        <v>0.0939853507907662</v>
+        <v>0.0850683997920485</v>
       </c>
       <c r="S31" t="n">
         <v>4.937</v>
@@ -3000,593 +3000,429 @@
         <v>3851</v>
       </c>
       <c r="V31" t="n">
-        <v>1.023647196329167</v>
+        <v>1.044337320177211</v>
       </c>
       <c r="W31" t="n">
-        <v>1.07489074847927</v>
+        <v>1.095604802976578</v>
       </c>
       <c r="X31" t="n">
-        <v>42.30950031280518</v>
+        <v>42.51500034332275</v>
       </c>
       <c r="Y31" t="n">
-        <v>40.29246826671918</v>
+        <v>40.52556305453519</v>
       </c>
       <c r="Z31" t="n">
-        <v>158059590.1518173</v>
+        <v>308873139.4149323</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>0050.TW</t>
+          <t>0053.TW</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>元大台灣50</t>
+          <t>元大電子</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3.222120773712524</v>
+        <v>6.963338122068993</v>
       </c>
       <c r="D32" t="n">
-        <v>3.222120773712524</v>
+        <v>3.330666428410618</v>
       </c>
       <c r="E32" t="n">
-        <v>112.8000030517578</v>
+        <v>263</v>
       </c>
       <c r="F32" t="n">
-        <v>79.34</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>1229</v>
+        <v>1145</v>
       </c>
       <c r="H32" t="n">
-        <v>90.89</v>
+        <v>90.31</v>
       </c>
       <c r="I32" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="J32" t="n">
-        <v>13.92758340113914</v>
+        <v>14.07598253275109</v>
       </c>
       <c r="K32" t="n">
-        <v>68224055</v>
+        <v>125541.3</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="n">
         <v>2</v>
       </c>
       <c r="N32" t="n">
-        <v>15.64</v>
+        <v>10.88</v>
       </c>
       <c r="O32" t="n">
-        <v>-8.890000000000001</v>
+        <v>-8.44</v>
       </c>
       <c r="P32" t="n">
-        <v>6.75</v>
+        <v>2.440000000000001</v>
       </c>
       <c r="Q32" t="n">
-        <v>7.36</v>
+        <v>7.63</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.632671693658375</v>
       </c>
       <c r="S32" t="n">
-        <v>13.505</v>
+        <v>18.91</v>
       </c>
       <c r="T32" t="n">
-        <v>2696.19</v>
+        <v>2466.25</v>
       </c>
       <c r="U32" t="n">
-        <v>17117</v>
+        <v>16117</v>
       </c>
       <c r="V32" t="n">
-        <v>1.027696815092032</v>
+        <v>1.060205993744484</v>
       </c>
       <c r="W32" t="n">
-        <v>1.071399288319003</v>
+        <v>1.117618135851378</v>
       </c>
       <c r="X32" t="n">
-        <v>109.7600006103516</v>
+        <v>248.0650001525879</v>
       </c>
       <c r="Y32" t="n">
-        <v>105.2828803244195</v>
+        <v>235.3218792388799</v>
       </c>
       <c r="Z32" t="n">
-        <v>7347432366.781769</v>
+        <v>57555183</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>0053.TW</t>
+          <t>00735.TW</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>元大電子</t>
+          <t>國泰臺韓科技</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6.752011936269088</v>
+        <v>3.425017075369201</v>
       </c>
       <c r="D33" t="n">
-        <v>3.222120773712524</v>
+        <v>2.879530295412196</v>
       </c>
       <c r="E33" t="n">
-        <v>255.5500030517578</v>
+        <v>112.1999969482422</v>
       </c>
       <c r="F33" t="n">
-        <v>89.88</v>
+        <v>81.37</v>
       </c>
       <c r="G33" t="n">
-        <v>1145</v>
+        <v>480</v>
       </c>
       <c r="H33" t="n">
-        <v>90.31</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="J33" t="n">
-        <v>14.07598253275109</v>
+        <v>14.04583333333333</v>
       </c>
       <c r="K33" t="n">
-        <v>117049.35</v>
+        <v>1304362.15</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="n">
         <v>2</v>
       </c>
       <c r="N33" t="n">
-        <v>10.88</v>
+        <v>21.39</v>
       </c>
       <c r="O33" t="n">
-        <v>-8.44</v>
+        <v>-8.82</v>
       </c>
       <c r="P33" t="n">
-        <v>2.440000000000001</v>
+        <v>12.57</v>
       </c>
       <c r="Q33" t="n">
-        <v>7.63</v>
+        <v>13.92</v>
       </c>
       <c r="R33" t="n">
-        <v>3.529891162556564</v>
+        <v>0.5454867799570047</v>
       </c>
       <c r="S33" t="n">
-        <v>18.91</v>
+        <v>13.37</v>
       </c>
       <c r="T33" t="n">
-        <v>2466.25</v>
+        <v>1011.13</v>
       </c>
       <c r="U33" t="n">
-        <v>16117</v>
+        <v>6742</v>
       </c>
       <c r="V33" t="n">
-        <v>1.035034439253778</v>
+        <v>1.053076135603725</v>
       </c>
       <c r="W33" t="n">
-        <v>1.084402178006938</v>
+        <v>1.115353671425007</v>
       </c>
       <c r="X33" t="n">
-        <v>246.9</v>
+        <v>106.5450000762939</v>
       </c>
       <c r="Y33" t="n">
-        <v>235.6598024558034</v>
+        <v>100.5958915299865</v>
       </c>
       <c r="Z33" t="n">
-        <v>39899277.526474</v>
+        <v>189106811.6564331</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>00735.TW</t>
+          <t>006203.TW</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>國泰臺韓科技</t>
+          <t>元大MSCI台灣</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3.352477462151255</v>
+        <v>4.554652994076354</v>
       </c>
       <c r="D34" t="n">
-        <v>2.780469132255372</v>
+        <v>3.587366007796832</v>
       </c>
       <c r="E34" t="n">
-        <v>110.1500015258789</v>
+        <v>208.8500061035156</v>
       </c>
       <c r="F34" t="n">
-        <v>74.33</v>
+        <v>86.73999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>480</v>
+        <v>1041</v>
       </c>
       <c r="H34" t="n">
-        <v>84.79000000000001</v>
+        <v>90.78</v>
       </c>
       <c r="I34" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="J34" t="n">
-        <v>14.04583333333333</v>
+        <v>12.95965417867435</v>
       </c>
       <c r="K34" t="n">
-        <v>1302759.4</v>
+        <v>9452.65</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="n">
         <v>2</v>
       </c>
       <c r="N34" t="n">
-        <v>21.39</v>
+        <v>8.85</v>
       </c>
       <c r="O34" t="n">
-        <v>-8.82</v>
+        <v>-7.69</v>
       </c>
       <c r="P34" t="n">
-        <v>12.57</v>
+        <v>1.159999999999999</v>
       </c>
       <c r="Q34" t="n">
-        <v>13.92</v>
+        <v>8.81</v>
       </c>
       <c r="R34" t="n">
-        <v>0.5720083298958825</v>
+        <v>0.9672869862795226</v>
       </c>
       <c r="S34" t="n">
-        <v>13.37</v>
+        <v>21.88</v>
       </c>
       <c r="T34" t="n">
-        <v>1011.13</v>
+        <v>2169.48</v>
       </c>
       <c r="U34" t="n">
-        <v>6742</v>
+        <v>13491</v>
       </c>
       <c r="V34" t="n">
-        <v>1.039494185507146</v>
+        <v>1.043767286554884</v>
       </c>
       <c r="W34" t="n">
-        <v>1.100699715636436</v>
+        <v>1.087783454122587</v>
       </c>
       <c r="X34" t="n">
-        <v>105.9650001525879</v>
+        <v>200.0925003051758</v>
       </c>
       <c r="Y34" t="n">
-        <v>100.0727082610256</v>
+        <v>191.9959393682591</v>
       </c>
       <c r="Z34" t="n">
-        <v>183361310.1900558</v>
+        <v>5585066.863220215</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>006203.TW</t>
+          <t>006208.TW</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>元大MSCI台灣</t>
+          <t>富邦台50</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4.457567612228822</v>
+        <v>4.56867464219185</v>
       </c>
       <c r="D35" t="n">
-        <v>3.472165036146328</v>
+        <v>3.769644201915613</v>
       </c>
       <c r="E35" t="n">
-        <v>204.8500061035156</v>
+        <v>265.3500061035156</v>
       </c>
       <c r="F35" t="n">
-        <v>84.73</v>
+        <v>87.13</v>
       </c>
       <c r="G35" t="n">
-        <v>1041</v>
+        <v>1012</v>
       </c>
       <c r="H35" t="n">
-        <v>90.78</v>
+        <v>89.23</v>
       </c>
       <c r="I35" t="n">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="J35" t="n">
-        <v>12.95965417867435</v>
+        <v>13.89624505928854</v>
       </c>
       <c r="K35" t="n">
-        <v>8466.35</v>
+        <v>1970488.55</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="n">
         <v>2</v>
       </c>
       <c r="N35" t="n">
-        <v>8.85</v>
+        <v>11.21</v>
       </c>
       <c r="O35" t="n">
-        <v>-7.69</v>
+        <v>-6.25</v>
       </c>
       <c r="P35" t="n">
-        <v>1.159999999999999</v>
+        <v>4.960000000000001</v>
       </c>
       <c r="Q35" t="n">
-        <v>8.81</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="R35" t="n">
-        <v>0.9854025760824943</v>
+        <v>0.7990304402762369</v>
       </c>
       <c r="S35" t="n">
-        <v>21.88</v>
+        <v>28.764</v>
       </c>
       <c r="T35" t="n">
-        <v>2169.48</v>
+        <v>1914.21</v>
       </c>
       <c r="U35" t="n">
-        <v>13491</v>
+        <v>14063</v>
       </c>
       <c r="V35" t="n">
-        <v>1.027654134839233</v>
+        <v>1.052162046144237</v>
       </c>
       <c r="W35" t="n">
-        <v>1.067730899590386</v>
+        <v>1.101071205442985</v>
       </c>
       <c r="X35" t="n">
-        <v>199.3375</v>
+        <v>252.1949989318848</v>
       </c>
       <c r="Y35" t="n">
-        <v>191.8554630029929</v>
+        <v>240.9925941136201</v>
       </c>
       <c r="Z35" t="n">
-        <v>409700.0122070312</v>
+        <v>1229073897.220856</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>006208.TW</t>
+          <t>0051.TW</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>富邦台50</t>
+          <t>元大中型100</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4.433550785271723</v>
+        <v>3.80321487131572</v>
       </c>
       <c r="D36" t="n">
-        <v>3.649759828213125</v>
+        <v>3.330666428410618</v>
       </c>
       <c r="E36" t="n">
-        <v>258.2999877929688</v>
+        <v>152.4499969482422</v>
       </c>
       <c r="F36" t="n">
-        <v>82.86</v>
+        <v>89.61</v>
       </c>
       <c r="G36" t="n">
-        <v>1012</v>
+        <v>1121</v>
       </c>
       <c r="H36" t="n">
-        <v>89.23</v>
+        <v>88.84999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>1.89</v>
+        <v>1.71</v>
       </c>
       <c r="J36" t="n">
-        <v>13.89624505928854</v>
+        <v>15.42908117752007</v>
       </c>
       <c r="K36" t="n">
-        <v>1808921</v>
+        <v>46876.85</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="n">
         <v>2</v>
       </c>
       <c r="N36" t="n">
-        <v>11.21</v>
+        <v>10</v>
       </c>
       <c r="O36" t="n">
-        <v>-6.25</v>
+        <v>-10.68</v>
       </c>
       <c r="P36" t="n">
-        <v>4.960000000000001</v>
+        <v>-0.6799999999999997</v>
       </c>
       <c r="Q36" t="n">
-        <v>8.109999999999999</v>
+        <v>6.55</v>
       </c>
       <c r="R36" t="n">
-        <v>0.7837909570585975</v>
+        <v>0.4725484429051017</v>
       </c>
       <c r="S36" t="n">
-        <v>28.764</v>
+        <v>19.36</v>
       </c>
       <c r="T36" t="n">
-        <v>1914.21</v>
+        <v>1920.98</v>
       </c>
       <c r="U36" t="n">
-        <v>14063</v>
+        <v>17296</v>
       </c>
       <c r="V36" t="n">
-        <v>1.028602104785953</v>
+        <v>1.040525531597933</v>
       </c>
       <c r="W36" t="n">
-        <v>1.071336074615511</v>
+        <v>1.078317653425235</v>
       </c>
       <c r="X36" t="n">
-        <v>251.1174987792969</v>
+        <v>146.5125</v>
       </c>
       <c r="Y36" t="n">
-        <v>241.100802925608</v>
+        <v>141.3776325222818</v>
       </c>
       <c r="Z36" t="n">
-        <v>520120087.8195801</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>0051.TW</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>元大中型100</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>3.742745184287324</v>
-      </c>
-      <c r="D37" t="n">
-        <v>3.222120773712524</v>
-      </c>
-      <c r="E37" t="n">
-        <v>150.3000030517578</v>
-      </c>
-      <c r="F37" t="n">
-        <v>89.11</v>
-      </c>
-      <c r="G37" t="n">
-        <v>1121</v>
-      </c>
-      <c r="H37" t="n">
-        <v>88.84999999999999</v>
-      </c>
-      <c r="I37" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="J37" t="n">
-        <v>15.42908117752007</v>
-      </c>
-      <c r="K37" t="n">
-        <v>44767.75</v>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="n">
-        <v>2</v>
-      </c>
-      <c r="N37" t="n">
-        <v>10</v>
-      </c>
-      <c r="O37" t="n">
-        <v>-10.68</v>
-      </c>
-      <c r="P37" t="n">
-        <v>-0.6799999999999997</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0.5206244105748006</v>
-      </c>
-      <c r="S37" t="n">
-        <v>19.36</v>
-      </c>
-      <c r="T37" t="n">
-        <v>1920.98</v>
-      </c>
-      <c r="U37" t="n">
-        <v>17296</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.028817871824031</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.061193174353157</v>
-      </c>
-      <c r="X37" t="n">
-        <v>146.0900001525879</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>141.6330284477868</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>8630677.075241089</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>00406A.TW</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>主動中信台灣收益</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>0.07069678317898975</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.0705083821254413</v>
-      </c>
-      <c r="E38" t="n">
-        <v>10.13000011444092</v>
-      </c>
-      <c r="F38" t="n">
-        <v>91.16</v>
-      </c>
-      <c r="G38" t="n">
-        <v>4</v>
-      </c>
-      <c r="H38" t="n">
-        <v>75</v>
-      </c>
-      <c r="I38" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="J38" t="n">
-        <v>12.75</v>
-      </c>
-      <c r="K38" t="n">
-        <v>247382499</v>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="n">
-        <v>2</v>
-      </c>
-      <c r="N38" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="O38" t="n">
-        <v>-7.44</v>
-      </c>
-      <c r="P38" t="n">
-        <v>-3.180000000000001</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>34.42</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0.0001884010535484482</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0.266</v>
-      </c>
-      <c r="T38" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="U38" t="n">
-        <v>51</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.048165980282491</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.104196360182026</v>
-      </c>
-      <c r="X38" t="n">
-        <v>9.664499998092651</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>9.174093014372007</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>3822853111.937642</v>
+        <v>14093544.86787415</v>
       </c>
     </row>
   </sheetData>

--- a/ETF動態清單.xlsx
+++ b/ETF動態清單.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z21"/>
+  <dimension ref="A1:Z20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,16 +567,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9680374205572622</v>
+        <v>0.9651578941631866</v>
       </c>
       <c r="D2" t="n">
-        <v>0.692302121387661</v>
+        <v>0.7002303463982145</v>
       </c>
       <c r="E2" t="n">
-        <v>32.65000152587891</v>
+        <v>32.59999847412109</v>
       </c>
       <c r="F2" t="n">
-        <v>93.28</v>
+        <v>92</v>
       </c>
       <c r="G2" t="n">
         <v>42</v>
@@ -591,7 +591,7 @@
         <v>8.761904761904763</v>
       </c>
       <c r="K2" t="n">
-        <v>154372794.75</v>
+        <v>146424846.25</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
@@ -610,7 +610,7 @@
         <v>347.51</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2757352991696012</v>
+        <v>0.2649275477649722</v>
       </c>
       <c r="S2" t="n">
         <v>1.67</v>
@@ -622,19 +622,19 @@
         <v>368</v>
       </c>
       <c r="V2" t="n">
-        <v>1.088805196735343</v>
+        <v>1.087228352941525</v>
       </c>
       <c r="W2" t="n">
-        <v>1.169119202604759</v>
+        <v>1.166896138081229</v>
       </c>
       <c r="X2" t="n">
-        <v>29.98700008392334</v>
+        <v>29.98449993133545</v>
       </c>
       <c r="Y2" t="n">
-        <v>27.92700817259333</v>
+        <v>27.93736084149398</v>
       </c>
       <c r="Z2" t="n">
-        <v>9102424544.146538</v>
+        <v>3906422120.155602</v>
       </c>
     </row>
     <row r="3">
@@ -649,16 +649,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.434723459059454</v>
+        <v>1.42235821935437</v>
       </c>
       <c r="D3" t="n">
-        <v>1.04209788083989</v>
+        <v>1.049790792447868</v>
       </c>
       <c r="E3" t="n">
-        <v>41.29999923706055</v>
+        <v>41.13000106811523</v>
       </c>
       <c r="F3" t="n">
-        <v>81.68000000000001</v>
+        <v>81.39</v>
       </c>
       <c r="G3" t="n">
         <v>67</v>
@@ -673,7 +673,7 @@
         <v>10.44776119402985</v>
       </c>
       <c r="K3" t="n">
-        <v>7004766.75</v>
+        <v>7198907.25</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
@@ -692,7 +692,7 @@
         <v>151.1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.392625578219564</v>
+        <v>0.3725674269065014</v>
       </c>
       <c r="S3" t="n">
         <v>0.78</v>
@@ -704,19 +704,19 @@
         <v>700</v>
       </c>
       <c r="V3" t="n">
-        <v>1.061874068706451</v>
+        <v>1.052496919877355</v>
       </c>
       <c r="W3" t="n">
-        <v>1.15756259006224</v>
+        <v>1.148996822968834</v>
       </c>
       <c r="X3" t="n">
-        <v>38.8935001373291</v>
+        <v>39.07850017547607</v>
       </c>
       <c r="Y3" t="n">
-        <v>35.67841565685008</v>
+        <v>35.79644455573127</v>
       </c>
       <c r="Z3" t="n">
-        <v>847423368.1454544</v>
+        <v>317641486.8289108</v>
       </c>
     </row>
     <row r="4">
@@ -731,16 +731,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.812583607435554</v>
+        <v>2.800440133416631</v>
       </c>
       <c r="D4" t="n">
-        <v>2.596870790978858</v>
+        <v>2.611765500262139</v>
       </c>
       <c r="E4" t="n">
-        <v>92.90000152587891</v>
+        <v>92.59999847412109</v>
       </c>
       <c r="F4" t="n">
-        <v>94.5</v>
+        <v>92.66</v>
       </c>
       <c r="G4" t="n">
         <v>489</v>
@@ -755,7 +755,7 @@
         <v>12.34560327198364</v>
       </c>
       <c r="K4" t="n">
-        <v>6935280.25</v>
+        <v>6962477.85</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
@@ -774,7 +774,7 @@
         <v>19.93</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2157128164566959</v>
+        <v>0.1886746331544922</v>
       </c>
       <c r="S4" t="n">
         <v>17.71</v>
@@ -786,19 +786,19 @@
         <v>6037</v>
       </c>
       <c r="V4" t="n">
-        <v>1.095486592690261</v>
+        <v>1.084499603438574</v>
       </c>
       <c r="W4" t="n">
-        <v>1.21190296230218</v>
+        <v>1.206179256876647</v>
       </c>
       <c r="X4" t="n">
-        <v>84.80249977111816</v>
+        <v>85.3849998474121</v>
       </c>
       <c r="Y4" t="n">
-        <v>76.65630369398743</v>
+        <v>76.77134053350008</v>
       </c>
       <c r="Z4" t="n">
-        <v>780375341.3176346</v>
+        <v>557326425.2162781</v>
       </c>
     </row>
     <row r="5">
@@ -813,16 +813,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.45207912237185</v>
+        <v>17.60149783089847</v>
       </c>
       <c r="D5" t="n">
-        <v>3.858061559756839</v>
+        <v>3.878363149125641</v>
       </c>
       <c r="E5" t="n">
-        <v>41.54000091552734</v>
+        <v>41.88999938964844</v>
       </c>
       <c r="F5" t="n">
-        <v>90.38</v>
+        <v>93.59</v>
       </c>
       <c r="G5" t="n">
         <v>618</v>
@@ -837,7 +837,7 @@
         <v>12.48705501618123</v>
       </c>
       <c r="K5" t="n">
-        <v>159482066.9</v>
+        <v>158306832.85</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
@@ -856,7 +856,7 @@
         <v>16.33</v>
       </c>
       <c r="R5" t="n">
-        <v>13.59401756261501</v>
+        <v>13.72313468177283</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -868,1331 +868,1249 @@
         <v>7717</v>
       </c>
       <c r="V5" t="n">
-        <v>1.099538116649976</v>
+        <v>1.101151326196401</v>
       </c>
       <c r="W5" t="n">
-        <v>1.200996893898137</v>
+        <v>1.21659062744427</v>
       </c>
       <c r="X5" t="n">
-        <v>37.77950057983399</v>
+        <v>38.04200057983398</v>
       </c>
       <c r="Y5" t="n">
-        <v>34.5879336795775</v>
+        <v>34.43228843349556</v>
       </c>
       <c r="Z5" t="n">
-        <v>11483532697.97311</v>
+        <v>5309235330.432632</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>00904.TW</t>
+          <t>00913.TW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>台新臺灣半導體30</t>
+          <t>兆豐台灣晶圓製造</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2.042329286411374</v>
+        <v>1.957770400209872</v>
       </c>
       <c r="D6" t="n">
-        <v>1.924449686178473</v>
+        <v>1.839293671622407</v>
       </c>
       <c r="E6" t="n">
-        <v>44.9900016784668</v>
+        <v>54.20000076293945</v>
       </c>
       <c r="F6" t="n">
-        <v>88.84999999999999</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>231</v>
+        <v>263</v>
       </c>
       <c r="H6" t="n">
-        <v>100</v>
+        <v>96.95999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>3.71</v>
+        <v>3.53</v>
       </c>
       <c r="J6" t="n">
-        <v>10.48917748917749</v>
+        <v>12.54372623574145</v>
       </c>
       <c r="K6" t="n">
-        <v>1225424</v>
+        <v>1438060</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>2</v>
       </c>
       <c r="N6" t="n">
-        <v>11.85</v>
+        <v>13.5</v>
       </c>
       <c r="O6" t="n">
-        <v>0.09</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>11.94</v>
+        <v>4.039999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>40.54</v>
+        <v>29.41</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1178796002329014</v>
+        <v>0.1184767285874657</v>
       </c>
       <c r="S6" t="n">
-        <v>4.850000000000001</v>
+        <v>6.699999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>857.38</v>
+        <v>928.22</v>
       </c>
       <c r="U6" t="n">
-        <v>2423</v>
+        <v>3299</v>
       </c>
       <c r="V6" t="n">
-        <v>1.063354611950043</v>
+        <v>1.067843545350555</v>
       </c>
       <c r="W6" t="n">
-        <v>1.134107209346856</v>
+        <v>1.164532587720557</v>
       </c>
       <c r="X6" t="n">
-        <v>42.30949974060059</v>
+        <v>50.7564998626709</v>
       </c>
       <c r="Y6" t="n">
-        <v>39.66997238680548</v>
+        <v>46.54227913795864</v>
       </c>
       <c r="Z6" t="n">
-        <v>175872215.1613617</v>
+        <v>97504229.57250595</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>00913.TW</t>
+          <t>00685L.TW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>兆豐台灣晶圓製造</t>
+          <t>群益臺灣加權正2</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.975194484945144</v>
+        <v>12.14208618378939</v>
       </c>
       <c r="D7" t="n">
-        <v>1.826242026597972</v>
+        <v>3.183971837787399</v>
       </c>
       <c r="E7" t="n">
-        <v>54.54999923706055</v>
+        <v>13.86999988555908</v>
       </c>
       <c r="F7" t="n">
-        <v>83.34</v>
+        <v>92.98</v>
       </c>
       <c r="G7" t="n">
-        <v>263</v>
+        <v>526</v>
       </c>
       <c r="H7" t="n">
-        <v>96.95999999999999</v>
+        <v>87.45</v>
       </c>
       <c r="I7" t="n">
-        <v>3.53</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
-        <v>12.54372623574145</v>
+        <v>12.24524714828897</v>
       </c>
       <c r="K7" t="n">
-        <v>1499524.55</v>
+        <v>199834803.75</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>2</v>
       </c>
       <c r="N7" t="n">
-        <v>13.5</v>
+        <v>15.89</v>
       </c>
       <c r="O7" t="n">
-        <v>-9.460000000000001</v>
+        <v>-18.5</v>
       </c>
       <c r="P7" t="n">
-        <v>4.039999999999999</v>
+        <v>-2.609999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>29.41</v>
+        <v>17.94</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1489524583471722</v>
+        <v>8.958114346001992</v>
       </c>
       <c r="S7" t="n">
-        <v>6.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>928.22</v>
+        <v>1738.26</v>
       </c>
       <c r="U7" t="n">
-        <v>3299</v>
+        <v>6441</v>
       </c>
       <c r="V7" t="n">
-        <v>1.074368760912484</v>
+        <v>1.103596415231766</v>
       </c>
       <c r="W7" t="n">
-        <v>1.173112197842067</v>
+        <v>1.224355411801913</v>
       </c>
       <c r="X7" t="n">
-        <v>50.77399978637695</v>
+        <v>12.56800012588501</v>
       </c>
       <c r="Y7" t="n">
-        <v>46.50024041809891</v>
+        <v>11.32840983252262</v>
       </c>
       <c r="Z7" t="n">
-        <v>165191689.7896194</v>
+        <v>2255033043.173796</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>00685L.TW</t>
+          <t>00715L.TW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>群益臺灣加權正2</t>
+          <t>期街口布蘭特正2</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12.04304935075706</v>
+        <v>4.536815017810124</v>
       </c>
       <c r="D8" t="n">
-        <v>3.166605229921184</v>
+        <v>3.029792625388506</v>
       </c>
       <c r="E8" t="n">
-        <v>13.76000022888184</v>
+        <v>68.90000152587891</v>
       </c>
       <c r="F8" t="n">
-        <v>89.84999999999999</v>
+        <v>69.11</v>
       </c>
       <c r="G8" t="n">
-        <v>526</v>
+        <v>429</v>
       </c>
       <c r="H8" t="n">
-        <v>87.45</v>
+        <v>78.55</v>
       </c>
       <c r="I8" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="J8" t="n">
-        <v>12.24524714828897</v>
+        <v>17.20745920745921</v>
       </c>
       <c r="K8" t="n">
-        <v>202281081.65</v>
+        <v>4779587.95</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>15.89</v>
+        <v>32.14</v>
       </c>
       <c r="O8" t="n">
-        <v>-18.5</v>
+        <v>-45.45</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.609999999999999</v>
+        <v>-13.31</v>
       </c>
       <c r="Q8" t="n">
-        <v>17.94</v>
+        <v>14.29</v>
       </c>
       <c r="R8" t="n">
-        <v>8.87644412083587</v>
+        <v>1.507022392421618</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1738.26</v>
+        <v>1389.98</v>
       </c>
       <c r="U8" t="n">
-        <v>6441</v>
+        <v>7382</v>
       </c>
       <c r="V8" t="n">
-        <v>1.102475769367826</v>
+        <v>1.042872840754252</v>
       </c>
       <c r="W8" t="n">
-        <v>1.208821734564203</v>
+        <v>1.189760232963335</v>
       </c>
       <c r="X8" t="n">
-        <v>12.4810001373291</v>
+        <v>66.06750011444092</v>
       </c>
       <c r="Y8" t="n">
-        <v>11.38298546050093</v>
+        <v>57.91082910400334</v>
       </c>
       <c r="Z8" t="n">
-        <v>3674961170.248768</v>
+        <v>135695039.1051407</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>00715L.TW</t>
+          <t>00675L.TW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>期街口布蘭特正2</t>
+          <t>富邦臺灣加權正2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4.619301116535601</v>
+        <v>12.85893633099761</v>
       </c>
       <c r="D9" t="n">
-        <v>3.013094419387573</v>
+        <v>3.319142657353297</v>
       </c>
       <c r="E9" t="n">
-        <v>69.90000152587891</v>
+        <v>367</v>
       </c>
       <c r="F9" t="n">
-        <v>65.45999999999999</v>
+        <v>92.95</v>
       </c>
       <c r="G9" t="n">
-        <v>429</v>
+        <v>555</v>
       </c>
       <c r="H9" t="n">
-        <v>78.55</v>
+        <v>86.31</v>
       </c>
       <c r="I9" t="n">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
       <c r="J9" t="n">
-        <v>17.20745920745921</v>
+        <v>12.35135135135135</v>
       </c>
       <c r="K9" t="n">
-        <v>4906926.3</v>
+        <v>951546.5</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>32.14</v>
+        <v>15.7</v>
       </c>
       <c r="O9" t="n">
-        <v>-45.45</v>
+        <v>-24.73</v>
       </c>
       <c r="P9" t="n">
-        <v>-13.31</v>
+        <v>-9.030000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>14.29</v>
+        <v>16.91</v>
       </c>
       <c r="R9" t="n">
-        <v>1.606206697148028</v>
+        <v>9.539793673644315</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1389.98</v>
+        <v>1779.77</v>
       </c>
       <c r="U9" t="n">
-        <v>7382</v>
+        <v>6855</v>
       </c>
       <c r="V9" t="n">
-        <v>1.067623834207527</v>
+        <v>1.10206071830687</v>
       </c>
       <c r="W9" t="n">
-        <v>1.236494703294306</v>
+        <v>1.221744377670775</v>
       </c>
       <c r="X9" t="n">
-        <v>65.47250003814698</v>
+        <v>333.0125045776367</v>
       </c>
       <c r="Y9" t="n">
-        <v>56.53077311180488</v>
+        <v>300.3901689317992</v>
       </c>
       <c r="Z9" t="n">
-        <v>138619112.4259796</v>
+        <v>331013081</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>00675L.TW</t>
+          <t>00935.TW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>富邦臺灣加權正2</t>
+          <t>野村臺灣新科技50</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12.76787946198546</v>
+        <v>1.747131698994631</v>
       </c>
       <c r="D10" t="n">
-        <v>3.301201567177383</v>
+        <v>1.322593304700856</v>
       </c>
       <c r="E10" t="n">
-        <v>364.4500122070312</v>
+        <v>63.5</v>
       </c>
       <c r="F10" t="n">
-        <v>90.06999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>555</v>
+        <v>137</v>
       </c>
       <c r="H10" t="n">
-        <v>86.31</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>3.21</v>
+        <v>3.14</v>
       </c>
       <c r="J10" t="n">
-        <v>12.35135135135135</v>
+        <v>12.38686131386861</v>
       </c>
       <c r="K10" t="n">
-        <v>967524.15</v>
+        <v>11475709.15</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>15.7</v>
+        <v>14.6</v>
       </c>
       <c r="O10" t="n">
-        <v>-24.73</v>
+        <v>-8.99</v>
       </c>
       <c r="P10" t="n">
-        <v>-9.030000000000001</v>
+        <v>5.609999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>16.91</v>
+        <v>43.19</v>
       </c>
       <c r="R10" t="n">
-        <v>9.466677894808077</v>
+        <v>0.424538394293775</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="T10" t="n">
-        <v>1779.77</v>
+        <v>430.76</v>
       </c>
       <c r="U10" t="n">
-        <v>6855</v>
+        <v>1697</v>
       </c>
       <c r="V10" t="n">
-        <v>1.1018396983832</v>
+        <v>1.061384811968502</v>
       </c>
       <c r="W10" t="n">
-        <v>1.207452796319666</v>
+        <v>1.130692299706662</v>
       </c>
       <c r="X10" t="n">
-        <v>330.7650039672852</v>
+        <v>59.82750015258789</v>
       </c>
       <c r="Y10" t="n">
-        <v>301.8337555868687</v>
+        <v>56.16028340908834</v>
       </c>
       <c r="Z10" t="n">
-        <v>766780229.7828369</v>
+        <v>960816658.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>00935.TW</t>
+          <t>00894.TW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>野村臺灣新科技50</t>
+          <t>中信小資高價30</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.749162911191024</v>
+        <v>2.368494218552121</v>
       </c>
       <c r="D11" t="n">
-        <v>1.311843173966012</v>
+        <v>1.995079210580925</v>
       </c>
       <c r="E11" t="n">
-        <v>63.54999923706055</v>
+        <v>52.70000076293945</v>
       </c>
       <c r="F11" t="n">
-        <v>87.13</v>
+        <v>90.19</v>
       </c>
       <c r="G11" t="n">
-        <v>137</v>
+        <v>243</v>
       </c>
       <c r="H11" t="n">
-        <v>83.20999999999999</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="J11" t="n">
-        <v>12.38686131386861</v>
+        <v>15.33333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>11328333.95</v>
+        <v>1142728.45</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>14.6</v>
+        <v>15.7</v>
       </c>
       <c r="O11" t="n">
-        <v>-8.99</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>5.609999999999999</v>
+        <v>7.319999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>43.19</v>
+        <v>22.72</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4373197372250113</v>
+        <v>0.3734150079711958</v>
       </c>
       <c r="S11" t="n">
-        <v>4.98</v>
+        <v>7.549999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>430.76</v>
+        <v>708.49</v>
       </c>
       <c r="U11" t="n">
-        <v>1697</v>
+        <v>3726</v>
       </c>
       <c r="V11" t="n">
-        <v>1.062176151019624</v>
+        <v>1.077852892702195</v>
       </c>
       <c r="W11" t="n">
-        <v>1.131735048794595</v>
+        <v>1.16605326834879</v>
       </c>
       <c r="X11" t="n">
-        <v>59.83000011444092</v>
+        <v>48.89350032806396</v>
       </c>
       <c r="Y11" t="n">
-        <v>56.15271816910441</v>
+        <v>45.19519150061319</v>
       </c>
       <c r="Z11" t="n">
-        <v>774259318.5547523</v>
+        <v>53082128.46847153</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>00894.TW</t>
+          <t>00901.TW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>中信小資高價30</t>
+          <t>永豐智能車供應鏈</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.37325183336789</v>
+        <v>2.069028559817832</v>
       </c>
       <c r="D12" t="n">
-        <v>1.982954182806191</v>
+        <v>1.956661327934444</v>
       </c>
       <c r="E12" t="n">
-        <v>52.75</v>
+        <v>50.25</v>
       </c>
       <c r="F12" t="n">
-        <v>89.72</v>
+        <v>87.81</v>
       </c>
       <c r="G12" t="n">
-        <v>243</v>
+        <v>269</v>
       </c>
       <c r="H12" t="n">
-        <v>83.54000000000001</v>
+        <v>90.33</v>
       </c>
       <c r="I12" t="n">
-        <v>2.92</v>
+        <v>2.79</v>
       </c>
       <c r="J12" t="n">
-        <v>15.33333333333333</v>
+        <v>13.22304832713755</v>
       </c>
       <c r="K12" t="n">
-        <v>1112408.2</v>
+        <v>262989.6</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>15.7</v>
+        <v>15.18</v>
       </c>
       <c r="O12" t="n">
-        <v>-8.380000000000001</v>
+        <v>-7.07</v>
       </c>
       <c r="P12" t="n">
-        <v>7.319999999999999</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>22.72</v>
+        <v>24.56</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3902976505617</v>
+        <v>0.112367231883387</v>
       </c>
       <c r="S12" t="n">
-        <v>7.549999999999999</v>
+        <v>4.671</v>
       </c>
       <c r="T12" t="n">
-        <v>708.49</v>
+        <v>750.16</v>
       </c>
       <c r="U12" t="n">
-        <v>3726</v>
+        <v>3557</v>
       </c>
       <c r="V12" t="n">
-        <v>1.084732513902628</v>
+        <v>1.063109560292487</v>
       </c>
       <c r="W12" t="n">
-        <v>1.163876439311488</v>
+        <v>1.125822760483312</v>
       </c>
       <c r="X12" t="n">
-        <v>48.62950019836425</v>
+        <v>47.26700038909912</v>
       </c>
       <c r="Y12" t="n">
-        <v>45.32268049966302</v>
+        <v>44.63402390126475</v>
       </c>
       <c r="Z12" t="n">
-        <v>99337903.25</v>
+        <v>8972288.25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>00901.TW</t>
+          <t>00881.TW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>永豐智能車供應鏈</t>
+          <t>國泰台灣科技龍頭</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.066175265086512</v>
+        <v>2.240835743173172</v>
       </c>
       <c r="D13" t="n">
-        <v>1.943112320989987</v>
+        <v>2.07690823531148</v>
       </c>
       <c r="E13" t="n">
-        <v>50.20000076293945</v>
+        <v>54.5</v>
       </c>
       <c r="F13" t="n">
-        <v>85.55</v>
+        <v>84.3</v>
       </c>
       <c r="G13" t="n">
-        <v>269</v>
+        <v>323</v>
       </c>
       <c r="H13" t="n">
-        <v>90.33</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>2.79</v>
+        <v>2.56</v>
       </c>
       <c r="J13" t="n">
-        <v>13.22304832713755</v>
+        <v>13.88854489164087</v>
       </c>
       <c r="K13" t="n">
-        <v>294600.05</v>
+        <v>14976138.85</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>2</v>
       </c>
       <c r="N13" t="n">
-        <v>15.18</v>
+        <v>10.9</v>
       </c>
       <c r="O13" t="n">
-        <v>-7.07</v>
+        <v>-7.15</v>
       </c>
       <c r="P13" t="n">
-        <v>8.109999999999999</v>
+        <v>3.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>24.56</v>
+        <v>19.85</v>
       </c>
       <c r="R13" t="n">
-        <v>0.123062944096525</v>
+        <v>0.163927507861692</v>
       </c>
       <c r="S13" t="n">
-        <v>4.671</v>
+        <v>12.5</v>
       </c>
       <c r="T13" t="n">
-        <v>750.16</v>
+        <v>825.49</v>
       </c>
       <c r="U13" t="n">
-        <v>3557</v>
+        <v>4486</v>
       </c>
       <c r="V13" t="n">
-        <v>1.062107931093273</v>
+        <v>1.062202171126568</v>
       </c>
       <c r="W13" t="n">
-        <v>1.124481782888495</v>
+        <v>1.120475237652817</v>
       </c>
       <c r="X13" t="n">
-        <v>47.26450042724609</v>
+        <v>51.30849990844727</v>
       </c>
       <c r="Y13" t="n">
-        <v>44.6427870391897</v>
+        <v>48.64007536138607</v>
       </c>
       <c r="Z13" t="n">
-        <v>40700253.01856232</v>
+        <v>933099677.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>00881.TW</t>
+          <t>0057.TW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>國泰台灣科技龍頭</t>
+          <t>富邦摩台</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.238330076865061</v>
+        <v>6.353055102179241</v>
       </c>
       <c r="D14" t="n">
-        <v>2.062872865056776</v>
+        <v>3.34580458284676</v>
       </c>
       <c r="E14" t="n">
-        <v>54.45000076293945</v>
+        <v>345.7000122070312</v>
       </c>
       <c r="F14" t="n">
-        <v>84.73</v>
+        <v>88.98999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>323</v>
+        <v>1250</v>
       </c>
       <c r="H14" t="n">
-        <v>90.70999999999999</v>
+        <v>93.52</v>
       </c>
       <c r="I14" t="n">
-        <v>2.56</v>
+        <v>2.51</v>
       </c>
       <c r="J14" t="n">
-        <v>13.88854489164087</v>
+        <v>13.0928</v>
       </c>
       <c r="K14" t="n">
-        <v>15823618.8</v>
+        <v>17881.25</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>10.9</v>
+        <v>14.45</v>
       </c>
       <c r="O14" t="n">
-        <v>-7.15</v>
+        <v>-6.48</v>
       </c>
       <c r="P14" t="n">
-        <v>3.75</v>
+        <v>7.969999999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>19.85</v>
+        <v>8.06</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1754572118082849</v>
+        <v>3.007250519332482</v>
       </c>
       <c r="S14" t="n">
-        <v>12.5</v>
+        <v>1.685</v>
       </c>
       <c r="T14" t="n">
-        <v>825.49</v>
+        <v>3133.95</v>
       </c>
       <c r="U14" t="n">
-        <v>4486</v>
+        <v>16366</v>
       </c>
       <c r="V14" t="n">
-        <v>1.061279398503448</v>
+        <v>1.052287164377184</v>
       </c>
       <c r="W14" t="n">
-        <v>1.119231050758579</v>
+        <v>1.098913075060533</v>
       </c>
       <c r="X14" t="n">
-        <v>51.30599994659424</v>
+        <v>328.5225021362305</v>
       </c>
       <c r="Y14" t="n">
-        <v>48.64947298061018</v>
+        <v>314.5835826805396</v>
       </c>
       <c r="Z14" t="n">
-        <v>1855149314.293877</v>
+        <v>6280332.121765137</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0057.TW</t>
+          <t>0050.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>富邦摩台</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6.309587311255153</v>
+        <v>3.348978940459001</v>
       </c>
       <c r="D15" t="n">
-        <v>3.32673903121997</v>
+        <v>3.348978940459001</v>
       </c>
       <c r="E15" t="n">
-        <v>343.6499938964844</v>
+        <v>116.5</v>
       </c>
       <c r="F15" t="n">
-        <v>86.81999999999999</v>
+        <v>89.51000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>1250</v>
+        <v>1229</v>
       </c>
       <c r="H15" t="n">
-        <v>93.52</v>
+        <v>90.89</v>
       </c>
       <c r="I15" t="n">
-        <v>2.51</v>
+        <v>2.19</v>
       </c>
       <c r="J15" t="n">
-        <v>13.0928</v>
+        <v>13.92758340113914</v>
       </c>
       <c r="K15" t="n">
-        <v>19465.7</v>
+        <v>72157019.59999999</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>14.45</v>
+        <v>15.64</v>
       </c>
       <c r="O15" t="n">
-        <v>-6.48</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>7.969999999999999</v>
+        <v>6.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.06</v>
+        <v>7.36</v>
       </c>
       <c r="R15" t="n">
-        <v>2.982848280035182</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.685</v>
+        <v>13.505</v>
       </c>
       <c r="T15" t="n">
-        <v>3133.95</v>
+        <v>2696.19</v>
       </c>
       <c r="U15" t="n">
-        <v>16366</v>
+        <v>17117</v>
       </c>
       <c r="V15" t="n">
-        <v>1.046373523595314</v>
+        <v>1.052607796867898</v>
       </c>
       <c r="W15" t="n">
-        <v>1.091069629905982</v>
+        <v>1.107602947310842</v>
       </c>
       <c r="X15" t="n">
-        <v>328.4200012207031</v>
+        <v>110.6775005340576</v>
       </c>
       <c r="Y15" t="n">
-        <v>314.9661437520691</v>
+        <v>105.1820964207899</v>
       </c>
       <c r="Z15" t="n">
-        <v>17133014.09570312</v>
+        <v>8230825190</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>0050.TW</t>
+          <t>0053.TW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>元大台灣50</t>
+          <t>元大電子</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3.330666428410618</v>
+        <v>6.966195744638434</v>
       </c>
       <c r="D16" t="n">
-        <v>3.330666428410618</v>
+        <v>3.349748437810618</v>
       </c>
       <c r="E16" t="n">
-        <v>115.9499969482422</v>
+        <v>263.1000061035156</v>
       </c>
       <c r="F16" t="n">
-        <v>85.17</v>
+        <v>92.58</v>
       </c>
       <c r="G16" t="n">
-        <v>1229</v>
+        <v>1145</v>
       </c>
       <c r="H16" t="n">
-        <v>90.89</v>
+        <v>90.31</v>
       </c>
       <c r="I16" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="J16" t="n">
-        <v>13.92758340113914</v>
+        <v>14.07598253275109</v>
       </c>
       <c r="K16" t="n">
-        <v>71075200.34999999</v>
+        <v>124121</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>15.64</v>
+        <v>10.88</v>
       </c>
       <c r="O16" t="n">
-        <v>-8.890000000000001</v>
+        <v>-8.44</v>
       </c>
       <c r="P16" t="n">
-        <v>6.75</v>
+        <v>2.440000000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.36</v>
+        <v>7.63</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>3.616447306827816</v>
       </c>
       <c r="S16" t="n">
-        <v>13.505</v>
+        <v>18.91</v>
       </c>
       <c r="T16" t="n">
-        <v>2696.19</v>
+        <v>2466.25</v>
       </c>
       <c r="U16" t="n">
-        <v>17117</v>
+        <v>16117</v>
       </c>
       <c r="V16" t="n">
-        <v>1.05172449539736</v>
+        <v>1.060587759979107</v>
       </c>
       <c r="W16" t="n">
-        <v>1.100869131799052</v>
+        <v>1.118130986406804</v>
       </c>
       <c r="X16" t="n">
-        <v>110.2475006103516</v>
+        <v>248.0700004577637</v>
       </c>
       <c r="Y16" t="n">
-        <v>105.3258680791199</v>
+        <v>235.3033851150184</v>
       </c>
       <c r="Z16" t="n">
-        <v>11879724652.13037</v>
+        <v>50103449.662323</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>0053.TW</t>
+          <t>00735.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>元大電子</t>
+          <t>國泰臺韓科技</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6.963338122068993</v>
+        <v>3.41790608917016</v>
       </c>
       <c r="D17" t="n">
-        <v>3.330666428410618</v>
+        <v>2.895643050144198</v>
       </c>
       <c r="E17" t="n">
-        <v>263</v>
+        <v>112.0500030517578</v>
       </c>
       <c r="F17" t="n">
-        <v>87.15000000000001</v>
+        <v>82.86</v>
       </c>
       <c r="G17" t="n">
-        <v>1145</v>
+        <v>480</v>
       </c>
       <c r="H17" t="n">
-        <v>90.31</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="J17" t="n">
-        <v>14.07598253275109</v>
+        <v>14.04583333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>125541.3</v>
+        <v>1305550.1</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>10.88</v>
+        <v>21.39</v>
       </c>
       <c r="O17" t="n">
-        <v>-8.44</v>
+        <v>-8.82</v>
       </c>
       <c r="P17" t="n">
-        <v>2.440000000000001</v>
+        <v>12.57</v>
       </c>
       <c r="Q17" t="n">
-        <v>7.63</v>
+        <v>13.92</v>
       </c>
       <c r="R17" t="n">
-        <v>3.632671693658375</v>
+        <v>0.5222630390259626</v>
       </c>
       <c r="S17" t="n">
-        <v>18.91</v>
+        <v>13.37</v>
       </c>
       <c r="T17" t="n">
-        <v>2466.25</v>
+        <v>1011.13</v>
       </c>
       <c r="U17" t="n">
-        <v>16117</v>
+        <v>6742</v>
       </c>
       <c r="V17" t="n">
-        <v>1.060205993744484</v>
+        <v>1.047734844750311</v>
       </c>
       <c r="W17" t="n">
-        <v>1.117618135851378</v>
+        <v>1.113211856356494</v>
       </c>
       <c r="X17" t="n">
-        <v>248.0650001525879</v>
+        <v>106.945000076294</v>
       </c>
       <c r="Y17" t="n">
-        <v>235.3218792388799</v>
+        <v>100.6546978564294</v>
       </c>
       <c r="Z17" t="n">
-        <v>57555183</v>
+        <v>187765551.6139221</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>00735.TW</t>
+          <t>006203.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>國泰臺韓科技</t>
+          <t>元大MSCI台灣</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3.425017075369201</v>
+        <v>4.603786560876608</v>
       </c>
       <c r="D18" t="n">
-        <v>2.879530295412196</v>
+        <v>3.607641338979411</v>
       </c>
       <c r="E18" t="n">
-        <v>112.1999969482422</v>
+        <v>210.8500061035156</v>
       </c>
       <c r="F18" t="n">
-        <v>81.37</v>
+        <v>89.66</v>
       </c>
       <c r="G18" t="n">
-        <v>480</v>
+        <v>1041</v>
       </c>
       <c r="H18" t="n">
-        <v>84.79000000000001</v>
+        <v>90.78</v>
       </c>
       <c r="I18" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="J18" t="n">
-        <v>14.04583333333333</v>
+        <v>12.95965417867435</v>
       </c>
       <c r="K18" t="n">
-        <v>1304362.15</v>
+        <v>8680</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>21.39</v>
+        <v>8.85</v>
       </c>
       <c r="O18" t="n">
-        <v>-8.82</v>
+        <v>-7.69</v>
       </c>
       <c r="P18" t="n">
-        <v>12.57</v>
+        <v>1.159999999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>13.92</v>
+        <v>8.81</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5454867799570047</v>
+        <v>0.9961452218971969</v>
       </c>
       <c r="S18" t="n">
-        <v>13.37</v>
+        <v>21.88</v>
       </c>
       <c r="T18" t="n">
-        <v>1011.13</v>
+        <v>2169.48</v>
       </c>
       <c r="U18" t="n">
-        <v>6742</v>
+        <v>13491</v>
       </c>
       <c r="V18" t="n">
-        <v>1.053076135603725</v>
+        <v>1.053236288982322</v>
       </c>
       <c r="W18" t="n">
-        <v>1.115353671425007</v>
+        <v>1.100298785033401</v>
       </c>
       <c r="X18" t="n">
-        <v>106.5450000762939</v>
+        <v>200.1925003051758</v>
       </c>
       <c r="Y18" t="n">
-        <v>100.5958915299865</v>
+        <v>191.6297727231563</v>
       </c>
       <c r="Z18" t="n">
-        <v>189106811.6564331</v>
+        <v>2380285.718902588</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>006203.TW</t>
+          <t>006208.TW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>元大MSCI台灣</t>
+          <t>富邦台50</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4.554652994076354</v>
+        <v>4.579315318082955</v>
       </c>
       <c r="D19" t="n">
-        <v>3.587366007796832</v>
+        <v>3.790759620208392</v>
       </c>
       <c r="E19" t="n">
-        <v>208.8500061035156</v>
+        <v>265.8999938964844</v>
       </c>
       <c r="F19" t="n">
-        <v>86.73999999999999</v>
+        <v>86.86</v>
       </c>
       <c r="G19" t="n">
-        <v>1041</v>
+        <v>1012</v>
       </c>
       <c r="H19" t="n">
-        <v>90.78</v>
+        <v>89.23</v>
       </c>
       <c r="I19" t="n">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="J19" t="n">
-        <v>12.95965417867435</v>
+        <v>13.89624505928854</v>
       </c>
       <c r="K19" t="n">
-        <v>9452.65</v>
+        <v>1886197.3</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>8.85</v>
+        <v>11.21</v>
       </c>
       <c r="O19" t="n">
-        <v>-7.69</v>
+        <v>-6.25</v>
       </c>
       <c r="P19" t="n">
-        <v>1.159999999999999</v>
+        <v>4.960000000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>8.81</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9672869862795226</v>
+        <v>0.7885556978745631</v>
       </c>
       <c r="S19" t="n">
-        <v>21.88</v>
+        <v>28.764</v>
       </c>
       <c r="T19" t="n">
-        <v>2169.48</v>
+        <v>1914.21</v>
       </c>
       <c r="U19" t="n">
-        <v>13491</v>
+        <v>14063</v>
       </c>
       <c r="V19" t="n">
-        <v>1.043767286554884</v>
+        <v>1.054227896662554</v>
       </c>
       <c r="W19" t="n">
-        <v>1.087783454122587</v>
+        <v>1.103827312615171</v>
       </c>
       <c r="X19" t="n">
-        <v>200.0925003051758</v>
+        <v>252.2224983215332</v>
       </c>
       <c r="Y19" t="n">
-        <v>191.9959393682591</v>
+        <v>240.8891235591175</v>
       </c>
       <c r="Z19" t="n">
-        <v>5585066.863220215</v>
+        <v>783360526.8186035</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>006208.TW</t>
+          <t>0051.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>富邦台50</t>
+          <t>元大中型100</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4.56867464219185</v>
+        <v>3.7994890180982</v>
       </c>
       <c r="D20" t="n">
-        <v>3.769644201915613</v>
+        <v>3.348978940459001</v>
       </c>
       <c r="E20" t="n">
-        <v>265.3500061035156</v>
+        <v>152.3500061035156</v>
       </c>
       <c r="F20" t="n">
-        <v>87.13</v>
+        <v>93.48999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>1012</v>
+        <v>1121</v>
       </c>
       <c r="H20" t="n">
-        <v>89.23</v>
+        <v>88.84999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>1.89</v>
+        <v>1.71</v>
       </c>
       <c r="J20" t="n">
-        <v>13.89624505928854</v>
+        <v>15.42908117752007</v>
       </c>
       <c r="K20" t="n">
-        <v>1970488.55</v>
+        <v>42720.5</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
         <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>11.21</v>
+        <v>10</v>
       </c>
       <c r="O20" t="n">
-        <v>-6.25</v>
+        <v>-10.68</v>
       </c>
       <c r="P20" t="n">
-        <v>4.960000000000001</v>
+        <v>-0.6799999999999997</v>
       </c>
       <c r="Q20" t="n">
-        <v>8.109999999999999</v>
+        <v>6.55</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7990304402762369</v>
+        <v>0.4505100776391986</v>
       </c>
       <c r="S20" t="n">
-        <v>28.764</v>
+        <v>19.36</v>
       </c>
       <c r="T20" t="n">
-        <v>1914.21</v>
+        <v>1920.98</v>
       </c>
       <c r="U20" t="n">
-        <v>14063</v>
+        <v>17296</v>
       </c>
       <c r="V20" t="n">
-        <v>1.052162046144237</v>
+        <v>1.037785368408214</v>
       </c>
       <c r="W20" t="n">
-        <v>1.101071205442985</v>
+        <v>1.079004272557284</v>
       </c>
       <c r="X20" t="n">
-        <v>252.1949989318848</v>
+        <v>146.8030006408691</v>
       </c>
       <c r="Y20" t="n">
-        <v>240.9925941136201</v>
+        <v>141.1949979979596</v>
       </c>
       <c r="Z20" t="n">
-        <v>1229073897.220856</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>0051.TW</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>元大中型100</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>3.80321487131572</v>
-      </c>
-      <c r="D21" t="n">
-        <v>3.330666428410618</v>
-      </c>
-      <c r="E21" t="n">
-        <v>152.4499969482422</v>
-      </c>
-      <c r="F21" t="n">
-        <v>89.61</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1121</v>
-      </c>
-      <c r="H21" t="n">
-        <v>88.84999999999999</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="J21" t="n">
-        <v>15.42908117752007</v>
-      </c>
-      <c r="K21" t="n">
-        <v>46876.85</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="n">
-        <v>2</v>
-      </c>
-      <c r="N21" t="n">
-        <v>10</v>
-      </c>
-      <c r="O21" t="n">
-        <v>-10.68</v>
-      </c>
-      <c r="P21" t="n">
-        <v>-0.6799999999999997</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.4725484429051017</v>
-      </c>
-      <c r="S21" t="n">
-        <v>19.36</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1920.98</v>
-      </c>
-      <c r="U21" t="n">
-        <v>17296</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.040525531597933</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.078317653425235</v>
-      </c>
-      <c r="X21" t="n">
-        <v>146.5125</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>141.3776325222818</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>14093544.86787415</v>
+        <v>6039306.591949463</v>
       </c>
     </row>
   </sheetData>

--- a/ETF動態清單.xlsx
+++ b/ETF動態清單.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z20"/>
+  <dimension ref="A1:Z21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,16 +567,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9651578941631866</v>
+        <v>0.9680374205572622</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7002303463982145</v>
+        <v>0.692302121387661</v>
       </c>
       <c r="E2" t="n">
-        <v>32.59999847412109</v>
+        <v>32.65000152587891</v>
       </c>
       <c r="F2" t="n">
-        <v>92</v>
+        <v>93.28</v>
       </c>
       <c r="G2" t="n">
         <v>42</v>
@@ -591,7 +591,7 @@
         <v>8.761904761904763</v>
       </c>
       <c r="K2" t="n">
-        <v>146424846.25</v>
+        <v>154266327.75</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
@@ -610,7 +610,7 @@
         <v>347.51</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2649275477649722</v>
+        <v>0.2757352991696012</v>
       </c>
       <c r="S2" t="n">
         <v>1.67</v>
@@ -622,19 +622,19 @@
         <v>368</v>
       </c>
       <c r="V2" t="n">
-        <v>1.087228352941525</v>
+        <v>1.088805196735343</v>
       </c>
       <c r="W2" t="n">
-        <v>1.166896138081229</v>
+        <v>1.169119202604759</v>
       </c>
       <c r="X2" t="n">
-        <v>29.98449993133545</v>
+        <v>29.98700008392334</v>
       </c>
       <c r="Y2" t="n">
-        <v>27.93736084149398</v>
+        <v>27.92700817259333</v>
       </c>
       <c r="Z2" t="n">
-        <v>3906422120.155602</v>
+        <v>9032901589.897423</v>
       </c>
     </row>
     <row r="3">
@@ -649,16 +649,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.42235821935437</v>
+        <v>1.434723459059454</v>
       </c>
       <c r="D3" t="n">
-        <v>1.049790792447868</v>
+        <v>1.04209788083989</v>
       </c>
       <c r="E3" t="n">
-        <v>41.13000106811523</v>
+        <v>41.29999923706055</v>
       </c>
       <c r="F3" t="n">
-        <v>81.39</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>67</v>
@@ -673,7 +673,7 @@
         <v>10.44776119402985</v>
       </c>
       <c r="K3" t="n">
-        <v>7198907.25</v>
+        <v>6999245.75</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
@@ -692,7 +692,7 @@
         <v>151.1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3725674269065014</v>
+        <v>0.392625578219564</v>
       </c>
       <c r="S3" t="n">
         <v>0.78</v>
@@ -704,19 +704,19 @@
         <v>700</v>
       </c>
       <c r="V3" t="n">
-        <v>1.052496919877355</v>
+        <v>1.061874068706451</v>
       </c>
       <c r="W3" t="n">
-        <v>1.148996822968834</v>
+        <v>1.15756259006224</v>
       </c>
       <c r="X3" t="n">
-        <v>39.07850017547607</v>
+        <v>38.8935001373291</v>
       </c>
       <c r="Y3" t="n">
-        <v>35.79644455573127</v>
+        <v>35.67841565685008</v>
       </c>
       <c r="Z3" t="n">
-        <v>317641486.8289108</v>
+        <v>842863022.2296982</v>
       </c>
     </row>
     <row r="4">
@@ -731,16 +731,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.800440133416631</v>
+        <v>2.812583607435554</v>
       </c>
       <c r="D4" t="n">
-        <v>2.611765500262139</v>
+        <v>2.596870790978858</v>
       </c>
       <c r="E4" t="n">
-        <v>92.59999847412109</v>
+        <v>92.90000152587891</v>
       </c>
       <c r="F4" t="n">
-        <v>92.66</v>
+        <v>94.5</v>
       </c>
       <c r="G4" t="n">
         <v>489</v>
@@ -755,7 +755,7 @@
         <v>12.34560327198364</v>
       </c>
       <c r="K4" t="n">
-        <v>6962477.85</v>
+        <v>6912740.4</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
@@ -774,7 +774,7 @@
         <v>19.93</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1886746331544922</v>
+        <v>0.2157128164566959</v>
       </c>
       <c r="S4" t="n">
         <v>17.71</v>
@@ -786,19 +786,19 @@
         <v>6037</v>
       </c>
       <c r="V4" t="n">
-        <v>1.084499603438574</v>
+        <v>1.095486592690261</v>
       </c>
       <c r="W4" t="n">
-        <v>1.206179256876647</v>
+        <v>1.21190296230218</v>
       </c>
       <c r="X4" t="n">
-        <v>85.3849998474121</v>
+        <v>84.80249977111816</v>
       </c>
       <c r="Y4" t="n">
-        <v>76.77134053350008</v>
+        <v>76.65630369398743</v>
       </c>
       <c r="Z4" t="n">
-        <v>557326425.2162781</v>
+        <v>738496299.3297729</v>
       </c>
     </row>
     <row r="5">
@@ -813,16 +813,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.60149783089847</v>
+        <v>17.45207912237185</v>
       </c>
       <c r="D5" t="n">
-        <v>3.878363149125641</v>
+        <v>3.858061559756839</v>
       </c>
       <c r="E5" t="n">
-        <v>41.88999938964844</v>
+        <v>41.54000091552734</v>
       </c>
       <c r="F5" t="n">
-        <v>93.59</v>
+        <v>90.38</v>
       </c>
       <c r="G5" t="n">
         <v>618</v>
@@ -837,7 +837,7 @@
         <v>12.48705501618123</v>
       </c>
       <c r="K5" t="n">
-        <v>158306832.85</v>
+        <v>159414795.35</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
@@ -856,7 +856,7 @@
         <v>16.33</v>
       </c>
       <c r="R5" t="n">
-        <v>13.72313468177283</v>
+        <v>13.59401756261501</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -868,1249 +868,1331 @@
         <v>7717</v>
       </c>
       <c r="V5" t="n">
-        <v>1.101151326196401</v>
+        <v>1.099538116649976</v>
       </c>
       <c r="W5" t="n">
-        <v>1.21659062744427</v>
+        <v>1.200996893898137</v>
       </c>
       <c r="X5" t="n">
-        <v>38.04200057983398</v>
+        <v>37.77950057983399</v>
       </c>
       <c r="Y5" t="n">
-        <v>34.43228843349556</v>
+        <v>34.5879336795775</v>
       </c>
       <c r="Z5" t="n">
-        <v>5309235330.432632</v>
+        <v>11427643493.00134</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>00913.TW</t>
+          <t>00904.TW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>兆豐台灣晶圓製造</t>
+          <t>台新臺灣半導體30</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.957770400209872</v>
+        <v>2.042329286411374</v>
       </c>
       <c r="D6" t="n">
-        <v>1.839293671622407</v>
+        <v>1.924449686178473</v>
       </c>
       <c r="E6" t="n">
-        <v>54.20000076293945</v>
+        <v>44.9900016784668</v>
       </c>
       <c r="F6" t="n">
-        <v>84.34999999999999</v>
+        <v>88.84999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>263</v>
+        <v>231</v>
       </c>
       <c r="H6" t="n">
-        <v>96.95999999999999</v>
+        <v>100</v>
       </c>
       <c r="I6" t="n">
-        <v>3.53</v>
+        <v>3.71</v>
       </c>
       <c r="J6" t="n">
-        <v>12.54372623574145</v>
+        <v>10.48917748917749</v>
       </c>
       <c r="K6" t="n">
-        <v>1438060</v>
+        <v>1221924.95</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>2</v>
       </c>
       <c r="N6" t="n">
-        <v>13.5</v>
+        <v>11.85</v>
       </c>
       <c r="O6" t="n">
-        <v>-9.460000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="P6" t="n">
-        <v>4.039999999999999</v>
+        <v>11.94</v>
       </c>
       <c r="Q6" t="n">
-        <v>29.41</v>
+        <v>40.54</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1184767285874657</v>
+        <v>0.1178796002329014</v>
       </c>
       <c r="S6" t="n">
-        <v>6.699999999999999</v>
+        <v>4.850000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>928.22</v>
+        <v>857.38</v>
       </c>
       <c r="U6" t="n">
-        <v>3299</v>
+        <v>2423</v>
       </c>
       <c r="V6" t="n">
-        <v>1.067843545350555</v>
+        <v>1.063354611950043</v>
       </c>
       <c r="W6" t="n">
-        <v>1.164532587720557</v>
+        <v>1.134107209346856</v>
       </c>
       <c r="X6" t="n">
-        <v>50.7564998626709</v>
+        <v>42.30949974060059</v>
       </c>
       <c r="Y6" t="n">
-        <v>46.54227913795864</v>
+        <v>39.66997238680548</v>
       </c>
       <c r="Z6" t="n">
-        <v>97504229.57250595</v>
+        <v>172723769.8539009</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>00685L.TW</t>
+          <t>00913.TW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>群益臺灣加權正2</t>
+          <t>兆豐台灣晶圓製造</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12.14208618378939</v>
+        <v>1.975194484945144</v>
       </c>
       <c r="D7" t="n">
-        <v>3.183971837787399</v>
+        <v>1.826242026597972</v>
       </c>
       <c r="E7" t="n">
-        <v>13.86999988555908</v>
+        <v>54.54999923706055</v>
       </c>
       <c r="F7" t="n">
-        <v>92.98</v>
+        <v>83.34</v>
       </c>
       <c r="G7" t="n">
-        <v>526</v>
+        <v>263</v>
       </c>
       <c r="H7" t="n">
-        <v>87.45</v>
+        <v>96.95999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3</v>
+        <v>3.53</v>
       </c>
       <c r="J7" t="n">
-        <v>12.24524714828897</v>
+        <v>12.54372623574145</v>
       </c>
       <c r="K7" t="n">
-        <v>199834803.75</v>
+        <v>1497502.8</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>2</v>
       </c>
       <c r="N7" t="n">
-        <v>15.89</v>
+        <v>13.5</v>
       </c>
       <c r="O7" t="n">
-        <v>-18.5</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.609999999999999</v>
+        <v>4.039999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>17.94</v>
+        <v>29.41</v>
       </c>
       <c r="R7" t="n">
-        <v>8.958114346001992</v>
+        <v>0.1489524583471722</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>6.699999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>1738.26</v>
+        <v>928.22</v>
       </c>
       <c r="U7" t="n">
-        <v>6441</v>
+        <v>3299</v>
       </c>
       <c r="V7" t="n">
-        <v>1.103596415231766</v>
+        <v>1.074368760912484</v>
       </c>
       <c r="W7" t="n">
-        <v>1.224355411801913</v>
+        <v>1.173112197842067</v>
       </c>
       <c r="X7" t="n">
-        <v>12.56800012588501</v>
+        <v>50.77399978637695</v>
       </c>
       <c r="Y7" t="n">
-        <v>11.32840983252262</v>
+        <v>46.50024041809891</v>
       </c>
       <c r="Z7" t="n">
-        <v>2255033043.173796</v>
+        <v>162985960.5704689</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>00715L.TW</t>
+          <t>00685L.TW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>期街口布蘭特正2</t>
+          <t>群益臺灣加權正2</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4.536815017810124</v>
+        <v>12.04304935075706</v>
       </c>
       <c r="D8" t="n">
-        <v>3.029792625388506</v>
+        <v>3.166605229921184</v>
       </c>
       <c r="E8" t="n">
-        <v>68.90000152587891</v>
+        <v>13.76000022888184</v>
       </c>
       <c r="F8" t="n">
-        <v>69.11</v>
+        <v>89.84999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>429</v>
+        <v>526</v>
       </c>
       <c r="H8" t="n">
-        <v>78.55</v>
+        <v>87.45</v>
       </c>
       <c r="I8" t="n">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
-        <v>17.20745920745921</v>
+        <v>12.24524714828897</v>
       </c>
       <c r="K8" t="n">
-        <v>4779587.95</v>
+        <v>202252599.2</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>32.14</v>
+        <v>15.89</v>
       </c>
       <c r="O8" t="n">
-        <v>-45.45</v>
+        <v>-18.5</v>
       </c>
       <c r="P8" t="n">
-        <v>-13.31</v>
+        <v>-2.609999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>14.29</v>
+        <v>17.94</v>
       </c>
       <c r="R8" t="n">
-        <v>1.507022392421618</v>
+        <v>8.87644412083587</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1389.98</v>
+        <v>1738.26</v>
       </c>
       <c r="U8" t="n">
-        <v>7382</v>
+        <v>6441</v>
       </c>
       <c r="V8" t="n">
-        <v>1.042872840754252</v>
+        <v>1.102475769367826</v>
       </c>
       <c r="W8" t="n">
-        <v>1.189760232963335</v>
+        <v>1.208821734564203</v>
       </c>
       <c r="X8" t="n">
-        <v>66.06750011444092</v>
+        <v>12.4810001373291</v>
       </c>
       <c r="Y8" t="n">
-        <v>57.91082910400334</v>
+        <v>11.38298546050093</v>
       </c>
       <c r="Z8" t="n">
-        <v>135695039.1051407</v>
+        <v>3667122799.878386</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>00675L.TW</t>
+          <t>00715L.TW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>富邦臺灣加權正2</t>
+          <t>期街口布蘭特正2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12.85893633099761</v>
+        <v>4.619301116535601</v>
       </c>
       <c r="D9" t="n">
-        <v>3.319142657353297</v>
+        <v>3.013094419387573</v>
       </c>
       <c r="E9" t="n">
-        <v>367</v>
+        <v>69.90000152587891</v>
       </c>
       <c r="F9" t="n">
-        <v>92.95</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>555</v>
+        <v>429</v>
       </c>
       <c r="H9" t="n">
-        <v>86.31</v>
+        <v>78.55</v>
       </c>
       <c r="I9" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="J9" t="n">
-        <v>12.35135135135135</v>
+        <v>17.20745920745921</v>
       </c>
       <c r="K9" t="n">
-        <v>951546.5</v>
+        <v>4906142.15</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>15.7</v>
+        <v>32.14</v>
       </c>
       <c r="O9" t="n">
-        <v>-24.73</v>
+        <v>-45.45</v>
       </c>
       <c r="P9" t="n">
-        <v>-9.030000000000001</v>
+        <v>-13.31</v>
       </c>
       <c r="Q9" t="n">
-        <v>16.91</v>
+        <v>14.29</v>
       </c>
       <c r="R9" t="n">
-        <v>9.539793673644315</v>
+        <v>1.606206697148028</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1779.77</v>
+        <v>1389.98</v>
       </c>
       <c r="U9" t="n">
-        <v>6855</v>
+        <v>7382</v>
       </c>
       <c r="V9" t="n">
-        <v>1.10206071830687</v>
+        <v>1.067623834207527</v>
       </c>
       <c r="W9" t="n">
-        <v>1.221744377670775</v>
+        <v>1.236494703294306</v>
       </c>
       <c r="X9" t="n">
-        <v>333.0125045776367</v>
+        <v>65.47250003814698</v>
       </c>
       <c r="Y9" t="n">
-        <v>300.3901689317992</v>
+        <v>56.53077311180488</v>
       </c>
       <c r="Z9" t="n">
-        <v>331013081</v>
+        <v>137522870.7020493</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>00935.TW</t>
+          <t>00675L.TW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>野村臺灣新科技50</t>
+          <t>富邦臺灣加權正2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.747131698994631</v>
+        <v>12.76787946198546</v>
       </c>
       <c r="D10" t="n">
-        <v>1.322593304700856</v>
+        <v>3.301201567177383</v>
       </c>
       <c r="E10" t="n">
-        <v>63.5</v>
+        <v>364.4500122070312</v>
       </c>
       <c r="F10" t="n">
-        <v>86.40000000000001</v>
+        <v>90.06999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>137</v>
+        <v>555</v>
       </c>
       <c r="H10" t="n">
-        <v>83.20999999999999</v>
+        <v>86.31</v>
       </c>
       <c r="I10" t="n">
-        <v>3.14</v>
+        <v>3.21</v>
       </c>
       <c r="J10" t="n">
-        <v>12.38686131386861</v>
+        <v>12.35135135135135</v>
       </c>
       <c r="K10" t="n">
-        <v>11475709.15</v>
+        <v>964512.05</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>14.6</v>
+        <v>15.7</v>
       </c>
       <c r="O10" t="n">
-        <v>-8.99</v>
+        <v>-24.73</v>
       </c>
       <c r="P10" t="n">
-        <v>5.609999999999999</v>
+        <v>-9.030000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>43.19</v>
+        <v>16.91</v>
       </c>
       <c r="R10" t="n">
-        <v>0.424538394293775</v>
+        <v>9.466677894808077</v>
       </c>
       <c r="S10" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>430.76</v>
+        <v>1779.77</v>
       </c>
       <c r="U10" t="n">
-        <v>1697</v>
+        <v>6855</v>
       </c>
       <c r="V10" t="n">
-        <v>1.061384811968502</v>
+        <v>1.1018396983832</v>
       </c>
       <c r="W10" t="n">
-        <v>1.130692299706662</v>
+        <v>1.207452796319666</v>
       </c>
       <c r="X10" t="n">
-        <v>59.82750015258789</v>
+        <v>330.7650039672852</v>
       </c>
       <c r="Y10" t="n">
-        <v>56.16028340908834</v>
+        <v>301.8337555868687</v>
       </c>
       <c r="Z10" t="n">
-        <v>960816658.5</v>
+        <v>744825032.1474609</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>00894.TW</t>
+          <t>00935.TW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>中信小資高價30</t>
+          <t>野村臺灣新科技50</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.368494218552121</v>
+        <v>1.749162911191024</v>
       </c>
       <c r="D11" t="n">
-        <v>1.995079210580925</v>
+        <v>1.311843173966012</v>
       </c>
       <c r="E11" t="n">
-        <v>52.70000076293945</v>
+        <v>63.54999923706055</v>
       </c>
       <c r="F11" t="n">
-        <v>90.19</v>
+        <v>87.13</v>
       </c>
       <c r="G11" t="n">
-        <v>243</v>
+        <v>137</v>
       </c>
       <c r="H11" t="n">
-        <v>83.54000000000001</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="J11" t="n">
-        <v>15.33333333333333</v>
+        <v>12.38686131386861</v>
       </c>
       <c r="K11" t="n">
-        <v>1142728.45</v>
+        <v>11313647.05</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>15.7</v>
+        <v>14.6</v>
       </c>
       <c r="O11" t="n">
-        <v>-8.380000000000001</v>
+        <v>-8.99</v>
       </c>
       <c r="P11" t="n">
-        <v>7.319999999999999</v>
+        <v>5.609999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>22.72</v>
+        <v>43.19</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3734150079711958</v>
+        <v>0.4373197372250113</v>
       </c>
       <c r="S11" t="n">
-        <v>7.549999999999999</v>
+        <v>4.98</v>
       </c>
       <c r="T11" t="n">
-        <v>708.49</v>
+        <v>430.76</v>
       </c>
       <c r="U11" t="n">
-        <v>3726</v>
+        <v>1697</v>
       </c>
       <c r="V11" t="n">
-        <v>1.077852892702195</v>
+        <v>1.062176151019624</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16605326834879</v>
+        <v>1.131735048794595</v>
       </c>
       <c r="X11" t="n">
-        <v>48.89350032806396</v>
+        <v>59.83000011444092</v>
       </c>
       <c r="Y11" t="n">
-        <v>45.19519150061319</v>
+        <v>56.15271816910441</v>
       </c>
       <c r="Z11" t="n">
-        <v>53082128.46847153</v>
+        <v>755592268.8788567</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>00901.TW</t>
+          <t>00894.TW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>永豐智能車供應鏈</t>
+          <t>中信小資高價30</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.069028559817832</v>
+        <v>2.37325183336789</v>
       </c>
       <c r="D12" t="n">
-        <v>1.956661327934444</v>
+        <v>1.982954182806191</v>
       </c>
       <c r="E12" t="n">
-        <v>50.25</v>
+        <v>52.75</v>
       </c>
       <c r="F12" t="n">
-        <v>87.81</v>
+        <v>89.72</v>
       </c>
       <c r="G12" t="n">
-        <v>269</v>
+        <v>243</v>
       </c>
       <c r="H12" t="n">
-        <v>90.33</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>2.79</v>
+        <v>2.92</v>
       </c>
       <c r="J12" t="n">
-        <v>13.22304832713755</v>
+        <v>15.33333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>262989.6</v>
+        <v>1109638.05</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>15.18</v>
+        <v>15.7</v>
       </c>
       <c r="O12" t="n">
-        <v>-7.07</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>8.109999999999999</v>
+        <v>7.319999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>24.56</v>
+        <v>22.72</v>
       </c>
       <c r="R12" t="n">
-        <v>0.112367231883387</v>
+        <v>0.3902976505617</v>
       </c>
       <c r="S12" t="n">
-        <v>4.671</v>
+        <v>7.549999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>750.16</v>
+        <v>708.49</v>
       </c>
       <c r="U12" t="n">
-        <v>3557</v>
+        <v>3726</v>
       </c>
       <c r="V12" t="n">
-        <v>1.063109560292487</v>
+        <v>1.084732513902628</v>
       </c>
       <c r="W12" t="n">
-        <v>1.125822760483312</v>
+        <v>1.163876439311488</v>
       </c>
       <c r="X12" t="n">
-        <v>47.26700038909912</v>
+        <v>48.62950019836425</v>
       </c>
       <c r="Y12" t="n">
-        <v>44.63402390126475</v>
+        <v>45.32268049966302</v>
       </c>
       <c r="Z12" t="n">
-        <v>8972288.25</v>
+        <v>96415395</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>00881.TW</t>
+          <t>00901.TW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>國泰台灣科技龍頭</t>
+          <t>永豐智能車供應鏈</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.240835743173172</v>
+        <v>2.066175265086512</v>
       </c>
       <c r="D13" t="n">
-        <v>2.07690823531148</v>
+        <v>1.943112320989987</v>
       </c>
       <c r="E13" t="n">
-        <v>54.5</v>
+        <v>50.20000076293945</v>
       </c>
       <c r="F13" t="n">
-        <v>84.3</v>
+        <v>85.55</v>
       </c>
       <c r="G13" t="n">
-        <v>323</v>
+        <v>269</v>
       </c>
       <c r="H13" t="n">
-        <v>90.70999999999999</v>
+        <v>90.33</v>
       </c>
       <c r="I13" t="n">
-        <v>2.56</v>
+        <v>2.79</v>
       </c>
       <c r="J13" t="n">
-        <v>13.88854489164087</v>
+        <v>13.22304832713755</v>
       </c>
       <c r="K13" t="n">
-        <v>14976138.85</v>
+        <v>294014.45</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>2</v>
       </c>
       <c r="N13" t="n">
-        <v>10.9</v>
+        <v>15.18</v>
       </c>
       <c r="O13" t="n">
-        <v>-7.15</v>
+        <v>-7.07</v>
       </c>
       <c r="P13" t="n">
-        <v>3.75</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>19.85</v>
+        <v>24.56</v>
       </c>
       <c r="R13" t="n">
-        <v>0.163927507861692</v>
+        <v>0.123062944096525</v>
       </c>
       <c r="S13" t="n">
-        <v>12.5</v>
+        <v>4.671</v>
       </c>
       <c r="T13" t="n">
-        <v>825.49</v>
+        <v>750.16</v>
       </c>
       <c r="U13" t="n">
-        <v>4486</v>
+        <v>3557</v>
       </c>
       <c r="V13" t="n">
-        <v>1.062202171126568</v>
+        <v>1.062107931093273</v>
       </c>
       <c r="W13" t="n">
-        <v>1.120475237652817</v>
+        <v>1.124481782888495</v>
       </c>
       <c r="X13" t="n">
-        <v>51.30849990844727</v>
+        <v>47.26450042724609</v>
       </c>
       <c r="Y13" t="n">
-        <v>48.64007536138607</v>
+        <v>44.6427870391897</v>
       </c>
       <c r="Z13" t="n">
-        <v>933099677.5</v>
+        <v>40112310.60962677</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>0057.TW</t>
+          <t>00881.TW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>富邦摩台</t>
+          <t>國泰台灣科技龍頭</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6.353055102179241</v>
+        <v>2.238330076865061</v>
       </c>
       <c r="D14" t="n">
-        <v>3.34580458284676</v>
+        <v>2.062872865056776</v>
       </c>
       <c r="E14" t="n">
-        <v>345.7000122070312</v>
+        <v>54.45000076293945</v>
       </c>
       <c r="F14" t="n">
-        <v>88.98999999999999</v>
+        <v>84.73</v>
       </c>
       <c r="G14" t="n">
-        <v>1250</v>
+        <v>323</v>
       </c>
       <c r="H14" t="n">
-        <v>93.52</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>2.51</v>
+        <v>2.56</v>
       </c>
       <c r="J14" t="n">
-        <v>13.0928</v>
+        <v>13.88854489164087</v>
       </c>
       <c r="K14" t="n">
-        <v>17881.25</v>
+        <v>15797318.6</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>14.45</v>
+        <v>10.9</v>
       </c>
       <c r="O14" t="n">
-        <v>-6.48</v>
+        <v>-7.15</v>
       </c>
       <c r="P14" t="n">
-        <v>7.969999999999999</v>
+        <v>3.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.06</v>
+        <v>19.85</v>
       </c>
       <c r="R14" t="n">
-        <v>3.007250519332482</v>
+        <v>0.1754572118082849</v>
       </c>
       <c r="S14" t="n">
-        <v>1.685</v>
+        <v>12.5</v>
       </c>
       <c r="T14" t="n">
-        <v>3133.95</v>
+        <v>825.49</v>
       </c>
       <c r="U14" t="n">
-        <v>16366</v>
+        <v>4486</v>
       </c>
       <c r="V14" t="n">
-        <v>1.052287164377184</v>
+        <v>1.061279398503448</v>
       </c>
       <c r="W14" t="n">
-        <v>1.098913075060533</v>
+        <v>1.119231050758579</v>
       </c>
       <c r="X14" t="n">
-        <v>328.5225021362305</v>
+        <v>51.30599994659424</v>
       </c>
       <c r="Y14" t="n">
-        <v>314.5835826805396</v>
+        <v>48.64947298061018</v>
       </c>
       <c r="Z14" t="n">
-        <v>6280332.121765137</v>
+        <v>1826508396.092567</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0050.TW</t>
+          <t>0057.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>元大台灣50</t>
+          <t>富邦摩台</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3.348978940459001</v>
+        <v>6.309587311255153</v>
       </c>
       <c r="D15" t="n">
-        <v>3.348978940459001</v>
+        <v>3.32673903121997</v>
       </c>
       <c r="E15" t="n">
-        <v>116.5</v>
+        <v>343.6499938964844</v>
       </c>
       <c r="F15" t="n">
-        <v>89.51000000000001</v>
+        <v>86.81999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>1229</v>
+        <v>1250</v>
       </c>
       <c r="H15" t="n">
-        <v>90.89</v>
+        <v>93.52</v>
       </c>
       <c r="I15" t="n">
-        <v>2.19</v>
+        <v>2.51</v>
       </c>
       <c r="J15" t="n">
-        <v>13.92758340113914</v>
+        <v>13.0928</v>
       </c>
       <c r="K15" t="n">
-        <v>72157019.59999999</v>
+        <v>19023.25</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>15.64</v>
+        <v>14.45</v>
       </c>
       <c r="O15" t="n">
-        <v>-8.890000000000001</v>
+        <v>-6.48</v>
       </c>
       <c r="P15" t="n">
-        <v>6.75</v>
+        <v>7.969999999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>7.36</v>
+        <v>8.06</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.982848280035182</v>
       </c>
       <c r="S15" t="n">
-        <v>13.505</v>
+        <v>1.685</v>
       </c>
       <c r="T15" t="n">
-        <v>2696.19</v>
+        <v>3133.95</v>
       </c>
       <c r="U15" t="n">
-        <v>17117</v>
+        <v>16366</v>
       </c>
       <c r="V15" t="n">
-        <v>1.052607796867898</v>
+        <v>1.046373523595314</v>
       </c>
       <c r="W15" t="n">
-        <v>1.107602947310842</v>
+        <v>1.091069629905982</v>
       </c>
       <c r="X15" t="n">
-        <v>110.6775005340576</v>
+        <v>328.4200012207031</v>
       </c>
       <c r="Y15" t="n">
-        <v>105.1820964207899</v>
+        <v>314.9661437520691</v>
       </c>
       <c r="Z15" t="n">
-        <v>8230825190</v>
+        <v>14092055.29971313</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>0053.TW</t>
+          <t>0050.TW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>元大電子</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6.966195744638434</v>
+        <v>3.330666428410618</v>
       </c>
       <c r="D16" t="n">
-        <v>3.349748437810618</v>
+        <v>3.330666428410618</v>
       </c>
       <c r="E16" t="n">
-        <v>263.1000061035156</v>
+        <v>115.9499969482422</v>
       </c>
       <c r="F16" t="n">
-        <v>92.58</v>
+        <v>85.17</v>
       </c>
       <c r="G16" t="n">
-        <v>1145</v>
+        <v>1229</v>
       </c>
       <c r="H16" t="n">
-        <v>90.31</v>
+        <v>90.89</v>
       </c>
       <c r="I16" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="J16" t="n">
-        <v>14.07598253275109</v>
+        <v>13.92758340113914</v>
       </c>
       <c r="K16" t="n">
-        <v>124121</v>
+        <v>70838920</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>10.88</v>
+        <v>15.64</v>
       </c>
       <c r="O16" t="n">
-        <v>-8.44</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>2.440000000000001</v>
+        <v>6.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.63</v>
+        <v>7.36</v>
       </c>
       <c r="R16" t="n">
-        <v>3.616447306827816</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>18.91</v>
+        <v>13.505</v>
       </c>
       <c r="T16" t="n">
-        <v>2466.25</v>
+        <v>2696.19</v>
       </c>
       <c r="U16" t="n">
-        <v>16117</v>
+        <v>17117</v>
       </c>
       <c r="V16" t="n">
-        <v>1.060587759979107</v>
+        <v>1.05172449539736</v>
       </c>
       <c r="W16" t="n">
-        <v>1.118130986406804</v>
+        <v>1.100869131799052</v>
       </c>
       <c r="X16" t="n">
-        <v>248.0700004577637</v>
+        <v>110.2475006103516</v>
       </c>
       <c r="Y16" t="n">
-        <v>235.3033851150184</v>
+        <v>105.3258680791199</v>
       </c>
       <c r="Z16" t="n">
-        <v>50103449.662323</v>
+        <v>11331790534.90178</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>00735.TW</t>
+          <t>0053.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>國泰臺韓科技</t>
+          <t>元大電子</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3.41790608917016</v>
+        <v>6.963338122068993</v>
       </c>
       <c r="D17" t="n">
-        <v>2.895643050144198</v>
+        <v>3.330666428410618</v>
       </c>
       <c r="E17" t="n">
-        <v>112.0500030517578</v>
+        <v>263</v>
       </c>
       <c r="F17" t="n">
-        <v>82.86</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>480</v>
+        <v>1145</v>
       </c>
       <c r="H17" t="n">
-        <v>84.79000000000001</v>
+        <v>90.31</v>
       </c>
       <c r="I17" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="J17" t="n">
-        <v>14.04583333333333</v>
+        <v>14.07598253275109</v>
       </c>
       <c r="K17" t="n">
-        <v>1305550.1</v>
+        <v>124580.7</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>21.39</v>
+        <v>10.88</v>
       </c>
       <c r="O17" t="n">
-        <v>-8.82</v>
+        <v>-8.44</v>
       </c>
       <c r="P17" t="n">
-        <v>12.57</v>
+        <v>2.440000000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>13.92</v>
+        <v>7.63</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5222630390259626</v>
+        <v>3.632671693658375</v>
       </c>
       <c r="S17" t="n">
-        <v>13.37</v>
+        <v>18.91</v>
       </c>
       <c r="T17" t="n">
-        <v>1011.13</v>
+        <v>2466.25</v>
       </c>
       <c r="U17" t="n">
-        <v>6742</v>
+        <v>16117</v>
       </c>
       <c r="V17" t="n">
-        <v>1.047734844750311</v>
+        <v>1.060205993744484</v>
       </c>
       <c r="W17" t="n">
-        <v>1.113211856356494</v>
+        <v>1.117618135851378</v>
       </c>
       <c r="X17" t="n">
-        <v>106.945000076294</v>
+        <v>248.0650001525879</v>
       </c>
       <c r="Y17" t="n">
-        <v>100.6546978564294</v>
+        <v>235.3218792388799</v>
       </c>
       <c r="Z17" t="n">
-        <v>187765551.6139221</v>
+        <v>52502427</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>006203.TW</t>
+          <t>00735.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>元大MSCI台灣</t>
+          <t>國泰臺韓科技</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4.603786560876608</v>
+        <v>3.425017075369201</v>
       </c>
       <c r="D18" t="n">
-        <v>3.607641338979411</v>
+        <v>2.879530295412196</v>
       </c>
       <c r="E18" t="n">
-        <v>210.8500061035156</v>
+        <v>112.1999969482422</v>
       </c>
       <c r="F18" t="n">
-        <v>89.66</v>
+        <v>81.37</v>
       </c>
       <c r="G18" t="n">
-        <v>1041</v>
+        <v>480</v>
       </c>
       <c r="H18" t="n">
-        <v>90.78</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="J18" t="n">
-        <v>12.95965417867435</v>
+        <v>14.04583333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>8680</v>
+        <v>1299952.35</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>8.85</v>
+        <v>21.39</v>
       </c>
       <c r="O18" t="n">
-        <v>-7.69</v>
+        <v>-8.82</v>
       </c>
       <c r="P18" t="n">
-        <v>1.159999999999999</v>
+        <v>12.57</v>
       </c>
       <c r="Q18" t="n">
-        <v>8.81</v>
+        <v>13.92</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9961452218971969</v>
+        <v>0.5454867799570047</v>
       </c>
       <c r="S18" t="n">
-        <v>21.88</v>
+        <v>13.37</v>
       </c>
       <c r="T18" t="n">
-        <v>2169.48</v>
+        <v>1011.13</v>
       </c>
       <c r="U18" t="n">
-        <v>13491</v>
+        <v>6742</v>
       </c>
       <c r="V18" t="n">
-        <v>1.053236288982322</v>
+        <v>1.053076135603725</v>
       </c>
       <c r="W18" t="n">
-        <v>1.100298785033401</v>
+        <v>1.115353671425007</v>
       </c>
       <c r="X18" t="n">
-        <v>200.1925003051758</v>
+        <v>106.5450000762939</v>
       </c>
       <c r="Y18" t="n">
-        <v>191.6297727231563</v>
+        <v>100.5958915299865</v>
       </c>
       <c r="Z18" t="n">
-        <v>2380285.718902588</v>
+        <v>179211220.7255859</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>006208.TW</t>
+          <t>006203.TW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>富邦台50</t>
+          <t>元大MSCI台灣</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4.579315318082955</v>
+        <v>4.554652994076354</v>
       </c>
       <c r="D19" t="n">
-        <v>3.790759620208392</v>
+        <v>3.587366007796832</v>
       </c>
       <c r="E19" t="n">
-        <v>265.8999938964844</v>
+        <v>208.8500061035156</v>
       </c>
       <c r="F19" t="n">
-        <v>86.86</v>
+        <v>86.73999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>1012</v>
+        <v>1041</v>
       </c>
       <c r="H19" t="n">
-        <v>89.23</v>
+        <v>90.78</v>
       </c>
       <c r="I19" t="n">
-        <v>1.89</v>
+        <v>2.08</v>
       </c>
       <c r="J19" t="n">
-        <v>13.89624505928854</v>
+        <v>12.95965417867435</v>
       </c>
       <c r="K19" t="n">
-        <v>1886197.3</v>
+        <v>9116.049999999999</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>11.21</v>
+        <v>8.85</v>
       </c>
       <c r="O19" t="n">
-        <v>-6.25</v>
+        <v>-7.69</v>
       </c>
       <c r="P19" t="n">
-        <v>4.960000000000001</v>
+        <v>1.159999999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>8.109999999999999</v>
+        <v>8.81</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7885556978745631</v>
+        <v>0.9672869862795226</v>
       </c>
       <c r="S19" t="n">
-        <v>28.764</v>
+        <v>21.88</v>
       </c>
       <c r="T19" t="n">
-        <v>1914.21</v>
+        <v>2169.48</v>
       </c>
       <c r="U19" t="n">
-        <v>14063</v>
+        <v>13491</v>
       </c>
       <c r="V19" t="n">
-        <v>1.054227896662554</v>
+        <v>1.043767286554884</v>
       </c>
       <c r="W19" t="n">
-        <v>1.103827312615171</v>
+        <v>1.087783454122587</v>
       </c>
       <c r="X19" t="n">
-        <v>252.2224983215332</v>
+        <v>200.0925003051758</v>
       </c>
       <c r="Y19" t="n">
-        <v>240.8891235591175</v>
+        <v>191.9959393682591</v>
       </c>
       <c r="Z19" t="n">
-        <v>783360526.8186035</v>
+        <v>4179088.622131348</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>0051.TW</t>
+          <t>006208.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>元大中型100</t>
+          <t>富邦台50</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3.7994890180982</v>
+        <v>4.56867464219185</v>
       </c>
       <c r="D20" t="n">
-        <v>3.348978940459001</v>
+        <v>3.769644201915613</v>
       </c>
       <c r="E20" t="n">
-        <v>152.3500061035156</v>
+        <v>265.3500061035156</v>
       </c>
       <c r="F20" t="n">
-        <v>93.48999999999999</v>
+        <v>87.13</v>
       </c>
       <c r="G20" t="n">
-        <v>1121</v>
+        <v>1012</v>
       </c>
       <c r="H20" t="n">
-        <v>88.84999999999999</v>
+        <v>89.23</v>
       </c>
       <c r="I20" t="n">
-        <v>1.71</v>
+        <v>1.89</v>
       </c>
       <c r="J20" t="n">
-        <v>15.42908117752007</v>
+        <v>13.89624505928854</v>
       </c>
       <c r="K20" t="n">
-        <v>42720.5</v>
+        <v>1943759.2</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
         <v>2</v>
       </c>
       <c r="N20" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-6.25</v>
+      </c>
+      <c r="P20" t="n">
+        <v>4.960000000000001</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.7990304402762369</v>
+      </c>
+      <c r="S20" t="n">
+        <v>28.764</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1914.21</v>
+      </c>
+      <c r="U20" t="n">
+        <v>14063</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.052162046144237</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.101071205442985</v>
+      </c>
+      <c r="X20" t="n">
+        <v>252.1949989318848</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>240.9925941136201</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1087221233.507996</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>0051.TW</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>元大中型100</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>3.80321487131572</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3.330666428410618</v>
+      </c>
+      <c r="E21" t="n">
+        <v>152.4499969482422</v>
+      </c>
+      <c r="F21" t="n">
+        <v>89.61</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1121</v>
+      </c>
+      <c r="H21" t="n">
+        <v>88.84999999999999</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="J21" t="n">
+        <v>15.42908117752007</v>
+      </c>
+      <c r="K21" t="n">
+        <v>46162.3</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>2</v>
+      </c>
+      <c r="N21" t="n">
         <v>10</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O21" t="n">
         <v>-10.68</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P21" t="n">
         <v>-0.6799999999999997</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q21" t="n">
         <v>6.55</v>
       </c>
-      <c r="R20" t="n">
-        <v>0.4505100776391986</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="R21" t="n">
+        <v>0.4725484429051017</v>
+      </c>
+      <c r="S21" t="n">
         <v>19.36</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T21" t="n">
         <v>1920.98</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
         <v>17296</v>
       </c>
-      <c r="V20" t="n">
-        <v>1.037785368408214</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.079004272557284</v>
-      </c>
-      <c r="X20" t="n">
-        <v>146.8030006408691</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>141.1949979979596</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>6039306.591949463</v>
+      <c r="V21" t="n">
+        <v>1.040525531597933</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.078317653425235</v>
+      </c>
+      <c r="X21" t="n">
+        <v>146.5125</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>141.3776325222818</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>11914881.96148682</v>
       </c>
     </row>
   </sheetData>

--- a/ETF動態清單.xlsx
+++ b/ETF動態清單.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z21"/>
+  <dimension ref="A1:Z20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,16 +567,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9680374205572622</v>
+        <v>0.9427785253009235</v>
       </c>
       <c r="D2" t="n">
-        <v>0.692302121387661</v>
+        <v>0.6917177283960629</v>
       </c>
       <c r="E2" t="n">
-        <v>32.65000152587891</v>
+        <v>32.2599983215332</v>
       </c>
       <c r="F2" t="n">
-        <v>93.28</v>
+        <v>88.14</v>
       </c>
       <c r="G2" t="n">
         <v>42</v>
@@ -591,7 +591,7 @@
         <v>8.761904761904763</v>
       </c>
       <c r="K2" t="n">
-        <v>154266327.75</v>
+        <v>154716695.45</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
@@ -610,7 +610,7 @@
         <v>347.51</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2757352991696012</v>
+        <v>0.2510607969048606</v>
       </c>
       <c r="S2" t="n">
         <v>1.67</v>
@@ -622,19 +622,19 @@
         <v>368</v>
       </c>
       <c r="V2" t="n">
-        <v>1.088805196735343</v>
+        <v>1.071351422083074</v>
       </c>
       <c r="W2" t="n">
-        <v>1.169119202604759</v>
+        <v>1.159182597412336</v>
       </c>
       <c r="X2" t="n">
-        <v>29.98700008392334</v>
+        <v>30.11149997711182</v>
       </c>
       <c r="Y2" t="n">
-        <v>27.92700817259333</v>
+        <v>27.82995396372218</v>
       </c>
       <c r="Z2" t="n">
-        <v>9032901589.897423</v>
+        <v>3914383806.577148</v>
       </c>
     </row>
     <row r="3">
@@ -649,16 +649,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.434723459059454</v>
+        <v>1.401493652785652</v>
       </c>
       <c r="D3" t="n">
-        <v>1.04209788083989</v>
+        <v>1.042003473458267</v>
       </c>
       <c r="E3" t="n">
-        <v>41.29999923706055</v>
+        <v>40.77000045776367</v>
       </c>
       <c r="F3" t="n">
-        <v>81.68000000000001</v>
+        <v>74.61</v>
       </c>
       <c r="G3" t="n">
         <v>67</v>
@@ -673,7 +673,7 @@
         <v>10.44776119402985</v>
       </c>
       <c r="K3" t="n">
-        <v>6999245.75</v>
+        <v>7434694.3</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
@@ -692,7 +692,7 @@
         <v>151.1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.392625578219564</v>
+        <v>0.359490179327385</v>
       </c>
       <c r="S3" t="n">
         <v>0.78</v>
@@ -704,19 +704,19 @@
         <v>700</v>
       </c>
       <c r="V3" t="n">
-        <v>1.061874068706451</v>
+        <v>1.043765448636372</v>
       </c>
       <c r="W3" t="n">
-        <v>1.15756259006224</v>
+        <v>1.138192219514847</v>
       </c>
       <c r="X3" t="n">
-        <v>38.8935001373291</v>
+        <v>39.0605001449585</v>
       </c>
       <c r="Y3" t="n">
-        <v>35.67841565685008</v>
+        <v>35.81996059957415</v>
       </c>
       <c r="Z3" t="n">
-        <v>842863022.2296982</v>
+        <v>507122013.0839424</v>
       </c>
     </row>
     <row r="4">
@@ -731,16 +731,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.812583607435554</v>
+        <v>2.798674672828787</v>
       </c>
       <c r="D4" t="n">
-        <v>2.596870790978858</v>
+        <v>2.598408444160768</v>
       </c>
       <c r="E4" t="n">
-        <v>92.90000152587891</v>
+        <v>92.55000305175781</v>
       </c>
       <c r="F4" t="n">
-        <v>94.5</v>
+        <v>92.41</v>
       </c>
       <c r="G4" t="n">
         <v>489</v>
@@ -755,7 +755,7 @@
         <v>12.34560327198364</v>
       </c>
       <c r="K4" t="n">
-        <v>6912740.4</v>
+        <v>7113180.55</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
@@ -774,7 +774,7 @@
         <v>19.93</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2157128164566959</v>
+        <v>0.2002662286680184</v>
       </c>
       <c r="S4" t="n">
         <v>17.71</v>
@@ -786,19 +786,19 @@
         <v>6037</v>
       </c>
       <c r="V4" t="n">
-        <v>1.095486592690261</v>
+        <v>1.083945808204952</v>
       </c>
       <c r="W4" t="n">
-        <v>1.21190296230218</v>
+        <v>1.205436143067745</v>
       </c>
       <c r="X4" t="n">
-        <v>84.80249977111816</v>
+        <v>85.38250007629395</v>
       </c>
       <c r="Y4" t="n">
-        <v>76.65630369398743</v>
+        <v>76.77719270655432</v>
       </c>
       <c r="Z4" t="n">
-        <v>738496299.3297729</v>
+        <v>835976227.4656067</v>
       </c>
     </row>
     <row r="5">
@@ -813,16 +813,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.45207912237185</v>
+        <v>17.53933143626826</v>
       </c>
       <c r="D5" t="n">
-        <v>3.858061559756839</v>
+        <v>3.860668235177411</v>
       </c>
       <c r="E5" t="n">
-        <v>41.54000091552734</v>
+        <v>41.75</v>
       </c>
       <c r="F5" t="n">
-        <v>90.38</v>
+        <v>91.91</v>
       </c>
       <c r="G5" t="n">
         <v>618</v>
@@ -837,7 +837,7 @@
         <v>12.48705501618123</v>
       </c>
       <c r="K5" t="n">
-        <v>159414795.35</v>
+        <v>156867081.95</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
@@ -856,7 +856,7 @@
         <v>16.33</v>
       </c>
       <c r="R5" t="n">
-        <v>13.59401756261501</v>
+        <v>13.67866320109085</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -868,1331 +868,1249 @@
         <v>7717</v>
       </c>
       <c r="V5" t="n">
-        <v>1.099538116649976</v>
+        <v>1.097673178126291</v>
       </c>
       <c r="W5" t="n">
-        <v>1.200996893898137</v>
+        <v>1.211734547037765</v>
       </c>
       <c r="X5" t="n">
-        <v>37.77950057983399</v>
+        <v>38.03500061035156</v>
       </c>
       <c r="Y5" t="n">
-        <v>34.5879336795775</v>
+        <v>34.45474101738128</v>
       </c>
       <c r="Z5" t="n">
-        <v>11427643493.00134</v>
+        <v>4089299482.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>00904.TW</t>
+          <t>00913.TW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>台新臺灣半導體30</t>
+          <t>兆豐台灣晶圓製造</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2.042329286411374</v>
+        <v>1.945886635804311</v>
       </c>
       <c r="D6" t="n">
-        <v>1.924449686178473</v>
+        <v>1.826816215451943</v>
       </c>
       <c r="E6" t="n">
-        <v>44.9900016784668</v>
+        <v>54</v>
       </c>
       <c r="F6" t="n">
-        <v>88.84999999999999</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>231</v>
+        <v>263</v>
       </c>
       <c r="H6" t="n">
-        <v>100</v>
+        <v>96.95999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>3.71</v>
+        <v>3.53</v>
       </c>
       <c r="J6" t="n">
-        <v>10.48917748917749</v>
+        <v>12.54372623574145</v>
       </c>
       <c r="K6" t="n">
-        <v>1221924.95</v>
+        <v>1521846.15</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>2</v>
       </c>
       <c r="N6" t="n">
-        <v>11.85</v>
+        <v>13.5</v>
       </c>
       <c r="O6" t="n">
-        <v>0.09</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>11.94</v>
+        <v>4.039999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>40.54</v>
+        <v>29.41</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1178796002329014</v>
+        <v>0.1190704203523678</v>
       </c>
       <c r="S6" t="n">
-        <v>4.850000000000001</v>
+        <v>6.699999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>857.38</v>
+        <v>928.22</v>
       </c>
       <c r="U6" t="n">
-        <v>2423</v>
+        <v>3299</v>
       </c>
       <c r="V6" t="n">
-        <v>1.063354611950043</v>
+        <v>1.056875565529021</v>
       </c>
       <c r="W6" t="n">
-        <v>1.134107209346856</v>
+        <v>1.15235488363484</v>
       </c>
       <c r="X6" t="n">
-        <v>42.30949974060059</v>
+        <v>51.0939998626709</v>
       </c>
       <c r="Y6" t="n">
-        <v>39.66997238680548</v>
+        <v>46.86056419500679</v>
       </c>
       <c r="Z6" t="n">
-        <v>172723769.8539009</v>
+        <v>62830674</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>00913.TW</t>
+          <t>00685L.TW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>兆豐台灣晶圓製造</t>
+          <t>群益臺灣加權正2</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.975194484945144</v>
+        <v>12.11366180313551</v>
       </c>
       <c r="D7" t="n">
-        <v>1.826242026597972</v>
+        <v>3.168647196339564</v>
       </c>
       <c r="E7" t="n">
-        <v>54.54999923706055</v>
+        <v>13.84000015258789</v>
       </c>
       <c r="F7" t="n">
-        <v>83.34</v>
+        <v>91.95</v>
       </c>
       <c r="G7" t="n">
-        <v>263</v>
+        <v>526</v>
       </c>
       <c r="H7" t="n">
-        <v>96.95999999999999</v>
+        <v>87.45</v>
       </c>
       <c r="I7" t="n">
-        <v>3.53</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
-        <v>12.54372623574145</v>
+        <v>12.24524714828897</v>
       </c>
       <c r="K7" t="n">
-        <v>1497502.8</v>
+        <v>198253962.6</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>2</v>
       </c>
       <c r="N7" t="n">
-        <v>13.5</v>
+        <v>15.89</v>
       </c>
       <c r="O7" t="n">
-        <v>-9.460000000000001</v>
+        <v>-18.5</v>
       </c>
       <c r="P7" t="n">
-        <v>4.039999999999999</v>
+        <v>-2.609999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>29.41</v>
+        <v>17.94</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1489524583471722</v>
+        <v>8.945014606795947</v>
       </c>
       <c r="S7" t="n">
-        <v>6.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>928.22</v>
+        <v>1738.26</v>
       </c>
       <c r="U7" t="n">
-        <v>3299</v>
+        <v>6441</v>
       </c>
       <c r="V7" t="n">
-        <v>1.074368760912484</v>
+        <v>1.101340866529352</v>
       </c>
       <c r="W7" t="n">
-        <v>1.173112197842067</v>
+        <v>1.221195306851143</v>
       </c>
       <c r="X7" t="n">
-        <v>50.77399978637695</v>
+        <v>12.56650013923645</v>
       </c>
       <c r="Y7" t="n">
-        <v>46.50024041809891</v>
+        <v>11.33315864787786</v>
       </c>
       <c r="Z7" t="n">
-        <v>162985960.5704689</v>
+        <v>1812578746.623928</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>00685L.TW</t>
+          <t>00715L.TW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>群益臺灣加權正2</t>
+          <t>期街口布蘭特正2</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12.04304935075706</v>
+        <v>4.617168475207561</v>
       </c>
       <c r="D8" t="n">
-        <v>3.166605229921184</v>
+        <v>3.014992477251937</v>
       </c>
       <c r="E8" t="n">
-        <v>13.76000022888184</v>
+        <v>69.90000152587891</v>
       </c>
       <c r="F8" t="n">
-        <v>89.84999999999999</v>
+        <v>72.02</v>
       </c>
       <c r="G8" t="n">
-        <v>526</v>
+        <v>433</v>
       </c>
       <c r="H8" t="n">
-        <v>87.45</v>
+        <v>78.75</v>
       </c>
       <c r="I8" t="n">
         <v>3.3</v>
       </c>
       <c r="J8" t="n">
-        <v>12.24524714828897</v>
+        <v>17.10392609699769</v>
       </c>
       <c r="K8" t="n">
-        <v>202252599.2</v>
+        <v>4762384</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>15.89</v>
+        <v>32.14</v>
       </c>
       <c r="O8" t="n">
-        <v>-18.5</v>
+        <v>-45.45</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.609999999999999</v>
+        <v>-13.31</v>
       </c>
       <c r="Q8" t="n">
-        <v>17.94</v>
+        <v>14.39</v>
       </c>
       <c r="R8" t="n">
-        <v>8.87644412083587</v>
+        <v>1.602175997955624</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1738.26</v>
+        <v>1430.47</v>
       </c>
       <c r="U8" t="n">
-        <v>6441</v>
+        <v>7406</v>
       </c>
       <c r="V8" t="n">
-        <v>1.102475769367826</v>
+        <v>1.057208778385313</v>
       </c>
       <c r="W8" t="n">
-        <v>1.208821734564203</v>
+        <v>1.207668377880776</v>
       </c>
       <c r="X8" t="n">
-        <v>12.4810001373291</v>
+        <v>66.11750011444092</v>
       </c>
       <c r="Y8" t="n">
-        <v>11.38298546050093</v>
+        <v>57.88012902063386</v>
       </c>
       <c r="Z8" t="n">
-        <v>3667122799.878386</v>
+        <v>113613365.4801178</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>00715L.TW</t>
+          <t>00675L.TW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>期街口布蘭特正2</t>
+          <t>富邦臺灣加權正2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4.619301116535601</v>
+        <v>12.83061509190995</v>
       </c>
       <c r="D9" t="n">
-        <v>3.013094419387573</v>
+        <v>3.303356364079289</v>
       </c>
       <c r="E9" t="n">
-        <v>69.90000152587891</v>
+        <v>366.25</v>
       </c>
       <c r="F9" t="n">
-        <v>65.45999999999999</v>
+        <v>92.27</v>
       </c>
       <c r="G9" t="n">
-        <v>429</v>
+        <v>555</v>
       </c>
       <c r="H9" t="n">
-        <v>78.55</v>
+        <v>86.31</v>
       </c>
       <c r="I9" t="n">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
       <c r="J9" t="n">
-        <v>17.20745920745921</v>
+        <v>12.35135135135135</v>
       </c>
       <c r="K9" t="n">
-        <v>4906142.15</v>
+        <v>956251.75</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>32.14</v>
+        <v>15.7</v>
       </c>
       <c r="O9" t="n">
-        <v>-45.45</v>
+        <v>-24.73</v>
       </c>
       <c r="P9" t="n">
-        <v>-13.31</v>
+        <v>-9.030000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>14.29</v>
+        <v>16.91</v>
       </c>
       <c r="R9" t="n">
-        <v>1.606206697148028</v>
+        <v>9.527258727830656</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1389.98</v>
+        <v>1779.77</v>
       </c>
       <c r="U9" t="n">
-        <v>7382</v>
+        <v>6855</v>
       </c>
       <c r="V9" t="n">
-        <v>1.067623834207527</v>
+        <v>1.099932412237883</v>
       </c>
       <c r="W9" t="n">
-        <v>1.236494703294306</v>
+        <v>1.218770863301016</v>
       </c>
       <c r="X9" t="n">
-        <v>65.47250003814698</v>
+        <v>332.9750045776367</v>
       </c>
       <c r="Y9" t="n">
-        <v>56.53077311180488</v>
+        <v>300.5076762403224</v>
       </c>
       <c r="Z9" t="n">
-        <v>137522870.7020493</v>
+        <v>364802580</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>00675L.TW</t>
+          <t>00935.TW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>富邦臺灣加權正2</t>
+          <t>野村臺灣新科技50</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12.76787946198546</v>
+        <v>1.722376052922168</v>
       </c>
       <c r="D10" t="n">
-        <v>3.301201567177383</v>
+        <v>1.311971794120206</v>
       </c>
       <c r="E10" t="n">
-        <v>364.4500122070312</v>
+        <v>62.95000076293945</v>
       </c>
       <c r="F10" t="n">
-        <v>90.06999999999999</v>
+        <v>84.67</v>
       </c>
       <c r="G10" t="n">
-        <v>555</v>
+        <v>137</v>
       </c>
       <c r="H10" t="n">
-        <v>86.31</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>3.21</v>
+        <v>3.14</v>
       </c>
       <c r="J10" t="n">
-        <v>12.35135135135135</v>
+        <v>12.38686131386861</v>
       </c>
       <c r="K10" t="n">
-        <v>964512.05</v>
+        <v>11388579.65</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>15.7</v>
+        <v>14.6</v>
       </c>
       <c r="O10" t="n">
-        <v>-24.73</v>
+        <v>-8.99</v>
       </c>
       <c r="P10" t="n">
-        <v>-9.030000000000001</v>
+        <v>5.609999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>16.91</v>
+        <v>43.19</v>
       </c>
       <c r="R10" t="n">
-        <v>9.466677894808077</v>
+        <v>0.4104042588019614</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="T10" t="n">
-        <v>1779.77</v>
+        <v>430.76</v>
       </c>
       <c r="U10" t="n">
-        <v>6855</v>
+        <v>1697</v>
       </c>
       <c r="V10" t="n">
-        <v>1.1018396983832</v>
+        <v>1.048380392754674</v>
       </c>
       <c r="W10" t="n">
-        <v>1.207452796319666</v>
+        <v>1.120679985087959</v>
       </c>
       <c r="X10" t="n">
-        <v>330.7650039672852</v>
+        <v>60.04500007629395</v>
       </c>
       <c r="Y10" t="n">
-        <v>301.8337555868687</v>
+        <v>56.17125459593063</v>
       </c>
       <c r="Z10" t="n">
-        <v>744825032.1474609</v>
+        <v>643763281.7522621</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>00935.TW</t>
+          <t>00894.TW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>野村臺灣新科技50</t>
+          <t>中信小資高價30</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.749162911191024</v>
+        <v>2.339797917594175</v>
       </c>
       <c r="D11" t="n">
-        <v>1.311843173966012</v>
+        <v>1.983868165852523</v>
       </c>
       <c r="E11" t="n">
-        <v>63.54999923706055</v>
+        <v>52.20000076293945</v>
       </c>
       <c r="F11" t="n">
-        <v>87.13</v>
+        <v>86.31</v>
       </c>
       <c r="G11" t="n">
-        <v>137</v>
+        <v>243</v>
       </c>
       <c r="H11" t="n">
-        <v>83.20999999999999</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="J11" t="n">
-        <v>12.38686131386861</v>
+        <v>15.33333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>11313647.05</v>
+        <v>1128135.45</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>14.6</v>
+        <v>15.7</v>
       </c>
       <c r="O11" t="n">
-        <v>-8.99</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>5.609999999999999</v>
+        <v>7.319999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>43.19</v>
+        <v>22.72</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4373197372250113</v>
+        <v>0.3559297517416522</v>
       </c>
       <c r="S11" t="n">
-        <v>4.98</v>
+        <v>7.549999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>430.76</v>
+        <v>708.49</v>
       </c>
       <c r="U11" t="n">
-        <v>1697</v>
+        <v>3726</v>
       </c>
       <c r="V11" t="n">
-        <v>1.062176151019624</v>
+        <v>1.068172757758279</v>
       </c>
       <c r="W11" t="n">
-        <v>1.131735048794595</v>
+        <v>1.153132774849284</v>
       </c>
       <c r="X11" t="n">
-        <v>59.83000011444092</v>
+        <v>48.86850032806397</v>
       </c>
       <c r="Y11" t="n">
-        <v>56.15271816910441</v>
+        <v>45.26798812891435</v>
       </c>
       <c r="Z11" t="n">
-        <v>755592268.8788567</v>
+        <v>37343410.74580002</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>00894.TW</t>
+          <t>00901.TW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>中信小資高價30</t>
+          <t>永豐智能車供應鏈</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.37325183336789</v>
+        <v>2.053006756834229</v>
       </c>
       <c r="D12" t="n">
-        <v>1.982954182806191</v>
+        <v>1.943918016282015</v>
       </c>
       <c r="E12" t="n">
-        <v>52.75</v>
+        <v>50</v>
       </c>
       <c r="F12" t="n">
-        <v>89.72</v>
+        <v>84.83</v>
       </c>
       <c r="G12" t="n">
-        <v>243</v>
+        <v>269</v>
       </c>
       <c r="H12" t="n">
-        <v>83.54000000000001</v>
+        <v>90.33</v>
       </c>
       <c r="I12" t="n">
-        <v>2.92</v>
+        <v>2.79</v>
       </c>
       <c r="J12" t="n">
-        <v>15.33333333333333</v>
+        <v>13.22304832713755</v>
       </c>
       <c r="K12" t="n">
-        <v>1109638.05</v>
+        <v>285490.55</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>15.7</v>
+        <v>15.18</v>
       </c>
       <c r="O12" t="n">
-        <v>-8.380000000000001</v>
+        <v>-7.07</v>
       </c>
       <c r="P12" t="n">
-        <v>7.319999999999999</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>22.72</v>
+        <v>24.56</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3902976505617</v>
+        <v>0.1090887405522136</v>
       </c>
       <c r="S12" t="n">
-        <v>7.549999999999999</v>
+        <v>4.671</v>
       </c>
       <c r="T12" t="n">
-        <v>708.49</v>
+        <v>750.16</v>
       </c>
       <c r="U12" t="n">
-        <v>3726</v>
+        <v>3557</v>
       </c>
       <c r="V12" t="n">
-        <v>1.084732513902628</v>
+        <v>1.053851818265042</v>
       </c>
       <c r="W12" t="n">
-        <v>1.163876439311488</v>
+        <v>1.12104386161425</v>
       </c>
       <c r="X12" t="n">
-        <v>48.62950019836425</v>
+        <v>47.44500045776367</v>
       </c>
       <c r="Y12" t="n">
-        <v>45.32268049966302</v>
+        <v>44.60128788181613</v>
       </c>
       <c r="Z12" t="n">
-        <v>96415395</v>
+        <v>2326850</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>00901.TW</t>
+          <t>00881.TW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>永豐智能車供應鏈</t>
+          <t>國泰台灣科技龍頭</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.066175265086512</v>
+        <v>2.211707921748164</v>
       </c>
       <c r="D13" t="n">
-        <v>1.943112320989987</v>
+        <v>2.063970974969814</v>
       </c>
       <c r="E13" t="n">
-        <v>50.20000076293945</v>
+        <v>53.95000076293945</v>
       </c>
       <c r="F13" t="n">
-        <v>85.55</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>269</v>
+        <v>323</v>
       </c>
       <c r="H13" t="n">
-        <v>90.33</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>2.79</v>
+        <v>2.56</v>
       </c>
       <c r="J13" t="n">
-        <v>13.22304832713755</v>
+        <v>13.88854489164087</v>
       </c>
       <c r="K13" t="n">
-        <v>294014.45</v>
+        <v>15725001.5</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>2</v>
       </c>
       <c r="N13" t="n">
-        <v>15.18</v>
+        <v>10.9</v>
       </c>
       <c r="O13" t="n">
-        <v>-7.07</v>
+        <v>-7.15</v>
       </c>
       <c r="P13" t="n">
-        <v>8.109999999999999</v>
+        <v>3.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>24.56</v>
+        <v>19.85</v>
       </c>
       <c r="R13" t="n">
-        <v>0.123062944096525</v>
+        <v>0.1477369467783505</v>
       </c>
       <c r="S13" t="n">
-        <v>4.671</v>
+        <v>12.5</v>
       </c>
       <c r="T13" t="n">
-        <v>750.16</v>
+        <v>825.49</v>
       </c>
       <c r="U13" t="n">
-        <v>3557</v>
+        <v>4486</v>
       </c>
       <c r="V13" t="n">
-        <v>1.062107931093273</v>
+        <v>1.047857683622408</v>
       </c>
       <c r="W13" t="n">
-        <v>1.124481782888495</v>
+        <v>1.109342208211493</v>
       </c>
       <c r="X13" t="n">
-        <v>47.26450042724609</v>
+        <v>51.48600006103516</v>
       </c>
       <c r="Y13" t="n">
-        <v>44.6427870391897</v>
+        <v>48.63242411908124</v>
       </c>
       <c r="Z13" t="n">
-        <v>40112310.60962677</v>
+        <v>789098391.3591156</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>00881.TW</t>
+          <t>0057.TW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>國泰台灣科技龍頭</t>
+          <t>富邦摩台</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.238330076865061</v>
+        <v>6.350531944148929</v>
       </c>
       <c r="D14" t="n">
-        <v>2.062872865056776</v>
+        <v>3.329438380926038</v>
       </c>
       <c r="E14" t="n">
-        <v>54.45000076293945</v>
+        <v>345.6499938964844</v>
       </c>
       <c r="F14" t="n">
-        <v>84.73</v>
+        <v>90.03</v>
       </c>
       <c r="G14" t="n">
-        <v>323</v>
+        <v>1250</v>
       </c>
       <c r="H14" t="n">
-        <v>90.70999999999999</v>
+        <v>93.52</v>
       </c>
       <c r="I14" t="n">
-        <v>2.56</v>
+        <v>2.51</v>
       </c>
       <c r="J14" t="n">
-        <v>13.88854489164087</v>
+        <v>13.0928</v>
       </c>
       <c r="K14" t="n">
-        <v>15797318.6</v>
+        <v>21472.35</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>10.9</v>
+        <v>14.45</v>
       </c>
       <c r="O14" t="n">
-        <v>-7.15</v>
+        <v>-6.48</v>
       </c>
       <c r="P14" t="n">
-        <v>3.75</v>
+        <v>7.969999999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>19.85</v>
+        <v>8.06</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1754572118082849</v>
+        <v>3.021093563222891</v>
       </c>
       <c r="S14" t="n">
-        <v>12.5</v>
+        <v>1.685</v>
       </c>
       <c r="T14" t="n">
-        <v>825.49</v>
+        <v>3133.95</v>
       </c>
       <c r="U14" t="n">
-        <v>4486</v>
+        <v>16366</v>
       </c>
       <c r="V14" t="n">
-        <v>1.061279398503448</v>
+        <v>1.048623784045249</v>
       </c>
       <c r="W14" t="n">
-        <v>1.119231050758579</v>
+        <v>1.098652411638338</v>
       </c>
       <c r="X14" t="n">
-        <v>51.30599994659424</v>
+        <v>329.6225006103516</v>
       </c>
       <c r="Y14" t="n">
-        <v>48.64947298061018</v>
+        <v>314.6126930000021</v>
       </c>
       <c r="Z14" t="n">
-        <v>1826508396.092567</v>
+        <v>26615395.18002319</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0057.TW</t>
+          <t>0050.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>富邦摩台</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6.309587311255153</v>
+        <v>3.333369278556089</v>
       </c>
       <c r="D15" t="n">
-        <v>3.32673903121997</v>
+        <v>3.333369278556089</v>
       </c>
       <c r="E15" t="n">
-        <v>343.6499938964844</v>
+        <v>116.0500030517578</v>
       </c>
       <c r="F15" t="n">
-        <v>86.81999999999999</v>
+        <v>87.08</v>
       </c>
       <c r="G15" t="n">
-        <v>1250</v>
+        <v>1229</v>
       </c>
       <c r="H15" t="n">
-        <v>93.52</v>
+        <v>90.89</v>
       </c>
       <c r="I15" t="n">
-        <v>2.51</v>
+        <v>2.19</v>
       </c>
       <c r="J15" t="n">
-        <v>13.0928</v>
+        <v>13.92758340113914</v>
       </c>
       <c r="K15" t="n">
-        <v>19023.25</v>
+        <v>71696597.09999999</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>14.45</v>
+        <v>15.64</v>
       </c>
       <c r="O15" t="n">
-        <v>-6.48</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>7.969999999999999</v>
+        <v>6.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.06</v>
+        <v>7.36</v>
       </c>
       <c r="R15" t="n">
-        <v>2.982848280035182</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.685</v>
+        <v>13.505</v>
       </c>
       <c r="T15" t="n">
-        <v>3133.95</v>
+        <v>2696.19</v>
       </c>
       <c r="U15" t="n">
-        <v>16366</v>
+        <v>17117</v>
       </c>
       <c r="V15" t="n">
-        <v>1.046373523595314</v>
+        <v>1.048755160920291</v>
       </c>
       <c r="W15" t="n">
-        <v>1.091069629905982</v>
+        <v>1.10258946228618</v>
       </c>
       <c r="X15" t="n">
-        <v>328.4200012207031</v>
+        <v>110.6550006866455</v>
       </c>
       <c r="Y15" t="n">
-        <v>314.9661437520691</v>
+        <v>105.2522330579255</v>
       </c>
       <c r="Z15" t="n">
-        <v>14092055.29971313</v>
+        <v>7130391868.007355</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>0050.TW</t>
+          <t>0053.TW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>元大台灣50</t>
+          <t>元大電子</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3.330666428410618</v>
+        <v>6.933167466987578</v>
       </c>
       <c r="D16" t="n">
-        <v>3.330666428410618</v>
+        <v>3.333369278556089</v>
       </c>
       <c r="E16" t="n">
-        <v>115.9499969482422</v>
+        <v>262</v>
       </c>
       <c r="F16" t="n">
-        <v>85.17</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>1229</v>
+        <v>1145</v>
       </c>
       <c r="H16" t="n">
-        <v>90.89</v>
+        <v>90.31</v>
       </c>
       <c r="I16" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="J16" t="n">
-        <v>13.92758340113914</v>
+        <v>14.07598253275109</v>
       </c>
       <c r="K16" t="n">
-        <v>70838920</v>
+        <v>132094.25</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>15.64</v>
+        <v>10.88</v>
       </c>
       <c r="O16" t="n">
-        <v>-8.890000000000001</v>
+        <v>-8.44</v>
       </c>
       <c r="P16" t="n">
-        <v>6.75</v>
+        <v>2.440000000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.36</v>
+        <v>7.63</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>3.599798188431489</v>
       </c>
       <c r="S16" t="n">
-        <v>13.505</v>
+        <v>18.91</v>
       </c>
       <c r="T16" t="n">
-        <v>2696.19</v>
+        <v>2466.25</v>
       </c>
       <c r="U16" t="n">
-        <v>17117</v>
+        <v>16117</v>
       </c>
       <c r="V16" t="n">
-        <v>1.05172449539736</v>
+        <v>1.052282789024543</v>
       </c>
       <c r="W16" t="n">
-        <v>1.100869131799052</v>
+        <v>1.114629855235686</v>
       </c>
       <c r="X16" t="n">
-        <v>110.2475006103516</v>
+        <v>248.9825004577637</v>
       </c>
       <c r="Y16" t="n">
-        <v>105.3258680791199</v>
+        <v>235.0556095095808</v>
       </c>
       <c r="Z16" t="n">
-        <v>11331790534.90178</v>
+        <v>44349002</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>0053.TW</t>
+          <t>00735.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>元大電子</t>
+          <t>國泰臺韓科技</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6.963338122068993</v>
+        <v>3.387155723263836</v>
       </c>
       <c r="D17" t="n">
-        <v>3.330666428410618</v>
+        <v>2.881301195683998</v>
       </c>
       <c r="E17" t="n">
-        <v>263</v>
+        <v>111.1999969482422</v>
       </c>
       <c r="F17" t="n">
-        <v>87.15000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>1145</v>
+        <v>480</v>
       </c>
       <c r="H17" t="n">
-        <v>90.31</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="J17" t="n">
-        <v>14.07598253275109</v>
+        <v>14.04583333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>124580.7</v>
+        <v>1295597</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>10.88</v>
+        <v>21.39</v>
       </c>
       <c r="O17" t="n">
-        <v>-8.44</v>
+        <v>-8.82</v>
       </c>
       <c r="P17" t="n">
-        <v>2.440000000000001</v>
+        <v>12.57</v>
       </c>
       <c r="Q17" t="n">
-        <v>7.63</v>
+        <v>13.92</v>
       </c>
       <c r="R17" t="n">
-        <v>3.632671693658375</v>
+        <v>0.5058545275798378</v>
       </c>
       <c r="S17" t="n">
-        <v>18.91</v>
+        <v>13.37</v>
       </c>
       <c r="T17" t="n">
-        <v>2466.25</v>
+        <v>1011.13</v>
       </c>
       <c r="U17" t="n">
-        <v>16117</v>
+        <v>6742</v>
       </c>
       <c r="V17" t="n">
-        <v>1.060205993744484</v>
+        <v>1.040200156089194</v>
       </c>
       <c r="W17" t="n">
-        <v>1.117618135851378</v>
+        <v>1.103825447300063</v>
       </c>
       <c r="X17" t="n">
-        <v>248.0650001525879</v>
+        <v>106.9024997711182</v>
       </c>
       <c r="Y17" t="n">
-        <v>235.3218792388799</v>
+        <v>100.7405629397613</v>
       </c>
       <c r="Z17" t="n">
-        <v>52502427</v>
+        <v>164205477.0935669</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>00735.TW</t>
+          <t>006203.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>國泰臺韓科技</t>
+          <t>元大MSCI台灣</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3.425017075369201</v>
+        <v>4.590288135786347</v>
       </c>
       <c r="D18" t="n">
-        <v>2.879530295412196</v>
+        <v>3.590101088316084</v>
       </c>
       <c r="E18" t="n">
-        <v>112.1999969482422</v>
+        <v>210.3500061035156</v>
       </c>
       <c r="F18" t="n">
-        <v>81.37</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>480</v>
+        <v>1041</v>
       </c>
       <c r="H18" t="n">
-        <v>84.79000000000001</v>
+        <v>90.78</v>
       </c>
       <c r="I18" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="J18" t="n">
-        <v>14.04583333333333</v>
+        <v>12.95965417867435</v>
       </c>
       <c r="K18" t="n">
-        <v>1299952.35</v>
+        <v>9753.6</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>21.39</v>
+        <v>8.85</v>
       </c>
       <c r="O18" t="n">
-        <v>-8.82</v>
+        <v>-7.69</v>
       </c>
       <c r="P18" t="n">
-        <v>12.57</v>
+        <v>1.159999999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>13.92</v>
+        <v>8.81</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5454867799570047</v>
+        <v>1.000187047470263</v>
       </c>
       <c r="S18" t="n">
-        <v>13.37</v>
+        <v>21.88</v>
       </c>
       <c r="T18" t="n">
-        <v>1011.13</v>
+        <v>2169.48</v>
       </c>
       <c r="U18" t="n">
-        <v>6742</v>
+        <v>13491</v>
       </c>
       <c r="V18" t="n">
-        <v>1.053076135603725</v>
+        <v>1.047455460731145</v>
       </c>
       <c r="W18" t="n">
-        <v>1.115353671425007</v>
+        <v>1.096536007248379</v>
       </c>
       <c r="X18" t="n">
-        <v>106.5450000762939</v>
+        <v>200.8200004577637</v>
       </c>
       <c r="Y18" t="n">
-        <v>100.5958915299865</v>
+        <v>191.8313714397422</v>
       </c>
       <c r="Z18" t="n">
-        <v>179211220.7255859</v>
+        <v>4156516.120605469</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>006203.TW</t>
+          <t>006208.TW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>元大MSCI台灣</t>
+          <t>富邦台50</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4.554652994076354</v>
+        <v>4.572198218429223</v>
       </c>
       <c r="D19" t="n">
-        <v>3.587366007796832</v>
+        <v>3.772400118059388</v>
       </c>
       <c r="E19" t="n">
-        <v>208.8500061035156</v>
+        <v>265.6000061035156</v>
       </c>
       <c r="F19" t="n">
-        <v>86.73999999999999</v>
+        <v>89.31</v>
       </c>
       <c r="G19" t="n">
-        <v>1041</v>
+        <v>1012</v>
       </c>
       <c r="H19" t="n">
-        <v>90.78</v>
+        <v>89.23</v>
       </c>
       <c r="I19" t="n">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="J19" t="n">
-        <v>12.95965417867435</v>
+        <v>13.89624505928854</v>
       </c>
       <c r="K19" t="n">
-        <v>9116.049999999999</v>
+        <v>1945910.75</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>8.85</v>
+        <v>11.21</v>
       </c>
       <c r="O19" t="n">
-        <v>-7.69</v>
+        <v>-6.25</v>
       </c>
       <c r="P19" t="n">
-        <v>1.159999999999999</v>
+        <v>4.960000000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>8.81</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9672869862795226</v>
+        <v>0.7997981003698351</v>
       </c>
       <c r="S19" t="n">
-        <v>21.88</v>
+        <v>28.764</v>
       </c>
       <c r="T19" t="n">
-        <v>2169.48</v>
+        <v>1914.21</v>
       </c>
       <c r="U19" t="n">
-        <v>13491</v>
+        <v>14063</v>
       </c>
       <c r="V19" t="n">
-        <v>1.043767286554884</v>
+        <v>1.049335796944423</v>
       </c>
       <c r="W19" t="n">
-        <v>1.087783454122587</v>
+        <v>1.103282763015944</v>
       </c>
       <c r="X19" t="n">
-        <v>200.0925003051758</v>
+        <v>253.1124992370605</v>
       </c>
       <c r="Y19" t="n">
-        <v>191.9959393682591</v>
+        <v>240.7361149896596</v>
       </c>
       <c r="Z19" t="n">
-        <v>4179088.622131348</v>
+        <v>364865617.9846497</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>006208.TW</t>
+          <t>0051.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>富邦台50</t>
+          <t>元大中型100</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4.56867464219185</v>
+        <v>3.822304591553163</v>
       </c>
       <c r="D20" t="n">
-        <v>3.769644201915613</v>
+        <v>3.333369278556089</v>
       </c>
       <c r="E20" t="n">
-        <v>265.3500061035156</v>
+        <v>153.1499938964844</v>
       </c>
       <c r="F20" t="n">
-        <v>87.13</v>
+        <v>91.98999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>1012</v>
+        <v>1121</v>
       </c>
       <c r="H20" t="n">
-        <v>89.23</v>
+        <v>88.84999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>1.89</v>
+        <v>1.71</v>
       </c>
       <c r="J20" t="n">
-        <v>13.89624505928854</v>
+        <v>15.42908117752007</v>
       </c>
       <c r="K20" t="n">
-        <v>1943759.2</v>
+        <v>46768.6</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
         <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>11.21</v>
+        <v>10</v>
       </c>
       <c r="O20" t="n">
-        <v>-6.25</v>
+        <v>-10.68</v>
       </c>
       <c r="P20" t="n">
-        <v>4.960000000000001</v>
+        <v>-0.6799999999999997</v>
       </c>
       <c r="Q20" t="n">
-        <v>8.109999999999999</v>
+        <v>6.55</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7990304402762369</v>
+        <v>0.4889353129970742</v>
       </c>
       <c r="S20" t="n">
-        <v>28.764</v>
+        <v>19.36</v>
       </c>
       <c r="T20" t="n">
-        <v>1914.21</v>
+        <v>1920.98</v>
       </c>
       <c r="U20" t="n">
-        <v>14063</v>
+        <v>17296</v>
       </c>
       <c r="V20" t="n">
-        <v>1.052162046144237</v>
+        <v>1.042741112567663</v>
       </c>
       <c r="W20" t="n">
-        <v>1.101071205442985</v>
+        <v>1.086242390318209</v>
       </c>
       <c r="X20" t="n">
-        <v>252.1949989318848</v>
+        <v>146.8724998474121</v>
       </c>
       <c r="Y20" t="n">
-        <v>240.9925941136201</v>
+        <v>140.9906253535363</v>
       </c>
       <c r="Z20" t="n">
-        <v>1087221233.507996</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>0051.TW</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>元大中型100</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>3.80321487131572</v>
-      </c>
-      <c r="D21" t="n">
-        <v>3.330666428410618</v>
-      </c>
-      <c r="E21" t="n">
-        <v>152.4499969482422</v>
-      </c>
-      <c r="F21" t="n">
-        <v>89.61</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1121</v>
-      </c>
-      <c r="H21" t="n">
-        <v>88.84999999999999</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="J21" t="n">
-        <v>15.42908117752007</v>
-      </c>
-      <c r="K21" t="n">
-        <v>46162.3</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="n">
-        <v>2</v>
-      </c>
-      <c r="N21" t="n">
-        <v>10</v>
-      </c>
-      <c r="O21" t="n">
-        <v>-10.68</v>
-      </c>
-      <c r="P21" t="n">
-        <v>-0.6799999999999997</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.4725484429051017</v>
-      </c>
-      <c r="S21" t="n">
-        <v>19.36</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1920.98</v>
-      </c>
-      <c r="U21" t="n">
-        <v>17296</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.040525531597933</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.078317653425235</v>
-      </c>
-      <c r="X21" t="n">
-        <v>146.5125</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>141.3776325222818</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>11914881.96148682</v>
+        <v>6500757.790924072</v>
       </c>
     </row>
   </sheetData>

--- a/ETF動態清單.xlsx
+++ b/ETF動態清單.xlsx
@@ -567,16 +567,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9427785253009235</v>
+        <v>0.9388510870058571</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6917177283960629</v>
+        <v>0.6738706180943519</v>
       </c>
       <c r="E2" t="n">
-        <v>32.2599983215332</v>
+        <v>32.2400016784668</v>
       </c>
       <c r="F2" t="n">
-        <v>88.14</v>
+        <v>87.67</v>
       </c>
       <c r="G2" t="n">
         <v>42</v>
@@ -591,7 +591,7 @@
         <v>8.761904761904763</v>
       </c>
       <c r="K2" t="n">
-        <v>154716695.45</v>
+        <v>151109633.2</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
@@ -610,7 +610,7 @@
         <v>347.51</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2510607969048606</v>
+        <v>0.2649804689115052</v>
       </c>
       <c r="S2" t="n">
         <v>1.67</v>
@@ -622,19 +622,19 @@
         <v>368</v>
       </c>
       <c r="V2" t="n">
-        <v>1.071351422083074</v>
+        <v>1.066331563280116</v>
       </c>
       <c r="W2" t="n">
-        <v>1.159182597412336</v>
+        <v>1.163422729991732</v>
       </c>
       <c r="X2" t="n">
-        <v>30.11149997711182</v>
+        <v>30.23450002670288</v>
       </c>
       <c r="Y2" t="n">
-        <v>27.82995396372218</v>
+        <v>27.71133900632654</v>
       </c>
       <c r="Z2" t="n">
-        <v>3914383806.577148</v>
+        <v>3190723392.194237</v>
       </c>
     </row>
     <row r="3">
@@ -649,16 +649,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.401493652785652</v>
+        <v>1.392659348264567</v>
       </c>
       <c r="D3" t="n">
-        <v>1.042003473458267</v>
+        <v>1.021155905208836</v>
       </c>
       <c r="E3" t="n">
-        <v>40.77000045776367</v>
+        <v>40.65999984741211</v>
       </c>
       <c r="F3" t="n">
-        <v>74.61</v>
+        <v>72.65000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>67</v>
@@ -673,7 +673,7 @@
         <v>10.44776119402985</v>
       </c>
       <c r="K3" t="n">
-        <v>7434694.3</v>
+        <v>7140320.05</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
@@ -692,7 +692,7 @@
         <v>151.1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.359490179327385</v>
+        <v>0.3715034430557314</v>
       </c>
       <c r="S3" t="n">
         <v>0.78</v>
@@ -704,19 +704,19 @@
         <v>700</v>
       </c>
       <c r="V3" t="n">
-        <v>1.043765448636372</v>
+        <v>1.037655188167393</v>
       </c>
       <c r="W3" t="n">
-        <v>1.138192219514847</v>
+        <v>1.134408478038682</v>
       </c>
       <c r="X3" t="n">
-        <v>39.0605001449585</v>
+        <v>39.18450012207031</v>
       </c>
       <c r="Y3" t="n">
-        <v>35.81996059957415</v>
+        <v>35.84246824187225</v>
       </c>
       <c r="Z3" t="n">
-        <v>507122013.0839424</v>
+        <v>277525398.1985092</v>
       </c>
     </row>
     <row r="4">
@@ -731,16 +731,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.798674672828787</v>
+        <v>2.774188886223059</v>
       </c>
       <c r="D4" t="n">
-        <v>2.598408444160768</v>
+        <v>2.56433727154422</v>
       </c>
       <c r="E4" t="n">
-        <v>92.55000305175781</v>
+        <v>91.90000152587891</v>
       </c>
       <c r="F4" t="n">
-        <v>92.41</v>
+        <v>87.67</v>
       </c>
       <c r="G4" t="n">
         <v>489</v>
@@ -755,7 +755,7 @@
         <v>12.34560327198364</v>
       </c>
       <c r="K4" t="n">
-        <v>7113180.55</v>
+        <v>6803168.4</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
@@ -774,7 +774,7 @@
         <v>19.93</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2002662286680184</v>
+        <v>0.2098516146788389</v>
       </c>
       <c r="S4" t="n">
         <v>17.71</v>
@@ -786,19 +786,19 @@
         <v>6037</v>
       </c>
       <c r="V4" t="n">
-        <v>1.083945808204952</v>
+        <v>1.070908369993479</v>
       </c>
       <c r="W4" t="n">
-        <v>1.205436143067745</v>
+        <v>1.196445938242432</v>
       </c>
       <c r="X4" t="n">
-        <v>85.38250007629395</v>
+        <v>85.81499977111817</v>
       </c>
       <c r="Y4" t="n">
-        <v>76.77719270655432</v>
+        <v>76.81082662278845</v>
       </c>
       <c r="Z4" t="n">
-        <v>835976227.4656067</v>
+        <v>531219687.8202057</v>
       </c>
     </row>
     <row r="5">
@@ -813,16 +813,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.53933143626826</v>
+        <v>17.15598799386017</v>
       </c>
       <c r="D5" t="n">
-        <v>3.860668235177411</v>
+        <v>3.816097521941979</v>
       </c>
       <c r="E5" t="n">
-        <v>41.75</v>
+        <v>40.90000152587891</v>
       </c>
       <c r="F5" t="n">
-        <v>91.91</v>
+        <v>86.88</v>
       </c>
       <c r="G5" t="n">
         <v>618</v>
@@ -837,7 +837,7 @@
         <v>12.48705501618123</v>
       </c>
       <c r="K5" t="n">
-        <v>156867081.95</v>
+        <v>153079164.1</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
@@ -856,7 +856,7 @@
         <v>16.33</v>
       </c>
       <c r="R5" t="n">
-        <v>13.67866320109085</v>
+        <v>13.33989047191819</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -868,19 +868,19 @@
         <v>7717</v>
       </c>
       <c r="V5" t="n">
-        <v>1.097673178126291</v>
+        <v>1.070820809829904</v>
       </c>
       <c r="W5" t="n">
-        <v>1.211734547037765</v>
+        <v>1.189679780734052</v>
       </c>
       <c r="X5" t="n">
-        <v>38.03500061035156</v>
+        <v>38.19500064849854</v>
       </c>
       <c r="Y5" t="n">
-        <v>34.45474101738128</v>
+        <v>34.3790002891727</v>
       </c>
       <c r="Z5" t="n">
-        <v>4089299482.75</v>
+        <v>6000728754.972496</v>
       </c>
     </row>
     <row r="6">
@@ -895,16 +895,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.945886635804311</v>
+        <v>1.916622816221098</v>
       </c>
       <c r="D6" t="n">
-        <v>1.826816215451943</v>
+        <v>1.79894556917569</v>
       </c>
       <c r="E6" t="n">
-        <v>54</v>
+        <v>53.45000076293945</v>
       </c>
       <c r="F6" t="n">
-        <v>77.93000000000001</v>
+        <v>70.66</v>
       </c>
       <c r="G6" t="n">
         <v>263</v>
@@ -919,7 +919,7 @@
         <v>12.54372623574145</v>
       </c>
       <c r="K6" t="n">
-        <v>1521846.15</v>
+        <v>1504326.75</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
@@ -938,7 +938,7 @@
         <v>29.41</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1190704203523678</v>
+        <v>0.1176772470454077</v>
       </c>
       <c r="S6" t="n">
         <v>6.699999999999999</v>
@@ -950,183 +950,183 @@
         <v>3299</v>
       </c>
       <c r="V6" t="n">
-        <v>1.056875565529021</v>
+        <v>1.042337035946892</v>
       </c>
       <c r="W6" t="n">
-        <v>1.15235488363484</v>
+        <v>1.138819129605281</v>
       </c>
       <c r="X6" t="n">
-        <v>51.0939998626709</v>
+        <v>51.27899990081787</v>
       </c>
       <c r="Y6" t="n">
-        <v>46.86056419500679</v>
+        <v>46.93458282656827</v>
       </c>
       <c r="Z6" t="n">
-        <v>62830674</v>
+        <v>104889693.547184</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>00685L.TW</t>
+          <t>00715L.TW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>群益臺灣加權正2</t>
+          <t>期街口布蘭特正2</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12.11366180313551</v>
+        <v>4.735529111607426</v>
       </c>
       <c r="D7" t="n">
-        <v>3.168647196339564</v>
+        <v>2.977433125863245</v>
       </c>
       <c r="E7" t="n">
-        <v>13.84000015258789</v>
+        <v>71.40000152587891</v>
       </c>
       <c r="F7" t="n">
-        <v>91.95</v>
+        <v>78.83</v>
       </c>
       <c r="G7" t="n">
-        <v>526</v>
+        <v>433</v>
       </c>
       <c r="H7" t="n">
-        <v>87.45</v>
+        <v>78.75</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="J7" t="n">
-        <v>12.24524714828897</v>
+        <v>17.11316397228637</v>
       </c>
       <c r="K7" t="n">
-        <v>198253962.6</v>
+        <v>4638196.7</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>2</v>
       </c>
       <c r="N7" t="n">
-        <v>15.89</v>
+        <v>32.14</v>
       </c>
       <c r="O7" t="n">
-        <v>-18.5</v>
+        <v>-45.45</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.609999999999999</v>
+        <v>-13.31</v>
       </c>
       <c r="Q7" t="n">
-        <v>17.94</v>
+        <v>14.42</v>
       </c>
       <c r="R7" t="n">
-        <v>8.945014606795947</v>
+        <v>1.758095985744181</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1738.26</v>
+        <v>1439.93</v>
       </c>
       <c r="U7" t="n">
-        <v>6441</v>
+        <v>7410</v>
       </c>
       <c r="V7" t="n">
-        <v>1.101340866529352</v>
+        <v>1.070785863877282</v>
       </c>
       <c r="W7" t="n">
-        <v>1.221195306851143</v>
+        <v>1.213041363496872</v>
       </c>
       <c r="X7" t="n">
-        <v>12.56650013923645</v>
+        <v>66.68000011444092</v>
       </c>
       <c r="Y7" t="n">
-        <v>11.33315864787786</v>
+        <v>58.86031892601904</v>
       </c>
       <c r="Z7" t="n">
-        <v>1812578746.623928</v>
+        <v>166346152.7549591</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>00715L.TW</t>
+          <t>00685L.TW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>期街口布蘭特正2</t>
+          <t>群益臺灣加權正2</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4.617168475207561</v>
+        <v>11.81484141640059</v>
       </c>
       <c r="D8" t="n">
-        <v>3.014992477251937</v>
+        <v>3.129832866019241</v>
       </c>
       <c r="E8" t="n">
-        <v>69.90000152587891</v>
+        <v>13.52999973297119</v>
       </c>
       <c r="F8" t="n">
-        <v>72.02</v>
+        <v>86.27</v>
       </c>
       <c r="G8" t="n">
-        <v>433</v>
+        <v>526</v>
       </c>
       <c r="H8" t="n">
-        <v>78.75</v>
+        <v>87.45</v>
       </c>
       <c r="I8" t="n">
         <v>3.3</v>
       </c>
       <c r="J8" t="n">
-        <v>17.10392609699769</v>
+        <v>12.24524714828897</v>
       </c>
       <c r="K8" t="n">
-        <v>4762384</v>
+        <v>196613407.25</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>32.14</v>
+        <v>15.89</v>
       </c>
       <c r="O8" t="n">
-        <v>-45.45</v>
+        <v>-18.5</v>
       </c>
       <c r="P8" t="n">
-        <v>-13.31</v>
+        <v>-2.609999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>14.39</v>
+        <v>17.94</v>
       </c>
       <c r="R8" t="n">
-        <v>1.602175997955624</v>
+        <v>8.685008550381347</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1430.47</v>
+        <v>1738.26</v>
       </c>
       <c r="U8" t="n">
-        <v>7406</v>
+        <v>6441</v>
       </c>
       <c r="V8" t="n">
-        <v>1.057208778385313</v>
+        <v>1.072235181428082</v>
       </c>
       <c r="W8" t="n">
-        <v>1.207668377880776</v>
+        <v>1.196239496774286</v>
       </c>
       <c r="X8" t="n">
-        <v>66.11750011444092</v>
+        <v>12.61850008964539</v>
       </c>
       <c r="Y8" t="n">
-        <v>57.88012902063386</v>
+        <v>11.31044391148716</v>
       </c>
       <c r="Z8" t="n">
-        <v>113613365.4801178</v>
+        <v>3192477175.493097</v>
       </c>
     </row>
     <row r="9">
@@ -1141,16 +1141,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12.83061509190995</v>
+        <v>12.50450381719158</v>
       </c>
       <c r="D9" t="n">
-        <v>3.303356364079289</v>
+        <v>3.263423699274465</v>
       </c>
       <c r="E9" t="n">
-        <v>366.25</v>
+        <v>357.75</v>
       </c>
       <c r="F9" t="n">
-        <v>92.27</v>
+        <v>85.91</v>
       </c>
       <c r="G9" t="n">
         <v>555</v>
@@ -1165,7 +1165,7 @@
         <v>12.35135135135135</v>
       </c>
       <c r="K9" t="n">
-        <v>956251.75</v>
+        <v>908515.5</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
@@ -1184,7 +1184,7 @@
         <v>16.91</v>
       </c>
       <c r="R9" t="n">
-        <v>9.527258727830656</v>
+        <v>9.241080117917111</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1196,19 +1196,19 @@
         <v>6855</v>
       </c>
       <c r="V9" t="n">
-        <v>1.099932412237883</v>
+        <v>1.070266617106939</v>
       </c>
       <c r="W9" t="n">
-        <v>1.218770863301016</v>
+        <v>1.192872165436869</v>
       </c>
       <c r="X9" t="n">
-        <v>332.9750045776367</v>
+        <v>334.2625045776367</v>
       </c>
       <c r="Y9" t="n">
-        <v>300.5076762403224</v>
+        <v>299.9064026856393</v>
       </c>
       <c r="Z9" t="n">
-        <v>364802580</v>
+        <v>298916939.25</v>
       </c>
     </row>
     <row r="10">
@@ -1223,16 +1223,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.722376052922168</v>
+        <v>1.695638294829261</v>
       </c>
       <c r="D10" t="n">
-        <v>1.311971794120206</v>
+        <v>1.288677417485138</v>
       </c>
       <c r="E10" t="n">
-        <v>62.95000076293945</v>
+        <v>62.34999847412109</v>
       </c>
       <c r="F10" t="n">
-        <v>84.67</v>
+        <v>80.36</v>
       </c>
       <c r="G10" t="n">
         <v>137</v>
@@ -1247,7 +1247,7 @@
         <v>12.38686131386861</v>
       </c>
       <c r="K10" t="n">
-        <v>11388579.65</v>
+        <v>10842137.85</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
@@ -1266,7 +1266,7 @@
         <v>43.19</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4104042588019614</v>
+        <v>0.4069608773441225</v>
       </c>
       <c r="S10" t="n">
         <v>4.98</v>
@@ -1278,19 +1278,19 @@
         <v>1697</v>
       </c>
       <c r="V10" t="n">
-        <v>1.048380392754674</v>
+        <v>1.036402899511061</v>
       </c>
       <c r="W10" t="n">
-        <v>1.120679985087959</v>
+        <v>1.111822033261225</v>
       </c>
       <c r="X10" t="n">
-        <v>60.04500007629395</v>
+        <v>60.16000003814698</v>
       </c>
       <c r="Y10" t="n">
-        <v>56.17125459593063</v>
+        <v>56.07911752858007</v>
       </c>
       <c r="Z10" t="n">
-        <v>643763281.7522621</v>
+        <v>467345161.7627563</v>
       </c>
     </row>
     <row r="11">
@@ -1305,16 +1305,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.339797917594175</v>
+        <v>2.323589925091385</v>
       </c>
       <c r="D11" t="n">
-        <v>1.983868165852523</v>
+        <v>1.954897258774325</v>
       </c>
       <c r="E11" t="n">
-        <v>52.20000076293945</v>
+        <v>51.95000076293945</v>
       </c>
       <c r="F11" t="n">
-        <v>86.31</v>
+        <v>84.18000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>243</v>
@@ -1329,7 +1329,7 @@
         <v>15.33333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>1128135.45</v>
+        <v>1101856.4</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
@@ -1348,7 +1348,7 @@
         <v>22.72</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3559297517416522</v>
+        <v>0.36869266631706</v>
       </c>
       <c r="S11" t="n">
         <v>7.549999999999999</v>
@@ -1360,19 +1360,19 @@
         <v>3726</v>
       </c>
       <c r="V11" t="n">
-        <v>1.068172757758279</v>
+        <v>1.058670099570276</v>
       </c>
       <c r="W11" t="n">
-        <v>1.153132774849284</v>
+        <v>1.150599188129244</v>
       </c>
       <c r="X11" t="n">
-        <v>48.86850032806397</v>
+        <v>49.071000289917</v>
       </c>
       <c r="Y11" t="n">
-        <v>45.26798812891435</v>
+        <v>45.15038885730904</v>
       </c>
       <c r="Z11" t="n">
-        <v>37343410.74580002</v>
+        <v>30231367.84397888</v>
       </c>
     </row>
     <row r="12">
@@ -1387,16 +1387,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.053006756834229</v>
+        <v>2.021042023260859</v>
       </c>
       <c r="D12" t="n">
-        <v>1.943918016282015</v>
+        <v>1.915190944781176</v>
       </c>
       <c r="E12" t="n">
-        <v>50</v>
+        <v>49.47000122070312</v>
       </c>
       <c r="F12" t="n">
-        <v>84.83</v>
+        <v>80.33</v>
       </c>
       <c r="G12" t="n">
         <v>269</v>
@@ -1411,7 +1411,7 @@
         <v>13.22304832713755</v>
       </c>
       <c r="K12" t="n">
-        <v>285490.55</v>
+        <v>289853</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
@@ -1430,7 +1430,7 @@
         <v>24.56</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1090887405522136</v>
+        <v>0.1058510784796827</v>
       </c>
       <c r="S12" t="n">
         <v>4.671</v>
@@ -1442,19 +1442,19 @@
         <v>3557</v>
       </c>
       <c r="V12" t="n">
-        <v>1.053851818265042</v>
+        <v>1.040137944123063</v>
       </c>
       <c r="W12" t="n">
-        <v>1.12104386161425</v>
+        <v>1.110662919672146</v>
       </c>
       <c r="X12" t="n">
-        <v>47.44500045776367</v>
+        <v>47.56100044250488</v>
       </c>
       <c r="Y12" t="n">
-        <v>44.60128788181613</v>
+        <v>44.5409676909949</v>
       </c>
       <c r="Z12" t="n">
-        <v>2326850</v>
+        <v>6024456.748657227</v>
       </c>
     </row>
     <row r="13">
@@ -1469,16 +1469,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.211707921748164</v>
+        <v>2.177599192637396</v>
       </c>
       <c r="D13" t="n">
-        <v>2.063970974969814</v>
+        <v>2.034471225915829</v>
       </c>
       <c r="E13" t="n">
-        <v>53.95000076293945</v>
+        <v>53.29999923706055</v>
       </c>
       <c r="F13" t="n">
-        <v>82.04000000000001</v>
+        <v>75.83</v>
       </c>
       <c r="G13" t="n">
         <v>323</v>
@@ -1493,7 +1493,7 @@
         <v>13.88854489164087</v>
       </c>
       <c r="K13" t="n">
-        <v>15725001.5</v>
+        <v>15169483.55</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
@@ -1512,7 +1512,7 @@
         <v>19.85</v>
       </c>
       <c r="R13" t="n">
-        <v>0.1477369467783505</v>
+        <v>0.1431279667215675</v>
       </c>
       <c r="S13" t="n">
         <v>12.5</v>
@@ -1524,19 +1524,19 @@
         <v>4486</v>
       </c>
       <c r="V13" t="n">
-        <v>1.047857683622408</v>
+        <v>1.032725565752029</v>
       </c>
       <c r="W13" t="n">
-        <v>1.109342208211493</v>
+        <v>1.097717770130841</v>
       </c>
       <c r="X13" t="n">
-        <v>51.48600006103516</v>
+        <v>51.61100006103516</v>
       </c>
       <c r="Y13" t="n">
-        <v>48.63242411908124</v>
+        <v>48.55528505355937</v>
       </c>
       <c r="Z13" t="n">
-        <v>789098391.3591156</v>
+        <v>584384869.3350792</v>
       </c>
     </row>
     <row r="14">
@@ -1551,16 +1551,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6.350531944148929</v>
+        <v>6.267467094479336</v>
       </c>
       <c r="D14" t="n">
-        <v>3.329438380926038</v>
+        <v>3.290552446376997</v>
       </c>
       <c r="E14" t="n">
-        <v>345.6499938964844</v>
+        <v>341.7999877929688</v>
       </c>
       <c r="F14" t="n">
-        <v>90.03</v>
+        <v>85.45</v>
       </c>
       <c r="G14" t="n">
         <v>1250</v>
@@ -1575,7 +1575,7 @@
         <v>13.0928</v>
       </c>
       <c r="K14" t="n">
-        <v>21472.35</v>
+        <v>18108.75</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
@@ -1594,7 +1594,7 @@
         <v>8.06</v>
       </c>
       <c r="R14" t="n">
-        <v>3.021093563222891</v>
+        <v>2.97691464810234</v>
       </c>
       <c r="S14" t="n">
         <v>1.685</v>
@@ -1606,19 +1606,19 @@
         <v>16366</v>
       </c>
       <c r="V14" t="n">
-        <v>1.048623784045249</v>
+        <v>1.034597531646434</v>
       </c>
       <c r="W14" t="n">
-        <v>1.098652411638338</v>
+        <v>1.08677167151221</v>
       </c>
       <c r="X14" t="n">
-        <v>329.6225006103516</v>
+        <v>330.3700012207031</v>
       </c>
       <c r="Y14" t="n">
-        <v>314.6126930000021</v>
+        <v>314.5094749455186</v>
       </c>
       <c r="Z14" t="n">
-        <v>26615395.18002319</v>
+        <v>2627416.506164551</v>
       </c>
     </row>
     <row r="15">
@@ -1633,16 +1633,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3.333369278556089</v>
+        <v>3.294450928364911</v>
       </c>
       <c r="D15" t="n">
-        <v>3.333369278556089</v>
+        <v>3.294450928364911</v>
       </c>
       <c r="E15" t="n">
-        <v>116.0500030517578</v>
+        <v>114.9499969482422</v>
       </c>
       <c r="F15" t="n">
-        <v>87.08</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>1229</v>
@@ -1657,7 +1657,7 @@
         <v>13.92758340113914</v>
       </c>
       <c r="K15" t="n">
-        <v>71696597.09999999</v>
+        <v>71684268.5</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
@@ -1688,19 +1688,19 @@
         <v>17117</v>
       </c>
       <c r="V15" t="n">
-        <v>1.048755160920291</v>
+        <v>1.036239039322159</v>
       </c>
       <c r="W15" t="n">
-        <v>1.10258946228618</v>
+        <v>1.093259476995431</v>
       </c>
       <c r="X15" t="n">
-        <v>110.6550006866455</v>
+        <v>110.9300003051758</v>
       </c>
       <c r="Y15" t="n">
-        <v>105.2522330579255</v>
+        <v>105.1442949885561</v>
       </c>
       <c r="Z15" t="n">
-        <v>7130391868.007355</v>
+        <v>11232187332.75151</v>
       </c>
     </row>
     <row r="16">
@@ -1715,16 +1715,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6.933167466987578</v>
+        <v>6.873017961901533</v>
       </c>
       <c r="D16" t="n">
-        <v>3.333369278556089</v>
+        <v>3.294450928364911</v>
       </c>
       <c r="E16" t="n">
-        <v>262</v>
+        <v>259.9500122070312</v>
       </c>
       <c r="F16" t="n">
-        <v>82.70999999999999</v>
+        <v>77.06</v>
       </c>
       <c r="G16" t="n">
         <v>1145</v>
@@ -1739,7 +1739,7 @@
         <v>14.07598253275109</v>
       </c>
       <c r="K16" t="n">
-        <v>132094.25</v>
+        <v>140793.25</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
@@ -1758,7 +1758,7 @@
         <v>7.63</v>
       </c>
       <c r="R16" t="n">
-        <v>3.599798188431489</v>
+        <v>3.578567033536622</v>
       </c>
       <c r="S16" t="n">
         <v>18.91</v>
@@ -1770,19 +1770,19 @@
         <v>16117</v>
       </c>
       <c r="V16" t="n">
-        <v>1.052282789024543</v>
+        <v>1.041382945820895</v>
       </c>
       <c r="W16" t="n">
-        <v>1.114629855235686</v>
+        <v>1.107530423517898</v>
       </c>
       <c r="X16" t="n">
-        <v>248.9825004577637</v>
+        <v>249.6200012207031</v>
       </c>
       <c r="Y16" t="n">
-        <v>235.0556095095808</v>
+        <v>234.7113963527434</v>
       </c>
       <c r="Z16" t="n">
-        <v>44349002</v>
+        <v>51246545.40649414</v>
       </c>
     </row>
     <row r="17">
@@ -1797,16 +1797,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3.387155723263836</v>
+        <v>3.347515485740338</v>
       </c>
       <c r="D17" t="n">
-        <v>2.881301195683998</v>
+        <v>2.844837022982891</v>
       </c>
       <c r="E17" t="n">
-        <v>111.1999969482422</v>
+        <v>110.1500015258789</v>
       </c>
       <c r="F17" t="n">
-        <v>79.40000000000001</v>
+        <v>72.64</v>
       </c>
       <c r="G17" t="n">
         <v>480</v>
@@ -1821,7 +1821,7 @@
         <v>14.04583333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>1295597</v>
+        <v>1302980.9</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
@@ -1840,7 +1840,7 @@
         <v>13.92</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5058545275798378</v>
+        <v>0.5026784627574474</v>
       </c>
       <c r="S17" t="n">
         <v>13.37</v>
@@ -1852,19 +1852,19 @@
         <v>6742</v>
       </c>
       <c r="V17" t="n">
-        <v>1.040200156089194</v>
+        <v>1.028382049206432</v>
       </c>
       <c r="W17" t="n">
-        <v>1.103825447300063</v>
+        <v>1.094201143104395</v>
       </c>
       <c r="X17" t="n">
-        <v>106.9024997711182</v>
+        <v>107.1100002288818</v>
       </c>
       <c r="Y17" t="n">
-        <v>100.7405629397613</v>
+        <v>100.6670503134082</v>
       </c>
       <c r="Z17" t="n">
-        <v>164205477.0935669</v>
+        <v>272280449.6718292</v>
       </c>
     </row>
     <row r="18">
@@ -1879,16 +1879,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4.590288135786347</v>
+        <v>4.54732522241241</v>
       </c>
       <c r="D18" t="n">
-        <v>3.590101088316084</v>
+        <v>3.548614604167279</v>
       </c>
       <c r="E18" t="n">
-        <v>210.3500061035156</v>
+        <v>208.6499938964844</v>
       </c>
       <c r="F18" t="n">
-        <v>87.90000000000001</v>
+        <v>85.51000000000001</v>
       </c>
       <c r="G18" t="n">
         <v>1041</v>
@@ -1903,7 +1903,7 @@
         <v>12.95965417867435</v>
       </c>
       <c r="K18" t="n">
-        <v>9753.6</v>
+        <v>8254.15</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
@@ -1922,7 +1922,7 @@
         <v>8.81</v>
       </c>
       <c r="R18" t="n">
-        <v>1.000187047470263</v>
+        <v>0.9987106182451315</v>
       </c>
       <c r="S18" t="n">
         <v>21.88</v>
@@ -1934,19 +1934,19 @@
         <v>13491</v>
       </c>
       <c r="V18" t="n">
-        <v>1.047455460731145</v>
+        <v>1.036396796456561</v>
       </c>
       <c r="W18" t="n">
-        <v>1.096536007248379</v>
+        <v>1.088660521990141</v>
       </c>
       <c r="X18" t="n">
-        <v>200.8200004577637</v>
+        <v>201.3224998474121</v>
       </c>
       <c r="Y18" t="n">
-        <v>191.8313714397422</v>
+        <v>191.6575366534453</v>
       </c>
       <c r="Z18" t="n">
-        <v>4156516.120605469</v>
+        <v>1185966.565307617</v>
       </c>
     </row>
     <row r="19">
@@ -1961,16 +1961,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4.572198218429223</v>
+        <v>4.528340976714462</v>
       </c>
       <c r="D19" t="n">
-        <v>3.772400118059388</v>
+        <v>3.729103898156925</v>
       </c>
       <c r="E19" t="n">
-        <v>265.6000061035156</v>
+        <v>263.3999938964844</v>
       </c>
       <c r="F19" t="n">
-        <v>89.31</v>
+        <v>83.98999999999999</v>
       </c>
       <c r="G19" t="n">
         <v>1012</v>
@@ -1985,7 +1985,7 @@
         <v>13.89624505928854</v>
       </c>
       <c r="K19" t="n">
-        <v>1945910.75</v>
+        <v>1932288.4</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
@@ -2004,7 +2004,7 @@
         <v>8.109999999999999</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7997981003698351</v>
+        <v>0.7992370785575371</v>
       </c>
       <c r="S19" t="n">
         <v>28.764</v>
@@ -2016,19 +2016,19 @@
         <v>14063</v>
       </c>
       <c r="V19" t="n">
-        <v>1.049335796944423</v>
+        <v>1.038172734454792</v>
       </c>
       <c r="W19" t="n">
-        <v>1.103282763015944</v>
+        <v>1.095104772674978</v>
       </c>
       <c r="X19" t="n">
-        <v>253.1124992370605</v>
+        <v>253.714998626709</v>
       </c>
       <c r="Y19" t="n">
-        <v>240.7361149896596</v>
+        <v>240.5249255311759</v>
       </c>
       <c r="Z19" t="n">
-        <v>364865617.9846497</v>
+        <v>470261969.3030701</v>
       </c>
     </row>
     <row r="20">
@@ -2043,16 +2043,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3.822304591553163</v>
+        <v>3.815723597659356</v>
       </c>
       <c r="D20" t="n">
-        <v>3.333369278556089</v>
+        <v>3.294450928364911</v>
       </c>
       <c r="E20" t="n">
-        <v>153.1499938964844</v>
+        <v>152.9499969482422</v>
       </c>
       <c r="F20" t="n">
-        <v>91.98999999999999</v>
+        <v>90.84</v>
       </c>
       <c r="G20" t="n">
         <v>1121</v>
@@ -2067,7 +2067,7 @@
         <v>15.42908117752007</v>
       </c>
       <c r="K20" t="n">
-        <v>46768.6</v>
+        <v>42729.15</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
@@ -2086,7 +2086,7 @@
         <v>6.55</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4889353129970742</v>
+        <v>0.5212726692944454</v>
       </c>
       <c r="S20" t="n">
         <v>19.36</v>
@@ -2098,19 +2098,19 @@
         <v>17296</v>
       </c>
       <c r="V20" t="n">
-        <v>1.042741112567663</v>
+        <v>1.039715830071873</v>
       </c>
       <c r="W20" t="n">
-        <v>1.086242390318209</v>
+        <v>1.086311368399896</v>
       </c>
       <c r="X20" t="n">
-        <v>146.8724998474121</v>
+        <v>147.1075004577637</v>
       </c>
       <c r="Y20" t="n">
-        <v>140.9906253535363</v>
+        <v>140.7975663308513</v>
       </c>
       <c r="Z20" t="n">
-        <v>6500757.790924072</v>
+        <v>3292707.534301758</v>
       </c>
     </row>
   </sheetData>

--- a/ETF動態清單.xlsx
+++ b/ETF動態清單.xlsx
@@ -567,31 +567,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9388510870058571</v>
+        <v>0.9424610019821669</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6738706180943519</v>
+        <v>0.6914065745461566</v>
       </c>
       <c r="E2" t="n">
-        <v>32.2400016784668</v>
+        <v>32.2599983215332</v>
       </c>
       <c r="F2" t="n">
-        <v>87.67</v>
+        <v>87.63</v>
       </c>
       <c r="G2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H2" t="n">
         <v>100</v>
       </c>
       <c r="I2" t="n">
-        <v>8.41</v>
+        <v>8.48</v>
       </c>
       <c r="J2" t="n">
-        <v>8.761904761904763</v>
+        <v>8.439024390243903</v>
       </c>
       <c r="K2" t="n">
-        <v>151109633.2</v>
+        <v>152175951.15</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
@@ -607,34 +607,34 @@
         <v>20.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>347.51</v>
+        <v>386.28</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2649804689115052</v>
+        <v>0.2510544274360103</v>
       </c>
       <c r="S2" t="n">
         <v>1.67</v>
       </c>
       <c r="T2" t="n">
-        <v>353.06</v>
+        <v>347.85</v>
       </c>
       <c r="U2" t="n">
-        <v>368</v>
+        <v>346</v>
       </c>
       <c r="V2" t="n">
-        <v>1.066331563280116</v>
+        <v>1.066957664736077</v>
       </c>
       <c r="W2" t="n">
-        <v>1.163422729991732</v>
+        <v>1.164236428347437</v>
       </c>
       <c r="X2" t="n">
-        <v>30.23450002670288</v>
+        <v>30.2354998588562</v>
       </c>
       <c r="Y2" t="n">
-        <v>27.71133900632654</v>
+        <v>27.7091469877165</v>
       </c>
       <c r="Z2" t="n">
-        <v>3190723392.194237</v>
+        <v>3880690722.350178</v>
       </c>
     </row>
     <row r="3">
@@ -649,31 +649,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.392659348264567</v>
+        <v>1.40130131448321</v>
       </c>
       <c r="D3" t="n">
-        <v>1.021155905208836</v>
+        <v>1.041817108105084</v>
       </c>
       <c r="E3" t="n">
-        <v>40.65999984741211</v>
+        <v>40.77000045776367</v>
       </c>
       <c r="F3" t="n">
-        <v>72.65000000000001</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H3" t="n">
-        <v>95.52</v>
+        <v>95.45</v>
       </c>
       <c r="I3" t="n">
-        <v>7.23</v>
+        <v>7.29</v>
       </c>
       <c r="J3" t="n">
-        <v>10.44776119402985</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K3" t="n">
-        <v>7140320.05</v>
+        <v>7410678.75</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
@@ -689,34 +689,34 @@
         <v>8</v>
       </c>
       <c r="Q3" t="n">
-        <v>151.1</v>
+        <v>160.43</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3715034430557314</v>
+        <v>0.3594842063781263</v>
       </c>
       <c r="S3" t="n">
         <v>0.78</v>
       </c>
       <c r="T3" t="n">
-        <v>484.57</v>
+        <v>481.01</v>
       </c>
       <c r="U3" t="n">
-        <v>700</v>
+        <v>671</v>
       </c>
       <c r="V3" t="n">
-        <v>1.037655188167393</v>
+        <v>1.040316414876856</v>
       </c>
       <c r="W3" t="n">
-        <v>1.134408478038682</v>
+        <v>1.13762163597193</v>
       </c>
       <c r="X3" t="n">
-        <v>39.18450012207031</v>
+        <v>39.19000015258789</v>
       </c>
       <c r="Y3" t="n">
-        <v>35.84246824187225</v>
+        <v>35.83792639714673</v>
       </c>
       <c r="Z3" t="n">
-        <v>277525398.1985092</v>
+        <v>498726695.3596802</v>
       </c>
     </row>
     <row r="4">
@@ -731,31 +731,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.774188886223059</v>
+        <v>2.7986587646885</v>
       </c>
       <c r="D4" t="n">
-        <v>2.56433727154422</v>
+        <v>2.598349813517975</v>
       </c>
       <c r="E4" t="n">
-        <v>91.90000152587891</v>
+        <v>92.55000305175781</v>
       </c>
       <c r="F4" t="n">
-        <v>87.67</v>
+        <v>91</v>
       </c>
       <c r="G4" t="n">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H4" t="n">
-        <v>96.93000000000001</v>
+        <v>97.13</v>
       </c>
       <c r="I4" t="n">
-        <v>3.93</v>
+        <v>3.94</v>
       </c>
       <c r="J4" t="n">
-        <v>12.34560327198364</v>
+        <v>12.31762295081967</v>
       </c>
       <c r="K4" t="n">
-        <v>6803168.4</v>
+        <v>6955996.7</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
@@ -771,34 +771,34 @@
         <v>0.9599999999999991</v>
       </c>
       <c r="Q4" t="n">
-        <v>19.93</v>
+        <v>20.03</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2098516146788389</v>
+        <v>0.2003089511705247</v>
       </c>
       <c r="S4" t="n">
         <v>17.71</v>
       </c>
       <c r="T4" t="n">
-        <v>1921.39</v>
+        <v>1921.22</v>
       </c>
       <c r="U4" t="n">
-        <v>6037</v>
+        <v>6011</v>
       </c>
       <c r="V4" t="n">
-        <v>1.070908369993479</v>
+        <v>1.078074530024275</v>
       </c>
       <c r="W4" t="n">
-        <v>1.196445938242432</v>
+        <v>1.205839924483739</v>
       </c>
       <c r="X4" t="n">
-        <v>85.81499977111817</v>
+        <v>85.84749984741211</v>
       </c>
       <c r="Y4" t="n">
-        <v>76.81082662278845</v>
+        <v>76.75148348681653</v>
       </c>
       <c r="Z4" t="n">
-        <v>531219687.8202057</v>
+        <v>817862155.7683105</v>
       </c>
     </row>
     <row r="5">
@@ -813,31 +813,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.15598799386017</v>
+        <v>17.53928385211141</v>
       </c>
       <c r="D5" t="n">
-        <v>3.816097521941979</v>
+        <v>3.860631666580619</v>
       </c>
       <c r="E5" t="n">
-        <v>40.90000152587891</v>
+        <v>41.75</v>
       </c>
       <c r="F5" t="n">
-        <v>86.88</v>
+        <v>94.05</v>
       </c>
       <c r="G5" t="n">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="H5" t="n">
-        <v>90.78</v>
+        <v>90.75</v>
       </c>
       <c r="I5" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="J5" t="n">
-        <v>12.48705501618123</v>
+        <v>12.46753246753247</v>
       </c>
       <c r="K5" t="n">
-        <v>153079164.1</v>
+        <v>150602237.5</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
@@ -853,34 +853,34 @@
         <v>-1.459999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>16.33</v>
+        <v>16.41</v>
       </c>
       <c r="R5" t="n">
-        <v>13.33989047191819</v>
+        <v>13.67865218553079</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2347.89</v>
+        <v>2346.5</v>
       </c>
       <c r="U5" t="n">
-        <v>7717</v>
+        <v>7680</v>
       </c>
       <c r="V5" t="n">
-        <v>1.070820809829904</v>
+        <v>1.09186006865597</v>
       </c>
       <c r="W5" t="n">
-        <v>1.189679780734052</v>
+        <v>1.217718295844813</v>
       </c>
       <c r="X5" t="n">
-        <v>38.19500064849854</v>
+        <v>38.23750057220459</v>
       </c>
       <c r="Y5" t="n">
-        <v>34.3790002891727</v>
+        <v>34.28543378420311</v>
       </c>
       <c r="Z5" t="n">
-        <v>6000728754.972496</v>
+        <v>4057204337.25</v>
       </c>
     </row>
     <row r="6">
@@ -895,31 +895,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.916622816221098</v>
+        <v>1.945807379855867</v>
       </c>
       <c r="D6" t="n">
-        <v>1.79894556917569</v>
+        <v>1.82671147665601</v>
       </c>
       <c r="E6" t="n">
-        <v>53.45000076293945</v>
+        <v>54</v>
       </c>
       <c r="F6" t="n">
-        <v>70.66</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H6" t="n">
-        <v>96.95999999999999</v>
+        <v>96.95</v>
       </c>
       <c r="I6" t="n">
-        <v>3.53</v>
+        <v>3.54</v>
       </c>
       <c r="J6" t="n">
-        <v>12.54372623574145</v>
+        <v>12.49618320610687</v>
       </c>
       <c r="K6" t="n">
-        <v>1504326.75</v>
+        <v>1460736.3</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
@@ -935,34 +935,34 @@
         <v>4.039999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>29.41</v>
+        <v>29.64</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1176772470454077</v>
+        <v>0.1190959031998569</v>
       </c>
       <c r="S6" t="n">
         <v>6.699999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>928.22</v>
+        <v>926.55</v>
       </c>
       <c r="U6" t="n">
-        <v>3299</v>
+        <v>3274</v>
       </c>
       <c r="V6" t="n">
-        <v>1.042337035946892</v>
+        <v>1.052498224290073</v>
       </c>
       <c r="W6" t="n">
-        <v>1.138819129605281</v>
+        <v>1.151363119673073</v>
       </c>
       <c r="X6" t="n">
-        <v>51.27899990081787</v>
+        <v>51.3064998626709</v>
       </c>
       <c r="Y6" t="n">
-        <v>46.93458282656827</v>
+        <v>46.90092906166144</v>
       </c>
       <c r="Z6" t="n">
-        <v>104889693.547184</v>
+        <v>58891320</v>
       </c>
     </row>
     <row r="7">
@@ -977,31 +977,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4.735529111607426</v>
+        <v>4.616804688591151</v>
       </c>
       <c r="D7" t="n">
-        <v>2.977433125863245</v>
+        <v>3.014943347696689</v>
       </c>
       <c r="E7" t="n">
-        <v>71.40000152587891</v>
+        <v>69.90000152587891</v>
       </c>
       <c r="F7" t="n">
-        <v>78.83</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>433</v>
       </c>
       <c r="H7" t="n">
-        <v>78.75</v>
+        <v>78.98</v>
       </c>
       <c r="I7" t="n">
-        <v>3.33</v>
+        <v>3.39</v>
       </c>
       <c r="J7" t="n">
         <v>17.11316397228637</v>
       </c>
       <c r="K7" t="n">
-        <v>4638196.7</v>
+        <v>4602900.9</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
@@ -1017,34 +1017,34 @@
         <v>-13.31</v>
       </c>
       <c r="Q7" t="n">
-        <v>14.42</v>
+        <v>14.52</v>
       </c>
       <c r="R7" t="n">
-        <v>1.758095985744181</v>
+        <v>1.601861340894462</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1439.93</v>
+        <v>1468.89</v>
       </c>
       <c r="U7" t="n">
         <v>7410</v>
       </c>
       <c r="V7" t="n">
-        <v>1.070785863877282</v>
+        <v>1.04947078155959</v>
       </c>
       <c r="W7" t="n">
-        <v>1.213041363496872</v>
+        <v>1.185939616252933</v>
       </c>
       <c r="X7" t="n">
-        <v>66.68000011444092</v>
+        <v>66.60500011444091</v>
       </c>
       <c r="Y7" t="n">
-        <v>58.86031892601904</v>
+        <v>58.940607572191</v>
       </c>
       <c r="Z7" t="n">
-        <v>166346152.7549591</v>
+        <v>113507956.2778168</v>
       </c>
     </row>
     <row r="8">
@@ -1059,31 +1059,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11.81484141640059</v>
+        <v>12.11359853412348</v>
       </c>
       <c r="D8" t="n">
-        <v>3.129832866019241</v>
+        <v>3.16860136747795</v>
       </c>
       <c r="E8" t="n">
-        <v>13.52999973297119</v>
+        <v>13.84000015258789</v>
       </c>
       <c r="F8" t="n">
-        <v>86.27</v>
+        <v>94.04000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H8" t="n">
-        <v>87.45</v>
+        <v>87.43000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="J8" t="n">
-        <v>12.24524714828897</v>
+        <v>12.22857142857143</v>
       </c>
       <c r="K8" t="n">
-        <v>196613407.25</v>
+        <v>191346571.55</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
@@ -1099,34 +1099,34 @@
         <v>-2.609999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>17.94</v>
+        <v>18</v>
       </c>
       <c r="R8" t="n">
-        <v>8.685008550381347</v>
+        <v>8.944997166645532</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1738.26</v>
+        <v>1736.81</v>
       </c>
       <c r="U8" t="n">
-        <v>6441</v>
+        <v>6420</v>
       </c>
       <c r="V8" t="n">
-        <v>1.072235181428082</v>
+        <v>1.095456706617196</v>
       </c>
       <c r="W8" t="n">
-        <v>1.196239496774286</v>
+        <v>1.227310725763724</v>
       </c>
       <c r="X8" t="n">
-        <v>12.61850008964539</v>
+        <v>12.63400011062622</v>
       </c>
       <c r="Y8" t="n">
-        <v>11.31044391148716</v>
+        <v>11.27668801555989</v>
       </c>
       <c r="Z8" t="n">
-        <v>3192477175.493097</v>
+        <v>1807763326.170837</v>
       </c>
     </row>
     <row r="9">
@@ -1141,31 +1141,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12.50450381719158</v>
+        <v>12.83055645749879</v>
       </c>
       <c r="D9" t="n">
-        <v>3.263423699274465</v>
+        <v>3.303312733650152</v>
       </c>
       <c r="E9" t="n">
-        <v>357.75</v>
+        <v>366.25</v>
       </c>
       <c r="F9" t="n">
-        <v>85.91</v>
+        <v>94.14</v>
       </c>
       <c r="G9" t="n">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="H9" t="n">
-        <v>86.31</v>
+        <v>86.23</v>
       </c>
       <c r="I9" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="J9" t="n">
-        <v>12.35135135135135</v>
+        <v>12.32971014492754</v>
       </c>
       <c r="K9" t="n">
-        <v>908515.5</v>
+        <v>915439.05</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
@@ -1181,34 +1181,34 @@
         <v>-9.030000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>16.91</v>
+        <v>17.04</v>
       </c>
       <c r="R9" t="n">
-        <v>9.241080117917111</v>
+        <v>9.527243723848633</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1779.77</v>
+        <v>1778.9</v>
       </c>
       <c r="U9" t="n">
-        <v>6855</v>
+        <v>6806</v>
       </c>
       <c r="V9" t="n">
-        <v>1.070266617106939</v>
+        <v>1.094304373454856</v>
       </c>
       <c r="W9" t="n">
-        <v>1.192872165436869</v>
+        <v>1.22493525564159</v>
       </c>
       <c r="X9" t="n">
-        <v>334.2625045776367</v>
+        <v>334.6875045776367</v>
       </c>
       <c r="Y9" t="n">
-        <v>299.9064026856393</v>
+        <v>298.9953945020283</v>
       </c>
       <c r="Z9" t="n">
-        <v>298916939.25</v>
+        <v>356734092.5</v>
       </c>
     </row>
     <row r="10">
@@ -1223,31 +1223,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.695638294829261</v>
+        <v>1.722226457964336</v>
       </c>
       <c r="D10" t="n">
-        <v>1.288677417485138</v>
+        <v>1.311823790480891</v>
       </c>
       <c r="E10" t="n">
-        <v>62.34999847412109</v>
+        <v>62.95000076293945</v>
       </c>
       <c r="F10" t="n">
-        <v>80.36</v>
+        <v>85.69</v>
       </c>
       <c r="G10" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H10" t="n">
-        <v>83.20999999999999</v>
+        <v>83.09</v>
       </c>
       <c r="I10" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="J10" t="n">
-        <v>12.38686131386861</v>
+        <v>12.30882352941176</v>
       </c>
       <c r="K10" t="n">
-        <v>10842137.85</v>
+        <v>10963097.2</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
@@ -1263,34 +1263,34 @@
         <v>5.609999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>43.19</v>
+        <v>43.8</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4069608773441225</v>
+        <v>0.4104026674834453</v>
       </c>
       <c r="S10" t="n">
         <v>4.98</v>
       </c>
       <c r="T10" t="n">
-        <v>430.76</v>
+        <v>429.07</v>
       </c>
       <c r="U10" t="n">
-        <v>1697</v>
+        <v>1674</v>
       </c>
       <c r="V10" t="n">
-        <v>1.036402899511061</v>
+        <v>1.045854803179177</v>
       </c>
       <c r="W10" t="n">
-        <v>1.111822033261225</v>
+        <v>1.123365401304318</v>
       </c>
       <c r="X10" t="n">
-        <v>60.16000003814698</v>
+        <v>60.19000015258789</v>
       </c>
       <c r="Y10" t="n">
-        <v>56.07911752858007</v>
+        <v>56.03697665056218</v>
       </c>
       <c r="Z10" t="n">
-        <v>467345161.7627563</v>
+        <v>624130309.614315</v>
       </c>
     </row>
     <row r="11">
@@ -1305,31 +1305,31 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.323589925091385</v>
+        <v>2.339677318592491</v>
       </c>
       <c r="D11" t="n">
-        <v>1.954897258774325</v>
+        <v>1.983783508241808</v>
       </c>
       <c r="E11" t="n">
-        <v>51.95000076293945</v>
+        <v>52.20000076293945</v>
       </c>
       <c r="F11" t="n">
-        <v>84.18000000000001</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H11" t="n">
-        <v>83.54000000000001</v>
+        <v>83.47</v>
       </c>
       <c r="I11" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="J11" t="n">
-        <v>15.33333333333333</v>
+        <v>15.29752066115702</v>
       </c>
       <c r="K11" t="n">
-        <v>1101856.4</v>
+        <v>1104809.95</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
@@ -1345,34 +1345,34 @@
         <v>7.319999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>22.72</v>
+        <v>22.8</v>
       </c>
       <c r="R11" t="n">
-        <v>0.36869266631706</v>
+        <v>0.3558938103506826</v>
       </c>
       <c r="S11" t="n">
         <v>7.549999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>708.49</v>
+        <v>703.14</v>
       </c>
       <c r="U11" t="n">
-        <v>3726</v>
+        <v>3702</v>
       </c>
       <c r="V11" t="n">
-        <v>1.058670099570276</v>
+        <v>1.063493851388237</v>
       </c>
       <c r="W11" t="n">
-        <v>1.150599188129244</v>
+        <v>1.156790750144374</v>
       </c>
       <c r="X11" t="n">
-        <v>49.071000289917</v>
+        <v>49.08350028991699</v>
       </c>
       <c r="Y11" t="n">
-        <v>45.15038885730904</v>
+        <v>45.12484280880064</v>
       </c>
       <c r="Z11" t="n">
-        <v>30231367.84397888</v>
+        <v>33460357.08904648</v>
       </c>
     </row>
     <row r="12">
@@ -1387,31 +1387,31 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.021042023260859</v>
+        <v>2.052919229141477</v>
       </c>
       <c r="D12" t="n">
-        <v>1.915190944781176</v>
+        <v>1.943827296233705</v>
       </c>
       <c r="E12" t="n">
-        <v>49.47000122070312</v>
+        <v>50</v>
       </c>
       <c r="F12" t="n">
-        <v>80.33</v>
+        <v>86.2</v>
       </c>
       <c r="G12" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H12" t="n">
-        <v>90.33</v>
+        <v>90.3</v>
       </c>
       <c r="I12" t="n">
         <v>2.79</v>
       </c>
       <c r="J12" t="n">
-        <v>13.22304832713755</v>
+        <v>13.1865671641791</v>
       </c>
       <c r="K12" t="n">
-        <v>289853</v>
+        <v>285816</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
@@ -1427,34 +1427,34 @@
         <v>8.109999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>24.56</v>
+        <v>24.7</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1058510784796827</v>
+        <v>0.1090919329077717</v>
       </c>
       <c r="S12" t="n">
         <v>4.671</v>
       </c>
       <c r="T12" t="n">
-        <v>750.16</v>
+        <v>747.59</v>
       </c>
       <c r="U12" t="n">
-        <v>3557</v>
+        <v>3534</v>
       </c>
       <c r="V12" t="n">
-        <v>1.040137944123063</v>
+        <v>1.050696077734516</v>
       </c>
       <c r="W12" t="n">
-        <v>1.110662919672146</v>
+        <v>1.123783473066263</v>
       </c>
       <c r="X12" t="n">
-        <v>47.56100044250488</v>
+        <v>47.58750038146972</v>
       </c>
       <c r="Y12" t="n">
-        <v>44.5409676909949</v>
+        <v>44.49255679439219</v>
       </c>
       <c r="Z12" t="n">
-        <v>6024456.748657227</v>
+        <v>2052000</v>
       </c>
     </row>
     <row r="13">
@@ -1469,31 +1469,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.177599192637396</v>
+        <v>2.211631449338959</v>
       </c>
       <c r="D13" t="n">
-        <v>2.034471225915829</v>
+        <v>2.06389603509892</v>
       </c>
       <c r="E13" t="n">
-        <v>53.29999923706055</v>
+        <v>53.95000076293945</v>
       </c>
       <c r="F13" t="n">
-        <v>75.83</v>
+        <v>82.81999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H13" t="n">
-        <v>90.70999999999999</v>
+        <v>90.68000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="J13" t="n">
-        <v>13.88854489164087</v>
+        <v>13.86335403726708</v>
       </c>
       <c r="K13" t="n">
-        <v>15169483.55</v>
+        <v>15332059.3</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
@@ -1509,34 +1509,34 @@
         <v>3.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>19.85</v>
+        <v>19.92</v>
       </c>
       <c r="R13" t="n">
-        <v>0.1431279667215675</v>
+        <v>0.1477354142400382</v>
       </c>
       <c r="S13" t="n">
         <v>12.5</v>
       </c>
       <c r="T13" t="n">
-        <v>825.49</v>
+        <v>822.15</v>
       </c>
       <c r="U13" t="n">
-        <v>4486</v>
+        <v>4464</v>
       </c>
       <c r="V13" t="n">
-        <v>1.032725565752029</v>
+        <v>1.044661973326304</v>
       </c>
       <c r="W13" t="n">
-        <v>1.097717770130841</v>
+        <v>1.112280691001375</v>
       </c>
       <c r="X13" t="n">
-        <v>51.61100006103516</v>
+        <v>51.6435001373291</v>
       </c>
       <c r="Y13" t="n">
-        <v>48.55528505355937</v>
+        <v>48.50394437250262</v>
       </c>
       <c r="Z13" t="n">
-        <v>584384869.3350792</v>
+        <v>766930767.6456299</v>
       </c>
     </row>
     <row r="14">
@@ -1551,31 +1551,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6.267467094479336</v>
+        <v>6.350508801659792</v>
       </c>
       <c r="D14" t="n">
-        <v>3.290552446376997</v>
+        <v>3.329413855778156</v>
       </c>
       <c r="E14" t="n">
-        <v>341.7999877929688</v>
+        <v>345.6499938964844</v>
       </c>
       <c r="F14" t="n">
-        <v>85.45</v>
+        <v>92.95999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="H14" t="n">
-        <v>93.52</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="J14" t="n">
-        <v>13.0928</v>
+        <v>13.08653846153846</v>
       </c>
       <c r="K14" t="n">
-        <v>18108.75</v>
+        <v>21175.1</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
@@ -1591,34 +1591,34 @@
         <v>7.969999999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.06</v>
+        <v>8.07</v>
       </c>
       <c r="R14" t="n">
-        <v>2.97691464810234</v>
+        <v>3.021094945881637</v>
       </c>
       <c r="S14" t="n">
         <v>1.685</v>
       </c>
       <c r="T14" t="n">
-        <v>3133.95</v>
+        <v>3124.7</v>
       </c>
       <c r="U14" t="n">
-        <v>16366</v>
+        <v>16332</v>
       </c>
       <c r="V14" t="n">
-        <v>1.034597531646434</v>
+        <v>1.045641874988728</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08677167151221</v>
+        <v>1.100547857480891</v>
       </c>
       <c r="X14" t="n">
-        <v>330.3700012207031</v>
+        <v>330.5625015258789</v>
       </c>
       <c r="Y14" t="n">
-        <v>314.5094749455186</v>
+        <v>314.0708434866823</v>
       </c>
       <c r="Z14" t="n">
-        <v>2627416.506164551</v>
+        <v>23854688.67877197</v>
       </c>
     </row>
     <row r="15">
@@ -1633,31 +1633,31 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3.294450928364911</v>
+        <v>3.333344798543052</v>
       </c>
       <c r="D15" t="n">
-        <v>3.294450928364911</v>
+        <v>3.333344798543052</v>
       </c>
       <c r="E15" t="n">
-        <v>114.9499969482422</v>
+        <v>116.0500030517578</v>
       </c>
       <c r="F15" t="n">
-        <v>83.09999999999999</v>
+        <v>89.7</v>
       </c>
       <c r="G15" t="n">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="H15" t="n">
-        <v>90.89</v>
+        <v>90.87</v>
       </c>
       <c r="I15" t="n">
         <v>2.19</v>
       </c>
       <c r="J15" t="n">
-        <v>13.92758340113914</v>
+        <v>13.92094539527302</v>
       </c>
       <c r="K15" t="n">
-        <v>71684268.5</v>
+        <v>69595247.90000001</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
@@ -1673,7 +1673,7 @@
         <v>6.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>7.36</v>
+        <v>7.37</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -1682,25 +1682,25 @@
         <v>13.505</v>
       </c>
       <c r="T15" t="n">
-        <v>2696.19</v>
+        <v>2689.93</v>
       </c>
       <c r="U15" t="n">
-        <v>17117</v>
+        <v>17081</v>
       </c>
       <c r="V15" t="n">
-        <v>1.036239039322159</v>
+        <v>1.045636819512112</v>
       </c>
       <c r="W15" t="n">
-        <v>1.093259476995431</v>
+        <v>1.104932204854724</v>
       </c>
       <c r="X15" t="n">
-        <v>110.9300003051758</v>
+        <v>110.9850006103516</v>
       </c>
       <c r="Y15" t="n">
-        <v>105.1442949885561</v>
+        <v>105.0290710523873</v>
       </c>
       <c r="Z15" t="n">
-        <v>11232187332.75151</v>
+        <v>6491056038.144791</v>
       </c>
     </row>
     <row r="16">
@@ -1715,31 +1715,31 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6.873017961901533</v>
+        <v>6.933142238974012</v>
       </c>
       <c r="D16" t="n">
-        <v>3.294450928364911</v>
+        <v>3.333344798543052</v>
       </c>
       <c r="E16" t="n">
-        <v>259.9500122070312</v>
+        <v>262</v>
       </c>
       <c r="F16" t="n">
-        <v>77.06</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H16" t="n">
-        <v>90.31</v>
+        <v>90.3</v>
       </c>
       <c r="I16" t="n">
         <v>2.15</v>
       </c>
       <c r="J16" t="n">
-        <v>14.07598253275109</v>
+        <v>14.06905594405594</v>
       </c>
       <c r="K16" t="n">
-        <v>140793.25</v>
+        <v>138546.7</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
@@ -1758,31 +1758,31 @@
         <v>7.63</v>
       </c>
       <c r="R16" t="n">
-        <v>3.578567033536622</v>
+        <v>3.59979744043096</v>
       </c>
       <c r="S16" t="n">
         <v>18.91</v>
       </c>
       <c r="T16" t="n">
-        <v>2466.25</v>
+        <v>2463.07</v>
       </c>
       <c r="U16" t="n">
-        <v>16117</v>
+        <v>16095</v>
       </c>
       <c r="V16" t="n">
-        <v>1.041382945820895</v>
+        <v>1.049164570111387</v>
       </c>
       <c r="W16" t="n">
-        <v>1.107530423517898</v>
+        <v>1.117241205905939</v>
       </c>
       <c r="X16" t="n">
-        <v>249.6200012207031</v>
+        <v>249.7225006103516</v>
       </c>
       <c r="Y16" t="n">
-        <v>234.7113963527434</v>
+        <v>234.5062092366632</v>
       </c>
       <c r="Z16" t="n">
-        <v>51246545.40649414</v>
+        <v>39878758</v>
       </c>
     </row>
     <row r="17">
@@ -1797,31 +1797,31 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3.347515485740338</v>
+        <v>3.387116675958203</v>
       </c>
       <c r="D17" t="n">
-        <v>2.844837022982891</v>
+        <v>2.881248852045696</v>
       </c>
       <c r="E17" t="n">
-        <v>110.1500015258789</v>
+        <v>111.1999969482422</v>
       </c>
       <c r="F17" t="n">
-        <v>72.64</v>
+        <v>78.84</v>
       </c>
       <c r="G17" t="n">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H17" t="n">
-        <v>84.79000000000001</v>
+        <v>84.97</v>
       </c>
       <c r="I17" t="n">
         <v>2.11</v>
       </c>
       <c r="J17" t="n">
-        <v>14.04583333333333</v>
+        <v>14.01461377870564</v>
       </c>
       <c r="K17" t="n">
-        <v>1302980.9</v>
+        <v>1250207.3</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
@@ -1837,34 +1837,34 @@
         <v>12.57</v>
       </c>
       <c r="Q17" t="n">
-        <v>13.92</v>
+        <v>14</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5026784627574474</v>
+        <v>0.505867823912507</v>
       </c>
       <c r="S17" t="n">
         <v>13.37</v>
       </c>
       <c r="T17" t="n">
-        <v>1011.13</v>
+        <v>1012.55</v>
       </c>
       <c r="U17" t="n">
-        <v>6742</v>
+        <v>6713</v>
       </c>
       <c r="V17" t="n">
-        <v>1.028382049206432</v>
+        <v>1.037676397510717</v>
       </c>
       <c r="W17" t="n">
-        <v>1.094201143104395</v>
+        <v>1.10531036857537</v>
       </c>
       <c r="X17" t="n">
-        <v>107.1100002288818</v>
+        <v>107.1625</v>
       </c>
       <c r="Y17" t="n">
-        <v>100.6670503134082</v>
+        <v>100.6052237540913</v>
       </c>
       <c r="Z17" t="n">
-        <v>272280449.6718292</v>
+        <v>157507456.4773865</v>
       </c>
     </row>
     <row r="18">
@@ -1879,16 +1879,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4.54732522241241</v>
+        <v>4.590262265259418</v>
       </c>
       <c r="D18" t="n">
-        <v>3.548614604167279</v>
+        <v>3.590072884071009</v>
       </c>
       <c r="E18" t="n">
-        <v>208.6499938964844</v>
+        <v>210.3500061035156</v>
       </c>
       <c r="F18" t="n">
-        <v>85.51000000000001</v>
+        <v>90.72</v>
       </c>
       <c r="G18" t="n">
         <v>1041</v>
@@ -1900,10 +1900,10 @@
         <v>2.08</v>
       </c>
       <c r="J18" t="n">
-        <v>12.95965417867435</v>
+        <v>12.95869356388088</v>
       </c>
       <c r="K18" t="n">
-        <v>8254.15</v>
+        <v>8820.5</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
@@ -1922,7 +1922,7 @@
         <v>8.81</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9987106182451315</v>
+        <v>1.000189381188409</v>
       </c>
       <c r="S18" t="n">
         <v>21.88</v>
@@ -1931,22 +1931,22 @@
         <v>2169.48</v>
       </c>
       <c r="U18" t="n">
-        <v>13491</v>
+        <v>13490</v>
       </c>
       <c r="V18" t="n">
-        <v>1.036396796456561</v>
+        <v>1.044400062685984</v>
       </c>
       <c r="W18" t="n">
-        <v>1.088660521990141</v>
+        <v>1.098660223137901</v>
       </c>
       <c r="X18" t="n">
-        <v>201.3224998474121</v>
+        <v>201.4075004577637</v>
       </c>
       <c r="Y18" t="n">
-        <v>191.6575366534453</v>
+        <v>191.4604731048983</v>
       </c>
       <c r="Z18" t="n">
-        <v>1185966.565307617</v>
+        <v>3578263.953826904</v>
       </c>
     </row>
     <row r="19">
@@ -1961,31 +1961,31 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4.528340976714462</v>
+        <v>4.572169081773092</v>
       </c>
       <c r="D19" t="n">
-        <v>3.729103898156925</v>
+        <v>3.772369556710547</v>
       </c>
       <c r="E19" t="n">
-        <v>263.3999938964844</v>
+        <v>265.6000061035156</v>
       </c>
       <c r="F19" t="n">
-        <v>83.98999999999999</v>
+        <v>90.03</v>
       </c>
       <c r="G19" t="n">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="H19" t="n">
-        <v>89.23</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="I19" t="n">
         <v>1.89</v>
       </c>
       <c r="J19" t="n">
-        <v>13.89624505928854</v>
+        <v>13.88613861386139</v>
       </c>
       <c r="K19" t="n">
-        <v>1932288.4</v>
+        <v>1899920.2</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
@@ -2001,34 +2001,34 @@
         <v>4.960000000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>8.109999999999999</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7992370785575371</v>
+        <v>0.7997995250625447</v>
       </c>
       <c r="S19" t="n">
         <v>28.764</v>
       </c>
       <c r="T19" t="n">
-        <v>1914.21</v>
+        <v>1907.67</v>
       </c>
       <c r="U19" t="n">
-        <v>14063</v>
+        <v>14025</v>
       </c>
       <c r="V19" t="n">
-        <v>1.038172734454792</v>
+        <v>1.046390256680185</v>
       </c>
       <c r="W19" t="n">
-        <v>1.095104772674978</v>
+        <v>1.105369184653776</v>
       </c>
       <c r="X19" t="n">
-        <v>253.714998626709</v>
+        <v>253.8249992370606</v>
       </c>
       <c r="Y19" t="n">
-        <v>240.5249255311759</v>
+        <v>240.2817174487335</v>
       </c>
       <c r="Z19" t="n">
-        <v>470261969.3030701</v>
+        <v>302249885.3457336</v>
       </c>
     </row>
     <row r="20">
@@ -2043,31 +2043,31 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3.815723597659356</v>
+        <v>3.822291606181272</v>
       </c>
       <c r="D20" t="n">
-        <v>3.294450928364911</v>
+        <v>3.333344798543052</v>
       </c>
       <c r="E20" t="n">
-        <v>152.9499969482422</v>
+        <v>153.1499938964844</v>
       </c>
       <c r="F20" t="n">
-        <v>90.84</v>
+        <v>91.91</v>
       </c>
       <c r="G20" t="n">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H20" t="n">
-        <v>88.84999999999999</v>
+        <v>88.84</v>
       </c>
       <c r="I20" t="n">
         <v>1.71</v>
       </c>
       <c r="J20" t="n">
-        <v>15.42908117752007</v>
+        <v>15.42410714285714</v>
       </c>
       <c r="K20" t="n">
-        <v>42729.15</v>
+        <v>43311.2</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
@@ -2086,31 +2086,31 @@
         <v>6.55</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5212726692944454</v>
+        <v>0.4889468076382197</v>
       </c>
       <c r="S20" t="n">
         <v>19.36</v>
       </c>
       <c r="T20" t="n">
-        <v>1920.98</v>
+        <v>1917.49</v>
       </c>
       <c r="U20" t="n">
-        <v>17296</v>
+        <v>17275</v>
       </c>
       <c r="V20" t="n">
-        <v>1.039715830071873</v>
+        <v>1.0410045955022</v>
       </c>
       <c r="W20" t="n">
-        <v>1.086311368399896</v>
+        <v>1.087944527425008</v>
       </c>
       <c r="X20" t="n">
-        <v>147.1075004577637</v>
+        <v>147.1175003051758</v>
       </c>
       <c r="Y20" t="n">
-        <v>140.7975663308513</v>
+        <v>140.7700393134621</v>
       </c>
       <c r="Z20" t="n">
-        <v>3292707.534301758</v>
+        <v>5079832.14755249</v>
       </c>
     </row>
   </sheetData>

--- a/ETF動態清單.xlsx
+++ b/ETF動態清單.xlsx
@@ -567,16 +567,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9424610019821669</v>
+        <v>0.9408868667740447</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6914065745461566</v>
+        <v>0.6752560381909085</v>
       </c>
       <c r="E2" t="n">
-        <v>32.2599983215332</v>
+        <v>32.2400016784668</v>
       </c>
       <c r="F2" t="n">
-        <v>87.63</v>
+        <v>84.13</v>
       </c>
       <c r="G2" t="n">
         <v>41</v>
@@ -591,7 +591,7 @@
         <v>8.439024390243903</v>
       </c>
       <c r="K2" t="n">
-        <v>152175951.15</v>
+        <v>150065872.95</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
@@ -610,7 +610,7 @@
         <v>386.28</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2510544274360103</v>
+        <v>0.2656308285831361</v>
       </c>
       <c r="S2" t="n">
         <v>1.67</v>
@@ -622,19 +622,19 @@
         <v>346</v>
       </c>
       <c r="V2" t="n">
-        <v>1.066957664736077</v>
+        <v>1.06188866357906</v>
       </c>
       <c r="W2" t="n">
-        <v>1.164236428347437</v>
+        <v>1.163828189656442</v>
       </c>
       <c r="X2" t="n">
-        <v>30.2354998588562</v>
+        <v>30.36099996566772</v>
       </c>
       <c r="Y2" t="n">
-        <v>27.7091469877165</v>
+        <v>27.70168480622895</v>
       </c>
       <c r="Z2" t="n">
-        <v>3880690722.350178</v>
+        <v>3156540414.574615</v>
       </c>
     </row>
     <row r="3">
@@ -649,31 +649,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.40130131448321</v>
+        <v>1.394709788329697</v>
       </c>
       <c r="D3" t="n">
-        <v>1.041817108105084</v>
+        <v>1.022593906890337</v>
       </c>
       <c r="E3" t="n">
-        <v>40.77000045776367</v>
+        <v>40.65999984741211</v>
       </c>
       <c r="F3" t="n">
-        <v>74.76000000000001</v>
+        <v>68.23</v>
       </c>
       <c r="G3" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H3" t="n">
-        <v>95.45</v>
+        <v>95.38</v>
       </c>
       <c r="I3" t="n">
-        <v>7.29</v>
+        <v>7.34</v>
       </c>
       <c r="J3" t="n">
-        <v>10.16666666666667</v>
+        <v>10.21538461538461</v>
       </c>
       <c r="K3" t="n">
-        <v>7410678.75</v>
+        <v>7501232.05</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
@@ -689,34 +689,34 @@
         <v>8</v>
       </c>
       <c r="Q3" t="n">
-        <v>160.43</v>
+        <v>162.08</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3594842063781263</v>
+        <v>0.3721158814393601</v>
       </c>
       <c r="S3" t="n">
         <v>0.78</v>
       </c>
       <c r="T3" t="n">
-        <v>481.01</v>
+        <v>477.03</v>
       </c>
       <c r="U3" t="n">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="V3" t="n">
-        <v>1.040316414876856</v>
+        <v>1.034658244628979</v>
       </c>
       <c r="W3" t="n">
-        <v>1.13762163597193</v>
+        <v>1.132499029025452</v>
       </c>
       <c r="X3" t="n">
-        <v>39.19000015258789</v>
+        <v>39.29800014495849</v>
       </c>
       <c r="Y3" t="n">
-        <v>35.83792639714673</v>
+        <v>35.90290040460452</v>
       </c>
       <c r="Z3" t="n">
-        <v>498726695.3596802</v>
+        <v>269600398.28825</v>
       </c>
     </row>
     <row r="4">
@@ -731,19 +731,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.7986587646885</v>
+        <v>2.775648968703858</v>
       </c>
       <c r="D4" t="n">
-        <v>2.598349813517975</v>
+        <v>2.56563990533291</v>
       </c>
       <c r="E4" t="n">
-        <v>92.55000305175781</v>
+        <v>91.90000152587891</v>
       </c>
       <c r="F4" t="n">
-        <v>91</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H4" t="n">
         <v>97.13</v>
@@ -752,10 +752,10 @@
         <v>3.94</v>
       </c>
       <c r="J4" t="n">
-        <v>12.31762295081967</v>
+        <v>12.31211498973306</v>
       </c>
       <c r="K4" t="n">
-        <v>6955996.7</v>
+        <v>6959525.7</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
@@ -771,34 +771,34 @@
         <v>0.9599999999999991</v>
       </c>
       <c r="Q4" t="n">
-        <v>20.03</v>
+        <v>20.08</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2003089511705247</v>
+        <v>0.2100090633709488</v>
       </c>
       <c r="S4" t="n">
         <v>17.71</v>
       </c>
       <c r="T4" t="n">
-        <v>1921.22</v>
+        <v>1919.78</v>
       </c>
       <c r="U4" t="n">
-        <v>6011</v>
+        <v>5996</v>
       </c>
       <c r="V4" t="n">
-        <v>1.078074530024275</v>
+        <v>1.065414618376306</v>
       </c>
       <c r="W4" t="n">
-        <v>1.205839924483739</v>
+        <v>1.195809809576962</v>
       </c>
       <c r="X4" t="n">
-        <v>85.84749984741211</v>
+        <v>86.25750007629395</v>
       </c>
       <c r="Y4" t="n">
-        <v>76.75148348681653</v>
+        <v>76.85168727491043</v>
       </c>
       <c r="Z4" t="n">
-        <v>817862155.7683105</v>
+        <v>505014494.2851028</v>
       </c>
     </row>
     <row r="5">
@@ -813,16 +813,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.53928385211141</v>
+        <v>17.16177825957456</v>
       </c>
       <c r="D5" t="n">
-        <v>3.860631666580619</v>
+        <v>3.817340147569769</v>
       </c>
       <c r="E5" t="n">
-        <v>41.75</v>
+        <v>40.90000152587891</v>
       </c>
       <c r="F5" t="n">
-        <v>94.05</v>
+        <v>86.86</v>
       </c>
       <c r="G5" t="n">
         <v>616</v>
@@ -837,7 +837,7 @@
         <v>12.46753246753247</v>
       </c>
       <c r="K5" t="n">
-        <v>150602237.5</v>
+        <v>150987920.1</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
@@ -856,7 +856,7 @@
         <v>16.41</v>
       </c>
       <c r="R5" t="n">
-        <v>13.67865218553079</v>
+        <v>13.34443811200479</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -868,19 +868,19 @@
         <v>7680</v>
       </c>
       <c r="V5" t="n">
-        <v>1.09186006865597</v>
+        <v>1.064882340259132</v>
       </c>
       <c r="W5" t="n">
-        <v>1.217718295844813</v>
+        <v>1.192135791450934</v>
       </c>
       <c r="X5" t="n">
-        <v>38.23750057220459</v>
+        <v>38.4080005645752</v>
       </c>
       <c r="Y5" t="n">
-        <v>34.28543378420311</v>
+        <v>34.3081734641152</v>
       </c>
       <c r="Z5" t="n">
-        <v>4057204337.25</v>
+        <v>5985724712.112732</v>
       </c>
     </row>
     <row r="6">
@@ -895,31 +895,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.945807379855867</v>
+        <v>1.918265883289643</v>
       </c>
       <c r="D6" t="n">
-        <v>1.82671147665601</v>
+        <v>1.800519278451383</v>
       </c>
       <c r="E6" t="n">
-        <v>54</v>
+        <v>53.45000076293945</v>
       </c>
       <c r="F6" t="n">
-        <v>75.48999999999999</v>
+        <v>67.87</v>
       </c>
       <c r="G6" t="n">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H6" t="n">
-        <v>96.95</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="J6" t="n">
-        <v>12.49618320610687</v>
+        <v>12.49808429118774</v>
       </c>
       <c r="K6" t="n">
-        <v>1460736.3</v>
+        <v>1500501.55</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
@@ -935,34 +935,34 @@
         <v>4.039999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>29.64</v>
+        <v>29.65</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1190959031998569</v>
+        <v>0.1177466048382598</v>
       </c>
       <c r="S6" t="n">
         <v>6.699999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>926.55</v>
+        <v>918</v>
       </c>
       <c r="U6" t="n">
-        <v>3274</v>
+        <v>3262</v>
       </c>
       <c r="V6" t="n">
-        <v>1.052498224290073</v>
+        <v>1.037934635267876</v>
       </c>
       <c r="W6" t="n">
-        <v>1.151363119673073</v>
+        <v>1.13565416352502</v>
       </c>
       <c r="X6" t="n">
-        <v>51.3064998626709</v>
+        <v>51.49649982452392</v>
       </c>
       <c r="Y6" t="n">
-        <v>46.90092906166144</v>
+        <v>47.06538529038897</v>
       </c>
       <c r="Z6" t="n">
-        <v>58891320</v>
+        <v>100700068.6873817</v>
       </c>
     </row>
     <row r="7">
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4.616804688591151</v>
+        <v>4.737178449183419</v>
       </c>
       <c r="D7" t="n">
-        <v>3.014943347696689</v>
+        <v>2.978715386334524</v>
       </c>
       <c r="E7" t="n">
-        <v>69.90000152587891</v>
+        <v>71.40000152587891</v>
       </c>
       <c r="F7" t="n">
-        <v>74.45999999999999</v>
+        <v>82.23</v>
       </c>
       <c r="G7" t="n">
         <v>433</v>
@@ -1001,7 +1001,7 @@
         <v>17.11316397228637</v>
       </c>
       <c r="K7" t="n">
-        <v>4602900.9</v>
+        <v>4557960.9</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
@@ -1020,7 +1020,7 @@
         <v>14.52</v>
       </c>
       <c r="R7" t="n">
-        <v>1.601861340894462</v>
+        <v>1.758463062848894</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1032,19 +1032,19 @@
         <v>7410</v>
       </c>
       <c r="V7" t="n">
-        <v>1.04947078155959</v>
+        <v>1.062579079427631</v>
       </c>
       <c r="W7" t="n">
-        <v>1.185939616252933</v>
+        <v>1.190505009478418</v>
       </c>
       <c r="X7" t="n">
-        <v>66.60500011444091</v>
+        <v>67.1950002670288</v>
       </c>
       <c r="Y7" t="n">
-        <v>58.940607572191</v>
+        <v>59.97454942013267</v>
       </c>
       <c r="Z7" t="n">
-        <v>113507956.2778168</v>
+        <v>166304240.9540634</v>
       </c>
     </row>
     <row r="8">
@@ -1059,16 +1059,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12.11359853412348</v>
+        <v>11.81978687819025</v>
       </c>
       <c r="D8" t="n">
-        <v>3.16860136747795</v>
+        <v>3.131094612755221</v>
       </c>
       <c r="E8" t="n">
-        <v>13.84000015258789</v>
+        <v>13.52999973297119</v>
       </c>
       <c r="F8" t="n">
-        <v>94.04000000000001</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="G8" t="n">
         <v>525</v>
@@ -1083,7 +1083,7 @@
         <v>12.22857142857143</v>
       </c>
       <c r="K8" t="n">
-        <v>191346571.55</v>
+        <v>195254360.1</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
@@ -1102,7 +1102,7 @@
         <v>18</v>
       </c>
       <c r="R8" t="n">
-        <v>8.944997166645532</v>
+        <v>8.68869226543503</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1114,19 +1114,19 @@
         <v>6420</v>
       </c>
       <c r="V8" t="n">
-        <v>1.095456706617196</v>
+        <v>1.065941830112122</v>
       </c>
       <c r="W8" t="n">
-        <v>1.227310725763724</v>
+        <v>1.198571825861892</v>
       </c>
       <c r="X8" t="n">
-        <v>12.63400011062622</v>
+        <v>12.69300007820129</v>
       </c>
       <c r="Y8" t="n">
-        <v>11.27668801555989</v>
+        <v>11.28843465283507</v>
       </c>
       <c r="Z8" t="n">
-        <v>1807763326.170837</v>
+        <v>3206874380.558953</v>
       </c>
     </row>
     <row r="9">
@@ -1141,16 +1141,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12.83055645749879</v>
+        <v>12.5094977665481</v>
       </c>
       <c r="D9" t="n">
-        <v>3.303312733650152</v>
+        <v>3.264679692203618</v>
       </c>
       <c r="E9" t="n">
-        <v>366.25</v>
+        <v>357.75</v>
       </c>
       <c r="F9" t="n">
-        <v>94.14</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>552</v>
@@ -1165,7 +1165,7 @@
         <v>12.32971014492754</v>
       </c>
       <c r="K9" t="n">
-        <v>915439.05</v>
+        <v>916677.05</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
@@ -1184,7 +1184,7 @@
         <v>17.04</v>
       </c>
       <c r="R9" t="n">
-        <v>9.527243723848633</v>
+        <v>9.244818074344487</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1196,19 +1196,19 @@
         <v>6806</v>
       </c>
       <c r="V9" t="n">
-        <v>1.094304373454856</v>
+        <v>1.06401961522583</v>
       </c>
       <c r="W9" t="n">
-        <v>1.22493525564159</v>
+        <v>1.195049369923079</v>
       </c>
       <c r="X9" t="n">
-        <v>334.6875045776367</v>
+        <v>336.2250045776367</v>
       </c>
       <c r="Y9" t="n">
-        <v>298.9953945020283</v>
+        <v>299.3600172543727</v>
       </c>
       <c r="Z9" t="n">
-        <v>356734092.5</v>
+        <v>283194184.5</v>
       </c>
     </row>
     <row r="10">
@@ -1223,31 +1223,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.722226457964336</v>
+        <v>1.697652534271771</v>
       </c>
       <c r="D10" t="n">
-        <v>1.311823790480891</v>
+        <v>1.290191493246491</v>
       </c>
       <c r="E10" t="n">
-        <v>62.95000076293945</v>
+        <v>62.34999847412109</v>
       </c>
       <c r="F10" t="n">
-        <v>85.69</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H10" t="n">
-        <v>83.09</v>
+        <v>82.95999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="J10" t="n">
-        <v>12.30882352941176</v>
+        <v>12.34074074074074</v>
       </c>
       <c r="K10" t="n">
-        <v>10963097.2</v>
+        <v>10839670.95</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
@@ -1263,34 +1263,34 @@
         <v>5.609999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>43.8</v>
+        <v>43.68</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4104026674834453</v>
+        <v>0.4074610410252792</v>
       </c>
       <c r="S10" t="n">
         <v>4.98</v>
       </c>
       <c r="T10" t="n">
-        <v>429.07</v>
+        <v>422.85</v>
       </c>
       <c r="U10" t="n">
-        <v>1674</v>
+        <v>1666</v>
       </c>
       <c r="V10" t="n">
-        <v>1.045854803179177</v>
+        <v>1.033739506198872</v>
       </c>
       <c r="W10" t="n">
-        <v>1.123365401304318</v>
+        <v>1.112178047661594</v>
       </c>
       <c r="X10" t="n">
-        <v>60.19000015258789</v>
+        <v>60.31500015258789</v>
       </c>
       <c r="Y10" t="n">
-        <v>56.03697665056218</v>
+        <v>56.06116629006915</v>
       </c>
       <c r="Z10" t="n">
-        <v>624130309.614315</v>
+        <v>448572886.5721664</v>
       </c>
     </row>
     <row r="11">
@@ -1305,31 +1305,31 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.339677318592491</v>
+        <v>2.325211195871371</v>
       </c>
       <c r="D11" t="n">
-        <v>1.983783508241808</v>
+        <v>1.956293313120947</v>
       </c>
       <c r="E11" t="n">
-        <v>52.20000076293945</v>
+        <v>51.95000076293945</v>
       </c>
       <c r="F11" t="n">
-        <v>86.29000000000001</v>
+        <v>81.58</v>
       </c>
       <c r="G11" t="n">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H11" t="n">
-        <v>83.47</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="J11" t="n">
-        <v>15.29752066115702</v>
+        <v>15.32365145228216</v>
       </c>
       <c r="K11" t="n">
-        <v>1104809.95</v>
+        <v>1064689.65</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
@@ -1345,34 +1345,34 @@
         <v>7.319999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>22.8</v>
+        <v>22.81</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3558938103506826</v>
+        <v>0.3689178827504245</v>
       </c>
       <c r="S11" t="n">
         <v>7.549999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>703.14</v>
+        <v>699.33</v>
       </c>
       <c r="U11" t="n">
-        <v>3702</v>
+        <v>3693</v>
       </c>
       <c r="V11" t="n">
-        <v>1.063493851388237</v>
+        <v>1.054148118575511</v>
       </c>
       <c r="W11" t="n">
-        <v>1.156790750144374</v>
+        <v>1.150142784548979</v>
       </c>
       <c r="X11" t="n">
-        <v>49.08350028991699</v>
+        <v>49.28150024414062</v>
       </c>
       <c r="Y11" t="n">
-        <v>45.12484280880064</v>
+        <v>45.16830558851987</v>
       </c>
       <c r="Z11" t="n">
-        <v>33460357.08904648</v>
+        <v>28373220.21669006</v>
       </c>
     </row>
     <row r="12">
@@ -1387,31 +1387,31 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.052919229141477</v>
+        <v>2.022589711693981</v>
       </c>
       <c r="D12" t="n">
-        <v>1.943827296233705</v>
+        <v>1.916653122104031</v>
       </c>
       <c r="E12" t="n">
-        <v>50</v>
+        <v>49.47000122070312</v>
       </c>
       <c r="F12" t="n">
-        <v>86.2</v>
+        <v>79.39</v>
       </c>
       <c r="G12" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H12" t="n">
-        <v>90.3</v>
+        <v>90.26000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="J12" t="n">
-        <v>13.1865671641791</v>
+        <v>13.2059925093633</v>
       </c>
       <c r="K12" t="n">
-        <v>285816</v>
+        <v>249412.6</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
@@ -1427,34 +1427,34 @@
         <v>8.109999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>24.7</v>
+        <v>24.69</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1090919329077717</v>
+        <v>0.10593658958995</v>
       </c>
       <c r="S12" t="n">
         <v>4.671</v>
       </c>
       <c r="T12" t="n">
-        <v>747.59</v>
+        <v>743.11</v>
       </c>
       <c r="U12" t="n">
-        <v>3534</v>
+        <v>3526</v>
       </c>
       <c r="V12" t="n">
-        <v>1.050696077734516</v>
+        <v>1.03688955744303</v>
       </c>
       <c r="W12" t="n">
-        <v>1.123783473066263</v>
+        <v>1.111134743563848</v>
       </c>
       <c r="X12" t="n">
-        <v>47.58750038146972</v>
+        <v>47.7100004196167</v>
       </c>
       <c r="Y12" t="n">
-        <v>44.49255679439219</v>
+        <v>44.5220541498264</v>
       </c>
       <c r="Z12" t="n">
-        <v>2052000</v>
+        <v>5838944.24407959</v>
       </c>
     </row>
     <row r="13">
@@ -1469,31 +1469,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.211631449338959</v>
+        <v>2.178995188077034</v>
       </c>
       <c r="D13" t="n">
-        <v>2.06389603509892</v>
+        <v>2.035763066958677</v>
       </c>
       <c r="E13" t="n">
-        <v>53.95000076293945</v>
+        <v>53.29999923706055</v>
       </c>
       <c r="F13" t="n">
-        <v>82.81999999999999</v>
+        <v>72.95</v>
       </c>
       <c r="G13" t="n">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H13" t="n">
-        <v>90.68000000000001</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="I13" t="n">
         <v>2.55</v>
       </c>
       <c r="J13" t="n">
-        <v>13.86335403726708</v>
+        <v>13.86915887850467</v>
       </c>
       <c r="K13" t="n">
-        <v>15332059.3</v>
+        <v>15267449.95</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
@@ -1512,31 +1512,31 @@
         <v>19.92</v>
       </c>
       <c r="R13" t="n">
-        <v>0.1477354142400382</v>
+        <v>0.1432321211183574</v>
       </c>
       <c r="S13" t="n">
         <v>12.5</v>
       </c>
       <c r="T13" t="n">
-        <v>822.15</v>
+        <v>817.08</v>
       </c>
       <c r="U13" t="n">
-        <v>4464</v>
+        <v>4452</v>
       </c>
       <c r="V13" t="n">
-        <v>1.044661973326304</v>
+        <v>1.029583609640394</v>
       </c>
       <c r="W13" t="n">
-        <v>1.112280691001375</v>
+        <v>1.097280612540143</v>
       </c>
       <c r="X13" t="n">
-        <v>51.6435001373291</v>
+        <v>51.7685001373291</v>
       </c>
       <c r="Y13" t="n">
-        <v>48.50394437250262</v>
+        <v>48.57462952313907</v>
       </c>
       <c r="Z13" t="n">
-        <v>766930767.6456299</v>
+        <v>553476519.5775032</v>
       </c>
     </row>
     <row r="14">
@@ -1551,16 +1551,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6.350508801659792</v>
+        <v>6.26886667977521</v>
       </c>
       <c r="D14" t="n">
-        <v>3.329413855778156</v>
+        <v>3.291264706229798</v>
       </c>
       <c r="E14" t="n">
-        <v>345.6499938964844</v>
+        <v>341.7999877929688</v>
       </c>
       <c r="F14" t="n">
-        <v>92.95999999999999</v>
+        <v>85.81</v>
       </c>
       <c r="G14" t="n">
         <v>1248</v>
@@ -1575,7 +1575,7 @@
         <v>13.08653846153846</v>
       </c>
       <c r="K14" t="n">
-        <v>21175.1</v>
+        <v>19825.05</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
@@ -1594,7 +1594,7 @@
         <v>8.07</v>
       </c>
       <c r="R14" t="n">
-        <v>3.021094945881637</v>
+        <v>2.977601973545412</v>
       </c>
       <c r="S14" t="n">
         <v>1.685</v>
@@ -1606,19 +1606,19 @@
         <v>16332</v>
       </c>
       <c r="V14" t="n">
-        <v>1.045641874988728</v>
+        <v>1.031817868632485</v>
       </c>
       <c r="W14" t="n">
-        <v>1.100547857480891</v>
+        <v>1.088122570458615</v>
       </c>
       <c r="X14" t="n">
-        <v>330.5625015258789</v>
+        <v>331.2600006103515</v>
       </c>
       <c r="Y14" t="n">
-        <v>314.0708434866823</v>
+        <v>314.1190129425485</v>
       </c>
       <c r="Z14" t="n">
-        <v>23854688.67877197</v>
+        <v>1372326.95098877</v>
       </c>
     </row>
     <row r="15">
@@ -1633,16 +1633,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3.333344798543052</v>
+        <v>3.295162774231783</v>
       </c>
       <c r="D15" t="n">
-        <v>3.333344798543052</v>
+        <v>3.295162774231783</v>
       </c>
       <c r="E15" t="n">
-        <v>116.0500030517578</v>
+        <v>114.9499969482422</v>
       </c>
       <c r="F15" t="n">
-        <v>89.7</v>
+        <v>83.23</v>
       </c>
       <c r="G15" t="n">
         <v>1227</v>
@@ -1657,7 +1657,7 @@
         <v>13.92094539527302</v>
       </c>
       <c r="K15" t="n">
-        <v>69595247.90000001</v>
+        <v>70448179.3</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
@@ -1688,19 +1688,19 @@
         <v>17081</v>
       </c>
       <c r="V15" t="n">
-        <v>1.045636819512112</v>
+        <v>1.033258395991779</v>
       </c>
       <c r="W15" t="n">
-        <v>1.104932204854724</v>
+        <v>1.093853358081359</v>
       </c>
       <c r="X15" t="n">
-        <v>110.9850006103516</v>
+        <v>111.2500003814697</v>
       </c>
       <c r="Y15" t="n">
-        <v>105.0290710523873</v>
+        <v>105.0872094499639</v>
       </c>
       <c r="Z15" t="n">
-        <v>6491056038.144791</v>
+        <v>10080260653.88351</v>
       </c>
     </row>
     <row r="16">
@@ -1715,16 +1715,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6.933142238974012</v>
+        <v>6.874554762804874</v>
       </c>
       <c r="D16" t="n">
-        <v>3.333344798543052</v>
+        <v>3.295162774231783</v>
       </c>
       <c r="E16" t="n">
-        <v>262</v>
+        <v>259.9500122070312</v>
       </c>
       <c r="F16" t="n">
-        <v>81.26000000000001</v>
+        <v>74.58</v>
       </c>
       <c r="G16" t="n">
         <v>1144</v>
@@ -1739,7 +1739,7 @@
         <v>14.06905594405594</v>
       </c>
       <c r="K16" t="n">
-        <v>138546.7</v>
+        <v>146747.7</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
@@ -1758,7 +1758,7 @@
         <v>7.63</v>
       </c>
       <c r="R16" t="n">
-        <v>3.59979744043096</v>
+        <v>3.579391988573091</v>
       </c>
       <c r="S16" t="n">
         <v>18.91</v>
@@ -1770,19 +1770,19 @@
         <v>16095</v>
       </c>
       <c r="V16" t="n">
-        <v>1.049164570111387</v>
+        <v>1.038056109495539</v>
       </c>
       <c r="W16" t="n">
-        <v>1.117241205905939</v>
+        <v>1.107677221521853</v>
       </c>
       <c r="X16" t="n">
-        <v>249.7225006103516</v>
+        <v>250.4200012207031</v>
       </c>
       <c r="Y16" t="n">
-        <v>234.5062092366632</v>
+        <v>234.6802905722683</v>
       </c>
       <c r="Z16" t="n">
-        <v>39878758</v>
+        <v>47857837.04736328</v>
       </c>
     </row>
     <row r="17">
@@ -1797,16 +1797,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3.387116675958203</v>
+        <v>3.349094851152814</v>
       </c>
       <c r="D17" t="n">
-        <v>2.881248852045696</v>
+        <v>2.846137947762975</v>
       </c>
       <c r="E17" t="n">
-        <v>111.1999969482422</v>
+        <v>110.1500015258789</v>
       </c>
       <c r="F17" t="n">
-        <v>78.84</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="G17" t="n">
         <v>479</v>
@@ -1821,7 +1821,7 @@
         <v>14.01461377870564</v>
       </c>
       <c r="K17" t="n">
-        <v>1250207.3</v>
+        <v>1264153.15</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
@@ -1840,7 +1840,7 @@
         <v>14</v>
       </c>
       <c r="R17" t="n">
-        <v>0.505867823912507</v>
+        <v>0.5029569033898387</v>
       </c>
       <c r="S17" t="n">
         <v>13.37</v>
@@ -1852,19 +1852,19 @@
         <v>6713</v>
       </c>
       <c r="V17" t="n">
-        <v>1.037676397510717</v>
+        <v>1.026393659973318</v>
       </c>
       <c r="W17" t="n">
-        <v>1.10531036857537</v>
+        <v>1.094572789664137</v>
       </c>
       <c r="X17" t="n">
-        <v>107.1625</v>
+        <v>107.3174999237061</v>
       </c>
       <c r="Y17" t="n">
-        <v>100.6052237540913</v>
+        <v>100.6328702540447</v>
       </c>
       <c r="Z17" t="n">
-        <v>157507456.4773865</v>
+        <v>263743053.5035629</v>
       </c>
     </row>
     <row r="18">
@@ -1879,31 +1879,31 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4.590262265259418</v>
+        <v>4.548479841506535</v>
       </c>
       <c r="D18" t="n">
-        <v>3.590072884071009</v>
+        <v>3.549502109510268</v>
       </c>
       <c r="E18" t="n">
-        <v>210.3500061035156</v>
+        <v>208.6499938964844</v>
       </c>
       <c r="F18" t="n">
-        <v>90.72</v>
+        <v>84.39</v>
       </c>
       <c r="G18" t="n">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H18" t="n">
-        <v>90.78</v>
+        <v>90.77</v>
       </c>
       <c r="I18" t="n">
         <v>2.08</v>
       </c>
       <c r="J18" t="n">
-        <v>12.95869356388088</v>
+        <v>12.96538461538461</v>
       </c>
       <c r="K18" t="n">
-        <v>8820.5</v>
+        <v>8719.25</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
@@ -1922,31 +1922,31 @@
         <v>8.81</v>
       </c>
       <c r="R18" t="n">
-        <v>1.000189381188409</v>
+        <v>0.9989777319962672</v>
       </c>
       <c r="S18" t="n">
         <v>21.88</v>
       </c>
       <c r="T18" t="n">
-        <v>2169.48</v>
+        <v>2166.47</v>
       </c>
       <c r="U18" t="n">
-        <v>13490</v>
+        <v>13484</v>
       </c>
       <c r="V18" t="n">
-        <v>1.044400062685984</v>
+        <v>1.033854812298125</v>
       </c>
       <c r="W18" t="n">
-        <v>1.098660223137901</v>
+        <v>1.090140125626574</v>
       </c>
       <c r="X18" t="n">
-        <v>201.4075004577637</v>
+        <v>201.8175003051758</v>
       </c>
       <c r="Y18" t="n">
-        <v>191.4604731048983</v>
+        <v>191.3974075365401</v>
       </c>
       <c r="Z18" t="n">
-        <v>3578263.953826904</v>
+        <v>625949.9816894531</v>
       </c>
     </row>
     <row r="19">
@@ -1961,16 +1961,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4.572169081773092</v>
+        <v>4.529583933593418</v>
       </c>
       <c r="D19" t="n">
-        <v>3.772369556710547</v>
+        <v>3.730117409631104</v>
       </c>
       <c r="E19" t="n">
-        <v>265.6000061035156</v>
+        <v>263.3999938964844</v>
       </c>
       <c r="F19" t="n">
-        <v>90.03</v>
+        <v>84.44</v>
       </c>
       <c r="G19" t="n">
         <v>1010</v>
@@ -1985,7 +1985,7 @@
         <v>13.88613861386139</v>
       </c>
       <c r="K19" t="n">
-        <v>1899920.2</v>
+        <v>1868394.9</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
@@ -2004,7 +2004,7 @@
         <v>8.119999999999999</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7997995250625447</v>
+        <v>0.7994665239623142</v>
       </c>
       <c r="S19" t="n">
         <v>28.764</v>
@@ -2016,19 +2016,19 @@
         <v>14025</v>
       </c>
       <c r="V19" t="n">
-        <v>1.046390256680185</v>
+        <v>1.035001012445999</v>
       </c>
       <c r="W19" t="n">
-        <v>1.105369184653776</v>
+        <v>1.095435058452675</v>
       </c>
       <c r="X19" t="n">
-        <v>253.8249992370606</v>
+        <v>254.4924987792969</v>
       </c>
       <c r="Y19" t="n">
-        <v>240.2817174487335</v>
+        <v>240.4524046076655</v>
       </c>
       <c r="Z19" t="n">
-        <v>302249885.3457336</v>
+        <v>359410081.8717346</v>
       </c>
     </row>
     <row r="20">
@@ -2043,31 +2043,31 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3.822291606181272</v>
+        <v>3.816569466791282</v>
       </c>
       <c r="D20" t="n">
-        <v>3.333344798543052</v>
+        <v>3.295162774231783</v>
       </c>
       <c r="E20" t="n">
-        <v>153.1499938964844</v>
+        <v>152.9499969482422</v>
       </c>
       <c r="F20" t="n">
-        <v>91.91</v>
+        <v>92.45999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H20" t="n">
-        <v>88.84</v>
+        <v>88.83</v>
       </c>
       <c r="I20" t="n">
         <v>1.71</v>
       </c>
       <c r="J20" t="n">
-        <v>15.42410714285714</v>
+        <v>15.43074173369079</v>
       </c>
       <c r="K20" t="n">
-        <v>43311.2</v>
+        <v>42969.75</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
@@ -2086,31 +2086,31 @@
         <v>6.55</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4889468076382197</v>
+        <v>0.5214066925594985</v>
       </c>
       <c r="S20" t="n">
         <v>19.36</v>
       </c>
       <c r="T20" t="n">
-        <v>1917.49</v>
+        <v>1913.8</v>
       </c>
       <c r="U20" t="n">
-        <v>17275</v>
+        <v>17267</v>
       </c>
       <c r="V20" t="n">
-        <v>1.0410045955022</v>
+        <v>1.037212830029616</v>
       </c>
       <c r="W20" t="n">
-        <v>1.087944527425008</v>
+        <v>1.087439576992383</v>
       </c>
       <c r="X20" t="n">
-        <v>147.1175003051758</v>
+        <v>147.4625</v>
       </c>
       <c r="Y20" t="n">
-        <v>140.7700393134621</v>
+        <v>140.6514901464851</v>
       </c>
       <c r="Z20" t="n">
-        <v>5079832.14755249</v>
+        <v>2036376.259368896</v>
       </c>
     </row>
   </sheetData>

--- a/ETF動態清單.xlsx
+++ b/ETF動態清單.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z20"/>
+  <dimension ref="A1:Z21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,13 +567,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9408868667740447</v>
+        <v>0.889043205104652</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6752560381909085</v>
+        <v>0.6423310454307738</v>
       </c>
       <c r="E2" t="n">
-        <v>32.2400016784668</v>
+        <v>32.24</v>
       </c>
       <c r="F2" t="n">
         <v>84.13</v>
@@ -591,7 +591,7 @@
         <v>8.439024390243903</v>
       </c>
       <c r="K2" t="n">
-        <v>150065872.95</v>
+        <v>151778290.3</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
@@ -610,7 +610,7 @@
         <v>386.28</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2656308285831361</v>
+        <v>0.2467121596738782</v>
       </c>
       <c r="S2" t="n">
         <v>1.67</v>
@@ -622,19 +622,19 @@
         <v>346</v>
       </c>
       <c r="V2" t="n">
-        <v>1.06188866357906</v>
+        <v>1.061888607094628</v>
       </c>
       <c r="W2" t="n">
-        <v>1.163828189656442</v>
+        <v>1.163828118798113</v>
       </c>
       <c r="X2" t="n">
-        <v>30.36099996566772</v>
+        <v>30.36100000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>27.70168480622895</v>
+        <v>27.70168505061925</v>
       </c>
       <c r="Z2" t="n">
-        <v>3156540414.574615</v>
+        <v>3195529436.32</v>
       </c>
     </row>
     <row r="3">
@@ -649,31 +649,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.394709788329697</v>
+        <v>1.382106335092956</v>
       </c>
       <c r="D3" t="n">
-        <v>1.022593906890337</v>
+        <v>1.005945493752752</v>
       </c>
       <c r="E3" t="n">
-        <v>40.65999984741211</v>
+        <v>40.66</v>
       </c>
       <c r="F3" t="n">
         <v>68.23</v>
       </c>
       <c r="G3" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H3" t="n">
-        <v>95.38</v>
+        <v>96.97</v>
       </c>
       <c r="I3" t="n">
-        <v>7.34</v>
+        <v>7.5</v>
       </c>
       <c r="J3" t="n">
-        <v>10.21538461538461</v>
+        <v>10.33333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>7501232.05</v>
+        <v>7705117.65</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
@@ -683,40 +683,40 @@
         <v>18.77</v>
       </c>
       <c r="O3" t="n">
-        <v>-10.77</v>
+        <v>-0.73</v>
       </c>
       <c r="P3" t="n">
-        <v>8</v>
+        <v>18.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>162.08</v>
+        <v>159.78</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3721158814393601</v>
+        <v>0.3761608413402042</v>
       </c>
       <c r="S3" t="n">
         <v>0.78</v>
       </c>
       <c r="T3" t="n">
-        <v>477.03</v>
+        <v>495.22</v>
       </c>
       <c r="U3" t="n">
-        <v>664</v>
+        <v>682</v>
       </c>
       <c r="V3" t="n">
-        <v>1.034658244628979</v>
+        <v>1.034658252328362</v>
       </c>
       <c r="W3" t="n">
-        <v>1.132499029025452</v>
+        <v>1.132499045991609</v>
       </c>
       <c r="X3" t="n">
-        <v>39.29800014495849</v>
+        <v>39.29800000000002</v>
       </c>
       <c r="Y3" t="n">
-        <v>35.90290040460452</v>
+        <v>35.90290000147273</v>
       </c>
       <c r="Z3" t="n">
-        <v>269600398.28825</v>
+        <v>279501678.54</v>
       </c>
     </row>
     <row r="4">
@@ -731,31 +731,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.775648968703858</v>
+        <v>2.765708222274599</v>
       </c>
       <c r="D4" t="n">
-        <v>2.56563990533291</v>
+        <v>2.48696380890904</v>
       </c>
       <c r="E4" t="n">
-        <v>91.90000152587891</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="F4" t="n">
         <v>86.56999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="H4" t="n">
-        <v>97.13</v>
+        <v>97.17</v>
       </c>
       <c r="I4" t="n">
-        <v>3.94</v>
+        <v>3.93</v>
       </c>
       <c r="J4" t="n">
-        <v>12.31211498973306</v>
+        <v>12.29090909090909</v>
       </c>
       <c r="K4" t="n">
-        <v>6959525.7</v>
+        <v>7362016.7</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
@@ -771,565 +771,565 @@
         <v>0.9599999999999991</v>
       </c>
       <c r="Q4" t="n">
-        <v>20.08</v>
+        <v>19.85</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2100090633709488</v>
+        <v>0.2787444133655597</v>
       </c>
       <c r="S4" t="n">
         <v>17.71</v>
       </c>
       <c r="T4" t="n">
-        <v>1919.78</v>
+        <v>1946.3</v>
       </c>
       <c r="U4" t="n">
-        <v>5996</v>
+        <v>6084</v>
       </c>
       <c r="V4" t="n">
-        <v>1.065414618376306</v>
+        <v>1.065414601628844</v>
       </c>
       <c r="W4" t="n">
-        <v>1.195809809576962</v>
+        <v>1.195809758274451</v>
       </c>
       <c r="X4" t="n">
-        <v>86.25750007629395</v>
+        <v>86.25749999999999</v>
       </c>
       <c r="Y4" t="n">
-        <v>76.85168727491043</v>
+        <v>76.85168929597241</v>
       </c>
       <c r="Z4" t="n">
-        <v>505014494.2851028</v>
+        <v>535654864.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>00631L.TW</t>
+          <t>00663L.TW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>國泰臺灣加權正2</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.16177825957456</v>
+        <v>13.13108146543407</v>
       </c>
       <c r="D5" t="n">
-        <v>3.817340147569769</v>
+        <v>3.209099559207814</v>
       </c>
       <c r="E5" t="n">
-        <v>40.90000152587891</v>
+        <v>118.1</v>
       </c>
       <c r="F5" t="n">
-        <v>86.86</v>
+        <v>86.66</v>
       </c>
       <c r="G5" t="n">
-        <v>616</v>
+        <v>564</v>
       </c>
       <c r="H5" t="n">
-        <v>90.75</v>
+        <v>89.89</v>
       </c>
       <c r="I5" t="n">
-        <v>3.81</v>
+        <v>3.76</v>
       </c>
       <c r="J5" t="n">
-        <v>12.46753246753247</v>
+        <v>11.9113475177305</v>
       </c>
       <c r="K5" t="n">
-        <v>150987920.1</v>
+        <v>4849020.85</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>14.65</v>
+        <v>15.99</v>
       </c>
       <c r="O5" t="n">
-        <v>-16.11</v>
+        <v>-24.46</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.459999999999999</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>16.41</v>
+        <v>18.35</v>
       </c>
       <c r="R5" t="n">
-        <v>13.34443811200479</v>
+        <v>9.921981906226257</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2346.5</v>
+        <v>2121.97</v>
       </c>
       <c r="U5" t="n">
-        <v>7680</v>
+        <v>6718</v>
       </c>
       <c r="V5" t="n">
-        <v>1.064882340259132</v>
+        <v>1.064395475643278</v>
       </c>
       <c r="W5" t="n">
-        <v>1.192135791450934</v>
+        <v>1.195043235807811</v>
       </c>
       <c r="X5" t="n">
-        <v>38.4080005645752</v>
+        <v>110.9550000000001</v>
       </c>
       <c r="Y5" t="n">
-        <v>34.3081734641152</v>
+        <v>98.82487634028415</v>
       </c>
       <c r="Z5" t="n">
-        <v>5985724712.112732</v>
+        <v>485080278.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>00913.TW</t>
+          <t>00631L.TW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>兆豐台灣晶圓製造</t>
+          <t>元大台灣50正2</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.918265883289643</v>
+        <v>17.54099128073863</v>
       </c>
       <c r="D6" t="n">
-        <v>1.800519278451383</v>
+        <v>3.655453318302473</v>
       </c>
       <c r="E6" t="n">
-        <v>53.45000076293945</v>
+        <v>40.9</v>
       </c>
       <c r="F6" t="n">
-        <v>67.87</v>
+        <v>86.86</v>
       </c>
       <c r="G6" t="n">
-        <v>261</v>
+        <v>644</v>
       </c>
       <c r="H6" t="n">
-        <v>96.93000000000001</v>
+        <v>89.44</v>
       </c>
       <c r="I6" t="n">
-        <v>3.52</v>
+        <v>3.74</v>
       </c>
       <c r="J6" t="n">
-        <v>12.49808429118774</v>
+        <v>12.68167701863354</v>
       </c>
       <c r="K6" t="n">
-        <v>1500501.55</v>
+        <v>152407612.3</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>2</v>
       </c>
       <c r="N6" t="n">
-        <v>13.5</v>
+        <v>17.37</v>
       </c>
       <c r="O6" t="n">
-        <v>-9.460000000000001</v>
+        <v>-12.43</v>
       </c>
       <c r="P6" t="n">
-        <v>4.039999999999999</v>
+        <v>4.940000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>29.65</v>
+        <v>15.49</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1177466048382598</v>
+        <v>13.88553796243616</v>
       </c>
       <c r="S6" t="n">
-        <v>6.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>918</v>
+        <v>2407.1</v>
       </c>
       <c r="U6" t="n">
-        <v>3262</v>
+        <v>8167</v>
       </c>
       <c r="V6" t="n">
-        <v>1.037934635267876</v>
+        <v>1.064882316184129</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13565416352502</v>
+        <v>1.192135773993529</v>
       </c>
       <c r="X6" t="n">
-        <v>51.49649982452392</v>
+        <v>38.40799999999999</v>
       </c>
       <c r="Y6" t="n">
-        <v>47.06538529038897</v>
+        <v>34.30817268656348</v>
       </c>
       <c r="Z6" t="n">
-        <v>100700068.6873817</v>
+        <v>6070032844.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>00715L.TW</t>
+          <t>00904.TW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>期街口布蘭特正2</t>
+          <t>台新臺灣半導體30</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4.737178449183419</v>
+        <v>1.993160407439695</v>
       </c>
       <c r="D7" t="n">
-        <v>2.978715386334524</v>
+        <v>1.866808375641466</v>
       </c>
       <c r="E7" t="n">
-        <v>71.40000152587891</v>
+        <v>44.27</v>
       </c>
       <c r="F7" t="n">
-        <v>82.23</v>
+        <v>76.23</v>
       </c>
       <c r="G7" t="n">
-        <v>433</v>
+        <v>239</v>
       </c>
       <c r="H7" t="n">
-        <v>78.98</v>
+        <v>99.16</v>
       </c>
       <c r="I7" t="n">
-        <v>3.39</v>
+        <v>3.55</v>
       </c>
       <c r="J7" t="n">
-        <v>17.11316397228637</v>
+        <v>10.78242677824268</v>
       </c>
       <c r="K7" t="n">
-        <v>4557960.9</v>
+        <v>1727945.1</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>2</v>
       </c>
       <c r="N7" t="n">
-        <v>32.14</v>
+        <v>11.85</v>
       </c>
       <c r="O7" t="n">
-        <v>-45.45</v>
+        <v>-12.45</v>
       </c>
       <c r="P7" t="n">
-        <v>-13.31</v>
+        <v>-0.5999999999999996</v>
       </c>
       <c r="Q7" t="n">
-        <v>14.52</v>
+        <v>37.53</v>
       </c>
       <c r="R7" t="n">
-        <v>1.758463062848894</v>
+        <v>0.1263520317982292</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4.850000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>1468.89</v>
+        <v>848.62</v>
       </c>
       <c r="U7" t="n">
-        <v>7410</v>
+        <v>2577</v>
       </c>
       <c r="V7" t="n">
-        <v>1.062579079427631</v>
+        <v>1.034817264875352</v>
       </c>
       <c r="W7" t="n">
-        <v>1.190505009478418</v>
+        <v>1.110272742392005</v>
       </c>
       <c r="X7" t="n">
-        <v>67.1950002670288</v>
+        <v>42.7805</v>
       </c>
       <c r="Y7" t="n">
-        <v>59.97454942013267</v>
+        <v>39.87308551286542</v>
       </c>
       <c r="Z7" t="n">
-        <v>166304240.9540634</v>
+        <v>207567199.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>00685L.TW</t>
+          <t>00913.TW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>群益臺灣加權正2</t>
+          <t>兆豐台灣晶圓製造</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11.81978687819025</v>
+        <v>1.90889450815724</v>
       </c>
       <c r="D8" t="n">
-        <v>3.131094612755221</v>
+        <v>1.769144891987639</v>
       </c>
       <c r="E8" t="n">
-        <v>13.52999973297119</v>
+        <v>53.45</v>
       </c>
       <c r="F8" t="n">
-        <v>86.79000000000001</v>
+        <v>67.87</v>
       </c>
       <c r="G8" t="n">
-        <v>525</v>
+        <v>262</v>
       </c>
       <c r="H8" t="n">
-        <v>87.43000000000001</v>
+        <v>96.18000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>3.31</v>
+        <v>3.5</v>
       </c>
       <c r="J8" t="n">
-        <v>12.22857142857143</v>
+        <v>12.79770992366412</v>
       </c>
       <c r="K8" t="n">
-        <v>195254360.1</v>
+        <v>1545722.5</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>15.89</v>
+        <v>13.5</v>
       </c>
       <c r="O8" t="n">
-        <v>-18.5</v>
+        <v>-9.19</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.609999999999999</v>
+        <v>4.31</v>
       </c>
       <c r="Q8" t="n">
-        <v>18</v>
+        <v>28.72</v>
       </c>
       <c r="R8" t="n">
-        <v>8.68869226543503</v>
+        <v>0.1397496161696008</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>6.699999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>1736.81</v>
+        <v>916.5599999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>6420</v>
+        <v>3353</v>
       </c>
       <c r="V8" t="n">
-        <v>1.065941830112122</v>
+        <v>1.037934616915713</v>
       </c>
       <c r="W8" t="n">
-        <v>1.198571825861892</v>
+        <v>1.135654129427339</v>
       </c>
       <c r="X8" t="n">
-        <v>12.69300007820129</v>
+        <v>51.49649999999997</v>
       </c>
       <c r="Y8" t="n">
-        <v>11.28843465283507</v>
+        <v>47.06538603170712</v>
       </c>
       <c r="Z8" t="n">
-        <v>3206874380.558953</v>
+        <v>105798609.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>00675L.TW</t>
+          <t>00685L.TW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>富邦臺灣加權正2</t>
+          <t>群益臺灣加權正2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12.5094977665481</v>
+        <v>11.90524461500531</v>
       </c>
       <c r="D9" t="n">
-        <v>3.264679692203618</v>
+        <v>3.028709694449856</v>
       </c>
       <c r="E9" t="n">
-        <v>357.75</v>
+        <v>13.53</v>
       </c>
       <c r="F9" t="n">
-        <v>86.70999999999999</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>552</v>
+        <v>514</v>
       </c>
       <c r="H9" t="n">
-        <v>86.23</v>
+        <v>88.52</v>
       </c>
       <c r="I9" t="n">
-        <v>3.22</v>
+        <v>3.46</v>
       </c>
       <c r="J9" t="n">
-        <v>12.32971014492754</v>
+        <v>12.18093385214008</v>
       </c>
       <c r="K9" t="n">
-        <v>916677.05</v>
+        <v>196257788.75</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>15.7</v>
+        <v>15.89</v>
       </c>
       <c r="O9" t="n">
-        <v>-24.73</v>
+        <v>-18.5</v>
       </c>
       <c r="P9" t="n">
-        <v>-9.030000000000001</v>
+        <v>-2.609999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>17.04</v>
+        <v>18.65</v>
       </c>
       <c r="R9" t="n">
-        <v>9.244818074344487</v>
+        <v>8.876534920555454</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1778.9</v>
+        <v>1777.84</v>
       </c>
       <c r="U9" t="n">
-        <v>6806</v>
+        <v>6261</v>
       </c>
       <c r="V9" t="n">
-        <v>1.06401961522583</v>
+        <v>1.065941857716852</v>
       </c>
       <c r="W9" t="n">
-        <v>1.195049369923079</v>
+        <v>1.198571856529974</v>
       </c>
       <c r="X9" t="n">
-        <v>336.2250045776367</v>
+        <v>12.693</v>
       </c>
       <c r="Y9" t="n">
-        <v>299.3600172543727</v>
+        <v>11.28843458678494</v>
       </c>
       <c r="Z9" t="n">
-        <v>283194184.5</v>
+        <v>3226934008.32</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>00935.TW</t>
+          <t>00715L.TW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>野村臺灣新科技50</t>
+          <t>期街口布蘭特正2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.697652534271771</v>
+        <v>4.754094182837063</v>
       </c>
       <c r="D10" t="n">
-        <v>1.290191493246491</v>
+        <v>2.879146757882967</v>
       </c>
       <c r="E10" t="n">
-        <v>62.34999847412109</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>78.01000000000001</v>
+        <v>82.23</v>
       </c>
       <c r="G10" t="n">
-        <v>135</v>
+        <v>425</v>
       </c>
       <c r="H10" t="n">
-        <v>82.95999999999999</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>3.13</v>
+        <v>3.32</v>
       </c>
       <c r="J10" t="n">
-        <v>12.34074074074074</v>
+        <v>17.11294117647059</v>
       </c>
       <c r="K10" t="n">
-        <v>10839670.95</v>
+        <v>4590983.75</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>14.6</v>
+        <v>32.14</v>
       </c>
       <c r="O10" t="n">
-        <v>-8.99</v>
+        <v>-44.86</v>
       </c>
       <c r="P10" t="n">
-        <v>5.609999999999999</v>
+        <v>-12.72</v>
       </c>
       <c r="Q10" t="n">
-        <v>43.68</v>
+        <v>14.59</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4074610410252792</v>
+        <v>1.874947424954096</v>
       </c>
       <c r="S10" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>422.85</v>
+        <v>1409.31</v>
       </c>
       <c r="U10" t="n">
-        <v>1666</v>
+        <v>7273</v>
       </c>
       <c r="V10" t="n">
-        <v>1.033739506198872</v>
+        <v>1.062579060942035</v>
       </c>
       <c r="W10" t="n">
-        <v>1.112178047661594</v>
+        <v>1.190504974996655</v>
       </c>
       <c r="X10" t="n">
-        <v>60.31500015258789</v>
+        <v>67.19499999999995</v>
       </c>
       <c r="Y10" t="n">
-        <v>56.06116629006915</v>
+        <v>59.9745498755271</v>
       </c>
       <c r="Z10" t="n">
-        <v>448572886.5721664</v>
+        <v>167644986.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>00894.TW</t>
+          <t>00675L.TW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>中信小資高價30</t>
+          <t>富邦臺灣加權正2</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.325211195871371</v>
+        <v>12.49937302709555</v>
       </c>
       <c r="D11" t="n">
-        <v>1.956293313120947</v>
+        <v>3.141635210852278</v>
       </c>
       <c r="E11" t="n">
-        <v>51.95000076293945</v>
+        <v>357.75</v>
       </c>
       <c r="F11" t="n">
-        <v>81.58</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>241</v>
+        <v>564</v>
       </c>
       <c r="H11" t="n">
-        <v>83.40000000000001</v>
+        <v>87.06</v>
       </c>
       <c r="I11" t="n">
-        <v>2.9</v>
+        <v>3.18</v>
       </c>
       <c r="J11" t="n">
-        <v>15.32365145228216</v>
+        <v>12.38297872340426</v>
       </c>
       <c r="K11" t="n">
-        <v>1064689.65</v>
+        <v>963287.4</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
@@ -1339,778 +1339,860 @@
         <v>15.7</v>
       </c>
       <c r="O11" t="n">
-        <v>-8.380000000000001</v>
+        <v>-24.73</v>
       </c>
       <c r="P11" t="n">
-        <v>7.319999999999999</v>
+        <v>-9.030000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>22.81</v>
+        <v>16.61</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3689178827504245</v>
+        <v>9.357737816243276</v>
       </c>
       <c r="S11" t="n">
-        <v>7.549999999999999</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>699.33</v>
+        <v>1792.47</v>
       </c>
       <c r="U11" t="n">
-        <v>3693</v>
+        <v>6984</v>
       </c>
       <c r="V11" t="n">
-        <v>1.054148118575511</v>
+        <v>1.064019629712246</v>
       </c>
       <c r="W11" t="n">
-        <v>1.150142784548979</v>
+        <v>1.195049399548598</v>
       </c>
       <c r="X11" t="n">
-        <v>49.28150024414062</v>
+        <v>336.2250000000002</v>
       </c>
       <c r="Y11" t="n">
-        <v>45.16830558851987</v>
+        <v>299.3600098331766</v>
       </c>
       <c r="Z11" t="n">
-        <v>28373220.21669006</v>
+        <v>299846373.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>00901.TW</t>
+          <t>00935.TW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>永豐智能車供應鏈</t>
+          <t>野村臺灣新科技50</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.022589711693981</v>
+        <v>1.6745263647463</v>
       </c>
       <c r="D12" t="n">
-        <v>1.916653122104031</v>
+        <v>1.263845043977293</v>
       </c>
       <c r="E12" t="n">
-        <v>49.47000122070312</v>
+        <v>62.35</v>
       </c>
       <c r="F12" t="n">
-        <v>79.39</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>267</v>
+        <v>136</v>
       </c>
       <c r="H12" t="n">
-        <v>90.26000000000001</v>
+        <v>83.09</v>
       </c>
       <c r="I12" t="n">
-        <v>2.78</v>
+        <v>3.15</v>
       </c>
       <c r="J12" t="n">
-        <v>13.2059925093633</v>
+        <v>12.30882352941176</v>
       </c>
       <c r="K12" t="n">
-        <v>249412.6</v>
+        <v>11157707.45</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>15.18</v>
+        <v>14.6</v>
       </c>
       <c r="O12" t="n">
-        <v>-7.07</v>
+        <v>-8.99</v>
       </c>
       <c r="P12" t="n">
-        <v>8.109999999999999</v>
+        <v>5.609999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>24.69</v>
+        <v>43.74</v>
       </c>
       <c r="R12" t="n">
-        <v>0.10593658958995</v>
+        <v>0.4106813207690077</v>
       </c>
       <c r="S12" t="n">
-        <v>4.671</v>
+        <v>4.98</v>
       </c>
       <c r="T12" t="n">
-        <v>743.11</v>
+        <v>428.12</v>
       </c>
       <c r="U12" t="n">
-        <v>3526</v>
+        <v>1674</v>
       </c>
       <c r="V12" t="n">
-        <v>1.03688955744303</v>
+        <v>1.033739534112575</v>
       </c>
       <c r="W12" t="n">
-        <v>1.111134743563848</v>
+        <v>1.112178072007453</v>
       </c>
       <c r="X12" t="n">
-        <v>47.7100004196167</v>
+        <v>60.31500000000001</v>
       </c>
       <c r="Y12" t="n">
-        <v>44.5220541498264</v>
+        <v>56.06116643484963</v>
       </c>
       <c r="Z12" t="n">
-        <v>5838944.24407959</v>
+        <v>470988470.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>00881.TW</t>
+          <t>00894.TW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>國泰台灣科技龍頭</t>
+          <t>中信小資高價30</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.178995188077034</v>
+        <v>2.32214527630802</v>
       </c>
       <c r="D13" t="n">
-        <v>2.035763066958677</v>
+        <v>1.919848354377049</v>
       </c>
       <c r="E13" t="n">
-        <v>53.29999923706055</v>
+        <v>51.95</v>
       </c>
       <c r="F13" t="n">
-        <v>72.95</v>
+        <v>81.58</v>
       </c>
       <c r="G13" t="n">
-        <v>321</v>
+        <v>243</v>
       </c>
       <c r="H13" t="n">
-        <v>90.65000000000001</v>
+        <v>82.72</v>
       </c>
       <c r="I13" t="n">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="J13" t="n">
-        <v>13.86915887850467</v>
+        <v>15.32921810699589</v>
       </c>
       <c r="K13" t="n">
-        <v>15267449.95</v>
+        <v>1107714.35</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>2</v>
       </c>
       <c r="N13" t="n">
-        <v>10.9</v>
+        <v>15.7</v>
       </c>
       <c r="O13" t="n">
-        <v>-7.15</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>3.75</v>
+        <v>7.319999999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>19.92</v>
+        <v>22.58</v>
       </c>
       <c r="R13" t="n">
-        <v>0.1432321211183574</v>
+        <v>0.4022969219309704</v>
       </c>
       <c r="S13" t="n">
-        <v>12.5</v>
+        <v>7.549999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>817.08</v>
+        <v>698.73</v>
       </c>
       <c r="U13" t="n">
-        <v>4452</v>
+        <v>3725</v>
       </c>
       <c r="V13" t="n">
-        <v>1.029583609640394</v>
+        <v>1.054148108316509</v>
       </c>
       <c r="W13" t="n">
-        <v>1.097280612540143</v>
+        <v>1.150142776118656</v>
       </c>
       <c r="X13" t="n">
-        <v>51.7685001373291</v>
+        <v>49.28149999999999</v>
       </c>
       <c r="Y13" t="n">
-        <v>48.57462952313907</v>
+        <v>45.16830525625152</v>
       </c>
       <c r="Z13" t="n">
-        <v>553476519.5775032</v>
+        <v>30291837.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>0057.TW</t>
+          <t>00901.TW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>富邦摩台</t>
+          <t>永豐智能車供應鏈</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6.26886667977521</v>
+        <v>2.018950855999971</v>
       </c>
       <c r="D14" t="n">
-        <v>3.291264706229798</v>
+        <v>1.883748645216536</v>
       </c>
       <c r="E14" t="n">
-        <v>341.7999877929688</v>
+        <v>49.47</v>
       </c>
       <c r="F14" t="n">
-        <v>85.81</v>
+        <v>79.39</v>
       </c>
       <c r="G14" t="n">
-        <v>1248</v>
+        <v>276</v>
       </c>
       <c r="H14" t="n">
-        <v>93.51000000000001</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>2.5</v>
+        <v>2.79</v>
       </c>
       <c r="J14" t="n">
-        <v>13.08653846153846</v>
+        <v>13.22463768115942</v>
       </c>
       <c r="K14" t="n">
-        <v>19825.05</v>
+        <v>255266.35</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>14.45</v>
+        <v>15.18</v>
       </c>
       <c r="O14" t="n">
-        <v>-6.48</v>
+        <v>-7.3</v>
       </c>
       <c r="P14" t="n">
-        <v>7.969999999999999</v>
+        <v>7.88</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.07</v>
+        <v>24.17</v>
       </c>
       <c r="R14" t="n">
-        <v>2.977601973545412</v>
+        <v>0.1352022107834343</v>
       </c>
       <c r="S14" t="n">
-        <v>1.685</v>
+        <v>4.671</v>
       </c>
       <c r="T14" t="n">
-        <v>3124.7</v>
+        <v>771.28</v>
       </c>
       <c r="U14" t="n">
-        <v>16332</v>
+        <v>3650</v>
       </c>
       <c r="V14" t="n">
-        <v>1.031817868632485</v>
+        <v>1.036889540976734</v>
       </c>
       <c r="W14" t="n">
-        <v>1.088122570458615</v>
+        <v>1.111134721063639</v>
       </c>
       <c r="X14" t="n">
-        <v>331.2600006103515</v>
+        <v>47.71</v>
       </c>
       <c r="Y14" t="n">
-        <v>314.1190129425485</v>
+        <v>44.52205395277775</v>
       </c>
       <c r="Z14" t="n">
-        <v>1372326.95098877</v>
+        <v>6025940.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0050.TW</t>
+          <t>0057.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>元大台灣50</t>
+          <t>富邦摩台</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3.295162774231783</v>
+        <v>6.589893126013595</v>
       </c>
       <c r="D15" t="n">
-        <v>3.295162774231783</v>
+        <v>5.258947965356257</v>
       </c>
       <c r="E15" t="n">
-        <v>114.9499969482422</v>
+        <v>341.8</v>
       </c>
       <c r="F15" t="n">
-        <v>83.23</v>
+        <v>85.81</v>
       </c>
       <c r="G15" t="n">
-        <v>1227</v>
+        <v>1245</v>
       </c>
       <c r="H15" t="n">
-        <v>90.87</v>
+        <v>93.33</v>
       </c>
       <c r="I15" t="n">
-        <v>2.19</v>
+        <v>2.64</v>
       </c>
       <c r="J15" t="n">
-        <v>13.92094539527302</v>
+        <v>12.02409638554217</v>
       </c>
       <c r="K15" t="n">
-        <v>70448179.3</v>
+        <v>26018.9</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>15.64</v>
+        <v>14.45</v>
       </c>
       <c r="O15" t="n">
-        <v>-8.890000000000001</v>
+        <v>-6.48</v>
       </c>
       <c r="P15" t="n">
-        <v>6.75</v>
+        <v>7.969999999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>7.37</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.330945160657338</v>
       </c>
       <c r="S15" t="n">
-        <v>13.505</v>
+        <v>1.685</v>
       </c>
       <c r="T15" t="n">
-        <v>2689.93</v>
+        <v>3287.55</v>
       </c>
       <c r="U15" t="n">
-        <v>17081</v>
+        <v>14970</v>
       </c>
       <c r="V15" t="n">
-        <v>1.033258395991779</v>
+        <v>1.031817907383928</v>
       </c>
       <c r="W15" t="n">
-        <v>1.093853358081359</v>
+        <v>1.088122625759537</v>
       </c>
       <c r="X15" t="n">
-        <v>111.2500003814697</v>
+        <v>331.26</v>
       </c>
       <c r="Y15" t="n">
-        <v>105.0872094499639</v>
+        <v>314.1190081967233</v>
       </c>
       <c r="Z15" t="n">
-        <v>10080260653.88351</v>
+        <v>2632543.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>0053.TW</t>
+          <t>00881.TW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>元大電子</t>
+          <t>國泰台灣科技龍頭</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6.874554762804874</v>
+        <v>2.173836683611807</v>
       </c>
       <c r="D16" t="n">
-        <v>3.295162774231783</v>
+        <v>1.989633791076708</v>
       </c>
       <c r="E16" t="n">
-        <v>259.9500122070312</v>
+        <v>53.3</v>
       </c>
       <c r="F16" t="n">
-        <v>74.58</v>
+        <v>72.95</v>
       </c>
       <c r="G16" t="n">
-        <v>1144</v>
+        <v>384</v>
       </c>
       <c r="H16" t="n">
-        <v>90.3</v>
+        <v>89.58</v>
       </c>
       <c r="I16" t="n">
-        <v>2.15</v>
+        <v>2.52</v>
       </c>
       <c r="J16" t="n">
-        <v>14.06905594405594</v>
+        <v>15.328125</v>
       </c>
       <c r="K16" t="n">
-        <v>146747.7</v>
+        <v>15815645.2</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>10.88</v>
+        <v>10.9</v>
       </c>
       <c r="O16" t="n">
-        <v>-8.44</v>
+        <v>-4.28</v>
       </c>
       <c r="P16" t="n">
-        <v>2.440000000000001</v>
+        <v>6.62</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.63</v>
+        <v>15.81</v>
       </c>
       <c r="R16" t="n">
-        <v>3.579391988573091</v>
+        <v>0.1842028925350987</v>
       </c>
       <c r="S16" t="n">
-        <v>18.91</v>
+        <v>12.5</v>
       </c>
       <c r="T16" t="n">
-        <v>2463.07</v>
+        <v>966.91</v>
       </c>
       <c r="U16" t="n">
-        <v>16095</v>
+        <v>5886</v>
       </c>
       <c r="V16" t="n">
-        <v>1.038056109495539</v>
+        <v>1.029583627109149</v>
       </c>
       <c r="W16" t="n">
-        <v>1.107677221521853</v>
+        <v>1.097280636652826</v>
       </c>
       <c r="X16" t="n">
-        <v>250.4200012207031</v>
+        <v>51.7685</v>
       </c>
       <c r="Y16" t="n">
-        <v>234.6802905722683</v>
+        <v>48.57462915101439</v>
       </c>
       <c r="Z16" t="n">
-        <v>47857837.04736328</v>
+        <v>589833630.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>00735.TW</t>
+          <t>0052.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>國泰臺韓科技</t>
+          <t>富邦科技</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3.349094851152814</v>
+        <v>8.856266526813652</v>
       </c>
       <c r="D17" t="n">
-        <v>2.846137947762975</v>
+        <v>5.359209199435752</v>
       </c>
       <c r="E17" t="n">
-        <v>110.1500015258789</v>
+        <v>67</v>
       </c>
       <c r="F17" t="n">
-        <v>69.95999999999999</v>
+        <v>81.59</v>
       </c>
       <c r="G17" t="n">
-        <v>479</v>
+        <v>1111</v>
       </c>
       <c r="H17" t="n">
-        <v>84.97</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>2.11</v>
+        <v>2.45</v>
       </c>
       <c r="J17" t="n">
-        <v>14.01461377870564</v>
+        <v>14.18091809180918</v>
       </c>
       <c r="K17" t="n">
-        <v>1264153.15</v>
+        <v>15259096.65</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>21.39</v>
+        <v>12.7</v>
       </c>
       <c r="O17" t="n">
-        <v>-8.82</v>
+        <v>-14.18</v>
       </c>
       <c r="P17" t="n">
-        <v>12.57</v>
+        <v>-1.48</v>
       </c>
       <c r="Q17" t="n">
-        <v>14</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5029569033898387</v>
+        <v>3.4970573273779</v>
       </c>
       <c r="S17" t="n">
-        <v>13.37</v>
+        <v>2.232857285714286</v>
       </c>
       <c r="T17" t="n">
-        <v>1012.55</v>
+        <v>2723.42</v>
       </c>
       <c r="U17" t="n">
-        <v>6713</v>
+        <v>15755</v>
       </c>
       <c r="V17" t="n">
-        <v>1.026393659973318</v>
+        <v>1.035068747103352</v>
       </c>
       <c r="W17" t="n">
-        <v>1.094572789664137</v>
+        <v>1.100825326252461</v>
       </c>
       <c r="X17" t="n">
-        <v>107.3174999237061</v>
+        <v>64.73000000000006</v>
       </c>
       <c r="Y17" t="n">
-        <v>100.6328702540447</v>
+        <v>60.8634252884498</v>
       </c>
       <c r="Z17" t="n">
-        <v>263743053.5035629</v>
+        <v>1279911318</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>006203.TW</t>
+          <t>00735.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>元大MSCI台灣</t>
+          <t>國泰臺韓科技</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4.548479841506535</v>
+        <v>3.344656297172801</v>
       </c>
       <c r="D18" t="n">
-        <v>3.549502109510268</v>
+        <v>2.750893495929951</v>
       </c>
       <c r="E18" t="n">
-        <v>208.6499938964844</v>
+        <v>110.15</v>
       </c>
       <c r="F18" t="n">
-        <v>84.39</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>1040</v>
+        <v>498</v>
       </c>
       <c r="H18" t="n">
-        <v>90.77</v>
+        <v>86.55</v>
       </c>
       <c r="I18" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="J18" t="n">
-        <v>12.96538461538461</v>
+        <v>13.81124497991968</v>
       </c>
       <c r="K18" t="n">
-        <v>8719.25</v>
+        <v>1325503.7</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>8.85</v>
+        <v>21.39</v>
       </c>
       <c r="O18" t="n">
-        <v>-7.69</v>
+        <v>-6.04</v>
       </c>
       <c r="P18" t="n">
-        <v>1.159999999999999</v>
+        <v>15.35</v>
       </c>
       <c r="Q18" t="n">
-        <v>8.81</v>
+        <v>14.26</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9989777319962672</v>
+        <v>0.5937628012428493</v>
       </c>
       <c r="S18" t="n">
-        <v>21.88</v>
+        <v>13.37</v>
       </c>
       <c r="T18" t="n">
-        <v>2166.47</v>
+        <v>1133.84</v>
       </c>
       <c r="U18" t="n">
-        <v>13484</v>
+        <v>6878</v>
       </c>
       <c r="V18" t="n">
-        <v>1.033854812298125</v>
+        <v>1.026393645025276</v>
       </c>
       <c r="W18" t="n">
-        <v>1.090140125626574</v>
+        <v>1.094572774631067</v>
       </c>
       <c r="X18" t="n">
-        <v>201.8175003051758</v>
+        <v>107.3174999999999</v>
       </c>
       <c r="Y18" t="n">
-        <v>191.3974075365401</v>
+        <v>100.632870242115</v>
       </c>
       <c r="Z18" t="n">
-        <v>625949.9816894531</v>
+        <v>272324395.75</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>006208.TW</t>
+          <t>0050.TW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>富邦台50</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4.529583933593418</v>
+        <v>5.917339071993916</v>
       </c>
       <c r="D19" t="n">
-        <v>3.730117409631104</v>
+        <v>5.917339071993916</v>
       </c>
       <c r="E19" t="n">
-        <v>263.3999938964844</v>
+        <v>114.95</v>
       </c>
       <c r="F19" t="n">
-        <v>84.44</v>
+        <v>83.23</v>
       </c>
       <c r="G19" t="n">
-        <v>1010</v>
+        <v>1695</v>
       </c>
       <c r="H19" t="n">
-        <v>89.20999999999999</v>
+        <v>90.97</v>
       </c>
       <c r="I19" t="n">
-        <v>1.89</v>
+        <v>2.26</v>
       </c>
       <c r="J19" t="n">
-        <v>13.88613861386139</v>
+        <v>13.46961651917404</v>
       </c>
       <c r="K19" t="n">
-        <v>1868394.9</v>
+        <v>76094921</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>11.21</v>
+        <v>13.94</v>
       </c>
       <c r="O19" t="n">
-        <v>-6.25</v>
+        <v>-5.91</v>
       </c>
       <c r="P19" t="n">
-        <v>4.960000000000001</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>8.119999999999999</v>
+        <v>6.04</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7994665239623142</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>28.764</v>
+        <v>4.84625</v>
       </c>
       <c r="T19" t="n">
-        <v>1907.67</v>
+        <v>3824.71</v>
       </c>
       <c r="U19" t="n">
-        <v>14025</v>
+        <v>22831</v>
       </c>
       <c r="V19" t="n">
-        <v>1.035001012445999</v>
+        <v>1.033258426966292</v>
       </c>
       <c r="W19" t="n">
-        <v>1.095435058452675</v>
+        <v>1.09385339779308</v>
       </c>
       <c r="X19" t="n">
-        <v>254.4924987792969</v>
+        <v>111.25</v>
       </c>
       <c r="Y19" t="n">
-        <v>240.4524046076655</v>
+        <v>105.0872084247478</v>
       </c>
       <c r="Z19" t="n">
-        <v>359410081.8717346</v>
+        <v>11480961846.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>0051.TW</t>
+          <t>0053.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>元大中型100</t>
+          <t>元大電子</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3.816569466791282</v>
+        <v>7.260905382222246</v>
       </c>
       <c r="D20" t="n">
-        <v>3.295162774231783</v>
+        <v>5.318830335500019</v>
       </c>
       <c r="E20" t="n">
-        <v>152.9499969482422</v>
+        <v>259.95</v>
       </c>
       <c r="F20" t="n">
-        <v>92.45999999999999</v>
+        <v>74.58</v>
       </c>
       <c r="G20" t="n">
-        <v>1119</v>
+        <v>1190</v>
       </c>
       <c r="H20" t="n">
-        <v>88.83</v>
+        <v>89.16</v>
       </c>
       <c r="I20" t="n">
-        <v>1.71</v>
+        <v>2.18</v>
       </c>
       <c r="J20" t="n">
-        <v>15.43074173369079</v>
+        <v>13.83697478991597</v>
       </c>
       <c r="K20" t="n">
-        <v>42969.75</v>
+        <v>166729.85</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
         <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>10</v>
+        <v>11.49</v>
       </c>
       <c r="O20" t="n">
-        <v>-10.68</v>
+        <v>-7.24</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6799999999999997</v>
+        <v>4.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.55</v>
+        <v>7.58</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5214066925594985</v>
+        <v>1.942075046722227</v>
       </c>
       <c r="S20" t="n">
-        <v>19.36</v>
+        <v>18.91</v>
       </c>
       <c r="T20" t="n">
-        <v>1913.8</v>
+        <v>2598</v>
       </c>
       <c r="U20" t="n">
-        <v>17267</v>
+        <v>16466</v>
       </c>
       <c r="V20" t="n">
-        <v>1.037212830029616</v>
+        <v>1.03805606580944</v>
       </c>
       <c r="W20" t="n">
-        <v>1.087439576992383</v>
+        <v>1.10767716157917</v>
       </c>
       <c r="X20" t="n">
-        <v>147.4625</v>
+        <v>250.4200000000001</v>
       </c>
       <c r="Y20" t="n">
-        <v>140.6514901464851</v>
+        <v>234.6802922517603</v>
       </c>
       <c r="Z20" t="n">
-        <v>2036376.259368896</v>
+        <v>51273577.8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>006208.TW</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>富邦台50</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>4.407296928049225</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4.147887349924367</v>
+      </c>
+      <c r="E21" t="n">
+        <v>263.4</v>
+      </c>
+      <c r="F21" t="n">
+        <v>84.44</v>
+      </c>
+      <c r="G21" t="n">
+        <v>895</v>
+      </c>
+      <c r="H21" t="n">
+        <v>88.48999999999999</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="J21" t="n">
+        <v>13.86703910614525</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2222986.85</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>2</v>
+      </c>
+      <c r="N21" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-6.25</v>
+      </c>
+      <c r="P21" t="n">
+        <v>4.960000000000001</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.259409578124858</v>
+      </c>
+      <c r="S21" t="n">
+        <v>28.764</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1745.92</v>
+      </c>
+      <c r="U21" t="n">
+        <v>12411</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.035001031464581</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.095435083247884</v>
+      </c>
+      <c r="X21" t="n">
+        <v>254.4925</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>240.4524047367904</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>478559870.4</v>
       </c>
     </row>
   </sheetData>

--- a/ETF動態清單.xlsx
+++ b/ETF動態清單.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z21"/>
+  <dimension ref="A1:Z22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,16 +567,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.889043205104652</v>
+        <v>0.8897191648212786</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6423310454307738</v>
+        <v>0.6382817168657253</v>
       </c>
       <c r="E2" t="n">
-        <v>32.24</v>
+        <v>32.3</v>
       </c>
       <c r="F2" t="n">
-        <v>84.13</v>
+        <v>82.52</v>
       </c>
       <c r="G2" t="n">
         <v>41</v>
@@ -591,7 +591,7 @@
         <v>8.439024390243903</v>
       </c>
       <c r="K2" t="n">
-        <v>151778290.3</v>
+        <v>150784442.6</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
@@ -610,7 +610,7 @@
         <v>386.28</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2467121596738782</v>
+        <v>0.2514374479555532</v>
       </c>
       <c r="S2" t="n">
         <v>1.67</v>
@@ -622,19 +622,19 @@
         <v>346</v>
       </c>
       <c r="V2" t="n">
-        <v>1.061888607094628</v>
+        <v>1.059711286089238</v>
       </c>
       <c r="W2" t="n">
-        <v>1.163828118798113</v>
+        <v>1.166064679098722</v>
       </c>
       <c r="X2" t="n">
-        <v>30.36100000000001</v>
+        <v>30.48000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>27.70168505061925</v>
+        <v>27.70000719425392</v>
       </c>
       <c r="Z2" t="n">
-        <v>3195529436.32</v>
+        <v>3435311009.4</v>
       </c>
     </row>
     <row r="3">
@@ -649,16 +649,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.382106335092956</v>
+        <v>1.348550165286301</v>
       </c>
       <c r="D3" t="n">
-        <v>1.005945493752752</v>
+        <v>1.001579600051825</v>
       </c>
       <c r="E3" t="n">
-        <v>40.66</v>
+        <v>40.12</v>
       </c>
       <c r="F3" t="n">
-        <v>68.23</v>
+        <v>53.53</v>
       </c>
       <c r="G3" t="n">
         <v>66</v>
@@ -673,7 +673,7 @@
         <v>10.33333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>7705117.65</v>
+        <v>8337668.95</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
@@ -692,7 +692,7 @@
         <v>159.78</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3761608413402042</v>
+        <v>0.3469705652344754</v>
       </c>
       <c r="S3" t="n">
         <v>0.78</v>
@@ -704,19 +704,19 @@
         <v>682</v>
       </c>
       <c r="V3" t="n">
-        <v>1.034658252328362</v>
+        <v>1.018597270707711</v>
       </c>
       <c r="W3" t="n">
-        <v>1.132499045991609</v>
+        <v>1.114294662652908</v>
       </c>
       <c r="X3" t="n">
-        <v>39.29800000000002</v>
+        <v>39.38750000000002</v>
       </c>
       <c r="Y3" t="n">
-        <v>35.90290000147273</v>
+        <v>36.00483906517371</v>
       </c>
       <c r="Z3" t="n">
-        <v>279501678.54</v>
+        <v>665333189.4799999</v>
       </c>
     </row>
     <row r="4">
@@ -731,16 +731,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.765708222274599</v>
+        <v>2.692002548245465</v>
       </c>
       <c r="D4" t="n">
-        <v>2.48696380890904</v>
+        <v>2.48114450172063</v>
       </c>
       <c r="E4" t="n">
-        <v>91.90000000000001</v>
+        <v>89.84999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>86.56999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>495</v>
@@ -755,7 +755,7 @@
         <v>12.29090909090909</v>
       </c>
       <c r="K4" t="n">
-        <v>7362016.7</v>
+        <v>7719537.85</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
@@ -774,7 +774,7 @@
         <v>19.85</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2787444133655597</v>
+        <v>0.2108580465248355</v>
       </c>
       <c r="S4" t="n">
         <v>17.71</v>
@@ -786,19 +786,19 @@
         <v>6084</v>
       </c>
       <c r="V4" t="n">
-        <v>1.065414601628844</v>
+        <v>1.037588775333449</v>
       </c>
       <c r="W4" t="n">
-        <v>1.195809758274451</v>
+        <v>1.164128593721029</v>
       </c>
       <c r="X4" t="n">
-        <v>86.25749999999999</v>
+        <v>86.595</v>
       </c>
       <c r="Y4" t="n">
-        <v>76.85168929597241</v>
+        <v>77.18219489206325</v>
       </c>
       <c r="Z4" t="n">
-        <v>535654864.9</v>
+        <v>1093625448</v>
       </c>
     </row>
     <row r="5">
@@ -813,16 +813,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13.13108146543407</v>
+        <v>13.16165753242944</v>
       </c>
       <c r="D5" t="n">
-        <v>3.209099559207814</v>
+        <v>3.202457986221948</v>
       </c>
       <c r="E5" t="n">
-        <v>118.1</v>
+        <v>118.4</v>
       </c>
       <c r="F5" t="n">
-        <v>86.66</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>564</v>
@@ -837,7 +837,7 @@
         <v>11.9113475177305</v>
       </c>
       <c r="K5" t="n">
-        <v>4849020.85</v>
+        <v>4856870.1</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
@@ -856,7 +856,7 @@
         <v>18.35</v>
       </c>
       <c r="R5" t="n">
-        <v>9.921981906226257</v>
+        <v>9.95919954620749</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -868,19 +868,19 @@
         <v>6718</v>
       </c>
       <c r="V5" t="n">
-        <v>1.064395475643278</v>
+        <v>1.062288316174326</v>
       </c>
       <c r="W5" t="n">
-        <v>1.195043235807811</v>
+        <v>1.196283694188915</v>
       </c>
       <c r="X5" t="n">
-        <v>110.9550000000001</v>
+        <v>111.4575000000001</v>
       </c>
       <c r="Y5" t="n">
-        <v>98.82487634028415</v>
+        <v>98.97317883303228</v>
       </c>
       <c r="Z5" t="n">
-        <v>485080278.9</v>
+        <v>503276723.2</v>
       </c>
     </row>
     <row r="6">
@@ -895,16 +895,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.54099128073863</v>
+        <v>17.53041930581944</v>
       </c>
       <c r="D6" t="n">
-        <v>3.655453318302473</v>
+        <v>3.648292890301905</v>
       </c>
       <c r="E6" t="n">
-        <v>40.9</v>
+        <v>40.89</v>
       </c>
       <c r="F6" t="n">
-        <v>86.86</v>
+        <v>81.98</v>
       </c>
       <c r="G6" t="n">
         <v>644</v>
@@ -919,7 +919,7 @@
         <v>12.68167701863354</v>
       </c>
       <c r="K6" t="n">
-        <v>152407612.3</v>
+        <v>152429063.4</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
@@ -938,7 +938,7 @@
         <v>15.49</v>
       </c>
       <c r="R6" t="n">
-        <v>13.88553796243616</v>
+        <v>13.88212641551753</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -950,19 +950,19 @@
         <v>8167</v>
       </c>
       <c r="V6" t="n">
-        <v>1.064882316184129</v>
+        <v>1.059999222304313</v>
       </c>
       <c r="W6" t="n">
-        <v>1.192135773993529</v>
+        <v>1.190076546804459</v>
       </c>
       <c r="X6" t="n">
-        <v>38.40799999999999</v>
+        <v>38.57549999999999</v>
       </c>
       <c r="Y6" t="n">
-        <v>34.30817268656348</v>
+        <v>34.35913438492342</v>
       </c>
       <c r="Z6" t="n">
-        <v>6070032844.9</v>
+        <v>5334644582.34</v>
       </c>
     </row>
     <row r="7">
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.993160407439695</v>
+        <v>1.980182984636244</v>
       </c>
       <c r="D7" t="n">
-        <v>1.866808375641466</v>
+        <v>1.861465583347427</v>
       </c>
       <c r="E7" t="n">
-        <v>44.27</v>
+        <v>44.09</v>
       </c>
       <c r="F7" t="n">
-        <v>76.23</v>
+        <v>68.95</v>
       </c>
       <c r="G7" t="n">
         <v>239</v>
@@ -1001,7 +1001,7 @@
         <v>10.78242677824268</v>
       </c>
       <c r="K7" t="n">
-        <v>1727945.1</v>
+        <v>2012213.45</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
@@ -1020,7 +1020,7 @@
         <v>37.53</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1263520317982292</v>
+        <v>0.118717401288817</v>
       </c>
       <c r="S7" t="n">
         <v>4.850000000000001</v>
@@ -1032,19 +1032,19 @@
         <v>2577</v>
       </c>
       <c r="V7" t="n">
-        <v>1.034817264875352</v>
+        <v>1.027918633793787</v>
       </c>
       <c r="W7" t="n">
-        <v>1.110272742392005</v>
+        <v>1.103226716380128</v>
       </c>
       <c r="X7" t="n">
-        <v>42.7805</v>
+        <v>42.8925</v>
       </c>
       <c r="Y7" t="n">
-        <v>39.87308551286542</v>
+        <v>39.96458692068907</v>
       </c>
       <c r="Z7" t="n">
-        <v>207567199.55</v>
+        <v>274841187.6</v>
       </c>
     </row>
     <row r="8">
@@ -1059,16 +1059,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.90889450815724</v>
+        <v>1.887172476537584</v>
       </c>
       <c r="D8" t="n">
-        <v>1.769144891987639</v>
+        <v>1.763843847996092</v>
       </c>
       <c r="E8" t="n">
-        <v>53.45</v>
+        <v>53.05</v>
       </c>
       <c r="F8" t="n">
-        <v>67.87</v>
+        <v>59.28</v>
       </c>
       <c r="G8" t="n">
         <v>262</v>
@@ -1083,7 +1083,7 @@
         <v>12.79770992366412</v>
       </c>
       <c r="K8" t="n">
-        <v>1545722.5</v>
+        <v>1582116.8</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
@@ -1102,7 +1102,7 @@
         <v>28.72</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1397496161696008</v>
+        <v>0.1233286285414916</v>
       </c>
       <c r="S8" t="n">
         <v>6.699999999999999</v>
@@ -1114,19 +1114,19 @@
         <v>3353</v>
       </c>
       <c r="V8" t="n">
-        <v>1.037934616915713</v>
+        <v>1.027035922057557</v>
       </c>
       <c r="W8" t="n">
-        <v>1.135654129427339</v>
+        <v>1.123087169026796</v>
       </c>
       <c r="X8" t="n">
-        <v>51.49649999999997</v>
+        <v>51.65349999999997</v>
       </c>
       <c r="Y8" t="n">
-        <v>47.06538603170712</v>
+        <v>47.23587043200765</v>
       </c>
       <c r="Z8" t="n">
-        <v>105798609.3</v>
+        <v>75566807.25</v>
       </c>
     </row>
     <row r="9">
@@ -1141,16 +1141,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11.90524461500531</v>
+        <v>11.91908424772292</v>
       </c>
       <c r="D9" t="n">
-        <v>3.028709694449856</v>
+        <v>3.022259519041445</v>
       </c>
       <c r="E9" t="n">
-        <v>13.53</v>
+        <v>13.55</v>
       </c>
       <c r="F9" t="n">
-        <v>86.79000000000001</v>
+        <v>82.48</v>
       </c>
       <c r="G9" t="n">
         <v>514</v>
@@ -1165,7 +1165,7 @@
         <v>12.18093385214008</v>
       </c>
       <c r="K9" t="n">
-        <v>196257788.75</v>
+        <v>197393535.2</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
@@ -1184,7 +1184,7 @@
         <v>18.65</v>
       </c>
       <c r="R9" t="n">
-        <v>8.876534920555454</v>
+        <v>8.896824728681478</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1196,19 +1196,19 @@
         <v>6261</v>
       </c>
       <c r="V9" t="n">
-        <v>1.065941857716852</v>
+        <v>1.062661752019449</v>
       </c>
       <c r="W9" t="n">
-        <v>1.198571856529974</v>
+        <v>1.198473218565535</v>
       </c>
       <c r="X9" t="n">
-        <v>12.693</v>
+        <v>12.751</v>
       </c>
       <c r="Y9" t="n">
-        <v>11.28843458678494</v>
+        <v>11.30605155801323</v>
       </c>
       <c r="Z9" t="n">
-        <v>3226934008.32</v>
+        <v>2407156375.35</v>
       </c>
     </row>
     <row r="10">
@@ -1223,16 +1223,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4.754094182837063</v>
+        <v>4.840492347539276</v>
       </c>
       <c r="D10" t="n">
-        <v>2.879146757882967</v>
+        <v>2.87287519833661</v>
       </c>
       <c r="E10" t="n">
-        <v>71.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="F10" t="n">
-        <v>82.23</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>425</v>
@@ -1247,7 +1247,7 @@
         <v>17.11294117647059</v>
       </c>
       <c r="K10" t="n">
-        <v>4590983.75</v>
+        <v>4522921.15</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
@@ -1266,7 +1266,7 @@
         <v>14.59</v>
       </c>
       <c r="R10" t="n">
-        <v>1.874947424954096</v>
+        <v>1.967617149202666</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1278,19 +1278,19 @@
         <v>7273</v>
       </c>
       <c r="V10" t="n">
-        <v>1.062579060942035</v>
+        <v>1.069558161835215</v>
       </c>
       <c r="W10" t="n">
-        <v>1.190504974996655</v>
+        <v>1.191228203137704</v>
       </c>
       <c r="X10" t="n">
-        <v>67.19499999999995</v>
+        <v>67.78499999999994</v>
       </c>
       <c r="Y10" t="n">
-        <v>59.9745498755271</v>
+        <v>60.86155432605983</v>
       </c>
       <c r="Z10" t="n">
-        <v>167644986.6</v>
+        <v>218961672.5</v>
       </c>
     </row>
     <row r="11">
@@ -1305,16 +1305,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>12.49937302709555</v>
+        <v>12.53007670913105</v>
       </c>
       <c r="D11" t="n">
-        <v>3.141635210852278</v>
+        <v>3.13508524984154</v>
       </c>
       <c r="E11" t="n">
-        <v>357.75</v>
+        <v>358.7</v>
       </c>
       <c r="F11" t="n">
-        <v>86.70999999999999</v>
+        <v>82.67</v>
       </c>
       <c r="G11" t="n">
         <v>564</v>
@@ -1329,7 +1329,7 @@
         <v>12.38297872340426</v>
       </c>
       <c r="K11" t="n">
-        <v>963287.4</v>
+        <v>975459.55</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
@@ -1348,7 +1348,7 @@
         <v>16.61</v>
       </c>
       <c r="R11" t="n">
-        <v>9.357737816243276</v>
+        <v>9.394991459289512</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1360,19 +1360,19 @@
         <v>6984</v>
       </c>
       <c r="V11" t="n">
-        <v>1.064019629712246</v>
+        <v>1.062012405441814</v>
       </c>
       <c r="W11" t="n">
-        <v>1.195049399548598</v>
+        <v>1.196301469185252</v>
       </c>
       <c r="X11" t="n">
-        <v>336.2250000000002</v>
+        <v>337.7550000000002</v>
       </c>
       <c r="Y11" t="n">
-        <v>299.3600098331766</v>
+        <v>299.8408087254919</v>
       </c>
       <c r="Z11" t="n">
-        <v>299846373.75</v>
+        <v>338486178.9</v>
       </c>
     </row>
     <row r="12">
@@ -1387,16 +1387,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.6745263647463</v>
+        <v>1.658090558569356</v>
       </c>
       <c r="D12" t="n">
-        <v>1.263845043977293</v>
+        <v>1.259158827151343</v>
       </c>
       <c r="E12" t="n">
-        <v>62.35</v>
+        <v>62</v>
       </c>
       <c r="F12" t="n">
-        <v>78.01000000000001</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>136</v>
@@ -1411,7 +1411,7 @@
         <v>12.30882352941176</v>
       </c>
       <c r="K12" t="n">
-        <v>11157707.45</v>
+        <v>11317131</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
@@ -1430,7 +1430,7 @@
         <v>43.74</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4106813207690077</v>
+        <v>0.398931731418013</v>
       </c>
       <c r="S12" t="n">
         <v>4.98</v>
@@ -1442,19 +1442,19 @@
         <v>1674</v>
       </c>
       <c r="V12" t="n">
-        <v>1.033739534112575</v>
+        <v>1.026235206488455</v>
       </c>
       <c r="W12" t="n">
-        <v>1.112178072007453</v>
+        <v>1.105132524642723</v>
       </c>
       <c r="X12" t="n">
-        <v>60.31500000000001</v>
+        <v>60.41500000000001</v>
       </c>
       <c r="Y12" t="n">
-        <v>56.06116643484963</v>
+        <v>56.10186888675988</v>
       </c>
       <c r="Z12" t="n">
-        <v>470988470.75</v>
+        <v>609220494</v>
       </c>
     </row>
     <row r="13">
@@ -1469,16 +1469,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.32214527630802</v>
+        <v>2.317419181505892</v>
       </c>
       <c r="D13" t="n">
-        <v>1.919848354377049</v>
+        <v>1.914577696476608</v>
       </c>
       <c r="E13" t="n">
-        <v>51.95</v>
+        <v>51.9</v>
       </c>
       <c r="F13" t="n">
-        <v>81.58</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>243</v>
@@ -1493,7 +1493,7 @@
         <v>15.32921810699589</v>
       </c>
       <c r="K13" t="n">
-        <v>1107714.35</v>
+        <v>1114592.55</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
@@ -1512,7 +1512,7 @@
         <v>22.58</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4022969219309704</v>
+        <v>0.4028414850292839</v>
       </c>
       <c r="S13" t="n">
         <v>7.549999999999999</v>
@@ -1524,19 +1524,19 @@
         <v>3725</v>
       </c>
       <c r="V13" t="n">
-        <v>1.054148108316509</v>
+        <v>1.049120679199515</v>
       </c>
       <c r="W13" t="n">
-        <v>1.150142776118656</v>
+        <v>1.147183257215304</v>
       </c>
       <c r="X13" t="n">
-        <v>49.28149999999999</v>
+        <v>49.46999999999998</v>
       </c>
       <c r="Y13" t="n">
-        <v>45.16830525625152</v>
+        <v>45.24124604641035</v>
       </c>
       <c r="Z13" t="n">
-        <v>30291837.2</v>
+        <v>44031233.4</v>
       </c>
     </row>
     <row r="14">
@@ -1551,16 +1551,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.018950855999971</v>
+        <v>2.010951789128791</v>
       </c>
       <c r="D14" t="n">
-        <v>1.883748645216536</v>
+        <v>1.878441105834197</v>
       </c>
       <c r="E14" t="n">
-        <v>49.47</v>
+        <v>49.36</v>
       </c>
       <c r="F14" t="n">
-        <v>79.39</v>
+        <v>73.64</v>
       </c>
       <c r="G14" t="n">
         <v>276</v>
@@ -1575,7 +1575,7 @@
         <v>13.22463768115942</v>
       </c>
       <c r="K14" t="n">
-        <v>255266.35</v>
+        <v>229027.25</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
@@ -1594,7 +1594,7 @@
         <v>24.17</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1352022107834343</v>
+        <v>0.1325106832945937</v>
       </c>
       <c r="S14" t="n">
         <v>4.671</v>
@@ -1606,19 +1606,19 @@
         <v>3650</v>
       </c>
       <c r="V14" t="n">
-        <v>1.036889540976734</v>
+        <v>1.032053024442261</v>
       </c>
       <c r="W14" t="n">
-        <v>1.111134721063639</v>
+        <v>1.107278467278829</v>
       </c>
       <c r="X14" t="n">
-        <v>47.71</v>
+        <v>47.82700000000001</v>
       </c>
       <c r="Y14" t="n">
-        <v>44.52205395277775</v>
+        <v>44.57776562864419</v>
       </c>
       <c r="Z14" t="n">
-        <v>6025940.7</v>
+        <v>6547159.76</v>
       </c>
     </row>
     <row r="15">
@@ -1633,16 +1633,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6.589893126013595</v>
+        <v>6.558544382672859</v>
       </c>
       <c r="D15" t="n">
-        <v>5.258947965356257</v>
+        <v>5.249885591783936</v>
       </c>
       <c r="E15" t="n">
-        <v>341.8</v>
+        <v>340.45</v>
       </c>
       <c r="F15" t="n">
-        <v>85.81</v>
+        <v>78.14</v>
       </c>
       <c r="G15" t="n">
         <v>1245</v>
@@ -1657,7 +1657,7 @@
         <v>12.02409638554217</v>
       </c>
       <c r="K15" t="n">
-        <v>26018.9</v>
+        <v>24764.75</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
@@ -1676,7 +1676,7 @@
         <v>8.970000000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>1.330945160657338</v>
+        <v>1.308658790888923</v>
       </c>
       <c r="S15" t="n">
         <v>1.685</v>
@@ -1688,19 +1688,19 @@
         <v>14970</v>
       </c>
       <c r="V15" t="n">
-        <v>1.031817907383928</v>
+        <v>1.025799404918835</v>
       </c>
       <c r="W15" t="n">
-        <v>1.088122625759537</v>
+        <v>1.08296046162292</v>
       </c>
       <c r="X15" t="n">
-        <v>331.26</v>
+        <v>331.8875</v>
       </c>
       <c r="Y15" t="n">
-        <v>314.1190081967233</v>
+        <v>314.3697411536179</v>
       </c>
       <c r="Z15" t="n">
-        <v>2632543.6</v>
+        <v>2701811.2</v>
       </c>
     </row>
     <row r="16">
@@ -1715,16 +1715,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2.173836683611807</v>
+        <v>2.177295438696302</v>
       </c>
       <c r="D16" t="n">
-        <v>1.989633791076708</v>
+        <v>1.984405102958954</v>
       </c>
       <c r="E16" t="n">
-        <v>53.3</v>
+        <v>53.4</v>
       </c>
       <c r="F16" t="n">
-        <v>72.95</v>
+        <v>67.45</v>
       </c>
       <c r="G16" t="n">
         <v>384</v>
@@ -1739,7 +1739,7 @@
         <v>15.328125</v>
       </c>
       <c r="K16" t="n">
-        <v>15815645.2</v>
+        <v>16156135.9</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
@@ -1758,7 +1758,7 @@
         <v>15.81</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1842028925350987</v>
+        <v>0.1928903357373479</v>
       </c>
       <c r="S16" t="n">
         <v>12.5</v>
@@ -1770,19 +1770,19 @@
         <v>5886</v>
       </c>
       <c r="V16" t="n">
-        <v>1.029583627109149</v>
+        <v>1.02908018731572</v>
       </c>
       <c r="W16" t="n">
-        <v>1.097280636652826</v>
+        <v>1.097758174122125</v>
       </c>
       <c r="X16" t="n">
-        <v>51.7685</v>
+        <v>51.891</v>
       </c>
       <c r="Y16" t="n">
-        <v>48.57462915101439</v>
+        <v>48.64459337112554</v>
       </c>
       <c r="Z16" t="n">
-        <v>589833630.1</v>
+        <v>896160722.4</v>
       </c>
     </row>
     <row r="17">
@@ -1797,16 +1797,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8.856266526813652</v>
+        <v>8.825872097466622</v>
       </c>
       <c r="D17" t="n">
-        <v>5.359209199435752</v>
+        <v>5.350063703246777</v>
       </c>
       <c r="E17" t="n">
-        <v>67</v>
+        <v>66.8</v>
       </c>
       <c r="F17" t="n">
-        <v>81.59</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="G17" t="n">
         <v>1111</v>
@@ -1821,7 +1821,7 @@
         <v>14.18091809180918</v>
       </c>
       <c r="K17" t="n">
-        <v>15259096.65</v>
+        <v>15684133</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
@@ -1840,7 +1840,7 @@
         <v>8.050000000000001</v>
       </c>
       <c r="R17" t="n">
-        <v>3.4970573273779</v>
+        <v>3.475808394219845</v>
       </c>
       <c r="S17" t="n">
         <v>2.232857285714286</v>
@@ -1852,19 +1852,19 @@
         <v>15755</v>
       </c>
       <c r="V17" t="n">
-        <v>1.035068747103352</v>
+        <v>1.029553423496319</v>
       </c>
       <c r="W17" t="n">
-        <v>1.100825326252461</v>
+        <v>1.096112166187248</v>
       </c>
       <c r="X17" t="n">
-        <v>64.73000000000006</v>
+        <v>64.88250000000006</v>
       </c>
       <c r="Y17" t="n">
-        <v>60.8634252884498</v>
+        <v>60.94266815079634</v>
       </c>
       <c r="Z17" t="n">
-        <v>1279911318</v>
+        <v>1370380356.8</v>
       </c>
     </row>
     <row r="18">
@@ -1879,16 +1879,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3.344656297172801</v>
+        <v>3.261720153722623</v>
       </c>
       <c r="D18" t="n">
-        <v>2.750893495929951</v>
+        <v>2.744761417961923</v>
       </c>
       <c r="E18" t="n">
-        <v>110.15</v>
+        <v>107.9</v>
       </c>
       <c r="F18" t="n">
-        <v>69.95999999999999</v>
+        <v>50.77</v>
       </c>
       <c r="G18" t="n">
         <v>498</v>
@@ -1903,7 +1903,7 @@
         <v>13.81124497991968</v>
       </c>
       <c r="K18" t="n">
-        <v>1325503.7</v>
+        <v>1353090</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
@@ -1922,7 +1922,7 @@
         <v>14.26</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5937628012428493</v>
+        <v>0.5169587357607002</v>
       </c>
       <c r="S18" t="n">
         <v>13.37</v>
@@ -1934,19 +1934,19 @@
         <v>6878</v>
       </c>
       <c r="V18" t="n">
-        <v>1.026393645025276</v>
+        <v>1.005029806259315</v>
       </c>
       <c r="W18" t="n">
-        <v>1.094572774631067</v>
+        <v>1.071798520349867</v>
       </c>
       <c r="X18" t="n">
-        <v>107.3174999999999</v>
+        <v>107.3599999999999</v>
       </c>
       <c r="Y18" t="n">
-        <v>100.632870242115</v>
+        <v>100.6719061011375</v>
       </c>
       <c r="Z18" t="n">
-        <v>272324395.75</v>
+        <v>223433709.2</v>
       </c>
     </row>
     <row r="19">
@@ -1961,16 +1961,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.917339071993916</v>
+        <v>5.907607131034982</v>
       </c>
       <c r="D19" t="n">
-        <v>5.917339071993916</v>
+        <v>5.907607131034982</v>
       </c>
       <c r="E19" t="n">
-        <v>114.95</v>
+        <v>114.8</v>
       </c>
       <c r="F19" t="n">
-        <v>83.23</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="G19" t="n">
         <v>1695</v>
@@ -1985,7 +1985,7 @@
         <v>13.46961651917404</v>
       </c>
       <c r="K19" t="n">
-        <v>76094921</v>
+        <v>79107287.25</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
@@ -2016,19 +2016,19 @@
         <v>22831</v>
       </c>
       <c r="V19" t="n">
-        <v>1.033258426966292</v>
+        <v>1.0295271618501</v>
       </c>
       <c r="W19" t="n">
-        <v>1.09385339779308</v>
+        <v>1.091204345016956</v>
       </c>
       <c r="X19" t="n">
-        <v>111.25</v>
+        <v>111.5075</v>
       </c>
       <c r="Y19" t="n">
-        <v>105.0872084247478</v>
+        <v>105.204859680261</v>
       </c>
       <c r="Z19" t="n">
-        <v>11480961846.2</v>
+        <v>12208825938.4</v>
       </c>
     </row>
     <row r="20">
@@ -2039,20 +2039,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>元大電子</t>
+          <t>元大科技市值</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7.260905382222246</v>
+        <v>7.226450478997096</v>
       </c>
       <c r="D20" t="n">
-        <v>5.318830335500019</v>
+        <v>5.309744215166474</v>
       </c>
       <c r="E20" t="n">
-        <v>259.95</v>
+        <v>258.85</v>
       </c>
       <c r="F20" t="n">
-        <v>74.58</v>
+        <v>64.55</v>
       </c>
       <c r="G20" t="n">
         <v>1190</v>
@@ -2067,7 +2067,7 @@
         <v>13.83697478991597</v>
       </c>
       <c r="K20" t="n">
-        <v>166729.85</v>
+        <v>209285</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
@@ -2086,7 +2086,7 @@
         <v>7.58</v>
       </c>
       <c r="R20" t="n">
-        <v>1.942075046722227</v>
+        <v>1.916706263830622</v>
       </c>
       <c r="S20" t="n">
         <v>18.91</v>
@@ -2098,101 +2098,183 @@
         <v>16466</v>
       </c>
       <c r="V20" t="n">
-        <v>1.03805606580944</v>
+        <v>1.031326261267991</v>
       </c>
       <c r="W20" t="n">
-        <v>1.10767716157917</v>
+        <v>1.101980179576345</v>
       </c>
       <c r="X20" t="n">
-        <v>250.4200000000001</v>
+        <v>250.9875000000001</v>
       </c>
       <c r="Y20" t="n">
-        <v>234.6802922517603</v>
+        <v>234.8953318738587</v>
       </c>
       <c r="Z20" t="n">
-        <v>51273577.8</v>
+        <v>233455779.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>006208.TW</t>
+          <t>00892.TW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>富邦台50</t>
+          <t>富邦台灣半導體</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4.407296928049225</v>
+        <v>2.051809130958175</v>
       </c>
       <c r="D21" t="n">
-        <v>4.147887349924367</v>
+        <v>1.932044354238441</v>
       </c>
       <c r="E21" t="n">
-        <v>263.4</v>
+        <v>43.92</v>
       </c>
       <c r="F21" t="n">
-        <v>84.44</v>
+        <v>60.6</v>
       </c>
       <c r="G21" t="n">
-        <v>895</v>
+        <v>241</v>
       </c>
       <c r="H21" t="n">
-        <v>88.48999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="J21" t="n">
-        <v>13.86703910614525</v>
+        <v>15.85892116182573</v>
       </c>
       <c r="K21" t="n">
-        <v>2222986.85</v>
+        <v>4288538.55</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
         <v>2</v>
       </c>
       <c r="N21" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-7.43</v>
+      </c>
+      <c r="P21" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.1197647767197338</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4.937</v>
+      </c>
+      <c r="T21" t="n">
+        <v>510.5</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3822</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.02582069158813</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.078161419761171</v>
+      </c>
+      <c r="X21" t="n">
+        <v>42.8145</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>40.73601521535519</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>175857700.32</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>006208.TW</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>富邦台50</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>4.401217721613286</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4.140112159270349</v>
+      </c>
+      <c r="E22" t="n">
+        <v>263.15</v>
+      </c>
+      <c r="F22" t="n">
+        <v>80.02</v>
+      </c>
+      <c r="G22" t="n">
+        <v>895</v>
+      </c>
+      <c r="H22" t="n">
+        <v>88.48999999999999</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="J22" t="n">
+        <v>13.86703910614525</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2308981.55</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>2</v>
+      </c>
+      <c r="N22" t="n">
         <v>11.21</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O22" t="n">
         <v>-6.25</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P22" t="n">
         <v>4.960000000000001</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q22" t="n">
         <v>8.949999999999999</v>
       </c>
-      <c r="R21" t="n">
-        <v>0.259409578124858</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="R22" t="n">
+        <v>0.2611055623429364</v>
+      </c>
+      <c r="S22" t="n">
         <v>28.764</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T22" t="n">
         <v>1745.92</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>12411</v>
       </c>
-      <c r="V21" t="n">
-        <v>1.035001031464581</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.095435083247884</v>
-      </c>
-      <c r="X21" t="n">
-        <v>254.4925</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>240.4524047367904</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>478559870.4</v>
+      <c r="V22" t="n">
+        <v>1.031414741215435</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.093045711667015</v>
+      </c>
+      <c r="X22" t="n">
+        <v>255.135</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>240.7493091928125</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>918836644.5999999</v>
       </c>
     </row>
   </sheetData>

--- a/ETF動態清單.xlsx
+++ b/ETF動態清單.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z22"/>
+  <dimension ref="A1:Z20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,16 +567,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8897191648212786</v>
+        <v>0.8178283126724888</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6382817168657253</v>
+        <v>0.6025702326289217</v>
       </c>
       <c r="E2" t="n">
-        <v>32.3</v>
+        <v>31.06</v>
       </c>
       <c r="F2" t="n">
-        <v>82.52</v>
+        <v>62.85</v>
       </c>
       <c r="G2" t="n">
         <v>41</v>
@@ -591,7 +591,7 @@
         <v>8.439024390243903</v>
       </c>
       <c r="K2" t="n">
-        <v>150784442.6</v>
+        <v>158607058.15</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
@@ -610,7 +610,7 @@
         <v>386.28</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2514374479555532</v>
+        <v>0.2152580800435671</v>
       </c>
       <c r="S2" t="n">
         <v>1.67</v>
@@ -622,19 +622,19 @@
         <v>346</v>
       </c>
       <c r="V2" t="n">
-        <v>1.059711286089238</v>
+        <v>1.017076804689163</v>
       </c>
       <c r="W2" t="n">
-        <v>1.166064679098722</v>
+        <v>1.1188199941258</v>
       </c>
       <c r="X2" t="n">
-        <v>30.48000000000001</v>
+        <v>30.53850000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>27.70000719425392</v>
+        <v>27.76139161176594</v>
       </c>
       <c r="Z2" t="n">
-        <v>3435311009.4</v>
+        <v>7280002696.88</v>
       </c>
     </row>
     <row r="3">
@@ -649,16 +649,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.348550165286301</v>
+        <v>1.263888617641034</v>
       </c>
       <c r="D3" t="n">
-        <v>1.001579600051825</v>
+        <v>0.9586213872950113</v>
       </c>
       <c r="E3" t="n">
-        <v>40.12</v>
+        <v>38.69</v>
       </c>
       <c r="F3" t="n">
-        <v>53.53</v>
+        <v>42.3</v>
       </c>
       <c r="G3" t="n">
         <v>66</v>
@@ -673,9 +673,13 @@
         <v>10.33333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>8337668.95</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
+        <v>9615802.199999999</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="M3" t="n">
         <v>2</v>
       </c>
@@ -692,7 +696,7 @@
         <v>159.78</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3469705652344754</v>
+        <v>0.3052672303460227</v>
       </c>
       <c r="S3" t="n">
         <v>0.78</v>
@@ -704,19 +708,19 @@
         <v>682</v>
       </c>
       <c r="V3" t="n">
-        <v>1.018597270707711</v>
+        <v>0.9816059875681842</v>
       </c>
       <c r="W3" t="n">
-        <v>1.114294662652908</v>
+        <v>1.072798212046816</v>
       </c>
       <c r="X3" t="n">
-        <v>39.38750000000002</v>
+        <v>39.41500000000002</v>
       </c>
       <c r="Y3" t="n">
-        <v>36.00483906517371</v>
+        <v>36.06456420745004</v>
       </c>
       <c r="Z3" t="n">
-        <v>665333189.4799999</v>
+        <v>1094762877.02</v>
       </c>
     </row>
     <row r="4">
@@ -731,16 +735,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.692002548245465</v>
+        <v>2.577892619745611</v>
       </c>
       <c r="D4" t="n">
-        <v>2.48114450172063</v>
+        <v>2.408711736834672</v>
       </c>
       <c r="E4" t="n">
-        <v>89.84999999999999</v>
+        <v>86.65000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>73.09999999999999</v>
+        <v>54.32</v>
       </c>
       <c r="G4" t="n">
         <v>495</v>
@@ -755,7 +759,7 @@
         <v>12.29090909090909</v>
       </c>
       <c r="K4" t="n">
-        <v>7719537.85</v>
+        <v>8367567.35</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
@@ -774,7 +778,7 @@
         <v>19.85</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2108580465248355</v>
+        <v>0.1691808829109389</v>
       </c>
       <c r="S4" t="n">
         <v>17.71</v>
@@ -786,19 +790,19 @@
         <v>6084</v>
       </c>
       <c r="V4" t="n">
-        <v>1.037588775333449</v>
+        <v>0.9985594929415154</v>
       </c>
       <c r="W4" t="n">
-        <v>1.164128593721029</v>
+        <v>1.11801230416752</v>
       </c>
       <c r="X4" t="n">
-        <v>86.595</v>
+        <v>86.77500000000001</v>
       </c>
       <c r="Y4" t="n">
-        <v>77.18219489206325</v>
+        <v>77.50361930454801</v>
       </c>
       <c r="Z4" t="n">
-        <v>1093625448</v>
+        <v>1485440950</v>
       </c>
     </row>
     <row r="5">
@@ -813,16 +817,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13.16165753242944</v>
+        <v>12.58843047628005</v>
       </c>
       <c r="D5" t="n">
-        <v>3.202457986221948</v>
+        <v>3.115671208676509</v>
       </c>
       <c r="E5" t="n">
-        <v>118.4</v>
+        <v>113.65</v>
       </c>
       <c r="F5" t="n">
-        <v>82.73999999999999</v>
+        <v>60.5</v>
       </c>
       <c r="G5" t="n">
         <v>564</v>
@@ -837,7 +841,7 @@
         <v>11.9113475177305</v>
       </c>
       <c r="K5" t="n">
-        <v>4856870.1</v>
+        <v>5091143.8</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
@@ -856,7 +860,7 @@
         <v>18.35</v>
       </c>
       <c r="R5" t="n">
-        <v>9.95919954620749</v>
+        <v>9.472759267603543</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -868,19 +872,19 @@
         <v>6718</v>
       </c>
       <c r="V5" t="n">
-        <v>1.062288316174326</v>
+        <v>1.016683812676119</v>
       </c>
       <c r="W5" t="n">
-        <v>1.196283694188915</v>
+        <v>1.142990562995831</v>
       </c>
       <c r="X5" t="n">
-        <v>111.4575000000001</v>
+        <v>111.7850000000001</v>
       </c>
       <c r="Y5" t="n">
-        <v>98.97317883303228</v>
+        <v>99.43214203109264</v>
       </c>
       <c r="Z5" t="n">
-        <v>503276723.2</v>
+        <v>996693679.8000001</v>
       </c>
     </row>
     <row r="6">
@@ -895,16 +899,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.53041930581944</v>
+        <v>16.80408088868726</v>
       </c>
       <c r="D6" t="n">
-        <v>3.648292890301905</v>
+        <v>3.552635722543141</v>
       </c>
       <c r="E6" t="n">
-        <v>40.89</v>
+        <v>39.3</v>
       </c>
       <c r="F6" t="n">
-        <v>81.98</v>
+        <v>59.04</v>
       </c>
       <c r="G6" t="n">
         <v>644</v>
@@ -919,7 +923,7 @@
         <v>12.68167701863354</v>
       </c>
       <c r="K6" t="n">
-        <v>152429063.4</v>
+        <v>163212043.3</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
@@ -938,7 +942,7 @@
         <v>15.49</v>
       </c>
       <c r="R6" t="n">
-        <v>13.88212641551753</v>
+        <v>13.25144516614412</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -950,19 +954,19 @@
         <v>8167</v>
       </c>
       <c r="V6" t="n">
-        <v>1.059999222304313</v>
+        <v>1.015950158984567</v>
       </c>
       <c r="W6" t="n">
-        <v>1.190076546804459</v>
+        <v>1.138864211543347</v>
       </c>
       <c r="X6" t="n">
-        <v>38.57549999999999</v>
+        <v>38.68299999999999</v>
       </c>
       <c r="Y6" t="n">
-        <v>34.35913438492342</v>
+        <v>34.50806479092189</v>
       </c>
       <c r="Z6" t="n">
-        <v>5334644582.34</v>
+        <v>12964066631.7</v>
       </c>
     </row>
     <row r="7">
@@ -977,16 +981,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.980182984636244</v>
+        <v>1.908831033317239</v>
       </c>
       <c r="D7" t="n">
-        <v>1.861465583347427</v>
+        <v>1.801157630571303</v>
       </c>
       <c r="E7" t="n">
-        <v>44.09</v>
+        <v>42.97</v>
       </c>
       <c r="F7" t="n">
-        <v>68.95</v>
+        <v>50.52</v>
       </c>
       <c r="G7" t="n">
         <v>239</v>
@@ -1001,7 +1005,7 @@
         <v>10.78242677824268</v>
       </c>
       <c r="K7" t="n">
-        <v>2012213.45</v>
+        <v>2555476.35</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
@@ -1020,7 +1024,7 @@
         <v>37.53</v>
       </c>
       <c r="R7" t="n">
-        <v>0.118717401288817</v>
+        <v>0.1076734027459367</v>
       </c>
       <c r="S7" t="n">
         <v>4.850000000000001</v>
@@ -1032,1249 +1036,1097 @@
         <v>2577</v>
       </c>
       <c r="V7" t="n">
-        <v>1.027918633793787</v>
+        <v>1.000523895453752</v>
       </c>
       <c r="W7" t="n">
-        <v>1.103226716380128</v>
+        <v>1.072710646257449</v>
       </c>
       <c r="X7" t="n">
-        <v>42.8925</v>
+        <v>42.9475</v>
       </c>
       <c r="Y7" t="n">
-        <v>39.96458692068907</v>
+        <v>40.05740052074327</v>
       </c>
       <c r="Z7" t="n">
-        <v>274841187.6</v>
+        <v>483921823.41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>00913.TW</t>
+          <t>00685L.TW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>兆豐台灣晶圓製造</t>
+          <t>群益臺灣加權正2</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.887172476537584</v>
+        <v>11.40875170209796</v>
       </c>
       <c r="D8" t="n">
-        <v>1.763843847996092</v>
+        <v>2.939038886552234</v>
       </c>
       <c r="E8" t="n">
-        <v>53.05</v>
+        <v>13.02</v>
       </c>
       <c r="F8" t="n">
-        <v>59.28</v>
+        <v>60.7</v>
       </c>
       <c r="G8" t="n">
-        <v>262</v>
+        <v>514</v>
       </c>
       <c r="H8" t="n">
-        <v>96.18000000000001</v>
+        <v>88.52</v>
       </c>
       <c r="I8" t="n">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="J8" t="n">
-        <v>12.79770992366412</v>
+        <v>12.18093385214008</v>
       </c>
       <c r="K8" t="n">
-        <v>1582116.8</v>
+        <v>214323107.55</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>13.5</v>
+        <v>15.89</v>
       </c>
       <c r="O8" t="n">
-        <v>-9.19</v>
+        <v>-18.5</v>
       </c>
       <c r="P8" t="n">
-        <v>4.31</v>
+        <v>-2.609999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>28.72</v>
+        <v>18.65</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1233286285414916</v>
+        <v>8.469712815545726</v>
       </c>
       <c r="S8" t="n">
-        <v>6.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>916.5599999999999</v>
+        <v>1777.84</v>
       </c>
       <c r="U8" t="n">
-        <v>3353</v>
+        <v>6261</v>
       </c>
       <c r="V8" t="n">
-        <v>1.027035922057557</v>
+        <v>1.018062397372742</v>
       </c>
       <c r="W8" t="n">
-        <v>1.123087169026796</v>
+        <v>1.146349560207693</v>
       </c>
       <c r="X8" t="n">
-        <v>51.65349999999997</v>
+        <v>12.789</v>
       </c>
       <c r="Y8" t="n">
-        <v>47.23587043200765</v>
+        <v>11.35779211852366</v>
       </c>
       <c r="Z8" t="n">
-        <v>75566807.25</v>
+        <v>6626951017.26</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>00685L.TW</t>
+          <t>00715L.TW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>群益臺灣加權正2</t>
+          <t>期街口布蘭特正2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11.91908424772292</v>
+        <v>5.055651058181655</v>
       </c>
       <c r="D9" t="n">
-        <v>3.022259519041445</v>
+        <v>2.792629136424982</v>
       </c>
       <c r="E9" t="n">
-        <v>13.55</v>
+        <v>75.2</v>
       </c>
       <c r="F9" t="n">
-        <v>82.48</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>514</v>
+        <v>425</v>
       </c>
       <c r="H9" t="n">
-        <v>88.52</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>3.46</v>
+        <v>3.32</v>
       </c>
       <c r="J9" t="n">
-        <v>12.18093385214008</v>
+        <v>17.11294117647059</v>
       </c>
       <c r="K9" t="n">
-        <v>197393535.2</v>
+        <v>4356497.3</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>15.89</v>
+        <v>32.14</v>
       </c>
       <c r="O9" t="n">
-        <v>-18.5</v>
+        <v>-44.86</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.609999999999999</v>
+        <v>-12.72</v>
       </c>
       <c r="Q9" t="n">
-        <v>18.65</v>
+        <v>14.59</v>
       </c>
       <c r="R9" t="n">
-        <v>8.896824728681478</v>
+        <v>2.263021921756673</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1777.84</v>
+        <v>1409.31</v>
       </c>
       <c r="U9" t="n">
-        <v>6261</v>
+        <v>7273</v>
       </c>
       <c r="V9" t="n">
-        <v>1.062661752019449</v>
+        <v>1.099495577162074</v>
       </c>
       <c r="W9" t="n">
-        <v>1.198473218565535</v>
+        <v>1.230279690708689</v>
       </c>
       <c r="X9" t="n">
-        <v>12.751</v>
+        <v>68.39499999999995</v>
       </c>
       <c r="Y9" t="n">
-        <v>11.30605155801323</v>
+        <v>61.12431227461936</v>
       </c>
       <c r="Z9" t="n">
-        <v>2407156375.35</v>
+        <v>160651264</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>00715L.TW</t>
+          <t>00675L.TW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>期街口布蘭特正2</t>
+          <t>富邦臺灣加權正2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4.840492347539276</v>
+        <v>11.98011030014668</v>
       </c>
       <c r="D10" t="n">
-        <v>2.87287519833661</v>
+        <v>3.049652145850465</v>
       </c>
       <c r="E10" t="n">
-        <v>72.5</v>
+        <v>344.25</v>
       </c>
       <c r="F10" t="n">
-        <v>88.15000000000001</v>
+        <v>60.22</v>
       </c>
       <c r="G10" t="n">
-        <v>425</v>
+        <v>564</v>
       </c>
       <c r="H10" t="n">
-        <v>77.65000000000001</v>
+        <v>87.06</v>
       </c>
       <c r="I10" t="n">
-        <v>3.32</v>
+        <v>3.18</v>
       </c>
       <c r="J10" t="n">
-        <v>17.11294117647059</v>
+        <v>12.38297872340426</v>
       </c>
       <c r="K10" t="n">
-        <v>4522921.15</v>
+        <v>1029749.6</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>32.14</v>
+        <v>15.7</v>
       </c>
       <c r="O10" t="n">
-        <v>-44.86</v>
+        <v>-24.73</v>
       </c>
       <c r="P10" t="n">
-        <v>-12.72</v>
+        <v>-9.030000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>14.59</v>
+        <v>16.61</v>
       </c>
       <c r="R10" t="n">
-        <v>1.967617149202666</v>
+        <v>8.930458154296218</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1409.31</v>
+        <v>1792.47</v>
       </c>
       <c r="U10" t="n">
-        <v>7273</v>
+        <v>6984</v>
       </c>
       <c r="V10" t="n">
-        <v>1.069558161835215</v>
+        <v>1.01625116237878</v>
       </c>
       <c r="W10" t="n">
-        <v>1.191228203137704</v>
+        <v>1.142775151870361</v>
       </c>
       <c r="X10" t="n">
-        <v>67.78499999999994</v>
+        <v>338.7450000000002</v>
       </c>
       <c r="Y10" t="n">
-        <v>60.86155432605983</v>
+        <v>301.2403616201944</v>
       </c>
       <c r="Z10" t="n">
-        <v>218961672.5</v>
+        <v>671789072.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>00675L.TW</t>
+          <t>00935.TW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>富邦臺灣加權正2</t>
+          <t>野村臺灣新科技50</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>12.53007670913105</v>
+        <v>1.575400246909418</v>
       </c>
       <c r="D11" t="n">
-        <v>3.13508524984154</v>
+        <v>1.210963069798623</v>
       </c>
       <c r="E11" t="n">
-        <v>358.7</v>
+        <v>60</v>
       </c>
       <c r="F11" t="n">
-        <v>82.67</v>
+        <v>50.45</v>
       </c>
       <c r="G11" t="n">
-        <v>564</v>
+        <v>136</v>
       </c>
       <c r="H11" t="n">
-        <v>87.06</v>
+        <v>83.09</v>
       </c>
       <c r="I11" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="J11" t="n">
-        <v>12.38297872340426</v>
+        <v>12.30882352941176</v>
       </c>
       <c r="K11" t="n">
-        <v>975459.55</v>
+        <v>11933751.55</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>15.7</v>
+        <v>14.6</v>
       </c>
       <c r="O11" t="n">
-        <v>-24.73</v>
+        <v>-8.99</v>
       </c>
       <c r="P11" t="n">
-        <v>-9.030000000000001</v>
+        <v>5.609999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>16.61</v>
+        <v>43.74</v>
       </c>
       <c r="R11" t="n">
-        <v>9.394991459289512</v>
+        <v>0.3644371771107955</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="T11" t="n">
-        <v>1792.47</v>
+        <v>428.12</v>
       </c>
       <c r="U11" t="n">
-        <v>6984</v>
+        <v>1674</v>
       </c>
       <c r="V11" t="n">
-        <v>1.062012405441814</v>
+        <v>0.9928843289756742</v>
       </c>
       <c r="W11" t="n">
-        <v>1.196301469185252</v>
+        <v>1.069045358062654</v>
       </c>
       <c r="X11" t="n">
-        <v>337.7550000000002</v>
+        <v>60.43000000000001</v>
       </c>
       <c r="Y11" t="n">
-        <v>299.8408087254919</v>
+        <v>56.12484030493642</v>
       </c>
       <c r="Z11" t="n">
-        <v>338486178.9</v>
+        <v>1220565840</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>00935.TW</t>
+          <t>00894.TW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>野村臺灣新科技50</t>
+          <t>中信小資高價30</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.658090558569356</v>
+        <v>2.229647402468231</v>
       </c>
       <c r="D12" t="n">
-        <v>1.259158827151343</v>
+        <v>1.853358795831452</v>
       </c>
       <c r="E12" t="n">
-        <v>62</v>
+        <v>50.4</v>
       </c>
       <c r="F12" t="n">
-        <v>69.79000000000001</v>
+        <v>59.66</v>
       </c>
       <c r="G12" t="n">
-        <v>136</v>
+        <v>243</v>
       </c>
       <c r="H12" t="n">
-        <v>83.09</v>
+        <v>82.72</v>
       </c>
       <c r="I12" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="J12" t="n">
-        <v>12.30882352941176</v>
+        <v>15.32921810699589</v>
       </c>
       <c r="K12" t="n">
-        <v>11317131</v>
+        <v>1185748.2</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>14.6</v>
+        <v>15.7</v>
       </c>
       <c r="O12" t="n">
-        <v>-8.99</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>5.609999999999999</v>
+        <v>7.319999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>43.74</v>
+        <v>22.58</v>
       </c>
       <c r="R12" t="n">
-        <v>0.398931731418013</v>
+        <v>0.3762886066367783</v>
       </c>
       <c r="S12" t="n">
-        <v>4.98</v>
+        <v>7.549999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>428.12</v>
+        <v>698.73</v>
       </c>
       <c r="U12" t="n">
-        <v>1674</v>
+        <v>3725</v>
       </c>
       <c r="V12" t="n">
-        <v>1.026235206488455</v>
+        <v>1.016262211781786</v>
       </c>
       <c r="W12" t="n">
-        <v>1.105132524642723</v>
+        <v>1.109941249215989</v>
       </c>
       <c r="X12" t="n">
-        <v>60.41500000000001</v>
+        <v>49.59349999999999</v>
       </c>
       <c r="Y12" t="n">
-        <v>56.10186888675988</v>
+        <v>45.4078087787081</v>
       </c>
       <c r="Z12" t="n">
-        <v>609220494</v>
+        <v>103466462.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>00894.TW</t>
+          <t>0057.TW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>中信小資高價30</t>
+          <t>富邦摩台</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.317419181505892</v>
+        <v>6.515041012330766</v>
       </c>
       <c r="D13" t="n">
-        <v>1.914577696476608</v>
+        <v>5.122588639247726</v>
       </c>
       <c r="E13" t="n">
-        <v>51.9</v>
+        <v>338.55</v>
       </c>
       <c r="F13" t="n">
-        <v>78.01000000000001</v>
+        <v>65.42</v>
       </c>
       <c r="G13" t="n">
-        <v>243</v>
+        <v>1245</v>
       </c>
       <c r="H13" t="n">
-        <v>82.72</v>
+        <v>93.33</v>
       </c>
       <c r="I13" t="n">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="J13" t="n">
-        <v>15.32921810699589</v>
+        <v>12.02409638554217</v>
       </c>
       <c r="K13" t="n">
-        <v>1114592.55</v>
+        <v>28350.65</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>2</v>
       </c>
       <c r="N13" t="n">
-        <v>15.7</v>
+        <v>14.45</v>
       </c>
       <c r="O13" t="n">
-        <v>-8.380000000000001</v>
+        <v>-6.48</v>
       </c>
       <c r="P13" t="n">
-        <v>7.319999999999999</v>
+        <v>7.969999999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>22.58</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4028414850292839</v>
+        <v>1.39245237308304</v>
       </c>
       <c r="S13" t="n">
-        <v>7.549999999999999</v>
+        <v>1.685</v>
       </c>
       <c r="T13" t="n">
-        <v>698.73</v>
+        <v>3287.55</v>
       </c>
       <c r="U13" t="n">
-        <v>3725</v>
+        <v>14970</v>
       </c>
       <c r="V13" t="n">
-        <v>1.049120679199515</v>
+        <v>1.01797352456983</v>
       </c>
       <c r="W13" t="n">
-        <v>1.147183257215304</v>
+        <v>1.074291818640501</v>
       </c>
       <c r="X13" t="n">
-        <v>49.46999999999998</v>
+        <v>332.5725</v>
       </c>
       <c r="Y13" t="n">
-        <v>45.24124604641035</v>
+        <v>315.1378369691296</v>
       </c>
       <c r="Z13" t="n">
-        <v>44031233.4</v>
+        <v>27209263.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>00901.TW</t>
+          <t>00881.TW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>永豐智能車供應鏈</t>
+          <t>國泰台灣科技龍頭</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.010951789128791</v>
+        <v>2.105792978231118</v>
       </c>
       <c r="D14" t="n">
-        <v>1.878441105834197</v>
+        <v>1.92193057511513</v>
       </c>
       <c r="E14" t="n">
-        <v>49.36</v>
+        <v>52</v>
       </c>
       <c r="F14" t="n">
-        <v>73.64</v>
+        <v>49.2</v>
       </c>
       <c r="G14" t="n">
-        <v>276</v>
+        <v>384</v>
       </c>
       <c r="H14" t="n">
-        <v>89.48999999999999</v>
+        <v>89.58</v>
       </c>
       <c r="I14" t="n">
-        <v>2.79</v>
+        <v>2.52</v>
       </c>
       <c r="J14" t="n">
-        <v>13.22463768115942</v>
+        <v>15.328125</v>
       </c>
       <c r="K14" t="n">
-        <v>229027.25</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
+        <v>17217653.85</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="M14" t="n">
         <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>15.18</v>
+        <v>10.9</v>
       </c>
       <c r="O14" t="n">
-        <v>-7.3</v>
+        <v>-4.28</v>
       </c>
       <c r="P14" t="n">
-        <v>7.88</v>
+        <v>6.62</v>
       </c>
       <c r="Q14" t="n">
-        <v>24.17</v>
+        <v>15.81</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1325106832945937</v>
+        <v>0.1838624031159886</v>
       </c>
       <c r="S14" t="n">
-        <v>4.671</v>
+        <v>12.5</v>
       </c>
       <c r="T14" t="n">
-        <v>771.28</v>
+        <v>966.91</v>
       </c>
       <c r="U14" t="n">
-        <v>3650</v>
+        <v>5886</v>
       </c>
       <c r="V14" t="n">
-        <v>1.032053024442261</v>
+        <v>1.000654273948351</v>
       </c>
       <c r="W14" t="n">
-        <v>1.107278467278829</v>
+        <v>1.065947049982376</v>
       </c>
       <c r="X14" t="n">
-        <v>47.82700000000001</v>
+        <v>51.96599999999999</v>
       </c>
       <c r="Y14" t="n">
-        <v>44.57776562864419</v>
+        <v>48.78291093432809</v>
       </c>
       <c r="Z14" t="n">
-        <v>6547159.76</v>
+        <v>1730199796</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0057.TW</t>
+          <t>0052.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>富邦摩台</t>
+          <t>富邦科技</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6.558544382672859</v>
+        <v>8.624188483881255</v>
       </c>
       <c r="D15" t="n">
-        <v>5.249885591783936</v>
+        <v>5.220452124095178</v>
       </c>
       <c r="E15" t="n">
-        <v>340.45</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>78.14</v>
+        <v>53.42</v>
       </c>
       <c r="G15" t="n">
-        <v>1245</v>
+        <v>1111</v>
       </c>
       <c r="H15" t="n">
-        <v>93.33</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>2.64</v>
+        <v>2.45</v>
       </c>
       <c r="J15" t="n">
-        <v>12.02409638554217</v>
+        <v>14.18091809180918</v>
       </c>
       <c r="K15" t="n">
-        <v>24764.75</v>
+        <v>17001249.3</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>14.45</v>
+        <v>12.7</v>
       </c>
       <c r="O15" t="n">
-        <v>-6.48</v>
+        <v>-14.18</v>
       </c>
       <c r="P15" t="n">
-        <v>7.969999999999999</v>
+        <v>-1.48</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.970000000000001</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>1.308658790888923</v>
+        <v>3.403736359786078</v>
       </c>
       <c r="S15" t="n">
-        <v>1.685</v>
+        <v>2.232857285714286</v>
       </c>
       <c r="T15" t="n">
-        <v>3287.55</v>
+        <v>2723.42</v>
       </c>
       <c r="U15" t="n">
-        <v>14970</v>
+        <v>15755</v>
       </c>
       <c r="V15" t="n">
-        <v>1.025799404918835</v>
+        <v>1.006579706799029</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08296046162292</v>
+        <v>1.070868465041976</v>
       </c>
       <c r="X15" t="n">
-        <v>331.8875</v>
+        <v>64.97250000000007</v>
       </c>
       <c r="Y15" t="n">
-        <v>314.3697411536179</v>
+        <v>61.07192632424415</v>
       </c>
       <c r="Z15" t="n">
-        <v>2701811.2</v>
+        <v>2252448724.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>00881.TW</t>
+          <t>00735.TW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>國泰台灣科技龍頭</t>
+          <t>國泰臺韓科技</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2.177295438696302</v>
+        <v>3.090378322319643</v>
       </c>
       <c r="D16" t="n">
-        <v>1.984405102958954</v>
+        <v>2.667056236535193</v>
       </c>
       <c r="E16" t="n">
-        <v>53.4</v>
+        <v>103.2</v>
       </c>
       <c r="F16" t="n">
-        <v>67.45</v>
+        <v>36.84</v>
       </c>
       <c r="G16" t="n">
-        <v>384</v>
+        <v>498</v>
       </c>
       <c r="H16" t="n">
-        <v>89.58</v>
+        <v>86.55</v>
       </c>
       <c r="I16" t="n">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="J16" t="n">
-        <v>15.328125</v>
+        <v>13.81124497991968</v>
       </c>
       <c r="K16" t="n">
-        <v>16156135.9</v>
-      </c>
-      <c r="L16" t="inlineStr"/>
+        <v>1542879.5</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>10.9</v>
+        <v>21.39</v>
       </c>
       <c r="O16" t="n">
-        <v>-4.28</v>
+        <v>-6.04</v>
       </c>
       <c r="P16" t="n">
-        <v>6.62</v>
+        <v>15.35</v>
       </c>
       <c r="Q16" t="n">
-        <v>15.81</v>
+        <v>14.26</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1928903357373479</v>
+        <v>0.4233220857844504</v>
       </c>
       <c r="S16" t="n">
-        <v>12.5</v>
+        <v>13.37</v>
       </c>
       <c r="T16" t="n">
-        <v>966.91</v>
+        <v>1133.84</v>
       </c>
       <c r="U16" t="n">
-        <v>5886</v>
+        <v>6878</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02908018731572</v>
+        <v>0.9629560511337139</v>
       </c>
       <c r="W16" t="n">
-        <v>1.097758174122125</v>
+        <v>1.029526536450664</v>
       </c>
       <c r="X16" t="n">
-        <v>51.891</v>
+        <v>107.1699999999999</v>
       </c>
       <c r="Y16" t="n">
-        <v>48.64459337112554</v>
+        <v>100.2402525298535</v>
       </c>
       <c r="Z16" t="n">
-        <v>896160722.4</v>
+        <v>485501613.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>0052.TW</t>
+          <t>0050.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>富邦科技</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8.825872097466622</v>
+        <v>5.767414424994361</v>
       </c>
       <c r="D17" t="n">
-        <v>5.350063703246777</v>
+        <v>5.767414424994361</v>
       </c>
       <c r="E17" t="n">
-        <v>66.8</v>
+        <v>112.4</v>
       </c>
       <c r="F17" t="n">
-        <v>74.48999999999999</v>
+        <v>56.77</v>
       </c>
       <c r="G17" t="n">
-        <v>1111</v>
+        <v>1695</v>
       </c>
       <c r="H17" t="n">
-        <v>88.20999999999999</v>
+        <v>90.97</v>
       </c>
       <c r="I17" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="J17" t="n">
-        <v>14.18091809180918</v>
+        <v>13.46961651917404</v>
       </c>
       <c r="K17" t="n">
-        <v>15684133</v>
+        <v>88922563.2</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>12.7</v>
+        <v>13.94</v>
       </c>
       <c r="O17" t="n">
-        <v>-14.18</v>
+        <v>-5.91</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.48</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>8.050000000000001</v>
+        <v>6.04</v>
       </c>
       <c r="R17" t="n">
-        <v>3.475808394219845</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.232857285714286</v>
+        <v>4.84625</v>
       </c>
       <c r="T17" t="n">
-        <v>2723.42</v>
+        <v>3824.71</v>
       </c>
       <c r="U17" t="n">
-        <v>15755</v>
+        <v>22831</v>
       </c>
       <c r="V17" t="n">
-        <v>1.029553423496319</v>
+        <v>1.006537118294976</v>
       </c>
       <c r="W17" t="n">
-        <v>1.096112166187248</v>
+        <v>1.065889322060972</v>
       </c>
       <c r="X17" t="n">
-        <v>64.88250000000006</v>
+        <v>111.67</v>
       </c>
       <c r="Y17" t="n">
-        <v>60.94266815079634</v>
+        <v>105.4518491494658</v>
       </c>
       <c r="Z17" t="n">
-        <v>1370380356.8</v>
+        <v>27208751850.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>00735.TW</t>
+          <t>0053.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>國泰臺韓科技</t>
+          <t>元大科技市值</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3.261720153722623</v>
+        <v>7.054393140488644</v>
       </c>
       <c r="D18" t="n">
-        <v>2.744761417961923</v>
+        <v>5.181319198857089</v>
       </c>
       <c r="E18" t="n">
-        <v>107.9</v>
+        <v>253.15</v>
       </c>
       <c r="F18" t="n">
-        <v>50.77</v>
+        <v>45.94</v>
       </c>
       <c r="G18" t="n">
-        <v>498</v>
+        <v>1190</v>
       </c>
       <c r="H18" t="n">
-        <v>86.55</v>
+        <v>89.16</v>
       </c>
       <c r="I18" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="J18" t="n">
-        <v>13.81124497991968</v>
+        <v>13.83697478991597</v>
       </c>
       <c r="K18" t="n">
-        <v>1353090</v>
-      </c>
-      <c r="L18" t="inlineStr"/>
+        <v>248461.2</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>21.39</v>
+        <v>11.49</v>
       </c>
       <c r="O18" t="n">
-        <v>-6.04</v>
+        <v>-7.24</v>
       </c>
       <c r="P18" t="n">
-        <v>15.35</v>
+        <v>4.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>14.26</v>
+        <v>7.58</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5169587357607002</v>
+        <v>1.873073941631555</v>
       </c>
       <c r="S18" t="n">
-        <v>13.37</v>
+        <v>18.91</v>
       </c>
       <c r="T18" t="n">
-        <v>1133.84</v>
+        <v>2598</v>
       </c>
       <c r="U18" t="n">
-        <v>6878</v>
+        <v>16466</v>
       </c>
       <c r="V18" t="n">
-        <v>1.005029806259315</v>
+        <v>1.007181364260279</v>
       </c>
       <c r="W18" t="n">
-        <v>1.071798520349867</v>
+        <v>1.075427041076161</v>
       </c>
       <c r="X18" t="n">
-        <v>107.3599999999999</v>
+        <v>251.3450000000001</v>
       </c>
       <c r="Y18" t="n">
-        <v>100.6719061011375</v>
+        <v>235.394862069562</v>
       </c>
       <c r="Z18" t="n">
-        <v>223433709.2</v>
+        <v>232628142.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>0050.TW</t>
+          <t>00892.TW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>元大台灣50</t>
+          <t>富邦台灣半導體</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.907607131034982</v>
+        <v>1.989866443422833</v>
       </c>
       <c r="D19" t="n">
-        <v>5.907607131034982</v>
+        <v>1.870520335342985</v>
       </c>
       <c r="E19" t="n">
-        <v>114.8</v>
+        <v>42.98</v>
       </c>
       <c r="F19" t="n">
-        <v>78.01000000000001</v>
+        <v>50.07</v>
       </c>
       <c r="G19" t="n">
-        <v>1695</v>
+        <v>241</v>
       </c>
       <c r="H19" t="n">
-        <v>90.97</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="J19" t="n">
-        <v>13.46961651917404</v>
+        <v>15.85892116182573</v>
       </c>
       <c r="K19" t="n">
-        <v>79107287.25</v>
+        <v>4392869.4</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>13.94</v>
+        <v>12.37</v>
       </c>
       <c r="O19" t="n">
-        <v>-5.91</v>
+        <v>-7.43</v>
       </c>
       <c r="P19" t="n">
-        <v>8.029999999999999</v>
+        <v>4.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.04</v>
+        <v>18.86</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.1193461080798479</v>
       </c>
       <c r="S19" t="n">
-        <v>4.84625</v>
+        <v>4.937</v>
       </c>
       <c r="T19" t="n">
-        <v>3824.71</v>
+        <v>510.5</v>
       </c>
       <c r="U19" t="n">
-        <v>22831</v>
+        <v>3822</v>
       </c>
       <c r="V19" t="n">
-        <v>1.0295271618501</v>
+        <v>1.003209429888545</v>
       </c>
       <c r="W19" t="n">
-        <v>1.091204345016956</v>
+        <v>1.0541819329649</v>
       </c>
       <c r="X19" t="n">
-        <v>111.5075</v>
+        <v>42.84250000000001</v>
       </c>
       <c r="Y19" t="n">
-        <v>105.204859680261</v>
+        <v>40.7709510626104</v>
       </c>
       <c r="Z19" t="n">
-        <v>12208825938.4</v>
+        <v>205292465.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>0053.TW</t>
+          <t>006208.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>元大科技市值</t>
+          <t>富邦台50</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7.226450478997096</v>
+        <v>4.299549233732197</v>
       </c>
       <c r="D20" t="n">
-        <v>5.309744215166474</v>
+        <v>4.034735232910645</v>
       </c>
       <c r="E20" t="n">
-        <v>258.85</v>
+        <v>257.85</v>
       </c>
       <c r="F20" t="n">
-        <v>64.55</v>
+        <v>58.48</v>
       </c>
       <c r="G20" t="n">
-        <v>1190</v>
+        <v>895</v>
       </c>
       <c r="H20" t="n">
-        <v>89.16</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="J20" t="n">
-        <v>13.83697478991597</v>
+        <v>13.86703910614525</v>
       </c>
       <c r="K20" t="n">
-        <v>209285</v>
+        <v>2584439.25</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
         <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>11.49</v>
+        <v>11.21</v>
       </c>
       <c r="O20" t="n">
-        <v>-7.24</v>
+        <v>-6.25</v>
       </c>
       <c r="P20" t="n">
-        <v>4.25</v>
+        <v>4.960000000000001</v>
       </c>
       <c r="Q20" t="n">
-        <v>7.58</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="R20" t="n">
-        <v>1.916706263830622</v>
+        <v>0.264814000821552</v>
       </c>
       <c r="S20" t="n">
-        <v>18.91</v>
+        <v>28.764</v>
       </c>
       <c r="T20" t="n">
-        <v>2598</v>
+        <v>1745.92</v>
       </c>
       <c r="U20" t="n">
-        <v>16466</v>
+        <v>12411</v>
       </c>
       <c r="V20" t="n">
-        <v>1.031326261267991</v>
+        <v>1.009000195656427</v>
       </c>
       <c r="W20" t="n">
-        <v>1.101980179576345</v>
+        <v>1.068342840073464</v>
       </c>
       <c r="X20" t="n">
-        <v>250.9875000000001</v>
+        <v>255.55</v>
       </c>
       <c r="Y20" t="n">
-        <v>234.8953318738587</v>
+        <v>241.3551065520026</v>
       </c>
       <c r="Z20" t="n">
-        <v>233455779.6</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>00892.TW</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>富邦台灣半導體</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>2.051809130958175</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1.932044354238441</v>
-      </c>
-      <c r="E21" t="n">
-        <v>43.92</v>
-      </c>
-      <c r="F21" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="G21" t="n">
-        <v>241</v>
-      </c>
-      <c r="H21" t="n">
-        <v>75.09999999999999</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="J21" t="n">
-        <v>15.85892116182573</v>
-      </c>
-      <c r="K21" t="n">
-        <v>4288538.55</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="n">
-        <v>2</v>
-      </c>
-      <c r="N21" t="n">
-        <v>12.37</v>
-      </c>
-      <c r="O21" t="n">
-        <v>-7.43</v>
-      </c>
-      <c r="P21" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>18.86</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.1197647767197338</v>
-      </c>
-      <c r="S21" t="n">
-        <v>4.937</v>
-      </c>
-      <c r="T21" t="n">
-        <v>510.5</v>
-      </c>
-      <c r="U21" t="n">
-        <v>3822</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.02582069158813</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.078161419761171</v>
-      </c>
-      <c r="X21" t="n">
-        <v>42.8145</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>40.73601521535519</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>175857700.32</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>006208.TW</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>富邦台50</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>4.401217721613286</v>
-      </c>
-      <c r="D22" t="n">
-        <v>4.140112159270349</v>
-      </c>
-      <c r="E22" t="n">
-        <v>263.15</v>
-      </c>
-      <c r="F22" t="n">
-        <v>80.02</v>
-      </c>
-      <c r="G22" t="n">
-        <v>895</v>
-      </c>
-      <c r="H22" t="n">
-        <v>88.48999999999999</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="J22" t="n">
-        <v>13.86703910614525</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2308981.55</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="n">
-        <v>2</v>
-      </c>
-      <c r="N22" t="n">
-        <v>11.21</v>
-      </c>
-      <c r="O22" t="n">
-        <v>-6.25</v>
-      </c>
-      <c r="P22" t="n">
-        <v>4.960000000000001</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0.2611055623429364</v>
-      </c>
-      <c r="S22" t="n">
-        <v>28.764</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1745.92</v>
-      </c>
-      <c r="U22" t="n">
-        <v>12411</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.031414741215435</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.093045711667015</v>
-      </c>
-      <c r="X22" t="n">
-        <v>255.135</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>240.7493091928125</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>918836644.5999999</v>
+        <v>1874491629.3</v>
       </c>
     </row>
   </sheetData>

--- a/ETF動態清單.xlsx
+++ b/ETF動態清單.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z20"/>
+  <dimension ref="A1:Z21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,16 +567,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8178283126724888</v>
+        <v>0.8226273621830802</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6025702326289217</v>
+        <v>0.6092054975365877</v>
       </c>
       <c r="E2" t="n">
-        <v>31.06</v>
+        <v>31.19</v>
       </c>
       <c r="F2" t="n">
-        <v>62.85</v>
+        <v>51.26</v>
       </c>
       <c r="G2" t="n">
         <v>41</v>
@@ -591,7 +591,7 @@
         <v>8.439024390243903</v>
       </c>
       <c r="K2" t="n">
-        <v>158607058.15</v>
+        <v>155485622.95</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
@@ -610,7 +610,7 @@
         <v>386.28</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2152580800435671</v>
+        <v>0.2134218646464925</v>
       </c>
       <c r="S2" t="n">
         <v>1.67</v>
@@ -622,19 +622,19 @@
         <v>346</v>
       </c>
       <c r="V2" t="n">
-        <v>1.017076804689163</v>
+        <v>1.018415725200809</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1188199941258</v>
+        <v>1.118611559049808</v>
       </c>
       <c r="X2" t="n">
-        <v>30.53850000000001</v>
+        <v>30.62600000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>27.76139161176594</v>
+        <v>27.88277999424036</v>
       </c>
       <c r="Z2" t="n">
-        <v>7280002696.88</v>
+        <v>2553005393.89</v>
       </c>
     </row>
     <row r="3">
@@ -649,16 +649,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.263888617641034</v>
+        <v>1.281188389779975</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9586213872950113</v>
+        <v>0.967207717501581</v>
       </c>
       <c r="E3" t="n">
-        <v>38.69</v>
+        <v>39.03</v>
       </c>
       <c r="F3" t="n">
-        <v>42.3</v>
+        <v>38.11</v>
       </c>
       <c r="G3" t="n">
         <v>66</v>
@@ -673,7 +673,7 @@
         <v>10.33333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>9615802.199999999</v>
+        <v>10067253.05</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
         <v>159.78</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3052672303460227</v>
+        <v>0.3139806722783938</v>
       </c>
       <c r="S3" t="n">
         <v>0.78</v>
@@ -708,19 +708,19 @@
         <v>682</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9816059875681842</v>
+        <v>0.987663693300436</v>
       </c>
       <c r="W3" t="n">
-        <v>1.072798212046816</v>
+        <v>1.073700314966607</v>
       </c>
       <c r="X3" t="n">
-        <v>39.41500000000002</v>
+        <v>39.51750000000002</v>
       </c>
       <c r="Y3" t="n">
-        <v>36.06456420745004</v>
+        <v>36.35092535221418</v>
       </c>
       <c r="Z3" t="n">
-        <v>1094762877.02</v>
+        <v>561140788.98</v>
       </c>
     </row>
     <row r="4">
@@ -735,16 +735,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.577892619745611</v>
+        <v>2.592299025024439</v>
       </c>
       <c r="D4" t="n">
-        <v>2.408711736834672</v>
+        <v>2.425138464277724</v>
       </c>
       <c r="E4" t="n">
-        <v>86.65000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>54.32</v>
+        <v>43.67</v>
       </c>
       <c r="G4" t="n">
         <v>495</v>
@@ -759,9 +759,13 @@
         <v>12.29090909090909</v>
       </c>
       <c r="K4" t="n">
-        <v>8367567.35</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
+        <v>8628169.699999999</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="M4" t="n">
         <v>2</v>
       </c>
@@ -778,7 +782,7 @@
         <v>19.85</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1691808829109389</v>
+        <v>0.1671605607467153</v>
       </c>
       <c r="S4" t="n">
         <v>17.71</v>
@@ -790,19 +794,19 @@
         <v>6084</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9985594929415154</v>
+        <v>1.000430725053841</v>
       </c>
       <c r="W4" t="n">
-        <v>1.11801230416752</v>
+        <v>1.114787340763515</v>
       </c>
       <c r="X4" t="n">
-        <v>86.77500000000001</v>
+        <v>87.0625</v>
       </c>
       <c r="Y4" t="n">
-        <v>77.50361930454801</v>
+        <v>78.13149361773826</v>
       </c>
       <c r="Z4" t="n">
-        <v>1485440950</v>
+        <v>850455635.9</v>
       </c>
     </row>
     <row r="5">
@@ -817,16 +821,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12.58843047628005</v>
+        <v>12.7925005976131</v>
       </c>
       <c r="D5" t="n">
-        <v>3.115671208676509</v>
+        <v>3.135780238823334</v>
       </c>
       <c r="E5" t="n">
-        <v>113.65</v>
+        <v>115.4</v>
       </c>
       <c r="F5" t="n">
-        <v>60.5</v>
+        <v>52.12</v>
       </c>
       <c r="G5" t="n">
         <v>564</v>
@@ -841,7 +845,7 @@
         <v>11.9113475177305</v>
       </c>
       <c r="K5" t="n">
-        <v>5091143.8</v>
+        <v>4844550.1</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
@@ -860,7 +864,7 @@
         <v>18.35</v>
       </c>
       <c r="R5" t="n">
-        <v>9.472759267603543</v>
+        <v>9.656720358789762</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -872,19 +876,19 @@
         <v>6718</v>
       </c>
       <c r="V5" t="n">
-        <v>1.016683812676119</v>
+        <v>1.026895953371448</v>
       </c>
       <c r="W5" t="n">
-        <v>1.142990562995831</v>
+        <v>1.147856384611062</v>
       </c>
       <c r="X5" t="n">
-        <v>111.7850000000001</v>
+        <v>112.3775000000001</v>
       </c>
       <c r="Y5" t="n">
-        <v>99.43214203109264</v>
+        <v>100.5352250918585</v>
       </c>
       <c r="Z5" t="n">
-        <v>996693679.8000001</v>
+        <v>391196768</v>
       </c>
     </row>
     <row r="6">
@@ -899,16 +903,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.80408088868726</v>
+        <v>17.01567793552954</v>
       </c>
       <c r="D6" t="n">
-        <v>3.552635722543141</v>
+        <v>3.575007246018012</v>
       </c>
       <c r="E6" t="n">
-        <v>39.3</v>
+        <v>39.78</v>
       </c>
       <c r="F6" t="n">
-        <v>59.04</v>
+        <v>49.01</v>
       </c>
       <c r="G6" t="n">
         <v>644</v>
@@ -923,9 +927,13 @@
         <v>12.68167701863354</v>
       </c>
       <c r="K6" t="n">
-        <v>163212043.3</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
+        <v>155704987.25</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="M6" t="n">
         <v>2</v>
       </c>
@@ -942,7 +950,7 @@
         <v>15.49</v>
       </c>
       <c r="R6" t="n">
-        <v>13.25144516614412</v>
+        <v>13.44067068951153</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -954,19 +962,19 @@
         <v>8167</v>
       </c>
       <c r="V6" t="n">
-        <v>1.015950158984567</v>
+        <v>1.023332390090809</v>
       </c>
       <c r="W6" t="n">
-        <v>1.138864211543347</v>
+        <v>1.140976649223057</v>
       </c>
       <c r="X6" t="n">
-        <v>38.68299999999999</v>
+        <v>38.87299999999998</v>
       </c>
       <c r="Y6" t="n">
-        <v>34.50806479092189</v>
+        <v>34.86486776665239</v>
       </c>
       <c r="Z6" t="n">
-        <v>12964066631.7</v>
+        <v>4855432790.52</v>
       </c>
     </row>
     <row r="7">
@@ -981,16 +989,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.908831033317239</v>
+        <v>1.914571005583118</v>
       </c>
       <c r="D7" t="n">
-        <v>1.801157630571303</v>
+        <v>1.814194956636023</v>
       </c>
       <c r="E7" t="n">
-        <v>42.97</v>
+        <v>43.09</v>
       </c>
       <c r="F7" t="n">
-        <v>50.52</v>
+        <v>39.8</v>
       </c>
       <c r="G7" t="n">
         <v>239</v>
@@ -1005,9 +1013,13 @@
         <v>10.78242677824268</v>
       </c>
       <c r="K7" t="n">
-        <v>2555476.35</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
+        <v>2767358</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="M7" t="n">
         <v>2</v>
       </c>
@@ -1024,7 +1036,7 @@
         <v>37.53</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1076734027459367</v>
+        <v>0.1003760489470951</v>
       </c>
       <c r="S7" t="n">
         <v>4.850000000000001</v>
@@ -1036,19 +1048,19 @@
         <v>2577</v>
       </c>
       <c r="V7" t="n">
-        <v>1.000523895453752</v>
+        <v>1.000859405848605</v>
       </c>
       <c r="W7" t="n">
-        <v>1.072710646257449</v>
+        <v>1.069032946920937</v>
       </c>
       <c r="X7" t="n">
-        <v>42.9475</v>
+        <v>43.053</v>
       </c>
       <c r="Y7" t="n">
-        <v>40.05740052074327</v>
+        <v>40.30745743067057</v>
       </c>
       <c r="Z7" t="n">
-        <v>483921823.41</v>
+        <v>209904317</v>
       </c>
     </row>
     <row r="8">
@@ -1063,16 +1075,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11.40875170209796</v>
+        <v>11.57521995665375</v>
       </c>
       <c r="D8" t="n">
-        <v>2.939038886552234</v>
+        <v>2.958216106611288</v>
       </c>
       <c r="E8" t="n">
-        <v>13.02</v>
+        <v>13.2</v>
       </c>
       <c r="F8" t="n">
-        <v>60.7</v>
+        <v>51.89</v>
       </c>
       <c r="G8" t="n">
         <v>514</v>
@@ -1087,7 +1099,7 @@
         <v>12.18093385214008</v>
       </c>
       <c r="K8" t="n">
-        <v>214323107.55</v>
+        <v>202377761.25</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
@@ -1106,7 +1118,7 @@
         <v>18.65</v>
       </c>
       <c r="R8" t="n">
-        <v>8.469712815545726</v>
+        <v>8.617003850042458</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1118,19 +1130,19 @@
         <v>6261</v>
       </c>
       <c r="V8" t="n">
-        <v>1.018062397372742</v>
+        <v>1.026678074200824</v>
       </c>
       <c r="W8" t="n">
-        <v>1.146349560207693</v>
+        <v>1.149366777042334</v>
       </c>
       <c r="X8" t="n">
-        <v>12.789</v>
+        <v>12.857</v>
       </c>
       <c r="Y8" t="n">
-        <v>11.35779211852366</v>
+        <v>11.48458461098689</v>
       </c>
       <c r="Z8" t="n">
-        <v>6626951017.26</v>
+        <v>2072410375.2</v>
       </c>
     </row>
     <row r="9">
@@ -1145,16 +1157,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5.055651058181655</v>
+        <v>5.230381716646164</v>
       </c>
       <c r="D9" t="n">
-        <v>2.792629136424982</v>
+        <v>2.811053896390728</v>
       </c>
       <c r="E9" t="n">
-        <v>75.2</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>90.45999999999999</v>
+        <v>91.09</v>
       </c>
       <c r="G9" t="n">
         <v>425</v>
@@ -1169,7 +1181,7 @@
         <v>17.11294117647059</v>
       </c>
       <c r="K9" t="n">
-        <v>4356497.3</v>
+        <v>3810471</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
@@ -1188,7 +1200,7 @@
         <v>14.59</v>
       </c>
       <c r="R9" t="n">
-        <v>2.263021921756673</v>
+        <v>2.419327820255436</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1200,19 +1212,19 @@
         <v>7273</v>
       </c>
       <c r="V9" t="n">
-        <v>1.099495577162074</v>
+        <v>1.126104826683157</v>
       </c>
       <c r="W9" t="n">
-        <v>1.230279690708689</v>
+        <v>1.279125834249105</v>
       </c>
       <c r="X9" t="n">
-        <v>68.39499999999995</v>
+        <v>68.73249999999994</v>
       </c>
       <c r="Y9" t="n">
-        <v>61.12431227461936</v>
+        <v>60.51007487112221</v>
       </c>
       <c r="Z9" t="n">
-        <v>160651264</v>
+        <v>276836889.6</v>
       </c>
     </row>
     <row r="10">
@@ -1227,16 +1239,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11.98011030014668</v>
+        <v>12.16553299238016</v>
       </c>
       <c r="D10" t="n">
-        <v>3.049652145850465</v>
+        <v>3.06943213416639</v>
       </c>
       <c r="E10" t="n">
-        <v>344.25</v>
+        <v>349.3</v>
       </c>
       <c r="F10" t="n">
-        <v>60.22</v>
+        <v>51.4</v>
       </c>
       <c r="G10" t="n">
         <v>564</v>
@@ -1251,7 +1263,7 @@
         <v>12.38297872340426</v>
       </c>
       <c r="K10" t="n">
-        <v>1029749.6</v>
+        <v>966418.25</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
@@ -1270,7 +1282,7 @@
         <v>16.61</v>
       </c>
       <c r="R10" t="n">
-        <v>8.930458154296218</v>
+        <v>9.096100858213767</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1282,19 +1294,19 @@
         <v>6984</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01625116237878</v>
+        <v>1.025769033110637</v>
       </c>
       <c r="W10" t="n">
-        <v>1.142775151870361</v>
+        <v>1.146757688777605</v>
       </c>
       <c r="X10" t="n">
-        <v>338.7450000000002</v>
+        <v>340.5250000000002</v>
       </c>
       <c r="Y10" t="n">
-        <v>301.2403616201944</v>
+        <v>304.5979141176189</v>
       </c>
       <c r="Z10" t="n">
-        <v>671789072.25</v>
+        <v>240269847.3</v>
       </c>
     </row>
     <row r="11">
@@ -1309,16 +1321,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.575400246909418</v>
+        <v>1.593256703683568</v>
       </c>
       <c r="D11" t="n">
-        <v>1.210963069798623</v>
+        <v>1.220856645370793</v>
       </c>
       <c r="E11" t="n">
-        <v>60</v>
+        <v>60.5</v>
       </c>
       <c r="F11" t="n">
-        <v>50.45</v>
+        <v>41.47</v>
       </c>
       <c r="G11" t="n">
         <v>136</v>
@@ -1333,9 +1345,13 @@
         <v>12.30882352941176</v>
       </c>
       <c r="K11" t="n">
-        <v>11933751.55</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
+        <v>11646996.75</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="M11" t="n">
         <v>2</v>
       </c>
@@ -1352,7 +1368,7 @@
         <v>43.74</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3644371771107955</v>
+        <v>0.3724000583127749</v>
       </c>
       <c r="S11" t="n">
         <v>4.98</v>
@@ -1364,19 +1380,19 @@
         <v>1674</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9928843289756742</v>
+        <v>0.9995456610631529</v>
       </c>
       <c r="W11" t="n">
-        <v>1.069045358062654</v>
+        <v>1.074416686286148</v>
       </c>
       <c r="X11" t="n">
-        <v>60.43000000000001</v>
+        <v>60.52750000000001</v>
       </c>
       <c r="Y11" t="n">
-        <v>56.12484030493642</v>
+        <v>56.30962434986522</v>
       </c>
       <c r="Z11" t="n">
-        <v>1220565840</v>
+        <v>443203700.5</v>
       </c>
     </row>
     <row r="12">
@@ -1391,16 +1407,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.229647402468231</v>
+        <v>2.236450828125559</v>
       </c>
       <c r="D12" t="n">
-        <v>1.853358795831452</v>
+        <v>1.866789945099285</v>
       </c>
       <c r="E12" t="n">
-        <v>50.4</v>
+        <v>50.55</v>
       </c>
       <c r="F12" t="n">
-        <v>59.66</v>
+        <v>48.88</v>
       </c>
       <c r="G12" t="n">
         <v>243</v>
@@ -1415,9 +1431,13 @@
         <v>15.32921810699589</v>
       </c>
       <c r="K12" t="n">
-        <v>1185748.2</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
+        <v>1126935.5</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="M12" t="n">
         <v>2</v>
       </c>
@@ -1434,7 +1454,7 @@
         <v>22.58</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3762886066367783</v>
+        <v>0.3696608830262744</v>
       </c>
       <c r="S12" t="n">
         <v>7.549999999999999</v>
@@ -1446,687 +1466,793 @@
         <v>3725</v>
       </c>
       <c r="V12" t="n">
-        <v>1.016262211781786</v>
+        <v>1.015621075895324</v>
       </c>
       <c r="W12" t="n">
-        <v>1.109941249215989</v>
+        <v>1.104971362785325</v>
       </c>
       <c r="X12" t="n">
-        <v>49.59349999999999</v>
+        <v>49.77249999999999</v>
       </c>
       <c r="Y12" t="n">
-        <v>45.4078087787081</v>
+        <v>45.74779193605299</v>
       </c>
       <c r="Z12" t="n">
-        <v>103466462.4</v>
+        <v>19924990.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>0057.TW</t>
+          <t>00901.TW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>富邦摩台</t>
+          <t>永豐智能車供應鏈</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6.515041012330766</v>
+        <v>1.934729166447378</v>
       </c>
       <c r="D13" t="n">
-        <v>5.122588639247726</v>
+        <v>1.831029724329293</v>
       </c>
       <c r="E13" t="n">
-        <v>338.55</v>
+        <v>48.08</v>
       </c>
       <c r="F13" t="n">
-        <v>65.42</v>
+        <v>40.56</v>
       </c>
       <c r="G13" t="n">
-        <v>1245</v>
+        <v>276</v>
       </c>
       <c r="H13" t="n">
-        <v>93.33</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>2.64</v>
+        <v>2.79</v>
       </c>
       <c r="J13" t="n">
-        <v>12.02409638554217</v>
+        <v>13.22463768115942</v>
       </c>
       <c r="K13" t="n">
-        <v>28350.65</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
+        <v>231867.45</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="M13" t="n">
         <v>2</v>
       </c>
       <c r="N13" t="n">
-        <v>14.45</v>
+        <v>15.18</v>
       </c>
       <c r="O13" t="n">
-        <v>-6.48</v>
+        <v>-7.3</v>
       </c>
       <c r="P13" t="n">
-        <v>7.969999999999999</v>
+        <v>7.88</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.970000000000001</v>
+        <v>24.17</v>
       </c>
       <c r="R13" t="n">
-        <v>1.39245237308304</v>
+        <v>0.103699442118085</v>
       </c>
       <c r="S13" t="n">
-        <v>1.685</v>
+        <v>4.671</v>
       </c>
       <c r="T13" t="n">
-        <v>3287.55</v>
+        <v>771.28</v>
       </c>
       <c r="U13" t="n">
-        <v>14970</v>
+        <v>3650</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01797352456983</v>
+        <v>1.001896267894726</v>
       </c>
       <c r="W13" t="n">
-        <v>1.074291818640501</v>
+        <v>1.070431385158977</v>
       </c>
       <c r="X13" t="n">
-        <v>332.5725</v>
+        <v>47.989</v>
       </c>
       <c r="Y13" t="n">
-        <v>315.1378369691296</v>
+        <v>44.91647074871533</v>
       </c>
       <c r="Z13" t="n">
-        <v>27209263.5</v>
+        <v>1065645.12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>00881.TW</t>
+          <t>0057.TW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>國泰台灣科技龍頭</t>
+          <t>富邦摩台</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.105792978231118</v>
+        <v>6.452754763888863</v>
       </c>
       <c r="D14" t="n">
-        <v>1.92193057511513</v>
+        <v>5.15296572257841</v>
       </c>
       <c r="E14" t="n">
-        <v>52</v>
+        <v>335.8</v>
       </c>
       <c r="F14" t="n">
-        <v>49.2</v>
+        <v>48.76</v>
       </c>
       <c r="G14" t="n">
-        <v>384</v>
+        <v>1245</v>
       </c>
       <c r="H14" t="n">
-        <v>89.58</v>
+        <v>93.33</v>
       </c>
       <c r="I14" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="J14" t="n">
-        <v>15.328125</v>
+        <v>12.02409638554217</v>
       </c>
       <c r="K14" t="n">
-        <v>17217653.85</v>
+        <v>29839.15</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>10.9</v>
+        <v>14.45</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.28</v>
+        <v>-6.48</v>
       </c>
       <c r="P14" t="n">
-        <v>6.62</v>
+        <v>7.969999999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>15.81</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1838624031159886</v>
+        <v>1.299789041310452</v>
       </c>
       <c r="S14" t="n">
-        <v>12.5</v>
+        <v>1.685</v>
       </c>
       <c r="T14" t="n">
-        <v>966.91</v>
+        <v>3287.55</v>
       </c>
       <c r="U14" t="n">
-        <v>5886</v>
+        <v>14970</v>
       </c>
       <c r="V14" t="n">
-        <v>1.000654273948351</v>
+        <v>1.007500750075007</v>
       </c>
       <c r="W14" t="n">
-        <v>1.065947049982376</v>
+        <v>1.060584537199488</v>
       </c>
       <c r="X14" t="n">
-        <v>51.96599999999999</v>
+        <v>333.3000000000001</v>
       </c>
       <c r="Y14" t="n">
-        <v>48.78291093432809</v>
+        <v>316.6178538550942</v>
       </c>
       <c r="Z14" t="n">
-        <v>1730199796</v>
+        <v>15541831.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0052.TW</t>
+          <t>00881.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>富邦科技</t>
+          <t>國泰台灣科技龍頭</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8.624188483881255</v>
+        <v>2.10929767948073</v>
       </c>
       <c r="D15" t="n">
-        <v>5.220452124095178</v>
+        <v>1.935830656188242</v>
       </c>
       <c r="E15" t="n">
-        <v>65.40000000000001</v>
+        <v>52.1</v>
       </c>
       <c r="F15" t="n">
-        <v>53.42</v>
+        <v>38.09</v>
       </c>
       <c r="G15" t="n">
-        <v>1111</v>
+        <v>384</v>
       </c>
       <c r="H15" t="n">
-        <v>88.20999999999999</v>
+        <v>89.58</v>
       </c>
       <c r="I15" t="n">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="J15" t="n">
-        <v>14.18091809180918</v>
+        <v>15.328125</v>
       </c>
       <c r="K15" t="n">
-        <v>17001249.3</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
+        <v>16339519.45</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="M15" t="n">
         <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>12.7</v>
+        <v>10.9</v>
       </c>
       <c r="O15" t="n">
-        <v>-14.18</v>
+        <v>-4.28</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.48</v>
+        <v>6.62</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.050000000000001</v>
+        <v>15.81</v>
       </c>
       <c r="R15" t="n">
-        <v>3.403736359786078</v>
+        <v>0.1734670232924884</v>
       </c>
       <c r="S15" t="n">
-        <v>2.232857285714286</v>
+        <v>12.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2723.42</v>
+        <v>966.91</v>
       </c>
       <c r="U15" t="n">
-        <v>15755</v>
+        <v>5886</v>
       </c>
       <c r="V15" t="n">
-        <v>1.006579706799029</v>
+        <v>1.00051850287097</v>
       </c>
       <c r="W15" t="n">
-        <v>1.070868465041976</v>
+        <v>1.062704393760517</v>
       </c>
       <c r="X15" t="n">
-        <v>64.97250000000007</v>
+        <v>52.07299999999999</v>
       </c>
       <c r="Y15" t="n">
-        <v>61.07192632424415</v>
+        <v>49.02586298306097</v>
       </c>
       <c r="Z15" t="n">
-        <v>2252448724.8</v>
+        <v>456972382.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>00735.TW</t>
+          <t>0052.TW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>國泰臺韓科技</t>
+          <t>富邦科技</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3.090378322319643</v>
+        <v>8.665215849489966</v>
       </c>
       <c r="D16" t="n">
-        <v>2.667056236535193</v>
+        <v>5.251488262372824</v>
       </c>
       <c r="E16" t="n">
-        <v>103.2</v>
+        <v>65.7</v>
       </c>
       <c r="F16" t="n">
-        <v>36.84</v>
+        <v>42.61</v>
       </c>
       <c r="G16" t="n">
-        <v>498</v>
+        <v>1111</v>
       </c>
       <c r="H16" t="n">
-        <v>86.55</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="J16" t="n">
-        <v>13.81124497991968</v>
+        <v>14.18091809180918</v>
       </c>
       <c r="K16" t="n">
-        <v>1542879.5</v>
+        <v>16949460.4</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>21.39</v>
+        <v>12.7</v>
       </c>
       <c r="O16" t="n">
-        <v>-6.04</v>
+        <v>-14.18</v>
       </c>
       <c r="P16" t="n">
-        <v>15.35</v>
+        <v>-1.48</v>
       </c>
       <c r="Q16" t="n">
-        <v>14.26</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4233220857844504</v>
+        <v>3.413727587117142</v>
       </c>
       <c r="S16" t="n">
-        <v>13.37</v>
+        <v>2.232857285714286</v>
       </c>
       <c r="T16" t="n">
-        <v>1133.84</v>
+        <v>2723.42</v>
       </c>
       <c r="U16" t="n">
-        <v>6878</v>
+        <v>15755</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9629560511337139</v>
+        <v>1.0087517273146</v>
       </c>
       <c r="W16" t="n">
-        <v>1.029526536450664</v>
+        <v>1.070346113680226</v>
       </c>
       <c r="X16" t="n">
-        <v>107.1699999999999</v>
+        <v>65.13000000000008</v>
       </c>
       <c r="Y16" t="n">
-        <v>100.2402525298535</v>
+        <v>61.38201387409192</v>
       </c>
       <c r="Z16" t="n">
-        <v>485501613.6</v>
+        <v>959480237.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>0050.TW</t>
+          <t>00735.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>元大台灣50</t>
+          <t>國泰臺韓科技</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5.767414424994361</v>
+        <v>3.114123809615423</v>
       </c>
       <c r="D17" t="n">
-        <v>5.767414424994361</v>
+        <v>2.684821291236675</v>
       </c>
       <c r="E17" t="n">
-        <v>112.4</v>
+        <v>103.9</v>
       </c>
       <c r="F17" t="n">
-        <v>56.77</v>
+        <v>29.75</v>
       </c>
       <c r="G17" t="n">
-        <v>1695</v>
+        <v>498</v>
       </c>
       <c r="H17" t="n">
-        <v>90.97</v>
+        <v>86.55</v>
       </c>
       <c r="I17" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="J17" t="n">
-        <v>13.46961651917404</v>
+        <v>13.81124497991968</v>
       </c>
       <c r="K17" t="n">
-        <v>88922563.2</v>
-      </c>
-      <c r="L17" t="inlineStr"/>
+        <v>1520740.05</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="M17" t="n">
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>13.94</v>
+        <v>21.39</v>
       </c>
       <c r="O17" t="n">
-        <v>-5.91</v>
+        <v>-6.04</v>
       </c>
       <c r="P17" t="n">
-        <v>8.029999999999999</v>
+        <v>15.35</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.04</v>
+        <v>14.26</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.4293025183787478</v>
       </c>
       <c r="S17" t="n">
-        <v>4.84625</v>
+        <v>13.37</v>
       </c>
       <c r="T17" t="n">
-        <v>3824.71</v>
+        <v>1133.84</v>
       </c>
       <c r="U17" t="n">
-        <v>22831</v>
+        <v>6878</v>
       </c>
       <c r="V17" t="n">
-        <v>1.006537118294976</v>
+        <v>0.9696460651874675</v>
       </c>
       <c r="W17" t="n">
-        <v>1.065889322060972</v>
+        <v>1.03701259685019</v>
       </c>
       <c r="X17" t="n">
-        <v>111.67</v>
+        <v>107.1524999999999</v>
       </c>
       <c r="Y17" t="n">
-        <v>105.4518491494658</v>
+        <v>100.1916469631947</v>
       </c>
       <c r="Z17" t="n">
-        <v>27208751850.4</v>
+        <v>121035084.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>0053.TW</t>
+          <t>0050.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>元大科技市值</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7.054393140488644</v>
+        <v>5.801193137925813</v>
       </c>
       <c r="D18" t="n">
-        <v>5.181319198857089</v>
+        <v>5.801193137925813</v>
       </c>
       <c r="E18" t="n">
-        <v>253.15</v>
+        <v>113</v>
       </c>
       <c r="F18" t="n">
-        <v>45.94</v>
+        <v>46.69</v>
       </c>
       <c r="G18" t="n">
-        <v>1190</v>
+        <v>1695</v>
       </c>
       <c r="H18" t="n">
-        <v>89.16</v>
+        <v>90.97</v>
       </c>
       <c r="I18" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="J18" t="n">
-        <v>13.83697478991597</v>
+        <v>13.46961651917404</v>
       </c>
       <c r="K18" t="n">
-        <v>248461.2</v>
+        <v>87027579.3</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>11.49</v>
+        <v>13.94</v>
       </c>
       <c r="O18" t="n">
-        <v>-7.24</v>
+        <v>-5.91</v>
       </c>
       <c r="P18" t="n">
-        <v>4.25</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.58</v>
+        <v>6.04</v>
       </c>
       <c r="R18" t="n">
-        <v>1.873073941631555</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>18.91</v>
+        <v>4.84625</v>
       </c>
       <c r="T18" t="n">
-        <v>2598</v>
+        <v>3824.71</v>
       </c>
       <c r="U18" t="n">
-        <v>16466</v>
+        <v>22831</v>
       </c>
       <c r="V18" t="n">
-        <v>1.007181364260279</v>
+        <v>1.00951445035065</v>
       </c>
       <c r="W18" t="n">
-        <v>1.075427041076161</v>
+        <v>1.066343641870528</v>
       </c>
       <c r="X18" t="n">
-        <v>251.3450000000001</v>
+        <v>111.935</v>
       </c>
       <c r="Y18" t="n">
-        <v>235.394862069562</v>
+        <v>105.9695913802993</v>
       </c>
       <c r="Z18" t="n">
-        <v>232628142.1</v>
+        <v>7244389433</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>00892.TW</t>
+          <t>0053.TW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>富邦台灣半導體</t>
+          <t>元大科技市值</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.989866443422833</v>
+        <v>7.049905875996625</v>
       </c>
       <c r="D19" t="n">
-        <v>1.870520335342985</v>
+        <v>5.212039339800091</v>
       </c>
       <c r="E19" t="n">
-        <v>42.98</v>
+        <v>253.05</v>
       </c>
       <c r="F19" t="n">
-        <v>50.07</v>
+        <v>33.35</v>
       </c>
       <c r="G19" t="n">
-        <v>241</v>
+        <v>1190</v>
       </c>
       <c r="H19" t="n">
-        <v>75.09999999999999</v>
+        <v>89.16</v>
       </c>
       <c r="I19" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="J19" t="n">
-        <v>15.85892116182573</v>
+        <v>13.83697478991597</v>
       </c>
       <c r="K19" t="n">
-        <v>4392869.4</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
+        <v>254820.35</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="M19" t="n">
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>12.37</v>
+        <v>11.49</v>
       </c>
       <c r="O19" t="n">
-        <v>-7.43</v>
+        <v>-7.24</v>
       </c>
       <c r="P19" t="n">
-        <v>4.94</v>
+        <v>4.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>18.86</v>
+        <v>7.58</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1193461080798479</v>
+        <v>1.837866536196534</v>
       </c>
       <c r="S19" t="n">
-        <v>4.937</v>
+        <v>18.91</v>
       </c>
       <c r="T19" t="n">
-        <v>510.5</v>
+        <v>2598</v>
       </c>
       <c r="U19" t="n">
-        <v>3822</v>
+        <v>16466</v>
       </c>
       <c r="V19" t="n">
-        <v>1.003209429888545</v>
+        <v>1.004405810907359</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0541819329649</v>
+        <v>1.06915283145858</v>
       </c>
       <c r="X19" t="n">
-        <v>42.84250000000001</v>
+        <v>251.9400000000001</v>
       </c>
       <c r="Y19" t="n">
-        <v>40.7709510626104</v>
+        <v>236.682719770549</v>
       </c>
       <c r="Z19" t="n">
-        <v>205292465.7</v>
+        <v>132700938.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>006208.TW</t>
+          <t>00892.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>富邦台50</t>
+          <t>富邦台灣半導體</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4.299549233732197</v>
+        <v>1.988971647181115</v>
       </c>
       <c r="D20" t="n">
-        <v>4.034735232910645</v>
+        <v>1.884076186128367</v>
       </c>
       <c r="E20" t="n">
-        <v>257.85</v>
+        <v>42.99</v>
       </c>
       <c r="F20" t="n">
-        <v>58.48</v>
+        <v>43.21</v>
       </c>
       <c r="G20" t="n">
-        <v>895</v>
+        <v>241</v>
       </c>
       <c r="H20" t="n">
-        <v>88.48999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="J20" t="n">
-        <v>13.86703910614525</v>
+        <v>15.85892116182573</v>
       </c>
       <c r="K20" t="n">
-        <v>2584439.25</v>
-      </c>
-      <c r="L20" t="inlineStr"/>
+        <v>4254290.15</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="M20" t="n">
         <v>2</v>
       </c>
       <c r="N20" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-7.43</v>
+      </c>
+      <c r="P20" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.1048954610527479</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4.937</v>
+      </c>
+      <c r="T20" t="n">
+        <v>510.5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3822</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.001595936768286</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.049644147510152</v>
+      </c>
+      <c r="X20" t="n">
+        <v>42.92150000000001</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>40.95673767340679</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>130107472.41</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>006208.TW</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>富邦台50</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>4.314323152396278</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4.059525979781002</v>
+      </c>
+      <c r="E21" t="n">
+        <v>258.7</v>
+      </c>
+      <c r="F21" t="n">
+        <v>46.84</v>
+      </c>
+      <c r="G21" t="n">
+        <v>895</v>
+      </c>
+      <c r="H21" t="n">
+        <v>88.48999999999999</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="J21" t="n">
+        <v>13.86703910614525</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2515871.7</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>2</v>
+      </c>
+      <c r="N21" t="n">
         <v>11.21</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O21" t="n">
         <v>-6.25</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P21" t="n">
         <v>4.960000000000001</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q21" t="n">
         <v>8.949999999999999</v>
       </c>
-      <c r="R20" t="n">
-        <v>0.264814000821552</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="R21" t="n">
+        <v>0.2547971726152758</v>
+      </c>
+      <c r="S21" t="n">
         <v>28.764</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T21" t="n">
         <v>1745.92</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
         <v>12411</v>
       </c>
-      <c r="V20" t="n">
-        <v>1.009000195656427</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.068342840073464</v>
-      </c>
-      <c r="X20" t="n">
-        <v>255.55</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>241.3551065520026</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1874491629.3</v>
+      <c r="V21" t="n">
+        <v>1.009836833476462</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.066302048625593</v>
+      </c>
+      <c r="X21" t="n">
+        <v>256.1799999999999</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>242.6141826637684</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>394450496.7</v>
       </c>
     </row>
   </sheetData>

--- a/ETF動態清單.xlsx
+++ b/ETF動態清單.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z21"/>
+  <dimension ref="A1:Z30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,16 +567,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8226273621830802</v>
+        <v>0.7205039476765183</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6092054975365877</v>
+        <v>0.5497818013755811</v>
       </c>
       <c r="E2" t="n">
-        <v>31.19</v>
+        <v>29.4</v>
       </c>
       <c r="F2" t="n">
-        <v>51.26</v>
+        <v>34.18</v>
       </c>
       <c r="G2" t="n">
         <v>41</v>
@@ -591,9 +591,13 @@
         <v>8.439024390243903</v>
       </c>
       <c r="K2" t="n">
-        <v>155485622.95</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
+        <v>168651975.4</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="M2" t="n">
         <v>2</v>
       </c>
@@ -610,7 +614,7 @@
         <v>386.28</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2134218646464925</v>
+        <v>0.1707221463009372</v>
       </c>
       <c r="S2" t="n">
         <v>1.67</v>
@@ -622,902 +626,918 @@
         <v>346</v>
       </c>
       <c r="V2" t="n">
-        <v>1.018415725200809</v>
+        <v>0.9598432908912828</v>
       </c>
       <c r="W2" t="n">
-        <v>1.118611559049808</v>
+        <v>1.053983089469733</v>
       </c>
       <c r="X2" t="n">
-        <v>30.62600000000001</v>
+        <v>30.63000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>27.88277999424036</v>
+        <v>27.89418567881518</v>
       </c>
       <c r="Z2" t="n">
-        <v>2553005393.89</v>
+        <v>11550054600</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>00947.TW</t>
+          <t>00992A.TW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>台新臺灣IC設計</t>
+          <t>主動群益科技創新</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.281188389779975</v>
+        <v>0.2231453995819146</v>
       </c>
       <c r="D3" t="n">
-        <v>0.967207717501581</v>
+        <v>0.2054871606186133</v>
       </c>
       <c r="E3" t="n">
-        <v>39.03</v>
+        <v>18.28</v>
       </c>
       <c r="F3" t="n">
-        <v>38.11</v>
+        <v>43.48</v>
       </c>
       <c r="G3" t="n">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="H3" t="n">
-        <v>96.97</v>
+        <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>7.5</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>10.33333333333333</v>
+        <v>10.27272727272727</v>
       </c>
       <c r="K3" t="n">
-        <v>10067253.05</v>
+        <v>48642233.35</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>18.77</v>
+        <v>15.18</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.73</v>
+        <v>2.64</v>
       </c>
       <c r="P3" t="n">
-        <v>18.04</v>
+        <v>17.82</v>
       </c>
       <c r="Q3" t="n">
-        <v>159.78</v>
+        <v>317.42</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3139806722783938</v>
+        <v>0.01765823896330132</v>
       </c>
       <c r="S3" t="n">
-        <v>0.78</v>
+        <v>0.47</v>
       </c>
       <c r="T3" t="n">
-        <v>495.22</v>
+        <v>277.02</v>
       </c>
       <c r="U3" t="n">
-        <v>682</v>
+        <v>339</v>
       </c>
       <c r="V3" t="n">
-        <v>0.987663693300436</v>
+        <v>0.9648219987860562</v>
       </c>
       <c r="W3" t="n">
-        <v>1.073700314966607</v>
+        <v>1.066380287693166</v>
       </c>
       <c r="X3" t="n">
-        <v>39.51750000000002</v>
+        <v>18.94649999999999</v>
       </c>
       <c r="Y3" t="n">
-        <v>36.35092535221418</v>
+        <v>17.14210231656099</v>
       </c>
       <c r="Z3" t="n">
-        <v>561140788.98</v>
+        <v>2993496240</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>00830.TW</t>
+          <t>00947.TW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>國泰費城半導體</t>
+          <t>台新臺灣IC設計</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.592299025024439</v>
+        <v>1.181887251638371</v>
       </c>
       <c r="D4" t="n">
-        <v>2.425138464277724</v>
+        <v>0.895268271485099</v>
       </c>
       <c r="E4" t="n">
-        <v>87.09999999999999</v>
+        <v>37.34</v>
       </c>
       <c r="F4" t="n">
-        <v>43.67</v>
+        <v>29.6</v>
       </c>
       <c r="G4" t="n">
-        <v>495</v>
+        <v>66</v>
       </c>
       <c r="H4" t="n">
-        <v>97.17</v>
+        <v>96.97</v>
       </c>
       <c r="I4" t="n">
-        <v>3.93</v>
+        <v>7.5</v>
       </c>
       <c r="J4" t="n">
-        <v>12.29090909090909</v>
+        <v>10.33333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>8628169.699999999</v>
+        <v>11811150.9</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>13.29</v>
+        <v>18.77</v>
       </c>
       <c r="O4" t="n">
-        <v>-12.33</v>
+        <v>-0.73</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9599999999999991</v>
+        <v>18.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>19.85</v>
+        <v>159.78</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1671605607467153</v>
+        <v>0.2866189801532717</v>
       </c>
       <c r="S4" t="n">
-        <v>17.71</v>
+        <v>0.78</v>
       </c>
       <c r="T4" t="n">
-        <v>1946.3</v>
+        <v>495.22</v>
       </c>
       <c r="U4" t="n">
-        <v>6084</v>
+        <v>682</v>
       </c>
       <c r="V4" t="n">
-        <v>1.000430725053841</v>
+        <v>0.944049756023563</v>
       </c>
       <c r="W4" t="n">
-        <v>1.114787340763515</v>
+        <v>1.022931570044068</v>
       </c>
       <c r="X4" t="n">
-        <v>87.0625</v>
+        <v>39.55300000000002</v>
       </c>
       <c r="Y4" t="n">
-        <v>78.13149361773826</v>
+        <v>36.50293049259531</v>
       </c>
       <c r="Z4" t="n">
-        <v>850455635.9</v>
+        <v>1445916820</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>00663L.TW</t>
+          <t>00980A.TW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>國泰臺灣加權正2</t>
+          <t>主動野村臺灣優選</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12.7925005976131</v>
+        <v>0.6137872465393484</v>
       </c>
       <c r="D5" t="n">
-        <v>3.135780238823334</v>
+        <v>0.592590124245038</v>
       </c>
       <c r="E5" t="n">
-        <v>115.4</v>
+        <v>24.5</v>
       </c>
       <c r="F5" t="n">
-        <v>52.12</v>
+        <v>37.91</v>
       </c>
       <c r="G5" t="n">
-        <v>564</v>
+        <v>40</v>
       </c>
       <c r="H5" t="n">
-        <v>89.89</v>
+        <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>3.76</v>
+        <v>7.02</v>
       </c>
       <c r="J5" t="n">
-        <v>11.9113475177305</v>
+        <v>9.824999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>4844550.1</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
+        <v>8529992.25</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="M5" t="n">
         <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>15.99</v>
+        <v>15.61</v>
       </c>
       <c r="O5" t="n">
-        <v>-24.46</v>
+        <v>2.11</v>
       </c>
       <c r="P5" t="n">
-        <v>-8.470000000000001</v>
+        <v>17.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>18.35</v>
+        <v>246.15</v>
       </c>
       <c r="R5" t="n">
-        <v>9.656720358789762</v>
+        <v>0.02119712229431037</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.814</v>
       </c>
       <c r="T5" t="n">
-        <v>2121.97</v>
+        <v>280.74</v>
       </c>
       <c r="U5" t="n">
-        <v>6718</v>
+        <v>393</v>
       </c>
       <c r="V5" t="n">
-        <v>1.026895953371448</v>
+        <v>0.9604829857299676</v>
       </c>
       <c r="W5" t="n">
-        <v>1.147856384611062</v>
+        <v>1.035582973345717</v>
       </c>
       <c r="X5" t="n">
-        <v>112.3775000000001</v>
+        <v>25.50799999999998</v>
       </c>
       <c r="Y5" t="n">
-        <v>100.5352250918585</v>
+        <v>23.65817189987825</v>
       </c>
       <c r="Z5" t="n">
-        <v>391196768</v>
+        <v>450016000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>00631L.TW</t>
+          <t>00985A.TW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>主動野村台灣50</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.01567793552954</v>
+        <v>0.4938936419142597</v>
       </c>
       <c r="D6" t="n">
-        <v>3.575007246018012</v>
+        <v>0.4645873966600014</v>
       </c>
       <c r="E6" t="n">
-        <v>39.78</v>
+        <v>23.04</v>
       </c>
       <c r="F6" t="n">
-        <v>49.01</v>
+        <v>28.28</v>
       </c>
       <c r="G6" t="n">
-        <v>644</v>
+        <v>37</v>
       </c>
       <c r="H6" t="n">
-        <v>89.44</v>
+        <v>100</v>
       </c>
       <c r="I6" t="n">
-        <v>3.74</v>
+        <v>6.95</v>
       </c>
       <c r="J6" t="n">
-        <v>12.68167701863354</v>
+        <v>9.972972972972974</v>
       </c>
       <c r="K6" t="n">
-        <v>155704987.25</v>
+        <v>45770703.95</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>2</v>
       </c>
       <c r="N6" t="n">
-        <v>17.37</v>
+        <v>15.02</v>
       </c>
       <c r="O6" t="n">
-        <v>-12.43</v>
+        <v>2.1</v>
       </c>
       <c r="P6" t="n">
-        <v>4.940000000000001</v>
+        <v>17.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>15.49</v>
+        <v>252.13</v>
       </c>
       <c r="R6" t="n">
-        <v>13.44067068951153</v>
+        <v>0.02930624525425829</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2407.1</v>
+        <v>257.02</v>
       </c>
       <c r="U6" t="n">
-        <v>8167</v>
+        <v>369</v>
       </c>
       <c r="V6" t="n">
-        <v>1.023332390090809</v>
+        <v>0.9773271967592098</v>
       </c>
       <c r="W6" t="n">
-        <v>1.140976649223057</v>
+        <v>1.0347467213535</v>
       </c>
       <c r="X6" t="n">
-        <v>38.87299999999998</v>
+        <v>23.57450000000001</v>
       </c>
       <c r="Y6" t="n">
-        <v>34.86486776665239</v>
+        <v>22.26631843767771</v>
       </c>
       <c r="Z6" t="n">
-        <v>4855432790.52</v>
+        <v>4445982720</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>00904.TW</t>
+          <t>009816.TW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>台新臺灣半導體30</t>
+          <t>凱基台灣TOP50</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.914571005583118</v>
+        <v>0.1881787786263047</v>
       </c>
       <c r="D7" t="n">
-        <v>1.814194956636023</v>
+        <v>0.1549200544580014</v>
       </c>
       <c r="E7" t="n">
-        <v>43.09</v>
+        <v>16.19</v>
       </c>
       <c r="F7" t="n">
-        <v>39.8</v>
+        <v>35.02</v>
       </c>
       <c r="G7" t="n">
-        <v>239</v>
+        <v>24</v>
       </c>
       <c r="H7" t="n">
-        <v>99.16</v>
+        <v>100</v>
       </c>
       <c r="I7" t="n">
-        <v>3.55</v>
+        <v>5.32</v>
       </c>
       <c r="J7" t="n">
-        <v>10.78242677824268</v>
+        <v>10.54166666666667</v>
       </c>
       <c r="K7" t="n">
-        <v>2767358</v>
+        <v>119874633.25</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>2</v>
       </c>
       <c r="N7" t="n">
-        <v>11.85</v>
+        <v>8.99</v>
       </c>
       <c r="O7" t="n">
-        <v>-12.45</v>
+        <v>0.64</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5999999999999996</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>37.53</v>
+        <v>227.93</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1003760489470951</v>
+        <v>0.03325872416830333</v>
       </c>
       <c r="S7" t="n">
-        <v>4.850000000000001</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>848.62</v>
+        <v>127.78</v>
       </c>
       <c r="U7" t="n">
-        <v>2577</v>
+        <v>253</v>
       </c>
       <c r="V7" t="n">
-        <v>1.000859405848605</v>
+        <v>0.9798462748895478</v>
       </c>
       <c r="W7" t="n">
-        <v>1.069032946920937</v>
+        <v>1.023707094574467</v>
       </c>
       <c r="X7" t="n">
-        <v>43.053</v>
+        <v>16.523</v>
       </c>
       <c r="Y7" t="n">
-        <v>40.30745743067057</v>
+        <v>15.81507062499145</v>
       </c>
       <c r="Z7" t="n">
-        <v>209904317</v>
+        <v>6005470030</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>00685L.TW</t>
+          <t>009804.TW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>群益臺灣加權正2</t>
+          <t>聯邦台精彩50</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11.57521995665375</v>
+        <v>0.6441778521262456</v>
       </c>
       <c r="D8" t="n">
-        <v>2.958216106611288</v>
+        <v>0.6294955437664567</v>
       </c>
       <c r="E8" t="n">
-        <v>13.2</v>
+        <v>23.21</v>
       </c>
       <c r="F8" t="n">
-        <v>51.89</v>
+        <v>30.51</v>
       </c>
       <c r="G8" t="n">
-        <v>514</v>
+        <v>62</v>
       </c>
       <c r="H8" t="n">
-        <v>88.52</v>
+        <v>100</v>
       </c>
       <c r="I8" t="n">
-        <v>3.46</v>
+        <v>4.12</v>
       </c>
       <c r="J8" t="n">
-        <v>12.18093385214008</v>
+        <v>8.82258064516129</v>
       </c>
       <c r="K8" t="n">
-        <v>202377761.25</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
+        <v>1146052.6</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="M8" t="n">
         <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>15.89</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>-18.5</v>
+        <v>0.76</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.609999999999999</v>
+        <v>10.39</v>
       </c>
       <c r="Q8" t="n">
-        <v>18.65</v>
+        <v>133.05</v>
       </c>
       <c r="R8" t="n">
-        <v>8.617003850042458</v>
+        <v>0.0146823083597889</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.786</v>
       </c>
       <c r="T8" t="n">
-        <v>1777.84</v>
+        <v>255.36</v>
       </c>
       <c r="U8" t="n">
-        <v>6261</v>
+        <v>547</v>
       </c>
       <c r="V8" t="n">
-        <v>1.026678074200824</v>
+        <v>0.9693248971580114</v>
       </c>
       <c r="W8" t="n">
-        <v>1.149366777042334</v>
+        <v>1.02316665365645</v>
       </c>
       <c r="X8" t="n">
-        <v>12.857</v>
+        <v>23.9445</v>
       </c>
       <c r="Y8" t="n">
-        <v>11.48458461098689</v>
+        <v>22.6844765875191</v>
       </c>
       <c r="Z8" t="n">
-        <v>2072410375.2</v>
+        <v>42427880</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>00715L.TW</t>
+          <t>00830.TW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>期街口布蘭特正2</t>
+          <t>國泰費城半導體</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5.230381716646164</v>
+        <v>2.458987228857474</v>
       </c>
       <c r="D9" t="n">
-        <v>2.811053896390728</v>
+        <v>2.302497611714684</v>
       </c>
       <c r="E9" t="n">
-        <v>77.40000000000001</v>
+        <v>83.34999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>91.09</v>
+        <v>31.72</v>
       </c>
       <c r="G9" t="n">
-        <v>425</v>
+        <v>495</v>
       </c>
       <c r="H9" t="n">
-        <v>77.65000000000001</v>
+        <v>97.17</v>
       </c>
       <c r="I9" t="n">
-        <v>3.32</v>
+        <v>3.93</v>
       </c>
       <c r="J9" t="n">
-        <v>17.11294117647059</v>
+        <v>12.29090909090909</v>
       </c>
       <c r="K9" t="n">
-        <v>3810471</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
+        <v>9366004.050000001</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="M9" t="n">
         <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>32.14</v>
+        <v>13.29</v>
       </c>
       <c r="O9" t="n">
-        <v>-44.86</v>
+        <v>-12.33</v>
       </c>
       <c r="P9" t="n">
-        <v>-12.72</v>
+        <v>0.9599999999999991</v>
       </c>
       <c r="Q9" t="n">
-        <v>14.59</v>
+        <v>19.85</v>
       </c>
       <c r="R9" t="n">
-        <v>2.419327820255436</v>
+        <v>0.1564896171427894</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>17.71</v>
       </c>
       <c r="T9" t="n">
-        <v>1409.31</v>
+        <v>1946.3</v>
       </c>
       <c r="U9" t="n">
-        <v>7273</v>
+        <v>6084</v>
       </c>
       <c r="V9" t="n">
-        <v>1.126104826683157</v>
+        <v>0.9560404897771916</v>
       </c>
       <c r="W9" t="n">
-        <v>1.279125834249105</v>
+        <v>1.06147425715696</v>
       </c>
       <c r="X9" t="n">
-        <v>68.73249999999994</v>
+        <v>87.18249999999999</v>
       </c>
       <c r="Y9" t="n">
-        <v>60.51007487112221</v>
+        <v>78.52286519245759</v>
       </c>
       <c r="Z9" t="n">
-        <v>276836889.6</v>
+        <v>1575315000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>00675L.TW</t>
+          <t>009818.TW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>富邦臺灣加權正2</t>
+          <t>華南永昌NASDAQxT</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12.16553299238016</v>
+        <v>0.1048090446430547</v>
       </c>
       <c r="D10" t="n">
-        <v>3.06943213416639</v>
+        <v>0.1032440051411441</v>
       </c>
       <c r="E10" t="n">
-        <v>349.3</v>
+        <v>20.88</v>
       </c>
       <c r="F10" t="n">
-        <v>51.4</v>
+        <v>48.65</v>
       </c>
       <c r="G10" t="n">
-        <v>564</v>
+        <v>21</v>
       </c>
       <c r="H10" t="n">
-        <v>87.06</v>
+        <v>100</v>
       </c>
       <c r="I10" t="n">
-        <v>3.18</v>
+        <v>3.81</v>
       </c>
       <c r="J10" t="n">
-        <v>12.38297872340426</v>
+        <v>8.714285714285714</v>
       </c>
       <c r="K10" t="n">
-        <v>966418.25</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
+        <v>182175.65</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="M10" t="n">
         <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>15.7</v>
+        <v>7.21</v>
       </c>
       <c r="O10" t="n">
-        <v>-24.73</v>
+        <v>1.65</v>
       </c>
       <c r="P10" t="n">
-        <v>-9.030000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>16.61</v>
+        <v>222.85</v>
       </c>
       <c r="R10" t="n">
-        <v>9.096100858213767</v>
+        <v>0.00156503950191067</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1792.47</v>
+        <v>79.97</v>
       </c>
       <c r="U10" t="n">
-        <v>6984</v>
+        <v>183</v>
       </c>
       <c r="V10" t="n">
-        <v>1.025769033110637</v>
+        <v>0.99215965787598</v>
       </c>
       <c r="W10" t="n">
-        <v>1.146757688777605</v>
+        <v>1.047933962657891</v>
       </c>
       <c r="X10" t="n">
-        <v>340.5250000000002</v>
+        <v>21.045</v>
       </c>
       <c r="Y10" t="n">
-        <v>304.5979141176189</v>
+        <v>19.92491964573964</v>
       </c>
       <c r="Z10" t="n">
-        <v>240269847.3</v>
+        <v>8059680</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>00935.TW</t>
+          <t>00400A.TW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>野村臺灣新科技50</t>
+          <t>主動國泰動能高息</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.593256703683568</v>
+        <v>0.08649947639092126</v>
       </c>
       <c r="D11" t="n">
-        <v>1.220856645370793</v>
+        <v>0.07311764947292709</v>
       </c>
       <c r="E11" t="n">
-        <v>60.5</v>
+        <v>14.94</v>
       </c>
       <c r="F11" t="n">
-        <v>41.47</v>
+        <v>32.65</v>
       </c>
       <c r="G11" t="n">
-        <v>136</v>
+        <v>16</v>
       </c>
       <c r="H11" t="n">
-        <v>83.09</v>
+        <v>68.75</v>
       </c>
       <c r="I11" t="n">
-        <v>3.15</v>
+        <v>3.77</v>
       </c>
       <c r="J11" t="n">
-        <v>12.30882352941176</v>
+        <v>13.1875</v>
       </c>
       <c r="K11" t="n">
-        <v>11646996.75</v>
+        <v>37299493.85</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>14.6</v>
+        <v>13.12</v>
       </c>
       <c r="O11" t="n">
-        <v>-8.99</v>
+        <v>-0.83</v>
       </c>
       <c r="P11" t="n">
-        <v>5.609999999999999</v>
+        <v>12.29</v>
       </c>
       <c r="Q11" t="n">
-        <v>43.74</v>
+        <v>126.3</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3724000583127749</v>
+        <v>0.01338182691799417</v>
       </c>
       <c r="S11" t="n">
-        <v>4.98</v>
+        <v>0.48</v>
       </c>
       <c r="T11" t="n">
-        <v>428.12</v>
+        <v>60.34</v>
       </c>
       <c r="U11" t="n">
-        <v>1674</v>
+        <v>211</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9995456610631529</v>
+        <v>0.9598766423592145</v>
       </c>
       <c r="W11" t="n">
-        <v>1.074416686286148</v>
+        <v>1.04435641155437</v>
       </c>
       <c r="X11" t="n">
-        <v>60.52750000000001</v>
+        <v>15.5645</v>
       </c>
       <c r="Y11" t="n">
-        <v>56.30962434986522</v>
+        <v>14.30546108082395</v>
       </c>
       <c r="Z11" t="n">
-        <v>443203700.5</v>
+        <v>1359988200</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>00894.TW</t>
+          <t>00663L.TW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>中信小資高價30</t>
+          <t>國泰臺灣加權正2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.236450828125559</v>
+        <v>11.78378313523225</v>
       </c>
       <c r="D12" t="n">
-        <v>1.866789945099285</v>
+        <v>2.98855211972696</v>
       </c>
       <c r="E12" t="n">
-        <v>50.55</v>
+        <v>107</v>
       </c>
       <c r="F12" t="n">
-        <v>48.88</v>
+        <v>35.43</v>
       </c>
       <c r="G12" t="n">
-        <v>243</v>
+        <v>564</v>
       </c>
       <c r="H12" t="n">
-        <v>82.72</v>
+        <v>89.89</v>
       </c>
       <c r="I12" t="n">
-        <v>2.88</v>
+        <v>3.76</v>
       </c>
       <c r="J12" t="n">
-        <v>15.32921810699589</v>
+        <v>11.9113475177305</v>
       </c>
       <c r="K12" t="n">
-        <v>1126935.5</v>
+        <v>5404375.15</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>15.7</v>
+        <v>15.99</v>
       </c>
       <c r="O12" t="n">
-        <v>-8.380000000000001</v>
+        <v>-24.46</v>
       </c>
       <c r="P12" t="n">
-        <v>7.319999999999999</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>22.58</v>
+        <v>18.35</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3696608830262744</v>
+        <v>8.795231015505291</v>
       </c>
       <c r="S12" t="n">
-        <v>7.549999999999999</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>698.73</v>
+        <v>2121.97</v>
       </c>
       <c r="U12" t="n">
-        <v>3725</v>
+        <v>6718</v>
       </c>
       <c r="V12" t="n">
-        <v>1.015621075895324</v>
+        <v>0.9501398570350302</v>
       </c>
       <c r="W12" t="n">
-        <v>1.104971362785325</v>
+        <v>1.054998324875417</v>
       </c>
       <c r="X12" t="n">
-        <v>49.77249999999999</v>
+        <v>112.6150000000001</v>
       </c>
       <c r="Y12" t="n">
-        <v>45.74779193605299</v>
+        <v>101.4219619852339</v>
       </c>
       <c r="Z12" t="n">
-        <v>19924990.2</v>
+        <v>1774702000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>00901.TW</t>
+          <t>00631L.TW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>永豐智能車供應鏈</t>
+          <t>元大台灣50正2</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.934729166447378</v>
+        <v>15.81462527384705</v>
       </c>
       <c r="D13" t="n">
-        <v>1.831029724329293</v>
+        <v>3.412594486979345</v>
       </c>
       <c r="E13" t="n">
-        <v>48.08</v>
+        <v>37.14</v>
       </c>
       <c r="F13" t="n">
-        <v>40.56</v>
+        <v>32.67</v>
       </c>
       <c r="G13" t="n">
-        <v>276</v>
+        <v>644</v>
       </c>
       <c r="H13" t="n">
-        <v>89.48999999999999</v>
+        <v>89.44</v>
       </c>
       <c r="I13" t="n">
-        <v>2.79</v>
+        <v>3.74</v>
       </c>
       <c r="J13" t="n">
-        <v>13.22463768115942</v>
+        <v>12.68167701863354</v>
       </c>
       <c r="K13" t="n">
-        <v>231867.45</v>
+        <v>179263211.8</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1528,82 +1548,82 @@
         <v>2</v>
       </c>
       <c r="N13" t="n">
-        <v>15.18</v>
+        <v>17.37</v>
       </c>
       <c r="O13" t="n">
-        <v>-7.3</v>
+        <v>-12.43</v>
       </c>
       <c r="P13" t="n">
-        <v>7.88</v>
+        <v>4.940000000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>24.17</v>
+        <v>15.49</v>
       </c>
       <c r="R13" t="n">
-        <v>0.103699442118085</v>
+        <v>12.4020307868677</v>
       </c>
       <c r="S13" t="n">
-        <v>4.671</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>771.28</v>
+        <v>2407.1</v>
       </c>
       <c r="U13" t="n">
-        <v>3650</v>
+        <v>8167</v>
       </c>
       <c r="V13" t="n">
-        <v>1.001896267894726</v>
+        <v>0.9532854209445588</v>
       </c>
       <c r="W13" t="n">
-        <v>1.070431385158977</v>
+        <v>1.05545427515227</v>
       </c>
       <c r="X13" t="n">
-        <v>47.989</v>
+        <v>38.95999999999999</v>
       </c>
       <c r="Y13" t="n">
-        <v>44.91647074871533</v>
+        <v>35.18863950277886</v>
       </c>
       <c r="Z13" t="n">
-        <v>1065645.12</v>
+        <v>23788095720</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>0057.TW</t>
+          <t>00904.TW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>富邦摩台</t>
+          <t>台新臺灣半導體30</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6.452754763888863</v>
+        <v>1.796820086612032</v>
       </c>
       <c r="D14" t="n">
-        <v>5.15296572257841</v>
+        <v>1.71251094841077</v>
       </c>
       <c r="E14" t="n">
-        <v>335.8</v>
+        <v>41.22</v>
       </c>
       <c r="F14" t="n">
-        <v>48.76</v>
+        <v>27.83</v>
       </c>
       <c r="G14" t="n">
-        <v>1245</v>
+        <v>239</v>
       </c>
       <c r="H14" t="n">
-        <v>93.33</v>
+        <v>99.16</v>
       </c>
       <c r="I14" t="n">
-        <v>2.64</v>
+        <v>3.55</v>
       </c>
       <c r="J14" t="n">
-        <v>12.02409638554217</v>
+        <v>10.78242677824268</v>
       </c>
       <c r="K14" t="n">
-        <v>29839.15</v>
+        <v>3518211.65</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1614,512 +1634,508 @@
         <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>14.45</v>
+        <v>11.85</v>
       </c>
       <c r="O14" t="n">
-        <v>-6.48</v>
+        <v>-12.45</v>
       </c>
       <c r="P14" t="n">
-        <v>7.969999999999999</v>
+        <v>-0.5999999999999996</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.970000000000001</v>
+        <v>37.53</v>
       </c>
       <c r="R14" t="n">
-        <v>1.299789041310452</v>
+        <v>0.08430913820126129</v>
       </c>
       <c r="S14" t="n">
-        <v>1.685</v>
+        <v>4.850000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>3287.55</v>
+        <v>848.62</v>
       </c>
       <c r="U14" t="n">
-        <v>14970</v>
+        <v>2577</v>
       </c>
       <c r="V14" t="n">
-        <v>1.007500750075007</v>
+        <v>0.9567578859410905</v>
       </c>
       <c r="W14" t="n">
-        <v>1.060584537199488</v>
+        <v>1.019464222846942</v>
       </c>
       <c r="X14" t="n">
-        <v>333.3000000000001</v>
+        <v>43.083</v>
       </c>
       <c r="Y14" t="n">
-        <v>316.6178538550942</v>
+        <v>40.43300301886964</v>
       </c>
       <c r="Z14" t="n">
-        <v>15541831.4</v>
+        <v>644722020</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>00881.TW</t>
+          <t>00913.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>國泰台灣科技龍頭</t>
+          <t>兆豐台灣晶圓製造</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.10929767948073</v>
+        <v>1.644147697334891</v>
       </c>
       <c r="D15" t="n">
-        <v>1.935830656188242</v>
+        <v>1.619496059933628</v>
       </c>
       <c r="E15" t="n">
-        <v>52.1</v>
+        <v>48.25</v>
       </c>
       <c r="F15" t="n">
-        <v>38.09</v>
+        <v>25.63</v>
       </c>
       <c r="G15" t="n">
-        <v>384</v>
+        <v>262</v>
       </c>
       <c r="H15" t="n">
-        <v>89.58</v>
+        <v>96.18000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>2.52</v>
+        <v>3.5</v>
       </c>
       <c r="J15" t="n">
-        <v>15.328125</v>
+        <v>12.79770992366412</v>
       </c>
       <c r="K15" t="n">
-        <v>16339519.45</v>
+        <v>1814171.75</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>10.9</v>
+        <v>13.5</v>
       </c>
       <c r="O15" t="n">
-        <v>-4.28</v>
+        <v>-9.19</v>
       </c>
       <c r="P15" t="n">
-        <v>6.62</v>
+        <v>4.31</v>
       </c>
       <c r="Q15" t="n">
-        <v>15.81</v>
+        <v>28.72</v>
       </c>
       <c r="R15" t="n">
-        <v>0.1734670232924884</v>
+        <v>0.02465163740126375</v>
       </c>
       <c r="S15" t="n">
-        <v>12.5</v>
+        <v>6.699999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>966.91</v>
+        <v>916.5599999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>5886</v>
+        <v>3353</v>
       </c>
       <c r="V15" t="n">
-        <v>1.00051850287097</v>
+        <v>0.9299232933739354</v>
       </c>
       <c r="W15" t="n">
-        <v>1.062704393760517</v>
+        <v>1.008639043299769</v>
       </c>
       <c r="X15" t="n">
-        <v>52.07299999999999</v>
+        <v>51.88599999999999</v>
       </c>
       <c r="Y15" t="n">
-        <v>49.02586298306097</v>
+        <v>47.83673636323836</v>
       </c>
       <c r="Z15" t="n">
-        <v>456972382.3</v>
+        <v>168923250</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>0052.TW</t>
+          <t>00685L.TW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>富邦科技</t>
+          <t>群益臺灣加權正2</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8.665215849489966</v>
+        <v>10.67502778467844</v>
       </c>
       <c r="D16" t="n">
-        <v>5.251488262372824</v>
+        <v>2.817107345266162</v>
       </c>
       <c r="E16" t="n">
-        <v>65.7</v>
+        <v>12.26</v>
       </c>
       <c r="F16" t="n">
-        <v>42.61</v>
+        <v>34.6</v>
       </c>
       <c r="G16" t="n">
-        <v>1111</v>
+        <v>514</v>
       </c>
       <c r="H16" t="n">
-        <v>88.20999999999999</v>
+        <v>88.52</v>
       </c>
       <c r="I16" t="n">
-        <v>2.45</v>
+        <v>3.46</v>
       </c>
       <c r="J16" t="n">
-        <v>14.18091809180918</v>
+        <v>12.18093385214008</v>
       </c>
       <c r="K16" t="n">
-        <v>16949460.4</v>
+        <v>237609617.3</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>12.7</v>
+        <v>15.89</v>
       </c>
       <c r="O16" t="n">
-        <v>-14.18</v>
+        <v>-18.5</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.48</v>
+        <v>-2.609999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.050000000000001</v>
+        <v>18.65</v>
       </c>
       <c r="R16" t="n">
-        <v>3.413727587117142</v>
+        <v>7.857920439412277</v>
       </c>
       <c r="S16" t="n">
-        <v>2.232857285714286</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2723.42</v>
+        <v>1777.84</v>
       </c>
       <c r="U16" t="n">
-        <v>15755</v>
+        <v>6261</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0087517273146</v>
+        <v>0.9514201458947694</v>
       </c>
       <c r="W16" t="n">
-        <v>1.070346113680226</v>
+        <v>1.057623833670449</v>
       </c>
       <c r="X16" t="n">
-        <v>65.13000000000008</v>
+        <v>12.886</v>
       </c>
       <c r="Y16" t="n">
-        <v>61.38201387409192</v>
+        <v>11.5920231841335</v>
       </c>
       <c r="Z16" t="n">
-        <v>959480237.7</v>
+        <v>11270985800</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>00735.TW</t>
+          <t>009809.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>國泰臺韓科技</t>
+          <t>富邦淨零ESG50</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3.114123809615423</v>
+        <v>0.3665561855062192</v>
       </c>
       <c r="D17" t="n">
-        <v>2.684821291236675</v>
+        <v>0.326851662852756</v>
       </c>
       <c r="E17" t="n">
-        <v>103.9</v>
+        <v>18.22</v>
       </c>
       <c r="F17" t="n">
-        <v>29.75</v>
+        <v>32.57</v>
       </c>
       <c r="G17" t="n">
-        <v>498</v>
+        <v>34</v>
       </c>
       <c r="H17" t="n">
-        <v>86.55</v>
+        <v>97.06</v>
       </c>
       <c r="I17" t="n">
-        <v>2.28</v>
+        <v>3.4</v>
       </c>
       <c r="J17" t="n">
-        <v>13.81124497991968</v>
+        <v>8.235294117647058</v>
       </c>
       <c r="K17" t="n">
-        <v>1520740.05</v>
+        <v>190734.35</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>21.39</v>
+        <v>7.76</v>
       </c>
       <c r="O17" t="n">
-        <v>-6.04</v>
+        <v>-0.12</v>
       </c>
       <c r="P17" t="n">
-        <v>15.35</v>
+        <v>7.64</v>
       </c>
       <c r="Q17" t="n">
-        <v>14.26</v>
+        <v>172.16</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4293025183787478</v>
+        <v>0.03970452265346314</v>
       </c>
       <c r="S17" t="n">
-        <v>13.37</v>
+        <v>0.315</v>
       </c>
       <c r="T17" t="n">
-        <v>1133.84</v>
+        <v>115.56</v>
       </c>
       <c r="U17" t="n">
-        <v>6878</v>
+        <v>280</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9696460651874675</v>
+        <v>0.9808090867493875</v>
       </c>
       <c r="W17" t="n">
-        <v>1.03701259685019</v>
+        <v>1.01613053783949</v>
       </c>
       <c r="X17" t="n">
-        <v>107.1524999999999</v>
+        <v>18.5765</v>
       </c>
       <c r="Y17" t="n">
-        <v>100.1916469631947</v>
+        <v>17.93076708307537</v>
       </c>
       <c r="Z17" t="n">
-        <v>121035084.1</v>
+        <v>6978260</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>0050.TW</t>
+          <t>00715L.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>元大台灣50</t>
+          <t>期街口布蘭特正2</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.801193137925813</v>
+        <v>5.058991702425611</v>
       </c>
       <c r="D18" t="n">
-        <v>5.801193137925813</v>
+        <v>2.67503331876492</v>
       </c>
       <c r="E18" t="n">
-        <v>113</v>
+        <v>75.3</v>
       </c>
       <c r="F18" t="n">
-        <v>46.69</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>1695</v>
+        <v>425</v>
       </c>
       <c r="H18" t="n">
-        <v>90.97</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>2.26</v>
+        <v>3.32</v>
       </c>
       <c r="J18" t="n">
-        <v>13.46961651917404</v>
+        <v>17.11294117647059</v>
       </c>
       <c r="K18" t="n">
-        <v>87027579.3</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
+        <v>3461435.6</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>13.94</v>
+        <v>32.14</v>
       </c>
       <c r="O18" t="n">
-        <v>-5.91</v>
+        <v>-44.86</v>
       </c>
       <c r="P18" t="n">
-        <v>8.029999999999999</v>
+        <v>-12.72</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.04</v>
+        <v>14.59</v>
       </c>
       <c r="R18" t="n">
+        <v>2.383958383660691</v>
+      </c>
+      <c r="S18" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="n">
-        <v>4.84625</v>
-      </c>
       <c r="T18" t="n">
-        <v>3824.71</v>
+        <v>1409.31</v>
       </c>
       <c r="U18" t="n">
-        <v>22831</v>
+        <v>7273</v>
       </c>
       <c r="V18" t="n">
-        <v>1.00951445035065</v>
+        <v>1.091739461379536</v>
       </c>
       <c r="W18" t="n">
-        <v>1.066343641870528</v>
+        <v>1.248955790732181</v>
       </c>
       <c r="X18" t="n">
-        <v>111.935</v>
+        <v>68.97249999999994</v>
       </c>
       <c r="Y18" t="n">
-        <v>105.9695913802993</v>
+        <v>60.2903646059854</v>
       </c>
       <c r="Z18" t="n">
-        <v>7244389433</v>
+        <v>145329000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>0053.TW</t>
+          <t>00675L.TW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>元大科技市值</t>
+          <t>富邦臺灣加權正2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7.049905875996625</v>
+        <v>11.20358322766104</v>
       </c>
       <c r="D19" t="n">
-        <v>5.212039339800091</v>
+        <v>2.924510748817748</v>
       </c>
       <c r="E19" t="n">
-        <v>253.05</v>
+        <v>323.9</v>
       </c>
       <c r="F19" t="n">
-        <v>33.35</v>
+        <v>34.76</v>
       </c>
       <c r="G19" t="n">
-        <v>1190</v>
+        <v>564</v>
       </c>
       <c r="H19" t="n">
-        <v>89.16</v>
+        <v>87.06</v>
       </c>
       <c r="I19" t="n">
-        <v>2.18</v>
+        <v>3.18</v>
       </c>
       <c r="J19" t="n">
-        <v>13.83697478991597</v>
+        <v>12.38297872340426</v>
       </c>
       <c r="K19" t="n">
-        <v>254820.35</v>
+        <v>1087463.25</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>11.49</v>
+        <v>15.7</v>
       </c>
       <c r="O19" t="n">
-        <v>-7.24</v>
+        <v>-24.73</v>
       </c>
       <c r="P19" t="n">
-        <v>4.25</v>
+        <v>-9.030000000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.58</v>
+        <v>16.61</v>
       </c>
       <c r="R19" t="n">
-        <v>1.837866536196534</v>
+        <v>8.279072478843293</v>
       </c>
       <c r="S19" t="n">
-        <v>18.91</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2598</v>
+        <v>1792.47</v>
       </c>
       <c r="U19" t="n">
-        <v>16466</v>
+        <v>6984</v>
       </c>
       <c r="V19" t="n">
-        <v>1.004405810907359</v>
+        <v>0.9491992322006823</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06915283145858</v>
+        <v>1.054139955467589</v>
       </c>
       <c r="X19" t="n">
-        <v>251.9400000000001</v>
+        <v>341.2350000000002</v>
       </c>
       <c r="Y19" t="n">
-        <v>236.682719770549</v>
+        <v>307.2647026801356</v>
       </c>
       <c r="Z19" t="n">
-        <v>132700938.3</v>
+        <v>1099964400</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>00892.TW</t>
+          <t>00935.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>富邦台灣半導體</t>
+          <t>野村臺灣新科技50</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.988971647181115</v>
+        <v>1.444612916212354</v>
       </c>
       <c r="D20" t="n">
-        <v>1.884076186128367</v>
+        <v>1.139957781524034</v>
       </c>
       <c r="E20" t="n">
-        <v>42.99</v>
+        <v>56.85</v>
       </c>
       <c r="F20" t="n">
-        <v>43.21</v>
+        <v>28.59</v>
       </c>
       <c r="G20" t="n">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="H20" t="n">
-        <v>75.09999999999999</v>
+        <v>83.09</v>
       </c>
       <c r="I20" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="J20" t="n">
-        <v>15.85892116182573</v>
+        <v>12.30882352941176</v>
       </c>
       <c r="K20" t="n">
-        <v>4254290.15</v>
+        <v>12886199.65</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -2130,82 +2146,82 @@
         <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>12.37</v>
+        <v>14.6</v>
       </c>
       <c r="O20" t="n">
-        <v>-7.43</v>
+        <v>-8.99</v>
       </c>
       <c r="P20" t="n">
-        <v>4.94</v>
+        <v>5.609999999999999</v>
       </c>
       <c r="Q20" t="n">
-        <v>18.86</v>
+        <v>43.74</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1048954610527479</v>
+        <v>0.30465513468832</v>
       </c>
       <c r="S20" t="n">
-        <v>4.937</v>
+        <v>4.98</v>
       </c>
       <c r="T20" t="n">
-        <v>510.5</v>
+        <v>428.12</v>
       </c>
       <c r="U20" t="n">
-        <v>3822</v>
+        <v>1674</v>
       </c>
       <c r="V20" t="n">
-        <v>1.001595936768286</v>
+        <v>0.9401356044319497</v>
       </c>
       <c r="W20" t="n">
-        <v>1.049644147510152</v>
+        <v>1.013590899120304</v>
       </c>
       <c r="X20" t="n">
-        <v>42.92150000000001</v>
+        <v>60.47000000000001</v>
       </c>
       <c r="Y20" t="n">
-        <v>40.95673767340679</v>
+        <v>56.08771748970928</v>
       </c>
       <c r="Z20" t="n">
-        <v>130107472.41</v>
+        <v>1956208500</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>006208.TW</t>
+          <t>00894.TW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>富邦台50</t>
+          <t>中信小資高價30</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4.314323152396278</v>
+        <v>2.076170136134475</v>
       </c>
       <c r="D21" t="n">
-        <v>4.059525979781002</v>
+        <v>1.763438952641097</v>
       </c>
       <c r="E21" t="n">
-        <v>258.7</v>
+        <v>47.78</v>
       </c>
       <c r="F21" t="n">
-        <v>46.84</v>
+        <v>35.64</v>
       </c>
       <c r="G21" t="n">
-        <v>895</v>
+        <v>243</v>
       </c>
       <c r="H21" t="n">
-        <v>88.48999999999999</v>
+        <v>82.72</v>
       </c>
       <c r="I21" t="n">
-        <v>1.95</v>
+        <v>2.88</v>
       </c>
       <c r="J21" t="n">
-        <v>13.86703910614525</v>
+        <v>15.32921810699589</v>
       </c>
       <c r="K21" t="n">
-        <v>2515871.7</v>
+        <v>1209628.4</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -2216,43 +2232,817 @@
         <v>2</v>
       </c>
       <c r="N21" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-8.380000000000001</v>
+      </c>
+      <c r="P21" t="n">
+        <v>7.319999999999999</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>22.58</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.3127311834933781</v>
+      </c>
+      <c r="S21" t="n">
+        <v>7.549999999999999</v>
+      </c>
+      <c r="T21" t="n">
+        <v>698.73</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3725</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.9590429642416278</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.040579903970262</v>
+      </c>
+      <c r="X21" t="n">
+        <v>49.82049999999998</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>45.91670453916959</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>169714560</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>00901.TW</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>永豐智能車供應鏈</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1.788118206173358</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.7288256294119</v>
+      </c>
+      <c r="E22" t="n">
+        <v>45.53</v>
+      </c>
+      <c r="F22" t="n">
+        <v>29</v>
+      </c>
+      <c r="G22" t="n">
+        <v>276</v>
+      </c>
+      <c r="H22" t="n">
+        <v>89.48999999999999</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="J22" t="n">
+        <v>13.22463768115942</v>
+      </c>
+      <c r="K22" t="n">
+        <v>232812.05</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>2</v>
+      </c>
+      <c r="N22" t="n">
+        <v>15.18</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="P22" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>24.17</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.05929257676145827</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4.671</v>
+      </c>
+      <c r="T22" t="n">
+        <v>771.28</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3650</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.9486602491978163</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.013176804538972</v>
+      </c>
+      <c r="X22" t="n">
+        <v>47.99400000000001</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>44.93786256853525</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>22036520</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>0057.TW</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>富邦摩台</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>6.211365795691149</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4.936435554359588</v>
+      </c>
+      <c r="E23" t="n">
+        <v>324.95</v>
+      </c>
+      <c r="F23" t="n">
+        <v>33.13</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1245</v>
+      </c>
+      <c r="H23" t="n">
+        <v>93.33</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J23" t="n">
+        <v>12.02409638554217</v>
+      </c>
+      <c r="K23" t="n">
+        <v>31873.85</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>2</v>
+      </c>
+      <c r="N23" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-6.48</v>
+      </c>
+      <c r="P23" t="n">
+        <v>7.969999999999999</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.274930241331561</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.685</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3287.55</v>
+      </c>
+      <c r="U23" t="n">
+        <v>14970</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.973983154992057</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.022142995869986</v>
+      </c>
+      <c r="X23" t="n">
+        <v>333.63</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>317.9105089140901</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>19172050</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>00881.TW</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>國泰台灣科技龍頭</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2.000460207685347</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.830231265165083</v>
+      </c>
+      <c r="E24" t="n">
+        <v>49.95</v>
+      </c>
+      <c r="F24" t="n">
+        <v>25.39</v>
+      </c>
+      <c r="G24" t="n">
+        <v>384</v>
+      </c>
+      <c r="H24" t="n">
+        <v>89.58</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="J24" t="n">
+        <v>15.328125</v>
+      </c>
+      <c r="K24" t="n">
+        <v>17329178.3</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>2</v>
+      </c>
+      <c r="N24" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-4.28</v>
+      </c>
+      <c r="P24" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>15.81</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.1702289425202639</v>
+      </c>
+      <c r="S24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="T24" t="n">
+        <v>966.91</v>
+      </c>
+      <c r="U24" t="n">
+        <v>5886</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.958852831927208</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.017105496294636</v>
+      </c>
+      <c r="X24" t="n">
+        <v>52.09349999999999</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>49.10994993338472</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2269578150</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>0052.TW</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>富邦科技</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>8.2995376310792</v>
+      </c>
+      <c r="D25" t="n">
+        <v>5.030952125938335</v>
+      </c>
+      <c r="E25" t="n">
+        <v>63.15</v>
+      </c>
+      <c r="F25" t="n">
+        <v>28.73</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1111</v>
+      </c>
+      <c r="H25" t="n">
+        <v>88.20999999999999</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="J25" t="n">
+        <v>14.18091809180918</v>
+      </c>
+      <c r="K25" t="n">
+        <v>19121497.55</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>2</v>
+      </c>
+      <c r="N25" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-14.18</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="R25" t="n">
+        <v>3.268585505140865</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.232857285714286</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2723.42</v>
+      </c>
+      <c r="U25" t="n">
+        <v>15755</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.9686697089389105</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.024751621097207</v>
+      </c>
+      <c r="X25" t="n">
+        <v>65.19250000000008</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>61.62468904648811</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3469839900</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>00735.TW</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>國泰臺韓科技</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2.850956917903808</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2.553158213192911</v>
+      </c>
+      <c r="E26" t="n">
+        <v>96.65000000000001</v>
+      </c>
+      <c r="F26" t="n">
+        <v>20.34</v>
+      </c>
+      <c r="G26" t="n">
+        <v>498</v>
+      </c>
+      <c r="H26" t="n">
+        <v>86.55</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="J26" t="n">
+        <v>13.81124497991968</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1697643.65</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N26" t="n">
+        <v>21.39</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-6.04</v>
+      </c>
+      <c r="P26" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>14.26</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.297798704710897</v>
+      </c>
+      <c r="S26" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1133.84</v>
+      </c>
+      <c r="U26" t="n">
+        <v>6878</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.904327485380118</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.9782970144468626</v>
+      </c>
+      <c r="X26" t="n">
+        <v>106.8749999999999</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>98.79412752235244</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>451935400</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>0050.TW</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>元大台灣50</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5.562516877867843</v>
+      </c>
+      <c r="D27" t="n">
+        <v>5.562516877867843</v>
+      </c>
+      <c r="E27" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="F27" t="n">
+        <v>32.57</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1695</v>
+      </c>
+      <c r="H27" t="n">
+        <v>90.97</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="J27" t="n">
+        <v>13.46961651917404</v>
+      </c>
+      <c r="K27" t="n">
+        <v>101926809.7</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N27" t="n">
+        <v>13.94</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-5.91</v>
+      </c>
+      <c r="P27" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4.84625</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3824.71</v>
+      </c>
+      <c r="U27" t="n">
+        <v>22831</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.9720176730486005</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.023976480321431</v>
+      </c>
+      <c r="X27" t="n">
+        <v>112.035</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>106.3500989454521</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>42464030400</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>0053.TW</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>元大科技市值</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>6.770289434336692</v>
+      </c>
+      <c r="D28" t="n">
+        <v>4.993542447352277</v>
+      </c>
+      <c r="E28" t="n">
+        <v>243.75</v>
+      </c>
+      <c r="F28" t="n">
+        <v>23.46</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1190</v>
+      </c>
+      <c r="H28" t="n">
+        <v>89.16</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="J28" t="n">
+        <v>13.83697478991597</v>
+      </c>
+      <c r="K28" t="n">
+        <v>317950.1</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>2</v>
+      </c>
+      <c r="N28" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-7.24</v>
+      </c>
+      <c r="P28" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.776746986984415</v>
+      </c>
+      <c r="S28" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2598</v>
+      </c>
+      <c r="U28" t="n">
+        <v>16466</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.9665714965500828</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.025831254609657</v>
+      </c>
+      <c r="X28" t="n">
+        <v>252.1800000000001</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>237.612179298193</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>337350000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>00892.TW</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>富邦台灣半導體</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1.844390375272075</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.780171686715981</v>
+      </c>
+      <c r="E29" t="n">
+        <v>40.76</v>
+      </c>
+      <c r="F29" t="n">
+        <v>30.46</v>
+      </c>
+      <c r="G29" t="n">
+        <v>241</v>
+      </c>
+      <c r="H29" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="J29" t="n">
+        <v>15.85892116182573</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4445764.4</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>2</v>
+      </c>
+      <c r="N29" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-7.43</v>
+      </c>
+      <c r="P29" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.06421868855609425</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4.937</v>
+      </c>
+      <c r="T29" t="n">
+        <v>510.5</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3822</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.950260528984578</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.9984073580245072</v>
+      </c>
+      <c r="X29" t="n">
+        <v>42.8935</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>40.82501963992887</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>331704880</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>006208.TW</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>富邦台50</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>4.150294481638475</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3.880513910592286</v>
+      </c>
+      <c r="E30" t="n">
+        <v>250.1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>31.72</v>
+      </c>
+      <c r="G30" t="n">
+        <v>895</v>
+      </c>
+      <c r="H30" t="n">
+        <v>88.48999999999999</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="J30" t="n">
+        <v>13.86703910614525</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2805820.25</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>2</v>
+      </c>
+      <c r="N30" t="n">
         <v>11.21</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O30" t="n">
         <v>-6.25</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P30" t="n">
         <v>4.960000000000001</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q30" t="n">
         <v>8.949999999999999</v>
       </c>
-      <c r="R21" t="n">
-        <v>0.2547971726152758</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="R30" t="n">
+        <v>0.2697805710461898</v>
+      </c>
+      <c r="S30" t="n">
         <v>28.764</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T30" t="n">
         <v>1745.92</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U30" t="n">
         <v>12411</v>
       </c>
-      <c r="V21" t="n">
-        <v>1.009836833476462</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.066302048625593</v>
-      </c>
-      <c r="X21" t="n">
-        <v>256.1799999999999</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>242.6141826637684</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>394450496.7</v>
+      <c r="V30" t="n">
+        <v>0.9752293309677231</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.026576864733604</v>
+      </c>
+      <c r="X30" t="n">
+        <v>256.4525</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>243.62520585821</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1949779600</v>
       </c>
     </row>
   </sheetData>

--- a/ETF動態清單.xlsx
+++ b/ETF動態清單.xlsx
@@ -591,7 +591,7 @@
         <v>8.439024390243903</v>
       </c>
       <c r="K2" t="n">
-        <v>168651975.4</v>
+        <v>169181894.8</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
         <v>27.89418567881518</v>
       </c>
       <c r="Z2" t="n">
-        <v>11550054600</v>
+        <v>11861647207.2</v>
       </c>
     </row>
     <row r="3">
@@ -677,7 +677,7 @@
         <v>10.27272727272727</v>
       </c>
       <c r="K3" t="n">
-        <v>48642233.35</v>
+        <v>48739331.45</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>17.14210231656099</v>
       </c>
       <c r="Z3" t="n">
-        <v>2993496240</v>
+        <v>3028995305.36</v>
       </c>
     </row>
     <row r="4">
@@ -763,7 +763,7 @@
         <v>10.33333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>11811150.9</v>
+        <v>11863214.7</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>36.50293049259531</v>
       </c>
       <c r="Z4" t="n">
-        <v>1445916820</v>
+        <v>1484798065.84</v>
       </c>
     </row>
     <row r="5">
@@ -849,7 +849,7 @@
         <v>9.824999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>8529992.25</v>
+        <v>8554822.550000001</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>23.65817189987825</v>
       </c>
       <c r="Z5" t="n">
-        <v>450016000</v>
+        <v>462182847</v>
       </c>
     </row>
     <row r="6">
@@ -935,7 +935,7 @@
         <v>9.972972972972974</v>
       </c>
       <c r="K6" t="n">
-        <v>45770703.95</v>
+        <v>45952589.7</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>22.26631843767771</v>
       </c>
       <c r="Z6" t="n">
-        <v>4445982720</v>
+        <v>4529795673.599999</v>
       </c>
     </row>
     <row r="7">
@@ -1021,7 +1021,7 @@
         <v>10.54166666666667</v>
       </c>
       <c r="K7" t="n">
-        <v>119874633.25</v>
+        <v>120397877.55</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>15.81507062499145</v>
       </c>
       <c r="Z7" t="n">
-        <v>6005470030</v>
+        <v>6174896534.34</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         <v>8.82258064516129</v>
       </c>
       <c r="K8" t="n">
-        <v>1146052.6</v>
+        <v>1149921.7</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>22.6844765875191</v>
       </c>
       <c r="Z8" t="n">
-        <v>42427880</v>
+        <v>44223916.22</v>
       </c>
     </row>
     <row r="9">
@@ -1193,7 +1193,7 @@
         <v>12.29090909090909</v>
       </c>
       <c r="K9" t="n">
-        <v>9366004.050000001</v>
+        <v>9479141.9</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>78.52286519245759</v>
       </c>
       <c r="Z9" t="n">
-        <v>1575315000</v>
+        <v>1763915795.95</v>
       </c>
     </row>
     <row r="10">
@@ -1279,7 +1279,7 @@
         <v>8.714285714285714</v>
       </c>
       <c r="K10" t="n">
-        <v>182175.65</v>
+        <v>182318.65</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>19.92491964573964</v>
       </c>
       <c r="Z10" t="n">
-        <v>8059680</v>
+        <v>8119396.8</v>
       </c>
     </row>
     <row r="11">
@@ -1365,7 +1365,7 @@
         <v>13.1875</v>
       </c>
       <c r="K11" t="n">
-        <v>37299493.85</v>
+        <v>37377468.1</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>14.30546108082395</v>
       </c>
       <c r="Z11" t="n">
-        <v>1359988200</v>
+        <v>1383286905.9</v>
       </c>
     </row>
     <row r="12">
@@ -1451,7 +1451,7 @@
         <v>11.9113475177305</v>
       </c>
       <c r="K12" t="n">
-        <v>5404375.15</v>
+        <v>5424874.3</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>101.4219619852339</v>
       </c>
       <c r="Z12" t="n">
-        <v>1774702000</v>
+        <v>1818570181</v>
       </c>
     </row>
     <row r="13">
@@ -1537,7 +1537,7 @@
         <v>12.68167701863354</v>
       </c>
       <c r="K13" t="n">
-        <v>179263211.8</v>
+        <v>179763768.8</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>35.18863950277886</v>
       </c>
       <c r="Z13" t="n">
-        <v>23788095720</v>
+        <v>24159909459.6</v>
       </c>
     </row>
     <row r="14">
@@ -1623,7 +1623,7 @@
         <v>10.78242677824268</v>
       </c>
       <c r="K14" t="n">
-        <v>3518211.65</v>
+        <v>3537058.2</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>40.43300301886964</v>
       </c>
       <c r="Z14" t="n">
-        <v>644722020</v>
+        <v>660259115.8199999</v>
       </c>
     </row>
     <row r="15">
@@ -1709,7 +1709,7 @@
         <v>12.79770992366412</v>
       </c>
       <c r="K15" t="n">
-        <v>1814171.75</v>
+        <v>1836429.4</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>47.83673636323836</v>
       </c>
       <c r="Z15" t="n">
-        <v>168923250</v>
+        <v>190401882.25</v>
       </c>
     </row>
     <row r="16">
@@ -1795,7 +1795,7 @@
         <v>12.18093385214008</v>
       </c>
       <c r="K16" t="n">
-        <v>237609617.3</v>
+        <v>238119754</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>11.5920231841335</v>
       </c>
       <c r="Z16" t="n">
-        <v>11270985800</v>
+        <v>11396071318.84</v>
       </c>
     </row>
     <row r="17">
@@ -1881,7 +1881,7 @@
         <v>8.235294117647058</v>
       </c>
       <c r="K17" t="n">
-        <v>190734.35</v>
+        <v>190930.1</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>17.93076708307537</v>
       </c>
       <c r="Z17" t="n">
-        <v>6978260</v>
+        <v>7049591.3</v>
       </c>
     </row>
     <row r="18">
@@ -1967,7 +1967,7 @@
         <v>17.11294117647059</v>
       </c>
       <c r="K18" t="n">
-        <v>3461435.6</v>
+        <v>3462197.15</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
@@ -2010,7 +2010,7 @@
         <v>60.2903646059854</v>
       </c>
       <c r="Z18" t="n">
-        <v>145329000</v>
+        <v>146475894.3</v>
       </c>
     </row>
     <row r="19">
@@ -2049,7 +2049,7 @@
         <v>12.38297872340426</v>
       </c>
       <c r="K19" t="n">
-        <v>1087463.25</v>
+        <v>1100508.7</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>307.2647026801356</v>
       </c>
       <c r="Z19" t="n">
-        <v>1099964400</v>
+        <v>1184472825.1</v>
       </c>
     </row>
     <row r="20">
@@ -2135,7 +2135,7 @@
         <v>12.30882352941176</v>
       </c>
       <c r="K20" t="n">
-        <v>12886199.65</v>
+        <v>13027750.2</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>56.08771748970928</v>
       </c>
       <c r="Z20" t="n">
-        <v>1956208500</v>
+        <v>2117151475.35</v>
       </c>
     </row>
     <row r="21">
@@ -2221,7 +2221,7 @@
         <v>15.32921810699589</v>
       </c>
       <c r="K21" t="n">
-        <v>1209628.4</v>
+        <v>1220986.9</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>45.91670453916959</v>
       </c>
       <c r="Z21" t="n">
-        <v>169714560</v>
+        <v>180568742.6</v>
       </c>
     </row>
     <row r="22">
@@ -2307,7 +2307,7 @@
         <v>13.22463768115942</v>
       </c>
       <c r="K22" t="n">
-        <v>232812.05</v>
+        <v>233737.95</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>44.93786256853525</v>
       </c>
       <c r="Z22" t="n">
-        <v>22036520</v>
+        <v>22879644.54</v>
       </c>
     </row>
     <row r="23">
@@ -2393,7 +2393,7 @@
         <v>12.02409638554217</v>
       </c>
       <c r="K23" t="n">
-        <v>31873.85</v>
+        <v>31999.85</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>317.9105089140901</v>
       </c>
       <c r="Z23" t="n">
-        <v>19172050</v>
+        <v>19990924</v>
       </c>
     </row>
     <row r="24">
@@ -2479,7 +2479,7 @@
         <v>15.328125</v>
       </c>
       <c r="K24" t="n">
-        <v>17329178.3</v>
+        <v>17470914.1</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>49.10994993338472</v>
       </c>
       <c r="Z24" t="n">
-        <v>2269578150</v>
+        <v>2411172214.2</v>
       </c>
     </row>
     <row r="25">
@@ -2565,7 +2565,7 @@
         <v>14.18091809180918</v>
       </c>
       <c r="K25" t="n">
-        <v>19121497.55</v>
+        <v>19297789.9</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>61.62468904648811</v>
       </c>
       <c r="Z25" t="n">
-        <v>3469839900</v>
+        <v>3692497138.05</v>
       </c>
     </row>
     <row r="26">
@@ -2651,7 +2651,7 @@
         <v>13.81124497991968</v>
       </c>
       <c r="K26" t="n">
-        <v>1697643.65</v>
+        <v>1718688.75</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>98.79412752235244</v>
       </c>
       <c r="Z26" t="n">
-        <v>451935400</v>
+        <v>492615578.3</v>
       </c>
     </row>
     <row r="27">
@@ -2737,7 +2737,7 @@
         <v>13.46961651917404</v>
       </c>
       <c r="K27" t="n">
-        <v>101926809.7</v>
+        <v>105099319.6</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>106.3500989454521</v>
       </c>
       <c r="Z27" t="n">
-        <v>42464030400</v>
+        <v>49373756962.2</v>
       </c>
     </row>
     <row r="28">
@@ -2823,7 +2823,7 @@
         <v>13.83697478991597</v>
       </c>
       <c r="K28" t="n">
-        <v>317950.1</v>
+        <v>328744.35</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>237.612179298193</v>
       </c>
       <c r="Z28" t="n">
-        <v>337350000</v>
+        <v>389971968.75</v>
       </c>
     </row>
     <row r="29">
@@ -2909,7 +2909,7 @@
         <v>15.85892116182573</v>
       </c>
       <c r="K29" t="n">
-        <v>4445764.4</v>
+        <v>4456380.55</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>40.82501963992887</v>
       </c>
       <c r="Z29" t="n">
-        <v>331704880</v>
+        <v>340359165.48</v>
       </c>
     </row>
     <row r="30">
@@ -2995,7 +2995,7 @@
         <v>13.86703910614525</v>
       </c>
       <c r="K30" t="n">
-        <v>2805820.25</v>
+        <v>2928117.1</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>243.62520585821</v>
       </c>
       <c r="Z30" t="n">
-        <v>1949779600</v>
+        <v>2561508443.7</v>
       </c>
     </row>
   </sheetData>

--- a/ETF動態清單.xlsx
+++ b/ETF動態清單.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z30"/>
+  <dimension ref="A1:Z32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,16 +567,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7205039476765183</v>
+        <v>0.7255896520598688</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5497818013755811</v>
+        <v>0.5495491016136373</v>
       </c>
       <c r="E2" t="n">
-        <v>29.4</v>
+        <v>29.53</v>
       </c>
       <c r="F2" t="n">
-        <v>34.18</v>
+        <v>24.75</v>
       </c>
       <c r="G2" t="n">
         <v>41</v>
@@ -591,7 +591,7 @@
         <v>8.439024390243903</v>
       </c>
       <c r="K2" t="n">
-        <v>169181894.8</v>
+        <v>166974010.75</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         <v>386.28</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1707221463009372</v>
+        <v>0.1760405504462315</v>
       </c>
       <c r="S2" t="n">
         <v>1.67</v>
@@ -626,19 +626,19 @@
         <v>346</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9598432908912828</v>
+        <v>0.9630342263603305</v>
       </c>
       <c r="W2" t="n">
-        <v>1.053983089469733</v>
+        <v>1.054652605538069</v>
       </c>
       <c r="X2" t="n">
-        <v>30.63000000000001</v>
+        <v>30.66350000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>27.89418567881518</v>
+        <v>27.99974118959693</v>
       </c>
       <c r="Z2" t="n">
-        <v>11861647207.2</v>
+        <v>3540808322.39</v>
       </c>
     </row>
     <row r="3">
@@ -653,16 +653,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2231453995819146</v>
+        <v>0.2311331798365219</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2054871606186133</v>
+        <v>0.2055125030732763</v>
       </c>
       <c r="E3" t="n">
-        <v>18.28</v>
+        <v>18.42</v>
       </c>
       <c r="F3" t="n">
-        <v>43.48</v>
+        <v>31.99</v>
       </c>
       <c r="G3" t="n">
         <v>33</v>
@@ -677,7 +677,7 @@
         <v>10.27272727272727</v>
       </c>
       <c r="K3" t="n">
-        <v>48739331.45</v>
+        <v>50872547.3</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         <v>317.42</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01765823896330132</v>
+        <v>0.02562067676324564</v>
       </c>
       <c r="S3" t="n">
         <v>0.47</v>
@@ -712,19 +712,19 @@
         <v>339</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9648219987860562</v>
+        <v>0.9693716450899912</v>
       </c>
       <c r="W3" t="n">
-        <v>1.066380287693166</v>
+        <v>1.062304008630692</v>
       </c>
       <c r="X3" t="n">
-        <v>18.94649999999999</v>
+        <v>19.00199999999999</v>
       </c>
       <c r="Y3" t="n">
-        <v>17.14210231656099</v>
+        <v>17.33966910634494</v>
       </c>
       <c r="Z3" t="n">
-        <v>3028995305.36</v>
+        <v>1133795392.2</v>
       </c>
     </row>
     <row r="4">
@@ -739,16 +739,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.181887251638371</v>
+        <v>1.062780275554555</v>
       </c>
       <c r="D4" t="n">
-        <v>0.895268271485099</v>
+        <v>0.8953979892033781</v>
       </c>
       <c r="E4" t="n">
-        <v>37.34</v>
+        <v>35.3</v>
       </c>
       <c r="F4" t="n">
-        <v>29.6</v>
+        <v>20.68</v>
       </c>
       <c r="G4" t="n">
         <v>66</v>
@@ -763,7 +763,7 @@
         <v>10.33333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>11863214.7</v>
+        <v>12466215.35</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         <v>159.78</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2866189801532717</v>
+        <v>0.1673822863511771</v>
       </c>
       <c r="S4" t="n">
         <v>0.78</v>
@@ -798,19 +798,19 @@
         <v>682</v>
       </c>
       <c r="V4" t="n">
-        <v>0.944049756023563</v>
+        <v>0.8932638291411504</v>
       </c>
       <c r="W4" t="n">
-        <v>1.022931570044068</v>
+        <v>0.9725987873236147</v>
       </c>
       <c r="X4" t="n">
-        <v>39.55300000000002</v>
+        <v>39.51800000000001</v>
       </c>
       <c r="Y4" t="n">
-        <v>36.50293049259531</v>
+        <v>36.29451368856638</v>
       </c>
       <c r="Z4" t="n">
-        <v>1484798065.84</v>
+        <v>536836363.6999999</v>
       </c>
     </row>
     <row r="5">
@@ -825,16 +825,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6137872465393484</v>
+        <v>0.6170159499064141</v>
       </c>
       <c r="D5" t="n">
-        <v>0.592590124245038</v>
+        <v>0.592348436023842</v>
       </c>
       <c r="E5" t="n">
-        <v>24.5</v>
+        <v>24.58</v>
       </c>
       <c r="F5" t="n">
-        <v>37.91</v>
+        <v>28.51</v>
       </c>
       <c r="G5" t="n">
         <v>40</v>
@@ -849,7 +849,7 @@
         <v>9.824999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>8554822.550000001</v>
+        <v>8590319.1</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>246.15</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02119712229431037</v>
+        <v>0.02466751388257205</v>
       </c>
       <c r="S5" t="n">
         <v>1.814</v>
@@ -884,19 +884,19 @@
         <v>393</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9604829857299676</v>
+        <v>0.962016398896304</v>
       </c>
       <c r="W5" t="n">
-        <v>1.035582973345717</v>
+        <v>1.031403705040077</v>
       </c>
       <c r="X5" t="n">
-        <v>25.50799999999998</v>
+        <v>25.55049999999998</v>
       </c>
       <c r="Y5" t="n">
-        <v>23.65817189987825</v>
+        <v>23.83159947931823</v>
       </c>
       <c r="Z5" t="n">
-        <v>462182847</v>
+        <v>145144924.58</v>
       </c>
     </row>
     <row r="6">
@@ -911,16 +911,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.4938936419142597</v>
+        <v>0.4987261442170574</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4645873966600014</v>
+        <v>0.4643816745978988</v>
       </c>
       <c r="E6" t="n">
-        <v>23.04</v>
+        <v>23.14</v>
       </c>
       <c r="F6" t="n">
-        <v>28.28</v>
+        <v>21.1</v>
       </c>
       <c r="G6" t="n">
         <v>37</v>
@@ -935,7 +935,7 @@
         <v>9.972972972972974</v>
       </c>
       <c r="K6" t="n">
-        <v>45952589.7</v>
+        <v>53732129.7</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         <v>252.13</v>
       </c>
       <c r="R6" t="n">
-        <v>0.02930624525425829</v>
+        <v>0.0343444696191586</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -970,144 +970,144 @@
         <v>369</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9773271967592098</v>
+        <v>0.9799686613306227</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0347467213535</v>
+        <v>1.032685622593113</v>
       </c>
       <c r="X6" t="n">
-        <v>23.57450000000001</v>
+        <v>23.61300000000001</v>
       </c>
       <c r="Y6" t="n">
-        <v>22.26631843767771</v>
+        <v>22.40759384438274</v>
       </c>
       <c r="Z6" t="n">
-        <v>4529795673.599999</v>
+        <v>3634093195.98</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>009816.TW</t>
+          <t>00410A.TW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>凱基台灣TOP50</t>
+          <t>主動永豐科技趨勢</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.1881787786263047</v>
+        <v>0.01465696374479331</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1549200544580014</v>
+        <v>0.0084235501626031</v>
       </c>
       <c r="E7" t="n">
-        <v>16.19</v>
+        <v>11.97</v>
       </c>
       <c r="F7" t="n">
-        <v>35.02</v>
+        <v>25.16</v>
       </c>
       <c r="G7" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
         <v>100</v>
       </c>
       <c r="I7" t="n">
-        <v>5.32</v>
+        <v>5.53</v>
       </c>
       <c r="J7" t="n">
-        <v>10.54166666666667</v>
+        <v>7.6</v>
       </c>
       <c r="K7" t="n">
-        <v>120397877.55</v>
+        <v>5509246.85</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>2</v>
       </c>
       <c r="N7" t="n">
-        <v>8.99</v>
+        <v>5.92</v>
       </c>
       <c r="O7" t="n">
-        <v>0.64</v>
+        <v>4.92</v>
       </c>
       <c r="P7" t="n">
-        <v>9.630000000000001</v>
+        <v>10.84</v>
       </c>
       <c r="Q7" t="n">
-        <v>227.93</v>
+        <v>942.39</v>
       </c>
       <c r="R7" t="n">
-        <v>0.03325872416830333</v>
+        <v>0.006233413582190206</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>127.78</v>
+        <v>27.64</v>
       </c>
       <c r="U7" t="n">
-        <v>253</v>
+        <v>38</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9798462748895478</v>
+        <v>0.9624120603015073</v>
       </c>
       <c r="W7" t="n">
-        <v>1.023707094574467</v>
+        <v>1.03918573634375</v>
       </c>
       <c r="X7" t="n">
-        <v>16.523</v>
+        <v>12.4375</v>
       </c>
       <c r="Y7" t="n">
-        <v>15.81507062499145</v>
+        <v>11.51863385087925</v>
       </c>
       <c r="Z7" t="n">
-        <v>6174896534.34</v>
+        <v>223274566.62</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>009804.TW</t>
+          <t>009816.TW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>聯邦台精彩50</t>
+          <t>凱基台灣TOP50</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.6441778521262456</v>
+        <v>0.1877881951291229</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6294955437664567</v>
+        <v>0.1550481558448826</v>
       </c>
       <c r="E8" t="n">
-        <v>23.21</v>
+        <v>16.2</v>
       </c>
       <c r="F8" t="n">
-        <v>30.51</v>
+        <v>24.08</v>
       </c>
       <c r="G8" t="n">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="H8" t="n">
         <v>100</v>
       </c>
       <c r="I8" t="n">
-        <v>4.12</v>
+        <v>5.32</v>
       </c>
       <c r="J8" t="n">
-        <v>8.82258064516129</v>
+        <v>10.54166666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>1149921.7</v>
+        <v>122203861</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1118,168 +1118,168 @@
         <v>2</v>
       </c>
       <c r="N8" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="P8" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="O8" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="P8" t="n">
-        <v>10.39</v>
-      </c>
       <c r="Q8" t="n">
-        <v>133.05</v>
+        <v>227.93</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0146823083597889</v>
+        <v>0.0327400392842403</v>
       </c>
       <c r="S8" t="n">
-        <v>2.786</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>255.36</v>
+        <v>127.78</v>
       </c>
       <c r="U8" t="n">
-        <v>547</v>
+        <v>253</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9693248971580114</v>
+        <v>0.9791181892357438</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02316665365645</v>
+        <v>1.018057953984275</v>
       </c>
       <c r="X8" t="n">
-        <v>23.9445</v>
+        <v>16.5455</v>
       </c>
       <c r="Y8" t="n">
-        <v>22.6844765875191</v>
+        <v>15.9126500967844</v>
       </c>
       <c r="Z8" t="n">
-        <v>44223916.22</v>
+        <v>2065562856</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>00830.TW</t>
+          <t>009824.TW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>國泰費城半導體</t>
+          <t>群益美國科技巨頭</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.458987228857474</v>
+        <v>0.02962496414078353</v>
       </c>
       <c r="D9" t="n">
-        <v>2.302497611714684</v>
+        <v>0.02427670054395836</v>
       </c>
       <c r="E9" t="n">
-        <v>83.34999999999999</v>
+        <v>10.46</v>
       </c>
       <c r="F9" t="n">
-        <v>31.72</v>
+        <v>34.6</v>
       </c>
       <c r="G9" t="n">
-        <v>495</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>97.17</v>
+        <v>100</v>
       </c>
       <c r="I9" t="n">
-        <v>3.93</v>
+        <v>5.26</v>
       </c>
       <c r="J9" t="n">
-        <v>12.29090909090909</v>
+        <v>5.75</v>
       </c>
       <c r="K9" t="n">
-        <v>9479141.9</v>
+        <v>5497301.8</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>13.29</v>
+        <v>7.35</v>
       </c>
       <c r="O9" t="n">
-        <v>-12.33</v>
+        <v>1.39</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9599999999999991</v>
+        <v>8.74</v>
       </c>
       <c r="Q9" t="n">
-        <v>19.85</v>
+        <v>1975.8</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1564896171427894</v>
+        <v>0.005348263596825165</v>
       </c>
       <c r="S9" t="n">
-        <v>17.71</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1946.3</v>
+        <v>21.06</v>
       </c>
       <c r="U9" t="n">
-        <v>6084</v>
+        <v>23</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9560404897771916</v>
+        <v>0.9916571861964349</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06147425715696</v>
+        <v>1.040831361411564</v>
       </c>
       <c r="X9" t="n">
-        <v>87.18249999999999</v>
+        <v>10.54800000000001</v>
       </c>
       <c r="Y9" t="n">
-        <v>78.52286519245759</v>
+        <v>10.0496587514564</v>
       </c>
       <c r="Z9" t="n">
-        <v>1763915795.95</v>
+        <v>23451435.06</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>009818.TW</t>
+          <t>009804.TW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>華南永昌NASDAQxT</t>
+          <t>聯邦台精彩50</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.1048090446430547</v>
+        <v>0.6527690309145673</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1032440051411441</v>
+        <v>0.6292409931374718</v>
       </c>
       <c r="E10" t="n">
-        <v>20.88</v>
+        <v>23.37</v>
       </c>
       <c r="F10" t="n">
-        <v>48.65</v>
+        <v>25.13</v>
       </c>
       <c r="G10" t="n">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="H10" t="n">
         <v>100</v>
       </c>
       <c r="I10" t="n">
-        <v>3.81</v>
+        <v>4.12</v>
       </c>
       <c r="J10" t="n">
-        <v>8.714285714285714</v>
+        <v>8.82258064516129</v>
       </c>
       <c r="K10" t="n">
-        <v>182318.65</v>
+        <v>1168846.5</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1290,168 +1290,168 @@
         <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>7.21</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>1.65</v>
+        <v>0.76</v>
       </c>
       <c r="P10" t="n">
-        <v>8.859999999999999</v>
+        <v>10.39</v>
       </c>
       <c r="Q10" t="n">
-        <v>222.85</v>
+        <v>133.05</v>
       </c>
       <c r="R10" t="n">
-        <v>0.00156503950191067</v>
+        <v>0.02352803777709545</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.786</v>
       </c>
       <c r="T10" t="n">
-        <v>79.97</v>
+        <v>255.36</v>
       </c>
       <c r="U10" t="n">
-        <v>183</v>
+        <v>547</v>
       </c>
       <c r="V10" t="n">
-        <v>0.99215965787598</v>
+        <v>0.974562135112594</v>
       </c>
       <c r="W10" t="n">
-        <v>1.047933962657891</v>
+        <v>1.023577788618202</v>
       </c>
       <c r="X10" t="n">
-        <v>21.045</v>
+        <v>23.98</v>
       </c>
       <c r="Y10" t="n">
-        <v>19.92491964573964</v>
+        <v>22.83167948725105</v>
       </c>
       <c r="Z10" t="n">
-        <v>8119396.8</v>
+        <v>23734548.63</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>00400A.TW</t>
+          <t>00830.TW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>主動國泰動能高息</t>
+          <t>國泰費城半導體</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.08649947639092126</v>
+        <v>2.478722479910694</v>
       </c>
       <c r="D11" t="n">
-        <v>0.07311764947292709</v>
+        <v>2.304183650310986</v>
       </c>
       <c r="E11" t="n">
-        <v>14.94</v>
+        <v>83.95</v>
       </c>
       <c r="F11" t="n">
-        <v>32.65</v>
+        <v>25.6</v>
       </c>
       <c r="G11" t="n">
-        <v>16</v>
+        <v>495</v>
       </c>
       <c r="H11" t="n">
-        <v>68.75</v>
+        <v>97.17</v>
       </c>
       <c r="I11" t="n">
-        <v>3.77</v>
+        <v>3.93</v>
       </c>
       <c r="J11" t="n">
-        <v>13.1875</v>
+        <v>12.29090909090909</v>
       </c>
       <c r="K11" t="n">
-        <v>37377468.1</v>
+        <v>9602204.550000001</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>13.12</v>
+        <v>13.29</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.83</v>
+        <v>-12.33</v>
       </c>
       <c r="P11" t="n">
-        <v>12.29</v>
+        <v>0.9599999999999991</v>
       </c>
       <c r="Q11" t="n">
-        <v>126.3</v>
+        <v>19.85</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01338182691799417</v>
+        <v>0.1745388295997077</v>
       </c>
       <c r="S11" t="n">
-        <v>0.48</v>
+        <v>17.71</v>
       </c>
       <c r="T11" t="n">
-        <v>60.34</v>
+        <v>1946.3</v>
       </c>
       <c r="U11" t="n">
-        <v>211</v>
+        <v>6084</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9598766423592145</v>
+        <v>0.9601967288116209</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04435641155437</v>
+        <v>1.056441757249984</v>
       </c>
       <c r="X11" t="n">
-        <v>15.5645</v>
+        <v>87.42999999999999</v>
       </c>
       <c r="Y11" t="n">
-        <v>14.30546108082395</v>
+        <v>79.46486346633029</v>
       </c>
       <c r="Z11" t="n">
-        <v>1383286905.9</v>
+        <v>1271012318.45</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>00663L.TW</t>
+          <t>009818.TW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>國泰臺灣加權正2</t>
+          <t>華南永昌NASDAQxT</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11.78378313523225</v>
+        <v>0.1156296842849658</v>
       </c>
       <c r="D12" t="n">
-        <v>2.98855211972696</v>
+        <v>0.103519499132803</v>
       </c>
       <c r="E12" t="n">
-        <v>107</v>
+        <v>21.1</v>
       </c>
       <c r="F12" t="n">
-        <v>35.43</v>
+        <v>44.03</v>
       </c>
       <c r="G12" t="n">
-        <v>564</v>
+        <v>21</v>
       </c>
       <c r="H12" t="n">
-        <v>89.89</v>
+        <v>100</v>
       </c>
       <c r="I12" t="n">
-        <v>3.76</v>
+        <v>3.81</v>
       </c>
       <c r="J12" t="n">
-        <v>11.9113475177305</v>
+        <v>8.714285714285714</v>
       </c>
       <c r="K12" t="n">
-        <v>5424874.3</v>
+        <v>177723.05</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1462,340 +1462,340 @@
         <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>15.99</v>
+        <v>7.21</v>
       </c>
       <c r="O12" t="n">
-        <v>-24.46</v>
+        <v>1.65</v>
       </c>
       <c r="P12" t="n">
-        <v>-8.470000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>18.35</v>
+        <v>222.85</v>
       </c>
       <c r="R12" t="n">
-        <v>8.795231015505291</v>
+        <v>0.01211018515216278</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2121.97</v>
+        <v>79.97</v>
       </c>
       <c r="U12" t="n">
-        <v>6718</v>
+        <v>183</v>
       </c>
       <c r="V12" t="n">
-        <v>0.9501398570350302</v>
+        <v>0.9998815306243337</v>
       </c>
       <c r="W12" t="n">
-        <v>1.054998324875417</v>
+        <v>1.049676926661034</v>
       </c>
       <c r="X12" t="n">
-        <v>112.6150000000001</v>
+        <v>21.1025</v>
       </c>
       <c r="Y12" t="n">
-        <v>101.4219619852339</v>
+        <v>20.10142307987847</v>
       </c>
       <c r="Z12" t="n">
-        <v>1818570181</v>
+        <v>2121415.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>00631L.TW</t>
+          <t>00400A.TW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>主動國泰動能高息</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15.81462527384705</v>
+        <v>0.09077376921705294</v>
       </c>
       <c r="D13" t="n">
-        <v>3.412594486979345</v>
+        <v>0.07353434444261109</v>
       </c>
       <c r="E13" t="n">
-        <v>37.14</v>
+        <v>15.01</v>
       </c>
       <c r="F13" t="n">
-        <v>32.67</v>
+        <v>23.82</v>
       </c>
       <c r="G13" t="n">
-        <v>644</v>
+        <v>16</v>
       </c>
       <c r="H13" t="n">
-        <v>89.44</v>
+        <v>68.75</v>
       </c>
       <c r="I13" t="n">
-        <v>3.74</v>
+        <v>3.77</v>
       </c>
       <c r="J13" t="n">
-        <v>12.68167701863354</v>
+        <v>13.1875</v>
       </c>
       <c r="K13" t="n">
-        <v>179763768.8</v>
+        <v>37244546.85</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>2</v>
       </c>
       <c r="N13" t="n">
-        <v>17.37</v>
+        <v>13.12</v>
       </c>
       <c r="O13" t="n">
-        <v>-12.43</v>
+        <v>-0.83</v>
       </c>
       <c r="P13" t="n">
-        <v>4.940000000000001</v>
+        <v>12.29</v>
       </c>
       <c r="Q13" t="n">
-        <v>15.49</v>
+        <v>126.3</v>
       </c>
       <c r="R13" t="n">
-        <v>12.4020307868677</v>
+        <v>0.01723942477444185</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="T13" t="n">
-        <v>2407.1</v>
+        <v>60.34</v>
       </c>
       <c r="U13" t="n">
-        <v>8167</v>
+        <v>211</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9532854209445588</v>
+        <v>0.9625496986020262</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05545427515227</v>
+        <v>1.04100574061017</v>
       </c>
       <c r="X13" t="n">
-        <v>38.95999999999999</v>
+        <v>15.594</v>
       </c>
       <c r="Y13" t="n">
-        <v>35.18863950277886</v>
+        <v>14.41874853754612</v>
       </c>
       <c r="Z13" t="n">
-        <v>24159909459.6</v>
+        <v>414207809.57</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>00904.TW</t>
+          <t>00663L.TW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>台新臺灣半導體30</t>
+          <t>國泰臺灣加權正2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.796820086612032</v>
+        <v>11.85068554150096</v>
       </c>
       <c r="D14" t="n">
-        <v>1.71251094841077</v>
+        <v>2.990905571760063</v>
       </c>
       <c r="E14" t="n">
-        <v>41.22</v>
+        <v>107.6</v>
       </c>
       <c r="F14" t="n">
-        <v>27.83</v>
+        <v>25.68</v>
       </c>
       <c r="G14" t="n">
-        <v>239</v>
+        <v>564</v>
       </c>
       <c r="H14" t="n">
-        <v>99.16</v>
+        <v>89.89</v>
       </c>
       <c r="I14" t="n">
-        <v>3.55</v>
+        <v>3.76</v>
       </c>
       <c r="J14" t="n">
-        <v>10.78242677824268</v>
+        <v>11.9113475177305</v>
       </c>
       <c r="K14" t="n">
-        <v>3537058.2</v>
+        <v>5490061.25</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>11.85</v>
+        <v>15.99</v>
       </c>
       <c r="O14" t="n">
-        <v>-12.45</v>
+        <v>-24.46</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.5999999999999996</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>37.53</v>
+        <v>18.35</v>
       </c>
       <c r="R14" t="n">
-        <v>0.08430913820126129</v>
+        <v>8.859779969740895</v>
       </c>
       <c r="S14" t="n">
-        <v>4.850000000000001</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>848.62</v>
+        <v>2121.97</v>
       </c>
       <c r="U14" t="n">
-        <v>2577</v>
+        <v>6718</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9567578859410905</v>
+        <v>0.9526760812784977</v>
       </c>
       <c r="W14" t="n">
-        <v>1.019464222846942</v>
+        <v>1.046680500137607</v>
       </c>
       <c r="X14" t="n">
-        <v>43.083</v>
+        <v>112.9450000000001</v>
       </c>
       <c r="Y14" t="n">
-        <v>40.43300301886964</v>
+        <v>102.8011890790493</v>
       </c>
       <c r="Z14" t="n">
-        <v>660259115.8199999</v>
+        <v>524698703.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>00913.TW</t>
+          <t>00631L.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>兆豐台灣晶圓製造</t>
+          <t>元大台灣50正2</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.644147697334891</v>
+        <v>15.81371276293106</v>
       </c>
       <c r="D15" t="n">
-        <v>1.619496059933628</v>
+        <v>3.41535122330414</v>
       </c>
       <c r="E15" t="n">
-        <v>48.25</v>
+        <v>37.15</v>
       </c>
       <c r="F15" t="n">
-        <v>25.63</v>
+        <v>22.13</v>
       </c>
       <c r="G15" t="n">
-        <v>262</v>
+        <v>644</v>
       </c>
       <c r="H15" t="n">
-        <v>96.18000000000001</v>
+        <v>89.44</v>
       </c>
       <c r="I15" t="n">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="J15" t="n">
-        <v>12.79770992366412</v>
+        <v>12.68167701863354</v>
       </c>
       <c r="K15" t="n">
-        <v>1836429.4</v>
+        <v>183487320.25</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>13.5</v>
+        <v>17.37</v>
       </c>
       <c r="O15" t="n">
-        <v>-9.19</v>
+        <v>-12.43</v>
       </c>
       <c r="P15" t="n">
-        <v>4.31</v>
+        <v>4.940000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>28.72</v>
+        <v>15.49</v>
       </c>
       <c r="R15" t="n">
-        <v>0.02465163740126375</v>
+        <v>12.39836153962693</v>
       </c>
       <c r="S15" t="n">
-        <v>6.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>916.5599999999999</v>
+        <v>2407.1</v>
       </c>
       <c r="U15" t="n">
-        <v>3353</v>
+        <v>8167</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9299232933739354</v>
+        <v>0.9510278268438168</v>
       </c>
       <c r="W15" t="n">
-        <v>1.008639043299769</v>
+        <v>1.042895193356935</v>
       </c>
       <c r="X15" t="n">
-        <v>51.88599999999999</v>
+        <v>39.06299999999998</v>
       </c>
       <c r="Y15" t="n">
-        <v>47.83673636323836</v>
+        <v>35.62198793957357</v>
       </c>
       <c r="Z15" t="n">
-        <v>190401882.25</v>
+        <v>6508238806.599999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>00685L.TW</t>
+          <t>00913.TW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>群益臺灣加權正2</t>
+          <t>兆豐台灣晶圓製造</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10.67502778467844</v>
+        <v>1.658344663775718</v>
       </c>
       <c r="D16" t="n">
-        <v>2.817107345266162</v>
+        <v>1.620251159374102</v>
       </c>
       <c r="E16" t="n">
-        <v>12.26</v>
+        <v>48.57</v>
       </c>
       <c r="F16" t="n">
-        <v>34.6</v>
+        <v>19.54</v>
       </c>
       <c r="G16" t="n">
-        <v>514</v>
+        <v>262</v>
       </c>
       <c r="H16" t="n">
-        <v>88.52</v>
+        <v>96.18000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="J16" t="n">
-        <v>12.18093385214008</v>
+        <v>12.79770992366412</v>
       </c>
       <c r="K16" t="n">
-        <v>238119754</v>
+        <v>1849223.85</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1806,82 +1806,82 @@
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>15.89</v>
+        <v>13.5</v>
       </c>
       <c r="O16" t="n">
-        <v>-18.5</v>
+        <v>-9.19</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.609999999999999</v>
+        <v>4.31</v>
       </c>
       <c r="Q16" t="n">
-        <v>18.65</v>
+        <v>28.72</v>
       </c>
       <c r="R16" t="n">
-        <v>7.857920439412277</v>
+        <v>0.03809350440161641</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>6.699999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>1777.84</v>
+        <v>916.5599999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>6261</v>
+        <v>3353</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9514201458947694</v>
+        <v>0.9350994397489462</v>
       </c>
       <c r="W16" t="n">
-        <v>1.057623833670449</v>
+        <v>1.009580139389076</v>
       </c>
       <c r="X16" t="n">
-        <v>12.886</v>
+        <v>51.94099999999999</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.5920231841335</v>
+        <v>48.1091080391013</v>
       </c>
       <c r="Z16" t="n">
-        <v>11396071318.84</v>
+        <v>54817996.23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>009809.TW</t>
+          <t>00685L.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>富邦淨零ESG50</t>
+          <t>群益臺灣加權正2</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.3665561855062192</v>
+        <v>10.72745992536771</v>
       </c>
       <c r="D17" t="n">
-        <v>0.326851662852756</v>
+        <v>2.819281252814454</v>
       </c>
       <c r="E17" t="n">
-        <v>18.22</v>
+        <v>12.32</v>
       </c>
       <c r="F17" t="n">
-        <v>32.57</v>
+        <v>24.29</v>
       </c>
       <c r="G17" t="n">
-        <v>34</v>
+        <v>514</v>
       </c>
       <c r="H17" t="n">
-        <v>97.06</v>
+        <v>88.52</v>
       </c>
       <c r="I17" t="n">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="J17" t="n">
-        <v>8.235294117647058</v>
+        <v>12.18093385214008</v>
       </c>
       <c r="K17" t="n">
-        <v>190930.1</v>
+        <v>241723801.8</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1892,340 +1892,340 @@
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>7.76</v>
+        <v>15.89</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.12</v>
+        <v>-18.5</v>
       </c>
       <c r="P17" t="n">
-        <v>7.64</v>
+        <v>-2.609999999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>172.16</v>
+        <v>18.65</v>
       </c>
       <c r="R17" t="n">
-        <v>0.03970452265346314</v>
+        <v>7.908178672553253</v>
       </c>
       <c r="S17" t="n">
-        <v>0.315</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>115.56</v>
+        <v>1777.84</v>
       </c>
       <c r="U17" t="n">
-        <v>280</v>
+        <v>6261</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9808090867493875</v>
+        <v>0.9532283647336454</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01613053783949</v>
+        <v>1.048361971452616</v>
       </c>
       <c r="X17" t="n">
-        <v>18.5765</v>
+        <v>12.9245</v>
       </c>
       <c r="Y17" t="n">
-        <v>17.93076708307537</v>
+        <v>11.75166625219087</v>
       </c>
       <c r="Z17" t="n">
-        <v>7049591.3</v>
+        <v>2639403215.68</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>00715L.TW</t>
+          <t>009809.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>期街口布蘭特正2</t>
+          <t>富邦淨零ESG50</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.058991702425611</v>
+        <v>0.3687387630861929</v>
       </c>
       <c r="D18" t="n">
-        <v>2.67503331876492</v>
+        <v>0.3267215405451394</v>
       </c>
       <c r="E18" t="n">
-        <v>75.3</v>
+        <v>18.27</v>
       </c>
       <c r="F18" t="n">
-        <v>83.73999999999999</v>
+        <v>23.89</v>
       </c>
       <c r="G18" t="n">
-        <v>425</v>
+        <v>34</v>
       </c>
       <c r="H18" t="n">
-        <v>77.65000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="I18" t="n">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="J18" t="n">
-        <v>17.11294117647059</v>
+        <v>8.235294117647058</v>
       </c>
       <c r="K18" t="n">
-        <v>3462197.15</v>
-      </c>
-      <c r="L18" t="inlineStr"/>
+        <v>205449.65</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>32.14</v>
+        <v>7.76</v>
       </c>
       <c r="O18" t="n">
-        <v>-44.86</v>
+        <v>-0.12</v>
       </c>
       <c r="P18" t="n">
-        <v>-12.72</v>
+        <v>7.64</v>
       </c>
       <c r="Q18" t="n">
-        <v>14.59</v>
+        <v>172.16</v>
       </c>
       <c r="R18" t="n">
-        <v>2.383958383660691</v>
+        <v>0.04201722254105356</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
       <c r="T18" t="n">
-        <v>1409.31</v>
+        <v>115.56</v>
       </c>
       <c r="U18" t="n">
-        <v>7273</v>
+        <v>280</v>
       </c>
       <c r="V18" t="n">
-        <v>1.091739461379536</v>
+        <v>0.9826542960871316</v>
       </c>
       <c r="W18" t="n">
-        <v>1.248955790732181</v>
+        <v>1.015245590929712</v>
       </c>
       <c r="X18" t="n">
-        <v>68.97249999999994</v>
+        <v>18.5925</v>
       </c>
       <c r="Y18" t="n">
-        <v>60.2903646059854</v>
+        <v>17.99564574643386</v>
       </c>
       <c r="Z18" t="n">
-        <v>146475894.3</v>
+        <v>6179571.72</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>00675L.TW</t>
+          <t>00715L.TW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>富邦臺灣加權正2</t>
+          <t>期街口布蘭特正2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>11.20358322766104</v>
+        <v>5.165222188860139</v>
       </c>
       <c r="D19" t="n">
-        <v>2.924510748817748</v>
+        <v>2.677077241273147</v>
       </c>
       <c r="E19" t="n">
-        <v>323.9</v>
+        <v>76.65000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>34.76</v>
+        <v>83.13</v>
       </c>
       <c r="G19" t="n">
-        <v>564</v>
+        <v>425</v>
       </c>
       <c r="H19" t="n">
-        <v>87.06</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>3.18</v>
+        <v>3.32</v>
       </c>
       <c r="J19" t="n">
-        <v>12.38297872340426</v>
+        <v>17.11294117647059</v>
       </c>
       <c r="K19" t="n">
-        <v>1100508.7</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
+        <v>3358093.8</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>15.7</v>
+        <v>32.14</v>
       </c>
       <c r="O19" t="n">
-        <v>-24.73</v>
+        <v>-44.86</v>
       </c>
       <c r="P19" t="n">
-        <v>-9.030000000000001</v>
+        <v>-12.72</v>
       </c>
       <c r="Q19" t="n">
-        <v>16.61</v>
+        <v>14.59</v>
       </c>
       <c r="R19" t="n">
-        <v>8.279072478843293</v>
+        <v>2.488144947586992</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1792.47</v>
+        <v>1409.31</v>
       </c>
       <c r="U19" t="n">
-        <v>6984</v>
+        <v>7273</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9491992322006823</v>
+        <v>1.107099010616019</v>
       </c>
       <c r="W19" t="n">
-        <v>1.054139955467589</v>
+        <v>1.277993965285937</v>
       </c>
       <c r="X19" t="n">
-        <v>341.2350000000002</v>
+        <v>69.23499999999994</v>
       </c>
       <c r="Y19" t="n">
-        <v>307.2647026801356</v>
+        <v>59.9768090319976</v>
       </c>
       <c r="Z19" t="n">
-        <v>1184472825.1</v>
+        <v>134777680.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>00935.TW</t>
+          <t>00401A.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>野村臺灣新科技50</t>
+          <t>主動摩根台灣鑫收</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.444612916212354</v>
+        <v>0.0716527544242318</v>
       </c>
       <c r="D20" t="n">
-        <v>1.139957781524034</v>
+        <v>0.07114066577626521</v>
       </c>
       <c r="E20" t="n">
-        <v>56.85</v>
+        <v>13.82</v>
       </c>
       <c r="F20" t="n">
-        <v>28.59</v>
+        <v>28.73</v>
       </c>
       <c r="G20" t="n">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="H20" t="n">
-        <v>83.09</v>
+        <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>3.15</v>
+        <v>3.23</v>
       </c>
       <c r="J20" t="n">
-        <v>12.30882352941176</v>
+        <v>15.19047619047619</v>
       </c>
       <c r="K20" t="n">
-        <v>13027750.2</v>
+        <v>6995277.45</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>14.6</v>
+        <v>11.76</v>
       </c>
       <c r="O20" t="n">
-        <v>-8.99</v>
+        <v>0.36</v>
       </c>
       <c r="P20" t="n">
-        <v>5.609999999999999</v>
+        <v>12.12</v>
       </c>
       <c r="Q20" t="n">
-        <v>43.74</v>
+        <v>80.95</v>
       </c>
       <c r="R20" t="n">
-        <v>0.30465513468832</v>
+        <v>0.0005120886479665909</v>
       </c>
       <c r="S20" t="n">
-        <v>4.98</v>
+        <v>0.377</v>
       </c>
       <c r="T20" t="n">
-        <v>428.12</v>
+        <v>67.92</v>
       </c>
       <c r="U20" t="n">
-        <v>1674</v>
+        <v>319</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9401356044319497</v>
+        <v>0.9677193473846365</v>
       </c>
       <c r="W20" t="n">
-        <v>1.013590899120304</v>
+        <v>1.006003017296597</v>
       </c>
       <c r="X20" t="n">
-        <v>60.47000000000001</v>
+        <v>14.28100000000001</v>
       </c>
       <c r="Y20" t="n">
-        <v>56.08771748970928</v>
+        <v>13.73753334968924</v>
       </c>
       <c r="Z20" t="n">
-        <v>2117151475.35</v>
+        <v>105251945.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>00894.TW</t>
+          <t>00675L.TW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>中信小資高價30</t>
+          <t>富邦臺灣加權正2</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.076170136134475</v>
+        <v>11.27055046677457</v>
       </c>
       <c r="D21" t="n">
-        <v>1.763438952641097</v>
+        <v>2.926815596457504</v>
       </c>
       <c r="E21" t="n">
-        <v>47.78</v>
+        <v>325.8</v>
       </c>
       <c r="F21" t="n">
-        <v>35.64</v>
+        <v>25.1</v>
       </c>
       <c r="G21" t="n">
-        <v>243</v>
+        <v>564</v>
       </c>
       <c r="H21" t="n">
-        <v>82.72</v>
+        <v>87.06</v>
       </c>
       <c r="I21" t="n">
-        <v>2.88</v>
+        <v>3.18</v>
       </c>
       <c r="J21" t="n">
-        <v>15.32921810699589</v>
+        <v>12.38297872340426</v>
       </c>
       <c r="K21" t="n">
-        <v>1220986.9</v>
+        <v>1135452.95</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M21" t="n">
@@ -2235,79 +2235,79 @@
         <v>15.7</v>
       </c>
       <c r="O21" t="n">
-        <v>-8.380000000000001</v>
+        <v>-24.73</v>
       </c>
       <c r="P21" t="n">
-        <v>7.319999999999999</v>
+        <v>-9.030000000000001</v>
       </c>
       <c r="Q21" t="n">
-        <v>22.58</v>
+        <v>16.61</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3127311834933781</v>
+        <v>8.343734870317068</v>
       </c>
       <c r="S21" t="n">
-        <v>7.549999999999999</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>698.73</v>
+        <v>1792.47</v>
       </c>
       <c r="U21" t="n">
-        <v>3725</v>
+        <v>6984</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9590429642416278</v>
+        <v>0.9520469886911541</v>
       </c>
       <c r="W21" t="n">
-        <v>1.040579903970262</v>
+        <v>1.046486786764947</v>
       </c>
       <c r="X21" t="n">
-        <v>49.82049999999998</v>
+        <v>342.2100000000002</v>
       </c>
       <c r="Y21" t="n">
-        <v>45.91670453916959</v>
+        <v>311.3273900066722</v>
       </c>
       <c r="Z21" t="n">
-        <v>180568742.6</v>
+        <v>380264963.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>00901.TW</t>
+          <t>00935.TW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>永豐智能車供應鏈</t>
+          <t>野村臺灣新科技50</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.788118206173358</v>
+        <v>1.448598760881438</v>
       </c>
       <c r="D22" t="n">
-        <v>1.7288256294119</v>
+        <v>1.14028886333536</v>
       </c>
       <c r="E22" t="n">
-        <v>45.53</v>
+        <v>57</v>
       </c>
       <c r="F22" t="n">
-        <v>29</v>
+        <v>20.7</v>
       </c>
       <c r="G22" t="n">
-        <v>276</v>
+        <v>136</v>
       </c>
       <c r="H22" t="n">
-        <v>89.48999999999999</v>
+        <v>83.09</v>
       </c>
       <c r="I22" t="n">
-        <v>2.79</v>
+        <v>3.15</v>
       </c>
       <c r="J22" t="n">
-        <v>13.22463768115942</v>
+        <v>12.30882352941176</v>
       </c>
       <c r="K22" t="n">
-        <v>233737.95</v>
+        <v>12874184.75</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -2318,82 +2318,82 @@
         <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>15.18</v>
+        <v>14.6</v>
       </c>
       <c r="O22" t="n">
-        <v>-7.3</v>
+        <v>-8.99</v>
       </c>
       <c r="P22" t="n">
-        <v>7.88</v>
+        <v>5.609999999999999</v>
       </c>
       <c r="Q22" t="n">
-        <v>24.17</v>
+        <v>43.74</v>
       </c>
       <c r="R22" t="n">
-        <v>0.05929257676145827</v>
+        <v>0.3083098975460787</v>
       </c>
       <c r="S22" t="n">
-        <v>4.671</v>
+        <v>4.98</v>
       </c>
       <c r="T22" t="n">
-        <v>771.28</v>
+        <v>428.12</v>
       </c>
       <c r="U22" t="n">
-        <v>3650</v>
+        <v>1674</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9486602491978163</v>
+        <v>0.9429280397022332</v>
       </c>
       <c r="W22" t="n">
-        <v>1.013176804538972</v>
+        <v>1.017700783615503</v>
       </c>
       <c r="X22" t="n">
-        <v>47.99400000000001</v>
+        <v>60.45</v>
       </c>
       <c r="Y22" t="n">
-        <v>44.93786256853525</v>
+        <v>56.00860382312048</v>
       </c>
       <c r="Z22" t="n">
-        <v>22879644.54</v>
+        <v>571879062</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>0057.TW</t>
+          <t>00894.TW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>富邦摩台</t>
+          <t>中信小資高價30</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6.211365795691149</v>
+        <v>2.077371287842047</v>
       </c>
       <c r="D23" t="n">
-        <v>4.936435554359588</v>
+        <v>1.764513564068301</v>
       </c>
       <c r="E23" t="n">
-        <v>324.95</v>
+        <v>47.83</v>
       </c>
       <c r="F23" t="n">
-        <v>33.13</v>
+        <v>27.09</v>
       </c>
       <c r="G23" t="n">
-        <v>1245</v>
+        <v>243</v>
       </c>
       <c r="H23" t="n">
-        <v>93.33</v>
+        <v>82.72</v>
       </c>
       <c r="I23" t="n">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="J23" t="n">
-        <v>12.02409638554217</v>
+        <v>15.32921810699589</v>
       </c>
       <c r="K23" t="n">
-        <v>31999.85</v>
+        <v>1243642.7</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -2404,168 +2404,168 @@
         <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>14.45</v>
+        <v>15.7</v>
       </c>
       <c r="O23" t="n">
-        <v>-6.48</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>7.969999999999999</v>
+        <v>7.319999999999999</v>
       </c>
       <c r="Q23" t="n">
-        <v>8.970000000000001</v>
+        <v>22.58</v>
       </c>
       <c r="R23" t="n">
-        <v>1.274930241331561</v>
+        <v>0.312857723773746</v>
       </c>
       <c r="S23" t="n">
-        <v>1.685</v>
+        <v>7.549999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>3287.55</v>
+        <v>698.73</v>
       </c>
       <c r="U23" t="n">
-        <v>14970</v>
+        <v>3725</v>
       </c>
       <c r="V23" t="n">
-        <v>0.973983154992057</v>
+        <v>0.9585746638074436</v>
       </c>
       <c r="W23" t="n">
-        <v>1.022142995869986</v>
+        <v>1.034862369645139</v>
       </c>
       <c r="X23" t="n">
-        <v>333.63</v>
+        <v>49.89699999999998</v>
       </c>
       <c r="Y23" t="n">
-        <v>317.9105089140901</v>
+        <v>46.21870637387387</v>
       </c>
       <c r="Z23" t="n">
-        <v>19990924</v>
+        <v>74313184.02</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>00881.TW</t>
+          <t>00901.TW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>國泰台灣科技龍頭</t>
+          <t>永豐智能車供應鏈</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2.000460207685347</v>
+        <v>1.799653169228881</v>
       </c>
       <c r="D24" t="n">
-        <v>1.830231265165083</v>
+        <v>1.729797367313188</v>
       </c>
       <c r="E24" t="n">
-        <v>49.95</v>
+        <v>45.76</v>
       </c>
       <c r="F24" t="n">
-        <v>25.39</v>
+        <v>22.74</v>
       </c>
       <c r="G24" t="n">
-        <v>384</v>
+        <v>276</v>
       </c>
       <c r="H24" t="n">
-        <v>89.58</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>2.52</v>
+        <v>2.79</v>
       </c>
       <c r="J24" t="n">
-        <v>15.328125</v>
+        <v>13.22463768115942</v>
       </c>
       <c r="K24" t="n">
-        <v>17470914.1</v>
+        <v>240996.05</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>10.9</v>
+        <v>15.18</v>
       </c>
       <c r="O24" t="n">
-        <v>-4.28</v>
+        <v>-7.3</v>
       </c>
       <c r="P24" t="n">
-        <v>6.62</v>
+        <v>7.88</v>
       </c>
       <c r="Q24" t="n">
-        <v>15.81</v>
+        <v>24.17</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1702289425202639</v>
+        <v>0.06985580191569341</v>
       </c>
       <c r="S24" t="n">
-        <v>12.5</v>
+        <v>4.671</v>
       </c>
       <c r="T24" t="n">
-        <v>966.91</v>
+        <v>771.28</v>
       </c>
       <c r="U24" t="n">
-        <v>5886</v>
+        <v>3650</v>
       </c>
       <c r="V24" t="n">
-        <v>0.958852831927208</v>
+        <v>0.9526982011992005</v>
       </c>
       <c r="W24" t="n">
-        <v>1.017105496294636</v>
+        <v>1.014414839709477</v>
       </c>
       <c r="X24" t="n">
-        <v>52.09349999999999</v>
+        <v>48.032</v>
       </c>
       <c r="Y24" t="n">
-        <v>49.10994993338472</v>
+        <v>45.10975018179486</v>
       </c>
       <c r="Z24" t="n">
-        <v>2411172214.2</v>
+        <v>26318040.32</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>0052.TW</t>
+          <t>0057.TW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>富邦科技</t>
+          <t>富邦摩台</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8.2995376310792</v>
+        <v>6.171282091000382</v>
       </c>
       <c r="D25" t="n">
-        <v>5.030952125938335</v>
+        <v>4.940582575916224</v>
       </c>
       <c r="E25" t="n">
-        <v>63.15</v>
+        <v>323.2</v>
       </c>
       <c r="F25" t="n">
-        <v>28.73</v>
+        <v>22.08</v>
       </c>
       <c r="G25" t="n">
-        <v>1111</v>
+        <v>1245</v>
       </c>
       <c r="H25" t="n">
-        <v>88.20999999999999</v>
+        <v>93.33</v>
       </c>
       <c r="I25" t="n">
-        <v>2.45</v>
+        <v>2.64</v>
       </c>
       <c r="J25" t="n">
-        <v>14.18091809180918</v>
+        <v>12.02409638554217</v>
       </c>
       <c r="K25" t="n">
-        <v>19297789.9</v>
+        <v>32711.15</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -2576,82 +2576,82 @@
         <v>2</v>
       </c>
       <c r="N25" t="n">
-        <v>12.7</v>
+        <v>14.45</v>
       </c>
       <c r="O25" t="n">
-        <v>-14.18</v>
+        <v>-6.48</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.48</v>
+        <v>7.969999999999999</v>
       </c>
       <c r="Q25" t="n">
-        <v>8.050000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="R25" t="n">
-        <v>3.268585505140865</v>
+        <v>1.230699515084158</v>
       </c>
       <c r="S25" t="n">
-        <v>2.232857285714286</v>
+        <v>1.685</v>
       </c>
       <c r="T25" t="n">
-        <v>2723.42</v>
+        <v>3287.55</v>
       </c>
       <c r="U25" t="n">
-        <v>15755</v>
+        <v>14970</v>
       </c>
       <c r="V25" t="n">
-        <v>0.9686697089389105</v>
+        <v>0.9679109953131784</v>
       </c>
       <c r="W25" t="n">
-        <v>1.024751621097207</v>
+        <v>1.012527865635011</v>
       </c>
       <c r="X25" t="n">
-        <v>65.19250000000008</v>
+        <v>333.915</v>
       </c>
       <c r="Y25" t="n">
-        <v>61.62468904648811</v>
+        <v>319.2010916137146</v>
       </c>
       <c r="Z25" t="n">
-        <v>3692497138.05</v>
+        <v>9745126.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>00735.TW</t>
+          <t>00881.TW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>國泰臺韓科技</t>
+          <t>國泰台灣科技龍頭</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2.850956917903808</v>
+        <v>2.001541810800669</v>
       </c>
       <c r="D26" t="n">
-        <v>2.553158213192911</v>
+        <v>1.831478871397924</v>
       </c>
       <c r="E26" t="n">
-        <v>96.65000000000001</v>
+        <v>50</v>
       </c>
       <c r="F26" t="n">
-        <v>20.34</v>
+        <v>17.28</v>
       </c>
       <c r="G26" t="n">
-        <v>498</v>
+        <v>384</v>
       </c>
       <c r="H26" t="n">
-        <v>86.55</v>
+        <v>89.58</v>
       </c>
       <c r="I26" t="n">
-        <v>2.28</v>
+        <v>2.52</v>
       </c>
       <c r="J26" t="n">
-        <v>13.81124497991968</v>
+        <v>15.328125</v>
       </c>
       <c r="K26" t="n">
-        <v>1718688.75</v>
+        <v>16905344.85</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -2662,82 +2662,82 @@
         <v>2</v>
       </c>
       <c r="N26" t="n">
-        <v>21.39</v>
+        <v>10.9</v>
       </c>
       <c r="O26" t="n">
-        <v>-6.04</v>
+        <v>-4.28</v>
       </c>
       <c r="P26" t="n">
-        <v>15.35</v>
+        <v>6.62</v>
       </c>
       <c r="Q26" t="n">
-        <v>14.26</v>
+        <v>15.81</v>
       </c>
       <c r="R26" t="n">
-        <v>0.297798704710897</v>
+        <v>0.1700629394027451</v>
       </c>
       <c r="S26" t="n">
-        <v>13.37</v>
+        <v>12.5</v>
       </c>
       <c r="T26" t="n">
-        <v>1133.84</v>
+        <v>966.91</v>
       </c>
       <c r="U26" t="n">
-        <v>6878</v>
+        <v>5886</v>
       </c>
       <c r="V26" t="n">
-        <v>0.904327485380118</v>
+        <v>0.9590854161471621</v>
       </c>
       <c r="W26" t="n">
-        <v>0.9782970144468626</v>
+        <v>1.014499722532838</v>
       </c>
       <c r="X26" t="n">
-        <v>106.8749999999999</v>
+        <v>52.133</v>
       </c>
       <c r="Y26" t="n">
-        <v>98.79412752235244</v>
+        <v>49.28537572703139</v>
       </c>
       <c r="Z26" t="n">
-        <v>492615578.3</v>
+        <v>521563400</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>0050.TW</t>
+          <t>0052.TW</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>元大台灣50</t>
+          <t>富邦科技</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5.562516877867843</v>
+        <v>8.319216498042723</v>
       </c>
       <c r="D27" t="n">
-        <v>5.562516877867843</v>
+        <v>5.035259790978672</v>
       </c>
       <c r="E27" t="n">
-        <v>108.9</v>
+        <v>63.3</v>
       </c>
       <c r="F27" t="n">
-        <v>32.57</v>
+        <v>20.48</v>
       </c>
       <c r="G27" t="n">
-        <v>1695</v>
+        <v>1111</v>
       </c>
       <c r="H27" t="n">
-        <v>90.97</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="J27" t="n">
-        <v>13.46961651917404</v>
+        <v>14.18091809180918</v>
       </c>
       <c r="K27" t="n">
-        <v>105099319.6</v>
+        <v>19618983.25</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2748,82 +2748,82 @@
         <v>2</v>
       </c>
       <c r="N27" t="n">
-        <v>13.94</v>
+        <v>12.7</v>
       </c>
       <c r="O27" t="n">
-        <v>-5.91</v>
+        <v>-14.18</v>
       </c>
       <c r="P27" t="n">
-        <v>8.029999999999999</v>
+        <v>-1.48</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.04</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.283956707064051</v>
       </c>
       <c r="S27" t="n">
-        <v>4.84625</v>
+        <v>2.232857285714286</v>
       </c>
       <c r="T27" t="n">
-        <v>3824.71</v>
+        <v>2723.42</v>
       </c>
       <c r="U27" t="n">
-        <v>22831</v>
+        <v>15755</v>
       </c>
       <c r="V27" t="n">
-        <v>0.9720176730486005</v>
+        <v>0.9697062540691651</v>
       </c>
       <c r="W27" t="n">
-        <v>1.023976480321431</v>
+        <v>1.021202095783834</v>
       </c>
       <c r="X27" t="n">
-        <v>112.035</v>
+        <v>65.27750000000007</v>
       </c>
       <c r="Y27" t="n">
-        <v>106.3500989454521</v>
+        <v>61.98577173053432</v>
       </c>
       <c r="Z27" t="n">
-        <v>49373756962.2</v>
+        <v>1082135781.6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>0053.TW</t>
+          <t>00735.TW</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>元大科技市值</t>
+          <t>國泰臺韓科技</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6.770289434336692</v>
+        <v>2.914485721579601</v>
       </c>
       <c r="D28" t="n">
-        <v>4.993542447352277</v>
+        <v>2.555077770627909</v>
       </c>
       <c r="E28" t="n">
-        <v>243.75</v>
+        <v>98.45</v>
       </c>
       <c r="F28" t="n">
-        <v>23.46</v>
+        <v>17.71</v>
       </c>
       <c r="G28" t="n">
-        <v>1190</v>
+        <v>498</v>
       </c>
       <c r="H28" t="n">
-        <v>89.16</v>
+        <v>86.55</v>
       </c>
       <c r="I28" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="J28" t="n">
-        <v>13.83697478991597</v>
+        <v>13.81124497991968</v>
       </c>
       <c r="K28" t="n">
-        <v>328744.35</v>
+        <v>1775845.55</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -2834,82 +2834,82 @@
         <v>2</v>
       </c>
       <c r="N28" t="n">
-        <v>11.49</v>
+        <v>21.39</v>
       </c>
       <c r="O28" t="n">
-        <v>-7.24</v>
+        <v>-6.04</v>
       </c>
       <c r="P28" t="n">
-        <v>4.25</v>
+        <v>15.35</v>
       </c>
       <c r="Q28" t="n">
-        <v>7.58</v>
+        <v>14.26</v>
       </c>
       <c r="R28" t="n">
-        <v>1.776746986984415</v>
+        <v>0.3594079509516925</v>
       </c>
       <c r="S28" t="n">
-        <v>18.91</v>
+        <v>13.37</v>
       </c>
       <c r="T28" t="n">
-        <v>2598</v>
+        <v>1133.84</v>
       </c>
       <c r="U28" t="n">
-        <v>16466</v>
+        <v>6878</v>
       </c>
       <c r="V28" t="n">
-        <v>0.9665714965500828</v>
+        <v>0.9222266457460024</v>
       </c>
       <c r="W28" t="n">
-        <v>1.025831254609657</v>
+        <v>1.0020380036608</v>
       </c>
       <c r="X28" t="n">
-        <v>252.1800000000001</v>
+        <v>106.7524999999999</v>
       </c>
       <c r="Y28" t="n">
-        <v>237.612179298193</v>
+        <v>98.24976661596389</v>
       </c>
       <c r="Z28" t="n">
-        <v>389971968.75</v>
+        <v>206614652.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>00892.TW</t>
+          <t>0050.TW</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>富邦台灣半導體</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.844390375272075</v>
+        <v>5.567342277892016</v>
       </c>
       <c r="D29" t="n">
-        <v>1.780171686715981</v>
+        <v>5.567342277892016</v>
       </c>
       <c r="E29" t="n">
-        <v>40.76</v>
+        <v>109</v>
       </c>
       <c r="F29" t="n">
-        <v>30.46</v>
+        <v>23.58</v>
       </c>
       <c r="G29" t="n">
-        <v>241</v>
+        <v>1695</v>
       </c>
       <c r="H29" t="n">
-        <v>75.09999999999999</v>
+        <v>90.97</v>
       </c>
       <c r="I29" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="J29" t="n">
-        <v>15.85892116182573</v>
+        <v>13.46961651917404</v>
       </c>
       <c r="K29" t="n">
-        <v>4456380.55</v>
+        <v>108038688.85</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -2920,129 +2920,301 @@
         <v>2</v>
       </c>
       <c r="N29" t="n">
-        <v>12.37</v>
+        <v>13.94</v>
       </c>
       <c r="O29" t="n">
-        <v>-7.43</v>
+        <v>-5.91</v>
       </c>
       <c r="P29" t="n">
-        <v>4.94</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="Q29" t="n">
-        <v>18.86</v>
+        <v>6.04</v>
       </c>
       <c r="R29" t="n">
-        <v>0.06421868855609425</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>4.937</v>
+        <v>4.84625</v>
       </c>
       <c r="T29" t="n">
-        <v>510.5</v>
+        <v>3824.71</v>
       </c>
       <c r="U29" t="n">
-        <v>3822</v>
+        <v>22831</v>
       </c>
       <c r="V29" t="n">
-        <v>0.950260528984578</v>
+        <v>0.9717176669861147</v>
       </c>
       <c r="W29" t="n">
-        <v>0.9984073580245072</v>
+        <v>1.019274447629305</v>
       </c>
       <c r="X29" t="n">
-        <v>42.8935</v>
+        <v>112.1725</v>
       </c>
       <c r="Y29" t="n">
-        <v>40.82501963992887</v>
+        <v>106.9388134407953</v>
       </c>
       <c r="Z29" t="n">
-        <v>340359165.48</v>
+        <v>13315516082</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>006208.TW</t>
+          <t>0053.TW</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>富邦台50</t>
+          <t>元大科技市值</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4.150294481638475</v>
+        <v>6.761379120499327</v>
       </c>
       <c r="D30" t="n">
-        <v>3.880513910592286</v>
+        <v>4.997785128026342</v>
       </c>
       <c r="E30" t="n">
-        <v>250.1</v>
+        <v>243.5</v>
       </c>
       <c r="F30" t="n">
-        <v>31.72</v>
+        <v>16.62</v>
       </c>
       <c r="G30" t="n">
-        <v>895</v>
+        <v>1190</v>
       </c>
       <c r="H30" t="n">
-        <v>88.48999999999999</v>
+        <v>89.16</v>
       </c>
       <c r="I30" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="J30" t="n">
-        <v>13.86703910614525</v>
+        <v>13.83697478991597</v>
       </c>
       <c r="K30" t="n">
-        <v>2928117.1</v>
+        <v>364240.2</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>2</v>
       </c>
       <c r="N30" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-7.24</v>
+      </c>
+      <c r="P30" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.763593992472985</v>
+      </c>
+      <c r="S30" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2598</v>
+      </c>
+      <c r="U30" t="n">
+        <v>16466</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.9644041784246741</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.01898837440031</v>
+      </c>
+      <c r="X30" t="n">
+        <v>252.4875000000001</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>238.9624907578591</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>241519127.5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>00892.TW</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>富邦台灣半導體</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1.862203102689735</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1.781296736363694</v>
+      </c>
+      <c r="E31" t="n">
+        <v>41.06</v>
+      </c>
+      <c r="F31" t="n">
+        <v>24.57</v>
+      </c>
+      <c r="G31" t="n">
+        <v>241</v>
+      </c>
+      <c r="H31" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="J31" t="n">
+        <v>15.85892116182573</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4494633.75</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>2</v>
+      </c>
+      <c r="N31" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-7.43</v>
+      </c>
+      <c r="P31" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.0809063663260412</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4.937</v>
+      </c>
+      <c r="T31" t="n">
+        <v>510.5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3822</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.9568753568473918</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.003684847366265</v>
+      </c>
+      <c r="X31" t="n">
+        <v>42.9105</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>40.90925563710975</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>163270984</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>006208.TW</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>富邦台50</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>4.153757639681457</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3.883665366759812</v>
+      </c>
+      <c r="E32" t="n">
+        <v>250.35</v>
+      </c>
+      <c r="F32" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="G32" t="n">
+        <v>895</v>
+      </c>
+      <c r="H32" t="n">
+        <v>88.48999999999999</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="J32" t="n">
+        <v>13.86703910614525</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2962549.85</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>2</v>
+      </c>
+      <c r="N32" t="n">
         <v>11.21</v>
       </c>
-      <c r="O30" t="n">
+      <c r="O32" t="n">
         <v>-6.25</v>
       </c>
-      <c r="P30" t="n">
+      <c r="P32" t="n">
         <v>4.960000000000001</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="Q32" t="n">
         <v>8.949999999999999</v>
       </c>
-      <c r="R30" t="n">
-        <v>0.2697805710461898</v>
-      </c>
-      <c r="S30" t="n">
+      <c r="R32" t="n">
+        <v>0.2700922729216453</v>
+      </c>
+      <c r="S32" t="n">
         <v>28.764</v>
       </c>
-      <c r="T30" t="n">
+      <c r="T32" t="n">
         <v>1745.92</v>
       </c>
-      <c r="U30" t="n">
+      <c r="U32" t="n">
         <v>12411</v>
       </c>
-      <c r="V30" t="n">
-        <v>0.9752293309677231</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.026576864733604</v>
-      </c>
-      <c r="X30" t="n">
-        <v>256.4525</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>243.62520585821</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2561508443.7</v>
+      <c r="V32" t="n">
+        <v>0.9749021593099553</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.021631766481664</v>
+      </c>
+      <c r="X32" t="n">
+        <v>256.795</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>245.0491539257489</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>648338154.4499999</v>
       </c>
     </row>
   </sheetData>

--- a/ETF動態清單.xlsx
+++ b/ETF動態清單.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z32"/>
+  <dimension ref="A1:Z34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.062780275554555</v>
+        <v>1.177604725738289</v>
       </c>
       <c r="D4" t="n">
         <v>0.8953979892033781</v>
@@ -786,10 +786,10 @@
         <v>159.78</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1673822863511771</v>
+        <v>0.2822067365349106</v>
       </c>
       <c r="S4" t="n">
-        <v>0.78</v>
+        <v>2.78</v>
       </c>
       <c r="T4" t="n">
         <v>495.22</v>
@@ -1762,126 +1762,126 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>00913.TW</t>
+          <t>00904.TW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>兆豐台灣晶圓製造</t>
+          <t>台新臺灣半導體30</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.658344663775718</v>
+        <v>1.783480168501113</v>
       </c>
       <c r="D16" t="n">
-        <v>1.620251159374102</v>
+        <v>1.713418307862876</v>
       </c>
       <c r="E16" t="n">
-        <v>48.57</v>
+        <v>38.83</v>
       </c>
       <c r="F16" t="n">
-        <v>19.54</v>
+        <v>18.71</v>
       </c>
       <c r="G16" t="n">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="H16" t="n">
-        <v>96.18000000000001</v>
+        <v>99.16</v>
       </c>
       <c r="I16" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J16" t="n">
-        <v>12.79770992366412</v>
+        <v>10.78242677824268</v>
       </c>
       <c r="K16" t="n">
-        <v>1849223.85</v>
+        <v>3774460.05</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>13.5</v>
+        <v>11.85</v>
       </c>
       <c r="O16" t="n">
-        <v>-9.19</v>
+        <v>-12.45</v>
       </c>
       <c r="P16" t="n">
-        <v>4.31</v>
+        <v>-0.5999999999999996</v>
       </c>
       <c r="Q16" t="n">
-        <v>28.72</v>
+        <v>37.53</v>
       </c>
       <c r="R16" t="n">
-        <v>0.03809350440161641</v>
+        <v>0.07006186063823705</v>
       </c>
       <c r="S16" t="n">
-        <v>6.699999999999999</v>
+        <v>7.050000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>916.5599999999999</v>
+        <v>848.62</v>
       </c>
       <c r="U16" t="n">
-        <v>3353</v>
+        <v>2577</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9350994397489462</v>
+        <v>0.9026558958563375</v>
       </c>
       <c r="W16" t="n">
-        <v>1.009580139389076</v>
+        <v>0.96988252482245</v>
       </c>
       <c r="X16" t="n">
-        <v>51.94099999999999</v>
+        <v>43.0175</v>
       </c>
       <c r="Y16" t="n">
-        <v>48.1091080391013</v>
+        <v>40.03577650510648</v>
       </c>
       <c r="Z16" t="n">
-        <v>54817996.23</v>
+        <v>205621430.41</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>00685L.TW</t>
+          <t>00913.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>群益臺灣加權正2</t>
+          <t>兆豐台灣晶圓製造</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10.72745992536771</v>
+        <v>1.658344663775718</v>
       </c>
       <c r="D17" t="n">
-        <v>2.819281252814454</v>
+        <v>1.620251159374102</v>
       </c>
       <c r="E17" t="n">
-        <v>12.32</v>
+        <v>48.57</v>
       </c>
       <c r="F17" t="n">
-        <v>24.29</v>
+        <v>19.54</v>
       </c>
       <c r="G17" t="n">
-        <v>514</v>
+        <v>262</v>
       </c>
       <c r="H17" t="n">
-        <v>88.52</v>
+        <v>96.18000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="J17" t="n">
-        <v>12.18093385214008</v>
+        <v>12.79770992366412</v>
       </c>
       <c r="K17" t="n">
-        <v>241723801.8</v>
+        <v>1849223.85</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1892,82 +1892,82 @@
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>15.89</v>
+        <v>13.5</v>
       </c>
       <c r="O17" t="n">
-        <v>-18.5</v>
+        <v>-9.19</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.609999999999999</v>
+        <v>4.31</v>
       </c>
       <c r="Q17" t="n">
-        <v>18.65</v>
+        <v>28.72</v>
       </c>
       <c r="R17" t="n">
-        <v>7.908178672553253</v>
+        <v>0.03809350440161641</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>6.699999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>1777.84</v>
+        <v>916.5599999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>6261</v>
+        <v>3353</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9532283647336454</v>
+        <v>0.9350994397489462</v>
       </c>
       <c r="W17" t="n">
-        <v>1.048361971452616</v>
+        <v>1.009580139389076</v>
       </c>
       <c r="X17" t="n">
-        <v>12.9245</v>
+        <v>51.94099999999999</v>
       </c>
       <c r="Y17" t="n">
-        <v>11.75166625219087</v>
+        <v>48.1091080391013</v>
       </c>
       <c r="Z17" t="n">
-        <v>2639403215.68</v>
+        <v>54817996.23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>009809.TW</t>
+          <t>00685L.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>富邦淨零ESG50</t>
+          <t>群益臺灣加權正2</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.3687387630861929</v>
+        <v>10.72745992536771</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3267215405451394</v>
+        <v>2.819281252814454</v>
       </c>
       <c r="E18" t="n">
-        <v>18.27</v>
+        <v>12.32</v>
       </c>
       <c r="F18" t="n">
-        <v>23.89</v>
+        <v>24.29</v>
       </c>
       <c r="G18" t="n">
-        <v>34</v>
+        <v>514</v>
       </c>
       <c r="H18" t="n">
-        <v>97.06</v>
+        <v>88.52</v>
       </c>
       <c r="I18" t="n">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="J18" t="n">
-        <v>8.235294117647058</v>
+        <v>12.18093385214008</v>
       </c>
       <c r="K18" t="n">
-        <v>205449.65</v>
+        <v>241723801.8</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1978,422 +1978,422 @@
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>7.76</v>
+        <v>15.89</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.12</v>
+        <v>-18.5</v>
       </c>
       <c r="P18" t="n">
-        <v>7.64</v>
+        <v>-2.609999999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>172.16</v>
+        <v>18.65</v>
       </c>
       <c r="R18" t="n">
-        <v>0.04201722254105356</v>
+        <v>7.908178672553253</v>
       </c>
       <c r="S18" t="n">
-        <v>0.315</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>115.56</v>
+        <v>1777.84</v>
       </c>
       <c r="U18" t="n">
-        <v>280</v>
+        <v>6261</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9826542960871316</v>
+        <v>0.9532283647336454</v>
       </c>
       <c r="W18" t="n">
-        <v>1.015245590929712</v>
+        <v>1.048361971452616</v>
       </c>
       <c r="X18" t="n">
-        <v>18.5925</v>
+        <v>12.9245</v>
       </c>
       <c r="Y18" t="n">
-        <v>17.99564574643386</v>
+        <v>11.75166625219087</v>
       </c>
       <c r="Z18" t="n">
-        <v>6179571.72</v>
+        <v>2639403215.68</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>00715L.TW</t>
+          <t>009809.TW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>期街口布蘭特正2</t>
+          <t>富邦淨零ESG50</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.165222188860139</v>
+        <v>0.3687387630861929</v>
       </c>
       <c r="D19" t="n">
-        <v>2.677077241273147</v>
+        <v>0.3267215405451394</v>
       </c>
       <c r="E19" t="n">
-        <v>76.65000000000001</v>
+        <v>18.27</v>
       </c>
       <c r="F19" t="n">
-        <v>83.13</v>
+        <v>23.89</v>
       </c>
       <c r="G19" t="n">
-        <v>425</v>
+        <v>34</v>
       </c>
       <c r="H19" t="n">
-        <v>77.65000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="I19" t="n">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="J19" t="n">
-        <v>17.11294117647059</v>
+        <v>8.235294117647058</v>
       </c>
       <c r="K19" t="n">
-        <v>3358093.8</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
+        <v>205449.65</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="M19" t="n">
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>32.14</v>
+        <v>7.76</v>
       </c>
       <c r="O19" t="n">
-        <v>-44.86</v>
+        <v>-0.12</v>
       </c>
       <c r="P19" t="n">
-        <v>-12.72</v>
+        <v>7.64</v>
       </c>
       <c r="Q19" t="n">
-        <v>14.59</v>
+        <v>172.16</v>
       </c>
       <c r="R19" t="n">
-        <v>2.488144947586992</v>
+        <v>0.04201722254105356</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
       <c r="T19" t="n">
-        <v>1409.31</v>
+        <v>115.56</v>
       </c>
       <c r="U19" t="n">
-        <v>7273</v>
+        <v>280</v>
       </c>
       <c r="V19" t="n">
-        <v>1.107099010616019</v>
+        <v>0.9826542960871316</v>
       </c>
       <c r="W19" t="n">
-        <v>1.277993965285937</v>
+        <v>1.015245590929712</v>
       </c>
       <c r="X19" t="n">
-        <v>69.23499999999994</v>
+        <v>18.5925</v>
       </c>
       <c r="Y19" t="n">
-        <v>59.9768090319976</v>
+        <v>17.99564574643386</v>
       </c>
       <c r="Z19" t="n">
-        <v>134777680.8</v>
+        <v>6179571.72</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>00401A.TW</t>
+          <t>00715L.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>主動摩根台灣鑫收</t>
+          <t>期街口布蘭特正2</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0716527544242318</v>
+        <v>5.165222188860139</v>
       </c>
       <c r="D20" t="n">
-        <v>0.07114066577626521</v>
+        <v>2.677077241273147</v>
       </c>
       <c r="E20" t="n">
-        <v>13.82</v>
+        <v>76.65000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>28.73</v>
+        <v>83.13</v>
       </c>
       <c r="G20" t="n">
-        <v>21</v>
+        <v>425</v>
       </c>
       <c r="H20" t="n">
-        <v>100</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>3.23</v>
+        <v>3.32</v>
       </c>
       <c r="J20" t="n">
-        <v>15.19047619047619</v>
+        <v>17.11294117647059</v>
       </c>
       <c r="K20" t="n">
-        <v>6995277.45</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
+        <v>3358093.8</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
         <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>11.76</v>
+        <v>32.14</v>
       </c>
       <c r="O20" t="n">
-        <v>0.36</v>
+        <v>-44.86</v>
       </c>
       <c r="P20" t="n">
-        <v>12.12</v>
+        <v>-12.72</v>
       </c>
       <c r="Q20" t="n">
-        <v>80.95</v>
+        <v>14.59</v>
       </c>
       <c r="R20" t="n">
-        <v>0.0005120886479665909</v>
+        <v>2.488144947586992</v>
       </c>
       <c r="S20" t="n">
-        <v>0.377</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>67.92</v>
+        <v>1409.31</v>
       </c>
       <c r="U20" t="n">
-        <v>319</v>
+        <v>7273</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9677193473846365</v>
+        <v>1.107099010616019</v>
       </c>
       <c r="W20" t="n">
-        <v>1.006003017296597</v>
+        <v>1.277993965285937</v>
       </c>
       <c r="X20" t="n">
-        <v>14.28100000000001</v>
+        <v>69.23499999999994</v>
       </c>
       <c r="Y20" t="n">
-        <v>13.73753334968924</v>
+        <v>59.9768090319976</v>
       </c>
       <c r="Z20" t="n">
-        <v>105251945.3</v>
+        <v>134777680.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>00675L.TW</t>
+          <t>00401A.TW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>富邦臺灣加權正2</t>
+          <t>主動摩根台灣鑫收</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>11.27055046677457</v>
+        <v>0.0716527544242318</v>
       </c>
       <c r="D21" t="n">
-        <v>2.926815596457504</v>
+        <v>0.07114066577626521</v>
       </c>
       <c r="E21" t="n">
-        <v>325.8</v>
+        <v>13.82</v>
       </c>
       <c r="F21" t="n">
-        <v>25.1</v>
+        <v>28.73</v>
       </c>
       <c r="G21" t="n">
-        <v>564</v>
+        <v>21</v>
       </c>
       <c r="H21" t="n">
-        <v>87.06</v>
+        <v>100</v>
       </c>
       <c r="I21" t="n">
-        <v>3.18</v>
+        <v>3.23</v>
       </c>
       <c r="J21" t="n">
-        <v>12.38297872340426</v>
+        <v>15.19047619047619</v>
       </c>
       <c r="K21" t="n">
-        <v>1135452.95</v>
+        <v>6995277.45</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>15.7</v>
+        <v>11.76</v>
       </c>
       <c r="O21" t="n">
-        <v>-24.73</v>
+        <v>0.36</v>
       </c>
       <c r="P21" t="n">
-        <v>-9.030000000000001</v>
+        <v>12.12</v>
       </c>
       <c r="Q21" t="n">
-        <v>16.61</v>
+        <v>80.95</v>
       </c>
       <c r="R21" t="n">
-        <v>8.343734870317068</v>
+        <v>0.0005120886479665909</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>0.377</v>
       </c>
       <c r="T21" t="n">
-        <v>1792.47</v>
+        <v>67.92</v>
       </c>
       <c r="U21" t="n">
-        <v>6984</v>
+        <v>319</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9520469886911541</v>
+        <v>0.9677193473846365</v>
       </c>
       <c r="W21" t="n">
-        <v>1.046486786764947</v>
+        <v>1.006003017296597</v>
       </c>
       <c r="X21" t="n">
-        <v>342.2100000000002</v>
+        <v>14.28100000000001</v>
       </c>
       <c r="Y21" t="n">
-        <v>311.3273900066722</v>
+        <v>13.73753334968924</v>
       </c>
       <c r="Z21" t="n">
-        <v>380264963.4</v>
+        <v>105251945.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>00935.TW</t>
+          <t>00675L.TW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>野村臺灣新科技50</t>
+          <t>富邦臺灣加權正2</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.448598760881438</v>
+        <v>11.27055046677457</v>
       </c>
       <c r="D22" t="n">
-        <v>1.14028886333536</v>
+        <v>2.926815596457504</v>
       </c>
       <c r="E22" t="n">
-        <v>57</v>
+        <v>325.8</v>
       </c>
       <c r="F22" t="n">
-        <v>20.7</v>
+        <v>25.1</v>
       </c>
       <c r="G22" t="n">
-        <v>136</v>
+        <v>564</v>
       </c>
       <c r="H22" t="n">
-        <v>83.09</v>
+        <v>87.06</v>
       </c>
       <c r="I22" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="J22" t="n">
-        <v>12.30882352941176</v>
+        <v>12.38297872340426</v>
       </c>
       <c r="K22" t="n">
-        <v>12874184.75</v>
+        <v>1135452.95</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>14.6</v>
+        <v>15.7</v>
       </c>
       <c r="O22" t="n">
-        <v>-8.99</v>
+        <v>-24.73</v>
       </c>
       <c r="P22" t="n">
-        <v>5.609999999999999</v>
+        <v>-9.030000000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>43.74</v>
+        <v>16.61</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3083098975460787</v>
+        <v>8.343734870317068</v>
       </c>
       <c r="S22" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>428.12</v>
+        <v>1792.47</v>
       </c>
       <c r="U22" t="n">
-        <v>1674</v>
+        <v>6984</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9429280397022332</v>
+        <v>0.9520469886911541</v>
       </c>
       <c r="W22" t="n">
-        <v>1.017700783615503</v>
+        <v>1.046486786764947</v>
       </c>
       <c r="X22" t="n">
-        <v>60.45</v>
+        <v>342.2100000000002</v>
       </c>
       <c r="Y22" t="n">
-        <v>56.00860382312048</v>
+        <v>311.3273900066722</v>
       </c>
       <c r="Z22" t="n">
-        <v>571879062</v>
+        <v>380264963.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>00894.TW</t>
+          <t>00935.TW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>中信小資高價30</t>
+          <t>野村臺灣新科技50</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2.077371287842047</v>
+        <v>1.448598760881438</v>
       </c>
       <c r="D23" t="n">
-        <v>1.764513564068301</v>
+        <v>1.14028886333536</v>
       </c>
       <c r="E23" t="n">
-        <v>47.83</v>
+        <v>57</v>
       </c>
       <c r="F23" t="n">
-        <v>27.09</v>
+        <v>20.7</v>
       </c>
       <c r="G23" t="n">
-        <v>243</v>
+        <v>136</v>
       </c>
       <c r="H23" t="n">
-        <v>82.72</v>
+        <v>83.09</v>
       </c>
       <c r="I23" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="J23" t="n">
-        <v>15.32921810699589</v>
+        <v>12.30882352941176</v>
       </c>
       <c r="K23" t="n">
-        <v>1243642.7</v>
+        <v>12874184.75</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -2404,82 +2404,82 @@
         <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>15.7</v>
+        <v>14.6</v>
       </c>
       <c r="O23" t="n">
-        <v>-8.380000000000001</v>
+        <v>-8.99</v>
       </c>
       <c r="P23" t="n">
-        <v>7.319999999999999</v>
+        <v>5.609999999999999</v>
       </c>
       <c r="Q23" t="n">
-        <v>22.58</v>
+        <v>43.74</v>
       </c>
       <c r="R23" t="n">
-        <v>0.312857723773746</v>
+        <v>0.3083098975460787</v>
       </c>
       <c r="S23" t="n">
-        <v>7.549999999999999</v>
+        <v>4.98</v>
       </c>
       <c r="T23" t="n">
-        <v>698.73</v>
+        <v>428.12</v>
       </c>
       <c r="U23" t="n">
-        <v>3725</v>
+        <v>1674</v>
       </c>
       <c r="V23" t="n">
-        <v>0.9585746638074436</v>
+        <v>0.9429280397022332</v>
       </c>
       <c r="W23" t="n">
-        <v>1.034862369645139</v>
+        <v>1.017700783615503</v>
       </c>
       <c r="X23" t="n">
-        <v>49.89699999999998</v>
+        <v>60.45</v>
       </c>
       <c r="Y23" t="n">
-        <v>46.21870637387387</v>
+        <v>56.00860382312048</v>
       </c>
       <c r="Z23" t="n">
-        <v>74313184.02</v>
+        <v>571879062</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>00901.TW</t>
+          <t>00894.TW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>永豐智能車供應鏈</t>
+          <t>中信小資高價30</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.799653169228881</v>
+        <v>2.077371287842047</v>
       </c>
       <c r="D24" t="n">
-        <v>1.729797367313188</v>
+        <v>1.764513564068301</v>
       </c>
       <c r="E24" t="n">
-        <v>45.76</v>
+        <v>47.83</v>
       </c>
       <c r="F24" t="n">
-        <v>22.74</v>
+        <v>27.09</v>
       </c>
       <c r="G24" t="n">
-        <v>276</v>
+        <v>243</v>
       </c>
       <c r="H24" t="n">
-        <v>89.48999999999999</v>
+        <v>82.72</v>
       </c>
       <c r="I24" t="n">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="J24" t="n">
-        <v>13.22463768115942</v>
+        <v>15.32921810699589</v>
       </c>
       <c r="K24" t="n">
-        <v>240996.05</v>
+        <v>1243642.7</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -2490,82 +2490,82 @@
         <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>15.18</v>
+        <v>15.7</v>
       </c>
       <c r="O24" t="n">
-        <v>-7.3</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>7.88</v>
+        <v>7.319999999999999</v>
       </c>
       <c r="Q24" t="n">
-        <v>24.17</v>
+        <v>22.58</v>
       </c>
       <c r="R24" t="n">
-        <v>0.06985580191569341</v>
+        <v>0.312857723773746</v>
       </c>
       <c r="S24" t="n">
-        <v>4.671</v>
+        <v>7.549999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>771.28</v>
+        <v>698.73</v>
       </c>
       <c r="U24" t="n">
-        <v>3650</v>
+        <v>3725</v>
       </c>
       <c r="V24" t="n">
-        <v>0.9526982011992005</v>
+        <v>0.9585746638074436</v>
       </c>
       <c r="W24" t="n">
-        <v>1.014414839709477</v>
+        <v>1.034862369645139</v>
       </c>
       <c r="X24" t="n">
-        <v>48.032</v>
+        <v>49.89699999999998</v>
       </c>
       <c r="Y24" t="n">
-        <v>45.10975018179486</v>
+        <v>46.21870637387387</v>
       </c>
       <c r="Z24" t="n">
-        <v>26318040.32</v>
+        <v>74313184.02</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>0057.TW</t>
+          <t>00901.TW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>富邦摩台</t>
+          <t>永豐智能車供應鏈</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6.171282091000382</v>
+        <v>1.799653169228881</v>
       </c>
       <c r="D25" t="n">
-        <v>4.940582575916224</v>
+        <v>1.729797367313188</v>
       </c>
       <c r="E25" t="n">
-        <v>323.2</v>
+        <v>45.76</v>
       </c>
       <c r="F25" t="n">
-        <v>22.08</v>
+        <v>22.74</v>
       </c>
       <c r="G25" t="n">
-        <v>1245</v>
+        <v>276</v>
       </c>
       <c r="H25" t="n">
-        <v>93.33</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>2.64</v>
+        <v>2.79</v>
       </c>
       <c r="J25" t="n">
-        <v>12.02409638554217</v>
+        <v>13.22463768115942</v>
       </c>
       <c r="K25" t="n">
-        <v>32711.15</v>
+        <v>240996.05</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -2576,598 +2576,598 @@
         <v>2</v>
       </c>
       <c r="N25" t="n">
-        <v>14.45</v>
+        <v>15.18</v>
       </c>
       <c r="O25" t="n">
-        <v>-6.48</v>
+        <v>-7.3</v>
       </c>
       <c r="P25" t="n">
-        <v>7.969999999999999</v>
+        <v>7.88</v>
       </c>
       <c r="Q25" t="n">
-        <v>8.970000000000001</v>
+        <v>24.17</v>
       </c>
       <c r="R25" t="n">
-        <v>1.230699515084158</v>
+        <v>0.06985580191569341</v>
       </c>
       <c r="S25" t="n">
-        <v>1.685</v>
+        <v>4.671</v>
       </c>
       <c r="T25" t="n">
-        <v>3287.55</v>
+        <v>771.28</v>
       </c>
       <c r="U25" t="n">
-        <v>14970</v>
+        <v>3650</v>
       </c>
       <c r="V25" t="n">
-        <v>0.9679109953131784</v>
+        <v>0.9526982011992005</v>
       </c>
       <c r="W25" t="n">
-        <v>1.012527865635011</v>
+        <v>1.014414839709477</v>
       </c>
       <c r="X25" t="n">
-        <v>333.915</v>
+        <v>48.032</v>
       </c>
       <c r="Y25" t="n">
-        <v>319.2010916137146</v>
+        <v>45.10975018179486</v>
       </c>
       <c r="Z25" t="n">
-        <v>9745126.4</v>
+        <v>26318040.32</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>00881.TW</t>
+          <t>0057.TW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>國泰台灣科技龍頭</t>
+          <t>富邦摩台</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2.001541810800669</v>
+        <v>6.171282091000382</v>
       </c>
       <c r="D26" t="n">
-        <v>1.831478871397924</v>
+        <v>4.940582575916224</v>
       </c>
       <c r="E26" t="n">
-        <v>50</v>
+        <v>323.2</v>
       </c>
       <c r="F26" t="n">
-        <v>17.28</v>
+        <v>22.08</v>
       </c>
       <c r="G26" t="n">
-        <v>384</v>
+        <v>1245</v>
       </c>
       <c r="H26" t="n">
-        <v>89.58</v>
+        <v>93.33</v>
       </c>
       <c r="I26" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="J26" t="n">
-        <v>15.328125</v>
+        <v>12.02409638554217</v>
       </c>
       <c r="K26" t="n">
-        <v>16905344.85</v>
+        <v>32711.15</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>2</v>
       </c>
       <c r="N26" t="n">
-        <v>10.9</v>
+        <v>14.45</v>
       </c>
       <c r="O26" t="n">
-        <v>-4.28</v>
+        <v>-6.48</v>
       </c>
       <c r="P26" t="n">
-        <v>6.62</v>
+        <v>7.969999999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>15.81</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="R26" t="n">
-        <v>0.1700629394027451</v>
+        <v>1.230699515084158</v>
       </c>
       <c r="S26" t="n">
-        <v>12.5</v>
+        <v>1.685</v>
       </c>
       <c r="T26" t="n">
-        <v>966.91</v>
+        <v>3287.55</v>
       </c>
       <c r="U26" t="n">
-        <v>5886</v>
+        <v>14970</v>
       </c>
       <c r="V26" t="n">
-        <v>0.9590854161471621</v>
+        <v>0.9679109953131784</v>
       </c>
       <c r="W26" t="n">
-        <v>1.014499722532838</v>
+        <v>1.012527865635011</v>
       </c>
       <c r="X26" t="n">
-        <v>52.133</v>
+        <v>333.915</v>
       </c>
       <c r="Y26" t="n">
-        <v>49.28537572703139</v>
+        <v>319.2010916137146</v>
       </c>
       <c r="Z26" t="n">
-        <v>521563400</v>
+        <v>9745126.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>0052.TW</t>
+          <t>00881.TW</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>富邦科技</t>
+          <t>國泰台灣科技龍頭</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8.319216498042723</v>
+        <v>2.001541810800669</v>
       </c>
       <c r="D27" t="n">
-        <v>5.035259790978672</v>
+        <v>1.831478871397924</v>
       </c>
       <c r="E27" t="n">
-        <v>63.3</v>
+        <v>50</v>
       </c>
       <c r="F27" t="n">
-        <v>20.48</v>
+        <v>17.28</v>
       </c>
       <c r="G27" t="n">
-        <v>1111</v>
+        <v>384</v>
       </c>
       <c r="H27" t="n">
-        <v>88.20999999999999</v>
+        <v>89.58</v>
       </c>
       <c r="I27" t="n">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="J27" t="n">
-        <v>14.18091809180918</v>
+        <v>15.328125</v>
       </c>
       <c r="K27" t="n">
-        <v>19618983.25</v>
+        <v>16905344.85</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="M27" t="n">
         <v>2</v>
       </c>
       <c r="N27" t="n">
-        <v>12.7</v>
+        <v>10.9</v>
       </c>
       <c r="O27" t="n">
-        <v>-14.18</v>
+        <v>-4.28</v>
       </c>
       <c r="P27" t="n">
-        <v>-1.48</v>
+        <v>6.62</v>
       </c>
       <c r="Q27" t="n">
-        <v>8.050000000000001</v>
+        <v>15.81</v>
       </c>
       <c r="R27" t="n">
-        <v>3.283956707064051</v>
+        <v>0.1700629394027451</v>
       </c>
       <c r="S27" t="n">
-        <v>2.232857285714286</v>
+        <v>12.5</v>
       </c>
       <c r="T27" t="n">
-        <v>2723.42</v>
+        <v>966.91</v>
       </c>
       <c r="U27" t="n">
-        <v>15755</v>
+        <v>5886</v>
       </c>
       <c r="V27" t="n">
-        <v>0.9697062540691651</v>
+        <v>0.9590854161471621</v>
       </c>
       <c r="W27" t="n">
-        <v>1.021202095783834</v>
+        <v>1.014499722532838</v>
       </c>
       <c r="X27" t="n">
-        <v>65.27750000000007</v>
+        <v>52.133</v>
       </c>
       <c r="Y27" t="n">
-        <v>61.98577173053432</v>
+        <v>49.28537572703139</v>
       </c>
       <c r="Z27" t="n">
-        <v>1082135781.6</v>
+        <v>521563400</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>00735.TW</t>
+          <t>0052.TW</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>國泰臺韓科技</t>
+          <t>富邦科技</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2.914485721579601</v>
+        <v>8.319216498042723</v>
       </c>
       <c r="D28" t="n">
-        <v>2.555077770627909</v>
+        <v>5.035259790978672</v>
       </c>
       <c r="E28" t="n">
-        <v>98.45</v>
+        <v>63.3</v>
       </c>
       <c r="F28" t="n">
-        <v>17.71</v>
+        <v>20.48</v>
       </c>
       <c r="G28" t="n">
-        <v>498</v>
+        <v>1111</v>
       </c>
       <c r="H28" t="n">
-        <v>86.55</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="J28" t="n">
-        <v>13.81124497991968</v>
+        <v>14.18091809180918</v>
       </c>
       <c r="K28" t="n">
-        <v>1775845.55</v>
+        <v>19618983.25</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>2</v>
       </c>
       <c r="N28" t="n">
-        <v>21.39</v>
+        <v>12.7</v>
       </c>
       <c r="O28" t="n">
-        <v>-6.04</v>
+        <v>-14.18</v>
       </c>
       <c r="P28" t="n">
-        <v>15.35</v>
+        <v>-1.48</v>
       </c>
       <c r="Q28" t="n">
-        <v>14.26</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="R28" t="n">
-        <v>0.3594079509516925</v>
+        <v>3.283956707064051</v>
       </c>
       <c r="S28" t="n">
-        <v>13.37</v>
+        <v>2.232857285714286</v>
       </c>
       <c r="T28" t="n">
-        <v>1133.84</v>
+        <v>2723.42</v>
       </c>
       <c r="U28" t="n">
-        <v>6878</v>
+        <v>15755</v>
       </c>
       <c r="V28" t="n">
-        <v>0.9222266457460024</v>
+        <v>0.9697062540691651</v>
       </c>
       <c r="W28" t="n">
-        <v>1.0020380036608</v>
+        <v>1.021202095783834</v>
       </c>
       <c r="X28" t="n">
-        <v>106.7524999999999</v>
+        <v>65.27750000000007</v>
       </c>
       <c r="Y28" t="n">
-        <v>98.24976661596389</v>
+        <v>61.98577173053432</v>
       </c>
       <c r="Z28" t="n">
-        <v>206614652.2</v>
+        <v>1082135781.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>0050.TW</t>
+          <t>00735.TW</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>元大台灣50</t>
+          <t>國泰臺韓科技</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5.567342277892016</v>
+        <v>2.914485721579601</v>
       </c>
       <c r="D29" t="n">
-        <v>5.567342277892016</v>
+        <v>2.555077770627909</v>
       </c>
       <c r="E29" t="n">
-        <v>109</v>
+        <v>98.45</v>
       </c>
       <c r="F29" t="n">
-        <v>23.58</v>
+        <v>17.71</v>
       </c>
       <c r="G29" t="n">
-        <v>1695</v>
+        <v>498</v>
       </c>
       <c r="H29" t="n">
-        <v>90.97</v>
+        <v>86.55</v>
       </c>
       <c r="I29" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="J29" t="n">
-        <v>13.46961651917404</v>
+        <v>13.81124497991968</v>
       </c>
       <c r="K29" t="n">
-        <v>108038688.85</v>
+        <v>1775845.55</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>2</v>
       </c>
       <c r="N29" t="n">
-        <v>13.94</v>
+        <v>21.39</v>
       </c>
       <c r="O29" t="n">
-        <v>-5.91</v>
+        <v>-6.04</v>
       </c>
       <c r="P29" t="n">
-        <v>8.029999999999999</v>
+        <v>15.35</v>
       </c>
       <c r="Q29" t="n">
-        <v>6.04</v>
+        <v>14.26</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>0.3594079509516925</v>
       </c>
       <c r="S29" t="n">
-        <v>4.84625</v>
+        <v>13.37</v>
       </c>
       <c r="T29" t="n">
-        <v>3824.71</v>
+        <v>1133.84</v>
       </c>
       <c r="U29" t="n">
-        <v>22831</v>
+        <v>6878</v>
       </c>
       <c r="V29" t="n">
-        <v>0.9717176669861147</v>
+        <v>0.9222266457460024</v>
       </c>
       <c r="W29" t="n">
-        <v>1.019274447629305</v>
+        <v>1.0020380036608</v>
       </c>
       <c r="X29" t="n">
-        <v>112.1725</v>
+        <v>106.7524999999999</v>
       </c>
       <c r="Y29" t="n">
-        <v>106.9388134407953</v>
+        <v>98.24976661596389</v>
       </c>
       <c r="Z29" t="n">
-        <v>13315516082</v>
+        <v>206614652.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>0053.TW</t>
+          <t>0050.TW</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>元大科技市值</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6.761379120499327</v>
+        <v>5.567342277892016</v>
       </c>
       <c r="D30" t="n">
-        <v>4.997785128026342</v>
+        <v>5.567342277892016</v>
       </c>
       <c r="E30" t="n">
-        <v>243.5</v>
+        <v>109</v>
       </c>
       <c r="F30" t="n">
-        <v>16.62</v>
+        <v>23.58</v>
       </c>
       <c r="G30" t="n">
-        <v>1190</v>
+        <v>1695</v>
       </c>
       <c r="H30" t="n">
-        <v>89.16</v>
+        <v>90.97</v>
       </c>
       <c r="I30" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="J30" t="n">
-        <v>13.83697478991597</v>
+        <v>13.46961651917404</v>
       </c>
       <c r="K30" t="n">
-        <v>364240.2</v>
+        <v>108038688.85</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>11.49</v>
+        <v>13.94</v>
       </c>
       <c r="O30" t="n">
-        <v>-7.24</v>
+        <v>-5.91</v>
       </c>
       <c r="P30" t="n">
-        <v>4.25</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="Q30" t="n">
-        <v>7.58</v>
+        <v>6.04</v>
       </c>
       <c r="R30" t="n">
-        <v>1.763593992472985</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>18.91</v>
+        <v>4.84625</v>
       </c>
       <c r="T30" t="n">
-        <v>2598</v>
+        <v>3824.71</v>
       </c>
       <c r="U30" t="n">
-        <v>16466</v>
+        <v>22831</v>
       </c>
       <c r="V30" t="n">
-        <v>0.9644041784246741</v>
+        <v>0.9717176669861147</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01898837440031</v>
+        <v>1.019274447629305</v>
       </c>
       <c r="X30" t="n">
-        <v>252.4875000000001</v>
+        <v>112.1725</v>
       </c>
       <c r="Y30" t="n">
-        <v>238.9624907578591</v>
+        <v>106.9388134407953</v>
       </c>
       <c r="Z30" t="n">
-        <v>241519127.5</v>
+        <v>13315516082</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>00892.TW</t>
+          <t>0053.TW</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>富邦台灣半導體</t>
+          <t>元大科技市值</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1.862203102689735</v>
+        <v>6.761379120499327</v>
       </c>
       <c r="D31" t="n">
-        <v>1.781296736363694</v>
+        <v>4.997785128026342</v>
       </c>
       <c r="E31" t="n">
-        <v>41.06</v>
+        <v>243.5</v>
       </c>
       <c r="F31" t="n">
-        <v>24.57</v>
+        <v>16.62</v>
       </c>
       <c r="G31" t="n">
-        <v>241</v>
+        <v>1190</v>
       </c>
       <c r="H31" t="n">
-        <v>75.09999999999999</v>
+        <v>89.16</v>
       </c>
       <c r="I31" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="J31" t="n">
-        <v>15.85892116182573</v>
+        <v>13.83697478991597</v>
       </c>
       <c r="K31" t="n">
-        <v>4494633.75</v>
+        <v>364240.2</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="M31" t="n">
         <v>2</v>
       </c>
       <c r="N31" t="n">
-        <v>12.37</v>
+        <v>11.49</v>
       </c>
       <c r="O31" t="n">
-        <v>-7.43</v>
+        <v>-7.24</v>
       </c>
       <c r="P31" t="n">
-        <v>4.94</v>
+        <v>4.25</v>
       </c>
       <c r="Q31" t="n">
-        <v>18.86</v>
+        <v>7.58</v>
       </c>
       <c r="R31" t="n">
-        <v>0.0809063663260412</v>
+        <v>1.763593992472985</v>
       </c>
       <c r="S31" t="n">
-        <v>4.937</v>
+        <v>18.91</v>
       </c>
       <c r="T31" t="n">
-        <v>510.5</v>
+        <v>2598</v>
       </c>
       <c r="U31" t="n">
-        <v>3822</v>
+        <v>16466</v>
       </c>
       <c r="V31" t="n">
-        <v>0.9568753568473918</v>
+        <v>0.9644041784246741</v>
       </c>
       <c r="W31" t="n">
-        <v>1.003684847366265</v>
+        <v>1.01898837440031</v>
       </c>
       <c r="X31" t="n">
-        <v>42.9105</v>
+        <v>252.4875000000001</v>
       </c>
       <c r="Y31" t="n">
-        <v>40.90925563710975</v>
+        <v>238.9624907578591</v>
       </c>
       <c r="Z31" t="n">
-        <v>163270984</v>
+        <v>241519127.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>006208.TW</t>
+          <t>00892.TW</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>富邦台50</t>
+          <t>富邦台灣半導體</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4.153757639681457</v>
+        <v>1.862203102689735</v>
       </c>
       <c r="D32" t="n">
-        <v>3.883665366759812</v>
+        <v>1.781296736363694</v>
       </c>
       <c r="E32" t="n">
-        <v>250.35</v>
+        <v>41.06</v>
       </c>
       <c r="F32" t="n">
-        <v>22.14</v>
+        <v>24.57</v>
       </c>
       <c r="G32" t="n">
-        <v>895</v>
+        <v>241</v>
       </c>
       <c r="H32" t="n">
-        <v>88.48999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="J32" t="n">
-        <v>13.86703910614525</v>
+        <v>15.85892116182573</v>
       </c>
       <c r="K32" t="n">
-        <v>2962549.85</v>
+        <v>4494633.75</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -3178,43 +3178,211 @@
         <v>2</v>
       </c>
       <c r="N32" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="O32" t="n">
+        <v>-7.43</v>
+      </c>
+      <c r="P32" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.0809063663260412</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4.937</v>
+      </c>
+      <c r="T32" t="n">
+        <v>510.5</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3822</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.9568753568473918</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.003684847366265</v>
+      </c>
+      <c r="X32" t="n">
+        <v>42.9105</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>40.90925563710975</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>163270984</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>006208.TW</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>富邦台50</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>4.153757639681457</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3.883665366759812</v>
+      </c>
+      <c r="E33" t="n">
+        <v>250.35</v>
+      </c>
+      <c r="F33" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="G33" t="n">
+        <v>895</v>
+      </c>
+      <c r="H33" t="n">
+        <v>88.48999999999999</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="J33" t="n">
+        <v>13.86703910614525</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2962549.85</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>2</v>
+      </c>
+      <c r="N33" t="n">
         <v>11.21</v>
       </c>
-      <c r="O32" t="n">
+      <c r="O33" t="n">
         <v>-6.25</v>
       </c>
-      <c r="P32" t="n">
+      <c r="P33" t="n">
         <v>4.960000000000001</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="Q33" t="n">
         <v>8.949999999999999</v>
       </c>
-      <c r="R32" t="n">
+      <c r="R33" t="n">
         <v>0.2700922729216453</v>
       </c>
-      <c r="S32" t="n">
+      <c r="S33" t="n">
         <v>28.764</v>
       </c>
-      <c r="T32" t="n">
+      <c r="T33" t="n">
         <v>1745.92</v>
       </c>
-      <c r="U32" t="n">
+      <c r="U33" t="n">
         <v>12411</v>
       </c>
-      <c r="V32" t="n">
+      <c r="V33" t="n">
         <v>0.9749021593099553</v>
       </c>
-      <c r="W32" t="n">
+      <c r="W33" t="n">
         <v>1.021631766481664</v>
       </c>
-      <c r="X32" t="n">
+      <c r="X33" t="n">
         <v>256.795</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="Y33" t="n">
         <v>245.0491539257489</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="Z33" t="n">
         <v>648338154.4499999</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>009823.TWO</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>群益S&amp;P500</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.03145641457412363</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.02427670054395836</v>
+      </c>
+      <c r="E34" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="F34" t="n">
+        <v>85.79000000000001</v>
+      </c>
+      <c r="G34" t="n">
+        <v>15</v>
+      </c>
+      <c r="H34" t="n">
+        <v>100</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="J34" t="n">
+        <v>16.93333333333333</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3179186.65</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="n">
+        <v>2</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P34" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>29.52</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.007179714030165263</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="U34" t="n">
+        <v>254</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.02026289564846</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.045460592772429</v>
+      </c>
+      <c r="X34" t="n">
+        <v>10.5365</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>10.28254921736683</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>30064095</v>
       </c>
     </row>
   </sheetData>

--- a/ETF動態清單.xlsx
+++ b/ETF動態清單.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z34"/>
+  <dimension ref="A1:Z30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,16 +567,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7255896520598688</v>
+        <v>0.7106597655702638</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5495491016136373</v>
+        <v>0.5360004308173951</v>
       </c>
       <c r="E2" t="n">
-        <v>29.53</v>
+        <v>29.3</v>
       </c>
       <c r="F2" t="n">
-        <v>24.75</v>
+        <v>22.02</v>
       </c>
       <c r="G2" t="n">
         <v>41</v>
@@ -591,7 +591,7 @@
         <v>8.439024390243903</v>
       </c>
       <c r="K2" t="n">
-        <v>166974010.75</v>
+        <v>168764951.85</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         <v>386.28</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1760405504462315</v>
+        <v>0.1746593347528687</v>
       </c>
       <c r="S2" t="n">
         <v>1.67</v>
@@ -626,230 +626,230 @@
         <v>346</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9630342263603305</v>
+        <v>0.9540244855431103</v>
       </c>
       <c r="W2" t="n">
-        <v>1.054652605538069</v>
+        <v>1.039437780953039</v>
       </c>
       <c r="X2" t="n">
-        <v>30.66350000000001</v>
+        <v>30.712</v>
       </c>
       <c r="Y2" t="n">
-        <v>27.99974118959693</v>
+        <v>28.18831539212999</v>
       </c>
       <c r="Z2" t="n">
-        <v>3540808322.39</v>
+        <v>5239257993.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>00992A.TW</t>
+          <t>00947.TW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>主動群益科技創新</t>
+          <t>台新臺灣IC設計</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2311331798365219</v>
+        <v>1.147445446668242</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2055125030732763</v>
+        <v>0.8792832653857314</v>
       </c>
       <c r="E3" t="n">
-        <v>18.42</v>
+        <v>34.81</v>
       </c>
       <c r="F3" t="n">
-        <v>31.99</v>
+        <v>17.81</v>
       </c>
       <c r="G3" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
+        <v>96.97</v>
       </c>
       <c r="I3" t="n">
-        <v>8.390000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="J3" t="n">
-        <v>10.27272727272727</v>
+        <v>10.33333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>50872547.3</v>
+        <v>12932063.2</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>15.18</v>
+        <v>18.77</v>
       </c>
       <c r="O3" t="n">
-        <v>2.64</v>
+        <v>-0.73</v>
       </c>
       <c r="P3" t="n">
-        <v>17.82</v>
+        <v>18.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>317.42</v>
+        <v>159.78</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02562067676324564</v>
+        <v>0.2681621812825108</v>
       </c>
       <c r="S3" t="n">
-        <v>0.47</v>
+        <v>2.78</v>
       </c>
       <c r="T3" t="n">
-        <v>277.02</v>
+        <v>495.22</v>
       </c>
       <c r="U3" t="n">
-        <v>339</v>
+        <v>682</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9693716450899912</v>
+        <v>0.8833007688599048</v>
       </c>
       <c r="W3" t="n">
-        <v>1.062304008630692</v>
+        <v>0.9741148649012943</v>
       </c>
       <c r="X3" t="n">
-        <v>19.00199999999999</v>
+        <v>39.40900000000001</v>
       </c>
       <c r="Y3" t="n">
-        <v>17.33966910634494</v>
+        <v>35.73500544366218</v>
       </c>
       <c r="Z3" t="n">
-        <v>1133795392.2</v>
+        <v>408671314.55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>00947.TW</t>
+          <t>00980A.TW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>台新臺灣IC設計</t>
+          <t>主動野村臺灣優選</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.177604725738289</v>
+        <v>0.6053329273268098</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8953979892033781</v>
+        <v>0.5784276669036545</v>
       </c>
       <c r="E4" t="n">
-        <v>35.3</v>
+        <v>24.42</v>
       </c>
       <c r="F4" t="n">
-        <v>20.68</v>
+        <v>25.04</v>
       </c>
       <c r="G4" t="n">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="H4" t="n">
-        <v>96.97</v>
+        <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>7.5</v>
+        <v>7.02</v>
       </c>
       <c r="J4" t="n">
-        <v>10.33333333333333</v>
+        <v>9.824999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>12466215.35</v>
+        <v>8719508.35</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>18.77</v>
+        <v>15.61</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.73</v>
+        <v>2.11</v>
       </c>
       <c r="P4" t="n">
-        <v>18.04</v>
+        <v>17.72</v>
       </c>
       <c r="Q4" t="n">
-        <v>159.78</v>
+        <v>246.15</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2822067365349106</v>
+        <v>0.02690526042315522</v>
       </c>
       <c r="S4" t="n">
-        <v>2.78</v>
+        <v>1.814</v>
       </c>
       <c r="T4" t="n">
-        <v>495.22</v>
+        <v>280.74</v>
       </c>
       <c r="U4" t="n">
-        <v>682</v>
+        <v>393</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8932638291411504</v>
+        <v>0.9551188031680851</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9725987873236147</v>
+        <v>1.021706527354016</v>
       </c>
       <c r="X4" t="n">
-        <v>39.51800000000001</v>
+        <v>25.56749999999998</v>
       </c>
       <c r="Y4" t="n">
-        <v>36.29451368856638</v>
+        <v>23.9011882044467</v>
       </c>
       <c r="Z4" t="n">
-        <v>536836363.6999999</v>
+        <v>246004857.78</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>00980A.TW</t>
+          <t>009816.TW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>主動野村臺灣優選</t>
+          <t>凱基台灣TOP50</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6170159499064141</v>
+        <v>0.1772017889114621</v>
       </c>
       <c r="D5" t="n">
-        <v>0.592348436023842</v>
+        <v>0.1452103122688952</v>
       </c>
       <c r="E5" t="n">
-        <v>24.58</v>
+        <v>16.07</v>
       </c>
       <c r="F5" t="n">
-        <v>28.51</v>
+        <v>19.03</v>
       </c>
       <c r="G5" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="H5" t="n">
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>7.02</v>
+        <v>5.32</v>
       </c>
       <c r="J5" t="n">
-        <v>9.824999999999999</v>
+        <v>10.54166666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>8590319.1</v>
+        <v>128377771.2</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -860,82 +860,82 @@
         <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>15.61</v>
+        <v>8.99</v>
       </c>
       <c r="O5" t="n">
-        <v>2.11</v>
+        <v>0.64</v>
       </c>
       <c r="P5" t="n">
-        <v>17.72</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>246.15</v>
+        <v>227.93</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02466751388257205</v>
+        <v>0.03199147664256685</v>
       </c>
       <c r="S5" t="n">
-        <v>1.814</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>280.74</v>
+        <v>127.78</v>
       </c>
       <c r="U5" t="n">
-        <v>393</v>
+        <v>253</v>
       </c>
       <c r="V5" t="n">
-        <v>0.962016398896304</v>
+        <v>0.9707330333142046</v>
       </c>
       <c r="W5" t="n">
-        <v>1.031403705040077</v>
+        <v>1.007210864962434</v>
       </c>
       <c r="X5" t="n">
-        <v>25.55049999999998</v>
+        <v>16.5545</v>
       </c>
       <c r="Y5" t="n">
-        <v>23.83159947931823</v>
+        <v>15.9549510028363</v>
       </c>
       <c r="Z5" t="n">
-        <v>145144924.58</v>
+        <v>3043774844.97</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>00985A.TW</t>
+          <t>009804.TW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>主動野村台灣50</t>
+          <t>聯邦台精彩50</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.4987261442170574</v>
+        <v>0.636100672909911</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4643816745978988</v>
+        <v>0.6149939475642905</v>
       </c>
       <c r="E6" t="n">
         <v>23.14</v>
       </c>
       <c r="F6" t="n">
-        <v>21.1</v>
+        <v>20.6</v>
       </c>
       <c r="G6" t="n">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="H6" t="n">
         <v>100</v>
       </c>
       <c r="I6" t="n">
-        <v>6.95</v>
+        <v>4.12</v>
       </c>
       <c r="J6" t="n">
-        <v>9.972972972972974</v>
+        <v>8.82258064516129</v>
       </c>
       <c r="K6" t="n">
-        <v>53732129.7</v>
+        <v>1203554.75</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -946,168 +946,168 @@
         <v>2</v>
       </c>
       <c r="N6" t="n">
-        <v>15.02</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>2.1</v>
+        <v>0.76</v>
       </c>
       <c r="P6" t="n">
-        <v>17.12</v>
+        <v>10.39</v>
       </c>
       <c r="Q6" t="n">
-        <v>252.13</v>
+        <v>133.05</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0343444696191586</v>
+        <v>0.02110672534562053</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.786</v>
       </c>
       <c r="T6" t="n">
-        <v>257.02</v>
+        <v>255.36</v>
       </c>
       <c r="U6" t="n">
-        <v>369</v>
+        <v>547</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9799686613306227</v>
+        <v>0.9643072948138272</v>
       </c>
       <c r="W6" t="n">
-        <v>1.032685622593113</v>
+        <v>1.010128656350611</v>
       </c>
       <c r="X6" t="n">
-        <v>23.61300000000001</v>
+        <v>23.9965</v>
       </c>
       <c r="Y6" t="n">
-        <v>22.40759384438274</v>
+        <v>22.90797301365561</v>
       </c>
       <c r="Z6" t="n">
-        <v>3634093195.98</v>
+        <v>31118741.42</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>00410A.TW</t>
+          <t>00830.TW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>主動永豐科技趨勢</t>
+          <t>國泰費城半導體</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01465696374479331</v>
+        <v>2.421126902386662</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0084235501626031</v>
+        <v>2.277783403816951</v>
       </c>
       <c r="E7" t="n">
-        <v>11.97</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>25.16</v>
+        <v>19.75</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>495</v>
       </c>
       <c r="H7" t="n">
-        <v>100</v>
+        <v>97.17</v>
       </c>
       <c r="I7" t="n">
-        <v>5.53</v>
+        <v>3.93</v>
       </c>
       <c r="J7" t="n">
-        <v>7.6</v>
+        <v>12.29090909090909</v>
       </c>
       <c r="K7" t="n">
-        <v>5509246.85</v>
+        <v>10002711.85</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>2</v>
       </c>
       <c r="N7" t="n">
-        <v>5.92</v>
+        <v>13.29</v>
       </c>
       <c r="O7" t="n">
-        <v>4.92</v>
+        <v>-12.33</v>
       </c>
       <c r="P7" t="n">
-        <v>10.84</v>
+        <v>0.9599999999999991</v>
       </c>
       <c r="Q7" t="n">
-        <v>942.39</v>
+        <v>19.85</v>
       </c>
       <c r="R7" t="n">
-        <v>0.006233413582190206</v>
+        <v>0.1433434985697111</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>17.71</v>
       </c>
       <c r="T7" t="n">
-        <v>27.64</v>
+        <v>1946.3</v>
       </c>
       <c r="U7" t="n">
-        <v>38</v>
+        <v>6084</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9624120603015073</v>
+        <v>0.9403368541250358</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03918573634375</v>
+        <v>1.028011627786029</v>
       </c>
       <c r="X7" t="n">
-        <v>12.4375</v>
+        <v>87.57499999999999</v>
       </c>
       <c r="Y7" t="n">
-        <v>11.51863385087925</v>
+        <v>80.10609780489796</v>
       </c>
       <c r="Z7" t="n">
-        <v>223274566.62</v>
+        <v>1093152769.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>009816.TW</t>
+          <t>009818.TW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>凱基台灣TOP50</t>
+          <t>華南永昌NASDAQxT</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.1877881951291229</v>
+        <v>0.09749486396746132</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1550481558448826</v>
+        <v>0.09427884909152739</v>
       </c>
       <c r="E8" t="n">
-        <v>16.2</v>
+        <v>20.77</v>
       </c>
       <c r="F8" t="n">
-        <v>24.08</v>
+        <v>33.16</v>
       </c>
       <c r="G8" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H8" t="n">
         <v>100</v>
       </c>
       <c r="I8" t="n">
-        <v>5.32</v>
+        <v>3.81</v>
       </c>
       <c r="J8" t="n">
-        <v>10.54166666666667</v>
+        <v>8.714285714285714</v>
       </c>
       <c r="K8" t="n">
-        <v>122203861</v>
+        <v>176191.7</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1118,168 +1118,168 @@
         <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>8.99</v>
+        <v>7.21</v>
       </c>
       <c r="O8" t="n">
-        <v>0.64</v>
+        <v>1.65</v>
       </c>
       <c r="P8" t="n">
-        <v>9.630000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>227.93</v>
+        <v>222.85</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0327400392842403</v>
+        <v>0.003216014875933926</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>127.78</v>
+        <v>79.97</v>
       </c>
       <c r="U8" t="n">
-        <v>253</v>
+        <v>183</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9791181892357438</v>
+        <v>0.9823349965710502</v>
       </c>
       <c r="W8" t="n">
-        <v>1.018057953984275</v>
+        <v>1.024344404685684</v>
       </c>
       <c r="X8" t="n">
-        <v>16.5455</v>
+        <v>21.1435</v>
       </c>
       <c r="Y8" t="n">
-        <v>15.9126500967844</v>
+        <v>20.27638351416894</v>
       </c>
       <c r="Z8" t="n">
-        <v>2065562856</v>
+        <v>1930841.51</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>009824.TW</t>
+          <t>00400A.TW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>群益美國科技巨頭</t>
+          <t>主動國泰動能高息</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.02962496414078353</v>
+        <v>0.07881171002614584</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02427670054395836</v>
+        <v>0.06469478096652637</v>
       </c>
       <c r="E9" t="n">
-        <v>10.46</v>
+        <v>14.85</v>
       </c>
       <c r="F9" t="n">
-        <v>34.6</v>
+        <v>20.03</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="H9" t="n">
-        <v>100</v>
+        <v>68.75</v>
       </c>
       <c r="I9" t="n">
-        <v>5.26</v>
+        <v>3.77</v>
       </c>
       <c r="J9" t="n">
-        <v>5.75</v>
+        <v>13.1875</v>
       </c>
       <c r="K9" t="n">
-        <v>5497301.8</v>
+        <v>37902131.9</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>7.35</v>
+        <v>13.12</v>
       </c>
       <c r="O9" t="n">
-        <v>1.39</v>
+        <v>-0.83</v>
       </c>
       <c r="P9" t="n">
-        <v>8.74</v>
+        <v>12.29</v>
       </c>
       <c r="Q9" t="n">
-        <v>1975.8</v>
+        <v>126.3</v>
       </c>
       <c r="R9" t="n">
-        <v>0.005348263596825165</v>
+        <v>0.01411692905961948</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="T9" t="n">
-        <v>21.06</v>
+        <v>60.34</v>
       </c>
       <c r="U9" t="n">
-        <v>23</v>
+        <v>211</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9916571861964349</v>
+        <v>0.9512827904295182</v>
       </c>
       <c r="W9" t="n">
-        <v>1.040831361411564</v>
+        <v>1.024990378763319</v>
       </c>
       <c r="X9" t="n">
-        <v>10.54800000000001</v>
+        <v>15.61050000000001</v>
       </c>
       <c r="Y9" t="n">
-        <v>10.0496587514564</v>
+        <v>14.48794087015428</v>
       </c>
       <c r="Z9" t="n">
-        <v>23451435.06</v>
+        <v>576965579.85</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>009804.TW</t>
+          <t>00663L.TW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>聯邦台精彩50</t>
+          <t>國泰臺灣加權正2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.6527690309145673</v>
+        <v>11.58326662672362</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6292409931374718</v>
+        <v>2.959457119635012</v>
       </c>
       <c r="E10" t="n">
-        <v>23.37</v>
+        <v>105.4</v>
       </c>
       <c r="F10" t="n">
-        <v>25.13</v>
+        <v>19.92</v>
       </c>
       <c r="G10" t="n">
-        <v>62</v>
+        <v>564</v>
       </c>
       <c r="H10" t="n">
-        <v>100</v>
+        <v>89.89</v>
       </c>
       <c r="I10" t="n">
-        <v>4.12</v>
+        <v>3.76</v>
       </c>
       <c r="J10" t="n">
-        <v>8.82258064516129</v>
+        <v>11.9113475177305</v>
       </c>
       <c r="K10" t="n">
-        <v>1168846.5</v>
+        <v>5594778.05</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1290,82 +1290,82 @@
         <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>9.630000000000001</v>
+        <v>15.99</v>
       </c>
       <c r="O10" t="n">
-        <v>0.76</v>
+        <v>-24.46</v>
       </c>
       <c r="P10" t="n">
-        <v>10.39</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>133.05</v>
+        <v>18.35</v>
       </c>
       <c r="R10" t="n">
-        <v>0.02352803777709545</v>
+        <v>8.623809507088607</v>
       </c>
       <c r="S10" t="n">
-        <v>2.786</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>255.36</v>
+        <v>2121.97</v>
       </c>
       <c r="U10" t="n">
-        <v>547</v>
+        <v>6718</v>
       </c>
       <c r="V10" t="n">
-        <v>0.974562135112594</v>
+        <v>0.9320216646402117</v>
       </c>
       <c r="W10" t="n">
-        <v>1.023577788618202</v>
+        <v>1.018700630342283</v>
       </c>
       <c r="X10" t="n">
-        <v>23.98</v>
+        <v>113.0875000000001</v>
       </c>
       <c r="Y10" t="n">
-        <v>22.83167948725105</v>
+        <v>103.4651367247958</v>
       </c>
       <c r="Z10" t="n">
-        <v>23734548.63</v>
+        <v>691706261.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>00830.TW</t>
+          <t>00631L.TW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>國泰費城半導體</t>
+          <t>元大台灣50正2</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.478722479910694</v>
+        <v>15.51871870100241</v>
       </c>
       <c r="D11" t="n">
-        <v>2.304183650310986</v>
+        <v>3.380778789132927</v>
       </c>
       <c r="E11" t="n">
-        <v>83.95</v>
+        <v>36.51</v>
       </c>
       <c r="F11" t="n">
-        <v>25.6</v>
+        <v>18.02</v>
       </c>
       <c r="G11" t="n">
-        <v>495</v>
+        <v>644</v>
       </c>
       <c r="H11" t="n">
-        <v>97.17</v>
+        <v>89.44</v>
       </c>
       <c r="I11" t="n">
-        <v>3.93</v>
+        <v>3.74</v>
       </c>
       <c r="J11" t="n">
-        <v>12.29090909090909</v>
+        <v>12.68167701863354</v>
       </c>
       <c r="K11" t="n">
-        <v>9602204.550000001</v>
+        <v>193742009.9</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1376,168 +1376,168 @@
         <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>13.29</v>
+        <v>17.37</v>
       </c>
       <c r="O11" t="n">
-        <v>-12.33</v>
+        <v>-12.43</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9599999999999991</v>
+        <v>4.940000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>19.85</v>
+        <v>15.49</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1745388295997077</v>
+        <v>12.13793991186948</v>
       </c>
       <c r="S11" t="n">
-        <v>17.71</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1946.3</v>
+        <v>2407.1</v>
       </c>
       <c r="U11" t="n">
-        <v>6084</v>
+        <v>8167</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9601967288116209</v>
+        <v>0.9335089042584477</v>
       </c>
       <c r="W11" t="n">
-        <v>1.056441757249984</v>
+        <v>1.018627817067844</v>
       </c>
       <c r="X11" t="n">
-        <v>87.42999999999999</v>
+        <v>39.11049999999998</v>
       </c>
       <c r="Y11" t="n">
-        <v>79.46486346633029</v>
+        <v>35.84233553045442</v>
       </c>
       <c r="Z11" t="n">
-        <v>1271012318.45</v>
+        <v>11116292252.85</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>009818.TW</t>
+          <t>00904.TW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>華南永昌NASDAQxT</t>
+          <t>台新臺灣半導體30</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.1156296842849658</v>
+        <v>1.751513407768048</v>
       </c>
       <c r="D12" t="n">
-        <v>0.103519499132803</v>
+        <v>1.691166121618151</v>
       </c>
       <c r="E12" t="n">
-        <v>21.1</v>
+        <v>38.34</v>
       </c>
       <c r="F12" t="n">
-        <v>44.03</v>
+        <v>14.91</v>
       </c>
       <c r="G12" t="n">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H12" t="n">
-        <v>100</v>
+        <v>99.16</v>
       </c>
       <c r="I12" t="n">
-        <v>3.81</v>
+        <v>3.55</v>
       </c>
       <c r="J12" t="n">
-        <v>8.714285714285714</v>
+        <v>10.78242677824268</v>
       </c>
       <c r="K12" t="n">
-        <v>177723.05</v>
+        <v>3892492.15</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>7.21</v>
+        <v>11.85</v>
       </c>
       <c r="O12" t="n">
-        <v>1.65</v>
+        <v>-12.45</v>
       </c>
       <c r="P12" t="n">
-        <v>8.859999999999999</v>
+        <v>-0.5999999999999996</v>
       </c>
       <c r="Q12" t="n">
-        <v>222.85</v>
+        <v>37.53</v>
       </c>
       <c r="R12" t="n">
-        <v>0.01211018515216278</v>
+        <v>0.06034728614989726</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>7.050000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>79.97</v>
+        <v>848.62</v>
       </c>
       <c r="U12" t="n">
-        <v>183</v>
+        <v>2577</v>
       </c>
       <c r="V12" t="n">
-        <v>0.9998815306243337</v>
+        <v>0.8937167099849649</v>
       </c>
       <c r="W12" t="n">
-        <v>1.049676926661034</v>
+        <v>0.9727079822132222</v>
       </c>
       <c r="X12" t="n">
-        <v>21.1025</v>
+        <v>42.8995</v>
       </c>
       <c r="Y12" t="n">
-        <v>20.10142307987847</v>
+        <v>39.41573493903507</v>
       </c>
       <c r="Z12" t="n">
-        <v>2121415.1</v>
+        <v>112866212.16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>00400A.TW</t>
+          <t>00913.TW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>主動國泰動能高息</t>
+          <t>兆豐台灣晶圓製造</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.09077376921705294</v>
+        <v>1.612228827033246</v>
       </c>
       <c r="D13" t="n">
-        <v>0.07353434444261109</v>
+        <v>1.598627925307246</v>
       </c>
       <c r="E13" t="n">
-        <v>15.01</v>
+        <v>47.67</v>
       </c>
       <c r="F13" t="n">
-        <v>23.82</v>
+        <v>17.39</v>
       </c>
       <c r="G13" t="n">
-        <v>16</v>
+        <v>262</v>
       </c>
       <c r="H13" t="n">
-        <v>68.75</v>
+        <v>96.18000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>3.77</v>
+        <v>3.5</v>
       </c>
       <c r="J13" t="n">
-        <v>13.1875</v>
+        <v>12.79770992366412</v>
       </c>
       <c r="K13" t="n">
-        <v>37244546.85</v>
+        <v>1896834.35</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1548,82 +1548,82 @@
         <v>2</v>
       </c>
       <c r="N13" t="n">
-        <v>13.12</v>
+        <v>13.5</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.83</v>
+        <v>-9.19</v>
       </c>
       <c r="P13" t="n">
-        <v>12.29</v>
+        <v>4.31</v>
       </c>
       <c r="Q13" t="n">
-        <v>126.3</v>
+        <v>28.72</v>
       </c>
       <c r="R13" t="n">
-        <v>0.01723942477444185</v>
+        <v>0.01360090172599993</v>
       </c>
       <c r="S13" t="n">
-        <v>0.48</v>
+        <v>6.699999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>60.34</v>
+        <v>916.5599999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>211</v>
+        <v>3353</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9625496986020262</v>
+        <v>0.9185148076070833</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04100574061017</v>
+        <v>0.995141878359042</v>
       </c>
       <c r="X13" t="n">
-        <v>15.594</v>
+        <v>51.89899999999999</v>
       </c>
       <c r="Y13" t="n">
-        <v>14.41874853754612</v>
+        <v>47.90271722722226</v>
       </c>
       <c r="Z13" t="n">
-        <v>414207809.57</v>
+        <v>81345136.74000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>00663L.TW</t>
+          <t>00685L.TW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>國泰臺灣加權正2</t>
+          <t>群益臺灣加權正2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11.85068554150096</v>
+        <v>10.48488725298811</v>
       </c>
       <c r="D14" t="n">
-        <v>2.990905571760063</v>
+        <v>2.789079106297023</v>
       </c>
       <c r="E14" t="n">
-        <v>107.6</v>
+        <v>12.07</v>
       </c>
       <c r="F14" t="n">
-        <v>25.68</v>
+        <v>19.04</v>
       </c>
       <c r="G14" t="n">
-        <v>564</v>
+        <v>514</v>
       </c>
       <c r="H14" t="n">
-        <v>89.89</v>
+        <v>88.52</v>
       </c>
       <c r="I14" t="n">
-        <v>3.76</v>
+        <v>3.46</v>
       </c>
       <c r="J14" t="n">
-        <v>11.9113475177305</v>
+        <v>12.18093385214008</v>
       </c>
       <c r="K14" t="n">
-        <v>5490061.25</v>
+        <v>256803747.15</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1634,254 +1634,250 @@
         <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>15.99</v>
+        <v>15.89</v>
       </c>
       <c r="O14" t="n">
-        <v>-24.46</v>
+        <v>-18.5</v>
       </c>
       <c r="P14" t="n">
-        <v>-8.470000000000001</v>
+        <v>-2.609999999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>18.35</v>
+        <v>18.65</v>
       </c>
       <c r="R14" t="n">
-        <v>8.859779969740895</v>
+        <v>7.695808146691082</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2121.97</v>
+        <v>1777.84</v>
       </c>
       <c r="U14" t="n">
-        <v>6718</v>
+        <v>6261</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9526760812784977</v>
+        <v>0.9326585017192751</v>
       </c>
       <c r="W14" t="n">
-        <v>1.046680500137607</v>
+        <v>1.020272612613784</v>
       </c>
       <c r="X14" t="n">
-        <v>112.9450000000001</v>
+        <v>12.9415</v>
       </c>
       <c r="Y14" t="n">
-        <v>102.8011890790493</v>
+        <v>11.83017151570744</v>
       </c>
       <c r="Z14" t="n">
-        <v>524698703.2</v>
+        <v>4973428484.92</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>00631L.TW</t>
+          <t>009809.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>富邦淨零ESG50</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>15.81371276293106</v>
+        <v>0.3562151369824964</v>
       </c>
       <c r="D15" t="n">
-        <v>3.41535122330414</v>
+        <v>0.3151695928446534</v>
       </c>
       <c r="E15" t="n">
-        <v>37.15</v>
+        <v>18.12</v>
       </c>
       <c r="F15" t="n">
-        <v>22.13</v>
+        <v>21.22</v>
       </c>
       <c r="G15" t="n">
-        <v>644</v>
+        <v>34</v>
       </c>
       <c r="H15" t="n">
-        <v>89.44</v>
+        <v>97.06</v>
       </c>
       <c r="I15" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="J15" t="n">
-        <v>12.68167701863354</v>
+        <v>8.235294117647058</v>
       </c>
       <c r="K15" t="n">
-        <v>183487320.25</v>
+        <v>277035.05</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>17.37</v>
+        <v>7.76</v>
       </c>
       <c r="O15" t="n">
-        <v>-12.43</v>
+        <v>-0.12</v>
       </c>
       <c r="P15" t="n">
-        <v>4.940000000000001</v>
+        <v>7.64</v>
       </c>
       <c r="Q15" t="n">
-        <v>15.49</v>
+        <v>172.16</v>
       </c>
       <c r="R15" t="n">
-        <v>12.39836153962693</v>
+        <v>0.041045544137843</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
       <c r="T15" t="n">
-        <v>2407.1</v>
+        <v>115.56</v>
       </c>
       <c r="U15" t="n">
-        <v>8167</v>
+        <v>280</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9510278268438168</v>
+        <v>0.9738008867392178</v>
       </c>
       <c r="W15" t="n">
-        <v>1.042895193356935</v>
+        <v>1.002337123860659</v>
       </c>
       <c r="X15" t="n">
-        <v>39.06299999999998</v>
+        <v>18.60750000000001</v>
       </c>
       <c r="Y15" t="n">
-        <v>35.62198793957357</v>
+        <v>18.0777500589901</v>
       </c>
       <c r="Z15" t="n">
-        <v>6508238806.599999</v>
+        <v>27616601.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>00904.TW</t>
+          <t>00715L.TW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>台新臺灣半導體30</t>
+          <t>期街口布蘭特正2</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.783480168501113</v>
+        <v>5.448233845009139</v>
       </c>
       <c r="D16" t="n">
-        <v>1.713418307862876</v>
+        <v>2.647925835384552</v>
       </c>
       <c r="E16" t="n">
-        <v>38.83</v>
+        <v>80.2</v>
       </c>
       <c r="F16" t="n">
-        <v>18.71</v>
+        <v>85.87</v>
       </c>
       <c r="G16" t="n">
-        <v>239</v>
+        <v>425</v>
       </c>
       <c r="H16" t="n">
-        <v>99.16</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>3.55</v>
+        <v>3.32</v>
       </c>
       <c r="J16" t="n">
-        <v>10.78242677824268</v>
+        <v>17.11294117647059</v>
       </c>
       <c r="K16" t="n">
-        <v>3774460.05</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
+        <v>3301946.05</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>11.85</v>
+        <v>32.14</v>
       </c>
       <c r="O16" t="n">
-        <v>-12.45</v>
+        <v>-44.86</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.5999999999999996</v>
+        <v>-12.72</v>
       </c>
       <c r="Q16" t="n">
-        <v>37.53</v>
+        <v>14.59</v>
       </c>
       <c r="R16" t="n">
-        <v>0.07006186063823705</v>
+        <v>2.800308009624588</v>
       </c>
       <c r="S16" t="n">
-        <v>7.050000000000001</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>848.62</v>
+        <v>1409.31</v>
       </c>
       <c r="U16" t="n">
-        <v>2577</v>
+        <v>7273</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9026558958563375</v>
+        <v>1.15122371348597</v>
       </c>
       <c r="W16" t="n">
-        <v>0.96988252482245</v>
+        <v>1.352960677914911</v>
       </c>
       <c r="X16" t="n">
-        <v>43.0175</v>
+        <v>69.66499999999995</v>
       </c>
       <c r="Y16" t="n">
-        <v>40.03577650510648</v>
+        <v>59.27740643844778</v>
       </c>
       <c r="Z16" t="n">
-        <v>205621430.41</v>
+        <v>211541053.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>00913.TW</t>
+          <t>00675L.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>兆豐台灣晶圓製造</t>
+          <t>富邦臺灣加權正2</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.658344663775718</v>
+        <v>11.01369753516261</v>
       </c>
       <c r="D17" t="n">
-        <v>1.620251159374102</v>
+        <v>2.895851187620472</v>
       </c>
       <c r="E17" t="n">
-        <v>48.57</v>
+        <v>319.1</v>
       </c>
       <c r="F17" t="n">
-        <v>19.54</v>
+        <v>19.57</v>
       </c>
       <c r="G17" t="n">
-        <v>262</v>
+        <v>564</v>
       </c>
       <c r="H17" t="n">
-        <v>96.18000000000001</v>
+        <v>87.06</v>
       </c>
       <c r="I17" t="n">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="J17" t="n">
-        <v>12.79770992366412</v>
+        <v>12.38297872340426</v>
       </c>
       <c r="K17" t="n">
-        <v>1849223.85</v>
+        <v>1192472.1</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1892,508 +1888,512 @@
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>13.5</v>
+        <v>15.7</v>
       </c>
       <c r="O17" t="n">
-        <v>-9.19</v>
+        <v>-24.73</v>
       </c>
       <c r="P17" t="n">
-        <v>4.31</v>
+        <v>-9.030000000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>28.72</v>
+        <v>16.61</v>
       </c>
       <c r="R17" t="n">
-        <v>0.03809350440161641</v>
+        <v>8.117846347542136</v>
       </c>
       <c r="S17" t="n">
-        <v>6.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>916.5599999999999</v>
+        <v>1792.47</v>
       </c>
       <c r="U17" t="n">
-        <v>3353</v>
+        <v>6984</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9350994397489462</v>
+        <v>0.9313457230625539</v>
       </c>
       <c r="W17" t="n">
-        <v>1.009580139389076</v>
+        <v>1.018699297244358</v>
       </c>
       <c r="X17" t="n">
-        <v>51.94099999999999</v>
+        <v>342.6225000000002</v>
       </c>
       <c r="Y17" t="n">
-        <v>48.1091080391013</v>
+        <v>313.2425838156405</v>
       </c>
       <c r="Z17" t="n">
-        <v>54817996.23</v>
+        <v>549165675.3000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>00685L.TW</t>
+          <t>00935.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>群益臺灣加權正2</t>
+          <t>野村臺灣新科技50</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10.72745992536771</v>
+        <v>1.426545859982833</v>
       </c>
       <c r="D18" t="n">
-        <v>2.819281252814454</v>
+        <v>1.122299718392824</v>
       </c>
       <c r="E18" t="n">
-        <v>12.32</v>
+        <v>56.5</v>
       </c>
       <c r="F18" t="n">
-        <v>24.29</v>
+        <v>17.84</v>
       </c>
       <c r="G18" t="n">
-        <v>514</v>
+        <v>136</v>
       </c>
       <c r="H18" t="n">
-        <v>88.52</v>
+        <v>83.09</v>
       </c>
       <c r="I18" t="n">
-        <v>3.46</v>
+        <v>3.15</v>
       </c>
       <c r="J18" t="n">
-        <v>12.18093385214008</v>
+        <v>12.30882352941176</v>
       </c>
       <c r="K18" t="n">
-        <v>241723801.8</v>
+        <v>13165792.8</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>15.89</v>
+        <v>14.6</v>
       </c>
       <c r="O18" t="n">
-        <v>-18.5</v>
+        <v>-8.99</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.609999999999999</v>
+        <v>5.609999999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>18.65</v>
+        <v>43.74</v>
       </c>
       <c r="R18" t="n">
-        <v>7.908178672553253</v>
+        <v>0.3042461415900086</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="T18" t="n">
-        <v>1777.84</v>
+        <v>428.12</v>
       </c>
       <c r="U18" t="n">
-        <v>6261</v>
+        <v>1674</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9532283647336454</v>
+        <v>0.9345407931191332</v>
       </c>
       <c r="W18" t="n">
-        <v>1.048361971452616</v>
+        <v>1.008147249540754</v>
       </c>
       <c r="X18" t="n">
-        <v>12.9245</v>
+        <v>60.4575</v>
       </c>
       <c r="Y18" t="n">
-        <v>11.75166625219087</v>
+        <v>56.04340043157158</v>
       </c>
       <c r="Z18" t="n">
-        <v>2639403215.68</v>
+        <v>901522418.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>009809.TW</t>
+          <t>00894.TW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>富邦淨零ESG50</t>
+          <t>中信小資高價30</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.3687387630861929</v>
+        <v>2.051706280811482</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3267215405451394</v>
+        <v>1.742009527647736</v>
       </c>
       <c r="E19" t="n">
-        <v>18.27</v>
+        <v>47.41</v>
       </c>
       <c r="F19" t="n">
-        <v>23.89</v>
+        <v>22.74</v>
       </c>
       <c r="G19" t="n">
-        <v>34</v>
+        <v>243</v>
       </c>
       <c r="H19" t="n">
-        <v>97.06</v>
+        <v>82.72</v>
       </c>
       <c r="I19" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="J19" t="n">
-        <v>8.235294117647058</v>
+        <v>15.32921810699589</v>
       </c>
       <c r="K19" t="n">
-        <v>205449.65</v>
+        <v>1244361.95</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>7.76</v>
+        <v>15.7</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.12</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>7.64</v>
+        <v>7.319999999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>172.16</v>
+        <v>22.58</v>
       </c>
       <c r="R19" t="n">
-        <v>0.04201722254105356</v>
+        <v>0.3096967531637467</v>
       </c>
       <c r="S19" t="n">
-        <v>0.315</v>
+        <v>7.549999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>115.56</v>
+        <v>698.73</v>
       </c>
       <c r="U19" t="n">
-        <v>280</v>
+        <v>3725</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9826542960871316</v>
+        <v>0.9493106935114086</v>
       </c>
       <c r="W19" t="n">
-        <v>1.015245590929712</v>
+        <v>1.021567767247863</v>
       </c>
       <c r="X19" t="n">
-        <v>18.5925</v>
+        <v>49.94149999999998</v>
       </c>
       <c r="Y19" t="n">
-        <v>17.99564574643386</v>
+        <v>46.4090601915956</v>
       </c>
       <c r="Z19" t="n">
-        <v>6179571.72</v>
+        <v>71626553.89999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>00715L.TW</t>
+          <t>00901.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>期街口布蘭特正2</t>
+          <t>永豐智能車供應鏈</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5.165222188860139</v>
+        <v>1.776534460812764</v>
       </c>
       <c r="D20" t="n">
-        <v>2.677077241273147</v>
+        <v>1.707475648568086</v>
       </c>
       <c r="E20" t="n">
-        <v>76.65000000000001</v>
+        <v>45.38</v>
       </c>
       <c r="F20" t="n">
-        <v>83.13</v>
+        <v>19.72</v>
       </c>
       <c r="G20" t="n">
-        <v>425</v>
+        <v>276</v>
       </c>
       <c r="H20" t="n">
-        <v>77.65000000000001</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>3.32</v>
+        <v>2.79</v>
       </c>
       <c r="J20" t="n">
-        <v>17.11294117647059</v>
+        <v>13.22463768115942</v>
       </c>
       <c r="K20" t="n">
-        <v>3358093.8</v>
-      </c>
-      <c r="L20" t="inlineStr"/>
+        <v>252017.7</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="M20" t="n">
         <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>32.14</v>
+        <v>15.18</v>
       </c>
       <c r="O20" t="n">
-        <v>-44.86</v>
+        <v>-7.3</v>
       </c>
       <c r="P20" t="n">
-        <v>-12.72</v>
+        <v>7.88</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.59</v>
+        <v>24.17</v>
       </c>
       <c r="R20" t="n">
-        <v>2.488144947586992</v>
+        <v>0.06905881224467825</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>4.671</v>
       </c>
       <c r="T20" t="n">
-        <v>1409.31</v>
+        <v>771.28</v>
       </c>
       <c r="U20" t="n">
-        <v>7273</v>
+        <v>3650</v>
       </c>
       <c r="V20" t="n">
-        <v>1.107099010616019</v>
+        <v>0.9448556586193615</v>
       </c>
       <c r="W20" t="n">
-        <v>1.277993965285937</v>
+        <v>1.006347937439428</v>
       </c>
       <c r="X20" t="n">
-        <v>69.23499999999994</v>
+        <v>48.0285</v>
       </c>
       <c r="Y20" t="n">
-        <v>59.9768090319976</v>
+        <v>45.0937477106236</v>
       </c>
       <c r="Z20" t="n">
-        <v>134777680.8</v>
+        <v>11695923.54</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>00401A.TW</t>
+          <t>0057.TW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>主動摩根台灣鑫收</t>
+          <t>富邦摩台</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0716527544242318</v>
+        <v>6.125688580451323</v>
       </c>
       <c r="D21" t="n">
-        <v>0.07114066577626521</v>
+        <v>4.894842106366574</v>
       </c>
       <c r="E21" t="n">
-        <v>13.82</v>
+        <v>321.2</v>
       </c>
       <c r="F21" t="n">
-        <v>28.73</v>
+        <v>18.29</v>
       </c>
       <c r="G21" t="n">
-        <v>21</v>
+        <v>1245</v>
       </c>
       <c r="H21" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="I21" t="n">
-        <v>3.23</v>
+        <v>2.64</v>
       </c>
       <c r="J21" t="n">
-        <v>15.19047619047619</v>
+        <v>12.02409638554217</v>
       </c>
       <c r="K21" t="n">
-        <v>6995277.45</v>
+        <v>32132.2</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>11.76</v>
+        <v>14.45</v>
       </c>
       <c r="O21" t="n">
-        <v>0.36</v>
+        <v>-6.48</v>
       </c>
       <c r="P21" t="n">
-        <v>12.12</v>
+        <v>7.969999999999999</v>
       </c>
       <c r="Q21" t="n">
-        <v>80.95</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="R21" t="n">
-        <v>0.0005120886479665909</v>
+        <v>1.230846474084749</v>
       </c>
       <c r="S21" t="n">
-        <v>0.377</v>
+        <v>1.685</v>
       </c>
       <c r="T21" t="n">
-        <v>67.92</v>
+        <v>3287.55</v>
       </c>
       <c r="U21" t="n">
-        <v>319</v>
+        <v>14970</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9677193473846365</v>
+        <v>0.9617054402826432</v>
       </c>
       <c r="W21" t="n">
-        <v>1.006003017296597</v>
+        <v>1.00515087507034</v>
       </c>
       <c r="X21" t="n">
-        <v>14.28100000000001</v>
+        <v>333.99</v>
       </c>
       <c r="Y21" t="n">
-        <v>13.73753334968924</v>
+        <v>319.5540171792842</v>
       </c>
       <c r="Z21" t="n">
-        <v>105251945.3</v>
+        <v>4663502.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>00675L.TW</t>
+          <t>00881.TW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>富邦臺灣加權正2</t>
+          <t>國泰台灣科技龍頭</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>11.27055046677457</v>
+        <v>1.982169333508977</v>
       </c>
       <c r="D22" t="n">
-        <v>2.926815596457504</v>
+        <v>1.808596225383848</v>
       </c>
       <c r="E22" t="n">
-        <v>325.8</v>
+        <v>49.64</v>
       </c>
       <c r="F22" t="n">
-        <v>25.1</v>
+        <v>15.07</v>
       </c>
       <c r="G22" t="n">
-        <v>564</v>
+        <v>384</v>
       </c>
       <c r="H22" t="n">
-        <v>87.06</v>
+        <v>89.58</v>
       </c>
       <c r="I22" t="n">
-        <v>3.18</v>
+        <v>2.52</v>
       </c>
       <c r="J22" t="n">
-        <v>12.38297872340426</v>
+        <v>15.328125</v>
       </c>
       <c r="K22" t="n">
-        <v>1135452.95</v>
+        <v>17187915.25</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>15.7</v>
+        <v>10.9</v>
       </c>
       <c r="O22" t="n">
-        <v>-24.73</v>
+        <v>-4.28</v>
       </c>
       <c r="P22" t="n">
-        <v>-9.030000000000001</v>
+        <v>6.62</v>
       </c>
       <c r="Q22" t="n">
-        <v>16.61</v>
+        <v>15.81</v>
       </c>
       <c r="R22" t="n">
-        <v>8.343734870317068</v>
+        <v>0.173573108125129</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="T22" t="n">
-        <v>1792.47</v>
+        <v>966.91</v>
       </c>
       <c r="U22" t="n">
-        <v>6984</v>
+        <v>5886</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9520469886911541</v>
+        <v>0.9521891334580158</v>
       </c>
       <c r="W22" t="n">
-        <v>1.046486786764947</v>
+        <v>1.007241240366367</v>
       </c>
       <c r="X22" t="n">
-        <v>342.2100000000002</v>
+        <v>52.13249999999999</v>
       </c>
       <c r="Y22" t="n">
-        <v>311.3273900066722</v>
+        <v>49.28312901678282</v>
       </c>
       <c r="Z22" t="n">
-        <v>380264963.4</v>
+        <v>934623905.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>00935.TW</t>
+          <t>0052.TW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>野村臺灣新科技50</t>
+          <t>富邦科技</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.448598760881438</v>
+        <v>8.217639073277233</v>
       </c>
       <c r="D23" t="n">
-        <v>1.14028886333536</v>
+        <v>4.988736001779501</v>
       </c>
       <c r="E23" t="n">
-        <v>57</v>
+        <v>62.6</v>
       </c>
       <c r="F23" t="n">
-        <v>20.7</v>
+        <v>17.15</v>
       </c>
       <c r="G23" t="n">
-        <v>136</v>
+        <v>1111</v>
       </c>
       <c r="H23" t="n">
-        <v>83.09</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>3.15</v>
+        <v>2.45</v>
       </c>
       <c r="J23" t="n">
-        <v>12.30882352941176</v>
+        <v>14.18091809180918</v>
       </c>
       <c r="K23" t="n">
-        <v>12874184.75</v>
+        <v>20295188.5</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -2404,254 +2404,254 @@
         <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>14.6</v>
+        <v>12.7</v>
       </c>
       <c r="O23" t="n">
-        <v>-8.99</v>
+        <v>-14.18</v>
       </c>
       <c r="P23" t="n">
-        <v>5.609999999999999</v>
+        <v>-1.48</v>
       </c>
       <c r="Q23" t="n">
-        <v>43.74</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3083098975460787</v>
+        <v>3.228903071497732</v>
       </c>
       <c r="S23" t="n">
-        <v>4.98</v>
+        <v>2.232857285714286</v>
       </c>
       <c r="T23" t="n">
-        <v>428.12</v>
+        <v>2723.42</v>
       </c>
       <c r="U23" t="n">
-        <v>1674</v>
+        <v>15755</v>
       </c>
       <c r="V23" t="n">
-        <v>0.9429280397022332</v>
+        <v>0.958505588730668</v>
       </c>
       <c r="W23" t="n">
-        <v>1.017700783615503</v>
+        <v>1.007406986055328</v>
       </c>
       <c r="X23" t="n">
-        <v>60.45</v>
+        <v>65.31000000000007</v>
       </c>
       <c r="Y23" t="n">
-        <v>56.00860382312048</v>
+        <v>62.13973187253829</v>
       </c>
       <c r="Z23" t="n">
-        <v>571879062</v>
+        <v>1615717017.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>00894.TW</t>
+          <t>006203.TW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>中信小資高價30</t>
+          <t>元大MSCI台灣</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2.077371287842047</v>
+        <v>4.102448231997496</v>
       </c>
       <c r="D24" t="n">
-        <v>1.764513564068301</v>
+        <v>4.10212694686185</v>
       </c>
       <c r="E24" t="n">
-        <v>47.83</v>
+        <v>196.35</v>
       </c>
       <c r="F24" t="n">
-        <v>27.09</v>
+        <v>20.3</v>
       </c>
       <c r="G24" t="n">
-        <v>243</v>
+        <v>890</v>
       </c>
       <c r="H24" t="n">
-        <v>82.72</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>2.88</v>
+        <v>2.36</v>
       </c>
       <c r="J24" t="n">
-        <v>15.32921810699589</v>
+        <v>13.44831460674157</v>
       </c>
       <c r="K24" t="n">
-        <v>1243642.7</v>
+        <v>13704.3</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>15.7</v>
+        <v>8.85</v>
       </c>
       <c r="O24" t="n">
-        <v>-8.380000000000001</v>
+        <v>-7.45</v>
       </c>
       <c r="P24" t="n">
-        <v>7.319999999999999</v>
+        <v>1.399999999999999</v>
       </c>
       <c r="Q24" t="n">
-        <v>22.58</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="R24" t="n">
-        <v>0.312857723773746</v>
+        <v>0.0003212851356453328</v>
       </c>
       <c r="S24" t="n">
-        <v>7.549999999999999</v>
+        <v>20.78</v>
       </c>
       <c r="T24" t="n">
-        <v>698.73</v>
+        <v>2099.49</v>
       </c>
       <c r="U24" t="n">
-        <v>3725</v>
+        <v>11969</v>
       </c>
       <c r="V24" t="n">
-        <v>0.9585746638074436</v>
+        <v>0.9670270137161717</v>
       </c>
       <c r="W24" t="n">
-        <v>1.034862369645139</v>
+        <v>1.013415380429336</v>
       </c>
       <c r="X24" t="n">
-        <v>49.89699999999998</v>
+        <v>203.0449999999999</v>
       </c>
       <c r="Y24" t="n">
-        <v>46.21870637387387</v>
+        <v>193.7507598481639</v>
       </c>
       <c r="Z24" t="n">
-        <v>74313184.02</v>
+        <v>4282589.85</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>00901.TW</t>
+          <t>00735.TW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>永豐智能車供應鏈</t>
+          <t>國泰臺韓科技</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.799653169228881</v>
+        <v>2.878791469220793</v>
       </c>
       <c r="D25" t="n">
-        <v>1.729797367313188</v>
+        <v>2.52681650557835</v>
       </c>
       <c r="E25" t="n">
-        <v>45.76</v>
+        <v>97.5</v>
       </c>
       <c r="F25" t="n">
-        <v>22.74</v>
+        <v>15.99</v>
       </c>
       <c r="G25" t="n">
-        <v>276</v>
+        <v>498</v>
       </c>
       <c r="H25" t="n">
-        <v>89.48999999999999</v>
+        <v>86.55</v>
       </c>
       <c r="I25" t="n">
-        <v>2.79</v>
+        <v>2.28</v>
       </c>
       <c r="J25" t="n">
-        <v>13.22463768115942</v>
+        <v>13.81124497991968</v>
       </c>
       <c r="K25" t="n">
-        <v>240996.05</v>
+        <v>1815689.8</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>2</v>
       </c>
       <c r="N25" t="n">
-        <v>15.18</v>
+        <v>21.39</v>
       </c>
       <c r="O25" t="n">
-        <v>-7.3</v>
+        <v>-6.04</v>
       </c>
       <c r="P25" t="n">
-        <v>7.88</v>
+        <v>15.35</v>
       </c>
       <c r="Q25" t="n">
-        <v>24.17</v>
+        <v>14.26</v>
       </c>
       <c r="R25" t="n">
-        <v>0.06985580191569341</v>
+        <v>0.3519749636424434</v>
       </c>
       <c r="S25" t="n">
-        <v>4.671</v>
+        <v>13.37</v>
       </c>
       <c r="T25" t="n">
-        <v>771.28</v>
+        <v>1133.84</v>
       </c>
       <c r="U25" t="n">
-        <v>3650</v>
+        <v>6878</v>
       </c>
       <c r="V25" t="n">
-        <v>0.9526982011992005</v>
+        <v>0.9153640332347568</v>
       </c>
       <c r="W25" t="n">
-        <v>1.014414839709477</v>
+        <v>1.002179415849688</v>
       </c>
       <c r="X25" t="n">
-        <v>48.032</v>
+        <v>106.5149999999999</v>
       </c>
       <c r="Y25" t="n">
-        <v>45.10975018179486</v>
+        <v>97.28796905825052</v>
       </c>
       <c r="Z25" t="n">
-        <v>26318040.32</v>
+        <v>126732255</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>0057.TW</t>
+          <t>0050.TW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>富邦摩台</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6.171282091000382</v>
+        <v>5.517113833119172</v>
       </c>
       <c r="D26" t="n">
-        <v>4.940582575916224</v>
+        <v>5.517113833119172</v>
       </c>
       <c r="E26" t="n">
-        <v>323.2</v>
+        <v>108.15</v>
       </c>
       <c r="F26" t="n">
-        <v>22.08</v>
+        <v>19.4</v>
       </c>
       <c r="G26" t="n">
-        <v>1245</v>
+        <v>1695</v>
       </c>
       <c r="H26" t="n">
-        <v>93.33</v>
+        <v>90.97</v>
       </c>
       <c r="I26" t="n">
-        <v>2.64</v>
+        <v>2.26</v>
       </c>
       <c r="J26" t="n">
-        <v>12.02409638554217</v>
+        <v>13.46961651917404</v>
       </c>
       <c r="K26" t="n">
-        <v>32711.15</v>
+        <v>112686684.55</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -2662,82 +2662,82 @@
         <v>2</v>
       </c>
       <c r="N26" t="n">
-        <v>14.45</v>
+        <v>13.94</v>
       </c>
       <c r="O26" t="n">
-        <v>-6.48</v>
+        <v>-5.91</v>
       </c>
       <c r="P26" t="n">
-        <v>7.969999999999999</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>8.970000000000001</v>
+        <v>6.04</v>
       </c>
       <c r="R26" t="n">
-        <v>1.230699515084158</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>1.685</v>
+        <v>4.84625</v>
       </c>
       <c r="T26" t="n">
-        <v>3287.55</v>
+        <v>3824.71</v>
       </c>
       <c r="U26" t="n">
-        <v>14970</v>
+        <v>22831</v>
       </c>
       <c r="V26" t="n">
-        <v>0.9679109953131784</v>
+        <v>0.9636031540963155</v>
       </c>
       <c r="W26" t="n">
-        <v>1.012527865635011</v>
+        <v>1.008581638228937</v>
       </c>
       <c r="X26" t="n">
-        <v>333.915</v>
+        <v>112.235</v>
       </c>
       <c r="Y26" t="n">
-        <v>319.2010916137146</v>
+        <v>107.2297927115853</v>
       </c>
       <c r="Z26" t="n">
-        <v>9745126.4</v>
+        <v>17888729413.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>00881.TW</t>
+          <t>0053.TW</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>國泰台灣科技龍頭</t>
+          <t>元大科技市值</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2.001541810800669</v>
+        <v>6.688198963573957</v>
       </c>
       <c r="D27" t="n">
-        <v>1.831478871397924</v>
+        <v>4.951672611201002</v>
       </c>
       <c r="E27" t="n">
-        <v>50</v>
+        <v>241.1</v>
       </c>
       <c r="F27" t="n">
-        <v>17.28</v>
+        <v>14.18</v>
       </c>
       <c r="G27" t="n">
-        <v>384</v>
+        <v>1190</v>
       </c>
       <c r="H27" t="n">
-        <v>89.58</v>
+        <v>89.16</v>
       </c>
       <c r="I27" t="n">
-        <v>2.52</v>
+        <v>2.18</v>
       </c>
       <c r="J27" t="n">
-        <v>15.328125</v>
+        <v>13.83697478991597</v>
       </c>
       <c r="K27" t="n">
-        <v>16905344.85</v>
+        <v>405886.35</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2748,82 +2748,82 @@
         <v>2</v>
       </c>
       <c r="N27" t="n">
-        <v>10.9</v>
+        <v>11.49</v>
       </c>
       <c r="O27" t="n">
-        <v>-4.28</v>
+        <v>-7.24</v>
       </c>
       <c r="P27" t="n">
-        <v>6.62</v>
+        <v>4.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>15.81</v>
+        <v>7.58</v>
       </c>
       <c r="R27" t="n">
-        <v>0.1700629394027451</v>
+        <v>1.736526352372955</v>
       </c>
       <c r="S27" t="n">
-        <v>12.5</v>
+        <v>18.91</v>
       </c>
       <c r="T27" t="n">
-        <v>966.91</v>
+        <v>2598</v>
       </c>
       <c r="U27" t="n">
-        <v>5886</v>
+        <v>16466</v>
       </c>
       <c r="V27" t="n">
-        <v>0.9590854161471621</v>
+        <v>0.9545962960396721</v>
       </c>
       <c r="W27" t="n">
-        <v>1.014499722532838</v>
+        <v>1.007374794288037</v>
       </c>
       <c r="X27" t="n">
-        <v>52.133</v>
+        <v>252.5675000000001</v>
       </c>
       <c r="Y27" t="n">
-        <v>49.28537572703139</v>
+        <v>239.3349539486916</v>
       </c>
       <c r="Z27" t="n">
-        <v>521563400</v>
+        <v>218445038.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>0052.TW</t>
+          <t>00892.TW</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>富邦科技</t>
+          <t>富邦台灣半導體</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8.319216498042723</v>
+        <v>1.853719051855981</v>
       </c>
       <c r="D28" t="n">
-        <v>5.035259790978672</v>
+        <v>1.758705315655066</v>
       </c>
       <c r="E28" t="n">
-        <v>63.3</v>
+        <v>40.95</v>
       </c>
       <c r="F28" t="n">
-        <v>20.48</v>
+        <v>22.4</v>
       </c>
       <c r="G28" t="n">
-        <v>1111</v>
+        <v>241</v>
       </c>
       <c r="H28" t="n">
-        <v>88.20999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="J28" t="n">
-        <v>14.18091809180918</v>
+        <v>15.85892116182573</v>
       </c>
       <c r="K28" t="n">
-        <v>19618983.25</v>
+        <v>4493193.8</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -2834,555 +2834,211 @@
         <v>2</v>
       </c>
       <c r="N28" t="n">
-        <v>12.7</v>
+        <v>12.37</v>
       </c>
       <c r="O28" t="n">
-        <v>-14.18</v>
+        <v>-7.43</v>
       </c>
       <c r="P28" t="n">
-        <v>-1.48</v>
+        <v>4.94</v>
       </c>
       <c r="Q28" t="n">
-        <v>8.050000000000001</v>
+        <v>18.86</v>
       </c>
       <c r="R28" t="n">
-        <v>3.283956707064051</v>
+        <v>0.09501373620091469</v>
       </c>
       <c r="S28" t="n">
-        <v>2.232857285714286</v>
+        <v>4.937</v>
       </c>
       <c r="T28" t="n">
-        <v>2723.42</v>
+        <v>510.5</v>
       </c>
       <c r="U28" t="n">
-        <v>15755</v>
+        <v>3822</v>
       </c>
       <c r="V28" t="n">
-        <v>0.9697062540691651</v>
+        <v>0.9545677055409216</v>
       </c>
       <c r="W28" t="n">
-        <v>1.021202095783834</v>
+        <v>1.002303087174216</v>
       </c>
       <c r="X28" t="n">
-        <v>65.27750000000007</v>
+        <v>42.89900000000001</v>
       </c>
       <c r="Y28" t="n">
-        <v>61.98577173053432</v>
+        <v>40.85590528853898</v>
       </c>
       <c r="Z28" t="n">
-        <v>1082135781.6</v>
+        <v>145582901.1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>00735.TW</t>
+          <t>006208.TW</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>國泰臺韓科技</t>
+          <t>富邦台50</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2.914485721579601</v>
+        <v>4.106159394851079</v>
       </c>
       <c r="D29" t="n">
-        <v>2.555077770627909</v>
+        <v>3.845643524581418</v>
       </c>
       <c r="E29" t="n">
-        <v>98.45</v>
+        <v>247.9</v>
       </c>
       <c r="F29" t="n">
-        <v>17.71</v>
+        <v>18.33</v>
       </c>
       <c r="G29" t="n">
-        <v>498</v>
+        <v>895</v>
       </c>
       <c r="H29" t="n">
-        <v>86.55</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="J29" t="n">
-        <v>13.81124497991968</v>
+        <v>13.86703910614525</v>
       </c>
       <c r="K29" t="n">
-        <v>1775845.55</v>
+        <v>3143357.3</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>2</v>
       </c>
       <c r="N29" t="n">
-        <v>21.39</v>
+        <v>11.21</v>
       </c>
       <c r="O29" t="n">
-        <v>-6.04</v>
+        <v>-6.25</v>
       </c>
       <c r="P29" t="n">
-        <v>15.35</v>
+        <v>4.960000000000001</v>
       </c>
       <c r="Q29" t="n">
-        <v>14.26</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="R29" t="n">
-        <v>0.3594079509516925</v>
+        <v>0.2605158702696606</v>
       </c>
       <c r="S29" t="n">
-        <v>13.37</v>
+        <v>28.764</v>
       </c>
       <c r="T29" t="n">
-        <v>1133.84</v>
+        <v>1745.92</v>
       </c>
       <c r="U29" t="n">
-        <v>6878</v>
+        <v>12411</v>
       </c>
       <c r="V29" t="n">
-        <v>0.9222266457460024</v>
+        <v>0.964741594022416</v>
       </c>
       <c r="W29" t="n">
-        <v>1.0020380036608</v>
+        <v>1.008431453555654</v>
       </c>
       <c r="X29" t="n">
-        <v>106.7524999999999</v>
+        <v>256.96</v>
       </c>
       <c r="Y29" t="n">
-        <v>98.24976661596389</v>
+        <v>245.8273183823483</v>
       </c>
       <c r="Z29" t="n">
-        <v>206614652.2</v>
+        <v>1415915803.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>0050.TW</t>
+          <t>009823.TWO</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>元大台灣50</t>
+          <t>群益S&amp;P500</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5.567342277892016</v>
+        <v>0.02726883674646041</v>
       </c>
       <c r="D30" t="n">
-        <v>5.567342277892016</v>
+        <v>0.01609313418732206</v>
       </c>
       <c r="E30" t="n">
-        <v>109</v>
+        <v>10.71</v>
       </c>
       <c r="F30" t="n">
-        <v>23.58</v>
+        <v>81.83</v>
       </c>
       <c r="G30" t="n">
-        <v>1695</v>
+        <v>15</v>
       </c>
       <c r="H30" t="n">
-        <v>90.97</v>
+        <v>100</v>
       </c>
       <c r="I30" t="n">
-        <v>2.26</v>
+        <v>1.31</v>
       </c>
       <c r="J30" t="n">
-        <v>13.46961651917404</v>
+        <v>16.93333333333333</v>
       </c>
       <c r="K30" t="n">
-        <v>108038688.85</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
+        <v>3298145.95</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="n">
         <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>13.94</v>
+        <v>3.64</v>
       </c>
       <c r="O30" t="n">
-        <v>-5.91</v>
+        <v>0.45</v>
       </c>
       <c r="P30" t="n">
-        <v>8.029999999999999</v>
+        <v>4.09</v>
       </c>
       <c r="Q30" t="n">
-        <v>6.04</v>
+        <v>29.52</v>
       </c>
       <c r="R30" t="n">
+        <v>0.01117570255913836</v>
+      </c>
+      <c r="S30" t="n">
         <v>0</v>
       </c>
-      <c r="S30" t="n">
-        <v>4.84625</v>
-      </c>
       <c r="T30" t="n">
-        <v>3824.71</v>
+        <v>19.72</v>
       </c>
       <c r="U30" t="n">
-        <v>22831</v>
+        <v>254</v>
       </c>
       <c r="V30" t="n">
-        <v>0.9717176669861147</v>
+        <v>1.01463691914168</v>
       </c>
       <c r="W30" t="n">
-        <v>1.019274447629305</v>
+        <v>1.038852374957421</v>
       </c>
       <c r="X30" t="n">
-        <v>112.1725</v>
+        <v>10.5555</v>
       </c>
       <c r="Y30" t="n">
-        <v>106.9388134407953</v>
+        <v>10.30945325647349</v>
       </c>
       <c r="Z30" t="n">
-        <v>13315516082</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>0053.TW</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>元大科技市值</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>6.761379120499327</v>
-      </c>
-      <c r="D31" t="n">
-        <v>4.997785128026342</v>
-      </c>
-      <c r="E31" t="n">
-        <v>243.5</v>
-      </c>
-      <c r="F31" t="n">
-        <v>16.62</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1190</v>
-      </c>
-      <c r="H31" t="n">
-        <v>89.16</v>
-      </c>
-      <c r="I31" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="J31" t="n">
-        <v>13.83697478991597</v>
-      </c>
-      <c r="K31" t="n">
-        <v>364240.2</v>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="M31" t="n">
-        <v>2</v>
-      </c>
-      <c r="N31" t="n">
-        <v>11.49</v>
-      </c>
-      <c r="O31" t="n">
-        <v>-7.24</v>
-      </c>
-      <c r="P31" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>7.58</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.763593992472985</v>
-      </c>
-      <c r="S31" t="n">
-        <v>18.91</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2598</v>
-      </c>
-      <c r="U31" t="n">
-        <v>16466</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0.9644041784246741</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.01898837440031</v>
-      </c>
-      <c r="X31" t="n">
-        <v>252.4875000000001</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>238.9624907578591</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>241519127.5</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>00892.TW</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>富邦台灣半導體</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>1.862203102689735</v>
-      </c>
-      <c r="D32" t="n">
-        <v>1.781296736363694</v>
-      </c>
-      <c r="E32" t="n">
-        <v>41.06</v>
-      </c>
-      <c r="F32" t="n">
-        <v>24.57</v>
-      </c>
-      <c r="G32" t="n">
-        <v>241</v>
-      </c>
-      <c r="H32" t="n">
-        <v>75.09999999999999</v>
-      </c>
-      <c r="I32" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="J32" t="n">
-        <v>15.85892116182573</v>
-      </c>
-      <c r="K32" t="n">
-        <v>4494633.75</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="M32" t="n">
-        <v>2</v>
-      </c>
-      <c r="N32" t="n">
-        <v>12.37</v>
-      </c>
-      <c r="O32" t="n">
-        <v>-7.43</v>
-      </c>
-      <c r="P32" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>18.86</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0.0809063663260412</v>
-      </c>
-      <c r="S32" t="n">
-        <v>4.937</v>
-      </c>
-      <c r="T32" t="n">
-        <v>510.5</v>
-      </c>
-      <c r="U32" t="n">
-        <v>3822</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0.9568753568473918</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.003684847366265</v>
-      </c>
-      <c r="X32" t="n">
-        <v>42.9105</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>40.90925563710975</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>163270984</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>006208.TW</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>富邦台50</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>4.153757639681457</v>
-      </c>
-      <c r="D33" t="n">
-        <v>3.883665366759812</v>
-      </c>
-      <c r="E33" t="n">
-        <v>250.35</v>
-      </c>
-      <c r="F33" t="n">
-        <v>22.14</v>
-      </c>
-      <c r="G33" t="n">
-        <v>895</v>
-      </c>
-      <c r="H33" t="n">
-        <v>88.48999999999999</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="J33" t="n">
-        <v>13.86703910614525</v>
-      </c>
-      <c r="K33" t="n">
-        <v>2962549.85</v>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="M33" t="n">
-        <v>2</v>
-      </c>
-      <c r="N33" t="n">
-        <v>11.21</v>
-      </c>
-      <c r="O33" t="n">
-        <v>-6.25</v>
-      </c>
-      <c r="P33" t="n">
-        <v>4.960000000000001</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0.2700922729216453</v>
-      </c>
-      <c r="S33" t="n">
-        <v>28.764</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1745.92</v>
-      </c>
-      <c r="U33" t="n">
-        <v>12411</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0.9749021593099553</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.021631766481664</v>
-      </c>
-      <c r="X33" t="n">
-        <v>256.795</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>245.0491539257489</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>648338154.4499999</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>009823.TWO</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>群益S&amp;P500</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>0.03145641457412363</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0.02427670054395836</v>
-      </c>
-      <c r="E34" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="F34" t="n">
-        <v>85.79000000000001</v>
-      </c>
-      <c r="G34" t="n">
-        <v>15</v>
-      </c>
-      <c r="H34" t="n">
-        <v>100</v>
-      </c>
-      <c r="I34" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="J34" t="n">
-        <v>16.93333333333333</v>
-      </c>
-      <c r="K34" t="n">
-        <v>3179186.65</v>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="n">
-        <v>2</v>
-      </c>
-      <c r="N34" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="P34" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>29.52</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0.007179714030165263</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>19.72</v>
-      </c>
-      <c r="U34" t="n">
-        <v>254</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.02026289564846</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.045460592772429</v>
-      </c>
-      <c r="X34" t="n">
-        <v>10.5365</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>10.28254921736683</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>30064095</v>
+        <v>41376714.12</v>
       </c>
     </row>
   </sheetData>

--- a/ETF動態清單.xlsx
+++ b/ETF動態清單.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z30"/>
+  <dimension ref="A1:Z31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,16 +567,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7106597655702638</v>
+        <v>0.67692909998079</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5360004308173951</v>
+        <v>0.5218083266187941</v>
       </c>
       <c r="E2" t="n">
-        <v>29.3</v>
+        <v>28.73</v>
       </c>
       <c r="F2" t="n">
-        <v>22.02</v>
+        <v>15.77</v>
       </c>
       <c r="G2" t="n">
         <v>41</v>
@@ -591,7 +591,7 @@
         <v>8.439024390243903</v>
       </c>
       <c r="K2" t="n">
-        <v>168764951.85</v>
+        <v>165333560.3</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         <v>386.28</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1746593347528687</v>
+        <v>0.1551207733619959</v>
       </c>
       <c r="S2" t="n">
         <v>1.67</v>
@@ -626,230 +626,230 @@
         <v>346</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9540244855431103</v>
+        <v>0.9345520785895517</v>
       </c>
       <c r="W2" t="n">
-        <v>1.039437780953039</v>
+        <v>1.014119011332104</v>
       </c>
       <c r="X2" t="n">
-        <v>30.712</v>
+        <v>30.742</v>
       </c>
       <c r="Y2" t="n">
-        <v>28.18831539212999</v>
+        <v>28.33000829188822</v>
       </c>
       <c r="Z2" t="n">
-        <v>5239257993.8</v>
+        <v>3688463672.27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>00947.TW</t>
+          <t>00992A.TW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>台新臺灣IC設計</t>
+          <t>主動群益科技創新</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.147445446668242</v>
+        <v>0.2068094916405983</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8792832653857314</v>
+        <v>0.1842930299504741</v>
       </c>
       <c r="E3" t="n">
-        <v>34.81</v>
+        <v>17.23</v>
       </c>
       <c r="F3" t="n">
-        <v>17.81</v>
+        <v>20.39</v>
       </c>
       <c r="G3" t="n">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="H3" t="n">
-        <v>96.97</v>
+        <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>7.5</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>10.33333333333333</v>
+        <v>10.27272727272727</v>
       </c>
       <c r="K3" t="n">
-        <v>12932063.2</v>
+        <v>52912859.25</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>18.77</v>
+        <v>15.18</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.73</v>
+        <v>2.64</v>
       </c>
       <c r="P3" t="n">
-        <v>18.04</v>
+        <v>17.82</v>
       </c>
       <c r="Q3" t="n">
-        <v>159.78</v>
+        <v>317.42</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2681621812825108</v>
+        <v>0.02251646169012411</v>
       </c>
       <c r="S3" t="n">
-        <v>2.78</v>
+        <v>1.32</v>
       </c>
       <c r="T3" t="n">
-        <v>495.22</v>
+        <v>277.02</v>
       </c>
       <c r="U3" t="n">
-        <v>682</v>
+        <v>339</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8833007688599048</v>
+        <v>0.9072957531397282</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9741148649012943</v>
+        <v>0.9969527034807439</v>
       </c>
       <c r="X3" t="n">
-        <v>39.40900000000001</v>
+        <v>18.99049999999999</v>
       </c>
       <c r="Y3" t="n">
-        <v>35.73500544366218</v>
+        <v>17.28266540613559</v>
       </c>
       <c r="Z3" t="n">
-        <v>408671314.55</v>
+        <v>728324884.66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>00980A.TW</t>
+          <t>00947.TW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>主動野村臺灣優選</t>
+          <t>台新臺灣IC設計</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6053329273268098</v>
+        <v>1.124238857310905</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5784276669036545</v>
+        <v>0.8623571061925754</v>
       </c>
       <c r="E4" t="n">
-        <v>24.42</v>
+        <v>34.44</v>
       </c>
       <c r="F4" t="n">
-        <v>25.04</v>
+        <v>14.36</v>
       </c>
       <c r="G4" t="n">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="H4" t="n">
-        <v>100</v>
+        <v>96.97</v>
       </c>
       <c r="I4" t="n">
-        <v>7.02</v>
+        <v>7.5</v>
       </c>
       <c r="J4" t="n">
-        <v>9.824999999999999</v>
+        <v>10.33333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>8719508.35</v>
+        <v>13064478.15</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>15.61</v>
+        <v>18.77</v>
       </c>
       <c r="O4" t="n">
-        <v>2.11</v>
+        <v>-0.73</v>
       </c>
       <c r="P4" t="n">
-        <v>17.72</v>
+        <v>18.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>246.15</v>
+        <v>159.78</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02690526042315522</v>
+        <v>0.2618817511183296</v>
       </c>
       <c r="S4" t="n">
-        <v>1.814</v>
+        <v>2.78</v>
       </c>
       <c r="T4" t="n">
-        <v>280.74</v>
+        <v>495.22</v>
       </c>
       <c r="U4" t="n">
-        <v>393</v>
+        <v>682</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9551188031680851</v>
+        <v>0.876871371830125</v>
       </c>
       <c r="W4" t="n">
-        <v>1.021706527354016</v>
+        <v>0.9807286215278754</v>
       </c>
       <c r="X4" t="n">
-        <v>25.56749999999998</v>
+        <v>39.27600000000001</v>
       </c>
       <c r="Y4" t="n">
-        <v>23.9011882044467</v>
+        <v>35.1167481441971</v>
       </c>
       <c r="Z4" t="n">
-        <v>246004857.78</v>
+        <v>202690145.28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>009816.TW</t>
+          <t>00980A.TW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>凱基台灣TOP50</t>
+          <t>主動野村臺灣優選</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1772017889114621</v>
+        <v>0.5800497772786859</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1452103122688952</v>
+        <v>0.5638439122245398</v>
       </c>
       <c r="E5" t="n">
-        <v>16.07</v>
+        <v>24.04</v>
       </c>
       <c r="F5" t="n">
-        <v>19.03</v>
+        <v>18.89</v>
       </c>
       <c r="G5" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H5" t="n">
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>5.32</v>
+        <v>7.02</v>
       </c>
       <c r="J5" t="n">
-        <v>10.54166666666667</v>
+        <v>9.824999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>128377771.2</v>
+        <v>8767389.300000001</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -860,340 +860,340 @@
         <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>8.99</v>
+        <v>15.61</v>
       </c>
       <c r="O5" t="n">
-        <v>0.64</v>
+        <v>2.11</v>
       </c>
       <c r="P5" t="n">
-        <v>9.630000000000001</v>
+        <v>17.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>227.93</v>
+        <v>246.15</v>
       </c>
       <c r="R5" t="n">
-        <v>0.03199147664256685</v>
+        <v>0.01620586505414612</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.814</v>
       </c>
       <c r="T5" t="n">
-        <v>127.78</v>
+        <v>280.74</v>
       </c>
       <c r="U5" t="n">
-        <v>253</v>
+        <v>393</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9707330333142046</v>
+        <v>0.9402745726913604</v>
       </c>
       <c r="W5" t="n">
-        <v>1.007210864962434</v>
+        <v>1.005905631962899</v>
       </c>
       <c r="X5" t="n">
-        <v>16.5545</v>
+        <v>25.56699999999999</v>
       </c>
       <c r="Y5" t="n">
-        <v>15.9549510028363</v>
+        <v>23.89886211601078</v>
       </c>
       <c r="Z5" t="n">
-        <v>3043774844.97</v>
+        <v>146418312.48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>009804.TW</t>
+          <t>00985A.TW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>聯邦台精彩50</t>
+          <t>主動野村台灣50</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.636100672909911</v>
+        <v>0.4590799121013069</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6149939475642905</v>
+        <v>0.438176499589271</v>
       </c>
       <c r="E6" t="n">
-        <v>23.14</v>
+        <v>20.42</v>
       </c>
       <c r="F6" t="n">
-        <v>20.6</v>
+        <v>10.69</v>
       </c>
       <c r="G6" t="n">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="H6" t="n">
         <v>100</v>
       </c>
       <c r="I6" t="n">
-        <v>4.12</v>
+        <v>6.95</v>
       </c>
       <c r="J6" t="n">
-        <v>8.82258064516129</v>
+        <v>9.972972972972974</v>
       </c>
       <c r="K6" t="n">
-        <v>1203554.75</v>
+        <v>57528731.1</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>2</v>
       </c>
       <c r="N6" t="n">
-        <v>9.630000000000001</v>
+        <v>15.02</v>
       </c>
       <c r="O6" t="n">
-        <v>0.76</v>
+        <v>2.1</v>
       </c>
       <c r="P6" t="n">
-        <v>10.39</v>
+        <v>17.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>133.05</v>
+        <v>252.13</v>
       </c>
       <c r="R6" t="n">
-        <v>0.02110672534562053</v>
+        <v>0.02090341251203598</v>
       </c>
       <c r="S6" t="n">
-        <v>2.786</v>
+        <v>2.15</v>
       </c>
       <c r="T6" t="n">
-        <v>255.36</v>
+        <v>257.02</v>
       </c>
       <c r="U6" t="n">
-        <v>547</v>
+        <v>369</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9643072948138272</v>
+        <v>0.872239545512793</v>
       </c>
       <c r="W6" t="n">
-        <v>1.010128656350611</v>
+        <v>0.9603529510805866</v>
       </c>
       <c r="X6" t="n">
-        <v>23.9965</v>
+        <v>23.411</v>
       </c>
       <c r="Y6" t="n">
-        <v>22.90797301365561</v>
+        <v>21.26301582873617</v>
       </c>
       <c r="Z6" t="n">
-        <v>31118741.42</v>
+        <v>495913585.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>00830.TW</t>
+          <t>009816.TW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>國泰費城半導體</t>
+          <t>凱基台灣TOP50</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2.421126902386662</v>
+        <v>0.1659641055872365</v>
       </c>
       <c r="D7" t="n">
-        <v>2.277783403816951</v>
+        <v>0.134917613707711</v>
       </c>
       <c r="E7" t="n">
-        <v>82.34999999999999</v>
+        <v>15.93</v>
       </c>
       <c r="F7" t="n">
-        <v>19.75</v>
+        <v>13.25</v>
       </c>
       <c r="G7" t="n">
-        <v>495</v>
+        <v>24</v>
       </c>
       <c r="H7" t="n">
-        <v>97.17</v>
+        <v>100</v>
       </c>
       <c r="I7" t="n">
-        <v>3.93</v>
+        <v>5.32</v>
       </c>
       <c r="J7" t="n">
-        <v>12.29090909090909</v>
+        <v>10.54166666666667</v>
       </c>
       <c r="K7" t="n">
-        <v>10002711.85</v>
+        <v>134203129.05</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>2</v>
       </c>
       <c r="N7" t="n">
-        <v>13.29</v>
+        <v>8.99</v>
       </c>
       <c r="O7" t="n">
-        <v>-12.33</v>
+        <v>0.64</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9599999999999991</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>19.85</v>
+        <v>227.93</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1433434985697111</v>
+        <v>0.03104649187952546</v>
       </c>
       <c r="S7" t="n">
-        <v>17.71</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1946.3</v>
+        <v>127.78</v>
       </c>
       <c r="U7" t="n">
-        <v>6084</v>
+        <v>253</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9403368541250358</v>
+        <v>0.9625959272463593</v>
       </c>
       <c r="W7" t="n">
-        <v>1.028011627786029</v>
+        <v>1.000062576055201</v>
       </c>
       <c r="X7" t="n">
-        <v>87.57499999999999</v>
+        <v>16.549</v>
       </c>
       <c r="Y7" t="n">
-        <v>80.10609780489796</v>
+        <v>15.92900322581484</v>
       </c>
       <c r="Z7" t="n">
-        <v>1093152769.2</v>
+        <v>3042296935.56</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>009818.TW</t>
+          <t>009824.TW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>華南永昌NASDAQxT</t>
+          <t>群益美國科技巨頭</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.09749486396746132</v>
+        <v>0.01351643248194301</v>
       </c>
       <c r="D8" t="n">
-        <v>0.09427884909152739</v>
+        <v>0.007552616385237076</v>
       </c>
       <c r="E8" t="n">
-        <v>20.77</v>
+        <v>10.3</v>
       </c>
       <c r="F8" t="n">
-        <v>33.16</v>
+        <v>23.75</v>
       </c>
       <c r="G8" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
         <v>100</v>
       </c>
       <c r="I8" t="n">
-        <v>3.81</v>
+        <v>5.26</v>
       </c>
       <c r="J8" t="n">
-        <v>8.714285714285714</v>
+        <v>5.75</v>
       </c>
       <c r="K8" t="n">
-        <v>176191.7</v>
+        <v>5192747.7</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>7.21</v>
+        <v>7.35</v>
       </c>
       <c r="O8" t="n">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="P8" t="n">
-        <v>8.859999999999999</v>
+        <v>8.74</v>
       </c>
       <c r="Q8" t="n">
-        <v>222.85</v>
+        <v>1975.8</v>
       </c>
       <c r="R8" t="n">
-        <v>0.003216014875933926</v>
+        <v>0.005963816096705932</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>79.97</v>
+        <v>21.06</v>
       </c>
       <c r="U8" t="n">
-        <v>183</v>
+        <v>23</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9823349965710502</v>
+        <v>0.9738110995556392</v>
       </c>
       <c r="W8" t="n">
-        <v>1.024344404685684</v>
+        <v>1.011394838385178</v>
       </c>
       <c r="X8" t="n">
-        <v>21.1435</v>
+        <v>10.57700000000001</v>
       </c>
       <c r="Y8" t="n">
-        <v>20.27638351416894</v>
+        <v>10.18395547326035</v>
       </c>
       <c r="Z8" t="n">
-        <v>1930841.51</v>
+        <v>16287647.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>00400A.TW</t>
+          <t>009804.TW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>主動國泰動能高息</t>
+          <t>聯邦台精彩50</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.07881171002614584</v>
+        <v>0.6162644045109318</v>
       </c>
       <c r="D9" t="n">
-        <v>0.06469478096652637</v>
+        <v>0.6000673775179672</v>
       </c>
       <c r="E9" t="n">
-        <v>14.85</v>
+        <v>22.86</v>
       </c>
       <c r="F9" t="n">
-        <v>20.03</v>
+        <v>14.52</v>
       </c>
       <c r="G9" t="n">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="H9" t="n">
-        <v>68.75</v>
+        <v>100</v>
       </c>
       <c r="I9" t="n">
-        <v>3.77</v>
+        <v>4.12</v>
       </c>
       <c r="J9" t="n">
-        <v>13.1875</v>
+        <v>8.82258064516129</v>
       </c>
       <c r="K9" t="n">
-        <v>37902131.9</v>
+        <v>1230997.35</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1204,340 +1204,340 @@
         <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>13.12</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.83</v>
+        <v>0.76</v>
       </c>
       <c r="P9" t="n">
-        <v>12.29</v>
+        <v>10.39</v>
       </c>
       <c r="Q9" t="n">
-        <v>126.3</v>
+        <v>133.05</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01411692905961948</v>
+        <v>0.01619702699296455</v>
       </c>
       <c r="S9" t="n">
-        <v>0.48</v>
+        <v>2.786</v>
       </c>
       <c r="T9" t="n">
-        <v>60.34</v>
+        <v>255.36</v>
       </c>
       <c r="U9" t="n">
-        <v>211</v>
+        <v>547</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9512827904295182</v>
+        <v>0.9529169011442506</v>
       </c>
       <c r="W9" t="n">
-        <v>1.024990378763319</v>
+        <v>0.9993894935719506</v>
       </c>
       <c r="X9" t="n">
-        <v>15.61050000000001</v>
+        <v>23.9895</v>
       </c>
       <c r="Y9" t="n">
-        <v>14.48794087015428</v>
+        <v>22.87396470248584</v>
       </c>
       <c r="Z9" t="n">
-        <v>576965579.85</v>
+        <v>34374810.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>00663L.TW</t>
+          <t>00830.TW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>國泰臺灣加權正2</t>
+          <t>國泰費城半導體</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11.58326662672362</v>
+        <v>2.372366540092322</v>
       </c>
       <c r="D10" t="n">
-        <v>2.959457119635012</v>
+        <v>2.24993035161264</v>
       </c>
       <c r="E10" t="n">
-        <v>105.4</v>
+        <v>81</v>
       </c>
       <c r="F10" t="n">
-        <v>19.92</v>
+        <v>13.72</v>
       </c>
       <c r="G10" t="n">
-        <v>564</v>
+        <v>495</v>
       </c>
       <c r="H10" t="n">
-        <v>89.89</v>
+        <v>97.17</v>
       </c>
       <c r="I10" t="n">
-        <v>3.76</v>
+        <v>3.93</v>
       </c>
       <c r="J10" t="n">
-        <v>11.9113475177305</v>
+        <v>12.29090909090909</v>
       </c>
       <c r="K10" t="n">
-        <v>5594778.05</v>
+        <v>10532745.05</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>15.99</v>
+        <v>13.29</v>
       </c>
       <c r="O10" t="n">
-        <v>-24.46</v>
+        <v>-12.33</v>
       </c>
       <c r="P10" t="n">
-        <v>-8.470000000000001</v>
+        <v>0.9599999999999991</v>
       </c>
       <c r="Q10" t="n">
-        <v>18.35</v>
+        <v>19.85</v>
       </c>
       <c r="R10" t="n">
-        <v>8.623809507088607</v>
+        <v>0.1224361884796816</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>17.71</v>
       </c>
       <c r="T10" t="n">
-        <v>2121.97</v>
+        <v>1946.3</v>
       </c>
       <c r="U10" t="n">
-        <v>6718</v>
+        <v>6084</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9320216646402117</v>
+        <v>0.9246311463713935</v>
       </c>
       <c r="W10" t="n">
-        <v>1.018700630342283</v>
+        <v>1.009529726497441</v>
       </c>
       <c r="X10" t="n">
-        <v>113.0875000000001</v>
+        <v>87.60249999999999</v>
       </c>
       <c r="Y10" t="n">
-        <v>103.4651367247958</v>
+        <v>80.23537878476266</v>
       </c>
       <c r="Z10" t="n">
-        <v>691706261.2</v>
+        <v>1189319922</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>00631L.TW</t>
+          <t>009818.TW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>華南永昌NASDAQxT</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15.51871870100241</v>
+        <v>0.09419414424551587</v>
       </c>
       <c r="D11" t="n">
-        <v>3.380778789132927</v>
+        <v>0.08461124580855595</v>
       </c>
       <c r="E11" t="n">
-        <v>36.51</v>
+        <v>20.72</v>
       </c>
       <c r="F11" t="n">
-        <v>18.02</v>
+        <v>24.33</v>
       </c>
       <c r="G11" t="n">
-        <v>644</v>
+        <v>21</v>
       </c>
       <c r="H11" t="n">
-        <v>89.44</v>
+        <v>100</v>
       </c>
       <c r="I11" t="n">
-        <v>3.74</v>
+        <v>3.81</v>
       </c>
       <c r="J11" t="n">
-        <v>12.68167701863354</v>
+        <v>8.714285714285714</v>
       </c>
       <c r="K11" t="n">
-        <v>193742009.9</v>
+        <v>168580</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>17.37</v>
+        <v>7.21</v>
       </c>
       <c r="O11" t="n">
-        <v>-12.43</v>
+        <v>1.65</v>
       </c>
       <c r="P11" t="n">
-        <v>4.940000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>15.49</v>
+        <v>222.85</v>
       </c>
       <c r="R11" t="n">
-        <v>12.13793991186948</v>
+        <v>0.009582898436959919</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2407.1</v>
+        <v>79.97</v>
       </c>
       <c r="U11" t="n">
-        <v>8167</v>
+        <v>183</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9335089042584477</v>
+        <v>0.9784892918703219</v>
       </c>
       <c r="W11" t="n">
-        <v>1.018627817067844</v>
+        <v>1.014250998476293</v>
       </c>
       <c r="X11" t="n">
-        <v>39.11049999999998</v>
+        <v>21.1755</v>
       </c>
       <c r="Y11" t="n">
-        <v>35.84233553045442</v>
+        <v>20.42886822998214</v>
       </c>
       <c r="Z11" t="n">
-        <v>11116292252.85</v>
+        <v>1247696.24</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>00904.TW</t>
+          <t>00400A.TW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>台新臺灣半導體30</t>
+          <t>主動國泰動能高息</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.751513407768048</v>
+        <v>0.06131321083695918</v>
       </c>
       <c r="D12" t="n">
-        <v>1.691166121618151</v>
+        <v>0.05544203170693041</v>
       </c>
       <c r="E12" t="n">
-        <v>38.34</v>
+        <v>14.61</v>
       </c>
       <c r="F12" t="n">
-        <v>14.91</v>
+        <v>13.83</v>
       </c>
       <c r="G12" t="n">
-        <v>239</v>
+        <v>16</v>
       </c>
       <c r="H12" t="n">
-        <v>99.16</v>
+        <v>68.75</v>
       </c>
       <c r="I12" t="n">
-        <v>3.55</v>
+        <v>3.77</v>
       </c>
       <c r="J12" t="n">
-        <v>10.78242677824268</v>
+        <v>13.1875</v>
       </c>
       <c r="K12" t="n">
-        <v>3892492.15</v>
+        <v>38019073.2</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>11.85</v>
+        <v>13.12</v>
       </c>
       <c r="O12" t="n">
-        <v>-12.45</v>
+        <v>-0.83</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.5999999999999996</v>
+        <v>12.29</v>
       </c>
       <c r="Q12" t="n">
-        <v>37.53</v>
+        <v>126.3</v>
       </c>
       <c r="R12" t="n">
-        <v>0.06034728614989726</v>
+        <v>0.00587117913002877</v>
       </c>
       <c r="S12" t="n">
-        <v>7.050000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="T12" t="n">
-        <v>848.62</v>
+        <v>60.34</v>
       </c>
       <c r="U12" t="n">
-        <v>2577</v>
+        <v>211</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8937167099849649</v>
+        <v>0.9357886309047234</v>
       </c>
       <c r="W12" t="n">
-        <v>0.9727079822132222</v>
+        <v>1.007777724703607</v>
       </c>
       <c r="X12" t="n">
-        <v>42.8995</v>
+        <v>15.61250000000001</v>
       </c>
       <c r="Y12" t="n">
-        <v>39.41573493903507</v>
+        <v>14.49724442390993</v>
       </c>
       <c r="Z12" t="n">
-        <v>112866212.16</v>
+        <v>445828825.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>00913.TW</t>
+          <t>00663L.TW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>兆豐台灣晶圓製造</t>
+          <t>國泰臺灣加權正2</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.612228827033246</v>
+        <v>11.34588930018312</v>
       </c>
       <c r="D13" t="n">
-        <v>1.598627925307246</v>
+        <v>2.926252414611309</v>
       </c>
       <c r="E13" t="n">
-        <v>47.67</v>
+        <v>103.45</v>
       </c>
       <c r="F13" t="n">
-        <v>17.39</v>
+        <v>14.28</v>
       </c>
       <c r="G13" t="n">
-        <v>262</v>
+        <v>564</v>
       </c>
       <c r="H13" t="n">
-        <v>96.18000000000001</v>
+        <v>89.89</v>
       </c>
       <c r="I13" t="n">
-        <v>3.5</v>
+        <v>3.76</v>
       </c>
       <c r="J13" t="n">
-        <v>12.79770992366412</v>
+        <v>11.9113475177305</v>
       </c>
       <c r="K13" t="n">
-        <v>1896834.35</v>
+        <v>5623571.55</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1548,336 +1548,340 @@
         <v>2</v>
       </c>
       <c r="N13" t="n">
-        <v>13.5</v>
+        <v>15.99</v>
       </c>
       <c r="O13" t="n">
-        <v>-9.19</v>
+        <v>-24.46</v>
       </c>
       <c r="P13" t="n">
-        <v>4.31</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>28.72</v>
+        <v>18.35</v>
       </c>
       <c r="R13" t="n">
-        <v>0.01360090172599993</v>
+        <v>8.419636885571808</v>
       </c>
       <c r="S13" t="n">
-        <v>6.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>916.5599999999999</v>
+        <v>2121.97</v>
       </c>
       <c r="U13" t="n">
-        <v>3353</v>
+        <v>6718</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9185148076070833</v>
+        <v>0.9153247212882671</v>
       </c>
       <c r="W13" t="n">
-        <v>0.995141878359042</v>
+        <v>1.002905676823877</v>
       </c>
       <c r="X13" t="n">
-        <v>51.89899999999999</v>
+        <v>113.0200000000001</v>
       </c>
       <c r="Y13" t="n">
-        <v>47.90271722722226</v>
+        <v>103.1502786260199</v>
       </c>
       <c r="Z13" t="n">
-        <v>81345136.74000001</v>
+        <v>635770389.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>00685L.TW</t>
+          <t>00631L.TW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>群益臺灣加權正2</t>
+          <t>元大台灣50正2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10.48488725298811</v>
+        <v>15.22392136026959</v>
       </c>
       <c r="D14" t="n">
-        <v>2.789079106297023</v>
+        <v>3.344263321462639</v>
       </c>
       <c r="E14" t="n">
-        <v>12.07</v>
+        <v>35.87</v>
       </c>
       <c r="F14" t="n">
-        <v>19.04</v>
+        <v>13.02</v>
       </c>
       <c r="G14" t="n">
-        <v>514</v>
+        <v>644</v>
       </c>
       <c r="H14" t="n">
-        <v>88.52</v>
+        <v>89.44</v>
       </c>
       <c r="I14" t="n">
-        <v>3.46</v>
+        <v>3.74</v>
       </c>
       <c r="J14" t="n">
-        <v>12.18093385214008</v>
+        <v>12.68167701863354</v>
       </c>
       <c r="K14" t="n">
-        <v>256803747.15</v>
+        <v>196583279.9</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>15.89</v>
+        <v>17.37</v>
       </c>
       <c r="O14" t="n">
-        <v>-18.5</v>
+        <v>-12.43</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.609999999999999</v>
+        <v>4.940000000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>18.65</v>
+        <v>15.49</v>
       </c>
       <c r="R14" t="n">
-        <v>7.695808146691082</v>
+        <v>11.87965803880695</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1777.84</v>
+        <v>2407.1</v>
       </c>
       <c r="U14" t="n">
-        <v>6261</v>
+        <v>8167</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9326585017192751</v>
+        <v>0.9177786022234451</v>
       </c>
       <c r="W14" t="n">
-        <v>1.020272612613784</v>
+        <v>1.004226400573346</v>
       </c>
       <c r="X14" t="n">
-        <v>12.9415</v>
+        <v>39.08349999999998</v>
       </c>
       <c r="Y14" t="n">
-        <v>11.83017151570744</v>
+        <v>35.71903704136898</v>
       </c>
       <c r="Z14" t="n">
-        <v>4973428484.92</v>
+        <v>8673473574.129999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>009809.TW</t>
+          <t>00904.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>富邦淨零ESG50</t>
+          <t>台新臺灣半導體30</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.3562151369824964</v>
+        <v>1.716494642229002</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3151695928446534</v>
+        <v>1.667728448296326</v>
       </c>
       <c r="E15" t="n">
-        <v>18.12</v>
+        <v>37.8</v>
       </c>
       <c r="F15" t="n">
-        <v>21.22</v>
+        <v>10.63</v>
       </c>
       <c r="G15" t="n">
-        <v>34</v>
+        <v>239</v>
       </c>
       <c r="H15" t="n">
-        <v>97.06</v>
+        <v>99.16</v>
       </c>
       <c r="I15" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="J15" t="n">
-        <v>8.235294117647058</v>
+        <v>10.78242677824268</v>
       </c>
       <c r="K15" t="n">
-        <v>277035.05</v>
+        <v>3968762.2</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>7.76</v>
+        <v>11.85</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.12</v>
+        <v>-12.45</v>
       </c>
       <c r="P15" t="n">
-        <v>7.64</v>
+        <v>-0.5999999999999996</v>
       </c>
       <c r="Q15" t="n">
-        <v>172.16</v>
+        <v>37.53</v>
       </c>
       <c r="R15" t="n">
-        <v>0.041045544137843</v>
+        <v>0.04876619393267623</v>
       </c>
       <c r="S15" t="n">
-        <v>0.315</v>
+        <v>7.050000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>115.56</v>
+        <v>848.62</v>
       </c>
       <c r="U15" t="n">
-        <v>280</v>
+        <v>2577</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9738008867392178</v>
+        <v>0.8846243856775099</v>
       </c>
       <c r="W15" t="n">
-        <v>1.002337123860659</v>
+        <v>0.9779823312439648</v>
       </c>
       <c r="X15" t="n">
-        <v>18.60750000000001</v>
+        <v>42.73</v>
       </c>
       <c r="Y15" t="n">
-        <v>18.0777500589901</v>
+        <v>38.65100502574469</v>
       </c>
       <c r="Z15" t="n">
-        <v>27616601.4</v>
+        <v>93658836.59999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>00715L.TW</t>
+          <t>00685L.TW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>期街口布蘭特正2</t>
+          <t>群益臺灣加權正2</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5.448233845009139</v>
+        <v>10.26154014351294</v>
       </c>
       <c r="D16" t="n">
-        <v>2.647925835384552</v>
+        <v>2.757196595596791</v>
       </c>
       <c r="E16" t="n">
-        <v>80.2</v>
+        <v>11.84</v>
       </c>
       <c r="F16" t="n">
-        <v>85.87</v>
+        <v>13.8</v>
       </c>
       <c r="G16" t="n">
-        <v>425</v>
+        <v>514</v>
       </c>
       <c r="H16" t="n">
-        <v>77.65000000000001</v>
+        <v>88.52</v>
       </c>
       <c r="I16" t="n">
-        <v>3.32</v>
+        <v>3.46</v>
       </c>
       <c r="J16" t="n">
-        <v>17.11294117647059</v>
+        <v>12.18093385214008</v>
       </c>
       <c r="K16" t="n">
-        <v>3301946.05</v>
-      </c>
-      <c r="L16" t="inlineStr"/>
+        <v>262914148.35</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>32.14</v>
+        <v>15.89</v>
       </c>
       <c r="O16" t="n">
-        <v>-44.86</v>
+        <v>-18.5</v>
       </c>
       <c r="P16" t="n">
-        <v>-12.72</v>
+        <v>-2.609999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>14.59</v>
+        <v>18.65</v>
       </c>
       <c r="R16" t="n">
-        <v>2.800308009624588</v>
+        <v>7.504343547916149</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1409.31</v>
+        <v>1777.84</v>
       </c>
       <c r="U16" t="n">
-        <v>7273</v>
+        <v>6261</v>
       </c>
       <c r="V16" t="n">
-        <v>1.15122371348597</v>
+        <v>0.9153813444663494</v>
       </c>
       <c r="W16" t="n">
-        <v>1.352960677914911</v>
+        <v>1.003596846599693</v>
       </c>
       <c r="X16" t="n">
-        <v>69.66499999999995</v>
+        <v>12.9345</v>
       </c>
       <c r="Y16" t="n">
-        <v>59.27740643844778</v>
+        <v>11.79756596497423</v>
       </c>
       <c r="Z16" t="n">
-        <v>211541053.8</v>
+        <v>4394906957.44</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>00675L.TW</t>
+          <t>009809.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>富邦臺灣加權正2</t>
+          <t>富邦淨零ESG50</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>11.01369753516261</v>
+        <v>0.3415566883107366</v>
       </c>
       <c r="D17" t="n">
-        <v>2.895851187620472</v>
+        <v>0.3030785259366744</v>
       </c>
       <c r="E17" t="n">
-        <v>319.1</v>
+        <v>17.94</v>
       </c>
       <c r="F17" t="n">
-        <v>19.57</v>
+        <v>14.45</v>
       </c>
       <c r="G17" t="n">
-        <v>564</v>
+        <v>34</v>
       </c>
       <c r="H17" t="n">
-        <v>87.06</v>
+        <v>97.06</v>
       </c>
       <c r="I17" t="n">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="J17" t="n">
-        <v>12.38297872340426</v>
+        <v>8.235294117647058</v>
       </c>
       <c r="K17" t="n">
-        <v>1192472.1</v>
+        <v>296860.9</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1888,172 +1892,168 @@
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>15.7</v>
+        <v>7.76</v>
       </c>
       <c r="O17" t="n">
-        <v>-24.73</v>
+        <v>-0.12</v>
       </c>
       <c r="P17" t="n">
-        <v>-9.030000000000001</v>
+        <v>7.64</v>
       </c>
       <c r="Q17" t="n">
-        <v>16.61</v>
+        <v>172.16</v>
       </c>
       <c r="R17" t="n">
-        <v>8.117846347542136</v>
+        <v>0.03847816237406221</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
       <c r="T17" t="n">
-        <v>1792.47</v>
+        <v>115.56</v>
       </c>
       <c r="U17" t="n">
-        <v>6984</v>
+        <v>280</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9313457230625539</v>
+        <v>0.9647235964723595</v>
       </c>
       <c r="W17" t="n">
-        <v>1.018699297244358</v>
+        <v>0.9955201797903795</v>
       </c>
       <c r="X17" t="n">
-        <v>342.6225000000002</v>
+        <v>18.596</v>
       </c>
       <c r="Y17" t="n">
-        <v>313.2425838156405</v>
+        <v>18.02072962878313</v>
       </c>
       <c r="Z17" t="n">
-        <v>549165675.3000001</v>
+        <v>9602582.34</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>00935.TW</t>
+          <t>00715L.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>野村臺灣新科技50</t>
+          <t>期街口布蘭特正2</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.426545859982833</v>
+        <v>5.634566129417959</v>
       </c>
       <c r="D18" t="n">
-        <v>1.122299718392824</v>
+        <v>2.61715656906853</v>
       </c>
       <c r="E18" t="n">
-        <v>56.5</v>
+        <v>82.55</v>
       </c>
       <c r="F18" t="n">
-        <v>17.84</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>136</v>
+        <v>425</v>
       </c>
       <c r="H18" t="n">
-        <v>83.09</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>3.15</v>
+        <v>3.32</v>
       </c>
       <c r="J18" t="n">
-        <v>12.30882352941176</v>
+        <v>17.11294117647059</v>
       </c>
       <c r="K18" t="n">
-        <v>13165792.8</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
+        <v>3302473.2</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>14.6</v>
+        <v>32.14</v>
       </c>
       <c r="O18" t="n">
-        <v>-8.99</v>
+        <v>-44.86</v>
       </c>
       <c r="P18" t="n">
-        <v>5.609999999999999</v>
+        <v>-12.72</v>
       </c>
       <c r="Q18" t="n">
-        <v>43.74</v>
+        <v>14.59</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3042461415900086</v>
+        <v>3.017409560349428</v>
       </c>
       <c r="S18" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>428.12</v>
+        <v>1409.31</v>
       </c>
       <c r="U18" t="n">
-        <v>1674</v>
+        <v>7273</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9345407931191332</v>
+        <v>1.173543732451932</v>
       </c>
       <c r="W18" t="n">
-        <v>1.008147249540754</v>
+        <v>1.41002777042993</v>
       </c>
       <c r="X18" t="n">
-        <v>60.4575</v>
+        <v>70.34249999999994</v>
       </c>
       <c r="Y18" t="n">
-        <v>56.04340043157158</v>
+        <v>58.54494622813689</v>
       </c>
       <c r="Z18" t="n">
-        <v>901522418.5</v>
+        <v>276884504.65</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>00894.TW</t>
+          <t>00675L.TW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>中信小資高價30</t>
+          <t>富邦臺灣加權正2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.051706280811482</v>
+        <v>10.77962625416551</v>
       </c>
       <c r="D19" t="n">
-        <v>1.742009527647736</v>
+        <v>2.863158504697493</v>
       </c>
       <c r="E19" t="n">
-        <v>47.41</v>
+        <v>313</v>
       </c>
       <c r="F19" t="n">
-        <v>22.74</v>
+        <v>14.06</v>
       </c>
       <c r="G19" t="n">
-        <v>243</v>
+        <v>564</v>
       </c>
       <c r="H19" t="n">
-        <v>82.72</v>
+        <v>87.06</v>
       </c>
       <c r="I19" t="n">
-        <v>2.88</v>
+        <v>3.18</v>
       </c>
       <c r="J19" t="n">
-        <v>15.32921810699589</v>
+        <v>12.38297872340426</v>
       </c>
       <c r="K19" t="n">
-        <v>1244361.95</v>
+        <v>1220342.05</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M19" t="n">
@@ -2063,79 +2063,79 @@
         <v>15.7</v>
       </c>
       <c r="O19" t="n">
-        <v>-8.380000000000001</v>
+        <v>-24.73</v>
       </c>
       <c r="P19" t="n">
-        <v>7.319999999999999</v>
+        <v>-9.030000000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>22.58</v>
+        <v>16.61</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3096967531637467</v>
+        <v>7.916467749468019</v>
       </c>
       <c r="S19" t="n">
-        <v>7.549999999999999</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>698.73</v>
+        <v>1792.47</v>
       </c>
       <c r="U19" t="n">
-        <v>3725</v>
+        <v>6984</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9493106935114086</v>
+        <v>0.914168887590814</v>
       </c>
       <c r="W19" t="n">
-        <v>1.021567767247863</v>
+        <v>1.002719037679424</v>
       </c>
       <c r="X19" t="n">
-        <v>49.94149999999998</v>
+        <v>342.3875000000002</v>
       </c>
       <c r="Y19" t="n">
-        <v>46.4090601915956</v>
+        <v>312.1512489923107</v>
       </c>
       <c r="Z19" t="n">
-        <v>71626553.89999999</v>
+        <v>482507654</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>00901.TW</t>
+          <t>00935.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>永豐智能車供應鏈</t>
+          <t>野村臺灣新科技50</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.776534460812764</v>
+        <v>1.390536372815003</v>
       </c>
       <c r="D20" t="n">
-        <v>1.707475648568086</v>
+        <v>1.103386361202003</v>
       </c>
       <c r="E20" t="n">
-        <v>45.38</v>
+        <v>55.65</v>
       </c>
       <c r="F20" t="n">
-        <v>19.72</v>
+        <v>12.52</v>
       </c>
       <c r="G20" t="n">
-        <v>276</v>
+        <v>136</v>
       </c>
       <c r="H20" t="n">
-        <v>89.48999999999999</v>
+        <v>83.09</v>
       </c>
       <c r="I20" t="n">
-        <v>2.79</v>
+        <v>3.15</v>
       </c>
       <c r="J20" t="n">
-        <v>13.22463768115942</v>
+        <v>12.30882352941176</v>
       </c>
       <c r="K20" t="n">
-        <v>252017.7</v>
+        <v>13273311.8</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -2146,82 +2146,82 @@
         <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>15.18</v>
+        <v>14.6</v>
       </c>
       <c r="O20" t="n">
-        <v>-7.3</v>
+        <v>-8.99</v>
       </c>
       <c r="P20" t="n">
-        <v>7.88</v>
+        <v>5.609999999999999</v>
       </c>
       <c r="Q20" t="n">
-        <v>24.17</v>
+        <v>43.74</v>
       </c>
       <c r="R20" t="n">
-        <v>0.06905881224467825</v>
+        <v>0.2871500116129995</v>
       </c>
       <c r="S20" t="n">
-        <v>4.671</v>
+        <v>4.98</v>
       </c>
       <c r="T20" t="n">
-        <v>771.28</v>
+        <v>428.12</v>
       </c>
       <c r="U20" t="n">
-        <v>3650</v>
+        <v>1674</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9448556586193615</v>
+        <v>0.9211669770328986</v>
       </c>
       <c r="W20" t="n">
-        <v>1.006347937439428</v>
+        <v>0.9968646563736249</v>
       </c>
       <c r="X20" t="n">
-        <v>48.0285</v>
+        <v>60.41250000000001</v>
       </c>
       <c r="Y20" t="n">
-        <v>45.0937477106236</v>
+        <v>55.82503065405338</v>
       </c>
       <c r="Z20" t="n">
-        <v>11695923.54</v>
+        <v>610833599.25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>0057.TW</t>
+          <t>00894.TW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>富邦摩台</t>
+          <t>中信小資高價30</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6.125688580451323</v>
+        <v>2.008364540345374</v>
       </c>
       <c r="D21" t="n">
-        <v>4.894842106366574</v>
+        <v>1.718294806500042</v>
       </c>
       <c r="E21" t="n">
-        <v>321.2</v>
+        <v>46.68</v>
       </c>
       <c r="F21" t="n">
-        <v>18.29</v>
+        <v>16.13</v>
       </c>
       <c r="G21" t="n">
-        <v>1245</v>
+        <v>243</v>
       </c>
       <c r="H21" t="n">
-        <v>93.33</v>
+        <v>82.72</v>
       </c>
       <c r="I21" t="n">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="J21" t="n">
-        <v>12.02409638554217</v>
+        <v>15.32921810699589</v>
       </c>
       <c r="K21" t="n">
-        <v>32132.2</v>
+        <v>1230531</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -2232,168 +2232,168 @@
         <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>14.45</v>
+        <v>15.7</v>
       </c>
       <c r="O21" t="n">
-        <v>-6.48</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>7.969999999999999</v>
+        <v>7.319999999999999</v>
       </c>
       <c r="Q21" t="n">
-        <v>8.970000000000001</v>
+        <v>22.58</v>
       </c>
       <c r="R21" t="n">
-        <v>1.230846474084749</v>
+        <v>0.2900697338453324</v>
       </c>
       <c r="S21" t="n">
-        <v>1.685</v>
+        <v>7.549999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>3287.55</v>
+        <v>698.73</v>
       </c>
       <c r="U21" t="n">
-        <v>14970</v>
+        <v>3725</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9617054402826432</v>
+        <v>0.934412939257154</v>
       </c>
       <c r="W21" t="n">
-        <v>1.00515087507034</v>
+        <v>1.004246345496669</v>
       </c>
       <c r="X21" t="n">
-        <v>333.99</v>
+        <v>49.95649999999998</v>
       </c>
       <c r="Y21" t="n">
-        <v>319.5540171792842</v>
+        <v>46.48261874123479</v>
       </c>
       <c r="Z21" t="n">
-        <v>4663502.8</v>
+        <v>37953874.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>00881.TW</t>
+          <t>00901.TW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>國泰台灣科技龍頭</t>
+          <t>永豐智能車供應鏈</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.982169333508977</v>
+        <v>1.739259580232981</v>
       </c>
       <c r="D22" t="n">
-        <v>1.808596225383848</v>
+        <v>1.683960124062911</v>
       </c>
       <c r="E22" t="n">
-        <v>49.64</v>
+        <v>44.75</v>
       </c>
       <c r="F22" t="n">
-        <v>15.07</v>
+        <v>14.06</v>
       </c>
       <c r="G22" t="n">
-        <v>384</v>
+        <v>276</v>
       </c>
       <c r="H22" t="n">
-        <v>89.58</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>2.52</v>
+        <v>2.79</v>
       </c>
       <c r="J22" t="n">
-        <v>15.328125</v>
+        <v>13.22463768115942</v>
       </c>
       <c r="K22" t="n">
-        <v>17187915.25</v>
+        <v>261154.1</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>10.9</v>
+        <v>15.18</v>
       </c>
       <c r="O22" t="n">
-        <v>-4.28</v>
+        <v>-7.3</v>
       </c>
       <c r="P22" t="n">
-        <v>6.62</v>
+        <v>7.88</v>
       </c>
       <c r="Q22" t="n">
-        <v>15.81</v>
+        <v>24.17</v>
       </c>
       <c r="R22" t="n">
-        <v>0.173573108125129</v>
+        <v>0.05529945617006993</v>
       </c>
       <c r="S22" t="n">
-        <v>12.5</v>
+        <v>4.671</v>
       </c>
       <c r="T22" t="n">
-        <v>966.91</v>
+        <v>771.28</v>
       </c>
       <c r="U22" t="n">
-        <v>5886</v>
+        <v>3650</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9521891334580158</v>
+        <v>0.9329038848410937</v>
       </c>
       <c r="W22" t="n">
-        <v>1.007241240366367</v>
+        <v>0.9983355361862268</v>
       </c>
       <c r="X22" t="n">
-        <v>52.13249999999999</v>
+        <v>47.9685</v>
       </c>
       <c r="Y22" t="n">
-        <v>49.28312901678282</v>
+        <v>44.82460893954641</v>
       </c>
       <c r="Z22" t="n">
-        <v>934623905.6</v>
+        <v>14384932.25</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>0052.TW</t>
+          <t>0057.TW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>富邦科技</t>
+          <t>富邦摩台</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8.217639073277233</v>
+        <v>6.074588606858966</v>
       </c>
       <c r="D23" t="n">
-        <v>4.988736001779501</v>
+        <v>4.84649526179438</v>
       </c>
       <c r="E23" t="n">
-        <v>62.6</v>
+        <v>318.95</v>
       </c>
       <c r="F23" t="n">
-        <v>17.15</v>
+        <v>13.09</v>
       </c>
       <c r="G23" t="n">
-        <v>1111</v>
+        <v>1245</v>
       </c>
       <c r="H23" t="n">
-        <v>88.20999999999999</v>
+        <v>93.33</v>
       </c>
       <c r="I23" t="n">
-        <v>2.45</v>
+        <v>2.64</v>
       </c>
       <c r="J23" t="n">
-        <v>14.18091809180918</v>
+        <v>12.02409638554217</v>
       </c>
       <c r="K23" t="n">
-        <v>20295188.5</v>
+        <v>31181.65</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -2404,512 +2404,512 @@
         <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>12.7</v>
+        <v>14.45</v>
       </c>
       <c r="O23" t="n">
-        <v>-14.18</v>
+        <v>-6.48</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.48</v>
+        <v>7.969999999999999</v>
       </c>
       <c r="Q23" t="n">
-        <v>8.050000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="R23" t="n">
-        <v>3.228903071497732</v>
+        <v>1.228093345064586</v>
       </c>
       <c r="S23" t="n">
-        <v>2.232857285714286</v>
+        <v>1.685</v>
       </c>
       <c r="T23" t="n">
-        <v>2723.42</v>
+        <v>3287.55</v>
       </c>
       <c r="U23" t="n">
-        <v>15755</v>
+        <v>14970</v>
       </c>
       <c r="V23" t="n">
-        <v>0.958505588730668</v>
+        <v>0.9557055426127213</v>
       </c>
       <c r="W23" t="n">
-        <v>1.007406986055328</v>
+        <v>1.001596386456068</v>
       </c>
       <c r="X23" t="n">
-        <v>65.31000000000007</v>
+        <v>333.7325</v>
       </c>
       <c r="Y23" t="n">
-        <v>62.13973187253829</v>
+        <v>318.4416440723548</v>
       </c>
       <c r="Z23" t="n">
-        <v>1615717017.6</v>
+        <v>6947687.85</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>006203.TW</t>
+          <t>00881.TW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>元大MSCI台灣</t>
+          <t>國泰台灣科技龍頭</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4.102448231997496</v>
+        <v>1.954342029673283</v>
       </c>
       <c r="D24" t="n">
-        <v>4.10212694686185</v>
+        <v>1.784470945466316</v>
       </c>
       <c r="E24" t="n">
-        <v>196.35</v>
+        <v>49.11</v>
       </c>
       <c r="F24" t="n">
-        <v>20.3</v>
+        <v>10.54</v>
       </c>
       <c r="G24" t="n">
-        <v>890</v>
+        <v>384</v>
       </c>
       <c r="H24" t="n">
-        <v>91.45999999999999</v>
+        <v>89.58</v>
       </c>
       <c r="I24" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="J24" t="n">
-        <v>13.44831460674157</v>
+        <v>15.328125</v>
       </c>
       <c r="K24" t="n">
-        <v>13704.3</v>
+        <v>17389307.9</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>8.85</v>
+        <v>10.9</v>
       </c>
       <c r="O24" t="n">
-        <v>-7.45</v>
+        <v>-4.28</v>
       </c>
       <c r="P24" t="n">
-        <v>1.399999999999999</v>
+        <v>6.62</v>
       </c>
       <c r="Q24" t="n">
-        <v>9.880000000000001</v>
+        <v>15.81</v>
       </c>
       <c r="R24" t="n">
-        <v>0.0003212851356453328</v>
+        <v>0.1698710842069673</v>
       </c>
       <c r="S24" t="n">
-        <v>20.78</v>
+        <v>12.5</v>
       </c>
       <c r="T24" t="n">
-        <v>2099.49</v>
+        <v>966.91</v>
       </c>
       <c r="U24" t="n">
-        <v>11969</v>
+        <v>5886</v>
       </c>
       <c r="V24" t="n">
-        <v>0.9670270137161717</v>
+        <v>0.9426555976774319</v>
       </c>
       <c r="W24" t="n">
-        <v>1.013415380429336</v>
+        <v>0.999785508398096</v>
       </c>
       <c r="X24" t="n">
-        <v>203.0449999999999</v>
+        <v>52.09749999999999</v>
       </c>
       <c r="Y24" t="n">
-        <v>193.7507598481639</v>
+        <v>49.12053594244068</v>
       </c>
       <c r="Z24" t="n">
-        <v>4282589.85</v>
+        <v>796216255.65</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>00735.TW</t>
+          <t>0052.TW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>國泰臺韓科技</t>
+          <t>富邦科技</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.878791469220793</v>
+        <v>8.166018168201376</v>
       </c>
       <c r="D25" t="n">
-        <v>2.52681650557835</v>
+        <v>4.939555082401423</v>
       </c>
       <c r="E25" t="n">
-        <v>97.5</v>
+        <v>62.25</v>
       </c>
       <c r="F25" t="n">
-        <v>15.99</v>
+        <v>13.08</v>
       </c>
       <c r="G25" t="n">
-        <v>498</v>
+        <v>1111</v>
       </c>
       <c r="H25" t="n">
-        <v>86.55</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="J25" t="n">
-        <v>13.81124497991968</v>
+        <v>14.18091809180918</v>
       </c>
       <c r="K25" t="n">
-        <v>1815689.8</v>
+        <v>20574417.55</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>2</v>
       </c>
       <c r="N25" t="n">
-        <v>21.39</v>
+        <v>12.7</v>
       </c>
       <c r="O25" t="n">
-        <v>-6.04</v>
+        <v>-14.18</v>
       </c>
       <c r="P25" t="n">
-        <v>15.35</v>
+        <v>-1.48</v>
       </c>
       <c r="Q25" t="n">
-        <v>14.26</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="R25" t="n">
-        <v>0.3519749636424434</v>
+        <v>3.226463085799953</v>
       </c>
       <c r="S25" t="n">
-        <v>13.37</v>
+        <v>2.232857285714286</v>
       </c>
       <c r="T25" t="n">
-        <v>1133.84</v>
+        <v>2723.42</v>
       </c>
       <c r="U25" t="n">
-        <v>6878</v>
+        <v>15755</v>
       </c>
       <c r="V25" t="n">
-        <v>0.9153640332347568</v>
+        <v>0.9534750143595625</v>
       </c>
       <c r="W25" t="n">
-        <v>1.002179415849688</v>
+        <v>1.003416326486596</v>
       </c>
       <c r="X25" t="n">
-        <v>106.5149999999999</v>
+        <v>65.28750000000007</v>
       </c>
       <c r="Y25" t="n">
-        <v>97.28796905825052</v>
+        <v>62.03805774016531</v>
       </c>
       <c r="Z25" t="n">
-        <v>126732255</v>
+        <v>1077808265.25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>0050.TW</t>
+          <t>00735.TW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>元大台灣50</t>
+          <t>國泰臺韓科技</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5.517113833119172</v>
+        <v>2.823300662446544</v>
       </c>
       <c r="D26" t="n">
-        <v>5.517113833119172</v>
+        <v>2.496991366533118</v>
       </c>
       <c r="E26" t="n">
-        <v>108.15</v>
+        <v>96</v>
       </c>
       <c r="F26" t="n">
-        <v>19.4</v>
+        <v>12.02</v>
       </c>
       <c r="G26" t="n">
-        <v>1695</v>
+        <v>498</v>
       </c>
       <c r="H26" t="n">
-        <v>90.97</v>
+        <v>86.55</v>
       </c>
       <c r="I26" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="J26" t="n">
-        <v>13.46961651917404</v>
+        <v>13.81124497991968</v>
       </c>
       <c r="K26" t="n">
-        <v>112686684.55</v>
+        <v>1834276.5</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>2</v>
       </c>
       <c r="N26" t="n">
-        <v>13.94</v>
+        <v>21.39</v>
       </c>
       <c r="O26" t="n">
-        <v>-5.91</v>
+        <v>-6.04</v>
       </c>
       <c r="P26" t="n">
-        <v>8.029999999999999</v>
+        <v>15.35</v>
       </c>
       <c r="Q26" t="n">
-        <v>6.04</v>
+        <v>14.26</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>0.3263092959134259</v>
       </c>
       <c r="S26" t="n">
-        <v>4.84625</v>
+        <v>13.37</v>
       </c>
       <c r="T26" t="n">
-        <v>3824.71</v>
+        <v>1133.84</v>
       </c>
       <c r="U26" t="n">
-        <v>22831</v>
+        <v>6878</v>
       </c>
       <c r="V26" t="n">
-        <v>0.9636031540963155</v>
+        <v>0.9040612124779294</v>
       </c>
       <c r="W26" t="n">
-        <v>1.008581638228937</v>
+        <v>0.9999451415637474</v>
       </c>
       <c r="X26" t="n">
-        <v>112.235</v>
+        <v>106.1874999999999</v>
       </c>
       <c r="Y26" t="n">
-        <v>107.2297927115853</v>
+        <v>96.00526669880311</v>
       </c>
       <c r="Z26" t="n">
-        <v>17888729413.8</v>
+        <v>120552192</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>0053.TW</t>
+          <t>0050.TW</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>元大科技市值</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6.688198963573957</v>
+        <v>5.464004471271062</v>
       </c>
       <c r="D27" t="n">
-        <v>4.951672611201002</v>
+        <v>5.464004471271062</v>
       </c>
       <c r="E27" t="n">
-        <v>241.1</v>
+        <v>107.25</v>
       </c>
       <c r="F27" t="n">
-        <v>14.18</v>
+        <v>13.64</v>
       </c>
       <c r="G27" t="n">
-        <v>1190</v>
+        <v>1695</v>
       </c>
       <c r="H27" t="n">
-        <v>89.16</v>
+        <v>90.97</v>
       </c>
       <c r="I27" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="J27" t="n">
-        <v>13.83697478991597</v>
+        <v>13.46961651917404</v>
       </c>
       <c r="K27" t="n">
-        <v>405886.35</v>
+        <v>116344424.15</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M27" t="n">
         <v>2</v>
       </c>
       <c r="N27" t="n">
-        <v>11.49</v>
+        <v>13.94</v>
       </c>
       <c r="O27" t="n">
-        <v>-7.24</v>
+        <v>-5.91</v>
       </c>
       <c r="P27" t="n">
-        <v>4.25</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="Q27" t="n">
-        <v>7.58</v>
+        <v>6.04</v>
       </c>
       <c r="R27" t="n">
-        <v>1.736526352372955</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>18.91</v>
+        <v>4.84625</v>
       </c>
       <c r="T27" t="n">
-        <v>2598</v>
+        <v>3824.71</v>
       </c>
       <c r="U27" t="n">
-        <v>16466</v>
+        <v>22831</v>
       </c>
       <c r="V27" t="n">
-        <v>0.9545962960396721</v>
+        <v>0.9559249520923391</v>
       </c>
       <c r="W27" t="n">
-        <v>1.007374794288037</v>
+        <v>1.001906358072304</v>
       </c>
       <c r="X27" t="n">
-        <v>252.5675000000001</v>
+        <v>112.195</v>
       </c>
       <c r="Y27" t="n">
-        <v>239.3349539486916</v>
+        <v>107.0459321231897</v>
       </c>
       <c r="Z27" t="n">
-        <v>218445038.5</v>
+        <v>13201031844</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>00892.TW</t>
+          <t>0053.TW</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>富邦台灣半導體</t>
+          <t>元大科技市值</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1.853719051855981</v>
+        <v>6.631486744757602</v>
       </c>
       <c r="D28" t="n">
-        <v>1.758705315655066</v>
+        <v>4.902928246727704</v>
       </c>
       <c r="E28" t="n">
-        <v>40.95</v>
+        <v>239.25</v>
       </c>
       <c r="F28" t="n">
-        <v>22.4</v>
+        <v>10.61</v>
       </c>
       <c r="G28" t="n">
-        <v>241</v>
+        <v>1190</v>
       </c>
       <c r="H28" t="n">
-        <v>75.09999999999999</v>
+        <v>89.16</v>
       </c>
       <c r="I28" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="J28" t="n">
-        <v>15.85892116182573</v>
+        <v>13.83697478991597</v>
       </c>
       <c r="K28" t="n">
-        <v>4493193.8</v>
+        <v>432151.3</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>2</v>
       </c>
       <c r="N28" t="n">
-        <v>12.37</v>
+        <v>11.49</v>
       </c>
       <c r="O28" t="n">
-        <v>-7.43</v>
+        <v>-7.24</v>
       </c>
       <c r="P28" t="n">
-        <v>4.94</v>
+        <v>4.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>18.86</v>
+        <v>7.58</v>
       </c>
       <c r="R28" t="n">
-        <v>0.09501373620091469</v>
+        <v>1.728558498029898</v>
       </c>
       <c r="S28" t="n">
-        <v>4.937</v>
+        <v>18.91</v>
       </c>
       <c r="T28" t="n">
-        <v>510.5</v>
+        <v>2598</v>
       </c>
       <c r="U28" t="n">
-        <v>3822</v>
+        <v>16466</v>
       </c>
       <c r="V28" t="n">
-        <v>0.9545677055409216</v>
+        <v>0.9477781189030726</v>
       </c>
       <c r="W28" t="n">
-        <v>1.002303087174216</v>
+        <v>1.002207868074815</v>
       </c>
       <c r="X28" t="n">
-        <v>42.89900000000001</v>
+        <v>252.4325000000001</v>
       </c>
       <c r="Y28" t="n">
-        <v>40.85590528853898</v>
+        <v>238.7229312613417</v>
       </c>
       <c r="Z28" t="n">
-        <v>145582901.1</v>
+        <v>137813024.25</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>006208.TW</t>
+          <t>00892.TW</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>富邦台50</t>
+          <t>富邦台灣半導體</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4.106159394851079</v>
+        <v>1.798486039015612</v>
       </c>
       <c r="D29" t="n">
-        <v>3.845643524581418</v>
+        <v>1.734895051074697</v>
       </c>
       <c r="E29" t="n">
-        <v>247.9</v>
+        <v>40.11</v>
       </c>
       <c r="F29" t="n">
-        <v>18.33</v>
+        <v>15.02</v>
       </c>
       <c r="G29" t="n">
-        <v>895</v>
+        <v>241</v>
       </c>
       <c r="H29" t="n">
-        <v>88.48999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="J29" t="n">
-        <v>13.86703910614525</v>
+        <v>15.85892116182573</v>
       </c>
       <c r="K29" t="n">
-        <v>3143357.3</v>
+        <v>4528127.05</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -2920,125 +2920,211 @@
         <v>2</v>
       </c>
       <c r="N29" t="n">
-        <v>11.21</v>
+        <v>12.37</v>
       </c>
       <c r="O29" t="n">
-        <v>-6.25</v>
+        <v>-7.43</v>
       </c>
       <c r="P29" t="n">
-        <v>4.960000000000001</v>
+        <v>4.94</v>
       </c>
       <c r="Q29" t="n">
-        <v>8.949999999999999</v>
+        <v>18.86</v>
       </c>
       <c r="R29" t="n">
-        <v>0.2605158702696606</v>
+        <v>0.06359098794091445</v>
       </c>
       <c r="S29" t="n">
-        <v>28.764</v>
+        <v>4.937</v>
       </c>
       <c r="T29" t="n">
-        <v>1745.92</v>
+        <v>510.5</v>
       </c>
       <c r="U29" t="n">
-        <v>12411</v>
+        <v>3822</v>
       </c>
       <c r="V29" t="n">
-        <v>0.964741594022416</v>
+        <v>0.9364275208367377</v>
       </c>
       <c r="W29" t="n">
-        <v>1.008431453555654</v>
+        <v>0.9895158711182126</v>
       </c>
       <c r="X29" t="n">
-        <v>256.96</v>
+        <v>42.83300000000001</v>
       </c>
       <c r="Y29" t="n">
-        <v>245.8273183823483</v>
+        <v>40.53497389048776</v>
       </c>
       <c r="Z29" t="n">
-        <v>1415915803.9</v>
+        <v>183572880.96</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>009823.TWO</t>
+          <t>006208.TW</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>群益S&amp;P500</t>
+          <t>富邦台50</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.02726883674646041</v>
+        <v>4.055751188242493</v>
       </c>
       <c r="D30" t="n">
-        <v>0.01609313418732206</v>
+        <v>3.805476054195616</v>
       </c>
       <c r="E30" t="n">
-        <v>10.71</v>
+        <v>245.3</v>
       </c>
       <c r="F30" t="n">
-        <v>81.83</v>
+        <v>12.22</v>
       </c>
       <c r="G30" t="n">
-        <v>15</v>
+        <v>895</v>
       </c>
       <c r="H30" t="n">
-        <v>100</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>1.31</v>
+        <v>1.95</v>
       </c>
       <c r="J30" t="n">
-        <v>16.93333333333333</v>
+        <v>13.86703910614525</v>
       </c>
       <c r="K30" t="n">
-        <v>3298145.95</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
+        <v>3266532</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="M30" t="n">
         <v>2</v>
       </c>
       <c r="N30" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-6.25</v>
+      </c>
+      <c r="P30" t="n">
+        <v>4.960000000000001</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.2502751340468778</v>
+      </c>
+      <c r="S30" t="n">
+        <v>28.764</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1745.92</v>
+      </c>
+      <c r="U30" t="n">
+        <v>12411</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.9550135290338907</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.9998740510571562</v>
+      </c>
+      <c r="X30" t="n">
+        <v>256.855</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>245.3308991673971</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>946543770.7</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>009823.TWO</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>群益S&amp;P500</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.02692797628712951</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.007552616385237076</v>
+      </c>
+      <c r="E31" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="F31" t="n">
+        <v>76.12</v>
+      </c>
+      <c r="G31" t="n">
+        <v>15</v>
+      </c>
+      <c r="H31" t="n">
+        <v>100</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="J31" t="n">
+        <v>16.93333333333333</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3344982.85</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>2</v>
+      </c>
+      <c r="N31" t="n">
         <v>3.64</v>
       </c>
-      <c r="O30" t="n">
+      <c r="O31" t="n">
         <v>0.45</v>
       </c>
-      <c r="P30" t="n">
+      <c r="P31" t="n">
         <v>4.09</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="Q31" t="n">
         <v>29.52</v>
       </c>
-      <c r="R30" t="n">
-        <v>0.01117570255913836</v>
-      </c>
-      <c r="S30" t="n">
+      <c r="R31" t="n">
+        <v>0.01937535990189243</v>
+      </c>
+      <c r="S31" t="n">
         <v>0</v>
       </c>
-      <c r="T30" t="n">
+      <c r="T31" t="n">
         <v>19.72</v>
       </c>
-      <c r="U30" t="n">
+      <c r="U31" t="n">
         <v>254</v>
       </c>
-      <c r="V30" t="n">
-        <v>1.01463691914168</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.038852374957421</v>
-      </c>
-      <c r="X30" t="n">
-        <v>10.5555</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>10.30945325647349</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>41376714.12</v>
+      <c r="V31" t="n">
+        <v>1.012861736334405</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.0357619518573</v>
+      </c>
+      <c r="X31" t="n">
+        <v>10.574</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>10.34021377286076</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>32758923.33</v>
       </c>
     </row>
   </sheetData>

--- a/ETF動態清單.xlsx
+++ b/ETF動態清單.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z31"/>
+  <dimension ref="A1:Z34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,16 +567,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.67692909998079</v>
+        <v>0.6832462980186436</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5218083266187941</v>
+        <v>0.5328629403948486</v>
       </c>
       <c r="E2" t="n">
-        <v>28.73</v>
+        <v>28.88</v>
       </c>
       <c r="F2" t="n">
-        <v>15.77</v>
+        <v>13.08</v>
       </c>
       <c r="G2" t="n">
         <v>41</v>
@@ -591,7 +591,7 @@
         <v>8.439024390243903</v>
       </c>
       <c r="K2" t="n">
-        <v>165333560.3</v>
+        <v>165691817.1</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         <v>386.28</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1551207733619959</v>
+        <v>0.150383357623795</v>
       </c>
       <c r="S2" t="n">
         <v>1.67</v>
@@ -626,19 +626,19 @@
         <v>346</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9345520785895517</v>
+        <v>0.9397217928902628</v>
       </c>
       <c r="W2" t="n">
-        <v>1.014119011332104</v>
+        <v>1.020750691758957</v>
       </c>
       <c r="X2" t="n">
-        <v>30.742</v>
+        <v>30.7325</v>
       </c>
       <c r="Y2" t="n">
-        <v>28.33000829188822</v>
+        <v>28.29290269716496</v>
       </c>
       <c r="Z2" t="n">
-        <v>3688463672.27</v>
+        <v>4386586116.88</v>
       </c>
     </row>
     <row r="3">
@@ -653,16 +653,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2068094916405983</v>
+        <v>0.2227059644355847</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1842930299504741</v>
+        <v>0.1931845860618198</v>
       </c>
       <c r="E3" t="n">
-        <v>17.23</v>
+        <v>17.49</v>
       </c>
       <c r="F3" t="n">
-        <v>20.39</v>
+        <v>18.78</v>
       </c>
       <c r="G3" t="n">
         <v>33</v>
@@ -677,7 +677,7 @@
         <v>10.27272727272727</v>
       </c>
       <c r="K3" t="n">
-        <v>52912859.25</v>
+        <v>52782795.5</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         <v>317.42</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02251646169012411</v>
+        <v>0.02952137837376489</v>
       </c>
       <c r="S3" t="n">
         <v>1.32</v>
@@ -712,19 +712,19 @@
         <v>339</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9072957531397282</v>
+        <v>0.9227360257458656</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9969527034807439</v>
+        <v>1.019557203799198</v>
       </c>
       <c r="X3" t="n">
-        <v>18.99049999999999</v>
+        <v>18.95449999999999</v>
       </c>
       <c r="Y3" t="n">
-        <v>17.28266540613559</v>
+        <v>17.15450583334277</v>
       </c>
       <c r="Z3" t="n">
-        <v>728324884.66</v>
+        <v>664882944.66</v>
       </c>
     </row>
     <row r="4">
@@ -739,16 +739,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.124238857310905</v>
+        <v>1.16459921302747</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8623571061925754</v>
+        <v>0.8762073867875242</v>
       </c>
       <c r="E4" t="n">
-        <v>34.44</v>
+        <v>35.18</v>
       </c>
       <c r="F4" t="n">
-        <v>14.36</v>
+        <v>15.62</v>
       </c>
       <c r="G4" t="n">
         <v>66</v>
@@ -763,7 +763,7 @@
         <v>10.33333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>13064478.15</v>
+        <v>12873934.75</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         <v>159.78</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2618817511183296</v>
+        <v>0.2883918262399456</v>
       </c>
       <c r="S4" t="n">
         <v>2.78</v>
@@ -798,19 +798,19 @@
         <v>682</v>
       </c>
       <c r="V4" t="n">
-        <v>0.876871371830125</v>
+        <v>0.8999513954618709</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9807286215278754</v>
+        <v>1.017798680186523</v>
       </c>
       <c r="X4" t="n">
-        <v>39.27600000000001</v>
+        <v>39.09100000000001</v>
       </c>
       <c r="Y4" t="n">
-        <v>35.1167481441971</v>
+        <v>34.56479231585647</v>
       </c>
       <c r="Z4" t="n">
-        <v>202690145.28</v>
+        <v>214261995.82</v>
       </c>
     </row>
     <row r="5">
@@ -825,16 +825,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.5800497772786859</v>
+        <v>0.6019671277034271</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5638439122245398</v>
+        <v>0.5751925578179764</v>
       </c>
       <c r="E5" t="n">
-        <v>24.04</v>
+        <v>24.42</v>
       </c>
       <c r="F5" t="n">
-        <v>18.89</v>
+        <v>19.64</v>
       </c>
       <c r="G5" t="n">
         <v>40</v>
@@ -849,7 +849,7 @@
         <v>9.824999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>8767389.300000001</v>
+        <v>8602203.449999999</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>246.15</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01620586505414612</v>
+        <v>0.02677456988545068</v>
       </c>
       <c r="S5" t="n">
         <v>1.814</v>
@@ -884,19 +884,19 @@
         <v>393</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9402745726913604</v>
+        <v>0.9558478158759988</v>
       </c>
       <c r="W5" t="n">
-        <v>1.005905631962899</v>
+        <v>1.024447514235748</v>
       </c>
       <c r="X5" t="n">
-        <v>25.56699999999999</v>
+        <v>25.54799999999998</v>
       </c>
       <c r="Y5" t="n">
-        <v>23.89886211601078</v>
+        <v>23.83723876592902</v>
       </c>
       <c r="Z5" t="n">
-        <v>146418312.48</v>
+        <v>98552819.64</v>
       </c>
     </row>
     <row r="6">
@@ -911,16 +911,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.4590799121013069</v>
+        <v>0.4659582618772986</v>
       </c>
       <c r="D6" t="n">
-        <v>0.438176499589271</v>
+        <v>0.4486571409991897</v>
       </c>
       <c r="E6" t="n">
-        <v>20.42</v>
+        <v>20.55</v>
       </c>
       <c r="F6" t="n">
-        <v>10.69</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>37</v>
@@ -935,7 +935,7 @@
         <v>9.972972972972974</v>
       </c>
       <c r="K6" t="n">
-        <v>57528731.1</v>
+        <v>58254585.8</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         <v>252.13</v>
       </c>
       <c r="R6" t="n">
-        <v>0.02090341251203598</v>
+        <v>0.01730112087810887</v>
       </c>
       <c r="S6" t="n">
         <v>2.15</v>
@@ -970,488 +970,488 @@
         <v>369</v>
       </c>
       <c r="V6" t="n">
-        <v>0.872239545512793</v>
+        <v>0.8825045091471269</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9603529510805866</v>
+        <v>0.9878100531050347</v>
       </c>
       <c r="X6" t="n">
-        <v>23.411</v>
+        <v>23.286</v>
       </c>
       <c r="Y6" t="n">
-        <v>21.26301582873617</v>
+        <v>20.80359471479777</v>
       </c>
       <c r="Z6" t="n">
-        <v>495913585.6</v>
+        <v>334689136.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>009816.TW</t>
+          <t>00410A.TW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>凱基台灣TOP50</t>
+          <t>主動永豐科技趨勢</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.1659641055872365</v>
+        <v>0.007221798312800898</v>
       </c>
       <c r="D7" t="n">
-        <v>0.134917613707711</v>
+        <v>0.0006817425719989334</v>
       </c>
       <c r="E7" t="n">
-        <v>15.93</v>
+        <v>11.88</v>
       </c>
       <c r="F7" t="n">
-        <v>13.25</v>
+        <v>16.62</v>
       </c>
       <c r="G7" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
         <v>100</v>
       </c>
       <c r="I7" t="n">
-        <v>5.32</v>
+        <v>5.53</v>
       </c>
       <c r="J7" t="n">
-        <v>10.54166666666667</v>
+        <v>7.6</v>
       </c>
       <c r="K7" t="n">
-        <v>134203129.05</v>
+        <v>5843770.65</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>2</v>
       </c>
       <c r="N7" t="n">
-        <v>8.99</v>
+        <v>5.92</v>
       </c>
       <c r="O7" t="n">
-        <v>0.64</v>
+        <v>4.92</v>
       </c>
       <c r="P7" t="n">
-        <v>9.630000000000001</v>
+        <v>10.84</v>
       </c>
       <c r="Q7" t="n">
-        <v>227.93</v>
+        <v>942.39</v>
       </c>
       <c r="R7" t="n">
-        <v>0.03104649187952546</v>
+        <v>0.006540055740801964</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>127.78</v>
+        <v>27.64</v>
       </c>
       <c r="U7" t="n">
-        <v>253</v>
+        <v>38</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9625959272463593</v>
+        <v>0.9557137685531553</v>
       </c>
       <c r="W7" t="n">
-        <v>1.000062576055201</v>
+        <v>1.033095053142372</v>
       </c>
       <c r="X7" t="n">
-        <v>16.549</v>
+        <v>12.4305</v>
       </c>
       <c r="Y7" t="n">
-        <v>15.92900322581484</v>
+        <v>11.49942588909368</v>
       </c>
       <c r="Z7" t="n">
-        <v>3042296935.56</v>
+        <v>85406496.12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>009824.TW</t>
+          <t>009816.TW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>群益美國科技巨頭</t>
+          <t>凱基台灣TOP50</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.01351643248194301</v>
+        <v>0.1759082972776618</v>
       </c>
       <c r="D8" t="n">
-        <v>0.007552616385237076</v>
+        <v>0.1435610197768122</v>
       </c>
       <c r="E8" t="n">
-        <v>10.3</v>
+        <v>16.08</v>
       </c>
       <c r="F8" t="n">
-        <v>23.75</v>
+        <v>14.23</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="H8" t="n">
         <v>100</v>
       </c>
       <c r="I8" t="n">
-        <v>5.26</v>
+        <v>5.32</v>
       </c>
       <c r="J8" t="n">
-        <v>5.75</v>
+        <v>10.54166666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>5192747.7</v>
+        <v>133555137</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>7.35</v>
+        <v>8.99</v>
       </c>
       <c r="O8" t="n">
-        <v>1.39</v>
+        <v>0.64</v>
       </c>
       <c r="P8" t="n">
-        <v>8.74</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>1975.8</v>
+        <v>227.93</v>
       </c>
       <c r="R8" t="n">
-        <v>0.005963816096705932</v>
+        <v>0.03234727750084954</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>21.06</v>
+        <v>127.78</v>
       </c>
       <c r="U8" t="n">
-        <v>23</v>
+        <v>253</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9738110995556392</v>
+        <v>0.9721592454883466</v>
       </c>
       <c r="W8" t="n">
-        <v>1.011394838385178</v>
+        <v>1.011319699585037</v>
       </c>
       <c r="X8" t="n">
-        <v>10.57700000000001</v>
+        <v>16.5405</v>
       </c>
       <c r="Y8" t="n">
-        <v>10.18395547326035</v>
+        <v>15.90001658881748</v>
       </c>
       <c r="Z8" t="n">
-        <v>16287647.5</v>
+        <v>1648663715.04</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>009804.TW</t>
+          <t>009824.TW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>聯邦台精彩50</t>
+          <t>群益美國科技巨頭</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.6162644045109318</v>
+        <v>0.01820880510014233</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6000673775179672</v>
+        <v>0.01579937295296352</v>
       </c>
       <c r="E9" t="n">
-        <v>22.86</v>
+        <v>10.35</v>
       </c>
       <c r="F9" t="n">
-        <v>14.52</v>
+        <v>23.08</v>
       </c>
       <c r="G9" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
         <v>100</v>
       </c>
       <c r="I9" t="n">
-        <v>4.12</v>
+        <v>5.26</v>
       </c>
       <c r="J9" t="n">
-        <v>8.82258064516129</v>
+        <v>5.75</v>
       </c>
       <c r="K9" t="n">
-        <v>1230997.35</v>
+        <v>4322912.3</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>9.630000000000001</v>
+        <v>7.35</v>
       </c>
       <c r="O9" t="n">
-        <v>0.76</v>
+        <v>1.39</v>
       </c>
       <c r="P9" t="n">
-        <v>10.39</v>
+        <v>8.74</v>
       </c>
       <c r="Q9" t="n">
-        <v>133.05</v>
+        <v>1975.8</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01619702699296455</v>
+        <v>0.002409432147178814</v>
       </c>
       <c r="S9" t="n">
-        <v>2.786</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>255.36</v>
+        <v>21.06</v>
       </c>
       <c r="U9" t="n">
-        <v>547</v>
+        <v>23</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9529169011442506</v>
+        <v>0.9777987718469527</v>
       </c>
       <c r="W9" t="n">
-        <v>0.9993894935719506</v>
+        <v>1.01290365550819</v>
       </c>
       <c r="X9" t="n">
-        <v>23.9895</v>
+        <v>10.585</v>
       </c>
       <c r="Y9" t="n">
-        <v>22.87396470248584</v>
+        <v>10.21814853141905</v>
       </c>
       <c r="Z9" t="n">
-        <v>34374810.6</v>
+        <v>24765366.15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>00830.TW</t>
+          <t>009804.TW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>國泰費城半導體</t>
+          <t>聯邦台精彩50</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2.372366540092322</v>
+        <v>0.6300843661102979</v>
       </c>
       <c r="D10" t="n">
-        <v>2.24993035161264</v>
+        <v>0.6116653473279499</v>
       </c>
       <c r="E10" t="n">
-        <v>81</v>
+        <v>23.1</v>
       </c>
       <c r="F10" t="n">
-        <v>13.72</v>
+        <v>14.76</v>
       </c>
       <c r="G10" t="n">
-        <v>495</v>
+        <v>62</v>
       </c>
       <c r="H10" t="n">
-        <v>97.17</v>
+        <v>100</v>
       </c>
       <c r="I10" t="n">
-        <v>3.93</v>
+        <v>4.12</v>
       </c>
       <c r="J10" t="n">
-        <v>12.29090909090909</v>
+        <v>8.82258064516129</v>
       </c>
       <c r="K10" t="n">
-        <v>10532745.05</v>
+        <v>1184276.45</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>13.29</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-12.33</v>
+        <v>0.76</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9599999999999991</v>
+        <v>10.39</v>
       </c>
       <c r="Q10" t="n">
-        <v>19.85</v>
+        <v>133.05</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1224361884796816</v>
+        <v>0.01841901878234808</v>
       </c>
       <c r="S10" t="n">
-        <v>17.71</v>
+        <v>2.786</v>
       </c>
       <c r="T10" t="n">
-        <v>1946.3</v>
+        <v>255.36</v>
       </c>
       <c r="U10" t="n">
-        <v>6084</v>
+        <v>547</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9246311463713935</v>
+        <v>0.9635237439779767</v>
       </c>
       <c r="W10" t="n">
-        <v>1.009529726497441</v>
+        <v>1.012258194532464</v>
       </c>
       <c r="X10" t="n">
-        <v>87.60249999999999</v>
+        <v>23.9745</v>
       </c>
       <c r="Y10" t="n">
-        <v>80.23537878476266</v>
+        <v>22.82026475534664</v>
       </c>
       <c r="Z10" t="n">
-        <v>1189319922</v>
+        <v>11465846.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>009818.TW</t>
+          <t>00830.TW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>華南永昌NASDAQxT</t>
+          <t>國泰費城半導體</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.09419414424551587</v>
+        <v>2.427245966666353</v>
       </c>
       <c r="D11" t="n">
-        <v>0.08461124580855595</v>
+        <v>2.275276692020235</v>
       </c>
       <c r="E11" t="n">
-        <v>20.72</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>24.33</v>
+        <v>14.29</v>
       </c>
       <c r="G11" t="n">
-        <v>21</v>
+        <v>495</v>
       </c>
       <c r="H11" t="n">
-        <v>100</v>
+        <v>97.17</v>
       </c>
       <c r="I11" t="n">
-        <v>3.81</v>
+        <v>3.93</v>
       </c>
       <c r="J11" t="n">
-        <v>8.714285714285714</v>
+        <v>12.29090909090909</v>
       </c>
       <c r="K11" t="n">
-        <v>168580</v>
+        <v>10553768.95</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>7.21</v>
+        <v>13.29</v>
       </c>
       <c r="O11" t="n">
-        <v>1.65</v>
+        <v>-12.33</v>
       </c>
       <c r="P11" t="n">
-        <v>8.859999999999999</v>
+        <v>0.9599999999999991</v>
       </c>
       <c r="Q11" t="n">
-        <v>222.85</v>
+        <v>19.85</v>
       </c>
       <c r="R11" t="n">
-        <v>0.009582898436959919</v>
+        <v>0.1519692746461176</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>17.71</v>
       </c>
       <c r="T11" t="n">
-        <v>79.97</v>
+        <v>1946.3</v>
       </c>
       <c r="U11" t="n">
-        <v>183</v>
+        <v>6084</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9784892918703219</v>
+        <v>0.9426264585889134</v>
       </c>
       <c r="W11" t="n">
-        <v>1.014250998476293</v>
+        <v>1.028230337748993</v>
       </c>
       <c r="X11" t="n">
-        <v>21.1755</v>
+        <v>87.62749999999998</v>
       </c>
       <c r="Y11" t="n">
-        <v>20.42886822998214</v>
+        <v>80.33219500294879</v>
       </c>
       <c r="Z11" t="n">
-        <v>1247696.24</v>
+        <v>648362339.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>00400A.TW</t>
+          <t>009818.TW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>主動國泰動能高息</t>
+          <t>華南永昌NASDAQxT</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.06131321083695918</v>
+        <v>0.1035089655468708</v>
       </c>
       <c r="D12" t="n">
-        <v>0.05544203170693041</v>
+        <v>0.09303632433434506</v>
       </c>
       <c r="E12" t="n">
-        <v>14.61</v>
+        <v>20.91</v>
       </c>
       <c r="F12" t="n">
-        <v>13.83</v>
+        <v>24.47</v>
       </c>
       <c r="G12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H12" t="n">
-        <v>68.75</v>
+        <v>100</v>
       </c>
       <c r="I12" t="n">
-        <v>3.77</v>
+        <v>3.81</v>
       </c>
       <c r="J12" t="n">
-        <v>13.1875</v>
+        <v>8.714285714285714</v>
       </c>
       <c r="K12" t="n">
-        <v>38019073.2</v>
+        <v>167194.3</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1462,82 +1462,82 @@
         <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>13.12</v>
+        <v>7.21</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.83</v>
+        <v>1.65</v>
       </c>
       <c r="P12" t="n">
-        <v>12.29</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>126.3</v>
+        <v>222.85</v>
       </c>
       <c r="R12" t="n">
-        <v>0.00587117913002877</v>
+        <v>0.01047264121252578</v>
       </c>
       <c r="S12" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>60.34</v>
+        <v>79.97</v>
       </c>
       <c r="U12" t="n">
-        <v>211</v>
+        <v>183</v>
       </c>
       <c r="V12" t="n">
-        <v>0.9357886309047234</v>
+        <v>0.9861812007734755</v>
       </c>
       <c r="W12" t="n">
-        <v>1.007777724703607</v>
+        <v>1.017862113287314</v>
       </c>
       <c r="X12" t="n">
-        <v>15.61250000000001</v>
+        <v>21.203</v>
       </c>
       <c r="Y12" t="n">
-        <v>14.49724442390993</v>
+        <v>20.54305757826913</v>
       </c>
       <c r="Z12" t="n">
-        <v>445828825.2</v>
+        <v>7556832.18</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>00663L.TW</t>
+          <t>00400A.TW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>國泰臺灣加權正2</t>
+          <t>主動國泰動能高息</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11.34588930018312</v>
+        <v>0.07705374132130549</v>
       </c>
       <c r="D13" t="n">
-        <v>2.926252414611309</v>
+        <v>0.06379181116397814</v>
       </c>
       <c r="E13" t="n">
-        <v>103.45</v>
+        <v>14.84</v>
       </c>
       <c r="F13" t="n">
-        <v>14.28</v>
+        <v>14.47</v>
       </c>
       <c r="G13" t="n">
-        <v>564</v>
+        <v>16</v>
       </c>
       <c r="H13" t="n">
-        <v>89.89</v>
+        <v>68.75</v>
       </c>
       <c r="I13" t="n">
-        <v>3.76</v>
+        <v>3.77</v>
       </c>
       <c r="J13" t="n">
-        <v>11.9113475177305</v>
+        <v>13.1875</v>
       </c>
       <c r="K13" t="n">
-        <v>5623571.55</v>
+        <v>37319182.4</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1548,508 +1548,512 @@
         <v>2</v>
       </c>
       <c r="N13" t="n">
-        <v>15.99</v>
+        <v>13.12</v>
       </c>
       <c r="O13" t="n">
-        <v>-24.46</v>
+        <v>-0.83</v>
       </c>
       <c r="P13" t="n">
-        <v>-8.470000000000001</v>
+        <v>12.29</v>
       </c>
       <c r="Q13" t="n">
-        <v>18.35</v>
+        <v>126.3</v>
       </c>
       <c r="R13" t="n">
-        <v>8.419636885571808</v>
+        <v>0.01326193015732735</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="T13" t="n">
-        <v>2121.97</v>
+        <v>60.34</v>
       </c>
       <c r="U13" t="n">
-        <v>6718</v>
+        <v>211</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9153247212882671</v>
+        <v>0.9510077221314361</v>
       </c>
       <c r="W13" t="n">
-        <v>1.002905676823877</v>
+        <v>1.025594155163499</v>
       </c>
       <c r="X13" t="n">
-        <v>113.0200000000001</v>
+        <v>15.60450000000001</v>
       </c>
       <c r="Y13" t="n">
-        <v>103.1502786260199</v>
+        <v>14.4696612449339</v>
       </c>
       <c r="Z13" t="n">
-        <v>635770389.1</v>
+        <v>328560538.32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>00631L.TW</t>
+          <t>00663L.TW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>國泰臺灣加權正2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>15.22392136026959</v>
+        <v>11.6156931381423</v>
       </c>
       <c r="D14" t="n">
-        <v>3.344263321462639</v>
+        <v>2.95707576482805</v>
       </c>
       <c r="E14" t="n">
-        <v>35.87</v>
+        <v>105.75</v>
       </c>
       <c r="F14" t="n">
-        <v>13.02</v>
+        <v>15.35</v>
       </c>
       <c r="G14" t="n">
-        <v>644</v>
+        <v>564</v>
       </c>
       <c r="H14" t="n">
-        <v>89.44</v>
+        <v>89.89</v>
       </c>
       <c r="I14" t="n">
-        <v>3.74</v>
+        <v>3.76</v>
       </c>
       <c r="J14" t="n">
-        <v>12.68167701863354</v>
+        <v>11.9113475177305</v>
       </c>
       <c r="K14" t="n">
-        <v>196583279.9</v>
+        <v>5562151.75</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>17.37</v>
+        <v>15.99</v>
       </c>
       <c r="O14" t="n">
-        <v>-12.43</v>
+        <v>-24.46</v>
       </c>
       <c r="P14" t="n">
-        <v>4.940000000000001</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>15.49</v>
+        <v>18.35</v>
       </c>
       <c r="R14" t="n">
-        <v>11.87965803880695</v>
+        <v>8.658617373314254</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2407.1</v>
+        <v>2121.97</v>
       </c>
       <c r="U14" t="n">
-        <v>8167</v>
+        <v>6718</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9177786022234451</v>
+        <v>0.9368770764119598</v>
       </c>
       <c r="W14" t="n">
-        <v>1.004226400573346</v>
+        <v>1.029967797730523</v>
       </c>
       <c r="X14" t="n">
-        <v>39.08349999999998</v>
+        <v>112.875</v>
       </c>
       <c r="Y14" t="n">
-        <v>35.71903704136898</v>
+        <v>102.6731129196605</v>
       </c>
       <c r="Z14" t="n">
-        <v>8673473574.129999</v>
+        <v>463915944</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>00904.TW</t>
+          <t>00631L.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>台新臺灣半導體30</t>
+          <t>元大台灣50正2</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.716494642229002</v>
+        <v>15.55327694858688</v>
       </c>
       <c r="D15" t="n">
-        <v>1.667728448296326</v>
+        <v>3.37845891075097</v>
       </c>
       <c r="E15" t="n">
-        <v>37.8</v>
+        <v>36.61</v>
       </c>
       <c r="F15" t="n">
-        <v>10.63</v>
+        <v>14.19</v>
       </c>
       <c r="G15" t="n">
-        <v>239</v>
+        <v>644</v>
       </c>
       <c r="H15" t="n">
-        <v>99.16</v>
+        <v>89.44</v>
       </c>
       <c r="I15" t="n">
-        <v>3.55</v>
+        <v>3.74</v>
       </c>
       <c r="J15" t="n">
-        <v>10.78242677824268</v>
+        <v>12.68167701863354</v>
       </c>
       <c r="K15" t="n">
-        <v>3968762.2</v>
+        <v>194017571.1</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>11.85</v>
+        <v>17.37</v>
       </c>
       <c r="O15" t="n">
-        <v>-12.45</v>
+        <v>-12.43</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.5999999999999996</v>
+        <v>4.940000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>37.53</v>
+        <v>15.49</v>
       </c>
       <c r="R15" t="n">
-        <v>0.04876619393267623</v>
+        <v>12.17481803783591</v>
       </c>
       <c r="S15" t="n">
-        <v>7.050000000000001</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>848.62</v>
+        <v>2407.1</v>
       </c>
       <c r="U15" t="n">
-        <v>2577</v>
+        <v>8167</v>
       </c>
       <c r="V15" t="n">
-        <v>0.8846243856775099</v>
+        <v>0.937960365345939</v>
       </c>
       <c r="W15" t="n">
-        <v>0.9779823312439648</v>
+        <v>1.029819691485076</v>
       </c>
       <c r="X15" t="n">
-        <v>42.73</v>
+        <v>39.03149999999998</v>
       </c>
       <c r="Y15" t="n">
-        <v>38.65100502574469</v>
+        <v>35.549912574701</v>
       </c>
       <c r="Z15" t="n">
-        <v>93658836.59999999</v>
+        <v>5307505425.39</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>00685L.TW</t>
+          <t>00904.TW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>群益臺灣加權正2</t>
+          <t>台新臺灣半導體30</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10.26154014351294</v>
+        <v>1.757070302017163</v>
       </c>
       <c r="D16" t="n">
-        <v>2.757196595596791</v>
+        <v>1.688156361908209</v>
       </c>
       <c r="E16" t="n">
-        <v>11.84</v>
+        <v>38.48</v>
       </c>
       <c r="F16" t="n">
-        <v>13.8</v>
+        <v>11.14</v>
       </c>
       <c r="G16" t="n">
-        <v>514</v>
+        <v>239</v>
       </c>
       <c r="H16" t="n">
-        <v>88.52</v>
+        <v>99.16</v>
       </c>
       <c r="I16" t="n">
-        <v>3.46</v>
+        <v>3.55</v>
       </c>
       <c r="J16" t="n">
-        <v>12.18093385214008</v>
+        <v>10.78242677824268</v>
       </c>
       <c r="K16" t="n">
-        <v>262914148.35</v>
+        <v>4009785.65</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>15.89</v>
+        <v>11.85</v>
       </c>
       <c r="O16" t="n">
-        <v>-18.5</v>
+        <v>-12.45</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.609999999999999</v>
+        <v>-0.5999999999999996</v>
       </c>
       <c r="Q16" t="n">
-        <v>18.65</v>
+        <v>37.53</v>
       </c>
       <c r="R16" t="n">
-        <v>7.504343547916149</v>
+        <v>0.06891394010895446</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>7.050000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>1777.84</v>
+        <v>848.62</v>
       </c>
       <c r="U16" t="n">
-        <v>6261</v>
+        <v>2577</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9153813444663494</v>
+        <v>0.9046986492999636</v>
       </c>
       <c r="W16" t="n">
-        <v>1.003596846599693</v>
+        <v>1.011223833010163</v>
       </c>
       <c r="X16" t="n">
-        <v>12.9345</v>
+        <v>42.5335</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.79756596497423</v>
+        <v>38.05290059813422</v>
       </c>
       <c r="Z16" t="n">
-        <v>4394906957.44</v>
+        <v>71453358.08</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>009809.TW</t>
+          <t>00913.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>富邦淨零ESG50</t>
+          <t>兆豐台灣晶圓製造</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.3415566883107366</v>
+        <v>1.621899753860291</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3030785259366744</v>
+        <v>1.595483088776454</v>
       </c>
       <c r="E17" t="n">
-        <v>17.94</v>
+        <v>47.93</v>
       </c>
       <c r="F17" t="n">
-        <v>14.45</v>
+        <v>14.68</v>
       </c>
       <c r="G17" t="n">
-        <v>34</v>
+        <v>262</v>
       </c>
       <c r="H17" t="n">
-        <v>97.06</v>
+        <v>96.18000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J17" t="n">
-        <v>8.235294117647058</v>
+        <v>12.79770992366412</v>
       </c>
       <c r="K17" t="n">
-        <v>296860.9</v>
+        <v>1818921.85</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>7.76</v>
+        <v>13.5</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.12</v>
+        <v>-9.19</v>
       </c>
       <c r="P17" t="n">
-        <v>7.64</v>
+        <v>4.31</v>
       </c>
       <c r="Q17" t="n">
-        <v>172.16</v>
+        <v>28.72</v>
       </c>
       <c r="R17" t="n">
-        <v>0.03847816237406221</v>
+        <v>0.02641666508383667</v>
       </c>
       <c r="S17" t="n">
-        <v>0.315</v>
+        <v>6.699999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>115.56</v>
+        <v>916.5599999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>280</v>
+        <v>3353</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9647235964723595</v>
+        <v>0.9284621195978536</v>
       </c>
       <c r="W17" t="n">
-        <v>0.9955201797903795</v>
+        <v>1.021547838622306</v>
       </c>
       <c r="X17" t="n">
-        <v>18.596</v>
+        <v>51.623</v>
       </c>
       <c r="Y17" t="n">
-        <v>18.02072962878313</v>
+        <v>46.91899702381047</v>
       </c>
       <c r="Z17" t="n">
-        <v>9602582.34</v>
+        <v>40809423.34</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>00715L.TW</t>
+          <t>00685L.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>期街口布蘭特正2</t>
+          <t>群益臺灣加權正2</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.634566129417959</v>
+        <v>10.53275822521513</v>
       </c>
       <c r="D18" t="n">
-        <v>2.61715656906853</v>
+        <v>2.786640504456303</v>
       </c>
       <c r="E18" t="n">
-        <v>82.55</v>
+        <v>12.13</v>
       </c>
       <c r="F18" t="n">
-        <v>90.20999999999999</v>
+        <v>15.55</v>
       </c>
       <c r="G18" t="n">
-        <v>425</v>
+        <v>514</v>
       </c>
       <c r="H18" t="n">
-        <v>77.65000000000001</v>
+        <v>88.52</v>
       </c>
       <c r="I18" t="n">
-        <v>3.32</v>
+        <v>3.46</v>
       </c>
       <c r="J18" t="n">
-        <v>17.11294117647059</v>
+        <v>12.18093385214008</v>
       </c>
       <c r="K18" t="n">
-        <v>3302473.2</v>
-      </c>
-      <c r="L18" t="inlineStr"/>
+        <v>259483421.25</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>32.14</v>
+        <v>15.89</v>
       </c>
       <c r="O18" t="n">
-        <v>-44.86</v>
+        <v>-18.5</v>
       </c>
       <c r="P18" t="n">
-        <v>-12.72</v>
+        <v>-2.609999999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>14.59</v>
+        <v>18.65</v>
       </c>
       <c r="R18" t="n">
-        <v>3.017409560349428</v>
+        <v>7.74611772075883</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1409.31</v>
+        <v>1777.84</v>
       </c>
       <c r="U18" t="n">
-        <v>7273</v>
+        <v>6261</v>
       </c>
       <c r="V18" t="n">
-        <v>1.173543732451932</v>
+        <v>0.9388544891640863</v>
       </c>
       <c r="W18" t="n">
-        <v>1.41002777042993</v>
+        <v>1.032317144603849</v>
       </c>
       <c r="X18" t="n">
-        <v>70.34249999999994</v>
+        <v>12.92000000000001</v>
       </c>
       <c r="Y18" t="n">
-        <v>58.54494622813689</v>
+        <v>11.75026498727276</v>
       </c>
       <c r="Z18" t="n">
-        <v>276884504.65</v>
+        <v>2399751468.45</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>00675L.TW</t>
+          <t>009809.TW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>富邦臺灣加權正2</t>
+          <t>富邦淨零ESG50</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10.77962625416551</v>
+        <v>0.3526493668090109</v>
       </c>
       <c r="D19" t="n">
-        <v>2.863158504697493</v>
+        <v>0.3126617397103886</v>
       </c>
       <c r="E19" t="n">
-        <v>313</v>
+        <v>18.11</v>
       </c>
       <c r="F19" t="n">
-        <v>14.06</v>
+        <v>15.64</v>
       </c>
       <c r="G19" t="n">
-        <v>564</v>
+        <v>34</v>
       </c>
       <c r="H19" t="n">
-        <v>87.06</v>
+        <v>97.06</v>
       </c>
       <c r="I19" t="n">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="J19" t="n">
-        <v>12.38297872340426</v>
+        <v>8.235294117647058</v>
       </c>
       <c r="K19" t="n">
-        <v>1220342.05</v>
+        <v>257533.7</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -2060,340 +2064,336 @@
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>15.7</v>
+        <v>7.76</v>
       </c>
       <c r="O19" t="n">
-        <v>-24.73</v>
+        <v>-0.12</v>
       </c>
       <c r="P19" t="n">
-        <v>-9.030000000000001</v>
+        <v>7.64</v>
       </c>
       <c r="Q19" t="n">
-        <v>16.61</v>
+        <v>172.16</v>
       </c>
       <c r="R19" t="n">
-        <v>7.916467749468019</v>
+        <v>0.03998762709862236</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
       <c r="T19" t="n">
-        <v>1792.47</v>
+        <v>115.56</v>
       </c>
       <c r="U19" t="n">
-        <v>6984</v>
+        <v>280</v>
       </c>
       <c r="V19" t="n">
-        <v>0.914168887590814</v>
+        <v>0.9745990743730489</v>
       </c>
       <c r="W19" t="n">
-        <v>1.002719037679424</v>
+        <v>1.007531432561726</v>
       </c>
       <c r="X19" t="n">
-        <v>342.3875000000002</v>
+        <v>18.582</v>
       </c>
       <c r="Y19" t="n">
-        <v>312.1512489923107</v>
+        <v>17.97462532156831</v>
       </c>
       <c r="Z19" t="n">
-        <v>482507654</v>
+        <v>6505238.77</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>00935.TW</t>
+          <t>00715L.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>野村臺灣新科技50</t>
+          <t>期街口布蘭特正2</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.390536372815003</v>
+        <v>5.615889716058136</v>
       </c>
       <c r="D20" t="n">
-        <v>1.103386361202003</v>
+        <v>2.645476803396419</v>
       </c>
       <c r="E20" t="n">
-        <v>55.65</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>12.52</v>
+        <v>92.14</v>
       </c>
       <c r="G20" t="n">
-        <v>136</v>
+        <v>425</v>
       </c>
       <c r="H20" t="n">
-        <v>83.09</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>3.15</v>
+        <v>3.32</v>
       </c>
       <c r="J20" t="n">
-        <v>12.30882352941176</v>
+        <v>17.11294117647059</v>
       </c>
       <c r="K20" t="n">
-        <v>13273311.8</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
+        <v>3222811.4</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
         <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>14.6</v>
+        <v>32.14</v>
       </c>
       <c r="O20" t="n">
-        <v>-8.99</v>
+        <v>-44.86</v>
       </c>
       <c r="P20" t="n">
-        <v>5.609999999999999</v>
+        <v>-12.72</v>
       </c>
       <c r="Q20" t="n">
-        <v>43.74</v>
+        <v>14.59</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2871500116129995</v>
+        <v>2.970412912661717</v>
       </c>
       <c r="S20" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>428.12</v>
+        <v>1409.31</v>
       </c>
       <c r="U20" t="n">
-        <v>1674</v>
+        <v>7273</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9211669770328986</v>
+        <v>1.157739350485028</v>
       </c>
       <c r="W20" t="n">
-        <v>0.9968646563736249</v>
+        <v>1.410750568586542</v>
       </c>
       <c r="X20" t="n">
-        <v>60.41250000000001</v>
+        <v>71.12999999999995</v>
       </c>
       <c r="Y20" t="n">
-        <v>55.82503065405338</v>
+        <v>58.37318221498789</v>
       </c>
       <c r="Z20" t="n">
-        <v>610833599.25</v>
+        <v>189852489.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>00894.TW</t>
+          <t>00401A.TW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>中信小資高價30</t>
+          <t>主動摩根台灣鑫收</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.008364540345374</v>
+        <v>0.06275094536995685</v>
       </c>
       <c r="D21" t="n">
-        <v>1.718294806500042</v>
+        <v>0.06145961825469559</v>
       </c>
       <c r="E21" t="n">
-        <v>46.68</v>
+        <v>13.72</v>
       </c>
       <c r="F21" t="n">
-        <v>16.13</v>
+        <v>18.26</v>
       </c>
       <c r="G21" t="n">
-        <v>243</v>
+        <v>21</v>
       </c>
       <c r="H21" t="n">
-        <v>82.72</v>
+        <v>100</v>
       </c>
       <c r="I21" t="n">
-        <v>2.88</v>
+        <v>3.23</v>
       </c>
       <c r="J21" t="n">
-        <v>15.32921810699589</v>
+        <v>15.19047619047619</v>
       </c>
       <c r="K21" t="n">
-        <v>1230531</v>
+        <v>6929884.6</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>15.7</v>
+        <v>11.76</v>
       </c>
       <c r="O21" t="n">
-        <v>-8.380000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="P21" t="n">
-        <v>7.319999999999999</v>
+        <v>12.12</v>
       </c>
       <c r="Q21" t="n">
-        <v>22.58</v>
+        <v>80.95</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2900697338453324</v>
+        <v>0.001291327115261254</v>
       </c>
       <c r="S21" t="n">
-        <v>7.549999999999999</v>
+        <v>0.377</v>
       </c>
       <c r="T21" t="n">
-        <v>698.73</v>
+        <v>67.92</v>
       </c>
       <c r="U21" t="n">
-        <v>3725</v>
+        <v>319</v>
       </c>
       <c r="V21" t="n">
-        <v>0.934412939257154</v>
+        <v>0.9643974273363087</v>
       </c>
       <c r="W21" t="n">
-        <v>1.004246345496669</v>
+        <v>1.013276976284115</v>
       </c>
       <c r="X21" t="n">
-        <v>49.95649999999998</v>
+        <v>14.22650000000001</v>
       </c>
       <c r="Y21" t="n">
-        <v>46.48261874123479</v>
+        <v>13.54022673081345</v>
       </c>
       <c r="Z21" t="n">
-        <v>37953874.2</v>
+        <v>58041101.72000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>00901.TW</t>
+          <t>00675L.TW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>永豐智能車供應鏈</t>
+          <t>富邦臺灣加權正2</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.739259580232981</v>
+        <v>11.04043089394563</v>
       </c>
       <c r="D22" t="n">
-        <v>1.683960124062911</v>
+        <v>2.89348485751947</v>
       </c>
       <c r="E22" t="n">
-        <v>44.75</v>
+        <v>320.05</v>
       </c>
       <c r="F22" t="n">
-        <v>14.06</v>
+        <v>15.24</v>
       </c>
       <c r="G22" t="n">
-        <v>276</v>
+        <v>564</v>
       </c>
       <c r="H22" t="n">
-        <v>89.48999999999999</v>
+        <v>87.06</v>
       </c>
       <c r="I22" t="n">
-        <v>2.79</v>
+        <v>3.18</v>
       </c>
       <c r="J22" t="n">
-        <v>13.22463768115942</v>
+        <v>12.38297872340426</v>
       </c>
       <c r="K22" t="n">
-        <v>261154.1</v>
+        <v>1211309</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>15.18</v>
+        <v>15.7</v>
       </c>
       <c r="O22" t="n">
-        <v>-7.3</v>
+        <v>-24.73</v>
       </c>
       <c r="P22" t="n">
-        <v>7.88</v>
+        <v>-9.030000000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>24.17</v>
+        <v>16.61</v>
       </c>
       <c r="R22" t="n">
-        <v>0.05529945617006993</v>
+        <v>8.146946036426163</v>
       </c>
       <c r="S22" t="n">
-        <v>4.671</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>771.28</v>
+        <v>1792.47</v>
       </c>
       <c r="U22" t="n">
-        <v>3650</v>
+        <v>6984</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9329038848410937</v>
+        <v>0.9360102945047227</v>
       </c>
       <c r="W22" t="n">
-        <v>0.9983355361862268</v>
+        <v>1.030257331635837</v>
       </c>
       <c r="X22" t="n">
-        <v>47.9685</v>
+        <v>341.9300000000002</v>
       </c>
       <c r="Y22" t="n">
-        <v>44.82460893954641</v>
+        <v>310.6505434829825</v>
       </c>
       <c r="Z22" t="n">
-        <v>14384932.25</v>
+        <v>379197800.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>0057.TW</t>
+          <t>00935.TW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>富邦摩台</t>
+          <t>野村臺灣新科技50</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6.074588606858966</v>
+        <v>1.418583822219333</v>
       </c>
       <c r="D23" t="n">
-        <v>4.84649526179438</v>
+        <v>1.119176523101771</v>
       </c>
       <c r="E23" t="n">
-        <v>318.95</v>
+        <v>56.4</v>
       </c>
       <c r="F23" t="n">
-        <v>13.09</v>
+        <v>12.66</v>
       </c>
       <c r="G23" t="n">
-        <v>1245</v>
+        <v>136</v>
       </c>
       <c r="H23" t="n">
-        <v>93.33</v>
+        <v>83.09</v>
       </c>
       <c r="I23" t="n">
-        <v>2.64</v>
+        <v>3.15</v>
       </c>
       <c r="J23" t="n">
-        <v>12.02409638554217</v>
+        <v>12.30882352941176</v>
       </c>
       <c r="K23" t="n">
-        <v>31181.65</v>
+        <v>12906237.4</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -2404,168 +2404,168 @@
         <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>14.45</v>
+        <v>14.6</v>
       </c>
       <c r="O23" t="n">
-        <v>-6.48</v>
+        <v>-8.99</v>
       </c>
       <c r="P23" t="n">
-        <v>7.969999999999999</v>
+        <v>5.609999999999999</v>
       </c>
       <c r="Q23" t="n">
-        <v>8.970000000000001</v>
+        <v>43.74</v>
       </c>
       <c r="R23" t="n">
-        <v>1.228093345064586</v>
+        <v>0.2994072991175627</v>
       </c>
       <c r="S23" t="n">
-        <v>1.685</v>
+        <v>4.98</v>
       </c>
       <c r="T23" t="n">
-        <v>3287.55</v>
+        <v>428.12</v>
       </c>
       <c r="U23" t="n">
-        <v>14970</v>
+        <v>1674</v>
       </c>
       <c r="V23" t="n">
-        <v>0.9557055426127213</v>
+        <v>0.9352458336787991</v>
       </c>
       <c r="W23" t="n">
-        <v>1.001596386456068</v>
+        <v>1.017045381546768</v>
       </c>
       <c r="X23" t="n">
-        <v>333.7325</v>
+        <v>60.30500000000002</v>
       </c>
       <c r="Y23" t="n">
-        <v>318.4416440723548</v>
+        <v>55.45475258363042</v>
       </c>
       <c r="Z23" t="n">
-        <v>6947687.85</v>
+        <v>364155398.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>00881.TW</t>
+          <t>00894.TW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>國泰台灣科技龍頭</t>
+          <t>中信小資高價30</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.954342029673283</v>
+        <v>2.034744485185609</v>
       </c>
       <c r="D24" t="n">
-        <v>1.784470945466316</v>
+        <v>1.739240103387254</v>
       </c>
       <c r="E24" t="n">
-        <v>49.11</v>
+        <v>47.17</v>
       </c>
       <c r="F24" t="n">
-        <v>10.54</v>
+        <v>14.79</v>
       </c>
       <c r="G24" t="n">
-        <v>384</v>
+        <v>243</v>
       </c>
       <c r="H24" t="n">
-        <v>89.58</v>
+        <v>82.72</v>
       </c>
       <c r="I24" t="n">
-        <v>2.52</v>
+        <v>2.88</v>
       </c>
       <c r="J24" t="n">
-        <v>15.328125</v>
+        <v>15.32921810699589</v>
       </c>
       <c r="K24" t="n">
-        <v>17389307.9</v>
+        <v>1225257.35</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>10.9</v>
+        <v>15.7</v>
       </c>
       <c r="O24" t="n">
-        <v>-4.28</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>6.62</v>
+        <v>7.319999999999999</v>
       </c>
       <c r="Q24" t="n">
-        <v>15.81</v>
+        <v>22.58</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1698710842069673</v>
+        <v>0.2955043817983545</v>
       </c>
       <c r="S24" t="n">
-        <v>12.5</v>
+        <v>7.549999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>966.91</v>
+        <v>698.73</v>
       </c>
       <c r="U24" t="n">
-        <v>5886</v>
+        <v>3725</v>
       </c>
       <c r="V24" t="n">
-        <v>0.9426555976774319</v>
+        <v>0.9450633114281138</v>
       </c>
       <c r="W24" t="n">
-        <v>0.999785508398096</v>
+        <v>1.018323180276911</v>
       </c>
       <c r="X24" t="n">
-        <v>52.09749999999999</v>
+        <v>49.91199999999998</v>
       </c>
       <c r="Y24" t="n">
-        <v>49.12053594244068</v>
+        <v>46.32124743264032</v>
       </c>
       <c r="Z24" t="n">
-        <v>796216255.65</v>
+        <v>48592411.35</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>0052.TW</t>
+          <t>00901.TW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>富邦科技</t>
+          <t>永豐智能車供應鏈</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8.166018168201376</v>
+        <v>1.762731962935627</v>
       </c>
       <c r="D25" t="n">
-        <v>4.939555082401423</v>
+        <v>1.704564059090527</v>
       </c>
       <c r="E25" t="n">
-        <v>62.25</v>
+        <v>45.19</v>
       </c>
       <c r="F25" t="n">
-        <v>13.08</v>
+        <v>13.27</v>
       </c>
       <c r="G25" t="n">
-        <v>1111</v>
+        <v>276</v>
       </c>
       <c r="H25" t="n">
-        <v>88.20999999999999</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>2.45</v>
+        <v>2.79</v>
       </c>
       <c r="J25" t="n">
-        <v>14.18091809180918</v>
+        <v>13.22463768115942</v>
       </c>
       <c r="K25" t="n">
-        <v>20574417.55</v>
+        <v>262901.5</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -2576,426 +2576,426 @@
         <v>2</v>
       </c>
       <c r="N25" t="n">
-        <v>12.7</v>
+        <v>15.18</v>
       </c>
       <c r="O25" t="n">
-        <v>-14.18</v>
+        <v>-7.3</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.48</v>
+        <v>7.88</v>
       </c>
       <c r="Q25" t="n">
-        <v>8.050000000000001</v>
+        <v>24.17</v>
       </c>
       <c r="R25" t="n">
-        <v>3.226463085799953</v>
+        <v>0.05816790384510018</v>
       </c>
       <c r="S25" t="n">
-        <v>2.232857285714286</v>
+        <v>4.671</v>
       </c>
       <c r="T25" t="n">
-        <v>2723.42</v>
+        <v>771.28</v>
       </c>
       <c r="U25" t="n">
-        <v>15755</v>
+        <v>3650</v>
       </c>
       <c r="V25" t="n">
-        <v>0.9534750143595625</v>
+        <v>0.9436996199306685</v>
       </c>
       <c r="W25" t="n">
-        <v>1.003416326486596</v>
+        <v>1.014424695644075</v>
       </c>
       <c r="X25" t="n">
-        <v>65.28750000000007</v>
+        <v>47.886</v>
       </c>
       <c r="Y25" t="n">
-        <v>62.03805774016531</v>
+        <v>44.54741706707771</v>
       </c>
       <c r="Z25" t="n">
-        <v>1077808265.25</v>
+        <v>11397189.14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>00735.TW</t>
+          <t>0057.TW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>國泰臺韓科技</t>
+          <t>富邦摩台</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2.823300662446544</v>
+        <v>6.125159123683923</v>
       </c>
       <c r="D26" t="n">
-        <v>2.496991366533118</v>
+        <v>4.892653897730256</v>
       </c>
       <c r="E26" t="n">
-        <v>96</v>
+        <v>321.3</v>
       </c>
       <c r="F26" t="n">
-        <v>12.02</v>
+        <v>13.09</v>
       </c>
       <c r="G26" t="n">
-        <v>498</v>
+        <v>1245</v>
       </c>
       <c r="H26" t="n">
-        <v>86.55</v>
+        <v>93.33</v>
       </c>
       <c r="I26" t="n">
-        <v>2.28</v>
+        <v>2.64</v>
       </c>
       <c r="J26" t="n">
-        <v>13.81124497991968</v>
+        <v>12.02409638554217</v>
       </c>
       <c r="K26" t="n">
-        <v>1834276.5</v>
+        <v>31923.9</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>2</v>
       </c>
       <c r="N26" t="n">
-        <v>21.39</v>
+        <v>14.45</v>
       </c>
       <c r="O26" t="n">
-        <v>-6.04</v>
+        <v>-6.48</v>
       </c>
       <c r="P26" t="n">
-        <v>15.35</v>
+        <v>7.969999999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>14.26</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="R26" t="n">
-        <v>0.3263092959134259</v>
+        <v>1.232505225953667</v>
       </c>
       <c r="S26" t="n">
-        <v>13.37</v>
+        <v>1.685</v>
       </c>
       <c r="T26" t="n">
-        <v>1133.84</v>
+        <v>3287.55</v>
       </c>
       <c r="U26" t="n">
-        <v>6878</v>
+        <v>14970</v>
       </c>
       <c r="V26" t="n">
-        <v>0.9040612124779294</v>
+        <v>0.9633749606464478</v>
       </c>
       <c r="W26" t="n">
-        <v>0.9999451415637474</v>
+        <v>1.011467635586717</v>
       </c>
       <c r="X26" t="n">
-        <v>106.1874999999999</v>
+        <v>333.515</v>
       </c>
       <c r="Y26" t="n">
-        <v>96.00526669880311</v>
+        <v>317.6572227282635</v>
       </c>
       <c r="Z26" t="n">
-        <v>120552192</v>
+        <v>19132772.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>0050.TW</t>
+          <t>00881.TW</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>元大台灣50</t>
+          <t>國泰台灣科技龍頭</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5.464004471271062</v>
+        <v>1.974895240595829</v>
       </c>
       <c r="D27" t="n">
-        <v>5.464004471271062</v>
+        <v>1.806051231841975</v>
       </c>
       <c r="E27" t="n">
-        <v>107.25</v>
+        <v>49.55</v>
       </c>
       <c r="F27" t="n">
-        <v>13.64</v>
+        <v>10.86</v>
       </c>
       <c r="G27" t="n">
-        <v>1695</v>
+        <v>384</v>
       </c>
       <c r="H27" t="n">
-        <v>90.97</v>
+        <v>89.58</v>
       </c>
       <c r="I27" t="n">
-        <v>2.26</v>
+        <v>2.52</v>
       </c>
       <c r="J27" t="n">
-        <v>13.46961651917404</v>
+        <v>15.328125</v>
       </c>
       <c r="K27" t="n">
-        <v>116344424.15</v>
+        <v>16934257.45</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="M27" t="n">
         <v>2</v>
       </c>
       <c r="N27" t="n">
-        <v>13.94</v>
+        <v>10.9</v>
       </c>
       <c r="O27" t="n">
-        <v>-5.91</v>
+        <v>-4.28</v>
       </c>
       <c r="P27" t="n">
-        <v>8.029999999999999</v>
+        <v>6.62</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.04</v>
+        <v>15.81</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>0.1688440087538541</v>
       </c>
       <c r="S27" t="n">
-        <v>4.84625</v>
+        <v>12.5</v>
       </c>
       <c r="T27" t="n">
-        <v>3824.71</v>
+        <v>966.91</v>
       </c>
       <c r="U27" t="n">
-        <v>22831</v>
+        <v>5886</v>
       </c>
       <c r="V27" t="n">
-        <v>0.9559249520923391</v>
+        <v>0.9524267179240751</v>
       </c>
       <c r="W27" t="n">
-        <v>1.001906358072304</v>
+        <v>1.013731151962443</v>
       </c>
       <c r="X27" t="n">
-        <v>112.195</v>
+        <v>52.02499999999999</v>
       </c>
       <c r="Y27" t="n">
-        <v>107.0459321231897</v>
+        <v>48.87883725786474</v>
       </c>
       <c r="Z27" t="n">
-        <v>13201031844</v>
+        <v>437569856.25</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>0053.TW</t>
+          <t>0052.TW</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>元大科技市值</t>
+          <t>富邦科技</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6.631486744757602</v>
+        <v>8.257010428881589</v>
       </c>
       <c r="D28" t="n">
-        <v>4.902928246727704</v>
+        <v>4.986669014345297</v>
       </c>
       <c r="E28" t="n">
-        <v>239.25</v>
+        <v>62.9</v>
       </c>
       <c r="F28" t="n">
-        <v>10.61</v>
+        <v>14.53</v>
       </c>
       <c r="G28" t="n">
-        <v>1190</v>
+        <v>1111</v>
       </c>
       <c r="H28" t="n">
-        <v>89.16</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="J28" t="n">
-        <v>13.83697478991597</v>
+        <v>14.18091809180918</v>
       </c>
       <c r="K28" t="n">
-        <v>432151.3</v>
+        <v>20331959.4</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>2</v>
       </c>
       <c r="N28" t="n">
-        <v>11.49</v>
+        <v>12.7</v>
       </c>
       <c r="O28" t="n">
-        <v>-7.24</v>
+        <v>-14.18</v>
       </c>
       <c r="P28" t="n">
-        <v>4.25</v>
+        <v>-1.48</v>
       </c>
       <c r="Q28" t="n">
-        <v>7.58</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="R28" t="n">
-        <v>1.728558498029898</v>
+        <v>3.270341414536292</v>
       </c>
       <c r="S28" t="n">
-        <v>18.91</v>
+        <v>2.232857285714286</v>
       </c>
       <c r="T28" t="n">
-        <v>2598</v>
+        <v>2723.42</v>
       </c>
       <c r="U28" t="n">
-        <v>16466</v>
+        <v>15755</v>
       </c>
       <c r="V28" t="n">
-        <v>0.9477781189030726</v>
+        <v>0.9640954899030528</v>
       </c>
       <c r="W28" t="n">
-        <v>1.002207868074815</v>
+        <v>1.016341360229043</v>
       </c>
       <c r="X28" t="n">
-        <v>252.4325000000001</v>
+        <v>65.24250000000008</v>
       </c>
       <c r="Y28" t="n">
-        <v>238.7229312613417</v>
+        <v>61.88865519142589</v>
       </c>
       <c r="Z28" t="n">
-        <v>137813024.25</v>
+        <v>740685994.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>00892.TW</t>
+          <t>00735.TW</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>富邦台灣半導體</t>
+          <t>國泰臺韓科技</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.798486039015612</v>
+        <v>2.901191117040621</v>
       </c>
       <c r="D29" t="n">
-        <v>1.734895051074697</v>
+        <v>2.524333611187225</v>
       </c>
       <c r="E29" t="n">
-        <v>40.11</v>
+        <v>98.2</v>
       </c>
       <c r="F29" t="n">
-        <v>15.02</v>
+        <v>14.21</v>
       </c>
       <c r="G29" t="n">
-        <v>241</v>
+        <v>498</v>
       </c>
       <c r="H29" t="n">
-        <v>75.09999999999999</v>
+        <v>86.55</v>
       </c>
       <c r="I29" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="J29" t="n">
-        <v>15.85892116182573</v>
+        <v>13.81124497991968</v>
       </c>
       <c r="K29" t="n">
-        <v>4528127.05</v>
+        <v>1857374.55</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>2</v>
       </c>
       <c r="N29" t="n">
-        <v>12.37</v>
+        <v>21.39</v>
       </c>
       <c r="O29" t="n">
-        <v>-7.43</v>
+        <v>-6.04</v>
       </c>
       <c r="P29" t="n">
-        <v>4.94</v>
+        <v>15.35</v>
       </c>
       <c r="Q29" t="n">
-        <v>18.86</v>
+        <v>14.26</v>
       </c>
       <c r="R29" t="n">
-        <v>0.06359098794091445</v>
+        <v>0.3768575058533963</v>
       </c>
       <c r="S29" t="n">
-        <v>4.937</v>
+        <v>13.37</v>
       </c>
       <c r="T29" t="n">
-        <v>510.5</v>
+        <v>1133.84</v>
       </c>
       <c r="U29" t="n">
-        <v>3822</v>
+        <v>6878</v>
       </c>
       <c r="V29" t="n">
-        <v>0.9364275208367377</v>
+        <v>0.9278374867131227</v>
       </c>
       <c r="W29" t="n">
-        <v>0.9895158711182126</v>
+        <v>1.032829147663534</v>
       </c>
       <c r="X29" t="n">
-        <v>42.83300000000001</v>
+        <v>105.8374999999999</v>
       </c>
       <c r="Y29" t="n">
-        <v>40.53497389048776</v>
+        <v>95.07864899257346</v>
       </c>
       <c r="Z29" t="n">
-        <v>183572880.96</v>
+        <v>142472095.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>006208.TW</t>
+          <t>0050.TW</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>富邦台50</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4.055751188242493</v>
+        <v>5.515191281060264</v>
       </c>
       <c r="D30" t="n">
-        <v>3.805476054195616</v>
+        <v>5.515191281060264</v>
       </c>
       <c r="E30" t="n">
-        <v>245.3</v>
+        <v>108.15</v>
       </c>
       <c r="F30" t="n">
-        <v>12.22</v>
+        <v>13.41</v>
       </c>
       <c r="G30" t="n">
-        <v>895</v>
+        <v>1695</v>
       </c>
       <c r="H30" t="n">
-        <v>88.48999999999999</v>
+        <v>90.97</v>
       </c>
       <c r="I30" t="n">
-        <v>1.95</v>
+        <v>2.26</v>
       </c>
       <c r="J30" t="n">
-        <v>13.86703910614525</v>
+        <v>13.46961651917404</v>
       </c>
       <c r="K30" t="n">
-        <v>3266532</v>
+        <v>116172962.85</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -3006,125 +3006,383 @@
         <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>11.21</v>
+        <v>13.94</v>
       </c>
       <c r="O30" t="n">
-        <v>-6.25</v>
+        <v>-5.91</v>
       </c>
       <c r="P30" t="n">
-        <v>4.960000000000001</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="Q30" t="n">
-        <v>8.949999999999999</v>
+        <v>6.04</v>
       </c>
       <c r="R30" t="n">
-        <v>0.2502751340468778</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>28.764</v>
+        <v>4.84625</v>
       </c>
       <c r="T30" t="n">
-        <v>1745.92</v>
+        <v>3824.71</v>
       </c>
       <c r="U30" t="n">
-        <v>12411</v>
+        <v>22831</v>
       </c>
       <c r="V30" t="n">
-        <v>0.9550135290338907</v>
+        <v>0.9646775488359643</v>
       </c>
       <c r="W30" t="n">
-        <v>0.9998740510571562</v>
+        <v>1.013050089400627</v>
       </c>
       <c r="X30" t="n">
-        <v>256.855</v>
+        <v>112.11</v>
       </c>
       <c r="Y30" t="n">
-        <v>245.3308991673971</v>
+        <v>106.7568140327465</v>
       </c>
       <c r="Z30" t="n">
-        <v>946543770.7</v>
+        <v>9009093887.85</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>009823.TWO</t>
+          <t>0053.TW</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>群益S&amp;P500</t>
+          <t>元大科技市值</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.02692797628712951</v>
+        <v>6.692837544939853</v>
       </c>
       <c r="D31" t="n">
-        <v>0.007552616385237076</v>
+        <v>4.949576222723458</v>
       </c>
       <c r="E31" t="n">
-        <v>10.71</v>
+        <v>241.35</v>
       </c>
       <c r="F31" t="n">
-        <v>76.12</v>
+        <v>10.43</v>
       </c>
       <c r="G31" t="n">
-        <v>15</v>
+        <v>1190</v>
       </c>
       <c r="H31" t="n">
-        <v>100</v>
+        <v>89.16</v>
       </c>
       <c r="I31" t="n">
-        <v>1.31</v>
+        <v>2.18</v>
       </c>
       <c r="J31" t="n">
-        <v>16.93333333333333</v>
+        <v>13.83697478991597</v>
       </c>
       <c r="K31" t="n">
-        <v>3344982.85</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
+        <v>451801</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="M31" t="n">
         <v>2</v>
       </c>
       <c r="N31" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-7.24</v>
+      </c>
+      <c r="P31" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.743261322216395</v>
+      </c>
+      <c r="S31" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2598</v>
+      </c>
+      <c r="U31" t="n">
+        <v>16466</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.9571303934010147</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.014878710228875</v>
+      </c>
+      <c r="X31" t="n">
+        <v>252.1600000000001</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>237.8116690866151</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>117009617.55</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>00892.TW</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>富邦台灣半導體</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1.835517372302171</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.756006070252821</v>
+      </c>
+      <c r="E32" t="n">
+        <v>40.71</v>
+      </c>
+      <c r="F32" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="G32" t="n">
+        <v>241</v>
+      </c>
+      <c r="H32" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="J32" t="n">
+        <v>15.85892116182573</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4490782.3</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>2</v>
+      </c>
+      <c r="N32" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="O32" t="n">
+        <v>-7.43</v>
+      </c>
+      <c r="P32" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.07951130204935009</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4.937</v>
+      </c>
+      <c r="T32" t="n">
+        <v>510.5</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3822</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.9526483906069008</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.011283929593973</v>
+      </c>
+      <c r="X32" t="n">
+        <v>42.73350000000001</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>40.25575687368526</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>123125237.37</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>006208.TW</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>富邦台50</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>4.097989821831891</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3.843302605799952</v>
+      </c>
+      <c r="E33" t="n">
+        <v>247.6</v>
+      </c>
+      <c r="F33" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="G33" t="n">
+        <v>895</v>
+      </c>
+      <c r="H33" t="n">
+        <v>88.48999999999999</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="J33" t="n">
+        <v>13.86703910614525</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3156014.6</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>2</v>
+      </c>
+      <c r="N33" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="O33" t="n">
+        <v>-6.25</v>
+      </c>
+      <c r="P33" t="n">
+        <v>4.960000000000001</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.2546872160319387</v>
+      </c>
+      <c r="S33" t="n">
+        <v>28.764</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1745.92</v>
+      </c>
+      <c r="U33" t="n">
+        <v>12411</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0.9646440050647703</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.011852951358082</v>
+      </c>
+      <c r="X33" t="n">
+        <v>256.6750000000001</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>244.6995876897704</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>371970222.8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>009823.TWO</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>群益S&amp;P500</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.03038358013963127</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.01579937295296352</v>
+      </c>
+      <c r="E34" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="F34" t="n">
+        <v>74.56</v>
+      </c>
+      <c r="G34" t="n">
+        <v>15</v>
+      </c>
+      <c r="H34" t="n">
+        <v>100</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="J34" t="n">
+        <v>16.93333333333333</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3341336.85</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="n">
+        <v>2</v>
+      </c>
+      <c r="N34" t="n">
         <v>3.64</v>
       </c>
-      <c r="O31" t="n">
+      <c r="O34" t="n">
         <v>0.45</v>
       </c>
-      <c r="P31" t="n">
+      <c r="P34" t="n">
         <v>4.09</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="Q34" t="n">
         <v>29.52</v>
       </c>
-      <c r="R31" t="n">
-        <v>0.01937535990189243</v>
-      </c>
-      <c r="S31" t="n">
+      <c r="R34" t="n">
+        <v>0.01458420718666775</v>
+      </c>
+      <c r="S34" t="n">
         <v>0</v>
       </c>
-      <c r="T31" t="n">
+      <c r="T34" t="n">
         <v>19.72</v>
       </c>
-      <c r="U31" t="n">
+      <c r="U34" t="n">
         <v>254</v>
       </c>
-      <c r="V31" t="n">
-        <v>1.012861736334405</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.0357619518573</v>
-      </c>
-      <c r="X31" t="n">
-        <v>10.574</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>10.34021377286076</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>32758923.33</v>
+      <c r="V34" t="n">
+        <v>1.014916918429003</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.037419247862923</v>
+      </c>
+      <c r="X34" t="n">
+        <v>10.592</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>10.36225231230761</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>34560379.25</v>
       </c>
     </row>
   </sheetData>

--- a/ETF動態清單.xlsx
+++ b/ETF動態清單.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z34"/>
+  <dimension ref="A1:Z30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,16 +567,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.6832462980186436</v>
+        <v>0.6430343840630024</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5328629403948486</v>
+        <v>0.5138216598021295</v>
       </c>
       <c r="E2" t="n">
-        <v>28.88</v>
+        <v>28.19</v>
       </c>
       <c r="F2" t="n">
-        <v>13.08</v>
+        <v>9.27</v>
       </c>
       <c r="G2" t="n">
         <v>41</v>
@@ -591,7 +591,7 @@
         <v>8.439024390243903</v>
       </c>
       <c r="K2" t="n">
-        <v>165691817.1</v>
+        <v>170395238.2</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         <v>386.28</v>
       </c>
       <c r="R2" t="n">
-        <v>0.150383357623795</v>
+        <v>0.1292127242608729</v>
       </c>
       <c r="S2" t="n">
         <v>1.67</v>
@@ -626,19 +626,19 @@
         <v>346</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9397217928902628</v>
+        <v>0.9193340616694116</v>
       </c>
       <c r="W2" t="n">
-        <v>1.020750691758957</v>
+        <v>1.005843304452886</v>
       </c>
       <c r="X2" t="n">
-        <v>30.7325</v>
+        <v>30.6635</v>
       </c>
       <c r="Y2" t="n">
-        <v>28.29290269716496</v>
+        <v>28.02623418101246</v>
       </c>
       <c r="Z2" t="n">
-        <v>4386586116.88</v>
+        <v>6775475802.700001</v>
       </c>
     </row>
     <row r="3">
@@ -653,16 +653,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2227059644355847</v>
+        <v>0.1850698488098292</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1931845860618198</v>
+        <v>0.1785476731583375</v>
       </c>
       <c r="E3" t="n">
-        <v>17.49</v>
+        <v>16.93</v>
       </c>
       <c r="F3" t="n">
-        <v>18.78</v>
+        <v>12.72</v>
       </c>
       <c r="G3" t="n">
         <v>33</v>
@@ -677,7 +677,7 @@
         <v>10.27272727272727</v>
       </c>
       <c r="K3" t="n">
-        <v>52782795.5</v>
+        <v>55088239.9</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         <v>317.42</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02952137837376489</v>
+        <v>0.006522175651491713</v>
       </c>
       <c r="S3" t="n">
         <v>1.32</v>
@@ -712,19 +712,19 @@
         <v>339</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9227360257458656</v>
+        <v>0.8965973785250898</v>
       </c>
       <c r="W3" t="n">
-        <v>1.019557203799198</v>
+        <v>1.002376884074319</v>
       </c>
       <c r="X3" t="n">
-        <v>18.95449999999999</v>
+        <v>18.88249999999999</v>
       </c>
       <c r="Y3" t="n">
-        <v>17.15450583334277</v>
+        <v>16.88985477317209</v>
       </c>
       <c r="Z3" t="n">
-        <v>664882944.66</v>
+        <v>1279678276.83</v>
       </c>
     </row>
     <row r="4">
@@ -739,16 +739,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.16459921302747</v>
+        <v>1.099679462078313</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8762073867875242</v>
+        <v>0.8533458910309029</v>
       </c>
       <c r="E4" t="n">
-        <v>35.18</v>
+        <v>34.08</v>
       </c>
       <c r="F4" t="n">
-        <v>15.62</v>
+        <v>11.33</v>
       </c>
       <c r="G4" t="n">
         <v>66</v>
@@ -763,7 +763,7 @@
         <v>10.33333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>12873934.75</v>
+        <v>12763021.65</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         <v>159.78</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2883918262399456</v>
+        <v>0.2463335710474102</v>
       </c>
       <c r="S4" t="n">
         <v>2.78</v>
@@ -798,19 +798,19 @@
         <v>682</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8999513954618709</v>
+        <v>0.8781241947951556</v>
       </c>
       <c r="W4" t="n">
-        <v>1.017798680186523</v>
+        <v>1.008338974466148</v>
       </c>
       <c r="X4" t="n">
-        <v>39.09100000000001</v>
+        <v>38.81000000000001</v>
       </c>
       <c r="Y4" t="n">
-        <v>34.56479231585647</v>
+        <v>33.79815802324136</v>
       </c>
       <c r="Z4" t="n">
-        <v>214261995.82</v>
+        <v>292035098.4</v>
       </c>
     </row>
     <row r="5">
@@ -825,16 +825,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6019671277034271</v>
+        <v>0.5587911331864652</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5751925578179764</v>
+        <v>0.5556268839929315</v>
       </c>
       <c r="E5" t="n">
-        <v>24.42</v>
+        <v>23.75</v>
       </c>
       <c r="F5" t="n">
-        <v>19.64</v>
+        <v>13.1</v>
       </c>
       <c r="G5" t="n">
         <v>40</v>
@@ -849,7 +849,7 @@
         <v>9.824999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>8602203.449999999</v>
+        <v>8725865.949999999</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>246.15</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02677456988545068</v>
+        <v>0.003164249193533752</v>
       </c>
       <c r="S5" t="n">
         <v>1.814</v>
@@ -884,19 +884,19 @@
         <v>393</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9558478158759988</v>
+        <v>0.9319755920497582</v>
       </c>
       <c r="W5" t="n">
-        <v>1.024447514235748</v>
+        <v>1.0058729197188</v>
       </c>
       <c r="X5" t="n">
-        <v>25.54799999999998</v>
+        <v>25.48349999999999</v>
       </c>
       <c r="Y5" t="n">
-        <v>23.83723876592902</v>
+        <v>23.61133253954139</v>
       </c>
       <c r="Z5" t="n">
-        <v>98552819.64</v>
+        <v>154871375</v>
       </c>
     </row>
     <row r="6">
@@ -911,16 +911,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.4659582618772986</v>
+        <v>0.4438326671170423</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4486571409991897</v>
+        <v>0.4306666972430557</v>
       </c>
       <c r="E6" t="n">
-        <v>20.55</v>
+        <v>20.23</v>
       </c>
       <c r="F6" t="n">
-        <v>8.300000000000001</v>
+        <v>5.61</v>
       </c>
       <c r="G6" t="n">
         <v>37</v>
@@ -935,7 +935,7 @@
         <v>9.972972972972974</v>
       </c>
       <c r="K6" t="n">
-        <v>58254585.8</v>
+        <v>59382249.25</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         <v>252.13</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01730112087810887</v>
+        <v>0.01316596987398655</v>
       </c>
       <c r="S6" t="n">
         <v>2.15</v>
@@ -970,488 +970,488 @@
         <v>369</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8825045091471269</v>
+        <v>0.8744137796892221</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9878100531050347</v>
+        <v>0.995676106844684</v>
       </c>
       <c r="X6" t="n">
-        <v>23.286</v>
+        <v>23.1355</v>
       </c>
       <c r="Y6" t="n">
-        <v>20.80359471479777</v>
+        <v>20.31785222215409</v>
       </c>
       <c r="Z6" t="n">
-        <v>334689136.8</v>
+        <v>488756779.77</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>00410A.TW</t>
+          <t>009816.TW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>主動永豐科技趨勢</t>
+          <t>凱基台灣TOP50</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.007221798312800898</v>
+        <v>0.1639800557652396</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0006817425719989334</v>
+        <v>0.1296347781660614</v>
       </c>
       <c r="E7" t="n">
-        <v>11.88</v>
+        <v>15.93</v>
       </c>
       <c r="F7" t="n">
-        <v>16.62</v>
+        <v>10.14</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="H7" t="n">
         <v>100</v>
       </c>
       <c r="I7" t="n">
-        <v>5.53</v>
+        <v>5.32</v>
       </c>
       <c r="J7" t="n">
-        <v>7.6</v>
+        <v>10.54166666666667</v>
       </c>
       <c r="K7" t="n">
-        <v>5843770.65</v>
+        <v>133722143.8</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>2</v>
       </c>
       <c r="N7" t="n">
-        <v>5.92</v>
+        <v>8.99</v>
       </c>
       <c r="O7" t="n">
-        <v>4.92</v>
+        <v>0.64</v>
       </c>
       <c r="P7" t="n">
-        <v>10.84</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>942.39</v>
+        <v>227.93</v>
       </c>
       <c r="R7" t="n">
-        <v>0.006540055740801964</v>
+        <v>0.03434527759917816</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>27.64</v>
+        <v>127.78</v>
       </c>
       <c r="U7" t="n">
-        <v>38</v>
+        <v>253</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9557137685531553</v>
+        <v>0.9646652738668362</v>
       </c>
       <c r="W7" t="n">
-        <v>1.033095053142372</v>
+        <v>1.006949036043636</v>
       </c>
       <c r="X7" t="n">
-        <v>12.4305</v>
+        <v>16.5135</v>
       </c>
       <c r="Y7" t="n">
-        <v>11.49942588909368</v>
+        <v>15.82006579259457</v>
       </c>
       <c r="Z7" t="n">
-        <v>85406496.12</v>
+        <v>1898753522.31</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>009816.TW</t>
+          <t>009824.TW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>凱基台灣TOP50</t>
+          <t>群益美國科技巨頭</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.1759082972776618</v>
+        <v>0.009240732374837135</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1435610197768122</v>
+        <v>0.004023674744812133</v>
       </c>
       <c r="E8" t="n">
-        <v>16.08</v>
+        <v>10.26</v>
       </c>
       <c r="F8" t="n">
-        <v>14.23</v>
+        <v>18.46</v>
       </c>
       <c r="G8" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
         <v>100</v>
       </c>
       <c r="I8" t="n">
-        <v>5.32</v>
+        <v>5.26</v>
       </c>
       <c r="J8" t="n">
-        <v>10.54166666666667</v>
+        <v>5.75</v>
       </c>
       <c r="K8" t="n">
-        <v>133555137</v>
+        <v>3791910.1</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>8.99</v>
+        <v>7.35</v>
       </c>
       <c r="O8" t="n">
-        <v>0.64</v>
+        <v>1.39</v>
       </c>
       <c r="P8" t="n">
-        <v>9.630000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="Q8" t="n">
-        <v>227.93</v>
+        <v>1975.8</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03234727750084954</v>
+        <v>0.005217057630025002</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>127.78</v>
+        <v>21.06</v>
       </c>
       <c r="U8" t="n">
-        <v>253</v>
+        <v>23</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9721592454883466</v>
+        <v>0.9697084258777936</v>
       </c>
       <c r="W8" t="n">
-        <v>1.011319699585037</v>
+        <v>1.00585626510936</v>
       </c>
       <c r="X8" t="n">
-        <v>16.5405</v>
+        <v>10.5805</v>
       </c>
       <c r="Y8" t="n">
-        <v>15.90001658881748</v>
+        <v>10.20026454662933</v>
       </c>
       <c r="Z8" t="n">
-        <v>1648663715.04</v>
+        <v>22495563</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>009824.TW</t>
+          <t>009804.TW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>群益美國科技巨頭</t>
+          <t>聯邦台精彩50</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.01820880510014233</v>
+        <v>0.6077251516304043</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01579937295296352</v>
+        <v>0.5916425396469043</v>
       </c>
       <c r="E9" t="n">
-        <v>10.35</v>
+        <v>22.78</v>
       </c>
       <c r="F9" t="n">
-        <v>23.08</v>
+        <v>10.41</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="H9" t="n">
         <v>100</v>
       </c>
       <c r="I9" t="n">
-        <v>5.26</v>
+        <v>4.12</v>
       </c>
       <c r="J9" t="n">
-        <v>5.75</v>
+        <v>8.82258064516129</v>
       </c>
       <c r="K9" t="n">
-        <v>4322912.3</v>
+        <v>1096973.7</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>7.35</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>1.39</v>
+        <v>0.76</v>
       </c>
       <c r="P9" t="n">
-        <v>8.74</v>
+        <v>10.39</v>
       </c>
       <c r="Q9" t="n">
-        <v>1975.8</v>
+        <v>133.05</v>
       </c>
       <c r="R9" t="n">
-        <v>0.002409432147178814</v>
+        <v>0.01608261198350003</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.786</v>
       </c>
       <c r="T9" t="n">
-        <v>21.06</v>
+        <v>255.36</v>
       </c>
       <c r="U9" t="n">
-        <v>23</v>
+        <v>547</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9777987718469527</v>
+        <v>0.9521620096553741</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01290365550819</v>
+        <v>1.00531494679553</v>
       </c>
       <c r="X9" t="n">
-        <v>10.585</v>
+        <v>23.9245</v>
       </c>
       <c r="Y9" t="n">
-        <v>10.21814853141905</v>
+        <v>22.6595656143499</v>
       </c>
       <c r="Z9" t="n">
-        <v>24765366.15</v>
+        <v>15222484.42</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>009804.TW</t>
+          <t>00830.TW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>聯邦台精彩50</t>
+          <t>國泰費城半導體</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.6300843661102979</v>
+        <v>2.366231255193935</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6116653473279499</v>
+        <v>2.237111163366611</v>
       </c>
       <c r="E10" t="n">
-        <v>23.1</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>14.76</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>62</v>
+        <v>495</v>
       </c>
       <c r="H10" t="n">
-        <v>100</v>
+        <v>97.17</v>
       </c>
       <c r="I10" t="n">
-        <v>4.12</v>
+        <v>3.93</v>
       </c>
       <c r="J10" t="n">
-        <v>8.82258064516129</v>
+        <v>12.29090909090909</v>
       </c>
       <c r="K10" t="n">
-        <v>1184276.45</v>
+        <v>10754959.45</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>9.630000000000001</v>
+        <v>13.29</v>
       </c>
       <c r="O10" t="n">
-        <v>0.76</v>
+        <v>-12.33</v>
       </c>
       <c r="P10" t="n">
-        <v>10.39</v>
+        <v>0.9599999999999991</v>
       </c>
       <c r="Q10" t="n">
-        <v>133.05</v>
+        <v>19.85</v>
       </c>
       <c r="R10" t="n">
-        <v>0.01841901878234808</v>
+        <v>0.1291200918273243</v>
       </c>
       <c r="S10" t="n">
-        <v>2.786</v>
+        <v>17.71</v>
       </c>
       <c r="T10" t="n">
-        <v>255.36</v>
+        <v>1946.3</v>
       </c>
       <c r="U10" t="n">
-        <v>547</v>
+        <v>6084</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9635237439779767</v>
+        <v>0.9252852200268781</v>
       </c>
       <c r="W10" t="n">
-        <v>1.012258194532464</v>
+        <v>1.015656761423235</v>
       </c>
       <c r="X10" t="n">
-        <v>23.9745</v>
+        <v>87.43249999999999</v>
       </c>
       <c r="Y10" t="n">
-        <v>22.82026475534664</v>
+        <v>79.65289364749088</v>
       </c>
       <c r="Z10" t="n">
-        <v>11465846.7</v>
+        <v>1038736584</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>00830.TW</t>
+          <t>009818.TW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>國泰費城半導體</t>
+          <t>華南永昌NASDAQxT</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.427245966666353</v>
+        <v>0.08969681154352349</v>
       </c>
       <c r="D11" t="n">
-        <v>2.275276692020235</v>
+        <v>0.07989367249948232</v>
       </c>
       <c r="E11" t="n">
-        <v>82.59999999999999</v>
+        <v>20.66</v>
       </c>
       <c r="F11" t="n">
-        <v>14.29</v>
+        <v>17.38</v>
       </c>
       <c r="G11" t="n">
-        <v>495</v>
+        <v>21</v>
       </c>
       <c r="H11" t="n">
-        <v>97.17</v>
+        <v>100</v>
       </c>
       <c r="I11" t="n">
-        <v>3.93</v>
+        <v>3.81</v>
       </c>
       <c r="J11" t="n">
-        <v>12.29090909090909</v>
+        <v>8.714285714285714</v>
       </c>
       <c r="K11" t="n">
-        <v>10553768.95</v>
+        <v>157366.45</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>13.29</v>
+        <v>7.21</v>
       </c>
       <c r="O11" t="n">
-        <v>-12.33</v>
+        <v>1.65</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9599999999999991</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>19.85</v>
+        <v>222.85</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1519692746461176</v>
+        <v>0.009803139044041176</v>
       </c>
       <c r="S11" t="n">
-        <v>17.71</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1946.3</v>
+        <v>79.97</v>
       </c>
       <c r="U11" t="n">
-        <v>6084</v>
+        <v>183</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9426264585889134</v>
+        <v>0.9741147626007827</v>
       </c>
       <c r="W11" t="n">
-        <v>1.028230337748993</v>
+        <v>1.004303207511007</v>
       </c>
       <c r="X11" t="n">
-        <v>87.62749999999998</v>
+        <v>21.209</v>
       </c>
       <c r="Y11" t="n">
-        <v>80.33219500294879</v>
+        <v>20.57147666709367</v>
       </c>
       <c r="Z11" t="n">
-        <v>648362339.8</v>
+        <v>1737485.34</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>009818.TW</t>
+          <t>00663L.TW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>華南永昌NASDAQxT</t>
+          <t>國泰臺灣加權正2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.1035089655468708</v>
+        <v>11.25922964735046</v>
       </c>
       <c r="D12" t="n">
-        <v>0.09303632433434506</v>
+        <v>2.911450387831949</v>
       </c>
       <c r="E12" t="n">
-        <v>20.91</v>
+        <v>102.8</v>
       </c>
       <c r="F12" t="n">
-        <v>24.47</v>
+        <v>10.54</v>
       </c>
       <c r="G12" t="n">
-        <v>21</v>
+        <v>564</v>
       </c>
       <c r="H12" t="n">
-        <v>100</v>
+        <v>89.89</v>
       </c>
       <c r="I12" t="n">
-        <v>3.81</v>
+        <v>3.76</v>
       </c>
       <c r="J12" t="n">
-        <v>8.714285714285714</v>
+        <v>11.9113475177305</v>
       </c>
       <c r="K12" t="n">
-        <v>167194.3</v>
+        <v>5518691.55</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1462,512 +1462,508 @@
         <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>7.21</v>
+        <v>15.99</v>
       </c>
       <c r="O12" t="n">
-        <v>1.65</v>
+        <v>-24.46</v>
       </c>
       <c r="P12" t="n">
-        <v>8.859999999999999</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>222.85</v>
+        <v>18.35</v>
       </c>
       <c r="R12" t="n">
-        <v>0.01047264121252578</v>
+        <v>8.347779259518511</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>79.97</v>
+        <v>2121.97</v>
       </c>
       <c r="U12" t="n">
-        <v>183</v>
+        <v>6718</v>
       </c>
       <c r="V12" t="n">
-        <v>0.9861812007734755</v>
+        <v>0.9141434351518379</v>
       </c>
       <c r="W12" t="n">
-        <v>1.017862113287314</v>
+        <v>1.014213044109562</v>
       </c>
       <c r="X12" t="n">
-        <v>21.203</v>
+        <v>112.4550000000001</v>
       </c>
       <c r="Y12" t="n">
-        <v>20.54305757826913</v>
+        <v>101.3593747359602</v>
       </c>
       <c r="Z12" t="n">
-        <v>7556832.18</v>
+        <v>548819182.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>00400A.TW</t>
+          <t>00631L.TW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>主動國泰動能高息</t>
+          <t>元大台灣50正2</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.07705374132130549</v>
+        <v>15.09593933491448</v>
       </c>
       <c r="D13" t="n">
-        <v>0.06379181116397814</v>
+        <v>3.328222133845613</v>
       </c>
       <c r="E13" t="n">
-        <v>14.84</v>
+        <v>35.61</v>
       </c>
       <c r="F13" t="n">
-        <v>14.47</v>
+        <v>9.58</v>
       </c>
       <c r="G13" t="n">
-        <v>16</v>
+        <v>644</v>
       </c>
       <c r="H13" t="n">
-        <v>68.75</v>
+        <v>89.44</v>
       </c>
       <c r="I13" t="n">
-        <v>3.77</v>
+        <v>3.74</v>
       </c>
       <c r="J13" t="n">
-        <v>13.1875</v>
+        <v>12.68167701863354</v>
       </c>
       <c r="K13" t="n">
-        <v>37319182.4</v>
+        <v>194225595.25</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>2</v>
       </c>
       <c r="N13" t="n">
-        <v>13.12</v>
+        <v>17.37</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.83</v>
+        <v>-12.43</v>
       </c>
       <c r="P13" t="n">
-        <v>12.29</v>
+        <v>4.940000000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>126.3</v>
+        <v>15.49</v>
       </c>
       <c r="R13" t="n">
-        <v>0.01326193015732735</v>
+        <v>11.76771720106886</v>
       </c>
       <c r="S13" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>60.34</v>
+        <v>2407.1</v>
       </c>
       <c r="U13" t="n">
-        <v>211</v>
+        <v>8167</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9510077221314361</v>
+        <v>0.9156713251648906</v>
       </c>
       <c r="W13" t="n">
-        <v>1.025594155163499</v>
+        <v>1.014355095014336</v>
       </c>
       <c r="X13" t="n">
-        <v>15.60450000000001</v>
+        <v>38.88949999999998</v>
       </c>
       <c r="Y13" t="n">
-        <v>14.4696612449339</v>
+        <v>35.1060493263424</v>
       </c>
       <c r="Z13" t="n">
-        <v>328560538.32</v>
+        <v>7874153957.07</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>00663L.TW</t>
+          <t>00904.TW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>國泰臺灣加權正2</t>
+          <t>台新臺灣半導體30</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11.6156931381423</v>
+        <v>1.701041216751999</v>
       </c>
       <c r="D14" t="n">
-        <v>2.95707576482805</v>
+        <v>1.656230220638771</v>
       </c>
       <c r="E14" t="n">
-        <v>105.75</v>
+        <v>37.6</v>
       </c>
       <c r="F14" t="n">
-        <v>15.35</v>
+        <v>7.42</v>
       </c>
       <c r="G14" t="n">
-        <v>564</v>
+        <v>239</v>
       </c>
       <c r="H14" t="n">
-        <v>89.89</v>
+        <v>99.16</v>
       </c>
       <c r="I14" t="n">
-        <v>3.76</v>
+        <v>3.55</v>
       </c>
       <c r="J14" t="n">
-        <v>11.9113475177305</v>
+        <v>10.78242677824268</v>
       </c>
       <c r="K14" t="n">
-        <v>5562151.75</v>
+        <v>4025045</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>15.99</v>
+        <v>11.85</v>
       </c>
       <c r="O14" t="n">
-        <v>-24.46</v>
+        <v>-12.45</v>
       </c>
       <c r="P14" t="n">
-        <v>-8.470000000000001</v>
+        <v>-0.5999999999999996</v>
       </c>
       <c r="Q14" t="n">
-        <v>18.35</v>
+        <v>37.53</v>
       </c>
       <c r="R14" t="n">
-        <v>8.658617373314254</v>
+        <v>0.04481099611322836</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>7.050000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>2121.97</v>
+        <v>848.62</v>
       </c>
       <c r="U14" t="n">
-        <v>6718</v>
+        <v>2577</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9368770764119598</v>
+        <v>0.8894461068991213</v>
       </c>
       <c r="W14" t="n">
-        <v>1.029967797730523</v>
+        <v>1.007834521042251</v>
       </c>
       <c r="X14" t="n">
-        <v>112.875</v>
+        <v>42.2735</v>
       </c>
       <c r="Y14" t="n">
-        <v>102.6731129196605</v>
+        <v>37.30771194572301</v>
       </c>
       <c r="Z14" t="n">
-        <v>463915944</v>
+        <v>60082882.40000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>00631L.TW</t>
+          <t>00685L.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>群益臺灣加權正2</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>15.55327694858688</v>
+        <v>10.19552719656999</v>
       </c>
       <c r="D15" t="n">
-        <v>3.37845891075097</v>
+        <v>2.742863585316234</v>
       </c>
       <c r="E15" t="n">
-        <v>36.61</v>
+        <v>11.78</v>
       </c>
       <c r="F15" t="n">
-        <v>14.19</v>
+        <v>10.9</v>
       </c>
       <c r="G15" t="n">
-        <v>644</v>
+        <v>514</v>
       </c>
       <c r="H15" t="n">
-        <v>89.44</v>
+        <v>88.52</v>
       </c>
       <c r="I15" t="n">
-        <v>3.74</v>
+        <v>3.46</v>
       </c>
       <c r="J15" t="n">
-        <v>12.68167701863354</v>
+        <v>12.18093385214008</v>
       </c>
       <c r="K15" t="n">
-        <v>194017571.1</v>
+        <v>264409179.35</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>17.37</v>
+        <v>15.89</v>
       </c>
       <c r="O15" t="n">
-        <v>-12.43</v>
+        <v>-18.5</v>
       </c>
       <c r="P15" t="n">
-        <v>4.940000000000001</v>
+        <v>-2.609999999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>15.49</v>
+        <v>18.65</v>
       </c>
       <c r="R15" t="n">
-        <v>12.17481803783591</v>
+        <v>7.452663611253757</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2407.1</v>
+        <v>1777.84</v>
       </c>
       <c r="U15" t="n">
-        <v>8167</v>
+        <v>6261</v>
       </c>
       <c r="V15" t="n">
-        <v>0.937960365345939</v>
+        <v>0.9150580650172833</v>
       </c>
       <c r="W15" t="n">
-        <v>1.029819691485076</v>
+        <v>1.015136195630888</v>
       </c>
       <c r="X15" t="n">
-        <v>39.03149999999998</v>
+        <v>12.8735</v>
       </c>
       <c r="Y15" t="n">
-        <v>35.549912574701</v>
+        <v>11.604354224291</v>
       </c>
       <c r="Z15" t="n">
-        <v>5307505425.39</v>
+        <v>4079711821.96</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>00904.TW</t>
+          <t>009809.TW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>台新臺灣半導體30</t>
+          <t>富邦淨零ESG50</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.757070302017163</v>
+        <v>0.3373099687703147</v>
       </c>
       <c r="D16" t="n">
-        <v>1.688156361908209</v>
+        <v>0.296412555363438</v>
       </c>
       <c r="E16" t="n">
-        <v>38.48</v>
+        <v>17.92</v>
       </c>
       <c r="F16" t="n">
-        <v>11.14</v>
+        <v>10.42</v>
       </c>
       <c r="G16" t="n">
-        <v>239</v>
+        <v>34</v>
       </c>
       <c r="H16" t="n">
-        <v>99.16</v>
+        <v>97.06</v>
       </c>
       <c r="I16" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="J16" t="n">
-        <v>10.78242677824268</v>
+        <v>8.235294117647058</v>
       </c>
       <c r="K16" t="n">
-        <v>4009785.65</v>
+        <v>266234.2</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>11.85</v>
+        <v>7.76</v>
       </c>
       <c r="O16" t="n">
-        <v>-12.45</v>
+        <v>-0.12</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.5999999999999996</v>
+        <v>7.64</v>
       </c>
       <c r="Q16" t="n">
-        <v>37.53</v>
+        <v>172.16</v>
       </c>
       <c r="R16" t="n">
-        <v>0.06891394010895446</v>
+        <v>0.04089741340687669</v>
       </c>
       <c r="S16" t="n">
-        <v>7.050000000000001</v>
+        <v>0.315</v>
       </c>
       <c r="T16" t="n">
-        <v>848.62</v>
+        <v>115.56</v>
       </c>
       <c r="U16" t="n">
-        <v>2577</v>
+        <v>280</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9046986492999636</v>
+        <v>0.9660637753039164</v>
       </c>
       <c r="W16" t="n">
-        <v>1.011223833010163</v>
+        <v>1.00240710746446</v>
       </c>
       <c r="X16" t="n">
-        <v>42.5335</v>
+        <v>18.54950000000001</v>
       </c>
       <c r="Y16" t="n">
-        <v>38.05290059813422</v>
+        <v>17.87696821636447</v>
       </c>
       <c r="Z16" t="n">
-        <v>71453358.08</v>
+        <v>6584865.28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>00913.TW</t>
+          <t>00715L.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>兆豐台灣晶圓製造</t>
+          <t>期街口布蘭特正2</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.621899753860291</v>
+        <v>5.693591246218765</v>
       </c>
       <c r="D17" t="n">
-        <v>1.595483088776454</v>
+        <v>2.603248403475678</v>
       </c>
       <c r="E17" t="n">
-        <v>47.93</v>
+        <v>83.34999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>14.68</v>
+        <v>94.37</v>
       </c>
       <c r="G17" t="n">
-        <v>262</v>
+        <v>425</v>
       </c>
       <c r="H17" t="n">
-        <v>96.18000000000001</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>3.5</v>
+        <v>3.32</v>
       </c>
       <c r="J17" t="n">
-        <v>12.79770992366412</v>
+        <v>17.11294117647059</v>
       </c>
       <c r="K17" t="n">
-        <v>1818921.85</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
+        <v>3123134.4</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>13.5</v>
+        <v>32.14</v>
       </c>
       <c r="O17" t="n">
-        <v>-9.19</v>
+        <v>-44.86</v>
       </c>
       <c r="P17" t="n">
-        <v>4.31</v>
+        <v>-12.72</v>
       </c>
       <c r="Q17" t="n">
-        <v>28.72</v>
+        <v>14.59</v>
       </c>
       <c r="R17" t="n">
-        <v>0.02641666508383667</v>
+        <v>3.090342842743087</v>
       </c>
       <c r="S17" t="n">
-        <v>6.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>916.5599999999999</v>
+        <v>1409.31</v>
       </c>
       <c r="U17" t="n">
-        <v>3353</v>
+        <v>7273</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9284621195978536</v>
+        <v>1.156755256401361</v>
       </c>
       <c r="W17" t="n">
-        <v>1.021547838622306</v>
+        <v>1.422584797114059</v>
       </c>
       <c r="X17" t="n">
-        <v>51.623</v>
+        <v>72.05499999999995</v>
       </c>
       <c r="Y17" t="n">
-        <v>46.91899702381047</v>
+        <v>58.59053194515278</v>
       </c>
       <c r="Z17" t="n">
-        <v>40809423.34</v>
+        <v>241625065.35</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>00685L.TW</t>
+          <t>00675L.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>群益臺灣加權正2</t>
+          <t>富邦臺灣加權正2</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10.53275822521513</v>
+        <v>10.695589391348</v>
       </c>
       <c r="D18" t="n">
-        <v>2.786640504456303</v>
+        <v>2.848567568452024</v>
       </c>
       <c r="E18" t="n">
-        <v>12.13</v>
+        <v>311</v>
       </c>
       <c r="F18" t="n">
-        <v>15.55</v>
+        <v>10.5</v>
       </c>
       <c r="G18" t="n">
-        <v>514</v>
+        <v>564</v>
       </c>
       <c r="H18" t="n">
-        <v>88.52</v>
+        <v>87.06</v>
       </c>
       <c r="I18" t="n">
-        <v>3.46</v>
+        <v>3.18</v>
       </c>
       <c r="J18" t="n">
-        <v>12.18093385214008</v>
+        <v>12.38297872340426</v>
       </c>
       <c r="K18" t="n">
-        <v>259483421.25</v>
+        <v>1205063.05</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1978,508 +1974,512 @@
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>15.89</v>
+        <v>15.7</v>
       </c>
       <c r="O18" t="n">
-        <v>-18.5</v>
+        <v>-24.73</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.609999999999999</v>
+        <v>-9.030000000000001</v>
       </c>
       <c r="Q18" t="n">
-        <v>18.65</v>
+        <v>16.61</v>
       </c>
       <c r="R18" t="n">
-        <v>7.74611772075883</v>
+        <v>7.84702182289598</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1777.84</v>
+        <v>1792.47</v>
       </c>
       <c r="U18" t="n">
-        <v>6261</v>
+        <v>6984</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9388544891640863</v>
+        <v>0.9130945390487371</v>
       </c>
       <c r="W18" t="n">
-        <v>1.032317144603849</v>
+        <v>1.014492553251156</v>
       </c>
       <c r="X18" t="n">
-        <v>12.92000000000001</v>
+        <v>340.6000000000002</v>
       </c>
       <c r="Y18" t="n">
-        <v>11.75026498727276</v>
+        <v>306.5572034051257</v>
       </c>
       <c r="Z18" t="n">
-        <v>2399751468.45</v>
+        <v>307076735</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>009809.TW</t>
+          <t>00935.TW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>富邦淨零ESG50</t>
+          <t>野村臺灣新科技50</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.3526493668090109</v>
+        <v>1.364663806801542</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3126617397103886</v>
+        <v>1.093561942376952</v>
       </c>
       <c r="E19" t="n">
-        <v>18.11</v>
+        <v>55.1</v>
       </c>
       <c r="F19" t="n">
-        <v>15.64</v>
+        <v>8.91</v>
       </c>
       <c r="G19" t="n">
-        <v>34</v>
+        <v>136</v>
       </c>
       <c r="H19" t="n">
-        <v>97.06</v>
+        <v>83.09</v>
       </c>
       <c r="I19" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="J19" t="n">
-        <v>8.235294117647058</v>
+        <v>12.30882352941176</v>
       </c>
       <c r="K19" t="n">
-        <v>257533.7</v>
+        <v>12744295.55</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>7.76</v>
+        <v>14.6</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.12</v>
+        <v>-8.99</v>
       </c>
       <c r="P19" t="n">
-        <v>7.64</v>
+        <v>5.609999999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>172.16</v>
+        <v>43.74</v>
       </c>
       <c r="R19" t="n">
-        <v>0.03998762709862236</v>
+        <v>0.2711018644245899</v>
       </c>
       <c r="S19" t="n">
-        <v>0.315</v>
+        <v>4.98</v>
       </c>
       <c r="T19" t="n">
-        <v>115.56</v>
+        <v>428.12</v>
       </c>
       <c r="U19" t="n">
-        <v>280</v>
+        <v>1674</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9745990743730489</v>
+        <v>0.9173395488221092</v>
       </c>
       <c r="W19" t="n">
-        <v>1.007531432561726</v>
+        <v>1.007135499668602</v>
       </c>
       <c r="X19" t="n">
-        <v>18.582</v>
+        <v>60.06500000000001</v>
       </c>
       <c r="Y19" t="n">
-        <v>17.97462532156831</v>
+        <v>54.70961952798871</v>
       </c>
       <c r="Z19" t="n">
-        <v>6505238.77</v>
+        <v>615959428.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>00715L.TW</t>
+          <t>00894.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>期街口布蘭特正2</t>
+          <t>中信小資高價30</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5.615889716058136</v>
+        <v>1.962923524208284</v>
       </c>
       <c r="D20" t="n">
-        <v>2.645476803396419</v>
+        <v>1.706878531101225</v>
       </c>
       <c r="E20" t="n">
-        <v>82.34999999999999</v>
+        <v>45.94</v>
       </c>
       <c r="F20" t="n">
-        <v>92.14</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>425</v>
+        <v>243</v>
       </c>
       <c r="H20" t="n">
-        <v>77.65000000000001</v>
+        <v>82.72</v>
       </c>
       <c r="I20" t="n">
-        <v>3.32</v>
+        <v>2.88</v>
       </c>
       <c r="J20" t="n">
-        <v>17.11294117647059</v>
+        <v>15.32921810699589</v>
       </c>
       <c r="K20" t="n">
-        <v>3222811.4</v>
-      </c>
-      <c r="L20" t="inlineStr"/>
+        <v>1244910.7</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="M20" t="n">
         <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>32.14</v>
+        <v>15.7</v>
       </c>
       <c r="O20" t="n">
-        <v>-44.86</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>-12.72</v>
+        <v>7.319999999999999</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.59</v>
+        <v>22.58</v>
       </c>
       <c r="R20" t="n">
-        <v>2.970412912661717</v>
+        <v>0.256044993107059</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>7.549999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>1409.31</v>
+        <v>698.73</v>
       </c>
       <c r="U20" t="n">
-        <v>7273</v>
+        <v>3725</v>
       </c>
       <c r="V20" t="n">
-        <v>1.157739350485028</v>
+        <v>0.9232778978043514</v>
       </c>
       <c r="W20" t="n">
-        <v>1.410750568586542</v>
+        <v>1.003432376723027</v>
       </c>
       <c r="X20" t="n">
-        <v>71.12999999999995</v>
+        <v>49.75749999999998</v>
       </c>
       <c r="Y20" t="n">
-        <v>58.37318221498789</v>
+        <v>45.78285599078355</v>
       </c>
       <c r="Z20" t="n">
-        <v>189852489.9</v>
+        <v>73000819.17999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>00401A.TW</t>
+          <t>00901.TW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>主動摩根台灣鑫收</t>
+          <t>永豐智能車供應鏈</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.06275094536995685</v>
+        <v>1.718705169458816</v>
       </c>
       <c r="D21" t="n">
-        <v>0.06145961825469559</v>
+        <v>1.672509106053912</v>
       </c>
       <c r="E21" t="n">
-        <v>13.72</v>
+        <v>44.44</v>
       </c>
       <c r="F21" t="n">
-        <v>18.26</v>
+        <v>8.84</v>
       </c>
       <c r="G21" t="n">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="H21" t="n">
-        <v>100</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>3.23</v>
+        <v>2.79</v>
       </c>
       <c r="J21" t="n">
-        <v>15.19047619047619</v>
+        <v>13.22463768115942</v>
       </c>
       <c r="K21" t="n">
-        <v>6929884.6</v>
+        <v>259846.35</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>11.76</v>
+        <v>15.18</v>
       </c>
       <c r="O21" t="n">
-        <v>0.36</v>
+        <v>-7.3</v>
       </c>
       <c r="P21" t="n">
-        <v>12.12</v>
+        <v>7.88</v>
       </c>
       <c r="Q21" t="n">
-        <v>80.95</v>
+        <v>24.17</v>
       </c>
       <c r="R21" t="n">
-        <v>0.001291327115261254</v>
+        <v>0.04619606340490412</v>
       </c>
       <c r="S21" t="n">
-        <v>0.377</v>
+        <v>4.671</v>
       </c>
       <c r="T21" t="n">
-        <v>67.92</v>
+        <v>771.28</v>
       </c>
       <c r="U21" t="n">
-        <v>319</v>
+        <v>3650</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9643974273363087</v>
+        <v>0.9311681508643268</v>
       </c>
       <c r="W21" t="n">
-        <v>1.013276976284115</v>
+        <v>1.008546480236058</v>
       </c>
       <c r="X21" t="n">
-        <v>14.22650000000001</v>
+        <v>47.725</v>
       </c>
       <c r="Y21" t="n">
-        <v>13.54022673081345</v>
+        <v>44.0634129124108</v>
       </c>
       <c r="Z21" t="n">
-        <v>58041101.72000001</v>
+        <v>11380772.92</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>00675L.TW</t>
+          <t>0057.TW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>富邦臺灣加權正2</t>
+          <t>富邦摩台</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>11.04043089394563</v>
+        <v>6.046462224145085</v>
       </c>
       <c r="D22" t="n">
-        <v>2.89348485751947</v>
+        <v>4.825956592107342</v>
       </c>
       <c r="E22" t="n">
-        <v>320.05</v>
+        <v>317.8</v>
       </c>
       <c r="F22" t="n">
-        <v>15.24</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>564</v>
+        <v>1245</v>
       </c>
       <c r="H22" t="n">
-        <v>87.06</v>
+        <v>93.33</v>
       </c>
       <c r="I22" t="n">
-        <v>3.18</v>
+        <v>2.64</v>
       </c>
       <c r="J22" t="n">
-        <v>12.38297872340426</v>
+        <v>12.02409638554217</v>
       </c>
       <c r="K22" t="n">
-        <v>1211309</v>
+        <v>31496.05</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>15.7</v>
+        <v>14.45</v>
       </c>
       <c r="O22" t="n">
-        <v>-24.73</v>
+        <v>-6.48</v>
       </c>
       <c r="P22" t="n">
-        <v>-9.030000000000001</v>
+        <v>7.969999999999999</v>
       </c>
       <c r="Q22" t="n">
-        <v>16.61</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="R22" t="n">
-        <v>8.146946036426163</v>
+        <v>1.220505632037742</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.685</v>
       </c>
       <c r="T22" t="n">
-        <v>1792.47</v>
+        <v>3287.55</v>
       </c>
       <c r="U22" t="n">
-        <v>6984</v>
+        <v>14970</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9360102945047227</v>
+        <v>0.9547700950864491</v>
       </c>
       <c r="W22" t="n">
-        <v>1.030257331635837</v>
+        <v>1.006981838902337</v>
       </c>
       <c r="X22" t="n">
-        <v>341.9300000000002</v>
+        <v>332.855</v>
       </c>
       <c r="Y22" t="n">
-        <v>310.6505434829825</v>
+        <v>315.5965556900397</v>
       </c>
       <c r="Z22" t="n">
-        <v>379197800.4</v>
+        <v>2602146.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>00935.TW</t>
+          <t>00881.TW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>野村臺灣新科技50</t>
+          <t>國泰台灣科技龍頭</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.418583822219333</v>
+        <v>1.936136014854752</v>
       </c>
       <c r="D23" t="n">
-        <v>1.119176523101771</v>
+        <v>1.773072221106335</v>
       </c>
       <c r="E23" t="n">
-        <v>56.4</v>
+        <v>48.8</v>
       </c>
       <c r="F23" t="n">
-        <v>12.66</v>
+        <v>7.45</v>
       </c>
       <c r="G23" t="n">
-        <v>136</v>
+        <v>384</v>
       </c>
       <c r="H23" t="n">
-        <v>83.09</v>
+        <v>89.58</v>
       </c>
       <c r="I23" t="n">
-        <v>3.15</v>
+        <v>2.52</v>
       </c>
       <c r="J23" t="n">
-        <v>12.30882352941176</v>
+        <v>15.328125</v>
       </c>
       <c r="K23" t="n">
-        <v>12906237.4</v>
+        <v>16954565.1</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="M23" t="n">
         <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>14.6</v>
+        <v>10.9</v>
       </c>
       <c r="O23" t="n">
-        <v>-8.99</v>
+        <v>-4.28</v>
       </c>
       <c r="P23" t="n">
-        <v>5.609999999999999</v>
+        <v>6.62</v>
       </c>
       <c r="Q23" t="n">
-        <v>43.74</v>
+        <v>15.81</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2994072991175627</v>
+        <v>0.1630637937484178</v>
       </c>
       <c r="S23" t="n">
-        <v>4.98</v>
+        <v>12.5</v>
       </c>
       <c r="T23" t="n">
-        <v>428.12</v>
+        <v>966.91</v>
       </c>
       <c r="U23" t="n">
-        <v>1674</v>
+        <v>5886</v>
       </c>
       <c r="V23" t="n">
-        <v>0.9352458336787991</v>
+        <v>0.9407228915662653</v>
       </c>
       <c r="W23" t="n">
-        <v>1.017045381546768</v>
+        <v>1.007671035595253</v>
       </c>
       <c r="X23" t="n">
-        <v>60.30500000000002</v>
+        <v>51.87499999999999</v>
       </c>
       <c r="Y23" t="n">
-        <v>55.45475258363042</v>
+        <v>48.42850322791387</v>
       </c>
       <c r="Z23" t="n">
-        <v>364155398.4</v>
+        <v>923159848</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>00894.TW</t>
+          <t>0052.TW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>中信小資高價30</t>
+          <t>富邦科技</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2.034744485185609</v>
+        <v>8.098475448463127</v>
       </c>
       <c r="D24" t="n">
-        <v>1.739240103387254</v>
+        <v>4.9187882871038</v>
       </c>
       <c r="E24" t="n">
-        <v>47.17</v>
+        <v>61.8</v>
       </c>
       <c r="F24" t="n">
-        <v>14.79</v>
+        <v>9.69</v>
       </c>
       <c r="G24" t="n">
-        <v>243</v>
+        <v>1111</v>
       </c>
       <c r="H24" t="n">
-        <v>82.72</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="J24" t="n">
-        <v>15.32921810699589</v>
+        <v>14.18091809180918</v>
       </c>
       <c r="K24" t="n">
-        <v>1225257.35</v>
+        <v>20397584.85</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -2490,168 +2490,168 @@
         <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>15.7</v>
+        <v>12.7</v>
       </c>
       <c r="O24" t="n">
-        <v>-8.380000000000001</v>
+        <v>-14.18</v>
       </c>
       <c r="P24" t="n">
-        <v>7.319999999999999</v>
+        <v>-1.48</v>
       </c>
       <c r="Q24" t="n">
-        <v>22.58</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2955043817983545</v>
+        <v>3.179687161359327</v>
       </c>
       <c r="S24" t="n">
-        <v>7.549999999999999</v>
+        <v>2.232857285714286</v>
       </c>
       <c r="T24" t="n">
-        <v>698.73</v>
+        <v>2723.42</v>
       </c>
       <c r="U24" t="n">
-        <v>3725</v>
+        <v>15755</v>
       </c>
       <c r="V24" t="n">
-        <v>0.9450633114281138</v>
+        <v>0.9492358497811216</v>
       </c>
       <c r="W24" t="n">
-        <v>1.018323180276911</v>
+        <v>1.005892143440553</v>
       </c>
       <c r="X24" t="n">
-        <v>49.91199999999998</v>
+        <v>65.10500000000008</v>
       </c>
       <c r="Y24" t="n">
-        <v>46.32124743264032</v>
+        <v>61.43799850013673</v>
       </c>
       <c r="Z24" t="n">
-        <v>48592411.35</v>
+        <v>1251534233.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>00901.TW</t>
+          <t>00735.TW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>永豐智能車供應鏈</t>
+          <t>國泰臺韓科技</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.762731962935627</v>
+        <v>2.807903913852103</v>
       </c>
       <c r="D25" t="n">
-        <v>1.704564059090527</v>
+        <v>2.483423711696157</v>
       </c>
       <c r="E25" t="n">
-        <v>45.19</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>13.27</v>
+        <v>10.36</v>
       </c>
       <c r="G25" t="n">
-        <v>276</v>
+        <v>498</v>
       </c>
       <c r="H25" t="n">
-        <v>89.48999999999999</v>
+        <v>86.55</v>
       </c>
       <c r="I25" t="n">
-        <v>2.79</v>
+        <v>2.28</v>
       </c>
       <c r="J25" t="n">
-        <v>13.22463768115942</v>
+        <v>13.81124497991968</v>
       </c>
       <c r="K25" t="n">
-        <v>262901.5</v>
+        <v>1916367.85</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>2</v>
       </c>
       <c r="N25" t="n">
-        <v>15.18</v>
+        <v>21.39</v>
       </c>
       <c r="O25" t="n">
-        <v>-7.3</v>
+        <v>-6.04</v>
       </c>
       <c r="P25" t="n">
-        <v>7.88</v>
+        <v>15.35</v>
       </c>
       <c r="Q25" t="n">
-        <v>24.17</v>
+        <v>14.26</v>
       </c>
       <c r="R25" t="n">
-        <v>0.05816790384510018</v>
+        <v>0.3244802021559456</v>
       </c>
       <c r="S25" t="n">
-        <v>4.671</v>
+        <v>13.37</v>
       </c>
       <c r="T25" t="n">
-        <v>771.28</v>
+        <v>1133.84</v>
       </c>
       <c r="U25" t="n">
-        <v>3650</v>
+        <v>6878</v>
       </c>
       <c r="V25" t="n">
-        <v>0.9436996199306685</v>
+        <v>0.9085943622503516</v>
       </c>
       <c r="W25" t="n">
-        <v>1.014424695644075</v>
+        <v>1.021310581878393</v>
       </c>
       <c r="X25" t="n">
-        <v>47.886</v>
+        <v>105.2724999999999</v>
       </c>
       <c r="Y25" t="n">
-        <v>44.54741706707771</v>
+        <v>93.6541750346703</v>
       </c>
       <c r="Z25" t="n">
-        <v>11397189.14</v>
+        <v>239170338.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>0057.TW</t>
+          <t>0050.TW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>富邦摩台</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6.125159123683923</v>
+        <v>5.44182433494266</v>
       </c>
       <c r="D26" t="n">
-        <v>4.892653897730256</v>
+        <v>5.44182433494266</v>
       </c>
       <c r="E26" t="n">
-        <v>321.3</v>
+        <v>106.9</v>
       </c>
       <c r="F26" t="n">
-        <v>13.09</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>1245</v>
+        <v>1695</v>
       </c>
       <c r="H26" t="n">
-        <v>93.33</v>
+        <v>90.97</v>
       </c>
       <c r="I26" t="n">
-        <v>2.64</v>
+        <v>2.26</v>
       </c>
       <c r="J26" t="n">
-        <v>12.02409638554217</v>
+        <v>13.46961651917404</v>
       </c>
       <c r="K26" t="n">
-        <v>31923.9</v>
+        <v>116815298.9</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -2662,82 +2662,82 @@
         <v>2</v>
       </c>
       <c r="N26" t="n">
-        <v>14.45</v>
+        <v>13.94</v>
       </c>
       <c r="O26" t="n">
-        <v>-6.48</v>
+        <v>-5.91</v>
       </c>
       <c r="P26" t="n">
-        <v>7.969999999999999</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>8.970000000000001</v>
+        <v>6.04</v>
       </c>
       <c r="R26" t="n">
-        <v>1.232505225953667</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>1.685</v>
+        <v>4.84625</v>
       </c>
       <c r="T26" t="n">
-        <v>3287.55</v>
+        <v>3824.71</v>
       </c>
       <c r="U26" t="n">
-        <v>14970</v>
+        <v>22831</v>
       </c>
       <c r="V26" t="n">
-        <v>0.9633749606464478</v>
+        <v>0.9554239749748628</v>
       </c>
       <c r="W26" t="n">
-        <v>1.011467635586717</v>
+        <v>1.007766660763678</v>
       </c>
       <c r="X26" t="n">
-        <v>333.515</v>
+        <v>111.8875</v>
       </c>
       <c r="Y26" t="n">
-        <v>317.6572227282635</v>
+        <v>106.0761425854195</v>
       </c>
       <c r="Z26" t="n">
-        <v>19132772.4</v>
+        <v>14158028954.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>00881.TW</t>
+          <t>0053.TW</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>國泰台灣科技龍頭</t>
+          <t>元大科技市值</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.974895240595829</v>
+        <v>6.592821644129143</v>
       </c>
       <c r="D27" t="n">
-        <v>1.806051231841975</v>
+        <v>4.882307814546531</v>
       </c>
       <c r="E27" t="n">
-        <v>49.55</v>
+        <v>238.05</v>
       </c>
       <c r="F27" t="n">
-        <v>10.86</v>
+        <v>7.01</v>
       </c>
       <c r="G27" t="n">
-        <v>384</v>
+        <v>1190</v>
       </c>
       <c r="H27" t="n">
-        <v>89.58</v>
+        <v>89.16</v>
       </c>
       <c r="I27" t="n">
-        <v>2.52</v>
+        <v>2.18</v>
       </c>
       <c r="J27" t="n">
-        <v>15.328125</v>
+        <v>13.83697478991597</v>
       </c>
       <c r="K27" t="n">
-        <v>16934257.45</v>
+        <v>476981.85</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2748,82 +2748,82 @@
         <v>2</v>
       </c>
       <c r="N27" t="n">
-        <v>10.9</v>
+        <v>11.49</v>
       </c>
       <c r="O27" t="n">
-        <v>-4.28</v>
+        <v>-7.24</v>
       </c>
       <c r="P27" t="n">
-        <v>6.62</v>
+        <v>4.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>15.81</v>
+        <v>7.58</v>
       </c>
       <c r="R27" t="n">
-        <v>0.1688440087538541</v>
+        <v>1.710513829582612</v>
       </c>
       <c r="S27" t="n">
-        <v>12.5</v>
+        <v>18.91</v>
       </c>
       <c r="T27" t="n">
-        <v>966.91</v>
+        <v>2598</v>
       </c>
       <c r="U27" t="n">
-        <v>5886</v>
+        <v>16466</v>
       </c>
       <c r="V27" t="n">
-        <v>0.9524267179240751</v>
+        <v>0.946154075457824</v>
       </c>
       <c r="W27" t="n">
-        <v>1.013731151962443</v>
+        <v>1.008619202489728</v>
       </c>
       <c r="X27" t="n">
-        <v>52.02499999999999</v>
+        <v>251.5975000000001</v>
       </c>
       <c r="Y27" t="n">
-        <v>48.87883725786474</v>
+        <v>236.0157326098739</v>
       </c>
       <c r="Z27" t="n">
-        <v>437569856.25</v>
+        <v>157493880</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>0052.TW</t>
+          <t>00892.TW</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>富邦科技</t>
+          <t>富邦台灣半導體</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8.257010428881589</v>
+        <v>1.779711358373551</v>
       </c>
       <c r="D28" t="n">
-        <v>4.986669014345297</v>
+        <v>1.723497032196059</v>
       </c>
       <c r="E28" t="n">
-        <v>62.9</v>
+        <v>39.86</v>
       </c>
       <c r="F28" t="n">
-        <v>14.53</v>
+        <v>10.71</v>
       </c>
       <c r="G28" t="n">
-        <v>1111</v>
+        <v>241</v>
       </c>
       <c r="H28" t="n">
-        <v>88.20999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="J28" t="n">
-        <v>14.18091809180918</v>
+        <v>15.85892116182573</v>
       </c>
       <c r="K28" t="n">
-        <v>20331959.4</v>
+        <v>4500101.1</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -2834,555 +2834,211 @@
         <v>2</v>
       </c>
       <c r="N28" t="n">
-        <v>12.7</v>
+        <v>12.37</v>
       </c>
       <c r="O28" t="n">
-        <v>-14.18</v>
+        <v>-7.43</v>
       </c>
       <c r="P28" t="n">
-        <v>-1.48</v>
+        <v>4.94</v>
       </c>
       <c r="Q28" t="n">
-        <v>8.050000000000001</v>
+        <v>18.86</v>
       </c>
       <c r="R28" t="n">
-        <v>3.270341414536292</v>
+        <v>0.05621432617749189</v>
       </c>
       <c r="S28" t="n">
-        <v>2.232857285714286</v>
+        <v>4.937</v>
       </c>
       <c r="T28" t="n">
-        <v>2723.42</v>
+        <v>510.5</v>
       </c>
       <c r="U28" t="n">
-        <v>15755</v>
+        <v>3822</v>
       </c>
       <c r="V28" t="n">
-        <v>0.9640954899030528</v>
+        <v>0.9360762763609035</v>
       </c>
       <c r="W28" t="n">
-        <v>1.016341360229043</v>
+        <v>1.001300956336052</v>
       </c>
       <c r="X28" t="n">
-        <v>65.24250000000008</v>
+        <v>42.58200000000001</v>
       </c>
       <c r="Y28" t="n">
-        <v>61.88865519142589</v>
+        <v>39.80821125534046</v>
       </c>
       <c r="Z28" t="n">
-        <v>740685994.8</v>
+        <v>150566924.84</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>00735.TW</t>
+          <t>006208.TW</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>國泰臺韓科技</t>
+          <t>富邦台50</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2.901191117040621</v>
+        <v>4.044773778041981</v>
       </c>
       <c r="D29" t="n">
-        <v>2.524333611187225</v>
+        <v>3.787997617953844</v>
       </c>
       <c r="E29" t="n">
-        <v>98.2</v>
+        <v>244.85</v>
       </c>
       <c r="F29" t="n">
-        <v>14.21</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>498</v>
+        <v>895</v>
       </c>
       <c r="H29" t="n">
-        <v>86.55</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="J29" t="n">
-        <v>13.81124497991968</v>
+        <v>13.86703910614525</v>
       </c>
       <c r="K29" t="n">
-        <v>1857374.55</v>
+        <v>3158750.7</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M29" t="n">
         <v>2</v>
       </c>
       <c r="N29" t="n">
-        <v>21.39</v>
+        <v>11.21</v>
       </c>
       <c r="O29" t="n">
-        <v>-6.04</v>
+        <v>-6.25</v>
       </c>
       <c r="P29" t="n">
-        <v>15.35</v>
+        <v>4.960000000000001</v>
       </c>
       <c r="Q29" t="n">
-        <v>14.26</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="R29" t="n">
-        <v>0.3768575058533963</v>
+        <v>0.2567761600881369</v>
       </c>
       <c r="S29" t="n">
-        <v>13.37</v>
+        <v>28.764</v>
       </c>
       <c r="T29" t="n">
-        <v>1133.84</v>
+        <v>1745.92</v>
       </c>
       <c r="U29" t="n">
-        <v>6878</v>
+        <v>12411</v>
       </c>
       <c r="V29" t="n">
-        <v>0.9278374867131227</v>
+        <v>0.9557639573351027</v>
       </c>
       <c r="W29" t="n">
-        <v>1.032829147663534</v>
+        <v>1.006956638074854</v>
       </c>
       <c r="X29" t="n">
-        <v>105.8374999999999</v>
+        <v>256.1825000000001</v>
       </c>
       <c r="Y29" t="n">
-        <v>95.07864899257346</v>
+        <v>243.1584347744263</v>
       </c>
       <c r="Z29" t="n">
-        <v>142472095.2</v>
+        <v>615465488.55</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>0050.TW</t>
+          <t>009823.TWO</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>元大台灣50</t>
+          <t>群益S&amp;P500</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5.515191281060264</v>
+        <v>0.02717262655342534</v>
       </c>
       <c r="D30" t="n">
-        <v>5.515191281060264</v>
+        <v>0.004023674744812133</v>
       </c>
       <c r="E30" t="n">
-        <v>108.15</v>
+        <v>10.72</v>
       </c>
       <c r="F30" t="n">
-        <v>13.41</v>
+        <v>68.75</v>
       </c>
       <c r="G30" t="n">
-        <v>1695</v>
+        <v>15</v>
       </c>
       <c r="H30" t="n">
-        <v>90.97</v>
+        <v>100</v>
       </c>
       <c r="I30" t="n">
-        <v>2.26</v>
+        <v>1.31</v>
       </c>
       <c r="J30" t="n">
-        <v>13.46961651917404</v>
+        <v>16.93333333333333</v>
       </c>
       <c r="K30" t="n">
-        <v>116172962.85</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
+        <v>3324514.25</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="n">
         <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>13.94</v>
+        <v>3.64</v>
       </c>
       <c r="O30" t="n">
-        <v>-5.91</v>
+        <v>0.45</v>
       </c>
       <c r="P30" t="n">
-        <v>8.029999999999999</v>
+        <v>4.09</v>
       </c>
       <c r="Q30" t="n">
-        <v>6.04</v>
+        <v>29.52</v>
       </c>
       <c r="R30" t="n">
+        <v>0.02314895180861321</v>
+      </c>
+      <c r="S30" t="n">
         <v>0</v>
       </c>
-      <c r="S30" t="n">
-        <v>4.84625</v>
-      </c>
       <c r="T30" t="n">
-        <v>3824.71</v>
+        <v>19.72</v>
       </c>
       <c r="U30" t="n">
-        <v>22831</v>
+        <v>254</v>
       </c>
       <c r="V30" t="n">
-        <v>0.9646775488359643</v>
+        <v>1.010605703511666</v>
       </c>
       <c r="W30" t="n">
-        <v>1.013050089400627</v>
+        <v>1.032026555525566</v>
       </c>
       <c r="X30" t="n">
-        <v>112.11</v>
+        <v>10.6075</v>
       </c>
       <c r="Y30" t="n">
-        <v>106.7568140327465</v>
+        <v>10.38732961143696</v>
       </c>
       <c r="Z30" t="n">
-        <v>9009093887.85</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>0053.TW</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>元大科技市值</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>6.692837544939853</v>
-      </c>
-      <c r="D31" t="n">
-        <v>4.949576222723458</v>
-      </c>
-      <c r="E31" t="n">
-        <v>241.35</v>
-      </c>
-      <c r="F31" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1190</v>
-      </c>
-      <c r="H31" t="n">
-        <v>89.16</v>
-      </c>
-      <c r="I31" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="J31" t="n">
-        <v>13.83697478991597</v>
-      </c>
-      <c r="K31" t="n">
-        <v>451801</v>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="M31" t="n">
-        <v>2</v>
-      </c>
-      <c r="N31" t="n">
-        <v>11.49</v>
-      </c>
-      <c r="O31" t="n">
-        <v>-7.24</v>
-      </c>
-      <c r="P31" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>7.58</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.743261322216395</v>
-      </c>
-      <c r="S31" t="n">
-        <v>18.91</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2598</v>
-      </c>
-      <c r="U31" t="n">
-        <v>16466</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0.9571303934010147</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.014878710228875</v>
-      </c>
-      <c r="X31" t="n">
-        <v>252.1600000000001</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>237.8116690866151</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>117009617.55</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>00892.TW</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>富邦台灣半導體</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>1.835517372302171</v>
-      </c>
-      <c r="D32" t="n">
-        <v>1.756006070252821</v>
-      </c>
-      <c r="E32" t="n">
-        <v>40.71</v>
-      </c>
-      <c r="F32" t="n">
-        <v>15.24</v>
-      </c>
-      <c r="G32" t="n">
-        <v>241</v>
-      </c>
-      <c r="H32" t="n">
-        <v>75.09999999999999</v>
-      </c>
-      <c r="I32" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="J32" t="n">
-        <v>15.85892116182573</v>
-      </c>
-      <c r="K32" t="n">
-        <v>4490782.3</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="M32" t="n">
-        <v>2</v>
-      </c>
-      <c r="N32" t="n">
-        <v>12.37</v>
-      </c>
-      <c r="O32" t="n">
-        <v>-7.43</v>
-      </c>
-      <c r="P32" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>18.86</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0.07951130204935009</v>
-      </c>
-      <c r="S32" t="n">
-        <v>4.937</v>
-      </c>
-      <c r="T32" t="n">
-        <v>510.5</v>
-      </c>
-      <c r="U32" t="n">
-        <v>3822</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0.9526483906069008</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.011283929593973</v>
-      </c>
-      <c r="X32" t="n">
-        <v>42.73350000000001</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>40.25575687368526</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>123125237.37</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>006208.TW</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>富邦台50</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>4.097989821831891</v>
-      </c>
-      <c r="D33" t="n">
-        <v>3.843302605799952</v>
-      </c>
-      <c r="E33" t="n">
-        <v>247.6</v>
-      </c>
-      <c r="F33" t="n">
-        <v>12.14</v>
-      </c>
-      <c r="G33" t="n">
-        <v>895</v>
-      </c>
-      <c r="H33" t="n">
-        <v>88.48999999999999</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="J33" t="n">
-        <v>13.86703910614525</v>
-      </c>
-      <c r="K33" t="n">
-        <v>3156014.6</v>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="M33" t="n">
-        <v>2</v>
-      </c>
-      <c r="N33" t="n">
-        <v>11.21</v>
-      </c>
-      <c r="O33" t="n">
-        <v>-6.25</v>
-      </c>
-      <c r="P33" t="n">
-        <v>4.960000000000001</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0.2546872160319387</v>
-      </c>
-      <c r="S33" t="n">
-        <v>28.764</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1745.92</v>
-      </c>
-      <c r="U33" t="n">
-        <v>12411</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0.9646440050647703</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.011852951358082</v>
-      </c>
-      <c r="X33" t="n">
-        <v>256.6750000000001</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>244.6995876897704</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>371970222.8</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>009823.TWO</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>群益S&amp;P500</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>0.03038358013963127</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0.01579937295296352</v>
-      </c>
-      <c r="E34" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="F34" t="n">
-        <v>74.56</v>
-      </c>
-      <c r="G34" t="n">
-        <v>15</v>
-      </c>
-      <c r="H34" t="n">
-        <v>100</v>
-      </c>
-      <c r="I34" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="J34" t="n">
-        <v>16.93333333333333</v>
-      </c>
-      <c r="K34" t="n">
-        <v>3341336.85</v>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="n">
-        <v>2</v>
-      </c>
-      <c r="N34" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="P34" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>29.52</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0.01458420718666775</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>19.72</v>
-      </c>
-      <c r="U34" t="n">
-        <v>254</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.014916918429003</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.037419247862923</v>
-      </c>
-      <c r="X34" t="n">
-        <v>10.592</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>10.36225231230761</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>34560379.25</v>
+        <v>35706100.96</v>
       </c>
     </row>
   </sheetData>

--- a/ETF動態清單.xlsx
+++ b/ETF動態清單.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z30"/>
+  <dimension ref="A1:Z27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,16 +567,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.6430343840630024</v>
+        <v>0.5974557964381386</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5138216598021295</v>
+        <v>0.508125151263835</v>
       </c>
       <c r="E2" t="n">
-        <v>28.19</v>
+        <v>27.4</v>
       </c>
       <c r="F2" t="n">
-        <v>9.27</v>
+        <v>7.67</v>
       </c>
       <c r="G2" t="n">
         <v>41</v>
@@ -591,7 +591,7 @@
         <v>8.439024390243903</v>
       </c>
       <c r="K2" t="n">
-        <v>170395238.2</v>
+        <v>170635036.05</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         <v>386.28</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1292127242608729</v>
+        <v>0.08933064517430367</v>
       </c>
       <c r="S2" t="n">
         <v>1.67</v>
@@ -626,230 +626,230 @@
         <v>346</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9193340616694116</v>
+        <v>0.8975954923671624</v>
       </c>
       <c r="W2" t="n">
-        <v>1.005843304452886</v>
+        <v>0.995162470835485</v>
       </c>
       <c r="X2" t="n">
-        <v>30.6635</v>
+        <v>30.526</v>
       </c>
       <c r="Y2" t="n">
-        <v>28.02623418101246</v>
+        <v>27.5331926223026</v>
       </c>
       <c r="Z2" t="n">
-        <v>6775475802.700001</v>
+        <v>7598889155.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>00992A.TW</t>
+          <t>00947.TW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>主動群益科技創新</t>
+          <t>台新臺灣IC設計</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1850698488098292</v>
+        <v>1.108033706688896</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1785476731583375</v>
+        <v>0.8467376334148036</v>
       </c>
       <c r="E3" t="n">
-        <v>16.93</v>
+        <v>34.26</v>
       </c>
       <c r="F3" t="n">
-        <v>12.72</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
+        <v>96.97</v>
       </c>
       <c r="I3" t="n">
-        <v>8.390000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="J3" t="n">
-        <v>10.27272727272727</v>
+        <v>10.33333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>55088239.9</v>
+        <v>12410892.9</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>15.18</v>
+        <v>18.77</v>
       </c>
       <c r="O3" t="n">
-        <v>2.64</v>
+        <v>-0.73</v>
       </c>
       <c r="P3" t="n">
-        <v>17.82</v>
+        <v>18.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>317.42</v>
+        <v>159.78</v>
       </c>
       <c r="R3" t="n">
-        <v>0.006522175651491713</v>
+        <v>0.2612960732740925</v>
       </c>
       <c r="S3" t="n">
-        <v>1.32</v>
+        <v>2.78</v>
       </c>
       <c r="T3" t="n">
-        <v>277.02</v>
+        <v>495.22</v>
       </c>
       <c r="U3" t="n">
-        <v>339</v>
+        <v>682</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8965973785250898</v>
+        <v>0.8899510345096304</v>
       </c>
       <c r="W3" t="n">
-        <v>1.002376884074319</v>
+        <v>1.032576298115363</v>
       </c>
       <c r="X3" t="n">
-        <v>18.88249999999999</v>
+        <v>38.49650000000001</v>
       </c>
       <c r="Y3" t="n">
-        <v>16.88985477317209</v>
+        <v>33.17914624084499</v>
       </c>
       <c r="Z3" t="n">
-        <v>1279678276.83</v>
+        <v>269346946.74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>00947.TW</t>
+          <t>00985A.TW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>台新臺灣IC設計</t>
+          <t>主動野村台灣50</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.099679462078313</v>
+        <v>0.4423916519640649</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8533458910309029</v>
+        <v>0.4253052321766908</v>
       </c>
       <c r="E4" t="n">
-        <v>34.08</v>
+        <v>20.23</v>
       </c>
       <c r="F4" t="n">
-        <v>11.33</v>
+        <v>5.23</v>
       </c>
       <c r="G4" t="n">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="H4" t="n">
-        <v>96.97</v>
+        <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>7.5</v>
+        <v>6.95</v>
       </c>
       <c r="J4" t="n">
-        <v>10.33333333333333</v>
+        <v>9.972972972972974</v>
       </c>
       <c r="K4" t="n">
-        <v>12763021.65</v>
+        <v>60093537.55</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>18.77</v>
+        <v>15.02</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.73</v>
+        <v>2.1</v>
       </c>
       <c r="P4" t="n">
-        <v>18.04</v>
+        <v>17.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>159.78</v>
+        <v>252.13</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2463335710474102</v>
+        <v>0.01708641978737413</v>
       </c>
       <c r="S4" t="n">
-        <v>2.78</v>
+        <v>2.15</v>
       </c>
       <c r="T4" t="n">
-        <v>495.22</v>
+        <v>257.02</v>
       </c>
       <c r="U4" t="n">
-        <v>682</v>
+        <v>369</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8781241947951556</v>
+        <v>0.8803690325949778</v>
       </c>
       <c r="W4" t="n">
-        <v>1.008338974466148</v>
+        <v>1.016908162083496</v>
       </c>
       <c r="X4" t="n">
-        <v>38.81000000000001</v>
+        <v>22.97900000000001</v>
       </c>
       <c r="Y4" t="n">
-        <v>33.79815802324136</v>
+        <v>19.89363519174799</v>
       </c>
       <c r="Z4" t="n">
-        <v>292035098.4</v>
+        <v>342370294.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>00980A.TW</t>
+          <t>009816.TW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>主動野村臺灣優選</t>
+          <t>凱基台灣TOP50</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.5587911331864652</v>
+        <v>0.1608528121611448</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5556268839929315</v>
+        <v>0.1257454038990293</v>
       </c>
       <c r="E5" t="n">
-        <v>23.75</v>
+        <v>15.9</v>
       </c>
       <c r="F5" t="n">
-        <v>13.1</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="H5" t="n">
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>7.02</v>
+        <v>5.32</v>
       </c>
       <c r="J5" t="n">
-        <v>9.824999999999999</v>
+        <v>10.54166666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>8725865.949999999</v>
+        <v>135021743</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -860,82 +860,82 @@
         <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>15.61</v>
+        <v>8.99</v>
       </c>
       <c r="O5" t="n">
-        <v>2.11</v>
+        <v>0.64</v>
       </c>
       <c r="P5" t="n">
-        <v>17.72</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>246.15</v>
+        <v>227.93</v>
       </c>
       <c r="R5" t="n">
-        <v>0.003164249193533752</v>
+        <v>0.03510740826211545</v>
       </c>
       <c r="S5" t="n">
-        <v>1.814</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>280.74</v>
+        <v>127.78</v>
       </c>
       <c r="U5" t="n">
-        <v>393</v>
+        <v>253</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9319755920497582</v>
+        <v>0.9646594873350522</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0058729197188</v>
+        <v>1.010207034706611</v>
       </c>
       <c r="X5" t="n">
-        <v>25.48349999999999</v>
+        <v>16.4825</v>
       </c>
       <c r="Y5" t="n">
-        <v>23.61133253954139</v>
+        <v>15.73934792942494</v>
       </c>
       <c r="Z5" t="n">
-        <v>154871375</v>
+        <v>1965275027.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>00985A.TW</t>
+          <t>009824.TW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>主動野村台灣50</t>
+          <t>群益美國科技巨頭</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.4438326671170423</v>
+        <v>0.00329851400727299</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4306666972430557</v>
+        <v>0.001194952732069154</v>
       </c>
       <c r="E6" t="n">
-        <v>20.23</v>
+        <v>10.2</v>
       </c>
       <c r="F6" t="n">
-        <v>5.61</v>
+        <v>12.93</v>
       </c>
       <c r="G6" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
         <v>100</v>
       </c>
       <c r="I6" t="n">
-        <v>6.95</v>
+        <v>5.26</v>
       </c>
       <c r="J6" t="n">
-        <v>9.972972972972974</v>
+        <v>5.75</v>
       </c>
       <c r="K6" t="n">
-        <v>59382249.25</v>
+        <v>3403265.55</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -946,82 +946,82 @@
         <v>2</v>
       </c>
       <c r="N6" t="n">
-        <v>15.02</v>
+        <v>7.35</v>
       </c>
       <c r="O6" t="n">
-        <v>2.1</v>
+        <v>1.39</v>
       </c>
       <c r="P6" t="n">
-        <v>17.12</v>
+        <v>8.74</v>
       </c>
       <c r="Q6" t="n">
-        <v>252.13</v>
+        <v>1975.8</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01316596987398655</v>
+        <v>0.002103561275203836</v>
       </c>
       <c r="S6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>257.02</v>
+        <v>21.06</v>
       </c>
       <c r="U6" t="n">
-        <v>369</v>
+        <v>23</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8744137796892221</v>
+        <v>0.9654519640321813</v>
       </c>
       <c r="W6" t="n">
-        <v>0.995676106844684</v>
+        <v>1.004849102541872</v>
       </c>
       <c r="X6" t="n">
-        <v>23.1355</v>
+        <v>10.565</v>
       </c>
       <c r="Y6" t="n">
-        <v>20.31785222215409</v>
+        <v>10.15077783738675</v>
       </c>
       <c r="Z6" t="n">
-        <v>488756779.77</v>
+        <v>19246818.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>009816.TW</t>
+          <t>009804.TW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>凱基台灣TOP50</t>
+          <t>聯邦台精彩50</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.1639800557652396</v>
+        <v>0.6002762533745891</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1296347781660614</v>
+        <v>0.5856369472573018</v>
       </c>
       <c r="E7" t="n">
-        <v>15.93</v>
+        <v>22.69</v>
       </c>
       <c r="F7" t="n">
-        <v>10.14</v>
+        <v>9.98</v>
       </c>
       <c r="G7" t="n">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="H7" t="n">
         <v>100</v>
       </c>
       <c r="I7" t="n">
-        <v>5.32</v>
+        <v>4.12</v>
       </c>
       <c r="J7" t="n">
-        <v>10.54166666666667</v>
+        <v>8.82258064516129</v>
       </c>
       <c r="K7" t="n">
-        <v>133722143.8</v>
+        <v>1009074.3</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -1032,168 +1032,168 @@
         <v>2</v>
       </c>
       <c r="N7" t="n">
-        <v>8.99</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>0.64</v>
+        <v>0.76</v>
       </c>
       <c r="P7" t="n">
-        <v>9.630000000000001</v>
+        <v>10.39</v>
       </c>
       <c r="Q7" t="n">
-        <v>227.93</v>
+        <v>133.05</v>
       </c>
       <c r="R7" t="n">
-        <v>0.03434527759917816</v>
+        <v>0.01463930611728737</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.786</v>
       </c>
       <c r="T7" t="n">
-        <v>127.78</v>
+        <v>255.36</v>
       </c>
       <c r="U7" t="n">
-        <v>253</v>
+        <v>547</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9646652738668362</v>
+        <v>0.951063606832233</v>
       </c>
       <c r="W7" t="n">
-        <v>1.006949036043636</v>
+        <v>1.009132208798136</v>
       </c>
       <c r="X7" t="n">
-        <v>16.5135</v>
+        <v>23.8575</v>
       </c>
       <c r="Y7" t="n">
-        <v>15.82006579259457</v>
+        <v>22.4846653413466</v>
       </c>
       <c r="Z7" t="n">
-        <v>1898753522.31</v>
+        <v>8899426.42</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>009824.TW</t>
+          <t>00830.TW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>群益美國科技巨頭</t>
+          <t>國泰費城半導體</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.009240732374837135</v>
+        <v>2.335100216795478</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004023674744812133</v>
+        <v>2.227023742992224</v>
       </c>
       <c r="E8" t="n">
-        <v>10.26</v>
+        <v>80.05</v>
       </c>
       <c r="F8" t="n">
-        <v>18.46</v>
+        <v>6.81</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>495</v>
       </c>
       <c r="H8" t="n">
-        <v>100</v>
+        <v>97.17</v>
       </c>
       <c r="I8" t="n">
-        <v>5.26</v>
+        <v>3.93</v>
       </c>
       <c r="J8" t="n">
-        <v>5.75</v>
+        <v>12.29090909090909</v>
       </c>
       <c r="K8" t="n">
-        <v>3791910.1</v>
+        <v>10535339.85</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>7.35</v>
+        <v>13.29</v>
       </c>
       <c r="O8" t="n">
-        <v>1.39</v>
+        <v>-12.33</v>
       </c>
       <c r="P8" t="n">
-        <v>8.74</v>
+        <v>0.9599999999999991</v>
       </c>
       <c r="Q8" t="n">
-        <v>1975.8</v>
+        <v>19.85</v>
       </c>
       <c r="R8" t="n">
-        <v>0.005217057630025002</v>
+        <v>0.108076473803254</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>17.71</v>
       </c>
       <c r="T8" t="n">
-        <v>21.06</v>
+        <v>1946.3</v>
       </c>
       <c r="U8" t="n">
-        <v>23</v>
+        <v>6084</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9697084258777936</v>
+        <v>0.9189794219785897</v>
       </c>
       <c r="W8" t="n">
-        <v>1.00585626510936</v>
+        <v>1.017275305986647</v>
       </c>
       <c r="X8" t="n">
-        <v>10.5805</v>
+        <v>87.10749999999999</v>
       </c>
       <c r="Y8" t="n">
-        <v>10.20026454662933</v>
+        <v>78.69059587793706</v>
       </c>
       <c r="Z8" t="n">
-        <v>22495563</v>
+        <v>894896000.65</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>009804.TW</t>
+          <t>00663L.TW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>聯邦台精彩50</t>
+          <t>國泰臺灣加權正2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.6077251516304043</v>
+        <v>11.23085590657439</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5916425396469043</v>
+        <v>2.899617202153657</v>
       </c>
       <c r="E9" t="n">
-        <v>22.78</v>
+        <v>102.6</v>
       </c>
       <c r="F9" t="n">
-        <v>10.41</v>
+        <v>9.32</v>
       </c>
       <c r="G9" t="n">
-        <v>62</v>
+        <v>564</v>
       </c>
       <c r="H9" t="n">
-        <v>100</v>
+        <v>89.89</v>
       </c>
       <c r="I9" t="n">
-        <v>4.12</v>
+        <v>3.76</v>
       </c>
       <c r="J9" t="n">
-        <v>8.82258064516129</v>
+        <v>11.9113475177305</v>
       </c>
       <c r="K9" t="n">
-        <v>1096973.7</v>
+        <v>5253136.45</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1204,82 +1204,82 @@
         <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>9.630000000000001</v>
+        <v>15.99</v>
       </c>
       <c r="O9" t="n">
-        <v>0.76</v>
+        <v>-24.46</v>
       </c>
       <c r="P9" t="n">
-        <v>10.39</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>133.05</v>
+        <v>18.35</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01608261198350003</v>
+        <v>8.331238704420731</v>
       </c>
       <c r="S9" t="n">
-        <v>2.786</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>255.36</v>
+        <v>2121.97</v>
       </c>
       <c r="U9" t="n">
-        <v>547</v>
+        <v>6718</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9521620096553741</v>
+        <v>0.9160918770508265</v>
       </c>
       <c r="W9" t="n">
-        <v>1.00531494679553</v>
+        <v>1.024996526178535</v>
       </c>
       <c r="X9" t="n">
-        <v>23.9245</v>
+        <v>111.9975000000001</v>
       </c>
       <c r="Y9" t="n">
-        <v>22.6595656143499</v>
+        <v>100.0979002168141</v>
       </c>
       <c r="Z9" t="n">
-        <v>15222484.42</v>
+        <v>361701525.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>00830.TW</t>
+          <t>00631L.TW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>國泰費城半導體</t>
+          <t>元大台灣50正2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2.366231255193935</v>
+        <v>15.0862385595298</v>
       </c>
       <c r="D10" t="n">
-        <v>2.237111163366611</v>
+        <v>3.315304290728562</v>
       </c>
       <c r="E10" t="n">
-        <v>80.90000000000001</v>
+        <v>35.6</v>
       </c>
       <c r="F10" t="n">
-        <v>9.890000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="G10" t="n">
-        <v>495</v>
+        <v>644</v>
       </c>
       <c r="H10" t="n">
-        <v>97.17</v>
+        <v>89.44</v>
       </c>
       <c r="I10" t="n">
-        <v>3.93</v>
+        <v>3.74</v>
       </c>
       <c r="J10" t="n">
-        <v>12.29090909090909</v>
+        <v>12.68167701863354</v>
       </c>
       <c r="K10" t="n">
-        <v>10754959.45</v>
+        <v>190656506.45</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1290,168 +1290,168 @@
         <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>13.29</v>
+        <v>17.37</v>
       </c>
       <c r="O10" t="n">
-        <v>-12.33</v>
+        <v>-12.43</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9599999999999991</v>
+        <v>4.940000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>19.85</v>
+        <v>15.49</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1291200918273243</v>
+        <v>11.77093426880123</v>
       </c>
       <c r="S10" t="n">
-        <v>17.71</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1946.3</v>
+        <v>2407.1</v>
       </c>
       <c r="U10" t="n">
-        <v>6084</v>
+        <v>8167</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9252852200268781</v>
+        <v>0.9188638094131923</v>
       </c>
       <c r="W10" t="n">
-        <v>1.015656761423235</v>
+        <v>1.025995810457242</v>
       </c>
       <c r="X10" t="n">
-        <v>87.43249999999999</v>
+        <v>38.74349999999998</v>
       </c>
       <c r="Y10" t="n">
-        <v>79.65289364749088</v>
+        <v>34.69799743542287</v>
       </c>
       <c r="Z10" t="n">
-        <v>1038736584</v>
+        <v>5281506921.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>009818.TW</t>
+          <t>00904.TW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>華南永昌NASDAQxT</t>
+          <t>台新臺灣半導體30</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.08969681154352349</v>
+        <v>1.70942383488989</v>
       </c>
       <c r="D11" t="n">
-        <v>0.07989367249948232</v>
+        <v>1.647458225646873</v>
       </c>
       <c r="E11" t="n">
-        <v>20.66</v>
+        <v>37.76</v>
       </c>
       <c r="F11" t="n">
-        <v>17.38</v>
+        <v>6.63</v>
       </c>
       <c r="G11" t="n">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H11" t="n">
-        <v>100</v>
+        <v>99.16</v>
       </c>
       <c r="I11" t="n">
-        <v>3.81</v>
+        <v>3.55</v>
       </c>
       <c r="J11" t="n">
-        <v>8.714285714285714</v>
+        <v>10.78242677824268</v>
       </c>
       <c r="K11" t="n">
-        <v>157366.45</v>
+        <v>4009061.95</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>7.21</v>
+        <v>11.85</v>
       </c>
       <c r="O11" t="n">
-        <v>1.65</v>
+        <v>-12.45</v>
       </c>
       <c r="P11" t="n">
-        <v>8.859999999999999</v>
+        <v>-0.5999999999999996</v>
       </c>
       <c r="Q11" t="n">
-        <v>222.85</v>
+        <v>37.53</v>
       </c>
       <c r="R11" t="n">
-        <v>0.009803139044041176</v>
+        <v>0.06196560924301675</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>7.050000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>79.97</v>
+        <v>848.62</v>
       </c>
       <c r="U11" t="n">
-        <v>183</v>
+        <v>2577</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9741147626007827</v>
+        <v>0.8992081919390367</v>
       </c>
       <c r="W11" t="n">
-        <v>1.004303207511007</v>
+        <v>1.029311773464305</v>
       </c>
       <c r="X11" t="n">
-        <v>21.209</v>
+        <v>41.9925</v>
       </c>
       <c r="Y11" t="n">
-        <v>20.57147666709367</v>
+        <v>36.68470620219662</v>
       </c>
       <c r="Z11" t="n">
-        <v>1737485.34</v>
+        <v>43644744.96</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>00663L.TW</t>
+          <t>00685L.TW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>國泰臺灣加權正2</t>
+          <t>群益臺灣加權正2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11.25922964735046</v>
+        <v>10.16256815379168</v>
       </c>
       <c r="D12" t="n">
-        <v>2.911450387831949</v>
+        <v>2.731453200941016</v>
       </c>
       <c r="E12" t="n">
-        <v>102.8</v>
+        <v>11.75</v>
       </c>
       <c r="F12" t="n">
-        <v>10.54</v>
+        <v>9.58</v>
       </c>
       <c r="G12" t="n">
-        <v>564</v>
+        <v>514</v>
       </c>
       <c r="H12" t="n">
-        <v>89.89</v>
+        <v>88.52</v>
       </c>
       <c r="I12" t="n">
-        <v>3.76</v>
+        <v>3.46</v>
       </c>
       <c r="J12" t="n">
-        <v>11.9113475177305</v>
+        <v>12.18093385214008</v>
       </c>
       <c r="K12" t="n">
-        <v>5518691.55</v>
+        <v>261073587.55</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1462,254 +1462,250 @@
         <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>15.99</v>
+        <v>15.89</v>
       </c>
       <c r="O12" t="n">
-        <v>-24.46</v>
+        <v>-18.5</v>
       </c>
       <c r="P12" t="n">
-        <v>-8.470000000000001</v>
+        <v>-2.609999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>18.35</v>
+        <v>18.65</v>
       </c>
       <c r="R12" t="n">
-        <v>8.347779259518511</v>
+        <v>7.431114952850666</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2121.97</v>
+        <v>1777.84</v>
       </c>
       <c r="U12" t="n">
-        <v>6718</v>
+        <v>6261</v>
       </c>
       <c r="V12" t="n">
-        <v>0.9141434351518379</v>
+        <v>0.9163579645155</v>
       </c>
       <c r="W12" t="n">
-        <v>1.014213044109562</v>
+        <v>1.025115813922667</v>
       </c>
       <c r="X12" t="n">
-        <v>112.4550000000001</v>
+        <v>12.8225</v>
       </c>
       <c r="Y12" t="n">
-        <v>101.3593747359602</v>
+        <v>11.46211953851138</v>
       </c>
       <c r="Z12" t="n">
-        <v>548819182.4</v>
+        <v>2473573304.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>00631L.TW</t>
+          <t>009809.TW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>富邦淨零ESG50</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15.09593933491448</v>
+        <v>0.339621216709336</v>
       </c>
       <c r="D13" t="n">
-        <v>3.328222133845613</v>
+        <v>0.2916316299414703</v>
       </c>
       <c r="E13" t="n">
-        <v>35.61</v>
+        <v>17.97</v>
       </c>
       <c r="F13" t="n">
-        <v>9.58</v>
+        <v>9.85</v>
       </c>
       <c r="G13" t="n">
-        <v>644</v>
+        <v>34</v>
       </c>
       <c r="H13" t="n">
-        <v>89.44</v>
+        <v>97.06</v>
       </c>
       <c r="I13" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="J13" t="n">
-        <v>12.68167701863354</v>
+        <v>8.235294117647058</v>
       </c>
       <c r="K13" t="n">
-        <v>194225595.25</v>
+        <v>288338.5</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>2</v>
       </c>
       <c r="N13" t="n">
-        <v>17.37</v>
+        <v>7.76</v>
       </c>
       <c r="O13" t="n">
-        <v>-12.43</v>
+        <v>-0.12</v>
       </c>
       <c r="P13" t="n">
-        <v>4.940000000000001</v>
+        <v>7.64</v>
       </c>
       <c r="Q13" t="n">
-        <v>15.49</v>
+        <v>172.16</v>
       </c>
       <c r="R13" t="n">
-        <v>11.76771720106886</v>
+        <v>0.04798958676786569</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
       <c r="T13" t="n">
-        <v>2407.1</v>
+        <v>115.56</v>
       </c>
       <c r="U13" t="n">
-        <v>8167</v>
+        <v>280</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9156713251648906</v>
+        <v>0.9705644072373748</v>
       </c>
       <c r="W13" t="n">
-        <v>1.014355095014336</v>
+        <v>1.009591592635989</v>
       </c>
       <c r="X13" t="n">
-        <v>38.88949999999998</v>
+        <v>18.515</v>
       </c>
       <c r="Y13" t="n">
-        <v>35.1060493263424</v>
+        <v>17.79927658973596</v>
       </c>
       <c r="Z13" t="n">
-        <v>7874153957.07</v>
+        <v>9024246.479999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>00904.TW</t>
+          <t>00715L.TW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>台新臺灣半導體30</t>
+          <t>期街口布蘭特正2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.701041216751999</v>
+        <v>5.987955068925254</v>
       </c>
       <c r="D14" t="n">
-        <v>1.656230220638771</v>
+        <v>2.592206134687774</v>
       </c>
       <c r="E14" t="n">
-        <v>37.6</v>
+        <v>87.05</v>
       </c>
       <c r="F14" t="n">
-        <v>7.42</v>
+        <v>94.33</v>
       </c>
       <c r="G14" t="n">
-        <v>239</v>
+        <v>425</v>
       </c>
       <c r="H14" t="n">
-        <v>99.16</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>3.55</v>
+        <v>3.32</v>
       </c>
       <c r="J14" t="n">
-        <v>10.78242677824268</v>
+        <v>17.11294117647059</v>
       </c>
       <c r="K14" t="n">
-        <v>4025045</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
+        <v>3113605.95</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>11.85</v>
+        <v>32.14</v>
       </c>
       <c r="O14" t="n">
-        <v>-12.45</v>
+        <v>-44.86</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.5999999999999996</v>
+        <v>-12.72</v>
       </c>
       <c r="Q14" t="n">
-        <v>37.53</v>
+        <v>14.59</v>
       </c>
       <c r="R14" t="n">
-        <v>0.04481099611322836</v>
+        <v>3.39574893423748</v>
       </c>
       <c r="S14" t="n">
-        <v>7.050000000000001</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>848.62</v>
+        <v>1409.31</v>
       </c>
       <c r="U14" t="n">
-        <v>2577</v>
+        <v>7273</v>
       </c>
       <c r="V14" t="n">
-        <v>0.8894461068991213</v>
+        <v>1.189532659196503</v>
       </c>
       <c r="W14" t="n">
-        <v>1.007834521042251</v>
+        <v>1.483194490295465</v>
       </c>
       <c r="X14" t="n">
-        <v>42.2735</v>
+        <v>73.17999999999995</v>
       </c>
       <c r="Y14" t="n">
-        <v>37.30771194572301</v>
+        <v>58.69088684563471</v>
       </c>
       <c r="Z14" t="n">
-        <v>60082882.40000001</v>
+        <v>329223970.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>00685L.TW</t>
+          <t>00675L.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>群益臺灣加權正2</t>
+          <t>富邦臺灣加權正2</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10.19552719656999</v>
+        <v>10.67242119452606</v>
       </c>
       <c r="D15" t="n">
-        <v>2.742863585316234</v>
+        <v>2.836910003943229</v>
       </c>
       <c r="E15" t="n">
-        <v>11.78</v>
+        <v>310.5</v>
       </c>
       <c r="F15" t="n">
-        <v>10.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>514</v>
+        <v>564</v>
       </c>
       <c r="H15" t="n">
-        <v>88.52</v>
+        <v>87.06</v>
       </c>
       <c r="I15" t="n">
-        <v>3.46</v>
+        <v>3.18</v>
       </c>
       <c r="J15" t="n">
-        <v>12.18093385214008</v>
+        <v>12.38297872340426</v>
       </c>
       <c r="K15" t="n">
-        <v>264409179.35</v>
+        <v>1174727.6</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1720,336 +1716,340 @@
         <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>15.89</v>
+        <v>15.7</v>
       </c>
       <c r="O15" t="n">
-        <v>-18.5</v>
+        <v>-24.73</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.609999999999999</v>
+        <v>-9.030000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>18.65</v>
+        <v>16.61</v>
       </c>
       <c r="R15" t="n">
-        <v>7.452663611253757</v>
+        <v>7.835511190582833</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1777.84</v>
+        <v>1792.47</v>
       </c>
       <c r="U15" t="n">
-        <v>6261</v>
+        <v>6984</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9150580650172833</v>
+        <v>0.9154363801198465</v>
       </c>
       <c r="W15" t="n">
-        <v>1.015136195630888</v>
+        <v>1.025790910999746</v>
       </c>
       <c r="X15" t="n">
-        <v>12.8735</v>
+        <v>339.1825000000002</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.604354224291</v>
+        <v>302.6932649436168</v>
       </c>
       <c r="Z15" t="n">
-        <v>4079711821.96</v>
+        <v>243390703.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>009809.TW</t>
+          <t>00935.TW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>富邦淨零ESG50</t>
+          <t>野村臺灣新科技50</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.3373099687703147</v>
+        <v>1.346793304092792</v>
       </c>
       <c r="D16" t="n">
-        <v>0.296412555363438</v>
+        <v>1.086270127628979</v>
       </c>
       <c r="E16" t="n">
-        <v>17.92</v>
+        <v>54.7</v>
       </c>
       <c r="F16" t="n">
-        <v>10.42</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>34</v>
+        <v>136</v>
       </c>
       <c r="H16" t="n">
-        <v>97.06</v>
+        <v>83.09</v>
       </c>
       <c r="I16" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="J16" t="n">
-        <v>8.235294117647058</v>
+        <v>12.30882352941176</v>
       </c>
       <c r="K16" t="n">
-        <v>266234.2</v>
+        <v>12187820.9</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>7.76</v>
+        <v>14.6</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.12</v>
+        <v>-8.99</v>
       </c>
       <c r="P16" t="n">
-        <v>7.64</v>
+        <v>5.609999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>172.16</v>
+        <v>43.74</v>
       </c>
       <c r="R16" t="n">
-        <v>0.04089741340687669</v>
+        <v>0.2605231764638134</v>
       </c>
       <c r="S16" t="n">
-        <v>0.315</v>
+        <v>4.98</v>
       </c>
       <c r="T16" t="n">
-        <v>115.56</v>
+        <v>428.12</v>
       </c>
       <c r="U16" t="n">
-        <v>280</v>
+        <v>1674</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9660637753039164</v>
+        <v>0.915481171548117</v>
       </c>
       <c r="W16" t="n">
-        <v>1.00240710746446</v>
+        <v>1.014265810432367</v>
       </c>
       <c r="X16" t="n">
-        <v>18.54950000000001</v>
+        <v>59.75000000000001</v>
       </c>
       <c r="Y16" t="n">
-        <v>17.87696821636447</v>
+        <v>53.93063577355741</v>
       </c>
       <c r="Z16" t="n">
-        <v>6584865.28</v>
+        <v>519592455.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>00715L.TW</t>
+          <t>00894.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>期街口布蘭特正2</t>
+          <t>中信小資高價30</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5.693591246218765</v>
+        <v>1.922000294969721</v>
       </c>
       <c r="D17" t="n">
-        <v>2.603248403475678</v>
+        <v>1.698089875876663</v>
       </c>
       <c r="E17" t="n">
-        <v>83.34999999999999</v>
+        <v>45.25</v>
       </c>
       <c r="F17" t="n">
-        <v>94.37</v>
+        <v>9.01</v>
       </c>
       <c r="G17" t="n">
-        <v>425</v>
+        <v>243</v>
       </c>
       <c r="H17" t="n">
-        <v>77.65000000000001</v>
+        <v>82.72</v>
       </c>
       <c r="I17" t="n">
-        <v>3.32</v>
+        <v>2.88</v>
       </c>
       <c r="J17" t="n">
-        <v>17.11294117647059</v>
+        <v>15.32921810699589</v>
       </c>
       <c r="K17" t="n">
-        <v>3123134.4</v>
-      </c>
-      <c r="L17" t="inlineStr"/>
+        <v>1259389.7</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="M17" t="n">
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>32.14</v>
+        <v>15.7</v>
       </c>
       <c r="O17" t="n">
-        <v>-44.86</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>-12.72</v>
+        <v>7.319999999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>14.59</v>
+        <v>22.58</v>
       </c>
       <c r="R17" t="n">
-        <v>3.090342842743087</v>
+        <v>0.2239104190930581</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>7.549999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>1409.31</v>
+        <v>698.73</v>
       </c>
       <c r="U17" t="n">
-        <v>7273</v>
+        <v>3725</v>
       </c>
       <c r="V17" t="n">
-        <v>1.156755256401361</v>
+        <v>0.913504729027244</v>
       </c>
       <c r="W17" t="n">
-        <v>1.422584797114059</v>
+        <v>1.003318790164492</v>
       </c>
       <c r="X17" t="n">
-        <v>72.05499999999995</v>
+        <v>49.53449999999998</v>
       </c>
       <c r="Y17" t="n">
-        <v>58.59053194515278</v>
+        <v>45.10032149660163</v>
       </c>
       <c r="Z17" t="n">
-        <v>241625065.35</v>
+        <v>71837135.25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>00675L.TW</t>
+          <t>00901.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>富邦臺灣加權正2</t>
+          <t>永豐智能車供應鏈</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10.695589391348</v>
+        <v>1.70023886133263</v>
       </c>
       <c r="D18" t="n">
-        <v>2.848567568452024</v>
+        <v>1.663742088908547</v>
       </c>
       <c r="E18" t="n">
-        <v>311</v>
+        <v>44.14</v>
       </c>
       <c r="F18" t="n">
-        <v>10.5</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>564</v>
+        <v>276</v>
       </c>
       <c r="H18" t="n">
-        <v>87.06</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>3.18</v>
+        <v>2.79</v>
       </c>
       <c r="J18" t="n">
-        <v>12.38297872340426</v>
+        <v>13.22463768115942</v>
       </c>
       <c r="K18" t="n">
-        <v>1205063.05</v>
+        <v>283133.55</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>15.7</v>
+        <v>15.18</v>
       </c>
       <c r="O18" t="n">
-        <v>-24.73</v>
+        <v>-7.3</v>
       </c>
       <c r="P18" t="n">
-        <v>-9.030000000000001</v>
+        <v>7.88</v>
       </c>
       <c r="Q18" t="n">
-        <v>16.61</v>
+        <v>24.17</v>
       </c>
       <c r="R18" t="n">
-        <v>7.84702182289598</v>
+        <v>0.03649677242408345</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>4.671</v>
       </c>
       <c r="T18" t="n">
-        <v>1792.47</v>
+        <v>771.28</v>
       </c>
       <c r="U18" t="n">
-        <v>6984</v>
+        <v>3650</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9130945390487371</v>
+        <v>0.9289013752538484</v>
       </c>
       <c r="W18" t="n">
-        <v>1.014492553251156</v>
+        <v>1.013543830740695</v>
       </c>
       <c r="X18" t="n">
-        <v>340.6000000000002</v>
+        <v>47.5185</v>
       </c>
       <c r="Y18" t="n">
-        <v>306.5572034051257</v>
+        <v>43.55016395072192</v>
       </c>
       <c r="Z18" t="n">
-        <v>307076735</v>
+        <v>24756757.66</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>00935.TW</t>
+          <t>0057.TW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>野村臺灣新科技50</t>
+          <t>富邦摩台</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.364663806801542</v>
+        <v>6.040692318946351</v>
       </c>
       <c r="D19" t="n">
-        <v>1.093561942376952</v>
+        <v>4.809135616516254</v>
       </c>
       <c r="E19" t="n">
-        <v>55.1</v>
+        <v>317.6</v>
       </c>
       <c r="F19" t="n">
-        <v>8.91</v>
+        <v>7.76</v>
       </c>
       <c r="G19" t="n">
-        <v>136</v>
+        <v>1245</v>
       </c>
       <c r="H19" t="n">
-        <v>83.09</v>
+        <v>93.33</v>
       </c>
       <c r="I19" t="n">
-        <v>3.15</v>
+        <v>2.64</v>
       </c>
       <c r="J19" t="n">
-        <v>12.30882352941176</v>
+        <v>12.02409638554217</v>
       </c>
       <c r="K19" t="n">
-        <v>12744295.55</v>
+        <v>30973.7</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -2060,168 +2060,168 @@
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>14.6</v>
+        <v>14.45</v>
       </c>
       <c r="O19" t="n">
-        <v>-8.99</v>
+        <v>-6.48</v>
       </c>
       <c r="P19" t="n">
-        <v>5.609999999999999</v>
+        <v>7.969999999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>43.74</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2711018644245899</v>
+        <v>1.231556702430098</v>
       </c>
       <c r="S19" t="n">
-        <v>4.98</v>
+        <v>1.685</v>
       </c>
       <c r="T19" t="n">
-        <v>428.12</v>
+        <v>3287.55</v>
       </c>
       <c r="U19" t="n">
-        <v>1674</v>
+        <v>14970</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9173395488221092</v>
+        <v>0.9565256674748144</v>
       </c>
       <c r="W19" t="n">
-        <v>1.007135499668602</v>
+        <v>1.012894740499916</v>
       </c>
       <c r="X19" t="n">
-        <v>60.06500000000001</v>
+        <v>332.035</v>
       </c>
       <c r="Y19" t="n">
-        <v>54.70961952798871</v>
+        <v>313.5567668593559</v>
       </c>
       <c r="Z19" t="n">
-        <v>615959428.7</v>
+        <v>6270059.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>00894.TW</t>
+          <t>00881.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>中信小資高價30</t>
+          <t>國泰台灣科技龍頭</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.962923524208284</v>
+        <v>1.906883058632524</v>
       </c>
       <c r="D20" t="n">
-        <v>1.706878531101225</v>
+        <v>1.764217461822757</v>
       </c>
       <c r="E20" t="n">
-        <v>45.94</v>
+        <v>48.24</v>
       </c>
       <c r="F20" t="n">
-        <v>9.970000000000001</v>
+        <v>6.94</v>
       </c>
       <c r="G20" t="n">
-        <v>243</v>
+        <v>384</v>
       </c>
       <c r="H20" t="n">
-        <v>82.72</v>
+        <v>89.58</v>
       </c>
       <c r="I20" t="n">
-        <v>2.88</v>
+        <v>2.52</v>
       </c>
       <c r="J20" t="n">
-        <v>15.32921810699589</v>
+        <v>15.328125</v>
       </c>
       <c r="K20" t="n">
-        <v>1244910.7</v>
+        <v>17280006.9</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>15.7</v>
+        <v>10.9</v>
       </c>
       <c r="O20" t="n">
-        <v>-8.380000000000001</v>
+        <v>-4.28</v>
       </c>
       <c r="P20" t="n">
-        <v>7.319999999999999</v>
+        <v>6.62</v>
       </c>
       <c r="Q20" t="n">
-        <v>22.58</v>
+        <v>15.81</v>
       </c>
       <c r="R20" t="n">
-        <v>0.256044993107059</v>
+        <v>0.1426655968097665</v>
       </c>
       <c r="S20" t="n">
-        <v>7.549999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="T20" t="n">
-        <v>698.73</v>
+        <v>966.91</v>
       </c>
       <c r="U20" t="n">
-        <v>3725</v>
+        <v>5886</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9232778978043514</v>
+        <v>0.9334907212105968</v>
       </c>
       <c r="W20" t="n">
-        <v>1.003432376723027</v>
+        <v>1.007313066654775</v>
       </c>
       <c r="X20" t="n">
-        <v>49.75749999999998</v>
+        <v>51.67699999999999</v>
       </c>
       <c r="Y20" t="n">
-        <v>45.78285599078355</v>
+        <v>47.88977885514984</v>
       </c>
       <c r="Z20" t="n">
-        <v>73000819.17999999</v>
+        <v>1194309036</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>00901.TW</t>
+          <t>0052.TW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>永豐智能車供應鏈</t>
+          <t>富邦科技</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.718705169458816</v>
+        <v>8.089669984550468</v>
       </c>
       <c r="D21" t="n">
-        <v>1.672509106053912</v>
+        <v>4.901728310967869</v>
       </c>
       <c r="E21" t="n">
-        <v>44.44</v>
+        <v>61.75</v>
       </c>
       <c r="F21" t="n">
-        <v>8.84</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>276</v>
+        <v>1111</v>
       </c>
       <c r="H21" t="n">
-        <v>89.48999999999999</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>2.79</v>
+        <v>2.45</v>
       </c>
       <c r="J21" t="n">
-        <v>13.22463768115942</v>
+        <v>14.18091809180918</v>
       </c>
       <c r="K21" t="n">
-        <v>259846.35</v>
+        <v>20495983.7</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -2232,426 +2232,426 @@
         <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>15.18</v>
+        <v>12.7</v>
       </c>
       <c r="O21" t="n">
-        <v>-7.3</v>
+        <v>-14.18</v>
       </c>
       <c r="P21" t="n">
-        <v>7.88</v>
+        <v>-1.48</v>
       </c>
       <c r="Q21" t="n">
-        <v>24.17</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="R21" t="n">
-        <v>0.04619606340490412</v>
+        <v>3.1879416735826</v>
       </c>
       <c r="S21" t="n">
-        <v>4.671</v>
+        <v>2.232857285714286</v>
       </c>
       <c r="T21" t="n">
-        <v>771.28</v>
+        <v>2723.42</v>
       </c>
       <c r="U21" t="n">
-        <v>3650</v>
+        <v>15755</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9311681508643268</v>
+        <v>0.9506581479485787</v>
       </c>
       <c r="W21" t="n">
-        <v>1.008546480236058</v>
+        <v>1.012170936840371</v>
       </c>
       <c r="X21" t="n">
-        <v>47.725</v>
+        <v>64.95500000000007</v>
       </c>
       <c r="Y21" t="n">
-        <v>44.0634129124108</v>
+        <v>61.00748179231564</v>
       </c>
       <c r="Z21" t="n">
-        <v>11380772.92</v>
+        <v>1149569430.75</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>0057.TW</t>
+          <t>00735.TW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>富邦摩台</t>
+          <t>國泰臺韓科技</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6.046462224145085</v>
+        <v>2.858739407784587</v>
       </c>
       <c r="D22" t="n">
-        <v>4.825956592107342</v>
+        <v>2.472685684082697</v>
       </c>
       <c r="E22" t="n">
-        <v>317.8</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>8.720000000000001</v>
+        <v>13.12</v>
       </c>
       <c r="G22" t="n">
-        <v>1245</v>
+        <v>498</v>
       </c>
       <c r="H22" t="n">
-        <v>93.33</v>
+        <v>86.55</v>
       </c>
       <c r="I22" t="n">
-        <v>2.64</v>
+        <v>2.28</v>
       </c>
       <c r="J22" t="n">
-        <v>12.02409638554217</v>
+        <v>13.81124497991968</v>
       </c>
       <c r="K22" t="n">
-        <v>31496.05</v>
+        <v>1841089.65</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>14.45</v>
+        <v>21.39</v>
       </c>
       <c r="O22" t="n">
-        <v>-6.48</v>
+        <v>-6.04</v>
       </c>
       <c r="P22" t="n">
-        <v>7.969999999999999</v>
+        <v>15.35</v>
       </c>
       <c r="Q22" t="n">
-        <v>8.970000000000001</v>
+        <v>14.26</v>
       </c>
       <c r="R22" t="n">
-        <v>1.220505632037742</v>
+        <v>0.3860537237018908</v>
       </c>
       <c r="S22" t="n">
-        <v>1.685</v>
+        <v>13.37</v>
       </c>
       <c r="T22" t="n">
-        <v>3287.55</v>
+        <v>1133.84</v>
       </c>
       <c r="U22" t="n">
-        <v>14970</v>
+        <v>6878</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9547700950864491</v>
+        <v>0.9275223880597027</v>
       </c>
       <c r="W22" t="n">
-        <v>1.006981838902337</v>
+        <v>1.047834878866253</v>
       </c>
       <c r="X22" t="n">
-        <v>332.855</v>
+        <v>104.6874999999999</v>
       </c>
       <c r="Y22" t="n">
-        <v>315.5965556900397</v>
+        <v>92.6672722567331</v>
       </c>
       <c r="Z22" t="n">
-        <v>2602146.4</v>
+        <v>122830140.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>00881.TW</t>
+          <t>0050.TW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>國泰台灣科技龍頭</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.936136014854752</v>
+        <v>5.42350102005824</v>
       </c>
       <c r="D23" t="n">
-        <v>1.773072221106335</v>
+        <v>5.42350102005824</v>
       </c>
       <c r="E23" t="n">
-        <v>48.8</v>
+        <v>106.6</v>
       </c>
       <c r="F23" t="n">
-        <v>7.45</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>384</v>
+        <v>1695</v>
       </c>
       <c r="H23" t="n">
-        <v>89.58</v>
+        <v>90.97</v>
       </c>
       <c r="I23" t="n">
-        <v>2.52</v>
+        <v>2.26</v>
       </c>
       <c r="J23" t="n">
-        <v>15.328125</v>
+        <v>13.46961651917404</v>
       </c>
       <c r="K23" t="n">
-        <v>16954565.1</v>
+        <v>120274806.65</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M23" t="n">
         <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>10.9</v>
+        <v>13.94</v>
       </c>
       <c r="O23" t="n">
-        <v>-4.28</v>
+        <v>-5.91</v>
       </c>
       <c r="P23" t="n">
-        <v>6.62</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="Q23" t="n">
-        <v>15.81</v>
+        <v>6.04</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1630637937484178</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>12.5</v>
+        <v>4.84625</v>
       </c>
       <c r="T23" t="n">
-        <v>966.91</v>
+        <v>3824.71</v>
       </c>
       <c r="U23" t="n">
-        <v>5886</v>
+        <v>22831</v>
       </c>
       <c r="V23" t="n">
-        <v>0.9407228915662653</v>
+        <v>0.9549832026875695</v>
       </c>
       <c r="W23" t="n">
-        <v>1.007671035595253</v>
+        <v>1.011644346050481</v>
       </c>
       <c r="X23" t="n">
-        <v>51.87499999999999</v>
+        <v>111.625</v>
       </c>
       <c r="Y23" t="n">
-        <v>48.42850322791387</v>
+        <v>105.3730003198977</v>
       </c>
       <c r="Z23" t="n">
-        <v>923159848</v>
+        <v>16363070045.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>0052.TW</t>
+          <t>0053.TW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>富邦科技</t>
+          <t>元大科技市值</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8.098475448463127</v>
+        <v>6.57200812316626</v>
       </c>
       <c r="D24" t="n">
-        <v>4.9187882871038</v>
+        <v>4.865383838883048</v>
       </c>
       <c r="E24" t="n">
-        <v>61.8</v>
+        <v>237.4</v>
       </c>
       <c r="F24" t="n">
-        <v>9.69</v>
+        <v>7.69</v>
       </c>
       <c r="G24" t="n">
-        <v>1111</v>
+        <v>1190</v>
       </c>
       <c r="H24" t="n">
-        <v>88.20999999999999</v>
+        <v>89.16</v>
       </c>
       <c r="I24" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="J24" t="n">
-        <v>14.18091809180918</v>
+        <v>13.83697478991597</v>
       </c>
       <c r="K24" t="n">
-        <v>20397584.85</v>
+        <v>495754.6</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>12.7</v>
+        <v>11.49</v>
       </c>
       <c r="O24" t="n">
-        <v>-14.18</v>
+        <v>-7.24</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.48</v>
+        <v>4.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>8.050000000000001</v>
+        <v>7.58</v>
       </c>
       <c r="R24" t="n">
-        <v>3.179687161359327</v>
+        <v>1.706624284283212</v>
       </c>
       <c r="S24" t="n">
-        <v>2.232857285714286</v>
+        <v>18.91</v>
       </c>
       <c r="T24" t="n">
-        <v>2723.42</v>
+        <v>2598</v>
       </c>
       <c r="U24" t="n">
-        <v>15755</v>
+        <v>16466</v>
       </c>
       <c r="V24" t="n">
-        <v>0.9492358497811216</v>
+        <v>0.9462125590386412</v>
       </c>
       <c r="W24" t="n">
-        <v>1.005892143440553</v>
+        <v>1.013974565412509</v>
       </c>
       <c r="X24" t="n">
-        <v>65.10500000000008</v>
+        <v>250.8950000000001</v>
       </c>
       <c r="Y24" t="n">
-        <v>61.43799850013673</v>
+        <v>234.1281607033408</v>
       </c>
       <c r="Z24" t="n">
-        <v>1251534233.4</v>
+        <v>127373409</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>00735.TW</t>
+          <t>00892.TW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>國泰臺韓科技</t>
+          <t>富邦台灣半導體</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.807903913852103</v>
+        <v>1.777065164027912</v>
       </c>
       <c r="D25" t="n">
-        <v>2.483423711696157</v>
+        <v>1.714698657403997</v>
       </c>
       <c r="E25" t="n">
-        <v>95.65000000000001</v>
+        <v>39.84</v>
       </c>
       <c r="F25" t="n">
-        <v>10.36</v>
+        <v>11.05</v>
       </c>
       <c r="G25" t="n">
-        <v>498</v>
+        <v>241</v>
       </c>
       <c r="H25" t="n">
-        <v>86.55</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="J25" t="n">
-        <v>13.81124497991968</v>
+        <v>15.85892116182573</v>
       </c>
       <c r="K25" t="n">
-        <v>1916367.85</v>
+        <v>4395759.1</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>2</v>
       </c>
       <c r="N25" t="n">
-        <v>21.39</v>
+        <v>12.37</v>
       </c>
       <c r="O25" t="n">
-        <v>-6.04</v>
+        <v>-7.43</v>
       </c>
       <c r="P25" t="n">
-        <v>15.35</v>
+        <v>4.94</v>
       </c>
       <c r="Q25" t="n">
-        <v>14.26</v>
+        <v>18.86</v>
       </c>
       <c r="R25" t="n">
-        <v>0.3244802021559456</v>
+        <v>0.06236650662391474</v>
       </c>
       <c r="S25" t="n">
-        <v>13.37</v>
+        <v>4.937</v>
       </c>
       <c r="T25" t="n">
-        <v>1133.84</v>
+        <v>510.5</v>
       </c>
       <c r="U25" t="n">
-        <v>6878</v>
+        <v>3822</v>
       </c>
       <c r="V25" t="n">
-        <v>0.9085943622503516</v>
+        <v>0.9395894013183493</v>
       </c>
       <c r="W25" t="n">
-        <v>1.021310581878393</v>
+        <v>1.010771656801848</v>
       </c>
       <c r="X25" t="n">
-        <v>105.2724999999999</v>
+        <v>42.40150000000001</v>
       </c>
       <c r="Y25" t="n">
-        <v>93.6541750346703</v>
+        <v>39.41543050985079</v>
       </c>
       <c r="Z25" t="n">
-        <v>239170338.1</v>
+        <v>135034572.48</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>0050.TW</t>
+          <t>006208.TW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>元大台灣50</t>
+          <t>富邦台50</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5.44182433494266</v>
+        <v>4.038818899709984</v>
       </c>
       <c r="D26" t="n">
-        <v>5.44182433494266</v>
+        <v>3.773855012175114</v>
       </c>
       <c r="E26" t="n">
-        <v>106.9</v>
+        <v>244.6</v>
       </c>
       <c r="F26" t="n">
-        <v>9.550000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="G26" t="n">
-        <v>1695</v>
+        <v>895</v>
       </c>
       <c r="H26" t="n">
-        <v>90.97</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>2.26</v>
+        <v>1.95</v>
       </c>
       <c r="J26" t="n">
-        <v>13.46961651917404</v>
+        <v>13.86703910614525</v>
       </c>
       <c r="K26" t="n">
-        <v>116815298.9</v>
+        <v>3353304</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -2662,383 +2662,125 @@
         <v>2</v>
       </c>
       <c r="N26" t="n">
-        <v>13.94</v>
+        <v>11.21</v>
       </c>
       <c r="O26" t="n">
-        <v>-5.91</v>
+        <v>-6.25</v>
       </c>
       <c r="P26" t="n">
-        <v>8.029999999999999</v>
+        <v>4.960000000000001</v>
       </c>
       <c r="Q26" t="n">
-        <v>6.04</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>0.2649638875348694</v>
       </c>
       <c r="S26" t="n">
-        <v>4.84625</v>
+        <v>28.764</v>
       </c>
       <c r="T26" t="n">
-        <v>3824.71</v>
+        <v>1745.92</v>
       </c>
       <c r="U26" t="n">
-        <v>22831</v>
+        <v>12411</v>
       </c>
       <c r="V26" t="n">
-        <v>0.9554239749748628</v>
+        <v>0.9568610575935683</v>
       </c>
       <c r="W26" t="n">
-        <v>1.007766660763678</v>
+        <v>1.01217895853859</v>
       </c>
       <c r="X26" t="n">
-        <v>111.8875</v>
+        <v>255.6275000000001</v>
       </c>
       <c r="Y26" t="n">
-        <v>106.0761425854195</v>
+        <v>241.6568709876757</v>
       </c>
       <c r="Z26" t="n">
-        <v>14158028954.5</v>
+        <v>1524960901.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>0053.TW</t>
+          <t>009823.TWO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>元大科技市值</t>
+          <t>群益S&amp;P500</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6.592821644129143</v>
+        <v>0.02873852359408247</v>
       </c>
       <c r="D27" t="n">
-        <v>4.882307814546531</v>
+        <v>0.001194952732069154</v>
       </c>
       <c r="E27" t="n">
-        <v>238.05</v>
+        <v>10.74</v>
       </c>
       <c r="F27" t="n">
-        <v>7.01</v>
+        <v>68.06</v>
       </c>
       <c r="G27" t="n">
-        <v>1190</v>
+        <v>15</v>
       </c>
       <c r="H27" t="n">
-        <v>89.16</v>
+        <v>100</v>
       </c>
       <c r="I27" t="n">
-        <v>2.18</v>
+        <v>1.31</v>
       </c>
       <c r="J27" t="n">
-        <v>13.83697478991597</v>
+        <v>16.93333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>476981.85</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
+        <v>3533665.3</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="n">
         <v>2</v>
       </c>
       <c r="N27" t="n">
-        <v>11.49</v>
+        <v>3.64</v>
       </c>
       <c r="O27" t="n">
-        <v>-7.24</v>
+        <v>0.45</v>
       </c>
       <c r="P27" t="n">
-        <v>4.25</v>
+        <v>4.09</v>
       </c>
       <c r="Q27" t="n">
-        <v>7.58</v>
+        <v>29.52</v>
       </c>
       <c r="R27" t="n">
-        <v>1.710513829582612</v>
+        <v>0.02754357086201331</v>
       </c>
       <c r="S27" t="n">
-        <v>18.91</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2598</v>
+        <v>19.72</v>
       </c>
       <c r="U27" t="n">
-        <v>16466</v>
+        <v>254</v>
       </c>
       <c r="V27" t="n">
-        <v>0.946154075457824</v>
+        <v>1.01134705023777</v>
       </c>
       <c r="W27" t="n">
-        <v>1.008619202489728</v>
+        <v>1.032899179677986</v>
       </c>
       <c r="X27" t="n">
-        <v>251.5975000000001</v>
+        <v>10.6195</v>
       </c>
       <c r="Y27" t="n">
-        <v>236.0157326098739</v>
+        <v>10.3979170584183</v>
       </c>
       <c r="Z27" t="n">
-        <v>157493880</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>00892.TW</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>富邦台灣半導體</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>1.779711358373551</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1.723497032196059</v>
-      </c>
-      <c r="E28" t="n">
-        <v>39.86</v>
-      </c>
-      <c r="F28" t="n">
-        <v>10.71</v>
-      </c>
-      <c r="G28" t="n">
-        <v>241</v>
-      </c>
-      <c r="H28" t="n">
-        <v>75.09999999999999</v>
-      </c>
-      <c r="I28" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="J28" t="n">
-        <v>15.85892116182573</v>
-      </c>
-      <c r="K28" t="n">
-        <v>4500101.1</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="M28" t="n">
-        <v>2</v>
-      </c>
-      <c r="N28" t="n">
-        <v>12.37</v>
-      </c>
-      <c r="O28" t="n">
-        <v>-7.43</v>
-      </c>
-      <c r="P28" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>18.86</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0.05621432617749189</v>
-      </c>
-      <c r="S28" t="n">
-        <v>4.937</v>
-      </c>
-      <c r="T28" t="n">
-        <v>510.5</v>
-      </c>
-      <c r="U28" t="n">
-        <v>3822</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0.9360762763609035</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.001300956336052</v>
-      </c>
-      <c r="X28" t="n">
-        <v>42.58200000000001</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>39.80821125534046</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>150566924.84</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>006208.TW</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>富邦台50</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>4.044773778041981</v>
-      </c>
-      <c r="D29" t="n">
-        <v>3.787997617953844</v>
-      </c>
-      <c r="E29" t="n">
-        <v>244.85</v>
-      </c>
-      <c r="F29" t="n">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="G29" t="n">
-        <v>895</v>
-      </c>
-      <c r="H29" t="n">
-        <v>88.48999999999999</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="J29" t="n">
-        <v>13.86703910614525</v>
-      </c>
-      <c r="K29" t="n">
-        <v>3158750.7</v>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="M29" t="n">
-        <v>2</v>
-      </c>
-      <c r="N29" t="n">
-        <v>11.21</v>
-      </c>
-      <c r="O29" t="n">
-        <v>-6.25</v>
-      </c>
-      <c r="P29" t="n">
-        <v>4.960000000000001</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0.2567761600881369</v>
-      </c>
-      <c r="S29" t="n">
-        <v>28.764</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1745.92</v>
-      </c>
-      <c r="U29" t="n">
-        <v>12411</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0.9557639573351027</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.006956638074854</v>
-      </c>
-      <c r="X29" t="n">
-        <v>256.1825000000001</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>243.1584347744263</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>615465488.55</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>009823.TWO</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>群益S&amp;P500</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>0.02717262655342534</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.004023674744812133</v>
-      </c>
-      <c r="E30" t="n">
-        <v>10.72</v>
-      </c>
-      <c r="F30" t="n">
-        <v>68.75</v>
-      </c>
-      <c r="G30" t="n">
-        <v>15</v>
-      </c>
-      <c r="H30" t="n">
-        <v>100</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="J30" t="n">
-        <v>16.93333333333333</v>
-      </c>
-      <c r="K30" t="n">
-        <v>3324514.25</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="n">
-        <v>2</v>
-      </c>
-      <c r="N30" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="P30" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>29.52</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0.02314895180861321</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>19.72</v>
-      </c>
-      <c r="U30" t="n">
-        <v>254</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.010605703511666</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.032026555525566</v>
-      </c>
-      <c r="X30" t="n">
-        <v>10.6075</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>10.38732961143696</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>35706100.96</v>
+        <v>107869627.98</v>
       </c>
     </row>
   </sheetData>

--- a/ETF動態清單.xlsx
+++ b/ETF動態清單.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z27"/>
+  <dimension ref="A1:Z31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,16 +567,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5974557964381386</v>
+        <v>0.6647743620677875</v>
       </c>
       <c r="D2" t="n">
-        <v>0.508125151263835</v>
+        <v>0.5352415408982445</v>
       </c>
       <c r="E2" t="n">
-        <v>27.4</v>
+        <v>28.65</v>
       </c>
       <c r="F2" t="n">
-        <v>7.67</v>
+        <v>16.38</v>
       </c>
       <c r="G2" t="n">
         <v>41</v>
@@ -591,7 +591,7 @@
         <v>8.439024390243903</v>
       </c>
       <c r="K2" t="n">
-        <v>170635036.05</v>
+        <v>165439924.5</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         <v>386.28</v>
       </c>
       <c r="R2" t="n">
-        <v>0.08933064517430367</v>
+        <v>0.129532821169543</v>
       </c>
       <c r="S2" t="n">
         <v>1.67</v>
@@ -626,316 +626,316 @@
         <v>346</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8975954923671624</v>
+        <v>0.941628870045356</v>
       </c>
       <c r="W2" t="n">
-        <v>0.995162470835485</v>
+        <v>1.048499642538038</v>
       </c>
       <c r="X2" t="n">
-        <v>30.526</v>
+        <v>30.426</v>
       </c>
       <c r="Y2" t="n">
-        <v>27.5331926223026</v>
+        <v>27.32475895809436</v>
       </c>
       <c r="Z2" t="n">
-        <v>7598889155.4</v>
+        <v>3456939856.05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>00947.TW</t>
+          <t>00992A.TW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>台新臺灣IC設計</t>
+          <t>主動群益科技創新</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.108033706688896</v>
+        <v>0.2035366679819564</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8467376334148036</v>
+        <v>0.195842705192713</v>
       </c>
       <c r="E3" t="n">
-        <v>34.26</v>
+        <v>17.24</v>
       </c>
       <c r="F3" t="n">
-        <v>9.539999999999999</v>
+        <v>16.21</v>
       </c>
       <c r="G3" t="n">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="H3" t="n">
-        <v>96.97</v>
+        <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>7.5</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>10.33333333333333</v>
+        <v>10.27272727272727</v>
       </c>
       <c r="K3" t="n">
-        <v>12410892.9</v>
+        <v>56533210.25</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>18.77</v>
+        <v>15.18</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.73</v>
+        <v>2.64</v>
       </c>
       <c r="P3" t="n">
-        <v>18.04</v>
+        <v>17.82</v>
       </c>
       <c r="Q3" t="n">
-        <v>159.78</v>
+        <v>317.42</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2612960732740925</v>
+        <v>0.007693962789243391</v>
       </c>
       <c r="S3" t="n">
-        <v>2.78</v>
+        <v>1.32</v>
       </c>
       <c r="T3" t="n">
-        <v>495.22</v>
+        <v>277.02</v>
       </c>
       <c r="U3" t="n">
-        <v>682</v>
+        <v>339</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8899510345096304</v>
+        <v>0.9219251336898399</v>
       </c>
       <c r="W3" t="n">
-        <v>1.032576298115363</v>
+        <v>1.054703846130648</v>
       </c>
       <c r="X3" t="n">
-        <v>38.49650000000001</v>
+        <v>18.69999999999999</v>
       </c>
       <c r="Y3" t="n">
-        <v>33.17914624084499</v>
+        <v>16.34582073749682</v>
       </c>
       <c r="Z3" t="n">
-        <v>269346946.74</v>
+        <v>722953848.7199999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>00985A.TW</t>
+          <t>00947.TW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>主動野村台灣50</t>
+          <t>台新臺灣IC設計</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.4423916519640649</v>
+        <v>1.219081336269761</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4253052321766908</v>
+        <v>0.8801740251202617</v>
       </c>
       <c r="E4" t="n">
-        <v>20.23</v>
+        <v>36.24</v>
       </c>
       <c r="F4" t="n">
-        <v>5.23</v>
+        <v>20.49</v>
       </c>
       <c r="G4" t="n">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="H4" t="n">
-        <v>100</v>
+        <v>96.97</v>
       </c>
       <c r="I4" t="n">
-        <v>6.95</v>
+        <v>7.5</v>
       </c>
       <c r="J4" t="n">
-        <v>9.972972972972974</v>
+        <v>10.33333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>60093537.55</v>
+        <v>12399993.05</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>15.02</v>
+        <v>18.77</v>
       </c>
       <c r="O4" t="n">
-        <v>2.1</v>
+        <v>-0.73</v>
       </c>
       <c r="P4" t="n">
-        <v>17.12</v>
+        <v>18.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>252.13</v>
+        <v>159.78</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01708641978737413</v>
+        <v>0.3389073111494998</v>
       </c>
       <c r="S4" t="n">
-        <v>2.15</v>
+        <v>2.78</v>
       </c>
       <c r="T4" t="n">
-        <v>257.02</v>
+        <v>495.22</v>
       </c>
       <c r="U4" t="n">
-        <v>369</v>
+        <v>682</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8803690325949778</v>
+        <v>0.9469558400836162</v>
       </c>
       <c r="W4" t="n">
-        <v>1.016908162083496</v>
+        <v>1.099066690115482</v>
       </c>
       <c r="X4" t="n">
-        <v>22.97900000000001</v>
+        <v>38.27000000000001</v>
       </c>
       <c r="Y4" t="n">
-        <v>19.89363519174799</v>
+        <v>32.97343129941658</v>
       </c>
       <c r="Z4" t="n">
-        <v>342370294.7</v>
+        <v>290106853.44</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>009816.TW</t>
+          <t>00980A.TW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>凱基台灣TOP50</t>
+          <t>主動野村臺灣優選</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1608528121611448</v>
+        <v>0.5946385218074199</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1257454038990293</v>
+        <v>0.5776118272732815</v>
       </c>
       <c r="E5" t="n">
-        <v>15.9</v>
+        <v>24.38</v>
       </c>
       <c r="F5" t="n">
-        <v>9.539999999999999</v>
+        <v>20.35</v>
       </c>
       <c r="G5" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H5" t="n">
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>5.32</v>
+        <v>7.02</v>
       </c>
       <c r="J5" t="n">
-        <v>10.54166666666667</v>
+        <v>9.824999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>135021743</v>
+        <v>8536183.550000001</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>8.99</v>
+        <v>15.61</v>
       </c>
       <c r="O5" t="n">
-        <v>0.64</v>
+        <v>2.11</v>
       </c>
       <c r="P5" t="n">
-        <v>9.630000000000001</v>
+        <v>17.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>227.93</v>
+        <v>246.15</v>
       </c>
       <c r="R5" t="n">
-        <v>0.03510740826211545</v>
+        <v>0.01702669453413841</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.814</v>
       </c>
       <c r="T5" t="n">
-        <v>127.78</v>
+        <v>280.74</v>
       </c>
       <c r="U5" t="n">
-        <v>253</v>
+        <v>393</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9646594873350522</v>
+        <v>0.9623051115058224</v>
       </c>
       <c r="W5" t="n">
-        <v>1.010207034706611</v>
+        <v>1.049632743902879</v>
       </c>
       <c r="X5" t="n">
-        <v>16.4825</v>
+        <v>25.33499999999999</v>
       </c>
       <c r="Y5" t="n">
-        <v>15.73934792942494</v>
+        <v>23.22717173375057</v>
       </c>
       <c r="Z5" t="n">
-        <v>1965275027.7</v>
+        <v>103421764.12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>009824.TW</t>
+          <t>00985A.TW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>群益美國科技巨頭</t>
+          <t>主動野村台灣50</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00329851400727299</v>
+        <v>0.4698961084001945</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001194952732069154</v>
+        <v>0.4509852750533967</v>
       </c>
       <c r="E6" t="n">
-        <v>10.2</v>
+        <v>20.68</v>
       </c>
       <c r="F6" t="n">
-        <v>12.93</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="H6" t="n">
         <v>100</v>
       </c>
       <c r="I6" t="n">
-        <v>5.26</v>
+        <v>6.95</v>
       </c>
       <c r="J6" t="n">
-        <v>5.75</v>
+        <v>9.972972972972974</v>
       </c>
       <c r="K6" t="n">
-        <v>3403265.55</v>
+        <v>60525343.4</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -946,512 +946,512 @@
         <v>2</v>
       </c>
       <c r="N6" t="n">
-        <v>7.35</v>
+        <v>15.02</v>
       </c>
       <c r="O6" t="n">
-        <v>1.39</v>
+        <v>2.1</v>
       </c>
       <c r="P6" t="n">
-        <v>8.74</v>
+        <v>17.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>1975.8</v>
+        <v>252.13</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002103561275203836</v>
+        <v>0.01891083334679777</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T6" t="n">
-        <v>21.06</v>
+        <v>257.02</v>
       </c>
       <c r="U6" t="n">
-        <v>23</v>
+        <v>369</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9654519640321813</v>
+        <v>0.9053894312858455</v>
       </c>
       <c r="W6" t="n">
-        <v>1.004849102541872</v>
+        <v>1.054718034269857</v>
       </c>
       <c r="X6" t="n">
-        <v>10.565</v>
+        <v>22.841</v>
       </c>
       <c r="Y6" t="n">
-        <v>10.15077783738675</v>
+        <v>19.6071360572838</v>
       </c>
       <c r="Z6" t="n">
-        <v>19246818.6</v>
+        <v>200838576.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>009804.TW</t>
+          <t>00410A.TW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>聯邦台精彩50</t>
+          <t>主動永豐科技趨勢</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6002762533745891</v>
+        <v>0.006571110938105029</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5856369472573018</v>
+        <v>0.005647359815790676</v>
       </c>
       <c r="E7" t="n">
-        <v>22.69</v>
+        <v>11.86</v>
       </c>
       <c r="F7" t="n">
-        <v>9.98</v>
+        <v>21.99</v>
       </c>
       <c r="G7" t="n">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
         <v>100</v>
       </c>
       <c r="I7" t="n">
-        <v>4.12</v>
+        <v>5.53</v>
       </c>
       <c r="J7" t="n">
-        <v>8.82258064516129</v>
+        <v>7.6</v>
       </c>
       <c r="K7" t="n">
-        <v>1009074.3</v>
+        <v>6113460.1</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>2</v>
       </c>
       <c r="N7" t="n">
-        <v>9.630000000000001</v>
+        <v>5.92</v>
       </c>
       <c r="O7" t="n">
-        <v>0.76</v>
+        <v>4.92</v>
       </c>
       <c r="P7" t="n">
-        <v>10.39</v>
+        <v>10.84</v>
       </c>
       <c r="Q7" t="n">
-        <v>133.05</v>
+        <v>942.39</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01463930611728737</v>
+        <v>0.0009237511223143535</v>
       </c>
       <c r="S7" t="n">
-        <v>2.786</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>255.36</v>
+        <v>27.64</v>
       </c>
       <c r="U7" t="n">
-        <v>547</v>
+        <v>38</v>
       </c>
       <c r="V7" t="n">
-        <v>0.951063606832233</v>
+        <v>0.9620376378974689</v>
       </c>
       <c r="W7" t="n">
-        <v>1.009132208798136</v>
+        <v>1.059199867756076</v>
       </c>
       <c r="X7" t="n">
-        <v>23.8575</v>
+        <v>12.328</v>
       </c>
       <c r="Y7" t="n">
-        <v>22.4846653413466</v>
+        <v>11.19713130735704</v>
       </c>
       <c r="Z7" t="n">
-        <v>8899426.42</v>
+        <v>106461764.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>00830.TW</t>
+          <t>009816.TW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>國泰費城半導體</t>
+          <t>凱基台灣TOP50</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.335100216795478</v>
+        <v>0.1795276748600119</v>
       </c>
       <c r="D8" t="n">
-        <v>2.227023742992224</v>
+        <v>0.1464668770438953</v>
       </c>
       <c r="E8" t="n">
-        <v>80.05</v>
+        <v>16.17</v>
       </c>
       <c r="F8" t="n">
-        <v>6.81</v>
+        <v>18.51</v>
       </c>
       <c r="G8" t="n">
-        <v>495</v>
+        <v>24</v>
       </c>
       <c r="H8" t="n">
-        <v>97.17</v>
+        <v>100</v>
       </c>
       <c r="I8" t="n">
-        <v>3.93</v>
+        <v>5.32</v>
       </c>
       <c r="J8" t="n">
-        <v>12.29090909090909</v>
+        <v>10.54166666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>10535339.85</v>
+        <v>135527571.3</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>13.29</v>
+        <v>8.99</v>
       </c>
       <c r="O8" t="n">
-        <v>-12.33</v>
+        <v>0.64</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9599999999999991</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>19.85</v>
+        <v>227.93</v>
       </c>
       <c r="R8" t="n">
-        <v>0.108076473803254</v>
+        <v>0.03306079781611659</v>
       </c>
       <c r="S8" t="n">
-        <v>17.71</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1946.3</v>
+        <v>127.78</v>
       </c>
       <c r="U8" t="n">
-        <v>6084</v>
+        <v>253</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9189794219785897</v>
+        <v>0.982321851649353</v>
       </c>
       <c r="W8" t="n">
-        <v>1.017275305986647</v>
+        <v>1.029419901484479</v>
       </c>
       <c r="X8" t="n">
-        <v>87.10749999999999</v>
+        <v>16.461</v>
       </c>
       <c r="Y8" t="n">
-        <v>78.69059587793706</v>
+        <v>15.70787584024943</v>
       </c>
       <c r="Z8" t="n">
-        <v>894896000.65</v>
+        <v>1479862262.34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>00663L.TW</t>
+          <t>009824.TW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>國泰臺灣加權正2</t>
+          <t>群益美國科技巨頭</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11.23085590657439</v>
+        <v>0.02172565303974339</v>
       </c>
       <c r="D9" t="n">
-        <v>2.899617202153657</v>
+        <v>0.02018182821583636</v>
       </c>
       <c r="E9" t="n">
-        <v>102.6</v>
+        <v>10.39</v>
       </c>
       <c r="F9" t="n">
-        <v>9.32</v>
+        <v>20.96</v>
       </c>
       <c r="G9" t="n">
-        <v>564</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>89.89</v>
+        <v>100</v>
       </c>
       <c r="I9" t="n">
-        <v>3.76</v>
+        <v>5.26</v>
       </c>
       <c r="J9" t="n">
-        <v>11.9113475177305</v>
+        <v>5.75</v>
       </c>
       <c r="K9" t="n">
-        <v>5253136.45</v>
+        <v>3124498.95</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>15.99</v>
+        <v>7.35</v>
       </c>
       <c r="O9" t="n">
-        <v>-24.46</v>
+        <v>1.39</v>
       </c>
       <c r="P9" t="n">
-        <v>-8.470000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="Q9" t="n">
-        <v>18.35</v>
+        <v>1975.8</v>
       </c>
       <c r="R9" t="n">
-        <v>8.331238704420731</v>
+        <v>0.001543824823907025</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2121.97</v>
+        <v>21.06</v>
       </c>
       <c r="U9" t="n">
-        <v>6718</v>
+        <v>23</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9160918770508265</v>
+        <v>0.9844608679173769</v>
       </c>
       <c r="W9" t="n">
-        <v>1.024996526178535</v>
+        <v>1.025311572363833</v>
       </c>
       <c r="X9" t="n">
-        <v>111.9975000000001</v>
+        <v>10.55400000000001</v>
       </c>
       <c r="Y9" t="n">
-        <v>100.0979002168141</v>
+        <v>10.1335050535381</v>
       </c>
       <c r="Z9" t="n">
-        <v>361701525.6</v>
+        <v>24638097.92</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>00631L.TW</t>
+          <t>009804.TW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>聯邦台精彩50</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>15.0862385595298</v>
+        <v>0.6315034722998587</v>
       </c>
       <c r="D10" t="n">
-        <v>3.315304290728562</v>
+        <v>0.6141066887296494</v>
       </c>
       <c r="E10" t="n">
-        <v>35.6</v>
+        <v>23.2</v>
       </c>
       <c r="F10" t="n">
-        <v>8.82</v>
+        <v>19.49</v>
       </c>
       <c r="G10" t="n">
-        <v>644</v>
+        <v>62</v>
       </c>
       <c r="H10" t="n">
-        <v>89.44</v>
+        <v>100</v>
       </c>
       <c r="I10" t="n">
-        <v>3.74</v>
+        <v>4.12</v>
       </c>
       <c r="J10" t="n">
-        <v>12.68167701863354</v>
+        <v>8.82258064516129</v>
       </c>
       <c r="K10" t="n">
-        <v>190656506.45</v>
+        <v>994403</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>17.37</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-12.43</v>
+        <v>0.76</v>
       </c>
       <c r="P10" t="n">
-        <v>4.940000000000001</v>
+        <v>10.39</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.49</v>
+        <v>133.05</v>
       </c>
       <c r="R10" t="n">
-        <v>11.77093426880123</v>
+        <v>0.01739678357020935</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.786</v>
       </c>
       <c r="T10" t="n">
-        <v>2407.1</v>
+        <v>255.36</v>
       </c>
       <c r="U10" t="n">
-        <v>8167</v>
+        <v>547</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9188638094131923</v>
+        <v>0.9742782152230971</v>
       </c>
       <c r="W10" t="n">
-        <v>1.025995810457242</v>
+        <v>1.034992584138269</v>
       </c>
       <c r="X10" t="n">
-        <v>38.74349999999998</v>
+        <v>23.8125</v>
       </c>
       <c r="Y10" t="n">
-        <v>34.69799743542287</v>
+        <v>22.41561954699051</v>
       </c>
       <c r="Z10" t="n">
-        <v>5281506921.6</v>
+        <v>11176901.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>00904.TW</t>
+          <t>00830.TW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>台新臺灣半導體30</t>
+          <t>國泰費城半導體</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.70942383488989</v>
+        <v>2.442561163164408</v>
       </c>
       <c r="D11" t="n">
-        <v>1.647458225646873</v>
+        <v>2.286288158315533</v>
       </c>
       <c r="E11" t="n">
-        <v>37.76</v>
+        <v>83.15000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>6.63</v>
+        <v>17.83</v>
       </c>
       <c r="G11" t="n">
-        <v>239</v>
+        <v>495</v>
       </c>
       <c r="H11" t="n">
-        <v>99.16</v>
+        <v>97.17</v>
       </c>
       <c r="I11" t="n">
-        <v>3.55</v>
+        <v>3.93</v>
       </c>
       <c r="J11" t="n">
-        <v>10.78242677824268</v>
+        <v>12.29090909090909</v>
       </c>
       <c r="K11" t="n">
-        <v>4009061.95</v>
+        <v>10404510.95</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>11.85</v>
+        <v>13.29</v>
       </c>
       <c r="O11" t="n">
-        <v>-12.45</v>
+        <v>-12.33</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.5999999999999996</v>
+        <v>0.9599999999999991</v>
       </c>
       <c r="Q11" t="n">
-        <v>37.53</v>
+        <v>19.85</v>
       </c>
       <c r="R11" t="n">
-        <v>0.06196560924301675</v>
+        <v>0.1562730048488752</v>
       </c>
       <c r="S11" t="n">
-        <v>7.050000000000001</v>
+        <v>17.71</v>
       </c>
       <c r="T11" t="n">
-        <v>848.62</v>
+        <v>1946.3</v>
       </c>
       <c r="U11" t="n">
-        <v>2577</v>
+        <v>6084</v>
       </c>
       <c r="V11" t="n">
-        <v>0.8992081919390367</v>
+        <v>0.9575631945644038</v>
       </c>
       <c r="W11" t="n">
-        <v>1.029311773464305</v>
+        <v>1.062249106391637</v>
       </c>
       <c r="X11" t="n">
-        <v>41.9925</v>
+        <v>86.83500000000001</v>
       </c>
       <c r="Y11" t="n">
-        <v>36.68470620219662</v>
+        <v>78.27730755401902</v>
       </c>
       <c r="Z11" t="n">
-        <v>43644744.96</v>
+        <v>602974614.35</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>00685L.TW</t>
+          <t>00663L.TW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>群益臺灣加權正2</t>
+          <t>國泰臺灣加權正2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10.16256815379168</v>
+        <v>11.71489716417418</v>
       </c>
       <c r="D12" t="n">
-        <v>2.731453200941016</v>
+        <v>2.971279655387812</v>
       </c>
       <c r="E12" t="n">
-        <v>11.75</v>
+        <v>106.7</v>
       </c>
       <c r="F12" t="n">
-        <v>9.58</v>
+        <v>17.47</v>
       </c>
       <c r="G12" t="n">
-        <v>514</v>
+        <v>564</v>
       </c>
       <c r="H12" t="n">
-        <v>88.52</v>
+        <v>89.89</v>
       </c>
       <c r="I12" t="n">
-        <v>3.46</v>
+        <v>3.76</v>
       </c>
       <c r="J12" t="n">
-        <v>12.18093385214008</v>
+        <v>11.9113475177305</v>
       </c>
       <c r="K12" t="n">
-        <v>261073587.55</v>
+        <v>5236277.2</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1462,766 +1462,766 @@
         <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>15.89</v>
+        <v>15.99</v>
       </c>
       <c r="O12" t="n">
-        <v>-18.5</v>
+        <v>-24.46</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.609999999999999</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>18.65</v>
+        <v>18.35</v>
       </c>
       <c r="R12" t="n">
-        <v>7.431114952850666</v>
+        <v>8.743617508786372</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1777.84</v>
+        <v>2121.97</v>
       </c>
       <c r="U12" t="n">
-        <v>6261</v>
+        <v>6718</v>
       </c>
       <c r="V12" t="n">
-        <v>0.9163579645155</v>
+        <v>0.9553227683767567</v>
       </c>
       <c r="W12" t="n">
-        <v>1.025115813922667</v>
+        <v>1.071516960547946</v>
       </c>
       <c r="X12" t="n">
-        <v>12.8225</v>
+        <v>111.6900000000001</v>
       </c>
       <c r="Y12" t="n">
-        <v>11.46211953851138</v>
+        <v>99.57845179178159</v>
       </c>
       <c r="Z12" t="n">
-        <v>2473573304.75</v>
+        <v>380418790.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>009809.TW</t>
+          <t>00631L.TW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>富邦淨零ESG50</t>
+          <t>元大台灣50正2</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.339621216709336</v>
+        <v>15.65924452887081</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2916316299414703</v>
+        <v>3.394610125113256</v>
       </c>
       <c r="E13" t="n">
-        <v>17.97</v>
+        <v>36.88</v>
       </c>
       <c r="F13" t="n">
-        <v>9.85</v>
+        <v>16.73</v>
       </c>
       <c r="G13" t="n">
-        <v>34</v>
+        <v>644</v>
       </c>
       <c r="H13" t="n">
-        <v>97.06</v>
+        <v>89.44</v>
       </c>
       <c r="I13" t="n">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="J13" t="n">
-        <v>8.235294117647058</v>
+        <v>12.68167701863354</v>
       </c>
       <c r="K13" t="n">
-        <v>288338.5</v>
+        <v>189715484.05</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>2</v>
       </c>
       <c r="N13" t="n">
-        <v>7.76</v>
+        <v>17.37</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.12</v>
+        <v>-12.43</v>
       </c>
       <c r="P13" t="n">
-        <v>7.64</v>
+        <v>4.940000000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>172.16</v>
+        <v>15.49</v>
       </c>
       <c r="R13" t="n">
-        <v>0.04798958676786569</v>
+        <v>12.26463440375755</v>
       </c>
       <c r="S13" t="n">
-        <v>0.315</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>115.56</v>
+        <v>2407.1</v>
       </c>
       <c r="U13" t="n">
-        <v>280</v>
+        <v>8167</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9705644072373748</v>
+        <v>0.9545007505564475</v>
       </c>
       <c r="W13" t="n">
-        <v>1.009591592635989</v>
+        <v>1.068539009026854</v>
       </c>
       <c r="X13" t="n">
-        <v>18.515</v>
+        <v>38.63799999999998</v>
       </c>
       <c r="Y13" t="n">
-        <v>17.79927658973596</v>
+        <v>34.51441612186679</v>
       </c>
       <c r="Z13" t="n">
-        <v>9024246.479999999</v>
+        <v>4387375834.64</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>00715L.TW</t>
+          <t>00904.TW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>期街口布蘭特正2</t>
+          <t>台新臺灣半導體30</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5.987955068925254</v>
+        <v>1.787659760576835</v>
       </c>
       <c r="D14" t="n">
-        <v>2.592206134687774</v>
+        <v>1.695829246054232</v>
       </c>
       <c r="E14" t="n">
-        <v>87.05</v>
+        <v>39.05</v>
       </c>
       <c r="F14" t="n">
-        <v>94.33</v>
+        <v>13.25</v>
       </c>
       <c r="G14" t="n">
-        <v>425</v>
+        <v>239</v>
       </c>
       <c r="H14" t="n">
-        <v>77.65000000000001</v>
+        <v>99.16</v>
       </c>
       <c r="I14" t="n">
-        <v>3.32</v>
+        <v>3.55</v>
       </c>
       <c r="J14" t="n">
-        <v>17.11294117647059</v>
+        <v>10.78242677824268</v>
       </c>
       <c r="K14" t="n">
-        <v>3113605.95</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
+        <v>4031262</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
       <c r="M14" t="n">
         <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>32.14</v>
+        <v>11.85</v>
       </c>
       <c r="O14" t="n">
-        <v>-44.86</v>
+        <v>-12.45</v>
       </c>
       <c r="P14" t="n">
-        <v>-12.72</v>
+        <v>-0.5999999999999996</v>
       </c>
       <c r="Q14" t="n">
-        <v>14.59</v>
+        <v>37.53</v>
       </c>
       <c r="R14" t="n">
-        <v>3.39574893423748</v>
+        <v>0.09183051452260305</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>7.050000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>1409.31</v>
+        <v>848.62</v>
       </c>
       <c r="U14" t="n">
-        <v>7273</v>
+        <v>2577</v>
       </c>
       <c r="V14" t="n">
-        <v>1.189532659196503</v>
+        <v>0.9348703032044146</v>
       </c>
       <c r="W14" t="n">
-        <v>1.483194490295465</v>
+        <v>1.073941965218162</v>
       </c>
       <c r="X14" t="n">
-        <v>73.17999999999995</v>
+        <v>41.7705</v>
       </c>
       <c r="Y14" t="n">
-        <v>58.69088684563471</v>
+        <v>36.36136892375494</v>
       </c>
       <c r="Z14" t="n">
-        <v>329223970.5</v>
+        <v>36163384.95</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>00675L.TW</t>
+          <t>00913.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>富邦臺灣加權正2</t>
+          <t>兆豐台灣晶圓製造</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10.67242119452606</v>
+        <v>1.660047031765524</v>
       </c>
       <c r="D15" t="n">
-        <v>2.836910003943229</v>
+        <v>1.602545188571406</v>
       </c>
       <c r="E15" t="n">
-        <v>310.5</v>
+        <v>48.8</v>
       </c>
       <c r="F15" t="n">
-        <v>9.300000000000001</v>
+        <v>20.51</v>
       </c>
       <c r="G15" t="n">
-        <v>564</v>
+        <v>262</v>
       </c>
       <c r="H15" t="n">
-        <v>87.06</v>
+        <v>96.18000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="J15" t="n">
-        <v>12.38297872340426</v>
+        <v>12.79770992366412</v>
       </c>
       <c r="K15" t="n">
-        <v>1174727.6</v>
+        <v>1669430.7</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>15.7</v>
+        <v>13.5</v>
       </c>
       <c r="O15" t="n">
-        <v>-24.73</v>
+        <v>-9.19</v>
       </c>
       <c r="P15" t="n">
-        <v>-9.030000000000001</v>
+        <v>4.31</v>
       </c>
       <c r="Q15" t="n">
-        <v>16.61</v>
+        <v>28.72</v>
       </c>
       <c r="R15" t="n">
-        <v>7.835511190582833</v>
+        <v>0.05750184319411833</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>6.699999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>1792.47</v>
+        <v>916.5599999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>6984</v>
+        <v>3353</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9154363801198465</v>
+        <v>0.9597419710110724</v>
       </c>
       <c r="W15" t="n">
-        <v>1.025790910999746</v>
+        <v>1.07778262272051</v>
       </c>
       <c r="X15" t="n">
-        <v>339.1825000000002</v>
+        <v>50.847</v>
       </c>
       <c r="Y15" t="n">
-        <v>302.6932649436168</v>
+        <v>45.27814697626163</v>
       </c>
       <c r="Z15" t="n">
-        <v>243390703.5</v>
+        <v>35824519.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>00935.TW</t>
+          <t>00685L.TW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>野村臺灣新科技50</t>
+          <t>群益臺灣加權正2</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.346793304092792</v>
+        <v>10.59493611672721</v>
       </c>
       <c r="D16" t="n">
-        <v>1.086270127628979</v>
+        <v>2.800008728150124</v>
       </c>
       <c r="E16" t="n">
-        <v>54.7</v>
+        <v>12.21</v>
       </c>
       <c r="F16" t="n">
-        <v>8.210000000000001</v>
+        <v>17.56</v>
       </c>
       <c r="G16" t="n">
-        <v>136</v>
+        <v>514</v>
       </c>
       <c r="H16" t="n">
-        <v>83.09</v>
+        <v>88.52</v>
       </c>
       <c r="I16" t="n">
-        <v>3.15</v>
+        <v>3.46</v>
       </c>
       <c r="J16" t="n">
-        <v>12.30882352941176</v>
+        <v>12.18093385214008</v>
       </c>
       <c r="K16" t="n">
-        <v>12187820.9</v>
+        <v>262555540</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>14.6</v>
+        <v>15.89</v>
       </c>
       <c r="O16" t="n">
-        <v>-8.99</v>
+        <v>-18.5</v>
       </c>
       <c r="P16" t="n">
-        <v>5.609999999999999</v>
+        <v>-2.609999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>43.74</v>
+        <v>18.65</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2605231764638134</v>
+        <v>7.794927388577085</v>
       </c>
       <c r="S16" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>428.12</v>
+        <v>1777.84</v>
       </c>
       <c r="U16" t="n">
-        <v>1674</v>
+        <v>6261</v>
       </c>
       <c r="V16" t="n">
-        <v>0.915481171548117</v>
+        <v>0.9547640458224185</v>
       </c>
       <c r="W16" t="n">
-        <v>1.014265810432367</v>
+        <v>1.070788495841365</v>
       </c>
       <c r="X16" t="n">
-        <v>59.75000000000001</v>
+        <v>12.7885</v>
       </c>
       <c r="Y16" t="n">
-        <v>53.93063577355741</v>
+        <v>11.40281208419789</v>
       </c>
       <c r="Z16" t="n">
-        <v>519592455.6</v>
+        <v>2245054702.44</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>00894.TW</t>
+          <t>009809.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>中信小資高價30</t>
+          <t>富邦淨零ESG50</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.922000294969721</v>
+        <v>0.3536275001024496</v>
       </c>
       <c r="D17" t="n">
-        <v>1.698089875876663</v>
+        <v>0.3150162020802492</v>
       </c>
       <c r="E17" t="n">
-        <v>45.25</v>
+        <v>18.18</v>
       </c>
       <c r="F17" t="n">
-        <v>9.01</v>
+        <v>17.07</v>
       </c>
       <c r="G17" t="n">
-        <v>243</v>
+        <v>34</v>
       </c>
       <c r="H17" t="n">
-        <v>82.72</v>
+        <v>97.06</v>
       </c>
       <c r="I17" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="J17" t="n">
-        <v>15.32921810699589</v>
+        <v>8.235294117647058</v>
       </c>
       <c r="K17" t="n">
-        <v>1259389.7</v>
+        <v>304118.35</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>15.7</v>
+        <v>7.76</v>
       </c>
       <c r="O17" t="n">
-        <v>-8.380000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="P17" t="n">
-        <v>7.319999999999999</v>
+        <v>7.64</v>
       </c>
       <c r="Q17" t="n">
-        <v>22.58</v>
+        <v>172.16</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2239104190930581</v>
+        <v>0.03861129802220042</v>
       </c>
       <c r="S17" t="n">
-        <v>7.549999999999999</v>
+        <v>0.315</v>
       </c>
       <c r="T17" t="n">
-        <v>698.73</v>
+        <v>115.56</v>
       </c>
       <c r="U17" t="n">
-        <v>3725</v>
+        <v>280</v>
       </c>
       <c r="V17" t="n">
-        <v>0.913504729027244</v>
+        <v>0.9832607696260037</v>
       </c>
       <c r="W17" t="n">
-        <v>1.003318790164492</v>
+        <v>1.023403406205444</v>
       </c>
       <c r="X17" t="n">
-        <v>49.53449999999998</v>
+        <v>18.4895</v>
       </c>
       <c r="Y17" t="n">
-        <v>45.10032149660163</v>
+        <v>17.76425590316088</v>
       </c>
       <c r="Z17" t="n">
-        <v>71837135.25</v>
+        <v>7219150.74</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>00901.TW</t>
+          <t>00715L.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>永豐智能車供應鏈</t>
+          <t>期街口布蘭特正2</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.70023886133263</v>
+        <v>6.153685352538137</v>
       </c>
       <c r="D18" t="n">
-        <v>1.663742088908547</v>
+        <v>2.658208680181279</v>
       </c>
       <c r="E18" t="n">
-        <v>44.14</v>
+        <v>89.15000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>8.460000000000001</v>
+        <v>94.78</v>
       </c>
       <c r="G18" t="n">
-        <v>276</v>
+        <v>425</v>
       </c>
       <c r="H18" t="n">
-        <v>89.48999999999999</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>2.79</v>
+        <v>3.32</v>
       </c>
       <c r="J18" t="n">
-        <v>13.22463768115942</v>
+        <v>17.11294117647059</v>
       </c>
       <c r="K18" t="n">
-        <v>283133.55</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
+        <v>2956230.9</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>15.18</v>
+        <v>32.14</v>
       </c>
       <c r="O18" t="n">
-        <v>-7.3</v>
+        <v>-44.86</v>
       </c>
       <c r="P18" t="n">
-        <v>7.88</v>
+        <v>-12.72</v>
       </c>
       <c r="Q18" t="n">
-        <v>24.17</v>
+        <v>14.59</v>
       </c>
       <c r="R18" t="n">
-        <v>0.03649677242408345</v>
+        <v>3.495476672356858</v>
       </c>
       <c r="S18" t="n">
-        <v>4.671</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>771.28</v>
+        <v>1409.31</v>
       </c>
       <c r="U18" t="n">
-        <v>3650</v>
+        <v>7273</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9289013752538484</v>
+        <v>1.195000167554708</v>
       </c>
       <c r="W18" t="n">
-        <v>1.013543830740695</v>
+        <v>1.492975791006813</v>
       </c>
       <c r="X18" t="n">
-        <v>47.5185</v>
+        <v>74.60249999999995</v>
       </c>
       <c r="Y18" t="n">
-        <v>43.55016395072192</v>
+        <v>59.71295752885598</v>
       </c>
       <c r="Z18" t="n">
-        <v>24756757.66</v>
+        <v>215302420.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>0057.TW</t>
+          <t>00675L.TW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>富邦摩台</t>
+          <t>富邦臺灣加權正2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6.040692318946351</v>
+        <v>11.13401426819352</v>
       </c>
       <c r="D19" t="n">
-        <v>4.809135616516254</v>
+        <v>2.907431265938468</v>
       </c>
       <c r="E19" t="n">
-        <v>317.6</v>
+        <v>322.9</v>
       </c>
       <c r="F19" t="n">
-        <v>7.76</v>
+        <v>17.39</v>
       </c>
       <c r="G19" t="n">
-        <v>1245</v>
+        <v>564</v>
       </c>
       <c r="H19" t="n">
-        <v>93.33</v>
+        <v>87.06</v>
       </c>
       <c r="I19" t="n">
-        <v>2.64</v>
+        <v>3.18</v>
       </c>
       <c r="J19" t="n">
-        <v>12.02409638554217</v>
+        <v>12.38297872340426</v>
       </c>
       <c r="K19" t="n">
-        <v>30973.7</v>
+        <v>1177863.5</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>14.45</v>
+        <v>15.7</v>
       </c>
       <c r="O19" t="n">
-        <v>-6.48</v>
+        <v>-24.73</v>
       </c>
       <c r="P19" t="n">
-        <v>7.969999999999999</v>
+        <v>-9.030000000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>8.970000000000001</v>
+        <v>16.61</v>
       </c>
       <c r="R19" t="n">
-        <v>1.231556702430098</v>
+        <v>8.226583002255047</v>
       </c>
       <c r="S19" t="n">
-        <v>1.685</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3287.55</v>
+        <v>1792.47</v>
       </c>
       <c r="U19" t="n">
-        <v>14970</v>
+        <v>6984</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9565256674748144</v>
+        <v>0.9546264200031038</v>
       </c>
       <c r="W19" t="n">
-        <v>1.012894740499916</v>
+        <v>1.072395717027313</v>
       </c>
       <c r="X19" t="n">
-        <v>332.035</v>
+        <v>338.2475000000001</v>
       </c>
       <c r="Y19" t="n">
-        <v>313.5567668593559</v>
+        <v>301.1015382410148</v>
       </c>
       <c r="Z19" t="n">
-        <v>6270059.2</v>
+        <v>291432103.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>00881.TW</t>
+          <t>00935.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>國泰台灣科技龍頭</t>
+          <t>野村臺灣新科技50</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.906883058632524</v>
+        <v>1.420719782562227</v>
       </c>
       <c r="D20" t="n">
-        <v>1.764217461822757</v>
+        <v>1.124151019321835</v>
       </c>
       <c r="E20" t="n">
-        <v>48.24</v>
+        <v>56.6</v>
       </c>
       <c r="F20" t="n">
-        <v>6.94</v>
+        <v>17.34</v>
       </c>
       <c r="G20" t="n">
-        <v>384</v>
+        <v>136</v>
       </c>
       <c r="H20" t="n">
-        <v>89.58</v>
+        <v>83.09</v>
       </c>
       <c r="I20" t="n">
-        <v>2.52</v>
+        <v>3.15</v>
       </c>
       <c r="J20" t="n">
-        <v>15.328125</v>
+        <v>12.30882352941176</v>
       </c>
       <c r="K20" t="n">
-        <v>17280006.9</v>
+        <v>11855076.45</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>10.9</v>
+        <v>14.6</v>
       </c>
       <c r="O20" t="n">
-        <v>-4.28</v>
+        <v>-8.99</v>
       </c>
       <c r="P20" t="n">
-        <v>6.62</v>
+        <v>5.609999999999999</v>
       </c>
       <c r="Q20" t="n">
-        <v>15.81</v>
+        <v>43.74</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1426655968097665</v>
+        <v>0.2965687632403915</v>
       </c>
       <c r="S20" t="n">
-        <v>12.5</v>
+        <v>4.98</v>
       </c>
       <c r="T20" t="n">
-        <v>966.91</v>
+        <v>428.12</v>
       </c>
       <c r="U20" t="n">
-        <v>5886</v>
+        <v>1674</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9334907212105968</v>
+        <v>0.9511406125278326</v>
       </c>
       <c r="W20" t="n">
-        <v>1.007313066654775</v>
+        <v>1.056199612288615</v>
       </c>
       <c r="X20" t="n">
-        <v>51.67699999999999</v>
+        <v>59.50750000000001</v>
       </c>
       <c r="Y20" t="n">
-        <v>47.88977885514984</v>
+        <v>53.58835521379989</v>
       </c>
       <c r="Z20" t="n">
-        <v>1194309036</v>
+        <v>408303117.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>0052.TW</t>
+          <t>00894.TW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>富邦科技</t>
+          <t>中信小資高價30</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>8.089669984550468</v>
+        <v>2.027096261812884</v>
       </c>
       <c r="D21" t="n">
-        <v>4.901728310967869</v>
+        <v>1.747491803525473</v>
       </c>
       <c r="E21" t="n">
-        <v>61.75</v>
+        <v>47.12</v>
       </c>
       <c r="F21" t="n">
-        <v>9.210000000000001</v>
+        <v>18.28</v>
       </c>
       <c r="G21" t="n">
-        <v>1111</v>
+        <v>243</v>
       </c>
       <c r="H21" t="n">
-        <v>88.20999999999999</v>
+        <v>82.72</v>
       </c>
       <c r="I21" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="J21" t="n">
-        <v>14.18091809180918</v>
+        <v>15.32921810699589</v>
       </c>
       <c r="K21" t="n">
-        <v>20495983.7</v>
+        <v>1280538.4</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -2232,168 +2232,168 @@
         <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>12.7</v>
+        <v>15.7</v>
       </c>
       <c r="O21" t="n">
-        <v>-14.18</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.48</v>
+        <v>7.319999999999999</v>
       </c>
       <c r="Q21" t="n">
-        <v>8.050000000000001</v>
+        <v>22.58</v>
       </c>
       <c r="R21" t="n">
-        <v>3.1879416735826</v>
+        <v>0.2796044582874111</v>
       </c>
       <c r="S21" t="n">
-        <v>2.232857285714286</v>
+        <v>7.549999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>2723.42</v>
+        <v>698.73</v>
       </c>
       <c r="U21" t="n">
-        <v>15755</v>
+        <v>3725</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9506581479485787</v>
+        <v>0.9540296210809774</v>
       </c>
       <c r="W21" t="n">
-        <v>1.012170936840371</v>
+        <v>1.050833471178522</v>
       </c>
       <c r="X21" t="n">
-        <v>64.95500000000007</v>
+        <v>49.39049999999998</v>
       </c>
       <c r="Y21" t="n">
-        <v>61.00748179231564</v>
+        <v>44.84059681421679</v>
       </c>
       <c r="Z21" t="n">
-        <v>1149569430.75</v>
+        <v>67884464.64</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>00735.TW</t>
+          <t>00901.TW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>國泰臺韓科技</t>
+          <t>永豐智能車供應鏈</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.858739407784587</v>
+        <v>1.776948615713315</v>
       </c>
       <c r="D22" t="n">
-        <v>2.472685684082697</v>
+        <v>1.712453763617668</v>
       </c>
       <c r="E22" t="n">
-        <v>97.09999999999999</v>
+        <v>45.52</v>
       </c>
       <c r="F22" t="n">
-        <v>13.12</v>
+        <v>18.43</v>
       </c>
       <c r="G22" t="n">
-        <v>498</v>
+        <v>276</v>
       </c>
       <c r="H22" t="n">
-        <v>86.55</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>2.28</v>
+        <v>2.79</v>
       </c>
       <c r="J22" t="n">
-        <v>13.81124497991968</v>
+        <v>13.22463768115942</v>
       </c>
       <c r="K22" t="n">
-        <v>1841089.65</v>
+        <v>309997.8</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>21.39</v>
+        <v>15.18</v>
       </c>
       <c r="O22" t="n">
-        <v>-6.04</v>
+        <v>-7.3</v>
       </c>
       <c r="P22" t="n">
-        <v>15.35</v>
+        <v>7.88</v>
       </c>
       <c r="Q22" t="n">
-        <v>14.26</v>
+        <v>24.17</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3860537237018908</v>
+        <v>0.0644948520956472</v>
       </c>
       <c r="S22" t="n">
-        <v>13.37</v>
+        <v>4.671</v>
       </c>
       <c r="T22" t="n">
-        <v>1133.84</v>
+        <v>771.28</v>
       </c>
       <c r="U22" t="n">
-        <v>6878</v>
+        <v>3650</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9275223880597027</v>
+        <v>0.960844327176781</v>
       </c>
       <c r="W22" t="n">
-        <v>1.047834878866253</v>
+        <v>1.050392994874493</v>
       </c>
       <c r="X22" t="n">
-        <v>104.6874999999999</v>
+        <v>47.375</v>
       </c>
       <c r="Y22" t="n">
-        <v>92.6672722567331</v>
+        <v>43.33616105792766</v>
       </c>
       <c r="Z22" t="n">
-        <v>122830140.6</v>
+        <v>28537944.64</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>0050.TW</t>
+          <t>0057.TW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>元大台灣50</t>
+          <t>富邦摩台</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5.42350102005824</v>
+        <v>6.133202817060743</v>
       </c>
       <c r="D23" t="n">
-        <v>5.42350102005824</v>
+        <v>4.915609864493642</v>
       </c>
       <c r="E23" t="n">
-        <v>106.6</v>
+        <v>321.85</v>
       </c>
       <c r="F23" t="n">
-        <v>9.720000000000001</v>
+        <v>13.74</v>
       </c>
       <c r="G23" t="n">
-        <v>1695</v>
+        <v>1245</v>
       </c>
       <c r="H23" t="n">
-        <v>90.97</v>
+        <v>93.33</v>
       </c>
       <c r="I23" t="n">
-        <v>2.26</v>
+        <v>2.64</v>
       </c>
       <c r="J23" t="n">
-        <v>13.46961651917404</v>
+        <v>12.02409638554217</v>
       </c>
       <c r="K23" t="n">
-        <v>120274806.65</v>
+        <v>32159.1</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -2404,82 +2404,82 @@
         <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>13.94</v>
+        <v>14.45</v>
       </c>
       <c r="O23" t="n">
-        <v>-5.91</v>
+        <v>-6.48</v>
       </c>
       <c r="P23" t="n">
-        <v>8.029999999999999</v>
+        <v>7.969999999999999</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.04</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.217592952567101</v>
       </c>
       <c r="S23" t="n">
-        <v>4.84625</v>
+        <v>1.685</v>
       </c>
       <c r="T23" t="n">
-        <v>3824.71</v>
+        <v>3287.55</v>
       </c>
       <c r="U23" t="n">
-        <v>22831</v>
+        <v>14970</v>
       </c>
       <c r="V23" t="n">
-        <v>0.9549832026875695</v>
+        <v>0.9712781126694681</v>
       </c>
       <c r="W23" t="n">
-        <v>1.011644346050481</v>
+        <v>1.030131369885674</v>
       </c>
       <c r="X23" t="n">
-        <v>111.625</v>
+        <v>331.3675000000001</v>
       </c>
       <c r="Y23" t="n">
-        <v>105.3730003198977</v>
+        <v>312.4358789653396</v>
       </c>
       <c r="Z23" t="n">
-        <v>16363070045.4</v>
+        <v>12123123.95</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>0053.TW</t>
+          <t>00881.TW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>元大科技市值</t>
+          <t>國泰台灣科技龍頭</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6.57200812316626</v>
+        <v>1.963786283105919</v>
       </c>
       <c r="D24" t="n">
-        <v>4.865383838883048</v>
+        <v>1.81492801826997</v>
       </c>
       <c r="E24" t="n">
-        <v>237.4</v>
+        <v>49.41</v>
       </c>
       <c r="F24" t="n">
-        <v>7.69</v>
+        <v>15.1</v>
       </c>
       <c r="G24" t="n">
-        <v>1190</v>
+        <v>384</v>
       </c>
       <c r="H24" t="n">
-        <v>89.16</v>
+        <v>89.58</v>
       </c>
       <c r="I24" t="n">
-        <v>2.18</v>
+        <v>2.52</v>
       </c>
       <c r="J24" t="n">
-        <v>13.83697478991597</v>
+        <v>15.328125</v>
       </c>
       <c r="K24" t="n">
-        <v>495754.6</v>
+        <v>17308965.75</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -2490,82 +2490,82 @@
         <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>11.49</v>
+        <v>10.9</v>
       </c>
       <c r="O24" t="n">
-        <v>-7.24</v>
+        <v>-4.28</v>
       </c>
       <c r="P24" t="n">
-        <v>4.25</v>
+        <v>6.62</v>
       </c>
       <c r="Q24" t="n">
-        <v>7.58</v>
+        <v>15.81</v>
       </c>
       <c r="R24" t="n">
-        <v>1.706624284283212</v>
+        <v>0.1488582648359489</v>
       </c>
       <c r="S24" t="n">
-        <v>18.91</v>
+        <v>12.5</v>
       </c>
       <c r="T24" t="n">
-        <v>2598</v>
+        <v>966.91</v>
       </c>
       <c r="U24" t="n">
-        <v>16466</v>
+        <v>5886</v>
       </c>
       <c r="V24" t="n">
-        <v>0.9462125590386412</v>
+        <v>0.9590915708254479</v>
       </c>
       <c r="W24" t="n">
-        <v>1.013974565412509</v>
+        <v>1.037332456076117</v>
       </c>
       <c r="X24" t="n">
-        <v>250.8950000000001</v>
+        <v>51.51749999999998</v>
       </c>
       <c r="Y24" t="n">
-        <v>234.1281607033408</v>
+        <v>47.63178835346726</v>
       </c>
       <c r="Z24" t="n">
-        <v>127373409</v>
+        <v>494301889.26</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>00892.TW</t>
+          <t>0052.TW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>富邦台灣半導體</t>
+          <t>富邦科技</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.777065164027912</v>
+        <v>8.287513719346043</v>
       </c>
       <c r="D25" t="n">
-        <v>1.714698657403997</v>
+        <v>5.010304235614528</v>
       </c>
       <c r="E25" t="n">
-        <v>39.84</v>
+        <v>63.15</v>
       </c>
       <c r="F25" t="n">
-        <v>11.05</v>
+        <v>18.51</v>
       </c>
       <c r="G25" t="n">
-        <v>241</v>
+        <v>1111</v>
       </c>
       <c r="H25" t="n">
-        <v>75.09999999999999</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>2.12</v>
+        <v>2.45</v>
       </c>
       <c r="J25" t="n">
-        <v>15.85892116182573</v>
+        <v>14.18091809180918</v>
       </c>
       <c r="K25" t="n">
-        <v>4395759.1</v>
+        <v>20220466.05</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -2576,211 +2576,555 @@
         <v>2</v>
       </c>
       <c r="N25" t="n">
-        <v>12.37</v>
+        <v>12.7</v>
       </c>
       <c r="O25" t="n">
-        <v>-7.43</v>
+        <v>-14.18</v>
       </c>
       <c r="P25" t="n">
-        <v>4.94</v>
+        <v>-1.48</v>
       </c>
       <c r="Q25" t="n">
-        <v>18.86</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="R25" t="n">
-        <v>0.06236650662391474</v>
+        <v>3.277209483731514</v>
       </c>
       <c r="S25" t="n">
-        <v>4.937</v>
+        <v>2.232857285714286</v>
       </c>
       <c r="T25" t="n">
-        <v>510.5</v>
+        <v>2723.42</v>
       </c>
       <c r="U25" t="n">
-        <v>3822</v>
+        <v>15755</v>
       </c>
       <c r="V25" t="n">
-        <v>0.9395894013183493</v>
+        <v>0.9739358420727934</v>
       </c>
       <c r="W25" t="n">
-        <v>1.010771656801848</v>
+        <v>1.038250714951938</v>
       </c>
       <c r="X25" t="n">
-        <v>42.40150000000001</v>
+        <v>64.84000000000007</v>
       </c>
       <c r="Y25" t="n">
-        <v>39.41543050985079</v>
+        <v>60.82345919975915</v>
       </c>
       <c r="Z25" t="n">
-        <v>135034572.48</v>
+        <v>516624150.75</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>006208.TW</t>
+          <t>00735.TW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>富邦台50</t>
+          <t>國泰臺韓科技</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4.038818899709984</v>
+        <v>3.022927188302206</v>
       </c>
       <c r="D26" t="n">
-        <v>3.773855012175114</v>
+        <v>2.536481423077639</v>
       </c>
       <c r="E26" t="n">
-        <v>244.6</v>
+        <v>101.7</v>
       </c>
       <c r="F26" t="n">
-        <v>8.69</v>
+        <v>30.85</v>
       </c>
       <c r="G26" t="n">
-        <v>895</v>
+        <v>498</v>
       </c>
       <c r="H26" t="n">
-        <v>88.48999999999999</v>
+        <v>86.55</v>
       </c>
       <c r="I26" t="n">
-        <v>1.95</v>
+        <v>2.28</v>
       </c>
       <c r="J26" t="n">
-        <v>13.86703910614525</v>
+        <v>13.81124497991968</v>
       </c>
       <c r="K26" t="n">
-        <v>3353304</v>
+        <v>1880108.25</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>2</v>
       </c>
       <c r="N26" t="n">
-        <v>11.21</v>
+        <v>21.39</v>
       </c>
       <c r="O26" t="n">
-        <v>-6.25</v>
+        <v>-6.04</v>
       </c>
       <c r="P26" t="n">
-        <v>4.960000000000001</v>
+        <v>15.35</v>
       </c>
       <c r="Q26" t="n">
-        <v>8.949999999999999</v>
+        <v>14.26</v>
       </c>
       <c r="R26" t="n">
-        <v>0.2649638875348694</v>
+        <v>0.4864457652245666</v>
       </c>
       <c r="S26" t="n">
-        <v>28.764</v>
+        <v>13.37</v>
       </c>
       <c r="T26" t="n">
-        <v>1745.92</v>
+        <v>1133.84</v>
       </c>
       <c r="U26" t="n">
-        <v>12411</v>
+        <v>6878</v>
       </c>
       <c r="V26" t="n">
-        <v>0.9568610575935683</v>
+        <v>0.9751420284296582</v>
       </c>
       <c r="W26" t="n">
-        <v>1.01217895853859</v>
+        <v>1.100342968083763</v>
       </c>
       <c r="X26" t="n">
-        <v>255.6275000000001</v>
+        <v>104.2924999999999</v>
       </c>
       <c r="Y26" t="n">
-        <v>241.6568709876757</v>
+        <v>92.42572811376222</v>
       </c>
       <c r="Z26" t="n">
-        <v>1524960901.4</v>
+        <v>161716932.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>009823.TWO</t>
+          <t>0050.TW</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>群益S&amp;P500</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.02873852359408247</v>
+        <v>5.541266058339022</v>
       </c>
       <c r="D27" t="n">
-        <v>0.001194952732069154</v>
+        <v>5.541266058339022</v>
       </c>
       <c r="E27" t="n">
-        <v>10.74</v>
+        <v>108.65</v>
       </c>
       <c r="F27" t="n">
-        <v>68.06</v>
+        <v>18.43</v>
       </c>
       <c r="G27" t="n">
-        <v>15</v>
+        <v>1695</v>
       </c>
       <c r="H27" t="n">
-        <v>100</v>
+        <v>90.97</v>
       </c>
       <c r="I27" t="n">
-        <v>1.31</v>
+        <v>2.26</v>
       </c>
       <c r="J27" t="n">
-        <v>16.93333333333333</v>
+        <v>13.46961651917404</v>
       </c>
       <c r="K27" t="n">
-        <v>3533665.3</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
+        <v>120053251.4</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="M27" t="n">
         <v>2</v>
       </c>
       <c r="N27" t="n">
+        <v>13.94</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-5.91</v>
+      </c>
+      <c r="P27" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4.84625</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3824.71</v>
+      </c>
+      <c r="U27" t="n">
+        <v>22831</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.9750078521110956</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.03412188868065</v>
+      </c>
+      <c r="X27" t="n">
+        <v>111.4350000000001</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>105.0649843014323</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>5826698280.200001</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>0053.TW</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>元大科技市值</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>6.713980055588679</v>
+      </c>
+      <c r="D28" t="n">
+        <v>4.972916621633672</v>
+      </c>
+      <c r="E28" t="n">
+        <v>242.2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>16.43</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1190</v>
+      </c>
+      <c r="H28" t="n">
+        <v>89.16</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="J28" t="n">
+        <v>13.83697478991597</v>
+      </c>
+      <c r="K28" t="n">
+        <v>499707.8</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>2</v>
+      </c>
+      <c r="N28" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-7.24</v>
+      </c>
+      <c r="P28" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.741063433955007</v>
+      </c>
+      <c r="S28" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2598</v>
+      </c>
+      <c r="U28" t="n">
+        <v>16466</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.9674262547182996</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.03858061399947</v>
+      </c>
+      <c r="X28" t="n">
+        <v>250.3550000000001</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>233.2028893427078</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>59108667.8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>00892.TW</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>富邦台灣半導體</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1.87479996881012</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.76443499118511</v>
+      </c>
+      <c r="E29" t="n">
+        <v>41.39</v>
+      </c>
+      <c r="F29" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="G29" t="n">
+        <v>241</v>
+      </c>
+      <c r="H29" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="J29" t="n">
+        <v>15.85892116182573</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4340864.7</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>2</v>
+      </c>
+      <c r="N29" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-7.43</v>
+      </c>
+      <c r="P29" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.11036497762501</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4.937</v>
+      </c>
+      <c r="T29" t="n">
+        <v>510.5</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3822</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.9788225278168639</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.052332035928971</v>
+      </c>
+      <c r="X29" t="n">
+        <v>42.28550000000001</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>39.33169245718345</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>121919956.82</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>006208.TW</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>富邦台50</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>4.121642645430467</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3.861444122508836</v>
+      </c>
+      <c r="E30" t="n">
+        <v>249.05</v>
+      </c>
+      <c r="F30" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="G30" t="n">
+        <v>895</v>
+      </c>
+      <c r="H30" t="n">
+        <v>88.48999999999999</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="J30" t="n">
+        <v>13.86703910614525</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3413206.65</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>2</v>
+      </c>
+      <c r="N30" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-6.25</v>
+      </c>
+      <c r="P30" t="n">
+        <v>4.960000000000001</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.2601985229216313</v>
+      </c>
+      <c r="S30" t="n">
+        <v>28.764</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1745.92</v>
+      </c>
+      <c r="U30" t="n">
+        <v>12411</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.9757865454687925</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.03345211654108</v>
+      </c>
+      <c r="X30" t="n">
+        <v>255.2300000000001</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>240.9884270531659</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>626616524.35</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>009823.TWO</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>群益S&amp;P500</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.02555703620032768</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.02018182821583636</v>
+      </c>
+      <c r="E31" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="F31" t="n">
+        <v>62.83</v>
+      </c>
+      <c r="G31" t="n">
+        <v>15</v>
+      </c>
+      <c r="H31" t="n">
+        <v>100</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="J31" t="n">
+        <v>16.93333333333333</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3803989.4</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>2</v>
+      </c>
+      <c r="N31" t="n">
         <v>3.64</v>
       </c>
-      <c r="O27" t="n">
+      <c r="O31" t="n">
         <v>0.45</v>
       </c>
-      <c r="P27" t="n">
+      <c r="P31" t="n">
         <v>4.09</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="Q31" t="n">
         <v>29.52</v>
       </c>
-      <c r="R27" t="n">
-        <v>0.02754357086201331</v>
-      </c>
-      <c r="S27" t="n">
+      <c r="R31" t="n">
+        <v>0.005375207984491315</v>
+      </c>
+      <c r="S31" t="n">
         <v>0</v>
       </c>
-      <c r="T27" t="n">
+      <c r="T31" t="n">
         <v>19.72</v>
       </c>
-      <c r="U27" t="n">
+      <c r="U31" t="n">
         <v>254</v>
       </c>
-      <c r="V27" t="n">
-        <v>1.01134705023777</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.032899179677986</v>
-      </c>
-      <c r="X27" t="n">
-        <v>10.6195</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>10.3979170584183</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>107869627.98</v>
+      <c r="V31" t="n">
+        <v>1.007573263088574</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.028764067142976</v>
+      </c>
+      <c r="X31" t="n">
+        <v>10.6295</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>10.41055023407183</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>101776423.14</v>
       </c>
     </row>
   </sheetData>

--- a/ETF動態清單.xlsx
+++ b/ETF動態清單.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z31"/>
+  <dimension ref="A1:Z29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,16 +567,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.6647743620677875</v>
+        <v>0.616474052865833</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5352415408982445</v>
+        <v>0.5141672853028441</v>
       </c>
       <c r="E2" t="n">
-        <v>28.65</v>
+        <v>27.81</v>
       </c>
       <c r="F2" t="n">
-        <v>16.38</v>
+        <v>18.08</v>
       </c>
       <c r="G2" t="n">
         <v>41</v>
@@ -591,7 +591,7 @@
         <v>8.439024390243903</v>
       </c>
       <c r="K2" t="n">
-        <v>165439924.5</v>
+        <v>165862764.95</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         <v>386.28</v>
       </c>
       <c r="R2" t="n">
-        <v>0.129532821169543</v>
+        <v>0.102306767562989</v>
       </c>
       <c r="S2" t="n">
         <v>1.67</v>
@@ -626,488 +626,488 @@
         <v>346</v>
       </c>
       <c r="V2" t="n">
-        <v>0.941628870045356</v>
+        <v>0.9186100284072143</v>
       </c>
       <c r="W2" t="n">
-        <v>1.048499642538038</v>
+        <v>1.030807480211824</v>
       </c>
       <c r="X2" t="n">
-        <v>30.426</v>
+        <v>30.27399999999999</v>
       </c>
       <c r="Y2" t="n">
-        <v>27.32475895809436</v>
+        <v>26.97884962406872</v>
       </c>
       <c r="Z2" t="n">
-        <v>3456939856.05</v>
+        <v>4773073405.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>00992A.TW</t>
+          <t>00947.TW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>主動群益科技創新</t>
+          <t>台新臺灣IC設計</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2035366679819564</v>
+        <v>1.174765228330572</v>
       </c>
       <c r="D3" t="n">
-        <v>0.195842705192713</v>
+        <v>0.854811519684304</v>
       </c>
       <c r="E3" t="n">
-        <v>17.24</v>
+        <v>35.5</v>
       </c>
       <c r="F3" t="n">
-        <v>16.21</v>
+        <v>27.16</v>
       </c>
       <c r="G3" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
+        <v>96.97</v>
       </c>
       <c r="I3" t="n">
-        <v>8.390000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="J3" t="n">
-        <v>10.27272727272727</v>
+        <v>10.33333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>56533210.25</v>
+        <v>12381952</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>15.18</v>
+        <v>18.77</v>
       </c>
       <c r="O3" t="n">
-        <v>2.64</v>
+        <v>-0.73</v>
       </c>
       <c r="P3" t="n">
-        <v>17.82</v>
+        <v>18.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>317.42</v>
+        <v>159.78</v>
       </c>
       <c r="R3" t="n">
-        <v>0.007693962789243391</v>
+        <v>0.3199537086462676</v>
       </c>
       <c r="S3" t="n">
-        <v>1.32</v>
+        <v>2.78</v>
       </c>
       <c r="T3" t="n">
-        <v>277.02</v>
+        <v>495.22</v>
       </c>
       <c r="U3" t="n">
-        <v>339</v>
+        <v>682</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9219251336898399</v>
+        <v>0.9339156055982317</v>
       </c>
       <c r="W3" t="n">
-        <v>1.054703846130648</v>
+        <v>1.085508761012832</v>
       </c>
       <c r="X3" t="n">
-        <v>18.69999999999999</v>
+        <v>38.01200000000001</v>
       </c>
       <c r="Y3" t="n">
-        <v>16.34582073749682</v>
+        <v>32.7035591742961</v>
       </c>
       <c r="Z3" t="n">
-        <v>722953848.7199999</v>
+        <v>190323168</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>00947.TW</t>
+          <t>00980A.TW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>台新臺灣IC設計</t>
+          <t>主動野村臺灣優選</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.219081336269761</v>
+        <v>0.5596367831124671</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8801740251202617</v>
+        <v>0.555957964872452</v>
       </c>
       <c r="E4" t="n">
-        <v>36.24</v>
+        <v>23.84</v>
       </c>
       <c r="F4" t="n">
-        <v>20.49</v>
+        <v>25.02</v>
       </c>
       <c r="G4" t="n">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="H4" t="n">
-        <v>96.97</v>
+        <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>7.5</v>
+        <v>7.02</v>
       </c>
       <c r="J4" t="n">
-        <v>10.33333333333333</v>
+        <v>9.824999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>12399993.05</v>
+        <v>8606781.050000001</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>18.77</v>
+        <v>15.61</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.73</v>
+        <v>2.11</v>
       </c>
       <c r="P4" t="n">
-        <v>18.04</v>
+        <v>17.72</v>
       </c>
       <c r="Q4" t="n">
-        <v>159.78</v>
+        <v>246.15</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3389073111494998</v>
+        <v>0.003678818240015147</v>
       </c>
       <c r="S4" t="n">
-        <v>2.78</v>
+        <v>1.814</v>
       </c>
       <c r="T4" t="n">
-        <v>495.22</v>
+        <v>280.74</v>
       </c>
       <c r="U4" t="n">
-        <v>682</v>
+        <v>393</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9469558400836162</v>
+        <v>0.9441958097350396</v>
       </c>
       <c r="W4" t="n">
-        <v>1.099066690115482</v>
+        <v>1.034422542062475</v>
       </c>
       <c r="X4" t="n">
-        <v>38.27000000000001</v>
+        <v>25.24899999999998</v>
       </c>
       <c r="Y4" t="n">
-        <v>32.97343129941658</v>
+        <v>23.04667486505737</v>
       </c>
       <c r="Z4" t="n">
-        <v>290106853.44</v>
+        <v>128776742.56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>00980A.TW</t>
+          <t>00985A.TW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>主動野村臺灣優選</t>
+          <t>主動野村台灣50</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.5946385218074199</v>
+        <v>0.448462472623314</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5776118272732815</v>
+        <v>0.431070957536938</v>
       </c>
       <c r="E5" t="n">
-        <v>24.38</v>
+        <v>20.37</v>
       </c>
       <c r="F5" t="n">
-        <v>20.35</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H5" t="n">
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>7.02</v>
+        <v>6.95</v>
       </c>
       <c r="J5" t="n">
-        <v>9.824999999999999</v>
+        <v>9.972972972972974</v>
       </c>
       <c r="K5" t="n">
-        <v>8536183.550000001</v>
+        <v>60932035.45</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>15.61</v>
+        <v>15.02</v>
       </c>
       <c r="O5" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="P5" t="n">
-        <v>17.72</v>
+        <v>17.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>246.15</v>
+        <v>252.13</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01702669453413841</v>
+        <v>0.01739151508637593</v>
       </c>
       <c r="S5" t="n">
-        <v>1.814</v>
+        <v>2.15</v>
       </c>
       <c r="T5" t="n">
-        <v>280.74</v>
+        <v>257.02</v>
       </c>
       <c r="U5" t="n">
-        <v>393</v>
+        <v>369</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9623051115058224</v>
+        <v>0.8979303960679728</v>
       </c>
       <c r="W5" t="n">
-        <v>1.049632743902879</v>
+        <v>1.05575561797411</v>
       </c>
       <c r="X5" t="n">
-        <v>25.33499999999999</v>
+        <v>22.6855</v>
       </c>
       <c r="Y5" t="n">
-        <v>23.22717173375057</v>
+        <v>19.29423784558021</v>
       </c>
       <c r="Z5" t="n">
-        <v>103421764.12</v>
+        <v>214651421.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>00985A.TW</t>
+          <t>009816.TW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>主動野村台灣50</t>
+          <t>凱基台灣TOP50</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.4698961084001945</v>
+        <v>0.1668972258908135</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4509852750533967</v>
+        <v>0.1309951930973374</v>
       </c>
       <c r="E6" t="n">
-        <v>20.68</v>
+        <v>16.01</v>
       </c>
       <c r="F6" t="n">
-        <v>8.880000000000001</v>
+        <v>24.52</v>
       </c>
       <c r="G6" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="H6" t="n">
         <v>100</v>
       </c>
       <c r="I6" t="n">
-        <v>6.95</v>
+        <v>5.32</v>
       </c>
       <c r="J6" t="n">
-        <v>9.972972972972974</v>
+        <v>10.54166666666667</v>
       </c>
       <c r="K6" t="n">
-        <v>60525343.4</v>
+        <v>137942747</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>2</v>
       </c>
       <c r="N6" t="n">
-        <v>15.02</v>
+        <v>8.99</v>
       </c>
       <c r="O6" t="n">
-        <v>2.1</v>
+        <v>0.64</v>
       </c>
       <c r="P6" t="n">
-        <v>17.12</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>252.13</v>
+        <v>227.93</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01891083334679777</v>
+        <v>0.03590203279347604</v>
       </c>
       <c r="S6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>257.02</v>
+        <v>127.78</v>
       </c>
       <c r="U6" t="n">
-        <v>369</v>
+        <v>253</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9053894312858455</v>
+        <v>0.974259112760908</v>
       </c>
       <c r="W6" t="n">
-        <v>1.054718034269857</v>
+        <v>1.022553736755391</v>
       </c>
       <c r="X6" t="n">
-        <v>22.841</v>
+        <v>16.433</v>
       </c>
       <c r="Y6" t="n">
-        <v>19.6071360572838</v>
+        <v>15.65687887543245</v>
       </c>
       <c r="Z6" t="n">
-        <v>200838576.4</v>
+        <v>1991009907.94</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>00410A.TW</t>
+          <t>009824.TW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>主動永豐科技趨勢</t>
+          <t>群益美國科技巨頭</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.006571110938105029</v>
+        <v>0.01758283729010124</v>
       </c>
       <c r="D7" t="n">
-        <v>0.005647359815790676</v>
+        <v>0.006969103206378779</v>
       </c>
       <c r="E7" t="n">
-        <v>11.86</v>
+        <v>10.35</v>
       </c>
       <c r="F7" t="n">
-        <v>21.99</v>
+        <v>33.02</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
         <v>100</v>
       </c>
       <c r="I7" t="n">
-        <v>5.53</v>
+        <v>5.26</v>
       </c>
       <c r="J7" t="n">
-        <v>7.6</v>
+        <v>5.75</v>
       </c>
       <c r="K7" t="n">
-        <v>6113460.1</v>
+        <v>3123653</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>2</v>
       </c>
       <c r="N7" t="n">
-        <v>5.92</v>
+        <v>7.35</v>
       </c>
       <c r="O7" t="n">
-        <v>4.92</v>
+        <v>1.39</v>
       </c>
       <c r="P7" t="n">
-        <v>10.84</v>
+        <v>8.74</v>
       </c>
       <c r="Q7" t="n">
-        <v>942.39</v>
+        <v>1975.8</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0009237511223143535</v>
+        <v>0.01061373408372246</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>27.64</v>
+        <v>21.06</v>
       </c>
       <c r="U7" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9620376378974689</v>
+        <v>0.9816009104704093</v>
       </c>
       <c r="W7" t="n">
-        <v>1.059199867756076</v>
+        <v>1.023314693788514</v>
       </c>
       <c r="X7" t="n">
-        <v>12.328</v>
+        <v>10.544</v>
       </c>
       <c r="Y7" t="n">
-        <v>11.19713130735704</v>
+        <v>10.11419073997877</v>
       </c>
       <c r="Z7" t="n">
-        <v>106461764.4</v>
+        <v>43232622.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>009816.TW</t>
+          <t>009804.TW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>凱基台灣TOP50</t>
+          <t>聯邦台精彩50</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.1795276748600119</v>
+        <v>0.6085646441427486</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1464668770438953</v>
+        <v>0.5919483143754691</v>
       </c>
       <c r="E8" t="n">
-        <v>16.17</v>
+        <v>22.87</v>
       </c>
       <c r="F8" t="n">
-        <v>18.51</v>
+        <v>23.79</v>
       </c>
       <c r="G8" t="n">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="H8" t="n">
         <v>100</v>
       </c>
       <c r="I8" t="n">
-        <v>5.32</v>
+        <v>4.12</v>
       </c>
       <c r="J8" t="n">
-        <v>10.54166666666667</v>
+        <v>8.82258064516129</v>
       </c>
       <c r="K8" t="n">
-        <v>135527571.3</v>
+        <v>973657.65</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1118,168 +1118,168 @@
         <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>8.99</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>0.64</v>
+        <v>0.76</v>
       </c>
       <c r="P8" t="n">
-        <v>9.630000000000001</v>
+        <v>10.39</v>
       </c>
       <c r="Q8" t="n">
-        <v>227.93</v>
+        <v>133.05</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03306079781611659</v>
+        <v>0.01661632976727945</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.786</v>
       </c>
       <c r="T8" t="n">
-        <v>127.78</v>
+        <v>255.36</v>
       </c>
       <c r="U8" t="n">
-        <v>253</v>
+        <v>547</v>
       </c>
       <c r="V8" t="n">
-        <v>0.982321851649353</v>
+        <v>0.9629473684210527</v>
       </c>
       <c r="W8" t="n">
-        <v>1.029419901484479</v>
+        <v>1.025431977512022</v>
       </c>
       <c r="X8" t="n">
-        <v>16.461</v>
+        <v>23.75</v>
       </c>
       <c r="Y8" t="n">
-        <v>15.70787584024943</v>
+        <v>22.30279579878996</v>
       </c>
       <c r="Z8" t="n">
-        <v>1479862262.34</v>
+        <v>7809190.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>009824.TW</t>
+          <t>00830.TW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>群益美國科技巨頭</t>
+          <t>國泰費城半導體</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.02172565303974339</v>
+        <v>2.434204279676043</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02018182821583636</v>
+        <v>2.243735914155907</v>
       </c>
       <c r="E9" t="n">
-        <v>10.39</v>
+        <v>82.95</v>
       </c>
       <c r="F9" t="n">
-        <v>20.96</v>
+        <v>35.87</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>495</v>
       </c>
       <c r="H9" t="n">
-        <v>100</v>
+        <v>97.17</v>
       </c>
       <c r="I9" t="n">
-        <v>5.26</v>
+        <v>3.93</v>
       </c>
       <c r="J9" t="n">
-        <v>5.75</v>
+        <v>12.29090909090909</v>
       </c>
       <c r="K9" t="n">
-        <v>3124498.95</v>
+        <v>10379313.9</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>7.35</v>
+        <v>13.29</v>
       </c>
       <c r="O9" t="n">
-        <v>1.39</v>
+        <v>-12.33</v>
       </c>
       <c r="P9" t="n">
-        <v>8.74</v>
+        <v>0.9599999999999991</v>
       </c>
       <c r="Q9" t="n">
-        <v>1975.8</v>
+        <v>19.85</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001543824823907025</v>
+        <v>0.190468365520136</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>17.71</v>
       </c>
       <c r="T9" t="n">
-        <v>21.06</v>
+        <v>1946.3</v>
       </c>
       <c r="U9" t="n">
-        <v>23</v>
+        <v>6084</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9844608679173769</v>
+        <v>0.9580457944734789</v>
       </c>
       <c r="W9" t="n">
-        <v>1.025311572363833</v>
+        <v>1.065094471943548</v>
       </c>
       <c r="X9" t="n">
-        <v>10.55400000000001</v>
+        <v>86.58250000000001</v>
       </c>
       <c r="Y9" t="n">
-        <v>10.1335050535381</v>
+        <v>77.88041547961066</v>
       </c>
       <c r="Z9" t="n">
-        <v>24638097.92</v>
+        <v>541734588.15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>009804.TW</t>
+          <t>00663L.TW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>聯邦台精彩50</t>
+          <t>國泰臺灣加權正2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.6315034722998587</v>
+        <v>11.33496630561449</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6141066887296494</v>
+        <v>2.920362190310692</v>
       </c>
       <c r="E10" t="n">
-        <v>23.2</v>
+        <v>103.55</v>
       </c>
       <c r="F10" t="n">
-        <v>19.49</v>
+        <v>19.73</v>
       </c>
       <c r="G10" t="n">
-        <v>62</v>
+        <v>564</v>
       </c>
       <c r="H10" t="n">
-        <v>100</v>
+        <v>89.89</v>
       </c>
       <c r="I10" t="n">
-        <v>4.12</v>
+        <v>3.76</v>
       </c>
       <c r="J10" t="n">
-        <v>8.82258064516129</v>
+        <v>11.9113475177305</v>
       </c>
       <c r="K10" t="n">
-        <v>994403</v>
+        <v>5295446.75</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1290,82 +1290,82 @@
         <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>9.630000000000001</v>
+        <v>15.99</v>
       </c>
       <c r="O10" t="n">
-        <v>0.76</v>
+        <v>-24.46</v>
       </c>
       <c r="P10" t="n">
-        <v>10.39</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>133.05</v>
+        <v>18.35</v>
       </c>
       <c r="R10" t="n">
-        <v>0.01739678357020935</v>
+        <v>8.414604115303796</v>
       </c>
       <c r="S10" t="n">
-        <v>2.786</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>255.36</v>
+        <v>2121.97</v>
       </c>
       <c r="U10" t="n">
-        <v>547</v>
+        <v>6718</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9742782152230971</v>
+        <v>0.9308701905789279</v>
       </c>
       <c r="W10" t="n">
-        <v>1.034992584138269</v>
+        <v>1.0498713731512</v>
       </c>
       <c r="X10" t="n">
-        <v>23.8125</v>
+        <v>111.2400000000001</v>
       </c>
       <c r="Y10" t="n">
-        <v>22.41561954699051</v>
+        <v>98.63113010615152</v>
       </c>
       <c r="Z10" t="n">
-        <v>11176901.6</v>
+        <v>506965992.35</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>00830.TW</t>
+          <t>00631L.TW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>國泰費城半導體</t>
+          <t>元大台灣50正2</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.442561163164408</v>
+        <v>15.20682826333405</v>
       </c>
       <c r="D11" t="n">
-        <v>2.286288158315533</v>
+        <v>3.338522960520756</v>
       </c>
       <c r="E11" t="n">
-        <v>83.15000000000001</v>
+        <v>35.89</v>
       </c>
       <c r="F11" t="n">
-        <v>17.83</v>
+        <v>19.45</v>
       </c>
       <c r="G11" t="n">
-        <v>495</v>
+        <v>644</v>
       </c>
       <c r="H11" t="n">
-        <v>97.17</v>
+        <v>89.44</v>
       </c>
       <c r="I11" t="n">
-        <v>3.93</v>
+        <v>3.74</v>
       </c>
       <c r="J11" t="n">
-        <v>12.29090909090909</v>
+        <v>12.68167701863354</v>
       </c>
       <c r="K11" t="n">
-        <v>10404510.95</v>
+        <v>193468483.75</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1376,512 +1376,508 @@
         <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>13.29</v>
+        <v>17.37</v>
       </c>
       <c r="O11" t="n">
-        <v>-12.33</v>
+        <v>-12.43</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9599999999999991</v>
+        <v>4.940000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>19.85</v>
+        <v>15.49</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1562730048488752</v>
+        <v>11.86830530281329</v>
       </c>
       <c r="S11" t="n">
-        <v>17.71</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1946.3</v>
+        <v>2407.1</v>
       </c>
       <c r="U11" t="n">
-        <v>6084</v>
+        <v>8167</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9575631945644038</v>
+        <v>0.9324742134116245</v>
       </c>
       <c r="W11" t="n">
-        <v>1.062249106391637</v>
+        <v>1.049483711323289</v>
       </c>
       <c r="X11" t="n">
-        <v>86.83500000000001</v>
+        <v>38.48899999999998</v>
       </c>
       <c r="Y11" t="n">
-        <v>78.27730755401902</v>
+        <v>34.19776754300118</v>
       </c>
       <c r="Z11" t="n">
-        <v>602974614.35</v>
+        <v>6268234618.650001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>00663L.TW</t>
+          <t>00904.TW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>國泰臺灣加權正2</t>
+          <t>台新臺灣半導體30</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11.71489716417418</v>
+        <v>1.745286191067325</v>
       </c>
       <c r="D12" t="n">
-        <v>2.971279655387812</v>
+        <v>1.660305801380985</v>
       </c>
       <c r="E12" t="n">
-        <v>106.7</v>
+        <v>38.39</v>
       </c>
       <c r="F12" t="n">
-        <v>17.47</v>
+        <v>16.37</v>
       </c>
       <c r="G12" t="n">
-        <v>564</v>
+        <v>239</v>
       </c>
       <c r="H12" t="n">
-        <v>89.89</v>
+        <v>99.16</v>
       </c>
       <c r="I12" t="n">
-        <v>3.76</v>
+        <v>3.55</v>
       </c>
       <c r="J12" t="n">
-        <v>11.9113475177305</v>
+        <v>10.78242677824268</v>
       </c>
       <c r="K12" t="n">
-        <v>5236277.2</v>
+        <v>4040201.3</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>15.99</v>
+        <v>11.85</v>
       </c>
       <c r="O12" t="n">
-        <v>-24.46</v>
+        <v>-12.45</v>
       </c>
       <c r="P12" t="n">
-        <v>-8.470000000000001</v>
+        <v>-0.5999999999999996</v>
       </c>
       <c r="Q12" t="n">
-        <v>18.35</v>
+        <v>37.53</v>
       </c>
       <c r="R12" t="n">
-        <v>8.743617508786372</v>
+        <v>0.08498038968633992</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>7.050000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>2121.97</v>
+        <v>848.62</v>
       </c>
       <c r="U12" t="n">
-        <v>6718</v>
+        <v>2577</v>
       </c>
       <c r="V12" t="n">
-        <v>0.9553227683767567</v>
+        <v>0.9245701074129378</v>
       </c>
       <c r="W12" t="n">
-        <v>1.071516960547946</v>
+        <v>1.067190732354679</v>
       </c>
       <c r="X12" t="n">
-        <v>111.6900000000001</v>
+        <v>41.522</v>
       </c>
       <c r="Y12" t="n">
-        <v>99.57845179178159</v>
+        <v>35.97295107248097</v>
       </c>
       <c r="Z12" t="n">
-        <v>380418790.4</v>
+        <v>33249425.44</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>00631L.TW</t>
+          <t>00913.TW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>兆豐台灣晶圓製造</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15.65924452887081</v>
+        <v>1.599806263419317</v>
       </c>
       <c r="D13" t="n">
-        <v>3.394610125113256</v>
+        <v>1.56811093503766</v>
       </c>
       <c r="E13" t="n">
-        <v>36.88</v>
+        <v>47.61</v>
       </c>
       <c r="F13" t="n">
-        <v>16.73</v>
+        <v>26.52</v>
       </c>
       <c r="G13" t="n">
-        <v>644</v>
+        <v>262</v>
       </c>
       <c r="H13" t="n">
-        <v>89.44</v>
+        <v>96.18000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="J13" t="n">
-        <v>12.68167701863354</v>
+        <v>12.79770992366412</v>
       </c>
       <c r="K13" t="n">
-        <v>189715484.05</v>
+        <v>1615721.45</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>2</v>
       </c>
       <c r="N13" t="n">
-        <v>17.37</v>
+        <v>13.5</v>
       </c>
       <c r="O13" t="n">
-        <v>-12.43</v>
+        <v>-9.19</v>
       </c>
       <c r="P13" t="n">
-        <v>4.940000000000001</v>
+        <v>4.31</v>
       </c>
       <c r="Q13" t="n">
-        <v>15.49</v>
+        <v>28.72</v>
       </c>
       <c r="R13" t="n">
-        <v>12.26463440375755</v>
+        <v>0.03169532838165656</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>6.699999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>2407.1</v>
+        <v>916.5599999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>8167</v>
+        <v>3353</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9545007505564475</v>
+        <v>0.9406767102988391</v>
       </c>
       <c r="W13" t="n">
-        <v>1.068539009026854</v>
+        <v>1.060010611598225</v>
       </c>
       <c r="X13" t="n">
-        <v>38.63799999999998</v>
+        <v>50.6125</v>
       </c>
       <c r="Y13" t="n">
-        <v>34.51441612186679</v>
+        <v>44.91464470173207</v>
       </c>
       <c r="Z13" t="n">
-        <v>4387375834.64</v>
+        <v>41321147.49</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>00904.TW</t>
+          <t>00685L.TW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>台新臺灣半導體30</t>
+          <t>群益臺灣加權正2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.787659760576835</v>
+        <v>10.25808155292319</v>
       </c>
       <c r="D14" t="n">
-        <v>1.695829246054232</v>
+        <v>2.751166080511013</v>
       </c>
       <c r="E14" t="n">
-        <v>39.05</v>
+        <v>11.86</v>
       </c>
       <c r="F14" t="n">
-        <v>13.25</v>
+        <v>19.86</v>
       </c>
       <c r="G14" t="n">
-        <v>239</v>
+        <v>514</v>
       </c>
       <c r="H14" t="n">
-        <v>99.16</v>
+        <v>88.52</v>
       </c>
       <c r="I14" t="n">
-        <v>3.55</v>
+        <v>3.46</v>
       </c>
       <c r="J14" t="n">
-        <v>10.78242677824268</v>
+        <v>12.18093385214008</v>
       </c>
       <c r="K14" t="n">
-        <v>4031262</v>
+        <v>269001514.1</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M14" t="n">
         <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>11.85</v>
+        <v>15.89</v>
       </c>
       <c r="O14" t="n">
-        <v>-12.45</v>
+        <v>-18.5</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.5999999999999996</v>
+        <v>-2.609999999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>37.53</v>
+        <v>18.65</v>
       </c>
       <c r="R14" t="n">
-        <v>0.09183051452260305</v>
+        <v>7.50691547241218</v>
       </c>
       <c r="S14" t="n">
-        <v>7.050000000000001</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>848.62</v>
+        <v>1777.84</v>
       </c>
       <c r="U14" t="n">
-        <v>2577</v>
+        <v>6261</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9348703032044146</v>
+        <v>0.9310723818495836</v>
       </c>
       <c r="W14" t="n">
-        <v>1.073941965218162</v>
+        <v>1.049982669828875</v>
       </c>
       <c r="X14" t="n">
-        <v>41.7705</v>
+        <v>12.738</v>
       </c>
       <c r="Y14" t="n">
-        <v>36.36136892375494</v>
+        <v>11.29542452537138</v>
       </c>
       <c r="Z14" t="n">
-        <v>36163384.95</v>
+        <v>3149814973</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>00913.TW</t>
+          <t>009809.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>兆豐台灣晶圓製造</t>
+          <t>富邦淨零ESG50</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.660047031765524</v>
+        <v>0.3361492940217485</v>
       </c>
       <c r="D15" t="n">
-        <v>1.602545188571406</v>
+        <v>0.2970180966987372</v>
       </c>
       <c r="E15" t="n">
-        <v>48.8</v>
+        <v>17.96</v>
       </c>
       <c r="F15" t="n">
-        <v>20.51</v>
+        <v>18.05</v>
       </c>
       <c r="G15" t="n">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="H15" t="n">
-        <v>96.18000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="I15" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J15" t="n">
-        <v>12.79770992366412</v>
+        <v>8.235294117647058</v>
       </c>
       <c r="K15" t="n">
-        <v>1669430.7</v>
+        <v>298691.1</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>13.5</v>
+        <v>7.76</v>
       </c>
       <c r="O15" t="n">
-        <v>-9.19</v>
+        <v>-0.12</v>
       </c>
       <c r="P15" t="n">
-        <v>4.31</v>
+        <v>7.64</v>
       </c>
       <c r="Q15" t="n">
-        <v>28.72</v>
+        <v>172.16</v>
       </c>
       <c r="R15" t="n">
-        <v>0.05750184319411833</v>
+        <v>0.03913119732301129</v>
       </c>
       <c r="S15" t="n">
-        <v>6.699999999999999</v>
+        <v>0.315</v>
       </c>
       <c r="T15" t="n">
-        <v>916.5599999999999</v>
+        <v>115.56</v>
       </c>
       <c r="U15" t="n">
-        <v>3353</v>
+        <v>280</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9597419710110724</v>
+        <v>0.9729407622091605</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07778262272051</v>
+        <v>1.014712611447139</v>
       </c>
       <c r="X15" t="n">
-        <v>50.847</v>
+        <v>18.4595</v>
       </c>
       <c r="Y15" t="n">
-        <v>45.27814697626163</v>
+        <v>17.69959276881977</v>
       </c>
       <c r="Z15" t="n">
-        <v>35824519.2</v>
+        <v>3822480.68</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>00685L.TW</t>
+          <t>00715L.TW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>群益臺灣加權正2</t>
+          <t>期街口布蘭特正2</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10.59493611672721</v>
+        <v>6.042562076290243</v>
       </c>
       <c r="D16" t="n">
-        <v>2.800008728150124</v>
+        <v>2.611101266995659</v>
       </c>
       <c r="E16" t="n">
-        <v>12.21</v>
+        <v>87.8</v>
       </c>
       <c r="F16" t="n">
-        <v>17.56</v>
+        <v>92.09</v>
       </c>
       <c r="G16" t="n">
-        <v>514</v>
+        <v>425</v>
       </c>
       <c r="H16" t="n">
-        <v>88.52</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>3.46</v>
+        <v>3.32</v>
       </c>
       <c r="J16" t="n">
-        <v>12.18093385214008</v>
+        <v>17.11294117647059</v>
       </c>
       <c r="K16" t="n">
-        <v>262555540</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
+        <v>2856794.45</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>15.89</v>
+        <v>32.14</v>
       </c>
       <c r="O16" t="n">
-        <v>-18.5</v>
+        <v>-44.86</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.609999999999999</v>
+        <v>-12.72</v>
       </c>
       <c r="Q16" t="n">
-        <v>18.65</v>
+        <v>14.59</v>
       </c>
       <c r="R16" t="n">
-        <v>7.794927388577085</v>
+        <v>3.431460809294584</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1777.84</v>
+        <v>1409.31</v>
       </c>
       <c r="U16" t="n">
-        <v>6261</v>
+        <v>7273</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9547640458224185</v>
+        <v>1.15896115896116</v>
       </c>
       <c r="W16" t="n">
-        <v>1.070788495841365</v>
+        <v>1.450291013862621</v>
       </c>
       <c r="X16" t="n">
-        <v>12.7885</v>
+        <v>75.75749999999995</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.40281208419789</v>
+        <v>60.53957389293792</v>
       </c>
       <c r="Z16" t="n">
-        <v>2245054702.44</v>
+        <v>138067343.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>009809.TW</t>
+          <t>00675L.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>富邦淨零ESG50</t>
+          <t>富邦臺灣加權正2</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.3536275001024496</v>
+        <v>10.76510601527469</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3150162020802492</v>
+        <v>2.857305715456577</v>
       </c>
       <c r="E17" t="n">
-        <v>18.18</v>
+        <v>313.2</v>
       </c>
       <c r="F17" t="n">
-        <v>17.07</v>
+        <v>19.41</v>
       </c>
       <c r="G17" t="n">
-        <v>34</v>
+        <v>564</v>
       </c>
       <c r="H17" t="n">
-        <v>97.06</v>
+        <v>87.06</v>
       </c>
       <c r="I17" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="J17" t="n">
-        <v>8.235294117647058</v>
+        <v>12.38297872340426</v>
       </c>
       <c r="K17" t="n">
-        <v>304118.35</v>
+        <v>1193137.45</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1892,168 +1888,172 @@
         <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>7.76</v>
+        <v>15.7</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.12</v>
+        <v>-24.73</v>
       </c>
       <c r="P17" t="n">
-        <v>7.64</v>
+        <v>-9.030000000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>172.16</v>
+        <v>16.61</v>
       </c>
       <c r="R17" t="n">
-        <v>0.03861129802220042</v>
+        <v>7.907800299818111</v>
       </c>
       <c r="S17" t="n">
-        <v>0.315</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>115.56</v>
+        <v>1792.47</v>
       </c>
       <c r="U17" t="n">
-        <v>280</v>
+        <v>6984</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9832607696260037</v>
+        <v>0.9297010085118695</v>
       </c>
       <c r="W17" t="n">
-        <v>1.023403406205444</v>
+        <v>1.050324320799554</v>
       </c>
       <c r="X17" t="n">
-        <v>18.4895</v>
+        <v>336.8825000000001</v>
       </c>
       <c r="Y17" t="n">
-        <v>17.76425590316088</v>
+        <v>298.1936091526264</v>
       </c>
       <c r="Z17" t="n">
-        <v>7219150.74</v>
+        <v>264359278.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>00715L.TW</t>
+          <t>00935.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>期街口布蘭特正2</t>
+          <t>野村臺灣新科技50</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6.153685352538137</v>
+        <v>1.362937422981553</v>
       </c>
       <c r="D18" t="n">
-        <v>2.658208680181279</v>
+        <v>1.095707517668272</v>
       </c>
       <c r="E18" t="n">
-        <v>89.15000000000001</v>
+        <v>55.2</v>
       </c>
       <c r="F18" t="n">
-        <v>94.78</v>
+        <v>20.01</v>
       </c>
       <c r="G18" t="n">
-        <v>425</v>
+        <v>136</v>
       </c>
       <c r="H18" t="n">
-        <v>77.65000000000001</v>
+        <v>83.09</v>
       </c>
       <c r="I18" t="n">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="J18" t="n">
-        <v>17.11294117647059</v>
+        <v>12.30882352941176</v>
       </c>
       <c r="K18" t="n">
-        <v>2956230.9</v>
-      </c>
-      <c r="L18" t="inlineStr"/>
+        <v>11830938.25</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>32.14</v>
+        <v>14.6</v>
       </c>
       <c r="O18" t="n">
-        <v>-44.86</v>
+        <v>-8.99</v>
       </c>
       <c r="P18" t="n">
-        <v>-12.72</v>
+        <v>5.609999999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>14.59</v>
+        <v>43.74</v>
       </c>
       <c r="R18" t="n">
-        <v>3.495476672356858</v>
+        <v>0.2672299053132807</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="T18" t="n">
-        <v>1409.31</v>
+        <v>428.12</v>
       </c>
       <c r="U18" t="n">
-        <v>7273</v>
+        <v>1674</v>
       </c>
       <c r="V18" t="n">
-        <v>1.195000167554708</v>
+        <v>0.9326687505280055</v>
       </c>
       <c r="W18" t="n">
-        <v>1.492975791006813</v>
+        <v>1.040167517504692</v>
       </c>
       <c r="X18" t="n">
-        <v>74.60249999999995</v>
+        <v>59.185</v>
       </c>
       <c r="Y18" t="n">
-        <v>59.71295752885598</v>
+        <v>53.06837511367585</v>
       </c>
       <c r="Z18" t="n">
-        <v>215302420.7</v>
+        <v>495106077.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>00675L.TW</t>
+          <t>00894.TW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>富邦臺灣加權正2</t>
+          <t>中信小資高價30</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>11.13401426819352</v>
+        <v>1.969066436607132</v>
       </c>
       <c r="D19" t="n">
-        <v>2.907431265938468</v>
+        <v>1.711461359660664</v>
       </c>
       <c r="E19" t="n">
-        <v>322.9</v>
+        <v>46.13</v>
       </c>
       <c r="F19" t="n">
-        <v>17.39</v>
+        <v>21.07</v>
       </c>
       <c r="G19" t="n">
-        <v>564</v>
+        <v>243</v>
       </c>
       <c r="H19" t="n">
-        <v>87.06</v>
+        <v>82.72</v>
       </c>
       <c r="I19" t="n">
-        <v>3.18</v>
+        <v>2.88</v>
       </c>
       <c r="J19" t="n">
-        <v>12.38297872340426</v>
+        <v>15.32921810699589</v>
       </c>
       <c r="K19" t="n">
-        <v>1177863.5</v>
+        <v>1319182.65</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M19" t="n">
@@ -2063,79 +2063,79 @@
         <v>15.7</v>
       </c>
       <c r="O19" t="n">
-        <v>-24.73</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>-9.030000000000001</v>
+        <v>7.319999999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>16.61</v>
+        <v>22.58</v>
       </c>
       <c r="R19" t="n">
-        <v>8.226583002255047</v>
+        <v>0.2576050769464686</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>7.549999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>1792.47</v>
+        <v>698.73</v>
       </c>
       <c r="U19" t="n">
-        <v>6984</v>
+        <v>3725</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9546264200031038</v>
+        <v>0.9378971017292038</v>
       </c>
       <c r="W19" t="n">
-        <v>1.072395717027313</v>
+        <v>1.038028849035007</v>
       </c>
       <c r="X19" t="n">
-        <v>338.2475000000001</v>
+        <v>49.18449999999998</v>
       </c>
       <c r="Y19" t="n">
-        <v>301.1015382410148</v>
+        <v>44.43999802402821</v>
       </c>
       <c r="Z19" t="n">
-        <v>291432103.4</v>
+        <v>65363488.33000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>00935.TW</t>
+          <t>00901.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>野村臺灣新科技50</t>
+          <t>永豐智能車供應鏈</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.420719782562227</v>
+        <v>1.705807688796962</v>
       </c>
       <c r="D20" t="n">
-        <v>1.124151019321835</v>
+        <v>1.676778151185065</v>
       </c>
       <c r="E20" t="n">
-        <v>56.6</v>
+        <v>44.29</v>
       </c>
       <c r="F20" t="n">
-        <v>17.34</v>
+        <v>19.35</v>
       </c>
       <c r="G20" t="n">
-        <v>136</v>
+        <v>276</v>
       </c>
       <c r="H20" t="n">
-        <v>83.09</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>3.15</v>
+        <v>2.79</v>
       </c>
       <c r="J20" t="n">
-        <v>12.30882352941176</v>
+        <v>13.22463768115942</v>
       </c>
       <c r="K20" t="n">
-        <v>11855076.45</v>
+        <v>319357.95</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -2146,82 +2146,82 @@
         <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>14.6</v>
+        <v>15.18</v>
       </c>
       <c r="O20" t="n">
-        <v>-8.99</v>
+        <v>-7.3</v>
       </c>
       <c r="P20" t="n">
-        <v>5.609999999999999</v>
+        <v>7.88</v>
       </c>
       <c r="Q20" t="n">
-        <v>43.74</v>
+        <v>24.17</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2965687632403915</v>
+        <v>0.02902953761189719</v>
       </c>
       <c r="S20" t="n">
-        <v>4.98</v>
+        <v>4.671</v>
       </c>
       <c r="T20" t="n">
-        <v>428.12</v>
+        <v>771.28</v>
       </c>
       <c r="U20" t="n">
-        <v>1674</v>
+        <v>3650</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9511406125278326</v>
+        <v>0.9390338276918512</v>
       </c>
       <c r="W20" t="n">
-        <v>1.056199612288615</v>
+        <v>1.031271547717579</v>
       </c>
       <c r="X20" t="n">
-        <v>59.50750000000001</v>
+        <v>47.16549999999999</v>
       </c>
       <c r="Y20" t="n">
-        <v>53.58835521379989</v>
+        <v>42.94698142116216</v>
       </c>
       <c r="Z20" t="n">
-        <v>408303117.6</v>
+        <v>17012807.67</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>00894.TW</t>
+          <t>0057.TW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>中信小資高價30</t>
+          <t>富邦摩台</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.027096261812884</v>
+        <v>6.062277776636446</v>
       </c>
       <c r="D21" t="n">
-        <v>1.747491803525473</v>
+        <v>4.841076327541531</v>
       </c>
       <c r="E21" t="n">
-        <v>47.12</v>
+        <v>318.7</v>
       </c>
       <c r="F21" t="n">
-        <v>18.28</v>
+        <v>17.04</v>
       </c>
       <c r="G21" t="n">
-        <v>243</v>
+        <v>1245</v>
       </c>
       <c r="H21" t="n">
-        <v>82.72</v>
+        <v>93.33</v>
       </c>
       <c r="I21" t="n">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="J21" t="n">
-        <v>15.32921810699589</v>
+        <v>12.02409638554217</v>
       </c>
       <c r="K21" t="n">
-        <v>1280538.4</v>
+        <v>30948.05</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -2232,168 +2232,168 @@
         <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>15.7</v>
+        <v>14.45</v>
       </c>
       <c r="O21" t="n">
-        <v>-8.380000000000001</v>
+        <v>-6.48</v>
       </c>
       <c r="P21" t="n">
-        <v>7.319999999999999</v>
+        <v>7.969999999999999</v>
       </c>
       <c r="Q21" t="n">
-        <v>22.58</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2796044582874111</v>
+        <v>1.221201449094915</v>
       </c>
       <c r="S21" t="n">
-        <v>7.549999999999999</v>
+        <v>1.685</v>
       </c>
       <c r="T21" t="n">
-        <v>698.73</v>
+        <v>3287.55</v>
       </c>
       <c r="U21" t="n">
-        <v>3725</v>
+        <v>14970</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9540296210809774</v>
+        <v>0.963924658414681</v>
       </c>
       <c r="W21" t="n">
-        <v>1.050833471178522</v>
+        <v>1.024939990475596</v>
       </c>
       <c r="X21" t="n">
-        <v>49.39049999999998</v>
+        <v>330.6275000000001</v>
       </c>
       <c r="Y21" t="n">
-        <v>44.84059681421679</v>
+        <v>310.9450338181417</v>
       </c>
       <c r="Z21" t="n">
-        <v>67884464.64</v>
+        <v>2930765.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>00901.TW</t>
+          <t>00881.TW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>永豐智能車供應鏈</t>
+          <t>國泰台灣科技龍頭</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.776948615713315</v>
+        <v>1.91115103015939</v>
       </c>
       <c r="D22" t="n">
-        <v>1.712453763617668</v>
+        <v>1.778188111242962</v>
       </c>
       <c r="E22" t="n">
-        <v>45.52</v>
+        <v>48.38</v>
       </c>
       <c r="F22" t="n">
-        <v>18.43</v>
+        <v>15.47</v>
       </c>
       <c r="G22" t="n">
-        <v>276</v>
+        <v>384</v>
       </c>
       <c r="H22" t="n">
-        <v>89.48999999999999</v>
+        <v>89.58</v>
       </c>
       <c r="I22" t="n">
-        <v>2.79</v>
+        <v>2.52</v>
       </c>
       <c r="J22" t="n">
-        <v>13.22463768115942</v>
+        <v>15.328125</v>
       </c>
       <c r="K22" t="n">
-        <v>309997.8</v>
+        <v>17686977.85</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>15.18</v>
+        <v>10.9</v>
       </c>
       <c r="O22" t="n">
-        <v>-7.3</v>
+        <v>-4.28</v>
       </c>
       <c r="P22" t="n">
-        <v>7.88</v>
+        <v>6.62</v>
       </c>
       <c r="Q22" t="n">
-        <v>24.17</v>
+        <v>15.81</v>
       </c>
       <c r="R22" t="n">
-        <v>0.0644948520956472</v>
+        <v>0.1329629189164279</v>
       </c>
       <c r="S22" t="n">
-        <v>4.671</v>
+        <v>12.5</v>
       </c>
       <c r="T22" t="n">
-        <v>771.28</v>
+        <v>966.91</v>
       </c>
       <c r="U22" t="n">
-        <v>3650</v>
+        <v>5886</v>
       </c>
       <c r="V22" t="n">
-        <v>0.960844327176781</v>
+        <v>0.9428685577307234</v>
       </c>
       <c r="W22" t="n">
-        <v>1.050392994874493</v>
+        <v>1.024471315404593</v>
       </c>
       <c r="X22" t="n">
-        <v>47.375</v>
+        <v>51.31149999999999</v>
       </c>
       <c r="Y22" t="n">
-        <v>43.33616105792766</v>
+        <v>47.22435784441009</v>
       </c>
       <c r="Z22" t="n">
-        <v>28537944.64</v>
+        <v>870941501.24</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>0057.TW</t>
+          <t>0052.TW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>富邦摩台</t>
+          <t>富邦科技</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6.133202817060743</v>
+        <v>8.143308767623157</v>
       </c>
       <c r="D23" t="n">
-        <v>4.915609864493642</v>
+        <v>4.934436041392456</v>
       </c>
       <c r="E23" t="n">
-        <v>321.85</v>
+        <v>62.15</v>
       </c>
       <c r="F23" t="n">
-        <v>13.74</v>
+        <v>22.6</v>
       </c>
       <c r="G23" t="n">
-        <v>1245</v>
+        <v>1111</v>
       </c>
       <c r="H23" t="n">
-        <v>93.33</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>2.64</v>
+        <v>2.45</v>
       </c>
       <c r="J23" t="n">
-        <v>12.02409638554217</v>
+        <v>14.18091809180918</v>
       </c>
       <c r="K23" t="n">
-        <v>32159.1</v>
+        <v>20482484.65</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -2404,82 +2404,82 @@
         <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>14.45</v>
+        <v>12.7</v>
       </c>
       <c r="O23" t="n">
-        <v>-6.48</v>
+        <v>-14.18</v>
       </c>
       <c r="P23" t="n">
-        <v>7.969999999999999</v>
+        <v>-1.48</v>
       </c>
       <c r="Q23" t="n">
-        <v>8.970000000000001</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="R23" t="n">
-        <v>1.217592952567101</v>
+        <v>3.208872726230702</v>
       </c>
       <c r="S23" t="n">
-        <v>1.685</v>
+        <v>2.232857285714286</v>
       </c>
       <c r="T23" t="n">
-        <v>3287.55</v>
+        <v>2723.42</v>
       </c>
       <c r="U23" t="n">
-        <v>14970</v>
+        <v>15755</v>
       </c>
       <c r="V23" t="n">
-        <v>0.9712781126694681</v>
+        <v>0.960921495110354</v>
       </c>
       <c r="W23" t="n">
-        <v>1.030131369885674</v>
+        <v>1.027191332233767</v>
       </c>
       <c r="X23" t="n">
-        <v>331.3675000000001</v>
+        <v>64.67750000000008</v>
       </c>
       <c r="Y23" t="n">
-        <v>312.4358789653396</v>
+        <v>60.50479404342945</v>
       </c>
       <c r="Z23" t="n">
-        <v>12123123.95</v>
+        <v>951384244.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>00881.TW</t>
+          <t>00735.TW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>國泰台灣科技龍頭</t>
+          <t>國泰臺韓科技</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.963786283105919</v>
+        <v>2.971062704400238</v>
       </c>
       <c r="D24" t="n">
-        <v>1.81492801826997</v>
+        <v>2.490853452794934</v>
       </c>
       <c r="E24" t="n">
-        <v>49.41</v>
+        <v>100.3</v>
       </c>
       <c r="F24" t="n">
-        <v>15.1</v>
+        <v>46.61</v>
       </c>
       <c r="G24" t="n">
-        <v>384</v>
+        <v>498</v>
       </c>
       <c r="H24" t="n">
-        <v>89.58</v>
+        <v>86.55</v>
       </c>
       <c r="I24" t="n">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="J24" t="n">
-        <v>15.328125</v>
+        <v>13.81124497991968</v>
       </c>
       <c r="K24" t="n">
-        <v>17308965.75</v>
+        <v>2001390.3</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -2490,82 +2490,82 @@
         <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>10.9</v>
+        <v>21.39</v>
       </c>
       <c r="O24" t="n">
-        <v>-4.28</v>
+        <v>-6.04</v>
       </c>
       <c r="P24" t="n">
-        <v>6.62</v>
+        <v>15.35</v>
       </c>
       <c r="Q24" t="n">
-        <v>15.81</v>
+        <v>14.26</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1488582648359489</v>
+        <v>0.480209251605304</v>
       </c>
       <c r="S24" t="n">
-        <v>12.5</v>
+        <v>13.37</v>
       </c>
       <c r="T24" t="n">
-        <v>966.91</v>
+        <v>1133.84</v>
       </c>
       <c r="U24" t="n">
-        <v>5886</v>
+        <v>6878</v>
       </c>
       <c r="V24" t="n">
-        <v>0.9590915708254479</v>
+        <v>0.9657463351226452</v>
       </c>
       <c r="W24" t="n">
-        <v>1.037332456076117</v>
+        <v>1.08932531891161</v>
       </c>
       <c r="X24" t="n">
-        <v>51.51749999999998</v>
+        <v>103.8574999999999</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.63178835346726</v>
+        <v>92.07534081757495</v>
       </c>
       <c r="Z24" t="n">
-        <v>494301889.26</v>
+        <v>315601171.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>0052.TW</t>
+          <t>0050.TW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>富邦科技</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8.287513719346043</v>
+        <v>5.459241993854328</v>
       </c>
       <c r="D25" t="n">
-        <v>5.010304235614528</v>
+        <v>5.459241993854328</v>
       </c>
       <c r="E25" t="n">
-        <v>63.15</v>
+        <v>107.25</v>
       </c>
       <c r="F25" t="n">
-        <v>18.51</v>
+        <v>23.4</v>
       </c>
       <c r="G25" t="n">
-        <v>1111</v>
+        <v>1695</v>
       </c>
       <c r="H25" t="n">
-        <v>88.20999999999999</v>
+        <v>90.97</v>
       </c>
       <c r="I25" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="J25" t="n">
-        <v>14.18091809180918</v>
+        <v>13.46961651917404</v>
       </c>
       <c r="K25" t="n">
-        <v>20220466.05</v>
+        <v>120860361.15</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -2576,82 +2576,82 @@
         <v>2</v>
       </c>
       <c r="N25" t="n">
-        <v>12.7</v>
+        <v>13.94</v>
       </c>
       <c r="O25" t="n">
-        <v>-14.18</v>
+        <v>-5.91</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.48</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="Q25" t="n">
-        <v>8.050000000000001</v>
+        <v>6.04</v>
       </c>
       <c r="R25" t="n">
-        <v>3.277209483731514</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.232857285714286</v>
+        <v>4.84625</v>
       </c>
       <c r="T25" t="n">
-        <v>2723.42</v>
+        <v>3824.71</v>
       </c>
       <c r="U25" t="n">
-        <v>15755</v>
+        <v>22831</v>
       </c>
       <c r="V25" t="n">
-        <v>0.9739358420727934</v>
+        <v>0.9646736075195066</v>
       </c>
       <c r="W25" t="n">
-        <v>1.038250714951938</v>
+        <v>1.025606064806033</v>
       </c>
       <c r="X25" t="n">
-        <v>64.84000000000007</v>
+        <v>111.1775000000001</v>
       </c>
       <c r="Y25" t="n">
-        <v>60.82345919975915</v>
+        <v>104.5723145370475</v>
       </c>
       <c r="Z25" t="n">
-        <v>516624150.75</v>
+        <v>9291081871.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>00735.TW</t>
+          <t>0053.TW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>國泰臺韓科技</t>
+          <t>元大科技市值</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3.022927188302206</v>
+        <v>6.593111081669522</v>
       </c>
       <c r="D26" t="n">
-        <v>2.536481423077639</v>
+        <v>4.897736359180728</v>
       </c>
       <c r="E26" t="n">
-        <v>101.7</v>
+        <v>238.2</v>
       </c>
       <c r="F26" t="n">
-        <v>30.85</v>
+        <v>18.08</v>
       </c>
       <c r="G26" t="n">
-        <v>498</v>
+        <v>1190</v>
       </c>
       <c r="H26" t="n">
-        <v>86.55</v>
+        <v>89.16</v>
       </c>
       <c r="I26" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="J26" t="n">
-        <v>13.81124497991968</v>
+        <v>13.83697478991597</v>
       </c>
       <c r="K26" t="n">
-        <v>1880108.25</v>
+        <v>519863.05</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -2662,82 +2662,82 @@
         <v>2</v>
       </c>
       <c r="N26" t="n">
-        <v>21.39</v>
+        <v>11.49</v>
       </c>
       <c r="O26" t="n">
-        <v>-6.04</v>
+        <v>-7.24</v>
       </c>
       <c r="P26" t="n">
-        <v>15.35</v>
+        <v>4.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>14.26</v>
+        <v>7.58</v>
       </c>
       <c r="R26" t="n">
-        <v>0.4864457652245666</v>
+        <v>1.695374722488794</v>
       </c>
       <c r="S26" t="n">
-        <v>13.37</v>
+        <v>18.91</v>
       </c>
       <c r="T26" t="n">
-        <v>1133.84</v>
+        <v>2598</v>
       </c>
       <c r="U26" t="n">
-        <v>6878</v>
+        <v>16466</v>
       </c>
       <c r="V26" t="n">
-        <v>0.9751420284296582</v>
+        <v>0.9543269230769227</v>
       </c>
       <c r="W26" t="n">
-        <v>1.100342968083763</v>
+        <v>1.027969077319239</v>
       </c>
       <c r="X26" t="n">
-        <v>104.2924999999999</v>
+        <v>249.6000000000001</v>
       </c>
       <c r="Y26" t="n">
-        <v>92.42572811376222</v>
+        <v>231.7190324646568</v>
       </c>
       <c r="Z26" t="n">
-        <v>161716932.9</v>
+        <v>131397075</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>0050.TW</t>
+          <t>00892.TW</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>元大台灣50</t>
+          <t>富邦台灣半導體</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5.541266058339022</v>
+        <v>1.806262935053582</v>
       </c>
       <c r="D27" t="n">
-        <v>5.541266058339022</v>
+        <v>1.728233769791223</v>
       </c>
       <c r="E27" t="n">
-        <v>108.65</v>
+        <v>40.34</v>
       </c>
       <c r="F27" t="n">
-        <v>18.43</v>
+        <v>30.89</v>
       </c>
       <c r="G27" t="n">
-        <v>1695</v>
+        <v>241</v>
       </c>
       <c r="H27" t="n">
-        <v>90.97</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="J27" t="n">
-        <v>13.46961651917404</v>
+        <v>15.85892116182573</v>
       </c>
       <c r="K27" t="n">
-        <v>120053251.4</v>
+        <v>4324321.8</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2748,383 +2748,211 @@
         <v>2</v>
       </c>
       <c r="N27" t="n">
-        <v>13.94</v>
+        <v>12.37</v>
       </c>
       <c r="O27" t="n">
-        <v>-5.91</v>
+        <v>-7.43</v>
       </c>
       <c r="P27" t="n">
-        <v>8.029999999999999</v>
+        <v>4.94</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.04</v>
+        <v>18.86</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>0.0780291652623597</v>
       </c>
       <c r="S27" t="n">
-        <v>4.84625</v>
+        <v>4.937</v>
       </c>
       <c r="T27" t="n">
-        <v>3824.71</v>
+        <v>510.5</v>
       </c>
       <c r="U27" t="n">
-        <v>22831</v>
+        <v>3822</v>
       </c>
       <c r="V27" t="n">
-        <v>0.9750078521110956</v>
+        <v>0.9573761154357318</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03412188868065</v>
+        <v>1.031526857622729</v>
       </c>
       <c r="X27" t="n">
-        <v>111.4350000000001</v>
+        <v>42.13600000000001</v>
       </c>
       <c r="Y27" t="n">
-        <v>105.0649843014323</v>
+        <v>39.10707675897854</v>
       </c>
       <c r="Z27" t="n">
-        <v>5826698280.200001</v>
+        <v>166699765.46</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>0053.TW</t>
+          <t>006208.TW</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>元大科技市值</t>
+          <t>富邦台50</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6.713980055588679</v>
+        <v>4.058071677573126</v>
       </c>
       <c r="D28" t="n">
-        <v>4.972916621633672</v>
+        <v>3.799682014083244</v>
       </c>
       <c r="E28" t="n">
-        <v>242.2</v>
+        <v>245.75</v>
       </c>
       <c r="F28" t="n">
-        <v>16.43</v>
+        <v>21.42</v>
       </c>
       <c r="G28" t="n">
-        <v>1190</v>
+        <v>895</v>
       </c>
       <c r="H28" t="n">
-        <v>89.16</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="J28" t="n">
-        <v>13.83697478991597</v>
+        <v>13.86703910614525</v>
       </c>
       <c r="K28" t="n">
-        <v>499707.8</v>
+        <v>3601859.9</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>2</v>
       </c>
       <c r="N28" t="n">
-        <v>11.49</v>
+        <v>11.21</v>
       </c>
       <c r="O28" t="n">
-        <v>-7.24</v>
+        <v>-6.25</v>
       </c>
       <c r="P28" t="n">
-        <v>4.25</v>
+        <v>4.960000000000001</v>
       </c>
       <c r="Q28" t="n">
-        <v>7.58</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="R28" t="n">
-        <v>1.741063433955007</v>
+        <v>0.2583896634898819</v>
       </c>
       <c r="S28" t="n">
-        <v>18.91</v>
+        <v>28.764</v>
       </c>
       <c r="T28" t="n">
-        <v>2598</v>
+        <v>1745.92</v>
       </c>
       <c r="U28" t="n">
-        <v>16466</v>
+        <v>12411</v>
       </c>
       <c r="V28" t="n">
-        <v>0.9674262547182996</v>
+        <v>0.9649553352311766</v>
       </c>
       <c r="W28" t="n">
-        <v>1.03858061399947</v>
+        <v>1.024491850732192</v>
       </c>
       <c r="X28" t="n">
-        <v>250.3550000000001</v>
+        <v>254.6750000000001</v>
       </c>
       <c r="Y28" t="n">
-        <v>233.2028893427078</v>
+        <v>239.8750168919016</v>
       </c>
       <c r="Z28" t="n">
-        <v>59108667.8</v>
+        <v>1167621162</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>00892.TW</t>
+          <t>009823.TWO</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>富邦台灣半導體</t>
+          <t>群益S&amp;P500</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.87479996881012</v>
+        <v>0.02809527739714124</v>
       </c>
       <c r="D29" t="n">
-        <v>1.76443499118511</v>
+        <v>0.006969103206378779</v>
       </c>
       <c r="E29" t="n">
-        <v>41.39</v>
+        <v>10.74</v>
       </c>
       <c r="F29" t="n">
-        <v>23.63</v>
+        <v>64.11</v>
       </c>
       <c r="G29" t="n">
-        <v>241</v>
+        <v>15</v>
       </c>
       <c r="H29" t="n">
-        <v>75.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I29" t="n">
-        <v>2.12</v>
+        <v>1.31</v>
       </c>
       <c r="J29" t="n">
-        <v>15.85892116182573</v>
+        <v>16.93333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>4340864.7</v>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
+        <v>3871837.65</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="n">
         <v>2</v>
       </c>
       <c r="N29" t="n">
-        <v>12.37</v>
+        <v>3.64</v>
       </c>
       <c r="O29" t="n">
-        <v>-7.43</v>
+        <v>0.45</v>
       </c>
       <c r="P29" t="n">
-        <v>4.94</v>
+        <v>4.09</v>
       </c>
       <c r="Q29" t="n">
-        <v>18.86</v>
+        <v>29.52</v>
       </c>
       <c r="R29" t="n">
-        <v>0.11036497762501</v>
+        <v>0.02112617419076246</v>
       </c>
       <c r="S29" t="n">
-        <v>4.937</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>510.5</v>
+        <v>19.72</v>
       </c>
       <c r="U29" t="n">
-        <v>3822</v>
+        <v>254</v>
       </c>
       <c r="V29" t="n">
-        <v>0.9788225278168639</v>
+        <v>1.009066566449006</v>
       </c>
       <c r="W29" t="n">
-        <v>1.052332035928971</v>
+        <v>1.02931795635844</v>
       </c>
       <c r="X29" t="n">
-        <v>42.28550000000001</v>
+        <v>10.6435</v>
       </c>
       <c r="Y29" t="n">
-        <v>39.33169245718345</v>
+        <v>10.43409369636995</v>
       </c>
       <c r="Z29" t="n">
-        <v>121919956.82</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>006208.TW</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>富邦台50</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>4.121642645430467</v>
-      </c>
-      <c r="D30" t="n">
-        <v>3.861444122508836</v>
-      </c>
-      <c r="E30" t="n">
-        <v>249.05</v>
-      </c>
-      <c r="F30" t="n">
-        <v>17.31</v>
-      </c>
-      <c r="G30" t="n">
-        <v>895</v>
-      </c>
-      <c r="H30" t="n">
-        <v>88.48999999999999</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="J30" t="n">
-        <v>13.86703910614525</v>
-      </c>
-      <c r="K30" t="n">
-        <v>3413206.65</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="M30" t="n">
-        <v>2</v>
-      </c>
-      <c r="N30" t="n">
-        <v>11.21</v>
-      </c>
-      <c r="O30" t="n">
-        <v>-6.25</v>
-      </c>
-      <c r="P30" t="n">
-        <v>4.960000000000001</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0.2601985229216313</v>
-      </c>
-      <c r="S30" t="n">
-        <v>28.764</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1745.92</v>
-      </c>
-      <c r="U30" t="n">
-        <v>12411</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0.9757865454687925</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.03345211654108</v>
-      </c>
-      <c r="X30" t="n">
-        <v>255.2300000000001</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>240.9884270531659</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>626616524.35</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>009823.TWO</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>群益S&amp;P500</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>0.02555703620032768</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.02018182821583636</v>
-      </c>
-      <c r="E31" t="n">
-        <v>10.71</v>
-      </c>
-      <c r="F31" t="n">
-        <v>62.83</v>
-      </c>
-      <c r="G31" t="n">
-        <v>15</v>
-      </c>
-      <c r="H31" t="n">
-        <v>100</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="J31" t="n">
-        <v>16.93333333333333</v>
-      </c>
-      <c r="K31" t="n">
-        <v>3803989.4</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="n">
-        <v>2</v>
-      </c>
-      <c r="N31" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="P31" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>29.52</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0.005375207984491315</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>19.72</v>
-      </c>
-      <c r="U31" t="n">
-        <v>254</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.007573263088574</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.028764067142976</v>
-      </c>
-      <c r="X31" t="n">
-        <v>10.6295</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>10.41055023407183</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>101776423.14</v>
+        <v>35897086.02</v>
       </c>
     </row>
   </sheetData>

--- a/ETF動態清單.xlsx
+++ b/ETF動態清單.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z29"/>
+  <dimension ref="A1:Z27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,16 +567,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.616474052865833</v>
+        <v>0.5512742315780399</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5141672853028441</v>
+        <v>0.4806451046454674</v>
       </c>
       <c r="E2" t="n">
-        <v>27.81</v>
+        <v>26.66</v>
       </c>
       <c r="F2" t="n">
-        <v>18.08</v>
+        <v>16.95</v>
       </c>
       <c r="G2" t="n">
         <v>41</v>
@@ -591,7 +591,7 @@
         <v>8.439024390243903</v>
       </c>
       <c r="K2" t="n">
-        <v>165862764.95</v>
+        <v>176080724.05</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         <v>386.28</v>
       </c>
       <c r="R2" t="n">
-        <v>0.102306767562989</v>
+        <v>0.07062912693257251</v>
       </c>
       <c r="S2" t="n">
         <v>1.67</v>
@@ -626,19 +626,19 @@
         <v>346</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9186100284072143</v>
+        <v>0.8859644750178624</v>
       </c>
       <c r="W2" t="n">
-        <v>1.030807480211824</v>
+        <v>1.008337847006773</v>
       </c>
       <c r="X2" t="n">
-        <v>30.27399999999999</v>
+        <v>30.0915</v>
       </c>
       <c r="Y2" t="n">
-        <v>26.97884962406872</v>
+        <v>26.43955106826505</v>
       </c>
       <c r="Z2" t="n">
-        <v>4773073405.5</v>
+        <v>8538225896.42</v>
       </c>
     </row>
     <row r="3">
@@ -653,16 +653,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.174765228330572</v>
+        <v>1.09240312685814</v>
       </c>
       <c r="D3" t="n">
-        <v>0.854811519684304</v>
+        <v>0.814209721409225</v>
       </c>
       <c r="E3" t="n">
-        <v>35.5</v>
+        <v>34.09</v>
       </c>
       <c r="F3" t="n">
-        <v>27.16</v>
+        <v>24.82</v>
       </c>
       <c r="G3" t="n">
         <v>66</v>
@@ -677,7 +677,7 @@
         <v>10.33333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>12381952</v>
+        <v>12228095.5</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         <v>159.78</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3199537086462676</v>
+        <v>0.2781934054489155</v>
       </c>
       <c r="S3" t="n">
         <v>2.78</v>
@@ -712,230 +712,230 @@
         <v>682</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9339156055982317</v>
+        <v>0.9038484482918615</v>
       </c>
       <c r="W3" t="n">
-        <v>1.085508761012832</v>
+        <v>1.057753775983993</v>
       </c>
       <c r="X3" t="n">
-        <v>38.01200000000001</v>
+        <v>37.71650000000001</v>
       </c>
       <c r="Y3" t="n">
-        <v>32.7035591742961</v>
+        <v>32.22867246991126</v>
       </c>
       <c r="Z3" t="n">
-        <v>190323168</v>
+        <v>300358024.33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>00980A.TW</t>
+          <t>00985A.TW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>主動野村臺灣優選</t>
+          <t>主動野村台灣50</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.5596367831124671</v>
+        <v>0.4110671500069321</v>
       </c>
       <c r="D4" t="n">
-        <v>0.555957964872452</v>
+        <v>0.3993870693716024</v>
       </c>
       <c r="E4" t="n">
-        <v>23.84</v>
+        <v>19.81</v>
       </c>
       <c r="F4" t="n">
-        <v>25.02</v>
+        <v>8.48</v>
       </c>
       <c r="G4" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H4" t="n">
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>7.02</v>
+        <v>6.95</v>
       </c>
       <c r="J4" t="n">
-        <v>9.824999999999999</v>
+        <v>9.972972972972974</v>
       </c>
       <c r="K4" t="n">
-        <v>8606781.050000001</v>
+        <v>61941711.35</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>15.61</v>
+        <v>15.02</v>
       </c>
       <c r="O4" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="P4" t="n">
-        <v>17.72</v>
+        <v>17.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>246.15</v>
+        <v>252.13</v>
       </c>
       <c r="R4" t="n">
-        <v>0.003678818240015147</v>
+        <v>0.01168008063532966</v>
       </c>
       <c r="S4" t="n">
-        <v>1.814</v>
+        <v>2.15</v>
       </c>
       <c r="T4" t="n">
-        <v>280.74</v>
+        <v>257.02</v>
       </c>
       <c r="U4" t="n">
-        <v>393</v>
+        <v>369</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9441958097350396</v>
+        <v>0.8800142152725333</v>
       </c>
       <c r="W4" t="n">
-        <v>1.034422542062475</v>
+        <v>1.047515665383063</v>
       </c>
       <c r="X4" t="n">
-        <v>25.24899999999998</v>
+        <v>22.511</v>
       </c>
       <c r="Y4" t="n">
-        <v>23.04667486505737</v>
+        <v>18.91141169020678</v>
       </c>
       <c r="Z4" t="n">
-        <v>128776742.56</v>
+        <v>446562111.17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>00985A.TW</t>
+          <t>009816.TW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>主動野村台灣50</t>
+          <t>凱基台灣TOP50</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.448462472623314</v>
+        <v>0.1413086699005885</v>
       </c>
       <c r="D5" t="n">
-        <v>0.431070957536938</v>
+        <v>0.106222889722142</v>
       </c>
       <c r="E5" t="n">
-        <v>20.37</v>
+        <v>15.67</v>
       </c>
       <c r="F5" t="n">
-        <v>9.210000000000001</v>
+        <v>22.77</v>
       </c>
       <c r="G5" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="H5" t="n">
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>6.95</v>
+        <v>5.32</v>
       </c>
       <c r="J5" t="n">
-        <v>9.972972972972974</v>
+        <v>10.54166666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>60932035.45</v>
+        <v>144554845.25</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>15.02</v>
+        <v>8.99</v>
       </c>
       <c r="O5" t="n">
-        <v>2.1</v>
+        <v>0.64</v>
       </c>
       <c r="P5" t="n">
-        <v>17.12</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>252.13</v>
+        <v>227.93</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01739151508637593</v>
+        <v>0.03508578017844655</v>
       </c>
       <c r="S5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>257.02</v>
+        <v>127.78</v>
       </c>
       <c r="U5" t="n">
-        <v>369</v>
+        <v>253</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8979303960679728</v>
+        <v>0.9556917634861096</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05575561797411</v>
+        <v>1.00759016239627</v>
       </c>
       <c r="X5" t="n">
-        <v>22.6855</v>
+        <v>16.3965</v>
       </c>
       <c r="Y5" t="n">
-        <v>19.29423784558021</v>
+        <v>15.55195811234729</v>
       </c>
       <c r="Z5" t="n">
-        <v>214651421.25</v>
+        <v>4039073031.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>009816.TW</t>
+          <t>009804.TW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>凱基台灣TOP50</t>
+          <t>聯邦台精彩50</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.1668972258908135</v>
+        <v>0.5657779524407172</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1309951930973374</v>
+        <v>0.5567062897931099</v>
       </c>
       <c r="E6" t="n">
-        <v>16.01</v>
+        <v>22.23</v>
       </c>
       <c r="F6" t="n">
-        <v>24.52</v>
+        <v>21.79</v>
       </c>
       <c r="G6" t="n">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="H6" t="n">
         <v>100</v>
       </c>
       <c r="I6" t="n">
-        <v>5.32</v>
+        <v>4.12</v>
       </c>
       <c r="J6" t="n">
-        <v>10.54166666666667</v>
+        <v>8.82258064516129</v>
       </c>
       <c r="K6" t="n">
-        <v>137942747</v>
+        <v>962806.5</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -946,168 +946,168 @@
         <v>2</v>
       </c>
       <c r="N6" t="n">
-        <v>8.99</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>0.64</v>
+        <v>0.76</v>
       </c>
       <c r="P6" t="n">
-        <v>9.630000000000001</v>
+        <v>10.39</v>
       </c>
       <c r="Q6" t="n">
-        <v>227.93</v>
+        <v>133.05</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03590203279347604</v>
+        <v>0.009071662647607281</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.786</v>
       </c>
       <c r="T6" t="n">
-        <v>127.78</v>
+        <v>255.36</v>
       </c>
       <c r="U6" t="n">
-        <v>253</v>
+        <v>547</v>
       </c>
       <c r="V6" t="n">
-        <v>0.974259112760908</v>
+        <v>0.9392031771515484</v>
       </c>
       <c r="W6" t="n">
-        <v>1.022553736755391</v>
+        <v>1.006841028094061</v>
       </c>
       <c r="X6" t="n">
-        <v>16.433</v>
+        <v>23.669</v>
       </c>
       <c r="Y6" t="n">
-        <v>15.65687887543245</v>
+        <v>22.07895723327956</v>
       </c>
       <c r="Z6" t="n">
-        <v>1991009907.94</v>
+        <v>17651331.36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>009824.TW</t>
+          <t>00830.TW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>群益美國科技巨頭</t>
+          <t>國泰費城半導體</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01758283729010124</v>
+        <v>2.331209318779754</v>
       </c>
       <c r="D7" t="n">
-        <v>0.006969103206378779</v>
+        <v>2.174686693801406</v>
       </c>
       <c r="E7" t="n">
-        <v>10.35</v>
+        <v>80.05</v>
       </c>
       <c r="F7" t="n">
-        <v>33.02</v>
+        <v>28.52</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>495</v>
       </c>
       <c r="H7" t="n">
-        <v>100</v>
+        <v>97.17</v>
       </c>
       <c r="I7" t="n">
-        <v>5.26</v>
+        <v>3.93</v>
       </c>
       <c r="J7" t="n">
-        <v>5.75</v>
+        <v>12.29090909090909</v>
       </c>
       <c r="K7" t="n">
-        <v>3123653</v>
+        <v>10944622</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>2</v>
       </c>
       <c r="N7" t="n">
-        <v>7.35</v>
+        <v>13.29</v>
       </c>
       <c r="O7" t="n">
-        <v>1.39</v>
+        <v>-12.33</v>
       </c>
       <c r="P7" t="n">
-        <v>8.74</v>
+        <v>0.9599999999999991</v>
       </c>
       <c r="Q7" t="n">
-        <v>1975.8</v>
+        <v>19.85</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01061373408372246</v>
+        <v>0.156522624978348</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>17.71</v>
       </c>
       <c r="T7" t="n">
-        <v>21.06</v>
+        <v>1946.3</v>
       </c>
       <c r="U7" t="n">
-        <v>23</v>
+        <v>6084</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9816009104704093</v>
+        <v>0.9281966547815751</v>
       </c>
       <c r="W7" t="n">
-        <v>1.023314693788514</v>
+        <v>1.038408466342389</v>
       </c>
       <c r="X7" t="n">
-        <v>10.544</v>
+        <v>86.24250000000001</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.11419073997877</v>
+        <v>77.08912493940078</v>
       </c>
       <c r="Z7" t="n">
-        <v>43232622.75</v>
+        <v>1347560099</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>009804.TW</t>
+          <t>00663L.TW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>聯邦台精彩50</t>
+          <t>國泰臺灣加權正2</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.6085646441427486</v>
+        <v>10.66359996090713</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5919483143754691</v>
+        <v>2.837525591715994</v>
       </c>
       <c r="E8" t="n">
-        <v>22.87</v>
+        <v>97.95</v>
       </c>
       <c r="F8" t="n">
-        <v>23.79</v>
+        <v>17.16</v>
       </c>
       <c r="G8" t="n">
-        <v>62</v>
+        <v>564</v>
       </c>
       <c r="H8" t="n">
-        <v>100</v>
+        <v>89.89</v>
       </c>
       <c r="I8" t="n">
-        <v>4.12</v>
+        <v>3.76</v>
       </c>
       <c r="J8" t="n">
-        <v>8.82258064516129</v>
+        <v>11.9113475177305</v>
       </c>
       <c r="K8" t="n">
-        <v>973657.65</v>
+        <v>5616717.2</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1118,82 +1118,82 @@
         <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>9.630000000000001</v>
+        <v>15.99</v>
       </c>
       <c r="O8" t="n">
-        <v>0.76</v>
+        <v>-24.46</v>
       </c>
       <c r="P8" t="n">
-        <v>10.39</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>133.05</v>
+        <v>18.35</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01661632976727945</v>
+        <v>7.826074369191138</v>
       </c>
       <c r="S8" t="n">
-        <v>2.786</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>255.36</v>
+        <v>2121.97</v>
       </c>
       <c r="U8" t="n">
-        <v>547</v>
+        <v>6718</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9629473684210527</v>
+        <v>0.8855037743524834</v>
       </c>
       <c r="W8" t="n">
-        <v>1.025431977512022</v>
+        <v>1.012547530140835</v>
       </c>
       <c r="X8" t="n">
-        <v>23.75</v>
+        <v>110.6150000000001</v>
       </c>
       <c r="Y8" t="n">
-        <v>22.30279579878996</v>
+        <v>96.73619961956371</v>
       </c>
       <c r="Z8" t="n">
-        <v>7809190.2</v>
+        <v>1027953220.35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>00830.TW</t>
+          <t>00631L.TW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>國泰費城半導體</t>
+          <t>元大台灣50正2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.434204279676043</v>
+        <v>14.42066602571507</v>
       </c>
       <c r="D9" t="n">
-        <v>2.243735914155907</v>
+        <v>3.247171611515903</v>
       </c>
       <c r="E9" t="n">
-        <v>82.95</v>
+        <v>34.16</v>
       </c>
       <c r="F9" t="n">
-        <v>35.87</v>
+        <v>16.92</v>
       </c>
       <c r="G9" t="n">
-        <v>495</v>
+        <v>644</v>
       </c>
       <c r="H9" t="n">
-        <v>97.17</v>
+        <v>89.44</v>
       </c>
       <c r="I9" t="n">
-        <v>3.93</v>
+        <v>3.74</v>
       </c>
       <c r="J9" t="n">
-        <v>12.29090909090909</v>
+        <v>12.68167701863354</v>
       </c>
       <c r="K9" t="n">
-        <v>10379313.9</v>
+        <v>207998588.25</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1204,512 +1204,508 @@
         <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>13.29</v>
+        <v>17.37</v>
       </c>
       <c r="O9" t="n">
-        <v>-12.33</v>
+        <v>-12.43</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9599999999999991</v>
+        <v>4.940000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>19.85</v>
+        <v>15.49</v>
       </c>
       <c r="R9" t="n">
-        <v>0.190468365520136</v>
+        <v>11.17349441419916</v>
       </c>
       <c r="S9" t="n">
-        <v>17.71</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1946.3</v>
+        <v>2407.1</v>
       </c>
       <c r="U9" t="n">
-        <v>6084</v>
+        <v>8167</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9580457944734789</v>
+        <v>0.8923020661912602</v>
       </c>
       <c r="W9" t="n">
-        <v>1.065094471943548</v>
+        <v>1.016840251700524</v>
       </c>
       <c r="X9" t="n">
-        <v>86.58250000000001</v>
+        <v>38.28299999999998</v>
       </c>
       <c r="Y9" t="n">
-        <v>77.88041547961066</v>
+        <v>33.59426413625162</v>
       </c>
       <c r="Z9" t="n">
-        <v>541734588.15</v>
+        <v>13834696768.48</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>00663L.TW</t>
+          <t>00904.TW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>國泰臺灣加權正2</t>
+          <t>台新臺灣半導體30</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11.33496630561449</v>
+        <v>1.674561633030607</v>
       </c>
       <c r="D10" t="n">
-        <v>2.920362190310692</v>
+        <v>1.602978373533956</v>
       </c>
       <c r="E10" t="n">
-        <v>103.55</v>
+        <v>37.27</v>
       </c>
       <c r="F10" t="n">
-        <v>19.73</v>
+        <v>18.35</v>
       </c>
       <c r="G10" t="n">
-        <v>564</v>
+        <v>239</v>
       </c>
       <c r="H10" t="n">
-        <v>89.89</v>
+        <v>99.16</v>
       </c>
       <c r="I10" t="n">
-        <v>3.76</v>
+        <v>3.55</v>
       </c>
       <c r="J10" t="n">
-        <v>11.9113475177305</v>
+        <v>10.78242677824268</v>
       </c>
       <c r="K10" t="n">
-        <v>5295446.75</v>
+        <v>4074368.5</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>15.99</v>
+        <v>11.85</v>
       </c>
       <c r="O10" t="n">
-        <v>-24.46</v>
+        <v>-12.45</v>
       </c>
       <c r="P10" t="n">
-        <v>-8.470000000000001</v>
+        <v>-0.5999999999999996</v>
       </c>
       <c r="Q10" t="n">
-        <v>18.35</v>
+        <v>37.53</v>
       </c>
       <c r="R10" t="n">
-        <v>8.414604115303796</v>
+        <v>0.07158325949665167</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>7.050000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>2121.97</v>
+        <v>848.62</v>
       </c>
       <c r="U10" t="n">
-        <v>6718</v>
+        <v>2577</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9308701905789279</v>
+        <v>0.9037999854499602</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0498713731512</v>
+        <v>1.05178598154007</v>
       </c>
       <c r="X10" t="n">
-        <v>111.2400000000001</v>
+        <v>41.23699999999999</v>
       </c>
       <c r="Y10" t="n">
-        <v>98.63113010615152</v>
+        <v>35.43496552923028</v>
       </c>
       <c r="Z10" t="n">
-        <v>506965992.35</v>
+        <v>53209335.44000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>00631L.TW</t>
+          <t>00913.TW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>兆豐台灣晶圓製造</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15.20682826333405</v>
+        <v>1.514062491908562</v>
       </c>
       <c r="D11" t="n">
-        <v>3.338522960520756</v>
+        <v>1.512619636909752</v>
       </c>
       <c r="E11" t="n">
-        <v>35.89</v>
+        <v>45.9</v>
       </c>
       <c r="F11" t="n">
-        <v>19.45</v>
+        <v>25.59</v>
       </c>
       <c r="G11" t="n">
-        <v>644</v>
+        <v>262</v>
       </c>
       <c r="H11" t="n">
-        <v>89.44</v>
+        <v>96.18000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="J11" t="n">
-        <v>12.68167701863354</v>
+        <v>12.79770992366412</v>
       </c>
       <c r="K11" t="n">
-        <v>193468483.75</v>
+        <v>1564956.05</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>17.37</v>
+        <v>13.5</v>
       </c>
       <c r="O11" t="n">
-        <v>-12.43</v>
+        <v>-9.19</v>
       </c>
       <c r="P11" t="n">
-        <v>4.940000000000001</v>
+        <v>4.31</v>
       </c>
       <c r="Q11" t="n">
-        <v>15.49</v>
+        <v>28.72</v>
       </c>
       <c r="R11" t="n">
-        <v>11.86830530281329</v>
+        <v>0.001442854998810361</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>6.699999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>2407.1</v>
+        <v>916.5599999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>8167</v>
+        <v>3353</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9324742134116245</v>
+        <v>0.9121621621621619</v>
       </c>
       <c r="W11" t="n">
-        <v>1.049483711323289</v>
+        <v>1.036244928038085</v>
       </c>
       <c r="X11" t="n">
-        <v>38.48899999999998</v>
+        <v>50.32000000000001</v>
       </c>
       <c r="Y11" t="n">
-        <v>34.19776754300118</v>
+        <v>44.29454731991032</v>
       </c>
       <c r="Z11" t="n">
-        <v>6268234618.650001</v>
+        <v>50253018.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>00904.TW</t>
+          <t>00685L.TW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>台新臺灣半導體30</t>
+          <t>群益臺灣加權正2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.745286191067325</v>
+        <v>9.665323424012344</v>
       </c>
       <c r="D12" t="n">
-        <v>1.660305801380985</v>
+        <v>2.671757984435356</v>
       </c>
       <c r="E12" t="n">
-        <v>38.39</v>
+        <v>11.24</v>
       </c>
       <c r="F12" t="n">
-        <v>16.37</v>
+        <v>17.78</v>
       </c>
       <c r="G12" t="n">
-        <v>239</v>
+        <v>514</v>
       </c>
       <c r="H12" t="n">
-        <v>99.16</v>
+        <v>88.52</v>
       </c>
       <c r="I12" t="n">
-        <v>3.55</v>
+        <v>3.46</v>
       </c>
       <c r="J12" t="n">
-        <v>10.78242677824268</v>
+        <v>12.18093385214008</v>
       </c>
       <c r="K12" t="n">
-        <v>4040201.3</v>
+        <v>293822522.75</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>11.85</v>
+        <v>15.89</v>
       </c>
       <c r="O12" t="n">
-        <v>-12.45</v>
+        <v>-18.5</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.5999999999999996</v>
+        <v>-2.609999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>37.53</v>
+        <v>18.65</v>
       </c>
       <c r="R12" t="n">
-        <v>0.08498038968633992</v>
+        <v>6.993565439576988</v>
       </c>
       <c r="S12" t="n">
-        <v>7.050000000000001</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>848.62</v>
+        <v>1777.84</v>
       </c>
       <c r="U12" t="n">
-        <v>2577</v>
+        <v>6261</v>
       </c>
       <c r="V12" t="n">
-        <v>0.9245701074129378</v>
+        <v>0.8872750236817175</v>
       </c>
       <c r="W12" t="n">
-        <v>1.067190732354679</v>
+        <v>1.014052622924962</v>
       </c>
       <c r="X12" t="n">
-        <v>41.522</v>
+        <v>12.668</v>
       </c>
       <c r="Y12" t="n">
-        <v>35.97295107248097</v>
+        <v>11.08423739152612</v>
       </c>
       <c r="Z12" t="n">
-        <v>33249425.44</v>
+        <v>7508100988.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>00913.TW</t>
+          <t>009809.TW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>兆豐台灣晶圓製造</t>
+          <t>富邦淨零ESG50</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.599806263419317</v>
+        <v>0.3114609288613821</v>
       </c>
       <c r="D13" t="n">
-        <v>1.56811093503766</v>
+        <v>0.2683534629896991</v>
       </c>
       <c r="E13" t="n">
-        <v>47.61</v>
+        <v>17.64</v>
       </c>
       <c r="F13" t="n">
-        <v>26.52</v>
+        <v>18.7</v>
       </c>
       <c r="G13" t="n">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="H13" t="n">
-        <v>96.18000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="I13" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J13" t="n">
-        <v>12.79770992366412</v>
+        <v>8.235294117647058</v>
       </c>
       <c r="K13" t="n">
-        <v>1615721.45</v>
+        <v>312868.2</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>2</v>
       </c>
       <c r="N13" t="n">
-        <v>13.5</v>
+        <v>7.76</v>
       </c>
       <c r="O13" t="n">
-        <v>-9.19</v>
+        <v>-0.12</v>
       </c>
       <c r="P13" t="n">
-        <v>4.31</v>
+        <v>7.64</v>
       </c>
       <c r="Q13" t="n">
-        <v>28.72</v>
+        <v>172.16</v>
       </c>
       <c r="R13" t="n">
-        <v>0.03169532838165656</v>
+        <v>0.04310746587168302</v>
       </c>
       <c r="S13" t="n">
-        <v>6.699999999999999</v>
+        <v>0.315</v>
       </c>
       <c r="T13" t="n">
-        <v>916.5599999999999</v>
+        <v>115.56</v>
       </c>
       <c r="U13" t="n">
-        <v>3353</v>
+        <v>280</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9406767102988391</v>
+        <v>0.9577067158911992</v>
       </c>
       <c r="W13" t="n">
-        <v>1.060010611598225</v>
+        <v>1.003456320501505</v>
       </c>
       <c r="X13" t="n">
-        <v>50.6125</v>
+        <v>18.419</v>
       </c>
       <c r="Y13" t="n">
-        <v>44.91464470173207</v>
+        <v>17.57924051062224</v>
       </c>
       <c r="Z13" t="n">
-        <v>41321147.49</v>
+        <v>8249081.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>00685L.TW</t>
+          <t>00715L.TW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>群益臺灣加權正2</t>
+          <t>期街口布蘭特正2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10.25808155292319</v>
+        <v>6.300336392211062</v>
       </c>
       <c r="D14" t="n">
-        <v>2.751166080511013</v>
+        <v>2.534547809451252</v>
       </c>
       <c r="E14" t="n">
-        <v>11.86</v>
+        <v>91.05</v>
       </c>
       <c r="F14" t="n">
-        <v>19.86</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>514</v>
+        <v>425</v>
       </c>
       <c r="H14" t="n">
-        <v>88.52</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>3.46</v>
+        <v>3.32</v>
       </c>
       <c r="J14" t="n">
-        <v>12.18093385214008</v>
+        <v>17.11294117647059</v>
       </c>
       <c r="K14" t="n">
-        <v>269001514.1</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
+        <v>2968688.6</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>15.89</v>
+        <v>32.14</v>
       </c>
       <c r="O14" t="n">
-        <v>-18.5</v>
+        <v>-44.86</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.609999999999999</v>
+        <v>-12.72</v>
       </c>
       <c r="Q14" t="n">
-        <v>18.65</v>
+        <v>14.59</v>
       </c>
       <c r="R14" t="n">
-        <v>7.50691547241218</v>
+        <v>3.76578858275981</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1777.84</v>
+        <v>1409.31</v>
       </c>
       <c r="U14" t="n">
-        <v>6261</v>
+        <v>7273</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9310723818495836</v>
+        <v>1.183774296301113</v>
       </c>
       <c r="W14" t="n">
-        <v>1.049982669828875</v>
+        <v>1.498263832023013</v>
       </c>
       <c r="X14" t="n">
-        <v>12.738</v>
+        <v>76.91499999999994</v>
       </c>
       <c r="Y14" t="n">
-        <v>11.29542452537138</v>
+        <v>60.77033834358855</v>
       </c>
       <c r="Z14" t="n">
-        <v>3149814973</v>
+        <v>600988363.05</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>009809.TW</t>
+          <t>00675L.TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>富邦淨零ESG50</t>
+          <t>富邦臺灣加權正2</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.3361492940217485</v>
+        <v>10.12613461925161</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2970180966987372</v>
+        <v>2.775765127801778</v>
       </c>
       <c r="E15" t="n">
-        <v>17.96</v>
+        <v>296.3</v>
       </c>
       <c r="F15" t="n">
-        <v>18.05</v>
+        <v>16.88</v>
       </c>
       <c r="G15" t="n">
-        <v>34</v>
+        <v>564</v>
       </c>
       <c r="H15" t="n">
-        <v>97.06</v>
+        <v>87.06</v>
       </c>
       <c r="I15" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="J15" t="n">
-        <v>8.235294117647058</v>
+        <v>12.38297872340426</v>
       </c>
       <c r="K15" t="n">
-        <v>298691.1</v>
+        <v>1303536.55</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1720,168 +1716,172 @@
         <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>7.76</v>
+        <v>15.7</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.12</v>
+        <v>-24.73</v>
       </c>
       <c r="P15" t="n">
-        <v>7.64</v>
+        <v>-9.030000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>172.16</v>
+        <v>16.61</v>
       </c>
       <c r="R15" t="n">
-        <v>0.03913119732301129</v>
+        <v>7.350369491449831</v>
       </c>
       <c r="S15" t="n">
-        <v>0.315</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>115.56</v>
+        <v>1792.47</v>
       </c>
       <c r="U15" t="n">
-        <v>280</v>
+        <v>6984</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9729407622091605</v>
+        <v>0.8844842125687502</v>
       </c>
       <c r="W15" t="n">
-        <v>1.014712611447139</v>
+        <v>1.013166830524721</v>
       </c>
       <c r="X15" t="n">
-        <v>18.4595</v>
+        <v>334.9975000000001</v>
       </c>
       <c r="Y15" t="n">
-        <v>17.69959276881977</v>
+        <v>292.4493687249371</v>
       </c>
       <c r="Z15" t="n">
-        <v>3822480.68</v>
+        <v>837214909.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>00715L.TW</t>
+          <t>00935.TW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>期街口布蘭特正2</t>
+          <t>野村臺灣新科技50</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6.042562076290243</v>
+        <v>1.285363417515469</v>
       </c>
       <c r="D16" t="n">
-        <v>2.611101266995659</v>
+        <v>1.050055739157653</v>
       </c>
       <c r="E16" t="n">
-        <v>87.8</v>
+        <v>53.3</v>
       </c>
       <c r="F16" t="n">
-        <v>92.09</v>
+        <v>18.84</v>
       </c>
       <c r="G16" t="n">
-        <v>425</v>
+        <v>136</v>
       </c>
       <c r="H16" t="n">
-        <v>77.65000000000001</v>
+        <v>83.09</v>
       </c>
       <c r="I16" t="n">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="J16" t="n">
-        <v>17.11294117647059</v>
+        <v>12.30882352941176</v>
       </c>
       <c r="K16" t="n">
-        <v>2856794.45</v>
-      </c>
-      <c r="L16" t="inlineStr"/>
+        <v>11922759.9</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>32.14</v>
+        <v>14.6</v>
       </c>
       <c r="O16" t="n">
-        <v>-44.86</v>
+        <v>-8.99</v>
       </c>
       <c r="P16" t="n">
-        <v>-12.72</v>
+        <v>5.609999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>14.59</v>
+        <v>43.74</v>
       </c>
       <c r="R16" t="n">
-        <v>3.431460809294584</v>
+        <v>0.2353076783578159</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="T16" t="n">
-        <v>1409.31</v>
+        <v>428.12</v>
       </c>
       <c r="U16" t="n">
-        <v>7273</v>
+        <v>1674</v>
       </c>
       <c r="V16" t="n">
-        <v>1.15896115896116</v>
+        <v>0.9060003399626041</v>
       </c>
       <c r="W16" t="n">
-        <v>1.450291013862621</v>
+        <v>1.020457296669452</v>
       </c>
       <c r="X16" t="n">
-        <v>75.75749999999995</v>
+        <v>58.83</v>
       </c>
       <c r="Y16" t="n">
-        <v>60.53957389293792</v>
+        <v>52.23148501555085</v>
       </c>
       <c r="Z16" t="n">
-        <v>138067343.8</v>
+        <v>811448207.6999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>00675L.TW</t>
+          <t>00894.TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>富邦臺灣加權正2</t>
+          <t>中信小資高價30</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10.76510601527469</v>
+        <v>1.868960096774013</v>
       </c>
       <c r="D17" t="n">
-        <v>2.857305715456577</v>
+        <v>1.653218619091069</v>
       </c>
       <c r="E17" t="n">
-        <v>313.2</v>
+        <v>44.4</v>
       </c>
       <c r="F17" t="n">
-        <v>19.41</v>
+        <v>20.04</v>
       </c>
       <c r="G17" t="n">
-        <v>564</v>
+        <v>243</v>
       </c>
       <c r="H17" t="n">
-        <v>87.06</v>
+        <v>82.72</v>
       </c>
       <c r="I17" t="n">
-        <v>3.18</v>
+        <v>2.88</v>
       </c>
       <c r="J17" t="n">
-        <v>12.38297872340426</v>
+        <v>15.32921810699589</v>
       </c>
       <c r="K17" t="n">
-        <v>1193137.45</v>
+        <v>1362553.1</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M17" t="n">
@@ -1891,79 +1891,79 @@
         <v>15.7</v>
       </c>
       <c r="O17" t="n">
-        <v>-24.73</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>-9.030000000000001</v>
+        <v>7.319999999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>16.61</v>
+        <v>22.58</v>
       </c>
       <c r="R17" t="n">
-        <v>7.907800299818111</v>
+        <v>0.2157414776829443</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>7.549999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>1792.47</v>
+        <v>698.73</v>
       </c>
       <c r="U17" t="n">
-        <v>6984</v>
+        <v>3725</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9297010085118695</v>
+        <v>0.9074187614960151</v>
       </c>
       <c r="W17" t="n">
-        <v>1.050324320799554</v>
+        <v>1.014808861167463</v>
       </c>
       <c r="X17" t="n">
-        <v>336.8825000000001</v>
+        <v>48.92999999999998</v>
       </c>
       <c r="Y17" t="n">
-        <v>298.1936091526264</v>
+        <v>43.75208149928948</v>
       </c>
       <c r="Z17" t="n">
-        <v>264359278.8</v>
+        <v>108079989.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>00935.TW</t>
+          <t>00901.TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>野村臺灣新科技50</t>
+          <t>永豐智能車供應鏈</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.362937422981553</v>
+        <v>1.626843208706587</v>
       </c>
       <c r="D18" t="n">
-        <v>1.095707517668272</v>
+        <v>1.619167113035596</v>
       </c>
       <c r="E18" t="n">
-        <v>55.2</v>
+        <v>42.92</v>
       </c>
       <c r="F18" t="n">
-        <v>20.01</v>
+        <v>18.11</v>
       </c>
       <c r="G18" t="n">
-        <v>136</v>
+        <v>276</v>
       </c>
       <c r="H18" t="n">
-        <v>83.09</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>3.15</v>
+        <v>2.79</v>
       </c>
       <c r="J18" t="n">
-        <v>12.30882352941176</v>
+        <v>13.22463768115942</v>
       </c>
       <c r="K18" t="n">
-        <v>11830938.25</v>
+        <v>328518.6</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1974,82 +1974,82 @@
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>14.6</v>
+        <v>15.18</v>
       </c>
       <c r="O18" t="n">
-        <v>-8.99</v>
+        <v>-7.3</v>
       </c>
       <c r="P18" t="n">
-        <v>5.609999999999999</v>
+        <v>7.88</v>
       </c>
       <c r="Q18" t="n">
-        <v>43.74</v>
+        <v>24.17</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2672299053132807</v>
+        <v>0.007676095670991145</v>
       </c>
       <c r="S18" t="n">
-        <v>4.98</v>
+        <v>4.671</v>
       </c>
       <c r="T18" t="n">
-        <v>428.12</v>
+        <v>771.28</v>
       </c>
       <c r="U18" t="n">
-        <v>1674</v>
+        <v>3650</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9326687505280055</v>
+        <v>0.9146607848778359</v>
       </c>
       <c r="W18" t="n">
-        <v>1.040167517504692</v>
+        <v>1.01391982778593</v>
       </c>
       <c r="X18" t="n">
-        <v>59.185</v>
+        <v>46.92449999999999</v>
       </c>
       <c r="Y18" t="n">
-        <v>53.06837511367585</v>
+        <v>42.33076306804579</v>
       </c>
       <c r="Z18" t="n">
-        <v>495106077.6</v>
+        <v>10173713.88</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>00894.TW</t>
+          <t>0057.TW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>中信小資高價30</t>
+          <t>富邦摩台</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.969066436607132</v>
+        <v>5.936191073613769</v>
       </c>
       <c r="D19" t="n">
-        <v>1.711461359660664</v>
+        <v>4.719373753012424</v>
       </c>
       <c r="E19" t="n">
-        <v>46.13</v>
+        <v>313.05</v>
       </c>
       <c r="F19" t="n">
-        <v>21.07</v>
+        <v>17.43</v>
       </c>
       <c r="G19" t="n">
-        <v>243</v>
+        <v>1245</v>
       </c>
       <c r="H19" t="n">
-        <v>82.72</v>
+        <v>93.33</v>
       </c>
       <c r="I19" t="n">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="J19" t="n">
-        <v>15.32921810699589</v>
+        <v>12.02409638554217</v>
       </c>
       <c r="K19" t="n">
-        <v>1319182.65</v>
+        <v>29885.4</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -2060,168 +2060,168 @@
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>15.7</v>
+        <v>14.45</v>
       </c>
       <c r="O19" t="n">
-        <v>-8.380000000000001</v>
+        <v>-6.48</v>
       </c>
       <c r="P19" t="n">
-        <v>7.319999999999999</v>
+        <v>7.969999999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>22.58</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2576050769464686</v>
+        <v>1.216817320601345</v>
       </c>
       <c r="S19" t="n">
-        <v>7.549999999999999</v>
+        <v>1.685</v>
       </c>
       <c r="T19" t="n">
-        <v>698.73</v>
+        <v>3287.55</v>
       </c>
       <c r="U19" t="n">
-        <v>3725</v>
+        <v>14970</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9378971017292038</v>
+        <v>0.9495211447030186</v>
       </c>
       <c r="W19" t="n">
-        <v>1.038028849035007</v>
+        <v>1.014462863131028</v>
       </c>
       <c r="X19" t="n">
-        <v>49.18449999999998</v>
+        <v>329.6925000000001</v>
       </c>
       <c r="Y19" t="n">
-        <v>44.43999802402821</v>
+        <v>308.5869491898459</v>
       </c>
       <c r="Z19" t="n">
-        <v>65363488.33000001</v>
+        <v>4709211.15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>00901.TW</t>
+          <t>00881.TW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>永豐智能車供應鏈</t>
+          <t>國泰台灣科技龍頭</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.705807688796962</v>
+        <v>1.836191360180621</v>
       </c>
       <c r="D20" t="n">
-        <v>1.676778151185065</v>
+        <v>1.718702772348137</v>
       </c>
       <c r="E20" t="n">
-        <v>44.29</v>
+        <v>46.9</v>
       </c>
       <c r="F20" t="n">
-        <v>19.35</v>
+        <v>14.66</v>
       </c>
       <c r="G20" t="n">
-        <v>276</v>
+        <v>384</v>
       </c>
       <c r="H20" t="n">
-        <v>89.48999999999999</v>
+        <v>89.58</v>
       </c>
       <c r="I20" t="n">
-        <v>2.79</v>
+        <v>2.52</v>
       </c>
       <c r="J20" t="n">
-        <v>13.22463768115942</v>
+        <v>15.328125</v>
       </c>
       <c r="K20" t="n">
-        <v>319357.95</v>
+        <v>18438351.55</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>15.18</v>
+        <v>10.9</v>
       </c>
       <c r="O20" t="n">
-        <v>-7.3</v>
+        <v>-4.28</v>
       </c>
       <c r="P20" t="n">
-        <v>7.88</v>
+        <v>6.62</v>
       </c>
       <c r="Q20" t="n">
-        <v>24.17</v>
+        <v>15.81</v>
       </c>
       <c r="R20" t="n">
-        <v>0.02902953761189719</v>
+        <v>0.1174885878324847</v>
       </c>
       <c r="S20" t="n">
-        <v>4.671</v>
+        <v>12.5</v>
       </c>
       <c r="T20" t="n">
-        <v>771.28</v>
+        <v>966.91</v>
       </c>
       <c r="U20" t="n">
-        <v>3650</v>
+        <v>5886</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9390338276918512</v>
+        <v>0.9185002399067793</v>
       </c>
       <c r="W20" t="n">
-        <v>1.031271547717579</v>
+        <v>1.007336592807397</v>
       </c>
       <c r="X20" t="n">
-        <v>47.16549999999999</v>
+        <v>51.06149999999999</v>
       </c>
       <c r="Y20" t="n">
-        <v>42.94698142116216</v>
+        <v>46.55841983193724</v>
       </c>
       <c r="Z20" t="n">
-        <v>17012807.67</v>
+        <v>1290498664.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>0057.TW</t>
+          <t>0052.TW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>富邦摩台</t>
+          <t>富邦科技</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6.062277776636446</v>
+        <v>7.949298567842233</v>
       </c>
       <c r="D21" t="n">
-        <v>4.841076327541531</v>
+        <v>4.810499656450608</v>
       </c>
       <c r="E21" t="n">
-        <v>318.7</v>
+        <v>60.8</v>
       </c>
       <c r="F21" t="n">
-        <v>17.04</v>
+        <v>20.78</v>
       </c>
       <c r="G21" t="n">
-        <v>1245</v>
+        <v>1111</v>
       </c>
       <c r="H21" t="n">
-        <v>93.33</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>2.64</v>
+        <v>2.45</v>
       </c>
       <c r="J21" t="n">
-        <v>12.02409638554217</v>
+        <v>14.18091809180918</v>
       </c>
       <c r="K21" t="n">
-        <v>30948.05</v>
+        <v>21138240</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -2232,82 +2232,82 @@
         <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>14.45</v>
+        <v>12.7</v>
       </c>
       <c r="O21" t="n">
-        <v>-6.48</v>
+        <v>-14.18</v>
       </c>
       <c r="P21" t="n">
-        <v>7.969999999999999</v>
+        <v>-1.48</v>
       </c>
       <c r="Q21" t="n">
-        <v>8.970000000000001</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="R21" t="n">
-        <v>1.221201449094915</v>
+        <v>3.138798911391625</v>
       </c>
       <c r="S21" t="n">
-        <v>1.685</v>
+        <v>2.232857285714286</v>
       </c>
       <c r="T21" t="n">
-        <v>3287.55</v>
+        <v>2723.42</v>
       </c>
       <c r="U21" t="n">
-        <v>14970</v>
+        <v>15755</v>
       </c>
       <c r="V21" t="n">
-        <v>0.963924658414681</v>
+        <v>0.943074298123157</v>
       </c>
       <c r="W21" t="n">
-        <v>1.024939990475596</v>
+        <v>1.013805308004383</v>
       </c>
       <c r="X21" t="n">
-        <v>330.6275000000001</v>
+        <v>64.47000000000007</v>
       </c>
       <c r="Y21" t="n">
-        <v>310.9450338181417</v>
+        <v>59.97206714145271</v>
       </c>
       <c r="Z21" t="n">
-        <v>2930765.2</v>
+        <v>1618030515.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>00881.TW</t>
+          <t>00735.TW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>國泰台灣科技龍頭</t>
+          <t>國泰臺韓科技</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.91115103015939</v>
+        <v>2.841900854214286</v>
       </c>
       <c r="D22" t="n">
-        <v>1.778188111242962</v>
+        <v>2.416742375541722</v>
       </c>
       <c r="E22" t="n">
-        <v>48.38</v>
+        <v>96.75</v>
       </c>
       <c r="F22" t="n">
-        <v>15.47</v>
+        <v>39.41</v>
       </c>
       <c r="G22" t="n">
-        <v>384</v>
+        <v>498</v>
       </c>
       <c r="H22" t="n">
-        <v>89.58</v>
+        <v>86.55</v>
       </c>
       <c r="I22" t="n">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="J22" t="n">
-        <v>15.328125</v>
+        <v>13.81124497991968</v>
       </c>
       <c r="K22" t="n">
-        <v>17686977.85</v>
+        <v>2041702.5</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -2318,82 +2318,82 @@
         <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>10.9</v>
+        <v>21.39</v>
       </c>
       <c r="O22" t="n">
-        <v>-4.28</v>
+        <v>-6.04</v>
       </c>
       <c r="P22" t="n">
-        <v>6.62</v>
+        <v>15.35</v>
       </c>
       <c r="Q22" t="n">
-        <v>15.81</v>
+        <v>14.26</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1329629189164279</v>
+        <v>0.425158478672564</v>
       </c>
       <c r="S22" t="n">
-        <v>12.5</v>
+        <v>13.37</v>
       </c>
       <c r="T22" t="n">
-        <v>966.91</v>
+        <v>1133.84</v>
       </c>
       <c r="U22" t="n">
-        <v>5886</v>
+        <v>6878</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9428685577307234</v>
+        <v>0.9362978733699477</v>
       </c>
       <c r="W22" t="n">
-        <v>1.024471315404593</v>
+        <v>1.060048552042703</v>
       </c>
       <c r="X22" t="n">
-        <v>51.31149999999999</v>
+        <v>103.3324999999999</v>
       </c>
       <c r="Y22" t="n">
-        <v>47.22435784441009</v>
+        <v>91.26940441884824</v>
       </c>
       <c r="Z22" t="n">
-        <v>870941501.24</v>
+        <v>171374436</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>0052.TW</t>
+          <t>0050.TW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>富邦科技</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8.143308767623157</v>
+        <v>5.32514280344295</v>
       </c>
       <c r="D23" t="n">
-        <v>4.934436041392456</v>
+        <v>5.32514280344295</v>
       </c>
       <c r="E23" t="n">
-        <v>62.15</v>
+        <v>104.95</v>
       </c>
       <c r="F23" t="n">
-        <v>22.6</v>
+        <v>21.87</v>
       </c>
       <c r="G23" t="n">
-        <v>1111</v>
+        <v>1695</v>
       </c>
       <c r="H23" t="n">
-        <v>88.20999999999999</v>
+        <v>90.97</v>
       </c>
       <c r="I23" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="J23" t="n">
-        <v>14.18091809180918</v>
+        <v>13.46961651917404</v>
       </c>
       <c r="K23" t="n">
-        <v>20482484.65</v>
+        <v>126699275.45</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -2404,82 +2404,82 @@
         <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>12.7</v>
+        <v>13.94</v>
       </c>
       <c r="O23" t="n">
-        <v>-14.18</v>
+        <v>-5.91</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.48</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="Q23" t="n">
-        <v>8.050000000000001</v>
+        <v>6.04</v>
       </c>
       <c r="R23" t="n">
-        <v>3.208872726230702</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.232857285714286</v>
+        <v>4.84625</v>
       </c>
       <c r="T23" t="n">
-        <v>2723.42</v>
+        <v>3824.71</v>
       </c>
       <c r="U23" t="n">
-        <v>15755</v>
+        <v>22831</v>
       </c>
       <c r="V23" t="n">
-        <v>0.960921495110354</v>
+        <v>0.9466895183113834</v>
       </c>
       <c r="W23" t="n">
-        <v>1.027191332233767</v>
+        <v>1.011858167578455</v>
       </c>
       <c r="X23" t="n">
-        <v>64.67750000000008</v>
+        <v>110.86</v>
       </c>
       <c r="Y23" t="n">
-        <v>60.50479404342945</v>
+        <v>103.7200700283547</v>
       </c>
       <c r="Z23" t="n">
-        <v>951384244.8</v>
+        <v>23853451602</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>00735.TW</t>
+          <t>0053.TW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>國泰臺韓科技</t>
+          <t>元大科技市值</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2.971062704400238</v>
+        <v>6.4095910657457</v>
       </c>
       <c r="D24" t="n">
-        <v>2.490853452794934</v>
+        <v>4.77494002757274</v>
       </c>
       <c r="E24" t="n">
-        <v>100.3</v>
+        <v>232.1</v>
       </c>
       <c r="F24" t="n">
-        <v>46.61</v>
+        <v>17.79</v>
       </c>
       <c r="G24" t="n">
-        <v>498</v>
+        <v>1190</v>
       </c>
       <c r="H24" t="n">
-        <v>86.55</v>
+        <v>89.16</v>
       </c>
       <c r="I24" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="J24" t="n">
-        <v>13.81124497991968</v>
+        <v>13.83697478991597</v>
       </c>
       <c r="K24" t="n">
-        <v>2001390.3</v>
+        <v>547626.25</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -2490,82 +2490,82 @@
         <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>21.39</v>
+        <v>11.49</v>
       </c>
       <c r="O24" t="n">
-        <v>-6.04</v>
+        <v>-7.24</v>
       </c>
       <c r="P24" t="n">
-        <v>15.35</v>
+        <v>4.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>14.26</v>
+        <v>7.58</v>
       </c>
       <c r="R24" t="n">
-        <v>0.480209251605304</v>
+        <v>1.634651038172961</v>
       </c>
       <c r="S24" t="n">
-        <v>13.37</v>
+        <v>18.91</v>
       </c>
       <c r="T24" t="n">
-        <v>1133.84</v>
+        <v>2598</v>
       </c>
       <c r="U24" t="n">
-        <v>6878</v>
+        <v>16466</v>
       </c>
       <c r="V24" t="n">
-        <v>0.9657463351226452</v>
+        <v>0.9333842720125466</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08932531891161</v>
+        <v>1.012460485661282</v>
       </c>
       <c r="X24" t="n">
-        <v>103.8574999999999</v>
+        <v>248.6650000000001</v>
       </c>
       <c r="Y24" t="n">
-        <v>92.07534081757495</v>
+        <v>229.2435144749431</v>
       </c>
       <c r="Z24" t="n">
-        <v>315601171.6</v>
+        <v>171195103.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>0050.TW</t>
+          <t>00892.TW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>元大台灣50</t>
+          <t>富邦台灣半導體</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5.459241993854328</v>
+        <v>1.730784839657892</v>
       </c>
       <c r="D25" t="n">
-        <v>5.459241993854328</v>
+        <v>1.669686395235912</v>
       </c>
       <c r="E25" t="n">
-        <v>107.25</v>
+        <v>39.18</v>
       </c>
       <c r="F25" t="n">
-        <v>23.4</v>
+        <v>28.79</v>
       </c>
       <c r="G25" t="n">
-        <v>1695</v>
+        <v>241</v>
       </c>
       <c r="H25" t="n">
-        <v>90.97</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="J25" t="n">
-        <v>13.46961651917404</v>
+        <v>15.85892116182573</v>
       </c>
       <c r="K25" t="n">
-        <v>120860361.15</v>
+        <v>4188817.75</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -2576,383 +2576,211 @@
         <v>2</v>
       </c>
       <c r="N25" t="n">
-        <v>13.94</v>
+        <v>12.37</v>
       </c>
       <c r="O25" t="n">
-        <v>-5.91</v>
+        <v>-7.43</v>
       </c>
       <c r="P25" t="n">
-        <v>8.029999999999999</v>
+        <v>4.94</v>
       </c>
       <c r="Q25" t="n">
-        <v>6.04</v>
+        <v>18.86</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>0.06109844442197954</v>
       </c>
       <c r="S25" t="n">
-        <v>4.84625</v>
+        <v>4.937</v>
       </c>
       <c r="T25" t="n">
-        <v>3824.71</v>
+        <v>510.5</v>
       </c>
       <c r="U25" t="n">
-        <v>22831</v>
+        <v>3822</v>
       </c>
       <c r="V25" t="n">
-        <v>0.9646736075195066</v>
+        <v>0.9340692088543466</v>
       </c>
       <c r="W25" t="n">
-        <v>1.025606064806033</v>
+        <v>1.012795973397309</v>
       </c>
       <c r="X25" t="n">
-        <v>111.1775000000001</v>
+        <v>41.9455</v>
       </c>
       <c r="Y25" t="n">
-        <v>104.5723145370475</v>
+        <v>38.68498792365371</v>
       </c>
       <c r="Z25" t="n">
-        <v>9291081871.5</v>
+        <v>157016984.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>0053.TW</t>
+          <t>006208.TW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>元大科技市值</t>
+          <t>富邦台50</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6.593111081669522</v>
+        <v>3.962440442809103</v>
       </c>
       <c r="D26" t="n">
-        <v>4.897736359180728</v>
+        <v>3.699014032052973</v>
       </c>
       <c r="E26" t="n">
-        <v>238.2</v>
+        <v>240.75</v>
       </c>
       <c r="F26" t="n">
-        <v>18.08</v>
+        <v>20.48</v>
       </c>
       <c r="G26" t="n">
-        <v>1190</v>
+        <v>895</v>
       </c>
       <c r="H26" t="n">
-        <v>89.16</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="J26" t="n">
-        <v>13.83697478991597</v>
+        <v>13.86703910614525</v>
       </c>
       <c r="K26" t="n">
-        <v>519863.05</v>
+        <v>3888439.2</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>2</v>
       </c>
       <c r="N26" t="n">
-        <v>11.49</v>
+        <v>11.21</v>
       </c>
       <c r="O26" t="n">
-        <v>-7.24</v>
+        <v>-6.25</v>
       </c>
       <c r="P26" t="n">
-        <v>4.25</v>
+        <v>4.960000000000001</v>
       </c>
       <c r="Q26" t="n">
-        <v>7.58</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="R26" t="n">
-        <v>1.695374722488794</v>
+        <v>0.2634264107561304</v>
       </c>
       <c r="S26" t="n">
-        <v>18.91</v>
+        <v>28.764</v>
       </c>
       <c r="T26" t="n">
-        <v>2598</v>
+        <v>1745.92</v>
       </c>
       <c r="U26" t="n">
-        <v>16466</v>
+        <v>12411</v>
       </c>
       <c r="V26" t="n">
-        <v>0.9543269230769227</v>
+        <v>0.9480119313651171</v>
       </c>
       <c r="W26" t="n">
-        <v>1.027969077319239</v>
+        <v>1.011713681591622</v>
       </c>
       <c r="X26" t="n">
-        <v>249.6000000000001</v>
+        <v>253.9525000000001</v>
       </c>
       <c r="Y26" t="n">
-        <v>231.7190324646568</v>
+        <v>237.9625820827624</v>
       </c>
       <c r="Z26" t="n">
-        <v>131397075</v>
+        <v>2113790778</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>00892.TW</t>
+          <t>009823.TWO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>富邦台灣半導體</t>
+          <t>群益S&amp;P500</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.806262935053582</v>
+        <v>0.02114569727960802</v>
       </c>
       <c r="D27" t="n">
-        <v>1.728233769791223</v>
+        <v>-0.01442997975844518</v>
       </c>
       <c r="E27" t="n">
-        <v>40.34</v>
+        <v>10.67</v>
       </c>
       <c r="F27" t="n">
-        <v>30.89</v>
+        <v>50.15</v>
       </c>
       <c r="G27" t="n">
-        <v>241</v>
+        <v>15</v>
       </c>
       <c r="H27" t="n">
-        <v>75.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I27" t="n">
-        <v>2.12</v>
+        <v>1.31</v>
       </c>
       <c r="J27" t="n">
-        <v>15.85892116182573</v>
+        <v>16.93333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>4324321.8</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
+        <v>3867003</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="n">
         <v>2</v>
       </c>
       <c r="N27" t="n">
-        <v>12.37</v>
+        <v>3.64</v>
       </c>
       <c r="O27" t="n">
-        <v>-7.43</v>
+        <v>0.45</v>
       </c>
       <c r="P27" t="n">
-        <v>4.94</v>
+        <v>4.09</v>
       </c>
       <c r="Q27" t="n">
-        <v>18.86</v>
+        <v>29.52</v>
       </c>
       <c r="R27" t="n">
-        <v>0.0780291652623597</v>
+        <v>0.0355756770380532</v>
       </c>
       <c r="S27" t="n">
-        <v>4.937</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>510.5</v>
+        <v>19.72</v>
       </c>
       <c r="U27" t="n">
-        <v>3822</v>
+        <v>254</v>
       </c>
       <c r="V27" t="n">
-        <v>0.9573761154357318</v>
+        <v>1.001360799587067</v>
       </c>
       <c r="W27" t="n">
-        <v>1.031526857622729</v>
+        <v>1.019072986442498</v>
       </c>
       <c r="X27" t="n">
-        <v>42.13600000000001</v>
+        <v>10.6555</v>
       </c>
       <c r="Y27" t="n">
-        <v>39.10707675897854</v>
+        <v>10.47030010799139</v>
       </c>
       <c r="Z27" t="n">
-        <v>166699765.46</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>006208.TW</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>富邦台50</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>4.058071677573126</v>
-      </c>
-      <c r="D28" t="n">
-        <v>3.799682014083244</v>
-      </c>
-      <c r="E28" t="n">
-        <v>245.75</v>
-      </c>
-      <c r="F28" t="n">
-        <v>21.42</v>
-      </c>
-      <c r="G28" t="n">
-        <v>895</v>
-      </c>
-      <c r="H28" t="n">
-        <v>88.48999999999999</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="J28" t="n">
-        <v>13.86703910614525</v>
-      </c>
-      <c r="K28" t="n">
-        <v>3601859.9</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="M28" t="n">
-        <v>2</v>
-      </c>
-      <c r="N28" t="n">
-        <v>11.21</v>
-      </c>
-      <c r="O28" t="n">
-        <v>-6.25</v>
-      </c>
-      <c r="P28" t="n">
-        <v>4.960000000000001</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0.2583896634898819</v>
-      </c>
-      <c r="S28" t="n">
-        <v>28.764</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1745.92</v>
-      </c>
-      <c r="U28" t="n">
-        <v>12411</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0.9649553352311766</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.024491850732192</v>
-      </c>
-      <c r="X28" t="n">
-        <v>254.6750000000001</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>239.8750168919016</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1167621162</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>009823.TWO</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>群益S&amp;P500</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>0.02809527739714124</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.006969103206378779</v>
-      </c>
-      <c r="E29" t="n">
-        <v>10.74</v>
-      </c>
-      <c r="F29" t="n">
-        <v>64.11</v>
-      </c>
-      <c r="G29" t="n">
-        <v>15</v>
-      </c>
-      <c r="H29" t="n">
-        <v>100</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="J29" t="n">
-        <v>16.93333333333333</v>
-      </c>
-      <c r="K29" t="n">
-        <v>3871837.65</v>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="n">
-        <v>2</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="P29" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>29.52</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0.02112617419076246</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>19.72</v>
-      </c>
-      <c r="U29" t="n">
-        <v>254</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.009066566449006</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.02931795635844</v>
-      </c>
-      <c r="X29" t="n">
-        <v>10.6435</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>10.43409369636995</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>35897086.02</v>
+        <v>29800317.69</v>
       </c>
     </row>
   </sheetData>
